--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -83,10 +83,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -462,8 +471,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:M34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -1051,6 +1060,1581 @@
       </c>
       <c r="M9" s="2" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4400429367</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>HR -Data Scientist</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Renton, WA</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:56 UTC</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/hr-data-scientist-at-tata-consultancy-services-4400429367?refId=vJILgNySaXYUQknbyaKZZQ%3D%3D&amp;trackingId=7cZ0KYh8Sv5%2Fh6%2FG86%2BLug%3D%3D&amp;position=5&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-tata-consultancy-services-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-tata-consultancy-services-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4390814627</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Data Analyst Intern</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Barcelona, Catalonia, Spain</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:19 UTC</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>https://es.linkedin.com/jobs/view/data-analyst-intern-at-criteo-4390814627?refId=PCZWvfzZIzNkx6giU9jTsA%3D%3D&amp;trackingId=T%2FMog6vtgG8P3ihAU9b1uQ%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-criteo-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-criteo-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4402983364</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>ENGIE Belgium</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Internship: Algorithmic trading strategies (hydropower)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Brussels, Brussels Region, Belgium</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:09 UTC</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402983364?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=zV4sJQyNyQg%2FS%2BYm6Ba9Eg%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4390725142</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Boston Consulting Group (BCG)</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Forward Deployed AI Engineer, Internship, United Kingdom - BCG X</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:24 UTC</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/forward-deployed-ai-engineer-internship-united-kingdom-bcg-x-at-boston-consulting-group-bcg-4390725142?refId=YHAZO5vAx9Qtg1RXMma%2F%2BA%3D%3D&amp;trackingId=E8kiSHzcdYe%2FH6s%2FCkGtMw%3D%3D&amp;position=7&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4400428064</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Fanatics</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:16 UTC</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/data-scientist-at-fanatics-4400428064?refId=SNMwEp9%2FBozAkX4FBnhJwQ%3D%3D&amp;trackingId=cAX0aKWV%2FBX1fvQzm%2FkEMg%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-fanatics-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-fanatics-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4390730090</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Boston Consulting Group (BCG)</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Forward Deployed AI Scientist, Internship, United Kingdom - BCG X</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:57 UTC</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/forward-deployed-ai-scientist-internship-united-kingdom-bcg-x-at-boston-consulting-group-bcg-4390730090?refId=YHAZO5vAx9Qtg1RXMma%2F%2BA%3D%3D&amp;trackingId=m50MzwjbYzUmAv7nJVAKgA%3D%3D&amp;position=5&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4402138096</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Kelly Tutors</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Research Intern (3-5hrs/week, flexible)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:40 UTC</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/research-intern-3-5hrs-week-flexible-at-kelly-tutors-4402138096?refId=HmOS2YEHUH3GOVent1txqw%3D%3D&amp;trackingId=3XBXMUoBdiHeRL4qw%2B2qRw%3D%3D&amp;position=3&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-kelly-tutors-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-kelly-tutors-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4378557045</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Fund for Public Health in NYC</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:13 UTC</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/data-scientist-at-fund-for-public-health-in-nyc-4378557045?refId=JsndNRa0tnfF7dsuxv62wA%3D%3D&amp;trackingId=Pmgt6JCxYmQun5Uv6%2BLbiQ%3D%3D&amp;position=4&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-fund-for-public-health-in-nyc-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-fund-for-public-health-in-nyc-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4402977457</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>ENGIE Belgium</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Internship: Algorithmic trading strategies (hydropower)</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Brussels, Brussels Region, Belgium</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:09 UTC</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402977457?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=gL9sbQh%2FaLMmzvXjuO71WQ%3D%3D&amp;position=3&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4371210537</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Gildan</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Intern, ERP GenAI</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:23 UTC</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/jobs/view/intern-erp-genai-at-gildan-4371210537?refId=jteS%2Ft3Cmc2XLVMFToCpKw%3D%3D&amp;trackingId=OQGg%2Bob2m9u4kkbRcgWoUw%3D%3D&amp;position=4&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-gildan-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-gildan-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4402974624</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>ENGIE Belgium</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Internship: Algorithmic trading strategies (hydropower)</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Uccle, Brussels Region, Belgium</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:09 UTC</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402974624?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=RJfkVsuYxv4DqyEhPJ367g%3D%3D&amp;position=2&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4402174633</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Cloudera</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>AI Enablement Intern (Ireland Based)</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Greater Dublin</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 18:24 UTC</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>https://ie.linkedin.com/jobs/view/ai-enablement-intern-ireland-based-at-cloudera-4402174633?refId=d9iDz5spYJk0nIor701k5g%3D%3D&amp;trackingId=6OZvFiMQ12VqIzY6EqUe7A%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-cloudera-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-cloudera-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4403115250</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Zoox</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>PhD Research Intern, Mapping Software</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Foster City, CA</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 19:55 UTC</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/phd-research-intern-mapping-software-at-zoox-4403115250?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=67WsHxTIXiO%2ByWr0OYU7ug%3D%3D&amp;position=10&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4379373115</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Woven by Toyota</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Applied Scientist, Computer Vision and Generative Models, Vision AI (Internship)</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo, Japan</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:55 UTC</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>https://jp.linkedin.com/jobs/view/applied-scientist-computer-vision-and-generative-models-vision-ai-internship-at-woven-by-toyota-4379373115?refId=4q6ISAXJ%2BcfZsJD688QZWg%3D%3D&amp;trackingId=pUnO9OuzZx4G6BOukom%2FQQ%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-woven-by-toyota-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-woven-by-toyota-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4325103488</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Binance Accelerator Program - DevOps (Artificial Intelligence)</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Hong Kong, Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:13 UTC</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>https://hk.linkedin.com/jobs/view/binance-accelerator-program-devops-artificial-intelligence-at-binance-4325103488?refId=KzaD5RMOfYQEZyaw6UmcpQ%3D%3D&amp;trackingId=8R4okHiG3RYyjThXHAqxIQ%3D%3D&amp;position=2&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-binance-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-binance-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4400563251</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Aylo</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Sr. Full-Stack Data Scientist - Data Services</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Greater Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:01 UTC</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/jobs/view/sr-full-stack-data-scientist-data-services-at-aylo-4400563251?refId=3X2hsLwn0XF5%2BC4ABneEzA%3D%3D&amp;trackingId=aJHp5psMKfAaMJdxBAz5Hw%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-aylo-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-aylo-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4400403670</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Schneider Electric</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Internship in Global AI Sales Enablement &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Warsaw, Mazowieckie, Poland</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 11:43 UTC</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>https://pl.linkedin.com/jobs/view/internship-in-global-ai-sales-enablement-analytics-at-schneider-electric-4400403670?refId=0j6PfgagLJw81v3dQ49jXQ%3D%3D&amp;trackingId=ErR9yiUH1tcny4hRKbXl8A%3D%3D&amp;position=4&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-schneider-electric-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-schneider-electric-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4297755027</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>PhD GenAI Research Scientist Intern</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 10:31 UTC</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/phd-genai-research-scientist-intern-at-databricks-4297755027?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=UXoh9K97xsqO%2FzDhCy7Uug%3D%3D&amp;position=8&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-databricks-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-databricks-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4401843829</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Tiger Brokers Singapore</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Quantitative Investment Analyst Intern</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Singapore, Singapore</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 06:09 UTC</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/quantitative-investment-analyst-intern-at-tiger-brokers-singapore-4401843829?refId=LJ4PwcXqLhd1gtOBe9ZVig%3D%3D&amp;trackingId=oxh8Ol2m1QKvqfrvl10UqA%3D%3D&amp;position=5&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-tiger-brokers-singapore-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-tiger-brokers-singapore-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4400148847</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Boomlet</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Data Analyst Intern</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Mumbai, Maharashtra, India</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 05:24 UTC</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-boomlet-4400148847?refId=vAgiKqchg4pd6EgGGQ%2FF%2FA%3D%3D&amp;trackingId=IoHiSd1L28nXXarEd4gYfw%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boomlet-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boomlet-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4401844394</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>On-us</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>AI Business Analyst Summer Intern</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Hong Kong, Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 04:56 UTC</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>https://hk.linkedin.com/jobs/view/ai-business-analyst-summer-intern-at-on-us-4401844394?refId=lslydLUu5l8kXOktysXYaw%3D%3D&amp;trackingId=BQ%2BoYgH5QtZKBWGZQgBfNQ%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-on-us-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-on-us-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4401837715</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Pathos Consultancy</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Quantitative Research &amp; Development Internships</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Hong Kong, Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 03:48 UTC</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>https://hk.linkedin.com/jobs/view/quantitative-research-development-internships-at-pathos-consultancy-4401837715?refId=KzaD5RMOfYQEZyaw6UmcpQ%3D%3D&amp;trackingId=eIGVr2dDtK%2F1o37C90xRoQ%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-pathos-consultancy-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-pathos-consultancy-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4402662606</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>PhD Machine Learning Engineer, Intern</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 02:23 UTC</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/phd-machine-learning-engineer-intern-at-stripe-4402662606?refId=vJILgNySaXYUQknbyaKZZQ%3D%3D&amp;trackingId=NDMzaPfHMoCKo5uxI3THcw%3D%3D&amp;position=4&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-stripe-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-stripe-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4402953925</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Skycliff IT</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Research Intern</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Dubai, Dubai, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Middle_East</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 00:00 UTC</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/research-intern-at-skycliff-it-4402953925?refId=f%2BmSR6Ncm83dISKgoQTrbw%3D%3D&amp;trackingId=CdPOXElDD3wJKKeBZSdWsw%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>linkedin_4402617206</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:37</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>PhD Machine Learning Engineer, Intern</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-15 20:25 UTC</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/phd-machine-learning-engineer-intern-at-stripe-4402617206?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=yAc4U29LYJcrlQSUWWcubA%3D%3D&amp;position=4&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-stripe-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-stripe-2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
@@ -1061,6 +2645,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -83,10 +83,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -471,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -557,508 +566,508 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>linkedin_4401809501</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>2026-04-15 22:19 UTC</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/research-intern-at-skycliff-it-4401809501?refId=HHi6SaK1fggu3E9dI3MtVg%3D%3D&amp;trackingId=r33pSo29lHStfk9FH82pyw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="M2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>linkedin_4402568578</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Webs X UM</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>2026-04-15 19:20 UTC</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-webs-x-um-4402568578?refId=g89JM6cY8EFeoLk6JL5tVg%3D%3D&amp;trackingId=uFZVJJX7SSI0XCPFIrLqmA%3D%3D&amp;position=19&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-webs-x-um-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-webs-x-um-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr"/>
+      <c r="M3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>linkedin_4399996740</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>SUN PHARMA</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Becario</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Mexico City, Mexico</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>2026-04-15 17:59 UTC</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>https://mx.linkedin.com/jobs/view/becario-at-sun-pharma-4399996740?refId=g89JM6cY8EFeoLk6JL5tVg%3D%3D&amp;trackingId=sZ0Fkcf4RHuIpzXu4mJRNg%3D%3D&amp;position=22&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-sun-pharma-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-sun-pharma-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>linkedin_4399975959</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>LS Direct</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Data Analytics Intern</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Suffern, NY</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>2026-04-15 14:26 UTC</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-analytics-intern-at-ls-direct-4399975959?refId=pg0ll3e89fatVyUznLcdpw%3D%3D&amp;trackingId=5b41IoyQfIfx3Tu42domiQ%3D%3D&amp;position=23&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-ls-direct-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-ls-direct-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr"/>
+      <c r="M5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>linkedin_4370546718</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Clarivate</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Lead Data Scientist</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Barcelona, Catalonia, Spain</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>2026-04-15 12:16 UTC</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/lead-data-scientist-at-clarivate-4370546718?refId=FyyqQfduMQ8KZ7B5LeF0UQ%3D%3D&amp;trackingId=1i1kXdbV7SMunyFTiSJHJg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-clarivate-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-clarivate-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>linkedin_4389810164</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Vitality</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Senior Data Scientist - 12 Month FTC</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>2026-04-15 09:39 UTC</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/senior-data-scientist-12-month-ftc-at-vitality-4389810164?refId=FPz%2BrPoaQeqgXBm%2FfOzGGA%3D%3D&amp;trackingId=yVNh55t2X2xocDT4i6HDqQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-vitality-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-vitality-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>linkedin_4399952059</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>traide AI</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>AI Associate (f/m/x) (B2B SaaS Startup) - Intern/Working Student</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>2026-04-15 07:04 UTC</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/ai-associate-f-m-x-b2b-saas-startup-intern-working-student-at-traide-ai-4399952059?refId=x0uIkl175n0hipT17L%2FGRw%3D%3D&amp;trackingId=8kdzUQgW%2B7rCk2pO2oIErg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-traide-ai-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-traide-ai-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>linkedin_4399933254</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Briink</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Growth Intern (Merantix AI Campus)</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>2026-04-15 05:03 UTC</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/growth-intern-merantix-ai-campus-at-briink-4399933254?refId=x0uIkl175n0hipT17L%2FGRw%3D%3D&amp;trackingId=qEKtyJNA03Kbr6AYDlhsBw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-briink-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-briink-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -2634,6 +2643,447 @@
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>linkedin_4403183407</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-17 08:58</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Hardware FYI</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>Robotics - Applied Scientist II Intern / Co-op - 2026 (Robotics, Manipulation, Perception, Motion Planning, Autonomous Mobile Robots, Computer Vision, Machine Learning, Controls, and more)</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-17 04:31 UTC</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J35" s="10" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/robotics-applied-scientist-ii-intern-co-op-2026-robotics-manipulation-perception-motion-planning-autonomous-mobile-robots-computer-vision-machine-learning-controls-and-more-at-hardware-fyi-4403183407?refId=s5WxXRPJ8QU7G2WPi2yNiw%3D%3D&amp;trackingId=rjd%2F8qdM5kQMmADtGJgSSw%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-hardware-fyi-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-hardware-fyi-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="M35" s="8" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>linkedin_4403153262</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-17 08:58</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Generali Malaysia</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>Intern, IT (AI Engineering)</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>Federal Territory of Kuala Lumpur, Malaysia</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-17 00:47 UTC</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>https://my.linkedin.com/jobs/view/intern-it-ai-engineering-at-generali-malaysia-4403153262?refId=h4J9hFjDRjjPW7bUqRcUZQ%3D%3D&amp;trackingId=WmqITEtGX486sbNH6b%2BYmA%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-generali-malaysia-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="L36" s="8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-generali-malaysia-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="M36" s="8" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>linkedin_4402311007</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-17 08:58</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>SAP iXp Intern - Customer Success Engineering, Operations &amp; AI Enablement [Boston]</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Burlington, MA</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:40 UTC</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/sap-ixp-intern-%C2%A0customer-success-engineering-operations-ai-enablement-boston-at-sap-4402311007?refId=ofb0jzd8xWUoUtvr7A%2BwXQ%3D%3D&amp;trackingId=S%2Fo4FvRdeOcn00Jo5DVUBw%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sap-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="L37" s="8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sap-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="M37" s="8" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>linkedin_4403154707</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-17 08:58</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Zoox</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern, Perception Data</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Foster City, CA</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:21 UTC</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/software-engineer-intern-perception-data-at-zoox-4403154707?refId=ON4L5FUhksKAgylRRsNllQ%3D%3D&amp;trackingId=1%2F3OkqP%2Bu0PqHp9bXnlS0A%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="L38" s="8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="M38" s="8" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>linkedin_4402947451</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-17 08:58</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Rubrik</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>India Benefits &amp; AI Operations Intern</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-16 11:40 UTC</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/india-benefits-ai-operations-intern-at-rubrik-4402947451?refId=9u2uyUYzyMZimaTtDELDWg%3D%3D&amp;trackingId=BjOmyeYm6McmUpzLwcES9g%3D%3D&amp;position=5&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K39" s="8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-rubrik-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-rubrik-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>linkedin_4390354006</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-17 08:58</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Lila Sciences</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>Intern, Next Gen AI Robotics</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Cambridge, MA</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-16 10:58 UTC</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/intern-next-gen-ai-robotics-at-lila-sciences-4390354006?refId=ZoXJQXesL%2FE%2B5EAGGzWfiA%3D%3D&amp;trackingId=FmSMwWhyyIaC52NsDwOCtw%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-lila-sciences-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="L40" s="8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-lila-sciences-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="M40" s="8" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow_ai-venture-development-tech-intern-berlin-100382</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-17 08:58</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Zeeg</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>AI &amp; Venture Development Tech Intern (w/m/d)</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-16 10:30 UTC</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J41" s="10" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/zeeg/ai-venture-development-tech-intern-berlin-100382</t>
+        </is>
+      </c>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zeeg-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="L41" s="8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zeeg-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="M41" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2670,6 +3120,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -83,10 +83,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -480,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -566,2083 +575,2083 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>linkedin_4401809501</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>2026-04-15 22:19 UTC</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/research-intern-at-skycliff-it-4401809501?refId=HHi6SaK1fggu3E9dI3MtVg%3D%3D&amp;trackingId=r33pSo29lHStfk9FH82pyw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K2" s="8" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="L2" s="8" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr"/>
+      <c r="M2" s="8" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>linkedin_4402568578</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Webs X UM</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>2026-04-15 19:20 UTC</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-webs-x-um-4402568578?refId=g89JM6cY8EFeoLk6JL5tVg%3D%3D&amp;trackingId=uFZVJJX7SSI0XCPFIrLqmA%3D%3D&amp;position=19&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-webs-x-um-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="L3" s="8" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-webs-x-um-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr"/>
+      <c r="M3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>linkedin_4399996740</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>SUN PHARMA</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Becario</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Mexico City, Mexico</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>2026-04-15 17:59 UTC</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
         <is>
           <t>https://mx.linkedin.com/jobs/view/becario-at-sun-pharma-4399996740?refId=g89JM6cY8EFeoLk6JL5tVg%3D%3D&amp;trackingId=sZ0Fkcf4RHuIpzXu4mJRNg%3D%3D&amp;position=22&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-sun-pharma-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-sun-pharma-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr"/>
+      <c r="M4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>linkedin_4399975959</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>LS Direct</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Data Analytics Intern</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Suffern, NY</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>2026-04-15 14:26 UTC</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-analytics-intern-at-ls-direct-4399975959?refId=pg0ll3e89fatVyUznLcdpw%3D%3D&amp;trackingId=5b41IoyQfIfx3Tu42domiQ%3D%3D&amp;position=23&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-ls-direct-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L5" s="8" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-ls-direct-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>linkedin_4370546718</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Clarivate</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Lead Data Scientist</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>Barcelona, Catalonia, Spain</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>2026-04-15 12:16 UTC</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/lead-data-scientist-at-clarivate-4370546718?refId=FyyqQfduMQ8KZ7B5LeF0UQ%3D%3D&amp;trackingId=1i1kXdbV7SMunyFTiSJHJg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-clarivate-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="L6" s="8" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-clarivate-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr"/>
+      <c r="M6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>linkedin_4389810164</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Vitality</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>Senior Data Scientist - 12 Month FTC</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>2026-04-15 09:39 UTC</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/senior-data-scientist-12-month-ftc-at-vitality-4389810164?refId=FPz%2BrPoaQeqgXBm%2FfOzGGA%3D%3D&amp;trackingId=yVNh55t2X2xocDT4i6HDqQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-vitality-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="L7" s="8" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-vitality-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr"/>
+      <c r="M7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>linkedin_4399952059</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>traide AI</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>AI Associate (f/m/x) (B2B SaaS Startup) - Intern/Working Student</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>2026-04-15 07:04 UTC</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/ai-associate-f-m-x-b2b-saas-startup-intern-working-student-at-traide-ai-4399952059?refId=x0uIkl175n0hipT17L%2FGRw%3D%3D&amp;trackingId=8kdzUQgW%2B7rCk2pO2oIErg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-traide-ai-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="L8" s="8" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-traide-ai-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M8" s="5" t="inlineStr"/>
+      <c r="M8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>linkedin_4399933254</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Briink</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>Growth Intern (Merantix AI Campus)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>2026-04-15 05:03 UTC</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/growth-intern-merantix-ai-campus-at-briink-4399933254?refId=x0uIkl175n0hipT17L%2FGRw%3D%3D&amp;trackingId=qEKtyJNA03Kbr6AYDlhsBw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-briink-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="L9" s="8" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-briink-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr"/>
+      <c r="M9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>linkedin_4400429367</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>Tata Consultancy Services</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>HR -Data Scientist</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>Renton, WA</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 16:56 UTC</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/hr-data-scientist-at-tata-consultancy-services-4400429367?refId=vJILgNySaXYUQknbyaKZZQ%3D%3D&amp;trackingId=7cZ0KYh8Sv5%2Fh6%2FG86%2BLug%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-tata-consultancy-services-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="L10" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-tata-consultancy-services-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr"/>
+      <c r="M10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>linkedin_4390814627</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>Criteo</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>Barcelona, Catalonia, Spain</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 12:19 UTC</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/data-analyst-intern-at-criteo-4390814627?refId=PCZWvfzZIzNkx6giU9jTsA%3D%3D&amp;trackingId=T%2FMog6vtgG8P3ihAU9b1uQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K11" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-criteo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="L11" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-criteo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr"/>
+      <c r="M11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>linkedin_4402983364</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>Brussels, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402983364?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=zV4sJQyNyQg%2FS%2BYm6Ba9Eg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="L12" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr"/>
+      <c r="M12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>linkedin_4390725142</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>Boston Consulting Group (BCG)</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>Forward Deployed AI Engineer, Internship, United Kingdom - BCG X</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 16:24 UTC</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/forward-deployed-ai-engineer-internship-united-kingdom-bcg-x-at-boston-consulting-group-bcg-4390725142?refId=YHAZO5vAx9Qtg1RXMma%2F%2BA%3D%3D&amp;trackingId=E8kiSHzcdYe%2FH6s%2FCkGtMw%3D%3D&amp;position=7&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K13" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="L13" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M13" s="5" t="inlineStr"/>
+      <c r="M13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>linkedin_4400428064</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Fanatics</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 16:16 UTC</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/data-scientist-at-fanatics-4400428064?refId=SNMwEp9%2FBozAkX4FBnhJwQ%3D%3D&amp;trackingId=cAX0aKWV%2FBX1fvQzm%2FkEMg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-fanatics-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="L14" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-fanatics-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M14" s="5" t="inlineStr"/>
+      <c r="M14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>linkedin_4390730090</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>Boston Consulting Group (BCG)</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>Forward Deployed AI Scientist, Internship, United Kingdom - BCG X</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 13:57 UTC</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/forward-deployed-ai-scientist-internship-united-kingdom-bcg-x-at-boston-consulting-group-bcg-4390730090?refId=YHAZO5vAx9Qtg1RXMma%2F%2BA%3D%3D&amp;trackingId=m50MzwjbYzUmAv7nJVAKgA%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="K15" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="L15" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M15" s="5" t="inlineStr"/>
+      <c r="M15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>linkedin_4402138096</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>Kelly Tutors</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>Research Intern (3-5hrs/week, flexible)</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 14:40 UTC</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/research-intern-3-5hrs-week-flexible-at-kelly-tutors-4402138096?refId=HmOS2YEHUH3GOVent1txqw%3D%3D&amp;trackingId=3XBXMUoBdiHeRL4qw%2B2qRw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K16" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-kelly-tutors-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="L16" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-kelly-tutors-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr"/>
+      <c r="M16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>linkedin_4378557045</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>Fund for Public Health in NYC</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 16:13 UTC</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-scientist-at-fund-for-public-health-in-nyc-4378557045?refId=JsndNRa0tnfF7dsuxv62wA%3D%3D&amp;trackingId=Pmgt6JCxYmQun5Uv6%2BLbiQ%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K17" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-fund-for-public-health-in-nyc-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="L17" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-fund-for-public-health-in-nyc-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M17" s="5" t="inlineStr"/>
+      <c r="M17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>linkedin_4402977457</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>Brussels, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402977457?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=gL9sbQh%2FaLMmzvXjuO71WQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="K18" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="L18" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M18" s="5" t="inlineStr"/>
+      <c r="M18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>linkedin_4371210537</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>Gildan</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>Intern, ERP GenAI</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 15:23 UTC</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/intern-erp-genai-at-gildan-4371210537?refId=jteS%2Ft3Cmc2XLVMFToCpKw%3D%3D&amp;trackingId=OQGg%2Bob2m9u4kkbRcgWoUw%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="K19" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-gildan-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="L19" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-gildan-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr"/>
+      <c r="M19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>linkedin_4402974624</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>Uccle, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402974624?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=RJfkVsuYxv4DqyEhPJ367g%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="K20" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="L20" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M20" s="5" t="inlineStr"/>
+      <c r="M20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>linkedin_4402174633</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>Cloudera</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>AI Enablement Intern (Ireland Based)</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>Greater Dublin</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 18:24 UTC</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
         <is>
           <t>https://ie.linkedin.com/jobs/view/ai-enablement-intern-ireland-based-at-cloudera-4402174633?refId=d9iDz5spYJk0nIor701k5g%3D%3D&amp;trackingId=6OZvFiMQ12VqIzY6EqUe7A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K21" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-cloudera-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L21" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-cloudera-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr"/>
+      <c r="M21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>linkedin_4403115250</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>PhD Research Intern, Mapping Software</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 19:55 UTC</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-mapping-software-at-zoox-4403115250?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=67WsHxTIXiO%2ByWr0OYU7ug%3D%3D&amp;position=10&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="K22" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="L22" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M22" s="5" t="inlineStr"/>
+      <c r="M22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>linkedin_4379373115</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>Woven by Toyota</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>Applied Scientist, Computer Vision and Generative Models, Vision AI (Internship)</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>Tokyo, Japan</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 14:55 UTC</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
         <is>
           <t>https://jp.linkedin.com/jobs/view/applied-scientist-computer-vision-and-generative-models-vision-ai-internship-at-woven-by-toyota-4379373115?refId=4q6ISAXJ%2BcfZsJD688QZWg%3D%3D&amp;trackingId=pUnO9OuzZx4G6BOukom%2FQQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="K23" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-woven-by-toyota-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="L23" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-woven-by-toyota-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr"/>
+      <c r="M23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>linkedin_4325103488</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>Binance</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>Binance Accelerator Program - DevOps (Artificial Intelligence)</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 12:13 UTC</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/binance-accelerator-program-devops-artificial-intelligence-at-binance-4325103488?refId=KzaD5RMOfYQEZyaw6UmcpQ%3D%3D&amp;trackingId=8R4okHiG3RYyjThXHAqxIQ%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="K24" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-binance-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L24" s="5" t="inlineStr">
+      <c r="L24" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-binance-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M24" s="5" t="inlineStr"/>
+      <c r="M24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>linkedin_4400563251</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>Aylo</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>Sr. Full-Stack Data Scientist - Data Services</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>Greater Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 12:01 UTC</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/sr-full-stack-data-scientist-data-services-at-aylo-4400563251?refId=3X2hsLwn0XF5%2BC4ABneEzA%3D%3D&amp;trackingId=aJHp5psMKfAaMJdxBAz5Hw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K25" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-aylo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="L25" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-aylo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M25" s="5" t="inlineStr"/>
+      <c r="M25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>linkedin_4400403670</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>Schneider Electric</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>Internship in Global AI Sales Enablement &amp; Analytics</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>Warsaw, Mazowieckie, Poland</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 11:43 UTC</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
         <is>
           <t>https://pl.linkedin.com/jobs/view/internship-in-global-ai-sales-enablement-analytics-at-schneider-electric-4400403670?refId=0j6PfgagLJw81v3dQ49jXQ%3D%3D&amp;trackingId=ErR9yiUH1tcny4hRKbXl8A%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="K26" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-schneider-electric-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="L26" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-schneider-electric-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M26" s="5" t="inlineStr"/>
+      <c r="M26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>linkedin_4297755027</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>Databricks</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>PhD GenAI Research Scientist Intern</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 10:31 UTC</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-genai-research-scientist-intern-at-databricks-4297755027?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=UXoh9K97xsqO%2FzDhCy7Uug%3D%3D&amp;position=8&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="K27" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-databricks-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="L27" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-databricks-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M27" s="5" t="inlineStr"/>
+      <c r="M27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>linkedin_4401843829</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>Tiger Brokers Singapore</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>Quantitative Investment Analyst Intern</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 06:09 UTC</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/quantitative-investment-analyst-intern-at-tiger-brokers-singapore-4401843829?refId=LJ4PwcXqLhd1gtOBe9ZVig%3D%3D&amp;trackingId=oxh8Ol2m1QKvqfrvl10UqA%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="K28" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-tiger-brokers-singapore-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L28" s="5" t="inlineStr">
+      <c r="L28" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-tiger-brokers-singapore-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M28" s="5" t="inlineStr"/>
+      <c r="M28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>linkedin_4400148847</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>Boomlet</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>Mumbai, Maharashtra, India</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 05:24 UTC</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-boomlet-4400148847?refId=vAgiKqchg4pd6EgGGQ%2FF%2FA%3D%3D&amp;trackingId=IoHiSd1L28nXXarEd4gYfw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K29" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boomlet-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="L29" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boomlet-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr"/>
+      <c r="M29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>linkedin_4401844394</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>On-us</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>AI Business Analyst Summer Intern</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 04:56 UTC</t>
         </is>
       </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J30" s="7" t="inlineStr">
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J30" s="10" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/ai-business-analyst-summer-intern-at-on-us-4401844394?refId=lslydLUu5l8kXOktysXYaw%3D%3D&amp;trackingId=BQ%2BoYgH5QtZKBWGZQgBfNQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="K30" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-on-us-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L30" s="5" t="inlineStr">
+      <c r="L30" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-on-us-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M30" s="5" t="inlineStr"/>
+      <c r="M30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>linkedin_4401837715</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>Pathos Consultancy</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>Quantitative Research &amp; Development Internships</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 03:48 UTC</t>
         </is>
       </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J31" s="10" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/quantitative-research-development-internships-at-pathos-consultancy-4401837715?refId=KzaD5RMOfYQEZyaw6UmcpQ%3D%3D&amp;trackingId=eIGVr2dDtK%2F1o37C90xRoQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="K31" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-pathos-consultancy-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L31" s="5" t="inlineStr">
+      <c r="L31" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-pathos-consultancy-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M31" s="5" t="inlineStr"/>
+      <c r="M31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>linkedin_4402662606</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>Stripe</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>PhD Machine Learning Engineer, Intern</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 02:23 UTC</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J32" s="7" t="inlineStr">
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-machine-learning-engineer-intern-at-stripe-4402662606?refId=vJILgNySaXYUQknbyaKZZQ%3D%3D&amp;trackingId=NDMzaPfHMoCKo5uxI3THcw%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="K32" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L32" s="5" t="inlineStr">
+      <c r="L32" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M32" s="5" t="inlineStr"/>
+      <c r="M32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>linkedin_4402953925</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>Middle_East</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 00:00 UTC</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J33" s="7" t="inlineStr">
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J33" s="10" t="inlineStr">
         <is>
           <t>https://ae.linkedin.com/jobs/view/research-intern-at-skycliff-it-4402953925?refId=f%2BmSR6Ncm83dISKgoQTrbw%3D%3D&amp;trackingId=CdPOXElDD3wJKKeBZSdWsw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="K33" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr">
+      <c r="L33" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M33" s="5" t="inlineStr"/>
+      <c r="M33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>linkedin_4402617206</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>Stripe</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>PhD Machine Learning Engineer, Intern</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>2026-04-15 20:25 UTC</t>
         </is>
       </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J34" s="7" t="inlineStr">
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J34" s="10" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-machine-learning-engineer-intern-at-stripe-4402617206?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=yAc4U29LYJcrlQSUWWcubA%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="K34" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L34" s="5" t="inlineStr">
+      <c r="L34" s="8" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M34" s="5" t="inlineStr"/>
+      <c r="M34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -3084,6 +3093,699 @@
         </is>
       </c>
       <c r="M41" s="8" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>linkedin_4391388054</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:18</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>Mackenzie Investments</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>Fall Intern 2026 - Data Science (Toronto Office)</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>Greater Toronto Area, Canada</t>
+        </is>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>2026-04-17 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J42" s="13" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/jobs/view/fall-intern-2026-data-science-toronto-office-at-mackenzie-investments-4391388054?refId=ay8O%2Bgf7Gtfb1Rpr3XZOhg%3D%3D&amp;trackingId=O%2F%2FJTpCmUhvp4jSfNkV5bg%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K42" s="11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-mackenzie-investments-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="L42" s="11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-mackenzie-investments-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="M42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>linkedin_4390747937</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:18</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>BCG X</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>Visiting Forward Deployed AI Engineer, Internship, Germany - BCG X</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>Berlin, Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>2026-04-17 13:51 UTC</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J43" s="13" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/visiting-forward-deployed-ai-engineer-internship-germany-bcg-x-at-bcg-x-4390747937?refId=1JxxxPqdlRpkbbaCzu2YGQ%3D%3D&amp;trackingId=7x%2BVQU%2BWOh9IPaVXWJkc5g%3D%3D&amp;position=2&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K43" s="11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bcg-x-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="L43" s="11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bcg-x-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="M43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>linkedin_4402726053</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:18</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>targetjobs UK</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>Internship: AI/ML for Ionospheric TEC Modelling</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>Reigate, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>2026-04-17 14:25 UTC</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J44" s="13" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/internship-ai-ml-for-ionospheric-tec-modelling-at-targetjobs-uk-4402726053?refId=a1g6hMZsvI1y2Eje2OvLAA%3D%3D&amp;trackingId=IVJSJGE7Non8cohorDs%2F5A%3D%3D&amp;position=2&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K44" s="11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-targetjobs-uk-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="L44" s="11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-targetjobs-uk-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="M44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>linkedin_4400837114</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:18</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>Innovexis</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>Data Analyst Intern</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India</t>
+        </is>
+      </c>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>2026-04-17 13:04 UTC</t>
+        </is>
+      </c>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J45" s="13" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-innovexis-4400837114?refId=CVM89%2F3%2F%2BshqMJLc4IfFMg%3D%3D&amp;trackingId=j9WpQwI4k1ip7aRr%2Fv5Img%3D%3D&amp;position=2&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K45" s="11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-innovexis-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="L45" s="11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-innovexis-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="M45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>linkedin_4391074158</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:18</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>BMW Group</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>Intern IT Technology, Sales Volume Planning &amp; AI Support (f/m/x)</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:45 UTC</t>
+        </is>
+      </c>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J46" s="13" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/intern-it-technology-sales-volume-planning-ai-support-f-m-x-at-bmw-group-4391074158?refId=tHG5EqbLn3IDBqsSj%2FsUUg%3D%3D&amp;trackingId=OakOlgDcU0hWTRXcoLe3UA%3D%3D&amp;position=2&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K46" s="11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bmw-group-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="L46" s="11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bmw-group-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="M46" s="11" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>linkedin_4402725075</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:18</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>DARE</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>Research Intern</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>WP. Kuala Lumpur, Federal Territory of Kuala Lumpur, Malaysia</t>
+        </is>
+      </c>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>2026-04-17 14:36 UTC</t>
+        </is>
+      </c>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J47" s="13" t="inlineStr">
+        <is>
+          <t>https://my.linkedin.com/jobs/view/research-intern-at-dare-4402725075?refId=xbzZXyF6FfcYy036eklDWw%3D%3D&amp;trackingId=QRt5DhbLSINvmHia0jEWIg%3D%3D&amp;position=2&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K47" s="11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dare-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="L47" s="11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dare-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="M47" s="11" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>linkedin_4402745391</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:18</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>Huawei Technologies Research &amp; Development (UK) Ltd</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>Research Intern - Computer Vision</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>2026-04-17 18:42 UTC</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J48" s="13" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/research-intern-computer-vision-at-huawei-technologies-research-development-uk-ltd-4402745391?refId=rRtCMQFBU%2FNi7vc62x5Nhg%3D%3D&amp;trackingId=%2Bt1We%2BmKhWHyXION%2FWwQVg%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K48" s="11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-huawei-technologies-research-development-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="L48" s="11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-huawei-technologies-research-development-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="M48" s="11" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>linkedin_4402366780</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:18</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>Binance Accelerator Program - Data Scientist (LLM &amp; Trading)</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>Hong Kong, Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H49" s="11" t="inlineStr">
+        <is>
+          <t>2026-04-17 09:43 UTC</t>
+        </is>
+      </c>
+      <c r="I49" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J49" s="13" t="inlineStr">
+        <is>
+          <t>https://hk.linkedin.com/jobs/view/binance-accelerator-program-data-scientist-llm-trading-at-binance-4402366780?refId=bc%2BXeBTeIKMQJTmlLFwbZQ%3D%3D&amp;trackingId=9UuyRRCEPapWNu6VKdZC5A%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K49" s="11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-binance-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="L49" s="11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-binance-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="M49" s="11" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>linkedin_4382411039</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:18</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>Intern, APAC Data Analytics &amp; Insights (Content Analytics) -  Jul to Dec 2026</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>Singapore, Singapore</t>
+        </is>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:55 UTC</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J50" s="13" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/intern-apac-data-analytics-insights-content-analytics-jul-to-dec-2026-at-the-walt-disney-company-4382411039?refId=JBvXH2fNOamnO4WZI1Y0ew%3D%3D&amp;trackingId=Rs%2FdjczlbLYSYtCwY%2F%2FJyA%3D%3D&amp;position=7&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K50" s="11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-the-walt-disney-company-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="L50" s="11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-the-walt-disney-company-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="M50" s="11" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>linkedin_4402305263</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:18</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>SAP iXp Intern - Software Developer (Agentic AI &amp; LLM systems)</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>Montreal, Quebec, Canada</t>
+        </is>
+      </c>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:40 UTC</t>
+        </is>
+      </c>
+      <c r="I51" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J51" s="13" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/jobs/view/sap-ixp-intern-software-developer-agentic-ai-llm-systems-at-sap-4402305263?refId=zBXuSSlfFyuxcdEqyfeS8g%3D%3D&amp;trackingId=Imq%2FVHMQWkkoDZp5%2BnATSA%3D%3D&amp;position=2&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K51" s="11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sap-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="L51" s="11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sap-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="M51" s="11" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>linkedin_4400467080</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:18</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>Saama</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>Intern for AI CoE</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>2026-04-16 19:45 UTC</t>
+        </is>
+      </c>
+      <c r="I52" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J52" s="13" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/intern-for-ai-coe-at-saama-4400467080?refId=7CvDuV2%2BR%2FzyGozq4UNPPw%3D%3D&amp;trackingId=Ls9yWFAC8lVRx8bmapJfLA%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K52" s="11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-saama-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="L52" s="11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-saama-2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="M52" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3127,6 +3829,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -83,10 +83,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -489,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -575,2524 +584,2524 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>linkedin_4401809501</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="11" t="inlineStr">
         <is>
           <t>2026-04-15 22:19 UTC</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/research-intern-at-skycliff-it-4401809501?refId=HHi6SaK1fggu3E9dI3MtVg%3D%3D&amp;trackingId=r33pSo29lHStfk9FH82pyw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K2" s="8" t="inlineStr">
+      <c r="K2" s="11" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L2" s="8" t="inlineStr">
+      <c r="L2" s="11" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr"/>
+      <c r="M2" s="11" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>linkedin_4402568578</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>Webs X UM</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="11" t="inlineStr">
         <is>
           <t>2026-04-15 19:20 UTC</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-webs-x-um-4402568578?refId=g89JM6cY8EFeoLk6JL5tVg%3D%3D&amp;trackingId=uFZVJJX7SSI0XCPFIrLqmA%3D%3D&amp;position=19&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="11" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-webs-x-um-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="L3" s="11" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-webs-x-um-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr"/>
+      <c r="M3" s="11" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>linkedin_4399996740</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>SUN PHARMA</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Becario</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Mexico City, Mexico</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>2026-04-15 17:59 UTC</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J4" s="10" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t>https://mx.linkedin.com/jobs/view/becario-at-sun-pharma-4399996740?refId=g89JM6cY8EFeoLk6JL5tVg%3D%3D&amp;trackingId=sZ0Fkcf4RHuIpzXu4mJRNg%3D%3D&amp;position=22&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-sun-pharma-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="L4" s="11" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-sun-pharma-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M4" s="8" t="inlineStr"/>
+      <c r="M4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>linkedin_4399975959</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>LS Direct</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Data Analytics Intern</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Suffern, NY</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H5" s="11" t="inlineStr">
         <is>
           <t>2026-04-15 14:26 UTC</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J5" s="10" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-analytics-intern-at-ls-direct-4399975959?refId=pg0ll3e89fatVyUznLcdpw%3D%3D&amp;trackingId=5b41IoyQfIfx3Tu42domiQ%3D%3D&amp;position=23&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr">
+      <c r="K5" s="11" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-ls-direct-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L5" s="8" t="inlineStr">
+      <c r="L5" s="11" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-ls-direct-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M5" s="8" t="inlineStr"/>
+      <c r="M5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>linkedin_4370546718</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Clarivate</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Lead Data Scientist</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Barcelona, Catalonia, Spain</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>2026-04-15 12:16 UTC</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J6" s="10" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/lead-data-scientist-at-clarivate-4370546718?refId=FyyqQfduMQ8KZ7B5LeF0UQ%3D%3D&amp;trackingId=1i1kXdbV7SMunyFTiSJHJg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="11" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-clarivate-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L6" s="8" t="inlineStr">
+      <c r="L6" s="11" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-clarivate-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr"/>
+      <c r="M6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>linkedin_4389810164</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Vitality</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>Senior Data Scientist - 12 Month FTC</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H7" s="11" t="inlineStr">
         <is>
           <t>2026-04-15 09:39 UTC</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J7" s="10" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/senior-data-scientist-12-month-ftc-at-vitality-4389810164?refId=FPz%2BrPoaQeqgXBm%2FfOzGGA%3D%3D&amp;trackingId=yVNh55t2X2xocDT4i6HDqQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="K7" s="11" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-vitality-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr">
+      <c r="L7" s="11" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-vitality-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M7" s="8" t="inlineStr"/>
+      <c r="M7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>linkedin_4399952059</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>traide AI</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>AI Associate (f/m/x) (B2B SaaS Startup) - Intern/Working Student</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>2026-04-15 07:04 UTC</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/ai-associate-f-m-x-b2b-saas-startup-intern-working-student-at-traide-ai-4399952059?refId=x0uIkl175n0hipT17L%2FGRw%3D%3D&amp;trackingId=8kdzUQgW%2B7rCk2pO2oIErg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K8" s="8" t="inlineStr">
+      <c r="K8" s="11" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-traide-ai-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L8" s="8" t="inlineStr">
+      <c r="L8" s="11" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-traide-ai-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M8" s="8" t="inlineStr"/>
+      <c r="M8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>linkedin_4399933254</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Briink</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Growth Intern (Merantix AI Campus)</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>2026-04-15 05:03 UTC</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J9" s="10" t="inlineStr">
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/growth-intern-merantix-ai-campus-at-briink-4399933254?refId=x0uIkl175n0hipT17L%2FGRw%3D%3D&amp;trackingId=qEKtyJNA03Kbr6AYDlhsBw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K9" s="11" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-briink-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L9" s="8" t="inlineStr">
+      <c r="L9" s="11" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-briink-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr"/>
+      <c r="M9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>linkedin_4400429367</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Tata Consultancy Services</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>HR -Data Scientist</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Renton, WA</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 16:56 UTC</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="inlineStr">
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/hr-data-scientist-at-tata-consultancy-services-4400429367?refId=vJILgNySaXYUQknbyaKZZQ%3D%3D&amp;trackingId=7cZ0KYh8Sv5%2Fh6%2FG86%2BLug%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-tata-consultancy-services-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L10" s="8" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-tata-consultancy-services-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M10" s="8" t="inlineStr"/>
+      <c r="M10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>linkedin_4390814627</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Criteo</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Barcelona, Catalonia, Spain</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 12:19 UTC</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J11" s="10" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/data-analyst-intern-at-criteo-4390814627?refId=PCZWvfzZIzNkx6giU9jTsA%3D%3D&amp;trackingId=T%2FMog6vtgG8P3ihAU9b1uQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="K11" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-criteo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L11" s="8" t="inlineStr">
+      <c r="L11" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-criteo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M11" s="8" t="inlineStr"/>
+      <c r="M11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>linkedin_4402983364</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Brussels, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J12" s="10" t="inlineStr">
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402983364?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=zV4sJQyNyQg%2FS%2BYm6Ba9Eg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K12" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L12" s="8" t="inlineStr">
+      <c r="L12" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr"/>
+      <c r="M12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>linkedin_4390725142</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Boston Consulting Group (BCG)</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Forward Deployed AI Engineer, Internship, United Kingdom - BCG X</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H13" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 16:24 UTC</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J13" s="10" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/forward-deployed-ai-engineer-internship-united-kingdom-bcg-x-at-boston-consulting-group-bcg-4390725142?refId=YHAZO5vAx9Qtg1RXMma%2F%2BA%3D%3D&amp;trackingId=E8kiSHzcdYe%2FH6s%2FCkGtMw%3D%3D&amp;position=7&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="K13" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L13" s="8" t="inlineStr">
+      <c r="L13" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M13" s="8" t="inlineStr"/>
+      <c r="M13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>linkedin_4400428064</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Fanatics</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 16:16 UTC</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J14" s="10" t="inlineStr">
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/data-scientist-at-fanatics-4400428064?refId=SNMwEp9%2FBozAkX4FBnhJwQ%3D%3D&amp;trackingId=cAX0aKWV%2FBX1fvQzm%2FkEMg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K14" s="8" t="inlineStr">
+      <c r="K14" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-fanatics-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr">
+      <c r="L14" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-fanatics-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr"/>
+      <c r="M14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>linkedin_4390730090</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Boston Consulting Group (BCG)</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>Forward Deployed AI Scientist, Internship, United Kingdom - BCG X</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 13:57 UTC</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J15" s="10" t="inlineStr">
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J15" s="13" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/forward-deployed-ai-scientist-internship-united-kingdom-bcg-x-at-boston-consulting-group-bcg-4390730090?refId=YHAZO5vAx9Qtg1RXMma%2F%2BA%3D%3D&amp;trackingId=m50MzwjbYzUmAv7nJVAKgA%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="K15" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L15" s="8" t="inlineStr">
+      <c r="L15" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr"/>
+      <c r="M15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>linkedin_4402138096</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Kelly Tutors</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Research Intern (3-5hrs/week, flexible)</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 14:40 UTC</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J16" s="10" t="inlineStr">
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/research-intern-3-5hrs-week-flexible-at-kelly-tutors-4402138096?refId=HmOS2YEHUH3GOVent1txqw%3D%3D&amp;trackingId=3XBXMUoBdiHeRL4qw%2B2qRw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K16" s="8" t="inlineStr">
+      <c r="K16" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-kelly-tutors-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L16" s="8" t="inlineStr">
+      <c r="L16" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-kelly-tutors-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M16" s="8" t="inlineStr"/>
+      <c r="M16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>linkedin_4378557045</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Fund for Public Health in NYC</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 16:13 UTC</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J17" s="10" t="inlineStr">
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J17" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-scientist-at-fund-for-public-health-in-nyc-4378557045?refId=JsndNRa0tnfF7dsuxv62wA%3D%3D&amp;trackingId=Pmgt6JCxYmQun5Uv6%2BLbiQ%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K17" s="8" t="inlineStr">
+      <c r="K17" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-fund-for-public-health-in-nyc-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L17" s="8" t="inlineStr">
+      <c r="L17" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-fund-for-public-health-in-nyc-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr"/>
+      <c r="M17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>linkedin_4402977457</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>Brussels, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J18" s="10" t="inlineStr">
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402977457?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=gL9sbQh%2FaLMmzvXjuO71WQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="K18" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="L18" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M18" s="8" t="inlineStr"/>
+      <c r="M18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>linkedin_4371210537</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Gildan</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Intern, ERP GenAI</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="H19" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 15:23 UTC</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J19" s="10" t="inlineStr">
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J19" s="13" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/intern-erp-genai-at-gildan-4371210537?refId=jteS%2Ft3Cmc2XLVMFToCpKw%3D%3D&amp;trackingId=OQGg%2Bob2m9u4kkbRcgWoUw%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="K19" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-gildan-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
+      <c r="L19" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-gildan-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M19" s="8" t="inlineStr"/>
+      <c r="M19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>linkedin_4402974624</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Uccle, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J20" s="10" t="inlineStr">
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402974624?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=RJfkVsuYxv4DqyEhPJ367g%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="K20" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="L20" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M20" s="8" t="inlineStr"/>
+      <c r="M20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>linkedin_4402174633</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Cloudera</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>AI Enablement Intern (Ireland Based)</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>Greater Dublin</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="H21" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 18:24 UTC</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J21" s="10" t="inlineStr">
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="inlineStr">
         <is>
           <t>https://ie.linkedin.com/jobs/view/ai-enablement-intern-ireland-based-at-cloudera-4402174633?refId=d9iDz5spYJk0nIor701k5g%3D%3D&amp;trackingId=6OZvFiMQ12VqIzY6EqUe7A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr">
+      <c r="K21" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-cloudera-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L21" s="8" t="inlineStr">
+      <c r="L21" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-cloudera-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M21" s="8" t="inlineStr"/>
+      <c r="M21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>linkedin_4403115250</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>PhD Research Intern, Mapping Software</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 19:55 UTC</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J22" s="10" t="inlineStr">
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J22" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-mapping-software-at-zoox-4403115250?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=67WsHxTIXiO%2ByWr0OYU7ug%3D%3D&amp;position=10&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K22" s="8" t="inlineStr">
+      <c r="K22" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L22" s="8" t="inlineStr">
+      <c r="L22" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M22" s="8" t="inlineStr"/>
+      <c r="M22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>linkedin_4379373115</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>Woven by Toyota</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>Applied Scientist, Computer Vision and Generative Models, Vision AI (Internship)</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>Tokyo, Japan</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="H23" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 14:55 UTC</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J23" s="10" t="inlineStr">
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
         <is>
           <t>https://jp.linkedin.com/jobs/view/applied-scientist-computer-vision-and-generative-models-vision-ai-internship-at-woven-by-toyota-4379373115?refId=4q6ISAXJ%2BcfZsJD688QZWg%3D%3D&amp;trackingId=pUnO9OuzZx4G6BOukom%2FQQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K23" s="8" t="inlineStr">
+      <c r="K23" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-woven-by-toyota-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L23" s="8" t="inlineStr">
+      <c r="L23" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-woven-by-toyota-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M23" s="8" t="inlineStr"/>
+      <c r="M23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>linkedin_4325103488</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>Binance</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Binance Accelerator Program - DevOps (Artificial Intelligence)</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H24" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 12:13 UTC</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J24" s="10" t="inlineStr">
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J24" s="13" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/binance-accelerator-program-devops-artificial-intelligence-at-binance-4325103488?refId=KzaD5RMOfYQEZyaw6UmcpQ%3D%3D&amp;trackingId=8R4okHiG3RYyjThXHAqxIQ%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K24" s="8" t="inlineStr">
+      <c r="K24" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-binance-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L24" s="8" t="inlineStr">
+      <c r="L24" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-binance-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M24" s="8" t="inlineStr"/>
+      <c r="M24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>linkedin_4400563251</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>Aylo</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>Sr. Full-Stack Data Scientist - Data Services</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>Greater Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G25" s="11" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H25" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 12:01 UTC</t>
         </is>
       </c>
-      <c r="I25" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J25" s="10" t="inlineStr">
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/sr-full-stack-data-scientist-data-services-at-aylo-4400563251?refId=3X2hsLwn0XF5%2BC4ABneEzA%3D%3D&amp;trackingId=aJHp5psMKfAaMJdxBAz5Hw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K25" s="8" t="inlineStr">
+      <c r="K25" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-aylo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L25" s="8" t="inlineStr">
+      <c r="L25" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-aylo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M25" s="8" t="inlineStr"/>
+      <c r="M25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>linkedin_4400403670</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>Schneider Electric</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Internship in Global AI Sales Enablement &amp; Analytics</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Warsaw, Mazowieckie, Poland</t>
         </is>
       </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 11:43 UTC</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J26" s="10" t="inlineStr">
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J26" s="13" t="inlineStr">
         <is>
           <t>https://pl.linkedin.com/jobs/view/internship-in-global-ai-sales-enablement-analytics-at-schneider-electric-4400403670?refId=0j6PfgagLJw81v3dQ49jXQ%3D%3D&amp;trackingId=ErR9yiUH1tcny4hRKbXl8A%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K26" s="8" t="inlineStr">
+      <c r="K26" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-schneider-electric-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L26" s="8" t="inlineStr">
+      <c r="L26" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-schneider-electric-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M26" s="8" t="inlineStr"/>
+      <c r="M26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>linkedin_4297755027</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>Databricks</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>PhD GenAI Research Scientist Intern</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G27" s="11" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H27" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 10:31 UTC</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J27" s="10" t="inlineStr">
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-genai-research-scientist-intern-at-databricks-4297755027?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=UXoh9K97xsqO%2FzDhCy7Uug%3D%3D&amp;position=8&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K27" s="8" t="inlineStr">
+      <c r="K27" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-databricks-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L27" s="8" t="inlineStr">
+      <c r="L27" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-databricks-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M27" s="8" t="inlineStr"/>
+      <c r="M27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>linkedin_4401843829</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>Tiger Brokers Singapore</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Quantitative Investment Analyst Intern</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 06:09 UTC</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J28" s="10" t="inlineStr">
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J28" s="13" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/quantitative-investment-analyst-intern-at-tiger-brokers-singapore-4401843829?refId=LJ4PwcXqLhd1gtOBe9ZVig%3D%3D&amp;trackingId=oxh8Ol2m1QKvqfrvl10UqA%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K28" s="8" t="inlineStr">
+      <c r="K28" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-tiger-brokers-singapore-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L28" s="8" t="inlineStr">
+      <c r="L28" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-tiger-brokers-singapore-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M28" s="8" t="inlineStr"/>
+      <c r="M28" s="11" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>linkedin_4400148847</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Boomlet</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>Mumbai, Maharashtra, India</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="H29" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 05:24 UTC</t>
         </is>
       </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J29" s="10" t="inlineStr">
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J29" s="13" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-boomlet-4400148847?refId=vAgiKqchg4pd6EgGGQ%2FF%2FA%3D%3D&amp;trackingId=IoHiSd1L28nXXarEd4gYfw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K29" s="8" t="inlineStr">
+      <c r="K29" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boomlet-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L29" s="8" t="inlineStr">
+      <c r="L29" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boomlet-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M29" s="8" t="inlineStr"/>
+      <c r="M29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>linkedin_4401844394</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>On-us</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>AI Business Analyst Summer Intern</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H30" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 04:56 UTC</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J30" s="10" t="inlineStr">
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J30" s="13" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/ai-business-analyst-summer-intern-at-on-us-4401844394?refId=lslydLUu5l8kXOktysXYaw%3D%3D&amp;trackingId=BQ%2BoYgH5QtZKBWGZQgBfNQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K30" s="8" t="inlineStr">
+      <c r="K30" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-on-us-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L30" s="8" t="inlineStr">
+      <c r="L30" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-on-us-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M30" s="8" t="inlineStr"/>
+      <c r="M30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>linkedin_4401837715</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>Pathos Consultancy</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>Quantitative Research &amp; Development Internships</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="H31" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 03:48 UTC</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J31" s="10" t="inlineStr">
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J31" s="13" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/quantitative-research-development-internships-at-pathos-consultancy-4401837715?refId=KzaD5RMOfYQEZyaw6UmcpQ%3D%3D&amp;trackingId=eIGVr2dDtK%2F1o37C90xRoQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K31" s="8" t="inlineStr">
+      <c r="K31" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-pathos-consultancy-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L31" s="8" t="inlineStr">
+      <c r="L31" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-pathos-consultancy-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M31" s="8" t="inlineStr"/>
+      <c r="M31" s="11" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>linkedin_4402662606</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>Stripe</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>PhD Machine Learning Engineer, Intern</t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="H32" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 02:23 UTC</t>
         </is>
       </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J32" s="10" t="inlineStr">
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J32" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-machine-learning-engineer-intern-at-stripe-4402662606?refId=vJILgNySaXYUQknbyaKZZQ%3D%3D&amp;trackingId=NDMzaPfHMoCKo5uxI3THcw%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K32" s="8" t="inlineStr">
+      <c r="K32" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L32" s="8" t="inlineStr">
+      <c r="L32" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M32" s="8" t="inlineStr"/>
+      <c r="M32" s="11" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>linkedin_4402953925</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>Middle_East</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="H33" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 00:00 UTC</t>
         </is>
       </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J33" s="10" t="inlineStr">
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J33" s="13" t="inlineStr">
         <is>
           <t>https://ae.linkedin.com/jobs/view/research-intern-at-skycliff-it-4402953925?refId=f%2BmSR6Ncm83dISKgoQTrbw%3D%3D&amp;trackingId=CdPOXElDD3wJKKeBZSdWsw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K33" s="8" t="inlineStr">
+      <c r="K33" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L33" s="8" t="inlineStr">
+      <c r="L33" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M33" s="8" t="inlineStr"/>
+      <c r="M33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>linkedin_4402617206</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
         <is>
           <t>Stripe</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>PhD Machine Learning Engineer, Intern</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="G34" s="11" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="H34" s="11" t="inlineStr">
         <is>
           <t>2026-04-15 20:25 UTC</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J34" s="10" t="inlineStr">
+      <c r="I34" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J34" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-machine-learning-engineer-intern-at-stripe-4402617206?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=yAc4U29LYJcrlQSUWWcubA%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K34" s="8" t="inlineStr">
+      <c r="K34" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L34" s="8" t="inlineStr">
+      <c r="L34" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M34" s="8" t="inlineStr"/>
+      <c r="M34" s="11" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>linkedin_4403183407</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>Hardware FYI</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>Robotics - Applied Scientist II Intern / Co-op - 2026 (Robotics, Manipulation, Perception, Motion Planning, Autonomous Mobile Robots, Computer Vision, Machine Learning, Controls, and more)</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>Boston, MA</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="H35" s="11" t="inlineStr">
         <is>
           <t>2026-04-17 04:31 UTC</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J35" s="10" t="inlineStr">
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J35" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/robotics-applied-scientist-ii-intern-co-op-2026-robotics-manipulation-perception-motion-planning-autonomous-mobile-robots-computer-vision-machine-learning-controls-and-more-at-hardware-fyi-4403183407?refId=s5WxXRPJ8QU7G2WPi2yNiw%3D%3D&amp;trackingId=rjd%2F8qdM5kQMmADtGJgSSw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K35" s="8" t="inlineStr">
+      <c r="K35" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-hardware-fyi-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L35" s="8" t="inlineStr">
+      <c r="L35" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-hardware-fyi-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M35" s="8" t="inlineStr"/>
+      <c r="M35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>linkedin_4403153262</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
         <is>
           <t>Generali Malaysia</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Intern, IT (AI Engineering)</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>Federal Territory of Kuala Lumpur, Malaysia</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="G36" s="11" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr">
+      <c r="H36" s="11" t="inlineStr">
         <is>
           <t>2026-04-17 00:47 UTC</t>
         </is>
       </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J36" s="10" t="inlineStr">
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J36" s="13" t="inlineStr">
         <is>
           <t>https://my.linkedin.com/jobs/view/intern-it-ai-engineering-at-generali-malaysia-4403153262?refId=h4J9hFjDRjjPW7bUqRcUZQ%3D%3D&amp;trackingId=WmqITEtGX486sbNH6b%2BYmA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K36" s="8" t="inlineStr">
+      <c r="K36" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-generali-malaysia-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L36" s="8" t="inlineStr">
+      <c r="L36" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-generali-malaysia-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M36" s="8" t="inlineStr"/>
+      <c r="M36" s="11" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>linkedin_4402311007</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
         <is>
           <t>SAP iXp Intern - Customer Success Engineering, Operations &amp; AI Enablement [Boston]</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>Burlington, MA</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr">
+      <c r="H37" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 21:40 UTC</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J37" s="10" t="inlineStr">
+      <c r="I37" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J37" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/sap-ixp-intern-%C2%A0customer-success-engineering-operations-ai-enablement-boston-at-sap-4402311007?refId=ofb0jzd8xWUoUtvr7A%2BwXQ%3D%3D&amp;trackingId=S%2Fo4FvRdeOcn00Jo5DVUBw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K37" s="8" t="inlineStr">
+      <c r="K37" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L37" s="8" t="inlineStr">
+      <c r="L37" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M37" s="8" t="inlineStr"/>
+      <c r="M37" s="11" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>linkedin_4403154707</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Software Engineer Intern, Perception Data</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="G38" s="11" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr">
+      <c r="H38" s="11" t="inlineStr">
         <is>
           <t>2026-04-17 02:21 UTC</t>
         </is>
       </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J38" s="10" t="inlineStr">
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J38" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/software-engineer-intern-perception-data-at-zoox-4403154707?refId=ON4L5FUhksKAgylRRsNllQ%3D%3D&amp;trackingId=1%2F3OkqP%2Bu0PqHp9bXnlS0A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K38" s="8" t="inlineStr">
+      <c r="K38" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L38" s="8" t="inlineStr">
+      <c r="L38" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M38" s="8" t="inlineStr"/>
+      <c r="M38" s="11" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>linkedin_4402947451</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>Rubrik</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>India Benefits &amp; AI Operations Intern</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G39" s="8" t="inlineStr">
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="H39" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 11:40 UTC</t>
         </is>
       </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J39" s="10" t="inlineStr">
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J39" s="13" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/india-benefits-ai-operations-intern-at-rubrik-4402947451?refId=9u2uyUYzyMZimaTtDELDWg%3D%3D&amp;trackingId=BjOmyeYm6McmUpzLwcES9g%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K39" s="8" t="inlineStr">
+      <c r="K39" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-rubrik-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L39" s="8" t="inlineStr">
+      <c r="L39" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-rubrik-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M39" s="8" t="inlineStr"/>
+      <c r="M39" s="11" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>linkedin_4390354006</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>Lila Sciences</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Intern, Next Gen AI Robotics</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>Cambridge, MA</t>
         </is>
       </c>
-      <c r="G40" s="8" t="inlineStr">
+      <c r="G40" s="11" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr">
+      <c r="H40" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 10:58 UTC</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J40" s="10" t="inlineStr">
+      <c r="I40" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J40" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/intern-next-gen-ai-robotics-at-lila-sciences-4390354006?refId=ZoXJQXesL%2FE%2B5EAGGzWfiA%3D%3D&amp;trackingId=FmSMwWhyyIaC52NsDwOCtw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K40" s="8" t="inlineStr">
+      <c r="K40" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-lila-sciences-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L40" s="8" t="inlineStr">
+      <c r="L40" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-lila-sciences-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M40" s="8" t="inlineStr"/>
+      <c r="M40" s="11" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>arbeitnow_ai-venture-development-tech-intern-berlin-100382</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D41" s="11" t="inlineStr">
         <is>
           <t>Zeeg</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>AI &amp; Venture Development Tech Intern (w/m/d)</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
+      <c r="G41" s="11" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr">
+      <c r="H41" s="11" t="inlineStr">
         <is>
           <t>2026-04-16 10:30 UTC</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J41" s="10" t="inlineStr">
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J41" s="13" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/zeeg/ai-venture-development-tech-intern-berlin-100382</t>
         </is>
       </c>
-      <c r="K41" s="8" t="inlineStr">
+      <c r="K41" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zeeg-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L41" s="8" t="inlineStr">
+      <c r="L41" s="11" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zeeg-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M41" s="8" t="inlineStr"/>
+      <c r="M41" s="11" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
@@ -3786,6 +3795,510 @@
         </is>
       </c>
       <c r="M52" s="11" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>linkedin_4400873418</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-18 08:17</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>SANOVIO</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="inlineStr">
+        <is>
+          <t>AI Engineering Intern</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H53" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-18 00:00 UTC</t>
+        </is>
+      </c>
+      <c r="I53" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J53" s="16" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/ai-engineering-intern-at-sanovio-4400873418?refId=egIYeNLcARu6P6oTIZ%2BHfA%3D%3D&amp;trackingId=c6wZ0DtTzvVZpTRC1l5tYQ%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K53" s="14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sanovio-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="L53" s="14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sanovio-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="M53" s="14" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>linkedin_4403524251</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-18 08:17</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>Nascent Markets</t>
+        </is>
+      </c>
+      <c r="E54" s="14" t="inlineStr">
+        <is>
+          <t>Agentic Systems Intern (Graduate Level)</t>
+        </is>
+      </c>
+      <c r="F54" s="14" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H54" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-17 19:53 UTC</t>
+        </is>
+      </c>
+      <c r="I54" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J54" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/agentic-systems-intern-graduate-level-at-nascent-markets-4403524251?refId=Ix0g0waARRaNpzTY4LxvsQ%3D%3D&amp;trackingId=RsqyOyJHkanw%2FTeHGUcadA%3D%3D&amp;position=2&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K54" s="14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-nascent-markets-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="L54" s="14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-nascent-markets-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="M54" s="14" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>linkedin_4402782985</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-18 08:17</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>Axiomatic_AI</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
+          <t>Internship - Research Intern (Agentic Learning, Memory &amp; Neurosymbolic Reasoning)</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
+        <is>
+          <t>Greater Barcelona Metropolitan Area</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-18 05:04 UTC</t>
+        </is>
+      </c>
+      <c r="I55" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>https://es.linkedin.com/jobs/view/internship-research-intern-agentic-learning-memory-neurosymbolic-reasoning-at-axiomatic-ai-4402782985?refId=vm6No12NjZrg2BBV%2BnbuLQ%3D%3D&amp;trackingId=X9FXk%2FBDFftROMNo9Cr20g%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K55" s="14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-axiomatic-ai-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="L55" s="14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-axiomatic-ai-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="M55" s="14" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>linkedin_4309694978</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-18 08:17</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>DataAnnotation</t>
+        </is>
+      </c>
+      <c r="E56" s="14" t="inlineStr">
+        <is>
+          <t>Graduate Physics Research Intern</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>New York, United States</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H56" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-17 17:37 UTC</t>
+        </is>
+      </c>
+      <c r="I56" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/graduate-physics-research-intern-at-dataannotation-4309694978?refId=hlpC50hTZs9sJFHirXWMSg%3D%3D&amp;trackingId=1E0ixzzpb6MzeHKgxpE3Cw%3D%3D&amp;position=9&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K56" s="14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="L56" s="14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="M56" s="14" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>linkedin_4403562730</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-18 08:17</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>BNM Business Solutions LLP</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="inlineStr">
+        <is>
+          <t>Data Analyst Internship in Navi Mumbai, Mumbai</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="inlineStr">
+        <is>
+          <t>Mumbai Metropolitan Region</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H57" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-18 00:06 UTC</t>
+        </is>
+      </c>
+      <c r="I57" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/data-analyst-internship-in-navi-mumbai-mumbai-at-bnm-business-solutions-llp-4403562730?refId=1X9LgKP3%2FAPeJuhZVjyhxw%3D%3D&amp;trackingId=oFY9Z69ZBEGkNtq0cbBOMw%3D%3D&amp;position=2&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K57" s="14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bnm-business-solutions-llp-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="L57" s="14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bnm-business-solutions-llp-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="M57" s="14" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>linkedin_4309694917</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-18 08:17</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>DataAnnotation</t>
+        </is>
+      </c>
+      <c r="E58" s="14" t="inlineStr">
+        <is>
+          <t>Graduate Biology Research Intern</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>New York, United States</t>
+        </is>
+      </c>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H58" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-17 17:35 UTC</t>
+        </is>
+      </c>
+      <c r="I58" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J58" s="16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/graduate-biology-research-intern-at-dataannotation-4309694917?refId=hlpC50hTZs9sJFHirXWMSg%3D%3D&amp;trackingId=BM%2FBx4ElnXDk5hEpiM0gzg%3D%3D&amp;position=8&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K58" s="14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="L58" s="14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="M58" s="14" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>linkedin_4346088677</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-18 08:17</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>revel8</t>
+        </is>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer Intern (all genders)</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H59" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-17 22:38 UTC</t>
+        </is>
+      </c>
+      <c r="I59" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J59" s="16" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/applied-ai-engineer-intern-all-genders-at-revel8-4346088677?refId=FHQDN2Ta3J6B7WhWnDAuhQ%3D%3D&amp;trackingId=Pf%2Ftwn6H5Hrw8BKjPenbSQ%3D%3D&amp;position=3&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K59" s="14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-revel8-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="L59" s="14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-revel8-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="M59" s="14" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>linkedin_4403475387</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-18 08:17</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>Inc42 Media</t>
+        </is>
+      </c>
+      <c r="E60" s="14" t="inlineStr">
+        <is>
+          <t>Operations Intern: Inc42 AI Summit 2026</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H60" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-17 16:23 UTC</t>
+        </is>
+      </c>
+      <c r="I60" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J60" s="16" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/operations-intern-inc42-ai-summit-2026-at-inc42-media-4403475387?refId=jyI2mJ9xFT%2BmdtkV0OCW0g%3D%3D&amp;trackingId=6sWKnvWNaTU69%2B7bcZNxLg%3D%3D&amp;position=10&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K60" s="14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-inc42-media-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="L60" s="14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-inc42-media-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="M60" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3840,6 +4353,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -83,10 +83,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -498,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -584,3217 +593,3217 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>linkedin_4401809501</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="H2" s="14" t="inlineStr">
         <is>
           <t>2026-04-15 22:19 UTC</t>
         </is>
       </c>
-      <c r="I2" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J2" s="13" t="inlineStr">
+      <c r="I2" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J2" s="16" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/research-intern-at-skycliff-it-4401809501?refId=HHi6SaK1fggu3E9dI3MtVg%3D%3D&amp;trackingId=r33pSo29lHStfk9FH82pyw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K2" s="11" t="inlineStr">
+      <c r="K2" s="14" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L2" s="11" t="inlineStr">
+      <c r="L2" s="14" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M2" s="11" t="inlineStr"/>
+      <c r="M2" s="14" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>linkedin_4402568578</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>Webs X UM</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t>2026-04-15 19:20 UTC</t>
         </is>
       </c>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J3" s="13" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-webs-x-um-4402568578?refId=g89JM6cY8EFeoLk6JL5tVg%3D%3D&amp;trackingId=uFZVJJX7SSI0XCPFIrLqmA%3D%3D&amp;position=19&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="K3" s="14" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-webs-x-um-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L3" s="11" t="inlineStr">
+      <c r="L3" s="14" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-webs-x-um-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr"/>
+      <c r="M3" s="14" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>linkedin_4399996740</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>SUN PHARMA</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>Becario</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>Mexico City, Mexico</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="14" t="inlineStr">
         <is>
           <t>2026-04-15 17:59 UTC</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t>https://mx.linkedin.com/jobs/view/becario-at-sun-pharma-4399996740?refId=g89JM6cY8EFeoLk6JL5tVg%3D%3D&amp;trackingId=sZ0Fkcf4RHuIpzXu4mJRNg%3D%3D&amp;position=22&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
+      <c r="K4" s="14" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-sun-pharma-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-sun-pharma-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr"/>
+      <c r="M4" s="14" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>linkedin_4399975959</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>LS Direct</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>Data Analytics Intern</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>Suffern, NY</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t>2026-04-15 14:26 UTC</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J5" s="13" t="inlineStr">
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-analytics-intern-at-ls-direct-4399975959?refId=pg0ll3e89fatVyUznLcdpw%3D%3D&amp;trackingId=5b41IoyQfIfx3Tu42domiQ%3D%3D&amp;position=23&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="K5" s="14" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-ls-direct-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="L5" s="14" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-ls-direct-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr"/>
+      <c r="M5" s="14" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>linkedin_4370546718</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Clarivate</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Lead Data Scientist</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>Barcelona, Catalonia, Spain</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>2026-04-15 12:16 UTC</t>
         </is>
       </c>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J6" s="13" t="inlineStr">
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/lead-data-scientist-at-clarivate-4370546718?refId=FyyqQfduMQ8KZ7B5LeF0UQ%3D%3D&amp;trackingId=1i1kXdbV7SMunyFTiSJHJg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="K6" s="14" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-clarivate-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L6" s="11" t="inlineStr">
+      <c r="L6" s="14" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-clarivate-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr"/>
+      <c r="M6" s="14" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>linkedin_4389810164</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>Vitality</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Senior Data Scientist - 12 Month FTC</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>2026-04-15 09:39 UTC</t>
         </is>
       </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J7" s="13" t="inlineStr">
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/senior-data-scientist-12-month-ftc-at-vitality-4389810164?refId=FPz%2BrPoaQeqgXBm%2FfOzGGA%3D%3D&amp;trackingId=yVNh55t2X2xocDT4i6HDqQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K7" s="11" t="inlineStr">
+      <c r="K7" s="14" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-vitality-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L7" s="11" t="inlineStr">
+      <c r="L7" s="14" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-vitality-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M7" s="11" t="inlineStr"/>
+      <c r="M7" s="14" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>linkedin_4399952059</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>traide AI</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>AI Associate (f/m/x) (B2B SaaS Startup) - Intern/Working Student</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>2026-04-15 07:04 UTC</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J8" s="13" t="inlineStr">
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/ai-associate-f-m-x-b2b-saas-startup-intern-working-student-at-traide-ai-4399952059?refId=x0uIkl175n0hipT17L%2FGRw%3D%3D&amp;trackingId=8kdzUQgW%2B7rCk2pO2oIErg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr">
+      <c r="K8" s="14" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-traide-ai-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L8" s="11" t="inlineStr">
+      <c r="L8" s="14" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-traide-ai-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M8" s="11" t="inlineStr"/>
+      <c r="M8" s="14" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>linkedin_4399933254</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>Briink</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>Growth Intern (Merantix AI Campus)</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>2026-04-15 05:03 UTC</t>
         </is>
       </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J9" s="13" t="inlineStr">
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/growth-intern-merantix-ai-campus-at-briink-4399933254?refId=x0uIkl175n0hipT17L%2FGRw%3D%3D&amp;trackingId=qEKtyJNA03Kbr6AYDlhsBw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr">
+      <c r="K9" s="14" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-briink-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L9" s="11" t="inlineStr">
+      <c r="L9" s="14" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-briink-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M9" s="11" t="inlineStr"/>
+      <c r="M9" s="14" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>linkedin_4400429367</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Tata Consultancy Services</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>HR -Data Scientist</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>Renton, WA</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H10" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 16:56 UTC</t>
         </is>
       </c>
-      <c r="I10" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J10" s="13" t="inlineStr">
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/hr-data-scientist-at-tata-consultancy-services-4400429367?refId=vJILgNySaXYUQknbyaKZZQ%3D%3D&amp;trackingId=7cZ0KYh8Sv5%2Fh6%2FG86%2BLug%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="K10" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-tata-consultancy-services-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="L10" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-tata-consultancy-services-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr"/>
+      <c r="M10" s="14" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>linkedin_4390814627</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>Criteo</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>Barcelona, Catalonia, Spain</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 12:19 UTC</t>
         </is>
       </c>
-      <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J11" s="13" t="inlineStr">
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/data-analyst-intern-at-criteo-4390814627?refId=PCZWvfzZIzNkx6giU9jTsA%3D%3D&amp;trackingId=T%2FMog6vtgG8P3ihAU9b1uQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K11" s="11" t="inlineStr">
+      <c r="K11" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-criteo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L11" s="11" t="inlineStr">
+      <c r="L11" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-criteo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M11" s="11" t="inlineStr"/>
+      <c r="M11" s="14" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>linkedin_4402983364</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="14" t="inlineStr">
         <is>
           <t>Brussels, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="14" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J12" s="13" t="inlineStr">
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J12" s="16" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402983364?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=zV4sJQyNyQg%2FS%2BYm6Ba9Eg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr">
+      <c r="K12" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L12" s="11" t="inlineStr">
+      <c r="L12" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M12" s="11" t="inlineStr"/>
+      <c r="M12" s="14" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>linkedin_4390725142</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>Boston Consulting Group (BCG)</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>Forward Deployed AI Engineer, Internship, United Kingdom - BCG X</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 16:24 UTC</t>
         </is>
       </c>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J13" s="13" t="inlineStr">
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/forward-deployed-ai-engineer-internship-united-kingdom-bcg-x-at-boston-consulting-group-bcg-4390725142?refId=YHAZO5vAx9Qtg1RXMma%2F%2BA%3D%3D&amp;trackingId=E8kiSHzcdYe%2FH6s%2FCkGtMw%3D%3D&amp;position=7&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr">
+      <c r="K13" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L13" s="11" t="inlineStr">
+      <c r="L13" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M13" s="11" t="inlineStr"/>
+      <c r="M13" s="14" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>linkedin_4400428064</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>Fanatics</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="14" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="14" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H14" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 16:16 UTC</t>
         </is>
       </c>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J14" s="13" t="inlineStr">
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J14" s="16" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/data-scientist-at-fanatics-4400428064?refId=SNMwEp9%2FBozAkX4FBnhJwQ%3D%3D&amp;trackingId=cAX0aKWV%2FBX1fvQzm%2FkEMg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr">
+      <c r="K14" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-fanatics-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L14" s="11" t="inlineStr">
+      <c r="L14" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-fanatics-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M14" s="11" t="inlineStr"/>
+      <c r="M14" s="14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>linkedin_4390730090</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Boston Consulting Group (BCG)</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>Forward Deployed AI Scientist, Internship, United Kingdom - BCG X</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="14" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 13:57 UTC</t>
         </is>
       </c>
-      <c r="I15" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J15" s="13" t="inlineStr">
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J15" s="16" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/forward-deployed-ai-scientist-internship-united-kingdom-bcg-x-at-boston-consulting-group-bcg-4390730090?refId=YHAZO5vAx9Qtg1RXMma%2F%2BA%3D%3D&amp;trackingId=m50MzwjbYzUmAv7nJVAKgA%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K15" s="11" t="inlineStr">
+      <c r="K15" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L15" s="11" t="inlineStr">
+      <c r="L15" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M15" s="11" t="inlineStr"/>
+      <c r="M15" s="14" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>linkedin_4402138096</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Kelly Tutors</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>Research Intern (3-5hrs/week, flexible)</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="H16" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 14:40 UTC</t>
         </is>
       </c>
-      <c r="I16" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J16" s="13" t="inlineStr">
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J16" s="16" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/research-intern-3-5hrs-week-flexible-at-kelly-tutors-4402138096?refId=HmOS2YEHUH3GOVent1txqw%3D%3D&amp;trackingId=3XBXMUoBdiHeRL4qw%2B2qRw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr">
+      <c r="K16" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-kelly-tutors-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L16" s="11" t="inlineStr">
+      <c r="L16" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-kelly-tutors-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M16" s="11" t="inlineStr"/>
+      <c r="M16" s="14" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>linkedin_4378557045</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>Fund for Public Health in NYC</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 16:13 UTC</t>
         </is>
       </c>
-      <c r="I17" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J17" s="13" t="inlineStr">
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J17" s="16" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-scientist-at-fund-for-public-health-in-nyc-4378557045?refId=JsndNRa0tnfF7dsuxv62wA%3D%3D&amp;trackingId=Pmgt6JCxYmQun5Uv6%2BLbiQ%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K17" s="11" t="inlineStr">
+      <c r="K17" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-fund-for-public-health-in-nyc-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L17" s="11" t="inlineStr">
+      <c r="L17" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-fund-for-public-health-in-nyc-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M17" s="11" t="inlineStr"/>
+      <c r="M17" s="14" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>linkedin_4402977457</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>Brussels, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I18" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J18" s="13" t="inlineStr">
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402977457?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=gL9sbQh%2FaLMmzvXjuO71WQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr">
+      <c r="K18" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L18" s="11" t="inlineStr">
+      <c r="L18" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M18" s="11" t="inlineStr"/>
+      <c r="M18" s="14" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>linkedin_4371210537</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>Gildan</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>Intern, ERP GenAI</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 15:23 UTC</t>
         </is>
       </c>
-      <c r="I19" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J19" s="13" t="inlineStr">
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/intern-erp-genai-at-gildan-4371210537?refId=jteS%2Ft3Cmc2XLVMFToCpKw%3D%3D&amp;trackingId=OQGg%2Bob2m9u4kkbRcgWoUw%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K19" s="11" t="inlineStr">
+      <c r="K19" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-gildan-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L19" s="11" t="inlineStr">
+      <c r="L19" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-gildan-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M19" s="11" t="inlineStr"/>
+      <c r="M19" s="14" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>linkedin_4402974624</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>Uccle, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="H20" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I20" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J20" s="13" t="inlineStr">
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J20" s="16" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402974624?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=RJfkVsuYxv4DqyEhPJ367g%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K20" s="11" t="inlineStr">
+      <c r="K20" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L20" s="11" t="inlineStr">
+      <c r="L20" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M20" s="11" t="inlineStr"/>
+      <c r="M20" s="14" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>linkedin_4402174633</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>Cloudera</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>AI Enablement Intern (Ireland Based)</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>Greater Dublin</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 18:24 UTC</t>
         </is>
       </c>
-      <c r="I21" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J21" s="13" t="inlineStr">
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
         <is>
           <t>https://ie.linkedin.com/jobs/view/ai-enablement-intern-ireland-based-at-cloudera-4402174633?refId=d9iDz5spYJk0nIor701k5g%3D%3D&amp;trackingId=6OZvFiMQ12VqIzY6EqUe7A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K21" s="11" t="inlineStr">
+      <c r="K21" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-cloudera-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L21" s="11" t="inlineStr">
+      <c r="L21" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-cloudera-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M21" s="11" t="inlineStr"/>
+      <c r="M21" s="14" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>linkedin_4403115250</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>PhD Research Intern, Mapping Software</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="14" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="14" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="H22" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 19:55 UTC</t>
         </is>
       </c>
-      <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J22" s="13" t="inlineStr">
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-mapping-software-at-zoox-4403115250?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=67WsHxTIXiO%2ByWr0OYU7ug%3D%3D&amp;position=10&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K22" s="11" t="inlineStr">
+      <c r="K22" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L22" s="11" t="inlineStr">
+      <c r="L22" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M22" s="11" t="inlineStr"/>
+      <c r="M22" s="14" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>linkedin_4379373115</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>Woven by Toyota</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>Applied Scientist, Computer Vision and Generative Models, Vision AI (Internship)</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>Tokyo, Japan</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 14:55 UTC</t>
         </is>
       </c>
-      <c r="I23" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J23" s="13" t="inlineStr">
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
         <is>
           <t>https://jp.linkedin.com/jobs/view/applied-scientist-computer-vision-and-generative-models-vision-ai-internship-at-woven-by-toyota-4379373115?refId=4q6ISAXJ%2BcfZsJD688QZWg%3D%3D&amp;trackingId=pUnO9OuzZx4G6BOukom%2FQQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="K23" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-woven-by-toyota-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L23" s="11" t="inlineStr">
+      <c r="L23" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-woven-by-toyota-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M23" s="11" t="inlineStr"/>
+      <c r="M23" s="14" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>linkedin_4325103488</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>Binance</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr">
         <is>
           <t>Binance Accelerator Program - DevOps (Artificial Intelligence)</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="14" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="14" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="H24" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 12:13 UTC</t>
         </is>
       </c>
-      <c r="I24" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J24" s="13" t="inlineStr">
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/binance-accelerator-program-devops-artificial-intelligence-at-binance-4325103488?refId=KzaD5RMOfYQEZyaw6UmcpQ%3D%3D&amp;trackingId=8R4okHiG3RYyjThXHAqxIQ%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K24" s="11" t="inlineStr">
+      <c r="K24" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-binance-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L24" s="11" t="inlineStr">
+      <c r="L24" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-binance-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M24" s="11" t="inlineStr"/>
+      <c r="M24" s="14" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>linkedin_4400563251</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>Aylo</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>Sr. Full-Stack Data Scientist - Data Services</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F25" s="14" t="inlineStr">
         <is>
           <t>Greater Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="G25" s="14" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="H25" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 12:01 UTC</t>
         </is>
       </c>
-      <c r="I25" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J25" s="13" t="inlineStr">
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/sr-full-stack-data-scientist-data-services-at-aylo-4400563251?refId=3X2hsLwn0XF5%2BC4ABneEzA%3D%3D&amp;trackingId=aJHp5psMKfAaMJdxBAz5Hw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K25" s="11" t="inlineStr">
+      <c r="K25" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-aylo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L25" s="11" t="inlineStr">
+      <c r="L25" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-aylo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M25" s="11" t="inlineStr"/>
+      <c r="M25" s="14" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>linkedin_4400403670</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>Schneider Electric</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="14" t="inlineStr">
         <is>
           <t>Internship in Global AI Sales Enablement &amp; Analytics</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="14" t="inlineStr">
         <is>
           <t>Warsaw, Mazowieckie, Poland</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G26" s="14" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H26" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 11:43 UTC</t>
         </is>
       </c>
-      <c r="I26" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J26" s="13" t="inlineStr">
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
         <is>
           <t>https://pl.linkedin.com/jobs/view/internship-in-global-ai-sales-enablement-analytics-at-schneider-electric-4400403670?refId=0j6PfgagLJw81v3dQ49jXQ%3D%3D&amp;trackingId=ErR9yiUH1tcny4hRKbXl8A%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K26" s="11" t="inlineStr">
+      <c r="K26" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-schneider-electric-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L26" s="11" t="inlineStr">
+      <c r="L26" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-schneider-electric-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M26" s="11" t="inlineStr"/>
+      <c r="M26" s="14" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>linkedin_4297755027</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>Databricks</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>PhD GenAI Research Scientist Intern</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="14" t="inlineStr">
         <is>
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 10:31 UTC</t>
         </is>
       </c>
-      <c r="I27" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J27" s="13" t="inlineStr">
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-genai-research-scientist-intern-at-databricks-4297755027?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=UXoh9K97xsqO%2FzDhCy7Uug%3D%3D&amp;position=8&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K27" s="11" t="inlineStr">
+      <c r="K27" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-databricks-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L27" s="11" t="inlineStr">
+      <c r="L27" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-databricks-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M27" s="11" t="inlineStr"/>
+      <c r="M27" s="14" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>linkedin_4401843829</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>Tiger Brokers Singapore</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>Quantitative Investment Analyst Intern</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F28" s="14" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G28" s="14" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H28" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 06:09 UTC</t>
         </is>
       </c>
-      <c r="I28" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J28" s="13" t="inlineStr">
+      <c r="I28" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J28" s="16" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/quantitative-investment-analyst-intern-at-tiger-brokers-singapore-4401843829?refId=LJ4PwcXqLhd1gtOBe9ZVig%3D%3D&amp;trackingId=oxh8Ol2m1QKvqfrvl10UqA%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K28" s="11" t="inlineStr">
+      <c r="K28" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-tiger-brokers-singapore-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L28" s="11" t="inlineStr">
+      <c r="L28" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-tiger-brokers-singapore-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M28" s="11" t="inlineStr"/>
+      <c r="M28" s="14" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>linkedin_4400148847</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
         <is>
           <t>Boomlet</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="14" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F29" s="14" t="inlineStr">
         <is>
           <t>Mumbai, Maharashtra, India</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="H29" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 05:24 UTC</t>
         </is>
       </c>
-      <c r="I29" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J29" s="13" t="inlineStr">
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-boomlet-4400148847?refId=vAgiKqchg4pd6EgGGQ%2FF%2FA%3D%3D&amp;trackingId=IoHiSd1L28nXXarEd4gYfw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K29" s="11" t="inlineStr">
+      <c r="K29" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boomlet-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L29" s="11" t="inlineStr">
+      <c r="L29" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boomlet-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M29" s="11" t="inlineStr"/>
+      <c r="M29" s="14" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>linkedin_4401844394</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
         <is>
           <t>On-us</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="14" t="inlineStr">
         <is>
           <t>AI Business Analyst Summer Intern</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F30" s="14" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G30" s="14" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="H30" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 04:56 UTC</t>
         </is>
       </c>
-      <c r="I30" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J30" s="13" t="inlineStr">
+      <c r="I30" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J30" s="16" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/ai-business-analyst-summer-intern-at-on-us-4401844394?refId=lslydLUu5l8kXOktysXYaw%3D%3D&amp;trackingId=BQ%2BoYgH5QtZKBWGZQgBfNQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K30" s="11" t="inlineStr">
+      <c r="K30" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-on-us-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L30" s="11" t="inlineStr">
+      <c r="L30" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-on-us-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M30" s="11" t="inlineStr"/>
+      <c r="M30" s="14" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>linkedin_4401837715</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
         <is>
           <t>Pathos Consultancy</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="14" t="inlineStr">
         <is>
           <t>Quantitative Research &amp; Development Internships</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F31" s="14" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="14" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H31" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 03:48 UTC</t>
         </is>
       </c>
-      <c r="I31" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J31" s="13" t="inlineStr">
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J31" s="16" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/quantitative-research-development-internships-at-pathos-consultancy-4401837715?refId=KzaD5RMOfYQEZyaw6UmcpQ%3D%3D&amp;trackingId=eIGVr2dDtK%2F1o37C90xRoQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K31" s="11" t="inlineStr">
+      <c r="K31" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-pathos-consultancy-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L31" s="11" t="inlineStr">
+      <c r="L31" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-pathos-consultancy-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M31" s="11" t="inlineStr"/>
+      <c r="M31" s="14" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>linkedin_4402662606</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
         <is>
           <t>Stripe</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E32" s="14" t="inlineStr">
         <is>
           <t>PhD Machine Learning Engineer, Intern</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F32" s="14" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="G32" s="14" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H32" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 02:23 UTC</t>
         </is>
       </c>
-      <c r="I32" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J32" s="13" t="inlineStr">
+      <c r="I32" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-machine-learning-engineer-intern-at-stripe-4402662606?refId=vJILgNySaXYUQknbyaKZZQ%3D%3D&amp;trackingId=NDMzaPfHMoCKo5uxI3THcw%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K32" s="11" t="inlineStr">
+      <c r="K32" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L32" s="11" t="inlineStr">
+      <c r="L32" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M32" s="11" t="inlineStr"/>
+      <c r="M32" s="14" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>linkedin_4402953925</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="14" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F33" s="14" t="inlineStr">
         <is>
           <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="G33" s="14" t="inlineStr">
         <is>
           <t>Middle_East</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H33" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 00:00 UTC</t>
         </is>
       </c>
-      <c r="I33" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J33" s="13" t="inlineStr">
+      <c r="I33" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J33" s="16" t="inlineStr">
         <is>
           <t>https://ae.linkedin.com/jobs/view/research-intern-at-skycliff-it-4402953925?refId=f%2BmSR6Ncm83dISKgoQTrbw%3D%3D&amp;trackingId=CdPOXElDD3wJKKeBZSdWsw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K33" s="11" t="inlineStr">
+      <c r="K33" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L33" s="11" t="inlineStr">
+      <c r="L33" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M33" s="11" t="inlineStr"/>
+      <c r="M33" s="14" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>linkedin_4402617206</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
         <is>
           <t>Stripe</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E34" s="14" t="inlineStr">
         <is>
           <t>PhD Machine Learning Engineer, Intern</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F34" s="14" t="inlineStr">
         <is>
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G34" s="14" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="H34" s="14" t="inlineStr">
         <is>
           <t>2026-04-15 20:25 UTC</t>
         </is>
       </c>
-      <c r="I34" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J34" s="13" t="inlineStr">
+      <c r="I34" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J34" s="16" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-machine-learning-engineer-intern-at-stripe-4402617206?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=yAc4U29LYJcrlQSUWWcubA%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K34" s="11" t="inlineStr">
+      <c r="K34" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L34" s="11" t="inlineStr">
+      <c r="L34" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M34" s="11" t="inlineStr"/>
+      <c r="M34" s="14" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>linkedin_4403183407</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
         <is>
           <t>Hardware FYI</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E35" s="14" t="inlineStr">
         <is>
           <t>Robotics - Applied Scientist II Intern / Co-op - 2026 (Robotics, Manipulation, Perception, Motion Planning, Autonomous Mobile Robots, Computer Vision, Machine Learning, Controls, and more)</t>
         </is>
       </c>
-      <c r="F35" s="11" t="inlineStr">
+      <c r="F35" s="14" t="inlineStr">
         <is>
           <t>Boston, MA</t>
         </is>
       </c>
-      <c r="G35" s="11" t="inlineStr">
+      <c r="G35" s="14" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="H35" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 04:31 UTC</t>
         </is>
       </c>
-      <c r="I35" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J35" s="13" t="inlineStr">
+      <c r="I35" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J35" s="16" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/robotics-applied-scientist-ii-intern-co-op-2026-robotics-manipulation-perception-motion-planning-autonomous-mobile-robots-computer-vision-machine-learning-controls-and-more-at-hardware-fyi-4403183407?refId=s5WxXRPJ8QU7G2WPi2yNiw%3D%3D&amp;trackingId=rjd%2F8qdM5kQMmADtGJgSSw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K35" s="11" t="inlineStr">
+      <c r="K35" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-hardware-fyi-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L35" s="11" t="inlineStr">
+      <c r="L35" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-hardware-fyi-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M35" s="11" t="inlineStr"/>
+      <c r="M35" s="14" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>linkedin_4403153262</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
         <is>
           <t>Generali Malaysia</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E36" s="14" t="inlineStr">
         <is>
           <t>Intern, IT (AI Engineering)</t>
         </is>
       </c>
-      <c r="F36" s="11" t="inlineStr">
+      <c r="F36" s="14" t="inlineStr">
         <is>
           <t>Federal Territory of Kuala Lumpur, Malaysia</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G36" s="14" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="H36" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 00:47 UTC</t>
         </is>
       </c>
-      <c r="I36" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J36" s="13" t="inlineStr">
+      <c r="I36" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J36" s="16" t="inlineStr">
         <is>
           <t>https://my.linkedin.com/jobs/view/intern-it-ai-engineering-at-generali-malaysia-4403153262?refId=h4J9hFjDRjjPW7bUqRcUZQ%3D%3D&amp;trackingId=WmqITEtGX486sbNH6b%2BYmA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K36" s="11" t="inlineStr">
+      <c r="K36" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-generali-malaysia-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L36" s="11" t="inlineStr">
+      <c r="L36" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-generali-malaysia-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M36" s="11" t="inlineStr"/>
+      <c r="M36" s="14" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>linkedin_4402311007</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E37" s="14" t="inlineStr">
         <is>
           <t>SAP iXp Intern - Customer Success Engineering, Operations &amp; AI Enablement [Boston]</t>
         </is>
       </c>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="F37" s="14" t="inlineStr">
         <is>
           <t>Burlington, MA</t>
         </is>
       </c>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="G37" s="14" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H37" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 21:40 UTC</t>
         </is>
       </c>
-      <c r="I37" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J37" s="13" t="inlineStr">
+      <c r="I37" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J37" s="16" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/sap-ixp-intern-%C2%A0customer-success-engineering-operations-ai-enablement-boston-at-sap-4402311007?refId=ofb0jzd8xWUoUtvr7A%2BwXQ%3D%3D&amp;trackingId=S%2Fo4FvRdeOcn00Jo5DVUBw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K37" s="11" t="inlineStr">
+      <c r="K37" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L37" s="11" t="inlineStr">
+      <c r="L37" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M37" s="11" t="inlineStr"/>
+      <c r="M37" s="14" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>linkedin_4403154707</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E38" s="14" t="inlineStr">
         <is>
           <t>Software Engineer Intern, Perception Data</t>
         </is>
       </c>
-      <c r="F38" s="11" t="inlineStr">
+      <c r="F38" s="14" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G38" s="11" t="inlineStr">
+      <c r="G38" s="14" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H38" s="11" t="inlineStr">
+      <c r="H38" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 02:21 UTC</t>
         </is>
       </c>
-      <c r="I38" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J38" s="13" t="inlineStr">
+      <c r="I38" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J38" s="16" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/software-engineer-intern-perception-data-at-zoox-4403154707?refId=ON4L5FUhksKAgylRRsNllQ%3D%3D&amp;trackingId=1%2F3OkqP%2Bu0PqHp9bXnlS0A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K38" s="11" t="inlineStr">
+      <c r="K38" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L38" s="11" t="inlineStr">
+      <c r="L38" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M38" s="11" t="inlineStr"/>
+      <c r="M38" s="14" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>linkedin_4402947451</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
         <is>
           <t>Rubrik</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E39" s="14" t="inlineStr">
         <is>
           <t>India Benefits &amp; AI Operations Intern</t>
         </is>
       </c>
-      <c r="F39" s="11" t="inlineStr">
+      <c r="F39" s="14" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G39" s="11" t="inlineStr">
+      <c r="G39" s="14" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="H39" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 11:40 UTC</t>
         </is>
       </c>
-      <c r="I39" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J39" s="13" t="inlineStr">
+      <c r="I39" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J39" s="16" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/india-benefits-ai-operations-intern-at-rubrik-4402947451?refId=9u2uyUYzyMZimaTtDELDWg%3D%3D&amp;trackingId=BjOmyeYm6McmUpzLwcES9g%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K39" s="11" t="inlineStr">
+      <c r="K39" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-rubrik-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L39" s="11" t="inlineStr">
+      <c r="L39" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-rubrik-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M39" s="11" t="inlineStr"/>
+      <c r="M39" s="14" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>linkedin_4390354006</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="inlineStr">
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
         <is>
           <t>Lila Sciences</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="E40" s="14" t="inlineStr">
         <is>
           <t>Intern, Next Gen AI Robotics</t>
         </is>
       </c>
-      <c r="F40" s="11" t="inlineStr">
+      <c r="F40" s="14" t="inlineStr">
         <is>
           <t>Cambridge, MA</t>
         </is>
       </c>
-      <c r="G40" s="11" t="inlineStr">
+      <c r="G40" s="14" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="H40" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 10:58 UTC</t>
         </is>
       </c>
-      <c r="I40" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J40" s="13" t="inlineStr">
+      <c r="I40" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J40" s="16" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/intern-next-gen-ai-robotics-at-lila-sciences-4390354006?refId=ZoXJQXesL%2FE%2B5EAGGzWfiA%3D%3D&amp;trackingId=FmSMwWhyyIaC52NsDwOCtw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K40" s="11" t="inlineStr">
+      <c r="K40" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-lila-sciences-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L40" s="11" t="inlineStr">
+      <c r="L40" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-lila-sciences-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M40" s="11" t="inlineStr"/>
+      <c r="M40" s="14" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>arbeitnow_ai-venture-development-tech-intern-berlin-100382</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C41" s="11" t="inlineStr">
+      <c r="C41" s="14" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="D41" s="11" t="inlineStr">
+      <c r="D41" s="14" t="inlineStr">
         <is>
           <t>Zeeg</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E41" s="14" t="inlineStr">
         <is>
           <t>AI &amp; Venture Development Tech Intern (w/m/d)</t>
         </is>
       </c>
-      <c r="F41" s="11" t="inlineStr">
+      <c r="F41" s="14" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="G41" s="11" t="inlineStr">
+      <c r="G41" s="14" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H41" s="11" t="inlineStr">
+      <c r="H41" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 10:30 UTC</t>
         </is>
       </c>
-      <c r="I41" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J41" s="13" t="inlineStr">
+      <c r="I41" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J41" s="16" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/zeeg/ai-venture-development-tech-intern-berlin-100382</t>
         </is>
       </c>
-      <c r="K41" s="11" t="inlineStr">
+      <c r="K41" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zeeg-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L41" s="11" t="inlineStr">
+      <c r="L41" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zeeg-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M41" s="11" t="inlineStr"/>
+      <c r="M41" s="14" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A42" s="14" t="inlineStr">
         <is>
           <t>linkedin_4391388054</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
         <is>
           <t>Mackenzie Investments</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E42" s="14" t="inlineStr">
         <is>
           <t>Fall Intern 2026 - Data Science (Toronto Office)</t>
         </is>
       </c>
-      <c r="F42" s="11" t="inlineStr">
+      <c r="F42" s="14" t="inlineStr">
         <is>
           <t>Greater Toronto Area, Canada</t>
         </is>
       </c>
-      <c r="G42" s="11" t="inlineStr">
+      <c r="G42" s="14" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H42" s="11" t="inlineStr">
+      <c r="H42" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 14:00 UTC</t>
         </is>
       </c>
-      <c r="I42" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J42" s="13" t="inlineStr">
+      <c r="I42" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J42" s="16" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/fall-intern-2026-data-science-toronto-office-at-mackenzie-investments-4391388054?refId=ay8O%2Bgf7Gtfb1Rpr3XZOhg%3D%3D&amp;trackingId=O%2F%2FJTpCmUhvp4jSfNkV5bg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K42" s="11" t="inlineStr">
+      <c r="K42" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-mackenzie-investments-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L42" s="11" t="inlineStr">
+      <c r="L42" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-mackenzie-investments-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M42" s="11" t="inlineStr"/>
+      <c r="M42" s="14" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>linkedin_4390747937</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="inlineStr">
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
         <is>
           <t>BCG X</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="14" t="inlineStr">
         <is>
           <t>Visiting Forward Deployed AI Engineer, Internship, Germany - BCG X</t>
         </is>
       </c>
-      <c r="F43" s="11" t="inlineStr">
+      <c r="F43" s="14" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G43" s="11" t="inlineStr">
+      <c r="G43" s="14" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr">
+      <c r="H43" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 13:51 UTC</t>
         </is>
       </c>
-      <c r="I43" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J43" s="13" t="inlineStr">
+      <c r="I43" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J43" s="16" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/visiting-forward-deployed-ai-engineer-internship-germany-bcg-x-at-bcg-x-4390747937?refId=1JxxxPqdlRpkbbaCzu2YGQ%3D%3D&amp;trackingId=7x%2BVQU%2BWOh9IPaVXWJkc5g%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K43" s="11" t="inlineStr">
+      <c r="K43" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bcg-x-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L43" s="11" t="inlineStr">
+      <c r="L43" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bcg-x-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M43" s="11" t="inlineStr"/>
+      <c r="M43" s="14" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="A44" s="14" t="inlineStr">
         <is>
           <t>linkedin_4402726053</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
         <is>
           <t>targetjobs UK</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E44" s="14" t="inlineStr">
         <is>
           <t>Internship: AI/ML for Ionospheric TEC Modelling</t>
         </is>
       </c>
-      <c r="F44" s="11" t="inlineStr">
+      <c r="F44" s="14" t="inlineStr">
         <is>
           <t>Reigate, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G44" s="11" t="inlineStr">
+      <c r="G44" s="14" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr">
+      <c r="H44" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 14:25 UTC</t>
         </is>
       </c>
-      <c r="I44" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J44" s="13" t="inlineStr">
+      <c r="I44" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J44" s="16" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/internship-ai-ml-for-ionospheric-tec-modelling-at-targetjobs-uk-4402726053?refId=a1g6hMZsvI1y2Eje2OvLAA%3D%3D&amp;trackingId=IVJSJGE7Non8cohorDs%2F5A%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K44" s="11" t="inlineStr">
+      <c r="K44" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-targetjobs-uk-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L44" s="11" t="inlineStr">
+      <c r="L44" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-targetjobs-uk-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M44" s="11" t="inlineStr"/>
+      <c r="M44" s="14" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>linkedin_4400837114</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
         <is>
           <t>Innovexis</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="14" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F45" s="11" t="inlineStr">
+      <c r="F45" s="14" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G45" s="11" t="inlineStr">
+      <c r="G45" s="14" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="H45" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 13:04 UTC</t>
         </is>
       </c>
-      <c r="I45" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J45" s="13" t="inlineStr">
+      <c r="I45" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J45" s="16" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-innovexis-4400837114?refId=CVM89%2F3%2F%2BshqMJLc4IfFMg%3D%3D&amp;trackingId=j9WpQwI4k1ip7aRr%2Fv5Img%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K45" s="11" t="inlineStr">
+      <c r="K45" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-innovexis-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L45" s="11" t="inlineStr">
+      <c r="L45" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-innovexis-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M45" s="11" t="inlineStr"/>
+      <c r="M45" s="14" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="inlineStr">
+      <c r="A46" s="14" t="inlineStr">
         <is>
           <t>linkedin_4391074158</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D46" s="11" t="inlineStr">
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
         <is>
           <t>BMW Group</t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr">
+      <c r="E46" s="14" t="inlineStr">
         <is>
           <t>Intern IT Technology, Sales Volume Planning &amp; AI Support (f/m/x)</t>
         </is>
       </c>
-      <c r="F46" s="11" t="inlineStr">
+      <c r="F46" s="14" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G46" s="11" t="inlineStr">
+      <c r="G46" s="14" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H46" s="11" t="inlineStr">
+      <c r="H46" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 12:45 UTC</t>
         </is>
       </c>
-      <c r="I46" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J46" s="13" t="inlineStr">
+      <c r="I46" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J46" s="16" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/intern-it-technology-sales-volume-planning-ai-support-f-m-x-at-bmw-group-4391074158?refId=tHG5EqbLn3IDBqsSj%2FsUUg%3D%3D&amp;trackingId=OakOlgDcU0hWTRXcoLe3UA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K46" s="11" t="inlineStr">
+      <c r="K46" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bmw-group-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L46" s="11" t="inlineStr">
+      <c r="L46" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bmw-group-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M46" s="11" t="inlineStr"/>
+      <c r="M46" s="14" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="11" t="inlineStr">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>linkedin_4402725075</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C47" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D47" s="11" t="inlineStr">
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr">
         <is>
           <t>DARE</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E47" s="14" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F47" s="11" t="inlineStr">
+      <c r="F47" s="14" t="inlineStr">
         <is>
           <t>WP. Kuala Lumpur, Federal Territory of Kuala Lumpur, Malaysia</t>
         </is>
       </c>
-      <c r="G47" s="11" t="inlineStr">
+      <c r="G47" s="14" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H47" s="11" t="inlineStr">
+      <c r="H47" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 14:36 UTC</t>
         </is>
       </c>
-      <c r="I47" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J47" s="13" t="inlineStr">
+      <c r="I47" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J47" s="16" t="inlineStr">
         <is>
           <t>https://my.linkedin.com/jobs/view/research-intern-at-dare-4402725075?refId=xbzZXyF6FfcYy036eklDWw%3D%3D&amp;trackingId=QRt5DhbLSINvmHia0jEWIg%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K47" s="11" t="inlineStr">
+      <c r="K47" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dare-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L47" s="11" t="inlineStr">
+      <c r="L47" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dare-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M47" s="11" t="inlineStr"/>
+      <c r="M47" s="14" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="inlineStr">
+      <c r="A48" s="14" t="inlineStr">
         <is>
           <t>linkedin_4402745391</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C48" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="inlineStr">
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
         <is>
           <t>Huawei Technologies Research &amp; Development (UK) Ltd</t>
         </is>
       </c>
-      <c r="E48" s="11" t="inlineStr">
+      <c r="E48" s="14" t="inlineStr">
         <is>
           <t>Research Intern - Computer Vision</t>
         </is>
       </c>
-      <c r="F48" s="11" t="inlineStr">
+      <c r="F48" s="14" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G48" s="11" t="inlineStr">
+      <c r="G48" s="14" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H48" s="11" t="inlineStr">
+      <c r="H48" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 18:42 UTC</t>
         </is>
       </c>
-      <c r="I48" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J48" s="13" t="inlineStr">
+      <c r="I48" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/research-intern-computer-vision-at-huawei-technologies-research-development-uk-ltd-4402745391?refId=rRtCMQFBU%2FNi7vc62x5Nhg%3D%3D&amp;trackingId=%2Bt1We%2BmKhWHyXION%2FWwQVg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K48" s="11" t="inlineStr">
+      <c r="K48" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-huawei-technologies-research-development-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L48" s="11" t="inlineStr">
+      <c r="L48" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-huawei-technologies-research-development-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M48" s="11" t="inlineStr"/>
+      <c r="M48" s="14" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="11" t="inlineStr">
+      <c r="A49" s="14" t="inlineStr">
         <is>
           <t>linkedin_4402366780</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="inlineStr">
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
         <is>
           <t>Binance</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E49" s="14" t="inlineStr">
         <is>
           <t>Binance Accelerator Program - Data Scientist (LLM &amp; Trading)</t>
         </is>
       </c>
-      <c r="F49" s="11" t="inlineStr">
+      <c r="F49" s="14" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G49" s="11" t="inlineStr">
+      <c r="G49" s="14" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H49" s="11" t="inlineStr">
+      <c r="H49" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 09:43 UTC</t>
         </is>
       </c>
-      <c r="I49" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J49" s="13" t="inlineStr">
+      <c r="I49" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/binance-accelerator-program-data-scientist-llm-trading-at-binance-4402366780?refId=bc%2BXeBTeIKMQJTmlLFwbZQ%3D%3D&amp;trackingId=9UuyRRCEPapWNu6VKdZC5A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K49" s="11" t="inlineStr">
+      <c r="K49" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-binance-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L49" s="11" t="inlineStr">
+      <c r="L49" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-binance-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M49" s="11" t="inlineStr"/>
+      <c r="M49" s="14" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="11" t="inlineStr">
+      <c r="A50" s="14" t="inlineStr">
         <is>
           <t>linkedin_4382411039</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C50" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="inlineStr">
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
         <is>
           <t>The Walt Disney Company</t>
         </is>
       </c>
-      <c r="E50" s="11" t="inlineStr">
+      <c r="E50" s="14" t="inlineStr">
         <is>
           <t>Intern, APAC Data Analytics &amp; Insights (Content Analytics) -  Jul to Dec 2026</t>
         </is>
       </c>
-      <c r="F50" s="11" t="inlineStr">
+      <c r="F50" s="14" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G50" s="11" t="inlineStr">
+      <c r="G50" s="14" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H50" s="11" t="inlineStr">
+      <c r="H50" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 23:55 UTC</t>
         </is>
       </c>
-      <c r="I50" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J50" s="13" t="inlineStr">
+      <c r="I50" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/intern-apac-data-analytics-insights-content-analytics-jul-to-dec-2026-at-the-walt-disney-company-4382411039?refId=JBvXH2fNOamnO4WZI1Y0ew%3D%3D&amp;trackingId=Rs%2FdjczlbLYSYtCwY%2F%2FJyA%3D%3D&amp;position=7&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K50" s="11" t="inlineStr">
+      <c r="K50" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-the-walt-disney-company-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L50" s="11" t="inlineStr">
+      <c r="L50" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-the-walt-disney-company-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M50" s="11" t="inlineStr"/>
+      <c r="M50" s="14" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="11" t="inlineStr">
+      <c r="A51" s="14" t="inlineStr">
         <is>
           <t>linkedin_4402305263</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C51" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="inlineStr">
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E51" s="14" t="inlineStr">
         <is>
           <t>SAP iXp Intern - Software Developer (Agentic AI &amp; LLM systems)</t>
         </is>
       </c>
-      <c r="F51" s="11" t="inlineStr">
+      <c r="F51" s="14" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G51" s="11" t="inlineStr">
+      <c r="G51" s="14" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H51" s="11" t="inlineStr">
+      <c r="H51" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 21:40 UTC</t>
         </is>
       </c>
-      <c r="I51" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J51" s="13" t="inlineStr">
+      <c r="I51" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/sap-ixp-intern-software-developer-agentic-ai-llm-systems-at-sap-4402305263?refId=zBXuSSlfFyuxcdEqyfeS8g%3D%3D&amp;trackingId=Imq%2FVHMQWkkoDZp5%2BnATSA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K51" s="11" t="inlineStr">
+      <c r="K51" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L51" s="11" t="inlineStr">
+      <c r="L51" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M51" s="11" t="inlineStr"/>
+      <c r="M51" s="14" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="11" t="inlineStr">
+      <c r="A52" s="14" t="inlineStr">
         <is>
           <t>linkedin_4400467080</t>
         </is>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C52" s="11" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
         <is>
           <t>Saama</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E52" s="14" t="inlineStr">
         <is>
           <t>Intern for AI CoE</t>
         </is>
       </c>
-      <c r="F52" s="11" t="inlineStr">
+      <c r="F52" s="14" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G52" s="11" t="inlineStr">
+      <c r="G52" s="14" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H52" s="11" t="inlineStr">
+      <c r="H52" s="14" t="inlineStr">
         <is>
           <t>2026-04-16 19:45 UTC</t>
         </is>
       </c>
-      <c r="I52" s="12" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J52" s="13" t="inlineStr">
+      <c r="I52" s="15" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/intern-for-ai-coe-at-saama-4400467080?refId=7CvDuV2%2BR%2FzyGozq4UNPPw%3D%3D&amp;trackingId=Ls9yWFAC8lVRx8bmapJfLA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K52" s="11" t="inlineStr">
+      <c r="K52" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-saama-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L52" s="11" t="inlineStr">
+      <c r="L52" s="14" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-saama-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M52" s="11" t="inlineStr"/>
+      <c r="M52" s="14" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
@@ -4299,6 +4308,636 @@
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="17" t="inlineStr">
+        <is>
+          <t>linkedin_4403008384</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-18 19:59</t>
+        </is>
+      </c>
+      <c r="C61" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D61" s="17" t="inlineStr">
+        <is>
+          <t>VEDANTA MOBILITY</t>
+        </is>
+      </c>
+      <c r="E61" s="17" t="inlineStr">
+        <is>
+          <t>Founding Psychology Interns | AI Prototype (Govt Proposal – Dubai)</t>
+        </is>
+      </c>
+      <c r="F61" s="17" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India</t>
+        </is>
+      </c>
+      <c r="G61" s="17" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H61" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-18 08:13 UTC</t>
+        </is>
+      </c>
+      <c r="I61" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J61" s="19" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/founding-psychology-interns-ai-prototype-govt-proposal-%E2%80%93-dubai-at-vedanta-mobility-4403008384?refId=moHjgKNH%2BrT9YT5JNnyyqw%3D%3D&amp;trackingId=RUjUOgXLH%2BLJwdPLtKtAMQ%3D%3D&amp;position=13&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K61" s="17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-vedanta-mobility-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="L61" s="17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-vedanta-mobility-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="M61" s="17" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="inlineStr">
+        <is>
+          <t>linkedin_4393616864</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-18 19:59</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D62" s="17" t="inlineStr">
+        <is>
+          <t>Medidata Solutions</t>
+        </is>
+      </c>
+      <c r="E62" s="17" t="inlineStr">
+        <is>
+          <t>Data Science Intern</t>
+        </is>
+      </c>
+      <c r="F62" s="17" t="inlineStr">
+        <is>
+          <t>New York, United States</t>
+        </is>
+      </c>
+      <c r="G62" s="17" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H62" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-18 13:13 UTC</t>
+        </is>
+      </c>
+      <c r="I62" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J62" s="19" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/data-science-intern-at-medidata-solutions-4393616864?refId=sPMU%2B0UtbDUVjDHc3gXCxA%3D%3D&amp;trackingId=%2BVrdVCzEYQ3jJQvUf4VUtA%3D%3D&amp;position=2&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K62" s="17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-medidata-solutions-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="L62" s="17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-medidata-solutions-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="M62" s="17" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t>linkedin_4403819462</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-18 19:59</t>
+        </is>
+      </c>
+      <c r="C63" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D63" s="17" t="inlineStr">
+        <is>
+          <t>Calypso Commodities</t>
+        </is>
+      </c>
+      <c r="E63" s="17" t="inlineStr">
+        <is>
+          <t>Trading - Quant &amp; Engineering Intern (Client-Facing)</t>
+        </is>
+      </c>
+      <c r="F63" s="17" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G63" s="17" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H63" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-18 12:44 UTC</t>
+        </is>
+      </c>
+      <c r="I63" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J63" s="19" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/trading-quant-engineering-intern-client-facing-at-calypso-commodities-4403819462?refId=wb%2BADKYeCTj8bBBZgf97xw%3D%3D&amp;trackingId=o0ZBUwzyVOiml0tJPOsNww%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K63" s="17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-calypso-commodities-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="L63" s="17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-calypso-commodities-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="M63" s="17" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t>linkedin_4355269413</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-18 19:59</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D64" s="17" t="inlineStr">
+        <is>
+          <t>Temasek</t>
+        </is>
+      </c>
+      <c r="E64" s="17" t="inlineStr">
+        <is>
+          <t>Data Analytics/Science Intern, People Technology (Jun/Jul - Dec 2026)</t>
+        </is>
+      </c>
+      <c r="F64" s="17" t="inlineStr">
+        <is>
+          <t>Singapore, Singapore</t>
+        </is>
+      </c>
+      <c r="G64" s="17" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H64" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-18 10:35 UTC</t>
+        </is>
+      </c>
+      <c r="I64" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J64" s="19" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/data-analytics-science-intern-people-technology-jun-jul-dec-2026-at-temasek-4355269413?refId=emjtNEhTXLtOX%2BguWexSsg%3D%3D&amp;trackingId=DPHM%2FIJzKL0emfNJ1LMMoA%3D%3D&amp;position=4&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K64" s="17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-temasek-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="L64" s="17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-temasek-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="M64" s="17" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="17" t="inlineStr">
+        <is>
+          <t>linkedin_4403065097</t>
+        </is>
+      </c>
+      <c r="B65" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-18 19:59</t>
+        </is>
+      </c>
+      <c r="C65" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D65" s="17" t="inlineStr">
+        <is>
+          <t>BLACK TREE GAMING LIMITED</t>
+        </is>
+      </c>
+      <c r="E65" s="17" t="inlineStr">
+        <is>
+          <t>Data Scientist (ML)</t>
+        </is>
+      </c>
+      <c r="F65" s="17" t="inlineStr">
+        <is>
+          <t>Greater London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="G65" s="17" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H65" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-18 14:22 UTC</t>
+        </is>
+      </c>
+      <c r="I65" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J65" s="19" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/data-scientist-ml-at-black-tree-gaming-limited-4403065097?refId=X9Gb9UkVv%2BJtfDRc0dJPwA%3D%3D&amp;trackingId=Mfl%2BC%2FBN9DJehDmug19dGA%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K65" s="17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-black-tree-gaming-limited-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="L65" s="17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-black-tree-gaming-limited-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="M65" s="17" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>linkedin_4291533663</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-18 19:59</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D66" s="17" t="inlineStr">
+        <is>
+          <t>McKinsey &amp; Company</t>
+        </is>
+      </c>
+      <c r="E66" s="17" t="inlineStr">
+        <is>
+          <t>Praktikum als Fellow Intern - Tech &amp; AI (m/w/d)</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G66" s="17" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H66" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-18 09:49 UTC</t>
+        </is>
+      </c>
+      <c r="I66" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J66" s="19" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/praktikum-als-fellow-intern-tech-ai-m-w-d-at-mckinsey-company-4291533663?refId=UmiOr88gcWDNbqipJy2ZTg%3D%3D&amp;trackingId=UvtRxMXKlReoOEeGgMaEfA%3D%3D&amp;position=4&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K66" s="17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-mckinsey-company-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="L66" s="17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-mckinsey-company-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="M66" s="17" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t>linkedin_4336838608</t>
+        </is>
+      </c>
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-18 19:59</t>
+        </is>
+      </c>
+      <c r="C67" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D67" s="17" t="inlineStr">
+        <is>
+          <t>Sendbird</t>
+        </is>
+      </c>
+      <c r="E67" s="17" t="inlineStr">
+        <is>
+          <t>AI Agent Engineer, Intern</t>
+        </is>
+      </c>
+      <c r="F67" s="17" t="inlineStr">
+        <is>
+          <t>Seoul, Seoul, South Korea</t>
+        </is>
+      </c>
+      <c r="G67" s="17" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H67" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-18 13:46 UTC</t>
+        </is>
+      </c>
+      <c r="I67" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J67" s="19" t="inlineStr">
+        <is>
+          <t>https://kr.linkedin.com/jobs/view/ai-agent-engineer-intern-at-sendbird-4336838608?refId=%2F1qLChSVn3giUiiNusHaIQ%3D%3D&amp;trackingId=l6mUUvSfC97HjoyrA8uuqg%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K67" s="17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sendbird-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="L67" s="17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sendbird-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="M67" s="17" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t>linkedin_4372783510</t>
+        </is>
+      </c>
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-18 19:59</t>
+        </is>
+      </c>
+      <c r="C68" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D68" s="17" t="inlineStr">
+        <is>
+          <t>42dot</t>
+        </is>
+      </c>
+      <c r="E68" s="17" t="inlineStr">
+        <is>
+          <t>[MS/PhD Intern] AI Engineer (정규직 전환형)</t>
+        </is>
+      </c>
+      <c r="F68" s="17" t="inlineStr">
+        <is>
+          <t>Seongnam, Gyeonggi, South Korea</t>
+        </is>
+      </c>
+      <c r="G68" s="17" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H68" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-18 15:08 UTC</t>
+        </is>
+      </c>
+      <c r="I68" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J68" s="19" t="inlineStr">
+        <is>
+          <t>https://kr.linkedin.com/jobs/view/ms-phd-intern-ai-engineer-%EC%A0%95%EA%B7%9C%EC%A7%81-%EC%A0%84%ED%99%98%ED%98%95-at-42dot-4372783510?refId=%2F1qLChSVn3giUiiNusHaIQ%3D%3D&amp;trackingId=TVYs5RWI1wgPuuVRiBioUA%3D%3D&amp;position=2&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K68" s="17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-42dot-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="L68" s="17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-42dot-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="M68" s="17" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="17" t="inlineStr">
+        <is>
+          <t>linkedin_4402753102</t>
+        </is>
+      </c>
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-18 19:59</t>
+        </is>
+      </c>
+      <c r="C69" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D69" s="17" t="inlineStr">
+        <is>
+          <t>Five9</t>
+        </is>
+      </c>
+      <c r="E69" s="17" t="inlineStr">
+        <is>
+          <t>Software Developer AI Insights Intern</t>
+        </is>
+      </c>
+      <c r="F69" s="17" t="inlineStr">
+        <is>
+          <t>San Ramon, CA</t>
+        </is>
+      </c>
+      <c r="G69" s="17" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H69" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:56 UTC</t>
+        </is>
+      </c>
+      <c r="I69" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J69" s="19" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/software-developer-ai-insights-intern-at-five9-4402753102?refId=%2FiKmLsIvYp2TclUyf8MJwg%3D%3D&amp;trackingId=X2UMBr3jE86J9JmPv42B2w%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K69" s="17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-five9-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="L69" s="17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-five9-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="M69" s="17" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="17" t="inlineStr">
+        <is>
+          <t>linkedin_4403519373</t>
+        </is>
+      </c>
+      <c r="B70" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-18 19:59</t>
+        </is>
+      </c>
+      <c r="C70" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D70" s="17" t="inlineStr">
+        <is>
+          <t>Zoox</t>
+        </is>
+      </c>
+      <c r="E70" s="17" t="inlineStr">
+        <is>
+          <t>PhD Research Intern, Physical AI in Perception</t>
+        </is>
+      </c>
+      <c r="F70" s="17" t="inlineStr">
+        <is>
+          <t>Foster City, CA</t>
+        </is>
+      </c>
+      <c r="G70" s="17" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H70" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:07 UTC</t>
+        </is>
+      </c>
+      <c r="I70" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J70" s="19" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/phd-research-intern-physical-ai-in-perception-at-zoox-4403519373?refId=LChV34e%2Bd7cvBpZ%2FbJAZjw%3D%3D&amp;trackingId=vlvuJ54NQfvZvNY3pNGqNw%3D%3D&amp;position=2&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K70" s="17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="L70" s="17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-18.pdf</t>
+        </is>
+      </c>
+      <c r="M70" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -4361,6 +5000,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId69"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -83,10 +83,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -507,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,3721 +602,3721 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>linkedin_4401809501</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F2" s="14" t="inlineStr">
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="17" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H2" s="14" t="inlineStr">
+      <c r="H2" s="17" t="inlineStr">
         <is>
           <t>2026-04-15 22:19 UTC</t>
         </is>
       </c>
-      <c r="I2" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J2" s="16" t="inlineStr">
+      <c r="I2" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J2" s="19" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/research-intern-at-skycliff-it-4401809501?refId=HHi6SaK1fggu3E9dI3MtVg%3D%3D&amp;trackingId=r33pSo29lHStfk9FH82pyw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K2" s="14" t="inlineStr">
+      <c r="K2" s="17" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L2" s="14" t="inlineStr">
+      <c r="L2" s="17" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M2" s="14" t="inlineStr"/>
+      <c r="M2" s="17" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>linkedin_4402568578</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>Webs X UM</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F3" s="14" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="17" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H3" s="14" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>2026-04-15 19:20 UTC</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J3" s="16" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J3" s="19" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-webs-x-um-4402568578?refId=g89JM6cY8EFeoLk6JL5tVg%3D%3D&amp;trackingId=uFZVJJX7SSI0XCPFIrLqmA%3D%3D&amp;position=19&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K3" s="14" t="inlineStr">
+      <c r="K3" s="17" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-webs-x-um-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L3" s="14" t="inlineStr">
+      <c r="L3" s="17" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-webs-x-um-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M3" s="14" t="inlineStr"/>
+      <c r="M3" s="17" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>linkedin_4399996740</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>SUN PHARMA</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>Becario</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>Mexico City, Mexico</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>2026-04-15 17:59 UTC</t>
         </is>
       </c>
-      <c r="I4" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="I4" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>https://mx.linkedin.com/jobs/view/becario-at-sun-pharma-4399996740?refId=g89JM6cY8EFeoLk6JL5tVg%3D%3D&amp;trackingId=sZ0Fkcf4RHuIpzXu4mJRNg%3D%3D&amp;position=22&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="17" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-sun-pharma-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="L4" s="17" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-sun-pharma-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M4" s="14" t="inlineStr"/>
+      <c r="M4" s="17" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>linkedin_4399975959</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>LS Direct</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>Data Analytics Intern</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>Suffern, NY</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H5" s="14" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t>2026-04-15 14:26 UTC</t>
         </is>
       </c>
-      <c r="I5" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J5" s="16" t="inlineStr">
+      <c r="I5" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J5" s="19" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-analytics-intern-at-ls-direct-4399975959?refId=pg0ll3e89fatVyUznLcdpw%3D%3D&amp;trackingId=5b41IoyQfIfx3Tu42domiQ%3D%3D&amp;position=23&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K5" s="14" t="inlineStr">
+      <c r="K5" s="17" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-ls-direct-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L5" s="14" t="inlineStr">
+      <c r="L5" s="17" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-ls-direct-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M5" s="14" t="inlineStr"/>
+      <c r="M5" s="17" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>linkedin_4370546718</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>Clarivate</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>Lead Data Scientist</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>Barcelona, Catalonia, Spain</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>2026-04-15 12:16 UTC</t>
         </is>
       </c>
-      <c r="I6" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J6" s="19" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/lead-data-scientist-at-clarivate-4370546718?refId=FyyqQfduMQ8KZ7B5LeF0UQ%3D%3D&amp;trackingId=1i1kXdbV7SMunyFTiSJHJg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K6" s="14" t="inlineStr">
+      <c r="K6" s="17" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-clarivate-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L6" s="14" t="inlineStr">
+      <c r="L6" s="17" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-clarivate-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M6" s="14" t="inlineStr"/>
+      <c r="M6" s="17" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>linkedin_4389810164</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>Vitality</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>Senior Data Scientist - 12 Month FTC</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t>2026-04-15 09:39 UTC</t>
         </is>
       </c>
-      <c r="I7" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J7" s="19" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/senior-data-scientist-12-month-ftc-at-vitality-4389810164?refId=FPz%2BrPoaQeqgXBm%2FfOzGGA%3D%3D&amp;trackingId=yVNh55t2X2xocDT4i6HDqQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K7" s="14" t="inlineStr">
+      <c r="K7" s="17" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-vitality-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L7" s="14" t="inlineStr">
+      <c r="L7" s="17" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-vitality-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M7" s="14" t="inlineStr"/>
+      <c r="M7" s="17" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>linkedin_4399952059</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>traide AI</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>AI Associate (f/m/x) (B2B SaaS Startup) - Intern/Working Student</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>2026-04-15 07:04 UTC</t>
         </is>
       </c>
-      <c r="I8" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="I8" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J8" s="19" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/ai-associate-f-m-x-b2b-saas-startup-intern-working-student-at-traide-ai-4399952059?refId=x0uIkl175n0hipT17L%2FGRw%3D%3D&amp;trackingId=8kdzUQgW%2B7rCk2pO2oIErg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K8" s="14" t="inlineStr">
+      <c r="K8" s="17" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-traide-ai-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L8" s="14" t="inlineStr">
+      <c r="L8" s="17" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-traide-ai-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M8" s="14" t="inlineStr"/>
+      <c r="M8" s="17" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>linkedin_4399933254</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>Briink</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>Growth Intern (Merantix AI Campus)</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G9" s="17" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t>2026-04-15 05:03 UTC</t>
         </is>
       </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J9" s="19" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/growth-intern-merantix-ai-campus-at-briink-4399933254?refId=x0uIkl175n0hipT17L%2FGRw%3D%3D&amp;trackingId=qEKtyJNA03Kbr6AYDlhsBw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K9" s="14" t="inlineStr">
+      <c r="K9" s="17" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-briink-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L9" s="14" t="inlineStr">
+      <c r="L9" s="17" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-briink-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M9" s="14" t="inlineStr"/>
+      <c r="M9" s="17" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>linkedin_4400429367</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>Tata Consultancy Services</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>HR -Data Scientist</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>Renton, WA</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 16:56 UTC</t>
         </is>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="I10" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J10" s="19" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/hr-data-scientist-at-tata-consultancy-services-4400429367?refId=vJILgNySaXYUQknbyaKZZQ%3D%3D&amp;trackingId=7cZ0KYh8Sv5%2Fh6%2FG86%2BLug%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K10" s="14" t="inlineStr">
+      <c r="K10" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-tata-consultancy-services-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L10" s="14" t="inlineStr">
+      <c r="L10" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-tata-consultancy-services-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M10" s="14" t="inlineStr"/>
+      <c r="M10" s="17" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>linkedin_4390814627</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Criteo</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>Barcelona, Catalonia, Spain</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 12:19 UTC</t>
         </is>
       </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J11" s="19" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/data-analyst-intern-at-criteo-4390814627?refId=PCZWvfzZIzNkx6giU9jTsA%3D%3D&amp;trackingId=T%2FMog6vtgG8P3ihAU9b1uQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K11" s="14" t="inlineStr">
+      <c r="K11" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-criteo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L11" s="14" t="inlineStr">
+      <c r="L11" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-criteo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M11" s="14" t="inlineStr"/>
+      <c r="M11" s="17" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>linkedin_4402983364</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>Brussels, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr">
+      <c r="H12" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
+      <c r="I12" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J12" s="19" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402983364?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=zV4sJQyNyQg%2FS%2BYm6Ba9Eg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K12" s="14" t="inlineStr">
+      <c r="K12" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L12" s="14" t="inlineStr">
+      <c r="L12" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M12" s="14" t="inlineStr"/>
+      <c r="M12" s="17" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>linkedin_4390725142</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>Boston Consulting Group (BCG)</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>Forward Deployed AI Engineer, Internship, United Kingdom - BCG X</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="H13" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 16:24 UTC</t>
         </is>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J13" s="19" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/forward-deployed-ai-engineer-internship-united-kingdom-bcg-x-at-boston-consulting-group-bcg-4390725142?refId=YHAZO5vAx9Qtg1RXMma%2F%2BA%3D%3D&amp;trackingId=E8kiSHzcdYe%2FH6s%2FCkGtMw%3D%3D&amp;position=7&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K13" s="14" t="inlineStr">
+      <c r="K13" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L13" s="14" t="inlineStr">
+      <c r="L13" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M13" s="14" t="inlineStr"/>
+      <c r="M13" s="17" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>linkedin_4400428064</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>Fanatics</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 16:16 UTC</t>
         </is>
       </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J14" s="19" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/data-scientist-at-fanatics-4400428064?refId=SNMwEp9%2FBozAkX4FBnhJwQ%3D%3D&amp;trackingId=cAX0aKWV%2FBX1fvQzm%2FkEMg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K14" s="14" t="inlineStr">
+      <c r="K14" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-fanatics-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L14" s="14" t="inlineStr">
+      <c r="L14" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-fanatics-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M14" s="14" t="inlineStr"/>
+      <c r="M14" s="17" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>linkedin_4390730090</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>Boston Consulting Group (BCG)</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>Forward Deployed AI Scientist, Internship, United Kingdom - BCG X</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="G15" s="17" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="H15" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 13:57 UTC</t>
         </is>
       </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
+      <c r="I15" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J15" s="19" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/forward-deployed-ai-scientist-internship-united-kingdom-bcg-x-at-boston-consulting-group-bcg-4390730090?refId=YHAZO5vAx9Qtg1RXMma%2F%2BA%3D%3D&amp;trackingId=m50MzwjbYzUmAv7nJVAKgA%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K15" s="14" t="inlineStr">
+      <c r="K15" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L15" s="14" t="inlineStr">
+      <c r="L15" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M15" s="14" t="inlineStr"/>
+      <c r="M15" s="17" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>linkedin_4402138096</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>Kelly Tutors</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>Research Intern (3-5hrs/week, flexible)</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="17" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="H16" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 14:40 UTC</t>
         </is>
       </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
+      <c r="I16" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J16" s="19" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/research-intern-3-5hrs-week-flexible-at-kelly-tutors-4402138096?refId=HmOS2YEHUH3GOVent1txqw%3D%3D&amp;trackingId=3XBXMUoBdiHeRL4qw%2B2qRw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K16" s="14" t="inlineStr">
+      <c r="K16" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-kelly-tutors-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L16" s="14" t="inlineStr">
+      <c r="L16" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-kelly-tutors-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M16" s="14" t="inlineStr"/>
+      <c r="M16" s="17" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>linkedin_4378557045</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>Fund for Public Health in NYC</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="17" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H17" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 16:13 UTC</t>
         </is>
       </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
+      <c r="I17" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J17" s="19" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-scientist-at-fund-for-public-health-in-nyc-4378557045?refId=JsndNRa0tnfF7dsuxv62wA%3D%3D&amp;trackingId=Pmgt6JCxYmQun5Uv6%2BLbiQ%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K17" s="14" t="inlineStr">
+      <c r="K17" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-fund-for-public-health-in-nyc-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L17" s="14" t="inlineStr">
+      <c r="L17" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-fund-for-public-health-in-nyc-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M17" s="14" t="inlineStr"/>
+      <c r="M17" s="17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>linkedin_4402977457</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>Brussels, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
+      <c r="G18" s="17" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H18" s="14" t="inlineStr">
+      <c r="H18" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
+      <c r="I18" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J18" s="19" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402977457?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=gL9sbQh%2FaLMmzvXjuO71WQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K18" s="14" t="inlineStr">
+      <c r="K18" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L18" s="14" t="inlineStr">
+      <c r="L18" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M18" s="14" t="inlineStr"/>
+      <c r="M18" s="17" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>linkedin_4371210537</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>Gildan</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>Intern, ERP GenAI</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G19" s="17" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr">
+      <c r="H19" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 15:23 UTC</t>
         </is>
       </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
+      <c r="I19" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J19" s="19" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/intern-erp-genai-at-gildan-4371210537?refId=jteS%2Ft3Cmc2XLVMFToCpKw%3D%3D&amp;trackingId=OQGg%2Bob2m9u4kkbRcgWoUw%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K19" s="14" t="inlineStr">
+      <c r="K19" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-gildan-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L19" s="14" t="inlineStr">
+      <c r="L19" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-gildan-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M19" s="14" t="inlineStr"/>
+      <c r="M19" s="17" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>linkedin_4402974624</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>Uccle, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G20" s="14" t="inlineStr">
+      <c r="G20" s="17" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H20" s="14" t="inlineStr">
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
+      <c r="I20" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J20" s="19" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402974624?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=RJfkVsuYxv4DqyEhPJ367g%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K20" s="14" t="inlineStr">
+      <c r="K20" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L20" s="14" t="inlineStr">
+      <c r="L20" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M20" s="14" t="inlineStr"/>
+      <c r="M20" s="17" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>linkedin_4402174633</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>Cloudera</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>AI Enablement Intern (Ireland Based)</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>Greater Dublin</t>
         </is>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="G21" s="17" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="H21" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 18:24 UTC</t>
         </is>
       </c>
-      <c r="I21" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
+      <c r="I21" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J21" s="19" t="inlineStr">
         <is>
           <t>https://ie.linkedin.com/jobs/view/ai-enablement-intern-ireland-based-at-cloudera-4402174633?refId=d9iDz5spYJk0nIor701k5g%3D%3D&amp;trackingId=6OZvFiMQ12VqIzY6EqUe7A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K21" s="14" t="inlineStr">
+      <c r="K21" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-cloudera-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L21" s="14" t="inlineStr">
+      <c r="L21" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-cloudera-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M21" s="14" t="inlineStr"/>
+      <c r="M21" s="17" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>linkedin_4403115250</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>PhD Research Intern, Mapping Software</t>
         </is>
       </c>
-      <c r="F22" s="14" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G22" s="14" t="inlineStr">
+      <c r="G22" s="17" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H22" s="14" t="inlineStr">
+      <c r="H22" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 19:55 UTC</t>
         </is>
       </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="I22" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J22" s="19" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-mapping-software-at-zoox-4403115250?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=67WsHxTIXiO%2ByWr0OYU7ug%3D%3D&amp;position=10&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K22" s="14" t="inlineStr">
+      <c r="K22" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L22" s="14" t="inlineStr">
+      <c r="L22" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M22" s="14" t="inlineStr"/>
+      <c r="M22" s="17" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>linkedin_4379373115</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>Woven by Toyota</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>Applied Scientist, Computer Vision and Generative Models, Vision AI (Internship)</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>Tokyo, Japan</t>
         </is>
       </c>
-      <c r="G23" s="14" t="inlineStr">
+      <c r="G23" s="17" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H23" s="14" t="inlineStr">
+      <c r="H23" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 14:55 UTC</t>
         </is>
       </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
+      <c r="I23" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J23" s="19" t="inlineStr">
         <is>
           <t>https://jp.linkedin.com/jobs/view/applied-scientist-computer-vision-and-generative-models-vision-ai-internship-at-woven-by-toyota-4379373115?refId=4q6ISAXJ%2BcfZsJD688QZWg%3D%3D&amp;trackingId=pUnO9OuzZx4G6BOukom%2FQQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K23" s="14" t="inlineStr">
+      <c r="K23" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-woven-by-toyota-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L23" s="14" t="inlineStr">
+      <c r="L23" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-woven-by-toyota-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M23" s="14" t="inlineStr"/>
+      <c r="M23" s="17" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>linkedin_4325103488</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>Binance</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>Binance Accelerator Program - DevOps (Artificial Intelligence)</t>
         </is>
       </c>
-      <c r="F24" s="14" t="inlineStr">
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G24" s="14" t="inlineStr">
+      <c r="G24" s="17" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H24" s="14" t="inlineStr">
+      <c r="H24" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 12:13 UTC</t>
         </is>
       </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
+      <c r="I24" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J24" s="19" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/binance-accelerator-program-devops-artificial-intelligence-at-binance-4325103488?refId=KzaD5RMOfYQEZyaw6UmcpQ%3D%3D&amp;trackingId=8R4okHiG3RYyjThXHAqxIQ%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K24" s="14" t="inlineStr">
+      <c r="K24" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-binance-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L24" s="14" t="inlineStr">
+      <c r="L24" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-binance-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M24" s="14" t="inlineStr"/>
+      <c r="M24" s="17" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>linkedin_4400563251</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>Aylo</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>Sr. Full-Stack Data Scientist - Data Services</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>Greater Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G25" s="14" t="inlineStr">
+      <c r="G25" s="17" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H25" s="14" t="inlineStr">
+      <c r="H25" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 12:01 UTC</t>
         </is>
       </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
+      <c r="I25" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J25" s="19" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/sr-full-stack-data-scientist-data-services-at-aylo-4400563251?refId=3X2hsLwn0XF5%2BC4ABneEzA%3D%3D&amp;trackingId=aJHp5psMKfAaMJdxBAz5Hw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K25" s="14" t="inlineStr">
+      <c r="K25" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-aylo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L25" s="14" t="inlineStr">
+      <c r="L25" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-aylo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M25" s="14" t="inlineStr"/>
+      <c r="M25" s="17" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>linkedin_4400403670</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>Schneider Electric</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>Internship in Global AI Sales Enablement &amp; Analytics</t>
         </is>
       </c>
-      <c r="F26" s="14" t="inlineStr">
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>Warsaw, Mazowieckie, Poland</t>
         </is>
       </c>
-      <c r="G26" s="14" t="inlineStr">
+      <c r="G26" s="17" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H26" s="14" t="inlineStr">
+      <c r="H26" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 11:43 UTC</t>
         </is>
       </c>
-      <c r="I26" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
+      <c r="I26" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J26" s="19" t="inlineStr">
         <is>
           <t>https://pl.linkedin.com/jobs/view/internship-in-global-ai-sales-enablement-analytics-at-schneider-electric-4400403670?refId=0j6PfgagLJw81v3dQ49jXQ%3D%3D&amp;trackingId=ErR9yiUH1tcny4hRKbXl8A%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K26" s="14" t="inlineStr">
+      <c r="K26" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-schneider-electric-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L26" s="14" t="inlineStr">
+      <c r="L26" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-schneider-electric-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M26" s="14" t="inlineStr"/>
+      <c r="M26" s="17" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>linkedin_4297755027</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>Databricks</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>PhD GenAI Research Scientist Intern</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="G27" s="14" t="inlineStr">
+      <c r="G27" s="17" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H27" s="14" t="inlineStr">
+      <c r="H27" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 10:31 UTC</t>
         </is>
       </c>
-      <c r="I27" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J27" s="16" t="inlineStr">
+      <c r="I27" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J27" s="19" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-genai-research-scientist-intern-at-databricks-4297755027?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=UXoh9K97xsqO%2FzDhCy7Uug%3D%3D&amp;position=8&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K27" s="14" t="inlineStr">
+      <c r="K27" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-databricks-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L27" s="14" t="inlineStr">
+      <c r="L27" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-databricks-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M27" s="14" t="inlineStr"/>
+      <c r="M27" s="17" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>linkedin_4401843829</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>Tiger Brokers Singapore</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>Quantitative Investment Analyst Intern</t>
         </is>
       </c>
-      <c r="F28" s="14" t="inlineStr">
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G28" s="14" t="inlineStr">
+      <c r="G28" s="17" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H28" s="14" t="inlineStr">
+      <c r="H28" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 06:09 UTC</t>
         </is>
       </c>
-      <c r="I28" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
+      <c r="I28" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J28" s="19" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/quantitative-investment-analyst-intern-at-tiger-brokers-singapore-4401843829?refId=LJ4PwcXqLhd1gtOBe9ZVig%3D%3D&amp;trackingId=oxh8Ol2m1QKvqfrvl10UqA%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K28" s="14" t="inlineStr">
+      <c r="K28" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-tiger-brokers-singapore-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L28" s="14" t="inlineStr">
+      <c r="L28" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-tiger-brokers-singapore-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M28" s="14" t="inlineStr"/>
+      <c r="M28" s="17" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>linkedin_4400148847</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>Boomlet</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F29" s="14" t="inlineStr">
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>Mumbai, Maharashtra, India</t>
         </is>
       </c>
-      <c r="G29" s="14" t="inlineStr">
+      <c r="G29" s="17" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H29" s="14" t="inlineStr">
+      <c r="H29" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 05:24 UTC</t>
         </is>
       </c>
-      <c r="I29" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J29" s="16" t="inlineStr">
+      <c r="I29" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J29" s="19" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-boomlet-4400148847?refId=vAgiKqchg4pd6EgGGQ%2FF%2FA%3D%3D&amp;trackingId=IoHiSd1L28nXXarEd4gYfw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K29" s="14" t="inlineStr">
+      <c r="K29" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boomlet-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L29" s="14" t="inlineStr">
+      <c r="L29" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boomlet-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M29" s="14" t="inlineStr"/>
+      <c r="M29" s="17" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>linkedin_4401844394</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D30" s="14" t="inlineStr">
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>On-us</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>AI Business Analyst Summer Intern</t>
         </is>
       </c>
-      <c r="F30" s="14" t="inlineStr">
+      <c r="F30" s="17" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G30" s="14" t="inlineStr">
+      <c r="G30" s="17" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H30" s="14" t="inlineStr">
+      <c r="H30" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 04:56 UTC</t>
         </is>
       </c>
-      <c r="I30" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
+      <c r="I30" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J30" s="19" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/ai-business-analyst-summer-intern-at-on-us-4401844394?refId=lslydLUu5l8kXOktysXYaw%3D%3D&amp;trackingId=BQ%2BoYgH5QtZKBWGZQgBfNQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K30" s="14" t="inlineStr">
+      <c r="K30" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-on-us-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L30" s="14" t="inlineStr">
+      <c r="L30" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-on-us-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M30" s="14" t="inlineStr"/>
+      <c r="M30" s="17" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>linkedin_4401837715</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>Pathos Consultancy</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>Quantitative Research &amp; Development Internships</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F31" s="17" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G31" s="14" t="inlineStr">
+      <c r="G31" s="17" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H31" s="14" t="inlineStr">
+      <c r="H31" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 03:48 UTC</t>
         </is>
       </c>
-      <c r="I31" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J31" s="16" t="inlineStr">
+      <c r="I31" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J31" s="19" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/quantitative-research-development-internships-at-pathos-consultancy-4401837715?refId=KzaD5RMOfYQEZyaw6UmcpQ%3D%3D&amp;trackingId=eIGVr2dDtK%2F1o37C90xRoQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K31" s="14" t="inlineStr">
+      <c r="K31" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-pathos-consultancy-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L31" s="14" t="inlineStr">
+      <c r="L31" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-pathos-consultancy-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M31" s="14" t="inlineStr"/>
+      <c r="M31" s="17" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>linkedin_4402662606</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C32" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D32" s="14" t="inlineStr">
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>Stripe</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>PhD Machine Learning Engineer, Intern</t>
         </is>
       </c>
-      <c r="F32" s="14" t="inlineStr">
+      <c r="F32" s="17" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G32" s="14" t="inlineStr">
+      <c r="G32" s="17" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H32" s="14" t="inlineStr">
+      <c r="H32" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 02:23 UTC</t>
         </is>
       </c>
-      <c r="I32" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
+      <c r="I32" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J32" s="19" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-machine-learning-engineer-intern-at-stripe-4402662606?refId=vJILgNySaXYUQknbyaKZZQ%3D%3D&amp;trackingId=NDMzaPfHMoCKo5uxI3THcw%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K32" s="14" t="inlineStr">
+      <c r="K32" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L32" s="14" t="inlineStr">
+      <c r="L32" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M32" s="14" t="inlineStr"/>
+      <c r="M32" s="17" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>linkedin_4402953925</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="F33" s="17" t="inlineStr">
         <is>
           <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
-      <c r="G33" s="14" t="inlineStr">
+      <c r="G33" s="17" t="inlineStr">
         <is>
           <t>Middle_East</t>
         </is>
       </c>
-      <c r="H33" s="14" t="inlineStr">
+      <c r="H33" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 00:00 UTC</t>
         </is>
       </c>
-      <c r="I33" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J33" s="16" t="inlineStr">
+      <c r="I33" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J33" s="19" t="inlineStr">
         <is>
           <t>https://ae.linkedin.com/jobs/view/research-intern-at-skycliff-it-4402953925?refId=f%2BmSR6Ncm83dISKgoQTrbw%3D%3D&amp;trackingId=CdPOXElDD3wJKKeBZSdWsw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K33" s="14" t="inlineStr">
+      <c r="K33" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L33" s="14" t="inlineStr">
+      <c r="L33" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M33" s="14" t="inlineStr"/>
+      <c r="M33" s="17" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>linkedin_4402617206</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D34" s="14" t="inlineStr">
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>Stripe</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>PhD Machine Learning Engineer, Intern</t>
         </is>
       </c>
-      <c r="F34" s="14" t="inlineStr">
+      <c r="F34" s="17" t="inlineStr">
         <is>
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="G34" s="14" t="inlineStr">
+      <c r="G34" s="17" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H34" s="14" t="inlineStr">
+      <c r="H34" s="17" t="inlineStr">
         <is>
           <t>2026-04-15 20:25 UTC</t>
         </is>
       </c>
-      <c r="I34" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J34" s="16" t="inlineStr">
+      <c r="I34" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J34" s="19" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-machine-learning-engineer-intern-at-stripe-4402617206?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=yAc4U29LYJcrlQSUWWcubA%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K34" s="14" t="inlineStr">
+      <c r="K34" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L34" s="14" t="inlineStr">
+      <c r="L34" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M34" s="14" t="inlineStr"/>
+      <c r="M34" s="17" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>linkedin_4403183407</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C35" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
         <is>
           <t>Hardware FYI</t>
         </is>
       </c>
-      <c r="E35" s="14" t="inlineStr">
+      <c r="E35" s="17" t="inlineStr">
         <is>
           <t>Robotics - Applied Scientist II Intern / Co-op - 2026 (Robotics, Manipulation, Perception, Motion Planning, Autonomous Mobile Robots, Computer Vision, Machine Learning, Controls, and more)</t>
         </is>
       </c>
-      <c r="F35" s="14" t="inlineStr">
+      <c r="F35" s="17" t="inlineStr">
         <is>
           <t>Boston, MA</t>
         </is>
       </c>
-      <c r="G35" s="14" t="inlineStr">
+      <c r="G35" s="17" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H35" s="14" t="inlineStr">
+      <c r="H35" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 04:31 UTC</t>
         </is>
       </c>
-      <c r="I35" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J35" s="16" t="inlineStr">
+      <c r="I35" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J35" s="19" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/robotics-applied-scientist-ii-intern-co-op-2026-robotics-manipulation-perception-motion-planning-autonomous-mobile-robots-computer-vision-machine-learning-controls-and-more-at-hardware-fyi-4403183407?refId=s5WxXRPJ8QU7G2WPi2yNiw%3D%3D&amp;trackingId=rjd%2F8qdM5kQMmADtGJgSSw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K35" s="14" t="inlineStr">
+      <c r="K35" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-hardware-fyi-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L35" s="14" t="inlineStr">
+      <c r="L35" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-hardware-fyi-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M35" s="14" t="inlineStr"/>
+      <c r="M35" s="17" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>linkedin_4403153262</t>
         </is>
       </c>
-      <c r="B36" s="14" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C36" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D36" s="14" t="inlineStr">
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>Generali Malaysia</t>
         </is>
       </c>
-      <c r="E36" s="14" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr">
         <is>
           <t>Intern, IT (AI Engineering)</t>
         </is>
       </c>
-      <c r="F36" s="14" t="inlineStr">
+      <c r="F36" s="17" t="inlineStr">
         <is>
           <t>Federal Territory of Kuala Lumpur, Malaysia</t>
         </is>
       </c>
-      <c r="G36" s="14" t="inlineStr">
+      <c r="G36" s="17" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H36" s="14" t="inlineStr">
+      <c r="H36" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 00:47 UTC</t>
         </is>
       </c>
-      <c r="I36" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J36" s="16" t="inlineStr">
+      <c r="I36" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J36" s="19" t="inlineStr">
         <is>
           <t>https://my.linkedin.com/jobs/view/intern-it-ai-engineering-at-generali-malaysia-4403153262?refId=h4J9hFjDRjjPW7bUqRcUZQ%3D%3D&amp;trackingId=WmqITEtGX486sbNH6b%2BYmA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K36" s="14" t="inlineStr">
+      <c r="K36" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-generali-malaysia-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L36" s="14" t="inlineStr">
+      <c r="L36" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-generali-malaysia-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M36" s="14" t="inlineStr"/>
+      <c r="M36" s="17" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="inlineStr">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>linkedin_4402311007</t>
         </is>
       </c>
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B37" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D37" s="14" t="inlineStr">
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E37" s="14" t="inlineStr">
+      <c r="E37" s="17" t="inlineStr">
         <is>
           <t>SAP iXp Intern - Customer Success Engineering, Operations &amp; AI Enablement [Boston]</t>
         </is>
       </c>
-      <c r="F37" s="14" t="inlineStr">
+      <c r="F37" s="17" t="inlineStr">
         <is>
           <t>Burlington, MA</t>
         </is>
       </c>
-      <c r="G37" s="14" t="inlineStr">
+      <c r="G37" s="17" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H37" s="14" t="inlineStr">
+      <c r="H37" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 21:40 UTC</t>
         </is>
       </c>
-      <c r="I37" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J37" s="16" t="inlineStr">
+      <c r="I37" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J37" s="19" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/sap-ixp-intern-%C2%A0customer-success-engineering-operations-ai-enablement-boston-at-sap-4402311007?refId=ofb0jzd8xWUoUtvr7A%2BwXQ%3D%3D&amp;trackingId=S%2Fo4FvRdeOcn00Jo5DVUBw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K37" s="14" t="inlineStr">
+      <c r="K37" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L37" s="14" t="inlineStr">
+      <c r="L37" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M37" s="14" t="inlineStr"/>
+      <c r="M37" s="17" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="14" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>linkedin_4403154707</t>
         </is>
       </c>
-      <c r="B38" s="14" t="inlineStr">
+      <c r="B38" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C38" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D38" s="14" t="inlineStr">
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E38" s="14" t="inlineStr">
+      <c r="E38" s="17" t="inlineStr">
         <is>
           <t>Software Engineer Intern, Perception Data</t>
         </is>
       </c>
-      <c r="F38" s="14" t="inlineStr">
+      <c r="F38" s="17" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G38" s="14" t="inlineStr">
+      <c r="G38" s="17" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H38" s="14" t="inlineStr">
+      <c r="H38" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 02:21 UTC</t>
         </is>
       </c>
-      <c r="I38" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J38" s="16" t="inlineStr">
+      <c r="I38" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J38" s="19" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/software-engineer-intern-perception-data-at-zoox-4403154707?refId=ON4L5FUhksKAgylRRsNllQ%3D%3D&amp;trackingId=1%2F3OkqP%2Bu0PqHp9bXnlS0A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K38" s="14" t="inlineStr">
+      <c r="K38" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L38" s="14" t="inlineStr">
+      <c r="L38" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M38" s="14" t="inlineStr"/>
+      <c r="M38" s="17" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="14" t="inlineStr">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>linkedin_4402947451</t>
         </is>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B39" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C39" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D39" s="14" t="inlineStr">
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="inlineStr">
         <is>
           <t>Rubrik</t>
         </is>
       </c>
-      <c r="E39" s="14" t="inlineStr">
+      <c r="E39" s="17" t="inlineStr">
         <is>
           <t>India Benefits &amp; AI Operations Intern</t>
         </is>
       </c>
-      <c r="F39" s="14" t="inlineStr">
+      <c r="F39" s="17" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G39" s="14" t="inlineStr">
+      <c r="G39" s="17" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H39" s="14" t="inlineStr">
+      <c r="H39" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 11:40 UTC</t>
         </is>
       </c>
-      <c r="I39" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J39" s="16" t="inlineStr">
+      <c r="I39" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J39" s="19" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/india-benefits-ai-operations-intern-at-rubrik-4402947451?refId=9u2uyUYzyMZimaTtDELDWg%3D%3D&amp;trackingId=BjOmyeYm6McmUpzLwcES9g%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K39" s="14" t="inlineStr">
+      <c r="K39" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-rubrik-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L39" s="14" t="inlineStr">
+      <c r="L39" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-rubrik-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M39" s="14" t="inlineStr"/>
+      <c r="M39" s="17" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="14" t="inlineStr">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>linkedin_4390354006</t>
         </is>
       </c>
-      <c r="B40" s="14" t="inlineStr">
+      <c r="B40" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C40" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D40" s="14" t="inlineStr">
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t>Lila Sciences</t>
         </is>
       </c>
-      <c r="E40" s="14" t="inlineStr">
+      <c r="E40" s="17" t="inlineStr">
         <is>
           <t>Intern, Next Gen AI Robotics</t>
         </is>
       </c>
-      <c r="F40" s="14" t="inlineStr">
+      <c r="F40" s="17" t="inlineStr">
         <is>
           <t>Cambridge, MA</t>
         </is>
       </c>
-      <c r="G40" s="14" t="inlineStr">
+      <c r="G40" s="17" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H40" s="14" t="inlineStr">
+      <c r="H40" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 10:58 UTC</t>
         </is>
       </c>
-      <c r="I40" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
+      <c r="I40" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J40" s="19" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/intern-next-gen-ai-robotics-at-lila-sciences-4390354006?refId=ZoXJQXesL%2FE%2B5EAGGzWfiA%3D%3D&amp;trackingId=FmSMwWhyyIaC52NsDwOCtw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K40" s="14" t="inlineStr">
+      <c r="K40" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-lila-sciences-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L40" s="14" t="inlineStr">
+      <c r="L40" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-lila-sciences-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M40" s="14" t="inlineStr"/>
+      <c r="M40" s="17" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="inlineStr">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>arbeitnow_ai-venture-development-tech-intern-berlin-100382</t>
         </is>
       </c>
-      <c r="B41" s="14" t="inlineStr">
+      <c r="B41" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C41" s="14" t="inlineStr">
+      <c r="C41" s="17" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="D41" s="14" t="inlineStr">
+      <c r="D41" s="17" t="inlineStr">
         <is>
           <t>Zeeg</t>
         </is>
       </c>
-      <c r="E41" s="14" t="inlineStr">
+      <c r="E41" s="17" t="inlineStr">
         <is>
           <t>AI &amp; Venture Development Tech Intern (w/m/d)</t>
         </is>
       </c>
-      <c r="F41" s="14" t="inlineStr">
+      <c r="F41" s="17" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="G41" s="14" t="inlineStr">
+      <c r="G41" s="17" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H41" s="14" t="inlineStr">
+      <c r="H41" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 10:30 UTC</t>
         </is>
       </c>
-      <c r="I41" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J41" s="16" t="inlineStr">
+      <c r="I41" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J41" s="19" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/zeeg/ai-venture-development-tech-intern-berlin-100382</t>
         </is>
       </c>
-      <c r="K41" s="14" t="inlineStr">
+      <c r="K41" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zeeg-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L41" s="14" t="inlineStr">
+      <c r="L41" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zeeg-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M41" s="14" t="inlineStr"/>
+      <c r="M41" s="17" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="14" t="inlineStr">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>linkedin_4391388054</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
+      <c r="B42" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C42" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D42" s="14" t="inlineStr">
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
         <is>
           <t>Mackenzie Investments</t>
         </is>
       </c>
-      <c r="E42" s="14" t="inlineStr">
+      <c r="E42" s="17" t="inlineStr">
         <is>
           <t>Fall Intern 2026 - Data Science (Toronto Office)</t>
         </is>
       </c>
-      <c r="F42" s="14" t="inlineStr">
+      <c r="F42" s="17" t="inlineStr">
         <is>
           <t>Greater Toronto Area, Canada</t>
         </is>
       </c>
-      <c r="G42" s="14" t="inlineStr">
+      <c r="G42" s="17" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H42" s="14" t="inlineStr">
+      <c r="H42" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 14:00 UTC</t>
         </is>
       </c>
-      <c r="I42" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J42" s="16" t="inlineStr">
+      <c r="I42" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J42" s="19" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/fall-intern-2026-data-science-toronto-office-at-mackenzie-investments-4391388054?refId=ay8O%2Bgf7Gtfb1Rpr3XZOhg%3D%3D&amp;trackingId=O%2F%2FJTpCmUhvp4jSfNkV5bg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K42" s="14" t="inlineStr">
+      <c r="K42" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-mackenzie-investments-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L42" s="14" t="inlineStr">
+      <c r="L42" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-mackenzie-investments-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M42" s="14" t="inlineStr"/>
+      <c r="M42" s="17" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="14" t="inlineStr">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>linkedin_4390747937</t>
         </is>
       </c>
-      <c r="B43" s="14" t="inlineStr">
+      <c r="B43" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C43" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D43" s="14" t="inlineStr">
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
         <is>
           <t>BCG X</t>
         </is>
       </c>
-      <c r="E43" s="14" t="inlineStr">
+      <c r="E43" s="17" t="inlineStr">
         <is>
           <t>Visiting Forward Deployed AI Engineer, Internship, Germany - BCG X</t>
         </is>
       </c>
-      <c r="F43" s="14" t="inlineStr">
+      <c r="F43" s="17" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G43" s="14" t="inlineStr">
+      <c r="G43" s="17" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H43" s="14" t="inlineStr">
+      <c r="H43" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 13:51 UTC</t>
         </is>
       </c>
-      <c r="I43" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J43" s="16" t="inlineStr">
+      <c r="I43" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J43" s="19" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/visiting-forward-deployed-ai-engineer-internship-germany-bcg-x-at-bcg-x-4390747937?refId=1JxxxPqdlRpkbbaCzu2YGQ%3D%3D&amp;trackingId=7x%2BVQU%2BWOh9IPaVXWJkc5g%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K43" s="14" t="inlineStr">
+      <c r="K43" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bcg-x-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L43" s="14" t="inlineStr">
+      <c r="L43" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bcg-x-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M43" s="14" t="inlineStr"/>
+      <c r="M43" s="17" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="14" t="inlineStr">
+      <c r="A44" s="17" t="inlineStr">
         <is>
           <t>linkedin_4402726053</t>
         </is>
       </c>
-      <c r="B44" s="14" t="inlineStr">
+      <c r="B44" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C44" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D44" s="14" t="inlineStr">
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="inlineStr">
         <is>
           <t>targetjobs UK</t>
         </is>
       </c>
-      <c r="E44" s="14" t="inlineStr">
+      <c r="E44" s="17" t="inlineStr">
         <is>
           <t>Internship: AI/ML for Ionospheric TEC Modelling</t>
         </is>
       </c>
-      <c r="F44" s="14" t="inlineStr">
+      <c r="F44" s="17" t="inlineStr">
         <is>
           <t>Reigate, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G44" s="14" t="inlineStr">
+      <c r="G44" s="17" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H44" s="14" t="inlineStr">
+      <c r="H44" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 14:25 UTC</t>
         </is>
       </c>
-      <c r="I44" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J44" s="16" t="inlineStr">
+      <c r="I44" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J44" s="19" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/internship-ai-ml-for-ionospheric-tec-modelling-at-targetjobs-uk-4402726053?refId=a1g6hMZsvI1y2Eje2OvLAA%3D%3D&amp;trackingId=IVJSJGE7Non8cohorDs%2F5A%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K44" s="14" t="inlineStr">
+      <c r="K44" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-targetjobs-uk-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L44" s="14" t="inlineStr">
+      <c r="L44" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-targetjobs-uk-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M44" s="14" t="inlineStr"/>
+      <c r="M44" s="17" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="14" t="inlineStr">
+      <c r="A45" s="17" t="inlineStr">
         <is>
           <t>linkedin_4400837114</t>
         </is>
       </c>
-      <c r="B45" s="14" t="inlineStr">
+      <c r="B45" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C45" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D45" s="14" t="inlineStr">
+      <c r="C45" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="inlineStr">
         <is>
           <t>Innovexis</t>
         </is>
       </c>
-      <c r="E45" s="14" t="inlineStr">
+      <c r="E45" s="17" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F45" s="14" t="inlineStr">
+      <c r="F45" s="17" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G45" s="14" t="inlineStr">
+      <c r="G45" s="17" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H45" s="14" t="inlineStr">
+      <c r="H45" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 13:04 UTC</t>
         </is>
       </c>
-      <c r="I45" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J45" s="16" t="inlineStr">
+      <c r="I45" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J45" s="19" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-innovexis-4400837114?refId=CVM89%2F3%2F%2BshqMJLc4IfFMg%3D%3D&amp;trackingId=j9WpQwI4k1ip7aRr%2Fv5Img%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K45" s="14" t="inlineStr">
+      <c r="K45" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-innovexis-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L45" s="14" t="inlineStr">
+      <c r="L45" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-innovexis-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M45" s="14" t="inlineStr"/>
+      <c r="M45" s="17" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="14" t="inlineStr">
+      <c r="A46" s="17" t="inlineStr">
         <is>
           <t>linkedin_4391074158</t>
         </is>
       </c>
-      <c r="B46" s="14" t="inlineStr">
+      <c r="B46" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C46" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D46" s="14" t="inlineStr">
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="inlineStr">
         <is>
           <t>BMW Group</t>
         </is>
       </c>
-      <c r="E46" s="14" t="inlineStr">
+      <c r="E46" s="17" t="inlineStr">
         <is>
           <t>Intern IT Technology, Sales Volume Planning &amp; AI Support (f/m/x)</t>
         </is>
       </c>
-      <c r="F46" s="14" t="inlineStr">
+      <c r="F46" s="17" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G46" s="14" t="inlineStr">
+      <c r="G46" s="17" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H46" s="14" t="inlineStr">
+      <c r="H46" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 12:45 UTC</t>
         </is>
       </c>
-      <c r="I46" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J46" s="16" t="inlineStr">
+      <c r="I46" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J46" s="19" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/intern-it-technology-sales-volume-planning-ai-support-f-m-x-at-bmw-group-4391074158?refId=tHG5EqbLn3IDBqsSj%2FsUUg%3D%3D&amp;trackingId=OakOlgDcU0hWTRXcoLe3UA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K46" s="14" t="inlineStr">
+      <c r="K46" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bmw-group-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L46" s="14" t="inlineStr">
+      <c r="L46" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bmw-group-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M46" s="14" t="inlineStr"/>
+      <c r="M46" s="17" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="14" t="inlineStr">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>linkedin_4402725075</t>
         </is>
       </c>
-      <c r="B47" s="14" t="inlineStr">
+      <c r="B47" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C47" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D47" s="14" t="inlineStr">
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="inlineStr">
         <is>
           <t>DARE</t>
         </is>
       </c>
-      <c r="E47" s="14" t="inlineStr">
+      <c r="E47" s="17" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F47" s="14" t="inlineStr">
+      <c r="F47" s="17" t="inlineStr">
         <is>
           <t>WP. Kuala Lumpur, Federal Territory of Kuala Lumpur, Malaysia</t>
         </is>
       </c>
-      <c r="G47" s="14" t="inlineStr">
+      <c r="G47" s="17" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H47" s="14" t="inlineStr">
+      <c r="H47" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 14:36 UTC</t>
         </is>
       </c>
-      <c r="I47" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J47" s="16" t="inlineStr">
+      <c r="I47" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J47" s="19" t="inlineStr">
         <is>
           <t>https://my.linkedin.com/jobs/view/research-intern-at-dare-4402725075?refId=xbzZXyF6FfcYy036eklDWw%3D%3D&amp;trackingId=QRt5DhbLSINvmHia0jEWIg%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K47" s="14" t="inlineStr">
+      <c r="K47" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dare-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L47" s="14" t="inlineStr">
+      <c r="L47" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dare-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M47" s="14" t="inlineStr"/>
+      <c r="M47" s="17" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="14" t="inlineStr">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>linkedin_4402745391</t>
         </is>
       </c>
-      <c r="B48" s="14" t="inlineStr">
+      <c r="B48" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C48" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D48" s="14" t="inlineStr">
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D48" s="17" t="inlineStr">
         <is>
           <t>Huawei Technologies Research &amp; Development (UK) Ltd</t>
         </is>
       </c>
-      <c r="E48" s="14" t="inlineStr">
+      <c r="E48" s="17" t="inlineStr">
         <is>
           <t>Research Intern - Computer Vision</t>
         </is>
       </c>
-      <c r="F48" s="14" t="inlineStr">
+      <c r="F48" s="17" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G48" s="14" t="inlineStr">
+      <c r="G48" s="17" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H48" s="14" t="inlineStr">
+      <c r="H48" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 18:42 UTC</t>
         </is>
       </c>
-      <c r="I48" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J48" s="16" t="inlineStr">
+      <c r="I48" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J48" s="19" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/research-intern-computer-vision-at-huawei-technologies-research-development-uk-ltd-4402745391?refId=rRtCMQFBU%2FNi7vc62x5Nhg%3D%3D&amp;trackingId=%2Bt1We%2BmKhWHyXION%2FWwQVg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K48" s="14" t="inlineStr">
+      <c r="K48" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-huawei-technologies-research-development-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L48" s="14" t="inlineStr">
+      <c r="L48" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-huawei-technologies-research-development-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M48" s="14" t="inlineStr"/>
+      <c r="M48" s="17" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="14" t="inlineStr">
+      <c r="A49" s="17" t="inlineStr">
         <is>
           <t>linkedin_4402366780</t>
         </is>
       </c>
-      <c r="B49" s="14" t="inlineStr">
+      <c r="B49" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C49" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D49" s="14" t="inlineStr">
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D49" s="17" t="inlineStr">
         <is>
           <t>Binance</t>
         </is>
       </c>
-      <c r="E49" s="14" t="inlineStr">
+      <c r="E49" s="17" t="inlineStr">
         <is>
           <t>Binance Accelerator Program - Data Scientist (LLM &amp; Trading)</t>
         </is>
       </c>
-      <c r="F49" s="14" t="inlineStr">
+      <c r="F49" s="17" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G49" s="14" t="inlineStr">
+      <c r="G49" s="17" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H49" s="14" t="inlineStr">
+      <c r="H49" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 09:43 UTC</t>
         </is>
       </c>
-      <c r="I49" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J49" s="16" t="inlineStr">
+      <c r="I49" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J49" s="19" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/binance-accelerator-program-data-scientist-llm-trading-at-binance-4402366780?refId=bc%2BXeBTeIKMQJTmlLFwbZQ%3D%3D&amp;trackingId=9UuyRRCEPapWNu6VKdZC5A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K49" s="14" t="inlineStr">
+      <c r="K49" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-binance-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L49" s="14" t="inlineStr">
+      <c r="L49" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-binance-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M49" s="14" t="inlineStr"/>
+      <c r="M49" s="17" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="14" t="inlineStr">
+      <c r="A50" s="17" t="inlineStr">
         <is>
           <t>linkedin_4382411039</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
+      <c r="B50" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D50" s="14" t="inlineStr">
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="inlineStr">
         <is>
           <t>The Walt Disney Company</t>
         </is>
       </c>
-      <c r="E50" s="14" t="inlineStr">
+      <c r="E50" s="17" t="inlineStr">
         <is>
           <t>Intern, APAC Data Analytics &amp; Insights (Content Analytics) -  Jul to Dec 2026</t>
         </is>
       </c>
-      <c r="F50" s="14" t="inlineStr">
+      <c r="F50" s="17" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G50" s="14" t="inlineStr">
+      <c r="G50" s="17" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H50" s="14" t="inlineStr">
+      <c r="H50" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 23:55 UTC</t>
         </is>
       </c>
-      <c r="I50" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J50" s="16" t="inlineStr">
+      <c r="I50" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J50" s="19" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/intern-apac-data-analytics-insights-content-analytics-jul-to-dec-2026-at-the-walt-disney-company-4382411039?refId=JBvXH2fNOamnO4WZI1Y0ew%3D%3D&amp;trackingId=Rs%2FdjczlbLYSYtCwY%2F%2FJyA%3D%3D&amp;position=7&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K50" s="14" t="inlineStr">
+      <c r="K50" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-the-walt-disney-company-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L50" s="14" t="inlineStr">
+      <c r="L50" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-the-walt-disney-company-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M50" s="14" t="inlineStr"/>
+      <c r="M50" s="17" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="14" t="inlineStr">
+      <c r="A51" s="17" t="inlineStr">
         <is>
           <t>linkedin_4402305263</t>
         </is>
       </c>
-      <c r="B51" s="14" t="inlineStr">
+      <c r="B51" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D51" s="14" t="inlineStr">
+      <c r="C51" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D51" s="17" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E51" s="14" t="inlineStr">
+      <c r="E51" s="17" t="inlineStr">
         <is>
           <t>SAP iXp Intern - Software Developer (Agentic AI &amp; LLM systems)</t>
         </is>
       </c>
-      <c r="F51" s="14" t="inlineStr">
+      <c r="F51" s="17" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G51" s="14" t="inlineStr">
+      <c r="G51" s="17" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H51" s="14" t="inlineStr">
+      <c r="H51" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 21:40 UTC</t>
         </is>
       </c>
-      <c r="I51" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J51" s="16" t="inlineStr">
+      <c r="I51" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J51" s="19" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/sap-ixp-intern-software-developer-agentic-ai-llm-systems-at-sap-4402305263?refId=zBXuSSlfFyuxcdEqyfeS8g%3D%3D&amp;trackingId=Imq%2FVHMQWkkoDZp5%2BnATSA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K51" s="14" t="inlineStr">
+      <c r="K51" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L51" s="14" t="inlineStr">
+      <c r="L51" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M51" s="14" t="inlineStr"/>
+      <c r="M51" s="17" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="14" t="inlineStr">
+      <c r="A52" s="17" t="inlineStr">
         <is>
           <t>linkedin_4400467080</t>
         </is>
       </c>
-      <c r="B52" s="14" t="inlineStr">
+      <c r="B52" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C52" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D52" s="14" t="inlineStr">
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="inlineStr">
         <is>
           <t>Saama</t>
         </is>
       </c>
-      <c r="E52" s="14" t="inlineStr">
+      <c r="E52" s="17" t="inlineStr">
         <is>
           <t>Intern for AI CoE</t>
         </is>
       </c>
-      <c r="F52" s="14" t="inlineStr">
+      <c r="F52" s="17" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G52" s="14" t="inlineStr">
+      <c r="G52" s="17" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H52" s="14" t="inlineStr">
+      <c r="H52" s="17" t="inlineStr">
         <is>
           <t>2026-04-16 19:45 UTC</t>
         </is>
       </c>
-      <c r="I52" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J52" s="16" t="inlineStr">
+      <c r="I52" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J52" s="19" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/intern-for-ai-coe-at-saama-4400467080?refId=7CvDuV2%2BR%2FzyGozq4UNPPw%3D%3D&amp;trackingId=Ls9yWFAC8lVRx8bmapJfLA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K52" s="14" t="inlineStr">
+      <c r="K52" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-saama-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L52" s="14" t="inlineStr">
+      <c r="L52" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-saama-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M52" s="14" t="inlineStr"/>
+      <c r="M52" s="17" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="14" t="inlineStr">
+      <c r="A53" s="17" t="inlineStr">
         <is>
           <t>linkedin_4400873418</t>
         </is>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B53" s="17" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C53" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D53" s="14" t="inlineStr">
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D53" s="17" t="inlineStr">
         <is>
           <t>SANOVIO</t>
         </is>
       </c>
-      <c r="E53" s="14" t="inlineStr">
+      <c r="E53" s="17" t="inlineStr">
         <is>
           <t>AI Engineering Intern</t>
         </is>
       </c>
-      <c r="F53" s="14" t="inlineStr">
+      <c r="F53" s="17" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G53" s="14" t="inlineStr">
+      <c r="G53" s="17" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H53" s="14" t="inlineStr">
+      <c r="H53" s="17" t="inlineStr">
         <is>
           <t>2026-04-18 00:00 UTC</t>
         </is>
       </c>
-      <c r="I53" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J53" s="16" t="inlineStr">
+      <c r="I53" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J53" s="19" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/ai-engineering-intern-at-sanovio-4400873418?refId=egIYeNLcARu6P6oTIZ%2BHfA%3D%3D&amp;trackingId=c6wZ0DtTzvVZpTRC1l5tYQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K53" s="14" t="inlineStr">
+      <c r="K53" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sanovio-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L53" s="14" t="inlineStr">
+      <c r="L53" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sanovio-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M53" s="14" t="inlineStr"/>
+      <c r="M53" s="17" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="14" t="inlineStr">
+      <c r="A54" s="17" t="inlineStr">
         <is>
           <t>linkedin_4403524251</t>
         </is>
       </c>
-      <c r="B54" s="14" t="inlineStr">
+      <c r="B54" s="17" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C54" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D54" s="14" t="inlineStr">
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
         <is>
           <t>Nascent Markets</t>
         </is>
       </c>
-      <c r="E54" s="14" t="inlineStr">
+      <c r="E54" s="17" t="inlineStr">
         <is>
           <t>Agentic Systems Intern (Graduate Level)</t>
         </is>
       </c>
-      <c r="F54" s="14" t="inlineStr">
+      <c r="F54" s="17" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G54" s="14" t="inlineStr">
+      <c r="G54" s="17" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H54" s="14" t="inlineStr">
+      <c r="H54" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 19:53 UTC</t>
         </is>
       </c>
-      <c r="I54" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J54" s="16" t="inlineStr">
+      <c r="I54" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J54" s="19" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/agentic-systems-intern-graduate-level-at-nascent-markets-4403524251?refId=Ix0g0waARRaNpzTY4LxvsQ%3D%3D&amp;trackingId=RsqyOyJHkanw%2FTeHGUcadA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K54" s="14" t="inlineStr">
+      <c r="K54" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-nascent-markets-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L54" s="14" t="inlineStr">
+      <c r="L54" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-nascent-markets-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M54" s="14" t="inlineStr"/>
+      <c r="M54" s="17" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="14" t="inlineStr">
+      <c r="A55" s="17" t="inlineStr">
         <is>
           <t>linkedin_4402782985</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B55" s="17" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C55" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D55" s="14" t="inlineStr">
+      <c r="C55" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D55" s="17" t="inlineStr">
         <is>
           <t>Axiomatic_AI</t>
         </is>
       </c>
-      <c r="E55" s="14" t="inlineStr">
+      <c r="E55" s="17" t="inlineStr">
         <is>
           <t>Internship - Research Intern (Agentic Learning, Memory &amp; Neurosymbolic Reasoning)</t>
         </is>
       </c>
-      <c r="F55" s="14" t="inlineStr">
+      <c r="F55" s="17" t="inlineStr">
         <is>
           <t>Greater Barcelona Metropolitan Area</t>
         </is>
       </c>
-      <c r="G55" s="14" t="inlineStr">
+      <c r="G55" s="17" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H55" s="14" t="inlineStr">
+      <c r="H55" s="17" t="inlineStr">
         <is>
           <t>2026-04-18 05:04 UTC</t>
         </is>
       </c>
-      <c r="I55" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J55" s="16" t="inlineStr">
+      <c r="I55" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J55" s="19" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/internship-research-intern-agentic-learning-memory-neurosymbolic-reasoning-at-axiomatic-ai-4402782985?refId=vm6No12NjZrg2BBV%2BnbuLQ%3D%3D&amp;trackingId=X9FXk%2FBDFftROMNo9Cr20g%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K55" s="14" t="inlineStr">
+      <c r="K55" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-axiomatic-ai-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L55" s="14" t="inlineStr">
+      <c r="L55" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-axiomatic-ai-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M55" s="14" t="inlineStr"/>
+      <c r="M55" s="17" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="14" t="inlineStr">
+      <c r="A56" s="17" t="inlineStr">
         <is>
           <t>linkedin_4309694978</t>
         </is>
       </c>
-      <c r="B56" s="14" t="inlineStr">
+      <c r="B56" s="17" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C56" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D56" s="14" t="inlineStr">
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E56" s="14" t="inlineStr">
+      <c r="E56" s="17" t="inlineStr">
         <is>
           <t>Graduate Physics Research Intern</t>
         </is>
       </c>
-      <c r="F56" s="14" t="inlineStr">
+      <c r="F56" s="17" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
       </c>
-      <c r="G56" s="14" t="inlineStr">
+      <c r="G56" s="17" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H56" s="14" t="inlineStr">
+      <c r="H56" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 17:37 UTC</t>
         </is>
       </c>
-      <c r="I56" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J56" s="16" t="inlineStr">
+      <c r="I56" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J56" s="19" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/graduate-physics-research-intern-at-dataannotation-4309694978?refId=hlpC50hTZs9sJFHirXWMSg%3D%3D&amp;trackingId=1E0ixzzpb6MzeHKgxpE3Cw%3D%3D&amp;position=9&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K56" s="14" t="inlineStr">
+      <c r="K56" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L56" s="14" t="inlineStr">
+      <c r="L56" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M56" s="14" t="inlineStr"/>
+      <c r="M56" s="17" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="14" t="inlineStr">
+      <c r="A57" s="17" t="inlineStr">
         <is>
           <t>linkedin_4403562730</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
+      <c r="B57" s="17" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C57" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D57" s="14" t="inlineStr">
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D57" s="17" t="inlineStr">
         <is>
           <t>BNM Business Solutions LLP</t>
         </is>
       </c>
-      <c r="E57" s="14" t="inlineStr">
+      <c r="E57" s="17" t="inlineStr">
         <is>
           <t>Data Analyst Internship in Navi Mumbai, Mumbai</t>
         </is>
       </c>
-      <c r="F57" s="14" t="inlineStr">
+      <c r="F57" s="17" t="inlineStr">
         <is>
           <t>Mumbai Metropolitan Region</t>
         </is>
       </c>
-      <c r="G57" s="14" t="inlineStr">
+      <c r="G57" s="17" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H57" s="14" t="inlineStr">
+      <c r="H57" s="17" t="inlineStr">
         <is>
           <t>2026-04-18 00:06 UTC</t>
         </is>
       </c>
-      <c r="I57" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J57" s="16" t="inlineStr">
+      <c r="I57" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J57" s="19" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-internship-in-navi-mumbai-mumbai-at-bnm-business-solutions-llp-4403562730?refId=1X9LgKP3%2FAPeJuhZVjyhxw%3D%3D&amp;trackingId=oFY9Z69ZBEGkNtq0cbBOMw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K57" s="14" t="inlineStr">
+      <c r="K57" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bnm-business-solutions-llp-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L57" s="14" t="inlineStr">
+      <c r="L57" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bnm-business-solutions-llp-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M57" s="14" t="inlineStr"/>
+      <c r="M57" s="17" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="14" t="inlineStr">
+      <c r="A58" s="17" t="inlineStr">
         <is>
           <t>linkedin_4309694917</t>
         </is>
       </c>
-      <c r="B58" s="14" t="inlineStr">
+      <c r="B58" s="17" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C58" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D58" s="14" t="inlineStr">
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D58" s="17" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E58" s="14" t="inlineStr">
+      <c r="E58" s="17" t="inlineStr">
         <is>
           <t>Graduate Biology Research Intern</t>
         </is>
       </c>
-      <c r="F58" s="14" t="inlineStr">
+      <c r="F58" s="17" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
       </c>
-      <c r="G58" s="14" t="inlineStr">
+      <c r="G58" s="17" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H58" s="14" t="inlineStr">
+      <c r="H58" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 17:35 UTC</t>
         </is>
       </c>
-      <c r="I58" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J58" s="16" t="inlineStr">
+      <c r="I58" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J58" s="19" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/graduate-biology-research-intern-at-dataannotation-4309694917?refId=hlpC50hTZs9sJFHirXWMSg%3D%3D&amp;trackingId=BM%2FBx4ElnXDk5hEpiM0gzg%3D%3D&amp;position=8&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K58" s="14" t="inlineStr">
+      <c r="K58" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L58" s="14" t="inlineStr">
+      <c r="L58" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M58" s="14" t="inlineStr"/>
+      <c r="M58" s="17" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="14" t="inlineStr">
+      <c r="A59" s="17" t="inlineStr">
         <is>
           <t>linkedin_4346088677</t>
         </is>
       </c>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B59" s="17" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C59" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D59" s="14" t="inlineStr">
+      <c r="C59" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D59" s="17" t="inlineStr">
         <is>
           <t>revel8</t>
         </is>
       </c>
-      <c r="E59" s="14" t="inlineStr">
+      <c r="E59" s="17" t="inlineStr">
         <is>
           <t>Applied AI Engineer Intern (all genders)</t>
         </is>
       </c>
-      <c r="F59" s="14" t="inlineStr">
+      <c r="F59" s="17" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G59" s="14" t="inlineStr">
+      <c r="G59" s="17" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H59" s="14" t="inlineStr">
+      <c r="H59" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 22:38 UTC</t>
         </is>
       </c>
-      <c r="I59" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J59" s="16" t="inlineStr">
+      <c r="I59" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J59" s="19" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/applied-ai-engineer-intern-all-genders-at-revel8-4346088677?refId=FHQDN2Ta3J6B7WhWnDAuhQ%3D%3D&amp;trackingId=Pf%2Ftwn6H5Hrw8BKjPenbSQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K59" s="14" t="inlineStr">
+      <c r="K59" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-revel8-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L59" s="14" t="inlineStr">
+      <c r="L59" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-revel8-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M59" s="14" t="inlineStr"/>
+      <c r="M59" s="17" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="14" t="inlineStr">
+      <c r="A60" s="17" t="inlineStr">
         <is>
           <t>linkedin_4403475387</t>
         </is>
       </c>
-      <c r="B60" s="14" t="inlineStr">
+      <c r="B60" s="17" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C60" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D60" s="14" t="inlineStr">
+      <c r="C60" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="inlineStr">
         <is>
           <t>Inc42 Media</t>
         </is>
       </c>
-      <c r="E60" s="14" t="inlineStr">
+      <c r="E60" s="17" t="inlineStr">
         <is>
           <t>Operations Intern: Inc42 AI Summit 2026</t>
         </is>
       </c>
-      <c r="F60" s="14" t="inlineStr">
+      <c r="F60" s="17" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G60" s="14" t="inlineStr">
+      <c r="G60" s="17" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H60" s="14" t="inlineStr">
+      <c r="H60" s="17" t="inlineStr">
         <is>
           <t>2026-04-17 16:23 UTC</t>
         </is>
       </c>
-      <c r="I60" s="15" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J60" s="16" t="inlineStr">
+      <c r="I60" s="18" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J60" s="19" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/operations-intern-inc42-ai-summit-2026-at-inc42-media-4403475387?refId=jyI2mJ9xFT%2BmdtkV0OCW0g%3D%3D&amp;trackingId=6sWKnvWNaTU69%2B7bcZNxLg%3D%3D&amp;position=10&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K60" s="14" t="inlineStr">
+      <c r="K60" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-inc42-media-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L60" s="14" t="inlineStr">
+      <c r="L60" s="17" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-inc42-media-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M60" s="14" t="inlineStr"/>
+      <c r="M60" s="17" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="17" t="inlineStr">
@@ -4938,6 +4947,258 @@
         </is>
       </c>
       <c r="M70" s="17" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="20" t="inlineStr">
+        <is>
+          <t>linkedin_4403095692</t>
+        </is>
+      </c>
+      <c r="B71" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-19 08:24</t>
+        </is>
+      </c>
+      <c r="C71" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D71" s="20" t="inlineStr">
+        <is>
+          <t>Starrycraze Technology</t>
+        </is>
+      </c>
+      <c r="E71" s="20" t="inlineStr">
+        <is>
+          <t>Data Scientist Intern</t>
+        </is>
+      </c>
+      <c r="F71" s="20" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="G71" s="20" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H71" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-19 04:58 UTC</t>
+        </is>
+      </c>
+      <c r="I71" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J71" s="22" t="inlineStr">
+        <is>
+          <t>https://hk.linkedin.com/jobs/view/data-scientist-intern-at-starrycraze-technology-4403095692?refId=TVQyGaR78N78VqNo32HHeA%3D%3D&amp;trackingId=iTU%2BdVDc304eRUiD2UiVkA%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K71" s="20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-starrycraze-technology-2026-04-19.pdf</t>
+        </is>
+      </c>
+      <c r="L71" s="20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-starrycraze-technology-2026-04-19.pdf</t>
+        </is>
+      </c>
+      <c r="M71" s="20" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="20" t="inlineStr">
+        <is>
+          <t>linkedin_4403848986</t>
+        </is>
+      </c>
+      <c r="B72" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-19 08:24</t>
+        </is>
+      </c>
+      <c r="C72" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D72" s="20" t="inlineStr">
+        <is>
+          <t>Zoox</t>
+        </is>
+      </c>
+      <c r="E72" s="20" t="inlineStr">
+        <is>
+          <t>PhD Research Intern, Offline Driving Intelligence</t>
+        </is>
+      </c>
+      <c r="F72" s="20" t="inlineStr">
+        <is>
+          <t>Foster City, CA</t>
+        </is>
+      </c>
+      <c r="G72" s="20" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H72" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-19 02:06 UTC</t>
+        </is>
+      </c>
+      <c r="I72" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J72" s="22" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/phd-research-intern-offline-driving-intelligence-at-zoox-4403848986?refId=5ydRxcXuf5aHqLJVjey87Q%3D%3D&amp;trackingId=FWtGym5%2BhCmPjiMPBVYS7w%3D%3D&amp;position=2&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K72" s="20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-19.pdf</t>
+        </is>
+      </c>
+      <c r="L72" s="20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-19.pdf</t>
+        </is>
+      </c>
+      <c r="M72" s="20" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="20" t="inlineStr">
+        <is>
+          <t>linkedin_4371758156</t>
+        </is>
+      </c>
+      <c r="B73" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-19 08:24</t>
+        </is>
+      </c>
+      <c r="C73" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D73" s="20" t="inlineStr">
+        <is>
+          <t>Lowe's India</t>
+        </is>
+      </c>
+      <c r="E73" s="20" t="inlineStr">
+        <is>
+          <t>DIH Intern, Data Engineering</t>
+        </is>
+      </c>
+      <c r="F73" s="20" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India</t>
+        </is>
+      </c>
+      <c r="G73" s="20" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H73" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-18 10:48 UTC</t>
+        </is>
+      </c>
+      <c r="I73" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J73" s="22" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/dih-intern-data-engineering-at-lowe-s-india-4371758156?refId=1mgTdTTgR1UncTTJ8Ts5OA%3D%3D&amp;trackingId=7HYWBNU0zclnyp9qIoW2Jw%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K73" s="20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-lowes-india-2026-04-19.pdf</t>
+        </is>
+      </c>
+      <c r="L73" s="20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-lowes-india-2026-04-19.pdf</t>
+        </is>
+      </c>
+      <c r="M73" s="20" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="20" t="inlineStr">
+        <is>
+          <t>linkedin_4327191639</t>
+        </is>
+      </c>
+      <c r="B74" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-19 08:24</t>
+        </is>
+      </c>
+      <c r="C74" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D74" s="20" t="inlineStr">
+        <is>
+          <t>Whatnot</t>
+        </is>
+      </c>
+      <c r="E74" s="20" t="inlineStr">
+        <is>
+          <t>Data Scientist, Product Analytics</t>
+        </is>
+      </c>
+      <c r="F74" s="20" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="G74" s="20" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H74" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-18 13:22 UTC</t>
+        </is>
+      </c>
+      <c r="I74" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J74" s="22" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/data-scientist-product-analytics-at-whatnot-4327191639?refId=mfQJnJ6mRr3La1qB9YnNGA%3D%3D&amp;trackingId=k4mLJmsHD9wYHSZlc4RA%2Fw%3D%3D&amp;position=2&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K74" s="20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-whatnot-2026-04-19.pdf</t>
+        </is>
+      </c>
+      <c r="L74" s="20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-whatnot-2026-04-19.pdf</t>
+        </is>
+      </c>
+      <c r="M74" s="20" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5010,6 +5271,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J69" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId73"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -83,10 +83,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -516,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -602,4351 +611,4351 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>linkedin_4401809501</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="20" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr">
+      <c r="F2" s="20" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr">
+      <c r="G2" s="20" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H2" s="17" t="inlineStr">
+      <c r="H2" s="20" t="inlineStr">
         <is>
           <t>2026-04-15 22:19 UTC</t>
         </is>
       </c>
-      <c r="I2" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J2" s="19" t="inlineStr">
+      <c r="I2" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J2" s="22" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/research-intern-at-skycliff-it-4401809501?refId=HHi6SaK1fggu3E9dI3MtVg%3D%3D&amp;trackingId=r33pSo29lHStfk9FH82pyw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K2" s="17" t="inlineStr">
+      <c r="K2" s="20" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L2" s="17" t="inlineStr">
+      <c r="L2" s="20" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M2" s="17" t="inlineStr"/>
+      <c r="M2" s="20" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>linkedin_4402568578</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C3" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>Webs X UM</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="20" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G3" s="17" t="inlineStr">
+      <c r="G3" s="20" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="20" t="inlineStr">
         <is>
           <t>2026-04-15 19:20 UTC</t>
         </is>
       </c>
-      <c r="I3" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J3" s="19" t="inlineStr">
+      <c r="I3" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J3" s="22" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-webs-x-um-4402568578?refId=g89JM6cY8EFeoLk6JL5tVg%3D%3D&amp;trackingId=uFZVJJX7SSI0XCPFIrLqmA%3D%3D&amp;position=19&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K3" s="17" t="inlineStr">
+      <c r="K3" s="20" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-webs-x-um-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="20" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-webs-x-um-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M3" s="17" t="inlineStr"/>
+      <c r="M3" s="20" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>linkedin_4399996740</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>SUN PHARMA</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>Becario</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>Mexico City, Mexico</t>
         </is>
       </c>
-      <c r="G4" s="17" t="inlineStr">
+      <c r="G4" s="20" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="20" t="inlineStr">
         <is>
           <t>2026-04-15 17:59 UTC</t>
         </is>
       </c>
-      <c r="I4" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J4" s="19" t="inlineStr">
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J4" s="22" t="inlineStr">
         <is>
           <t>https://mx.linkedin.com/jobs/view/becario-at-sun-pharma-4399996740?refId=g89JM6cY8EFeoLk6JL5tVg%3D%3D&amp;trackingId=sZ0Fkcf4RHuIpzXu4mJRNg%3D%3D&amp;position=22&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K4" s="17" t="inlineStr">
+      <c r="K4" s="20" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-sun-pharma-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="20" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-sun-pharma-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M4" s="17" t="inlineStr"/>
+      <c r="M4" s="20" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>linkedin_4399975959</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>LS Direct</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>Data Analytics Intern</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>Suffern, NY</t>
         </is>
       </c>
-      <c r="G5" s="17" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>2026-04-15 14:26 UTC</t>
         </is>
       </c>
-      <c r="I5" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J5" s="19" t="inlineStr">
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J5" s="22" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-analytics-intern-at-ls-direct-4399975959?refId=pg0ll3e89fatVyUznLcdpw%3D%3D&amp;trackingId=5b41IoyQfIfx3Tu42domiQ%3D%3D&amp;position=23&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K5" s="17" t="inlineStr">
+      <c r="K5" s="20" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-ls-direct-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="20" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-ls-direct-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M5" s="17" t="inlineStr"/>
+      <c r="M5" s="20" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>linkedin_4370546718</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>Clarivate</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>Lead Data Scientist</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>Barcelona, Catalonia, Spain</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>2026-04-15 12:16 UTC</t>
         </is>
       </c>
-      <c r="I6" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J6" s="19" t="inlineStr">
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/lead-data-scientist-at-clarivate-4370546718?refId=FyyqQfduMQ8KZ7B5LeF0UQ%3D%3D&amp;trackingId=1i1kXdbV7SMunyFTiSJHJg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K6" s="17" t="inlineStr">
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-clarivate-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-clarivate-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M6" s="17" t="inlineStr"/>
+      <c r="M6" s="20" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>linkedin_4389810164</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>Vitality</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>Senior Data Scientist - 12 Month FTC</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>2026-04-15 09:39 UTC</t>
         </is>
       </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/senior-data-scientist-12-month-ftc-at-vitality-4389810164?refId=FPz%2BrPoaQeqgXBm%2FfOzGGA%3D%3D&amp;trackingId=yVNh55t2X2xocDT4i6HDqQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K7" s="17" t="inlineStr">
+      <c r="K7" s="20" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-vitality-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-vitality-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M7" s="17" t="inlineStr"/>
+      <c r="M7" s="20" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>linkedin_4399952059</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>traide AI</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>AI Associate (f/m/x) (B2B SaaS Startup) - Intern/Working Student</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>2026-04-15 07:04 UTC</t>
         </is>
       </c>
-      <c r="I8" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J8" s="19" t="inlineStr">
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/ai-associate-f-m-x-b2b-saas-startup-intern-working-student-at-traide-ai-4399952059?refId=x0uIkl175n0hipT17L%2FGRw%3D%3D&amp;trackingId=8kdzUQgW%2B7rCk2pO2oIErg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K8" s="17" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-traide-ai-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-traide-ai-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M8" s="17" t="inlineStr"/>
+      <c r="M8" s="20" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>linkedin_4399933254</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>Briink</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>Growth Intern (Merantix AI Campus)</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>2026-04-15 05:03 UTC</t>
         </is>
       </c>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J9" s="19" t="inlineStr">
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/growth-intern-merantix-ai-campus-at-briink-4399933254?refId=x0uIkl175n0hipT17L%2FGRw%3D%3D&amp;trackingId=qEKtyJNA03Kbr6AYDlhsBw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K9" s="17" t="inlineStr">
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-briink-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="20" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-briink-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M9" s="17" t="inlineStr"/>
+      <c r="M9" s="20" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>linkedin_4400429367</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>Tata Consultancy Services</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>HR -Data Scientist</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>Renton, WA</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 16:56 UTC</t>
         </is>
       </c>
-      <c r="I10" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J10" s="19" t="inlineStr">
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/hr-data-scientist-at-tata-consultancy-services-4400429367?refId=vJILgNySaXYUQknbyaKZZQ%3D%3D&amp;trackingId=7cZ0KYh8Sv5%2Fh6%2FG86%2BLug%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K10" s="17" t="inlineStr">
+      <c r="K10" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-tata-consultancy-services-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-tata-consultancy-services-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M10" s="17" t="inlineStr"/>
+      <c r="M10" s="20" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>linkedin_4390814627</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>Criteo</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>Barcelona, Catalonia, Spain</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 12:19 UTC</t>
         </is>
       </c>
-      <c r="I11" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J11" s="19" t="inlineStr">
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J11" s="22" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/data-analyst-intern-at-criteo-4390814627?refId=PCZWvfzZIzNkx6giU9jTsA%3D%3D&amp;trackingId=T%2FMog6vtgG8P3ihAU9b1uQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K11" s="17" t="inlineStr">
+      <c r="K11" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-criteo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-criteo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M11" s="17" t="inlineStr"/>
+      <c r="M11" s="20" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>linkedin_4402983364</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>Brussels, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I12" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J12" s="19" t="inlineStr">
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402983364?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=zV4sJQyNyQg%2FS%2BYm6Ba9Eg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K12" s="17" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M12" s="17" t="inlineStr"/>
+      <c r="M12" s="20" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>linkedin_4390725142</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>Boston Consulting Group (BCG)</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>Forward Deployed AI Engineer, Internship, United Kingdom - BCG X</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 16:24 UTC</t>
         </is>
       </c>
-      <c r="I13" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J13" s="19" t="inlineStr">
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J13" s="22" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/forward-deployed-ai-engineer-internship-united-kingdom-bcg-x-at-boston-consulting-group-bcg-4390725142?refId=YHAZO5vAx9Qtg1RXMma%2F%2BA%3D%3D&amp;trackingId=E8kiSHzcdYe%2FH6s%2FCkGtMw%3D%3D&amp;position=7&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K13" s="17" t="inlineStr">
+      <c r="K13" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M13" s="17" t="inlineStr"/>
+      <c r="M13" s="20" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>linkedin_4400428064</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>Fanatics</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 16:16 UTC</t>
         </is>
       </c>
-      <c r="I14" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J14" s="19" t="inlineStr">
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/data-scientist-at-fanatics-4400428064?refId=SNMwEp9%2FBozAkX4FBnhJwQ%3D%3D&amp;trackingId=cAX0aKWV%2FBX1fvQzm%2FkEMg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K14" s="17" t="inlineStr">
+      <c r="K14" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-fanatics-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-fanatics-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M14" s="17" t="inlineStr"/>
+      <c r="M14" s="20" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>linkedin_4390730090</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>Boston Consulting Group (BCG)</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>Forward Deployed AI Scientist, Internship, United Kingdom - BCG X</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 13:57 UTC</t>
         </is>
       </c>
-      <c r="I15" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J15" s="19" t="inlineStr">
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J15" s="22" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/forward-deployed-ai-scientist-internship-united-kingdom-bcg-x-at-boston-consulting-group-bcg-4390730090?refId=YHAZO5vAx9Qtg1RXMma%2F%2BA%3D%3D&amp;trackingId=m50MzwjbYzUmAv7nJVAKgA%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K15" s="17" t="inlineStr">
+      <c r="K15" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="L15" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M15" s="17" t="inlineStr"/>
+      <c r="M15" s="20" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>linkedin_4402138096</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>Kelly Tutors</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>Research Intern (3-5hrs/week, flexible)</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 14:40 UTC</t>
         </is>
       </c>
-      <c r="I16" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J16" s="19" t="inlineStr">
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/research-intern-3-5hrs-week-flexible-at-kelly-tutors-4402138096?refId=HmOS2YEHUH3GOVent1txqw%3D%3D&amp;trackingId=3XBXMUoBdiHeRL4qw%2B2qRw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K16" s="17" t="inlineStr">
+      <c r="K16" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-kelly-tutors-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L16" s="17" t="inlineStr">
+      <c r="L16" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-kelly-tutors-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M16" s="17" t="inlineStr"/>
+      <c r="M16" s="20" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>linkedin_4378557045</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>Fund for Public Health in NYC</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G17" s="17" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 16:13 UTC</t>
         </is>
       </c>
-      <c r="I17" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J17" s="19" t="inlineStr">
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J17" s="22" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-scientist-at-fund-for-public-health-in-nyc-4378557045?refId=JsndNRa0tnfF7dsuxv62wA%3D%3D&amp;trackingId=Pmgt6JCxYmQun5Uv6%2BLbiQ%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K17" s="17" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-fund-for-public-health-in-nyc-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-fund-for-public-health-in-nyc-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M17" s="17" t="inlineStr"/>
+      <c r="M17" s="20" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>linkedin_4402977457</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>Brussels, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G18" s="17" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I18" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J18" s="19" t="inlineStr">
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402977457?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=gL9sbQh%2FaLMmzvXjuO71WQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K18" s="17" t="inlineStr">
+      <c r="K18" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L18" s="17" t="inlineStr">
+      <c r="L18" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M18" s="17" t="inlineStr"/>
+      <c r="M18" s="20" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>linkedin_4371210537</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>Gildan</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>Intern, ERP GenAI</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H19" s="17" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 15:23 UTC</t>
         </is>
       </c>
-      <c r="I19" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J19" s="19" t="inlineStr">
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J19" s="22" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/intern-erp-genai-at-gildan-4371210537?refId=jteS%2Ft3Cmc2XLVMFToCpKw%3D%3D&amp;trackingId=OQGg%2Bob2m9u4kkbRcgWoUw%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K19" s="17" t="inlineStr">
+      <c r="K19" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-gildan-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L19" s="17" t="inlineStr">
+      <c r="L19" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-gildan-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M19" s="17" t="inlineStr"/>
+      <c r="M19" s="20" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>linkedin_4402974624</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>Uccle, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G20" s="17" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H20" s="17" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I20" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J20" s="19" t="inlineStr">
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J20" s="22" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402974624?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=RJfkVsuYxv4DqyEhPJ367g%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K20" s="17" t="inlineStr">
+      <c r="K20" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L20" s="17" t="inlineStr">
+      <c r="L20" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M20" s="17" t="inlineStr"/>
+      <c r="M20" s="20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>linkedin_4402174633</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>Cloudera</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>AI Enablement Intern (Ireland Based)</t>
         </is>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>Greater Dublin</t>
         </is>
       </c>
-      <c r="G21" s="17" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H21" s="17" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 18:24 UTC</t>
         </is>
       </c>
-      <c r="I21" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J21" s="19" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J21" s="22" t="inlineStr">
         <is>
           <t>https://ie.linkedin.com/jobs/view/ai-enablement-intern-ireland-based-at-cloudera-4402174633?refId=d9iDz5spYJk0nIor701k5g%3D%3D&amp;trackingId=6OZvFiMQ12VqIzY6EqUe7A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K21" s="17" t="inlineStr">
+      <c r="K21" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-cloudera-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L21" s="17" t="inlineStr">
+      <c r="L21" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-cloudera-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M21" s="17" t="inlineStr"/>
+      <c r="M21" s="20" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>linkedin_4403115250</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>PhD Research Intern, Mapping Software</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G22" s="17" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H22" s="17" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 19:55 UTC</t>
         </is>
       </c>
-      <c r="I22" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J22" s="19" t="inlineStr">
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-mapping-software-at-zoox-4403115250?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=67WsHxTIXiO%2ByWr0OYU7ug%3D%3D&amp;position=10&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K22" s="17" t="inlineStr">
+      <c r="K22" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L22" s="17" t="inlineStr">
+      <c r="L22" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M22" s="17" t="inlineStr"/>
+      <c r="M22" s="20" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>linkedin_4379373115</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>Woven by Toyota</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>Applied Scientist, Computer Vision and Generative Models, Vision AI (Internship)</t>
         </is>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>Tokyo, Japan</t>
         </is>
       </c>
-      <c r="G23" s="17" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 14:55 UTC</t>
         </is>
       </c>
-      <c r="I23" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J23" s="19" t="inlineStr">
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
         <is>
           <t>https://jp.linkedin.com/jobs/view/applied-scientist-computer-vision-and-generative-models-vision-ai-internship-at-woven-by-toyota-4379373115?refId=4q6ISAXJ%2BcfZsJD688QZWg%3D%3D&amp;trackingId=pUnO9OuzZx4G6BOukom%2FQQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K23" s="17" t="inlineStr">
+      <c r="K23" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-woven-by-toyota-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L23" s="17" t="inlineStr">
+      <c r="L23" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-woven-by-toyota-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M23" s="17" t="inlineStr"/>
+      <c r="M23" s="20" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>linkedin_4325103488</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>Binance</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>Binance Accelerator Program - DevOps (Artificial Intelligence)</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G24" s="17" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H24" s="17" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 12:13 UTC</t>
         </is>
       </c>
-      <c r="I24" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J24" s="19" t="inlineStr">
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/binance-accelerator-program-devops-artificial-intelligence-at-binance-4325103488?refId=KzaD5RMOfYQEZyaw6UmcpQ%3D%3D&amp;trackingId=8R4okHiG3RYyjThXHAqxIQ%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K24" s="17" t="inlineStr">
+      <c r="K24" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-binance-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L24" s="17" t="inlineStr">
+      <c r="L24" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-binance-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M24" s="17" t="inlineStr"/>
+      <c r="M24" s="20" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>linkedin_4400563251</t>
         </is>
       </c>
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>Aylo</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>Sr. Full-Stack Data Scientist - Data Services</t>
         </is>
       </c>
-      <c r="F25" s="17" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>Greater Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G25" s="17" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H25" s="17" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 12:01 UTC</t>
         </is>
       </c>
-      <c r="I25" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J25" s="19" t="inlineStr">
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J25" s="22" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/sr-full-stack-data-scientist-data-services-at-aylo-4400563251?refId=3X2hsLwn0XF5%2BC4ABneEzA%3D%3D&amp;trackingId=aJHp5psMKfAaMJdxBAz5Hw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K25" s="17" t="inlineStr">
+      <c r="K25" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-aylo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L25" s="17" t="inlineStr">
+      <c r="L25" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-aylo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M25" s="17" t="inlineStr"/>
+      <c r="M25" s="20" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>linkedin_4400403670</t>
         </is>
       </c>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>Schneider Electric</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>Internship in Global AI Sales Enablement &amp; Analytics</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>Warsaw, Mazowieckie, Poland</t>
         </is>
       </c>
-      <c r="G26" s="17" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H26" s="17" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 11:43 UTC</t>
         </is>
       </c>
-      <c r="I26" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J26" s="19" t="inlineStr">
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
         <is>
           <t>https://pl.linkedin.com/jobs/view/internship-in-global-ai-sales-enablement-analytics-at-schneider-electric-4400403670?refId=0j6PfgagLJw81v3dQ49jXQ%3D%3D&amp;trackingId=ErR9yiUH1tcny4hRKbXl8A%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K26" s="17" t="inlineStr">
+      <c r="K26" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-schneider-electric-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L26" s="17" t="inlineStr">
+      <c r="L26" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-schneider-electric-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M26" s="17" t="inlineStr"/>
+      <c r="M26" s="20" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>linkedin_4297755027</t>
         </is>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>Databricks</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>PhD GenAI Research Scientist Intern</t>
         </is>
       </c>
-      <c r="F27" s="17" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="G27" s="17" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H27" s="17" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 10:31 UTC</t>
         </is>
       </c>
-      <c r="I27" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J27" s="19" t="inlineStr">
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J27" s="22" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-genai-research-scientist-intern-at-databricks-4297755027?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=UXoh9K97xsqO%2FzDhCy7Uug%3D%3D&amp;position=8&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K27" s="17" t="inlineStr">
+      <c r="K27" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-databricks-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L27" s="17" t="inlineStr">
+      <c r="L27" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-databricks-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M27" s="17" t="inlineStr"/>
+      <c r="M27" s="20" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>linkedin_4401843829</t>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>Tiger Brokers Singapore</t>
         </is>
       </c>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>Quantitative Investment Analyst Intern</t>
         </is>
       </c>
-      <c r="F28" s="17" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G28" s="17" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H28" s="17" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 06:09 UTC</t>
         </is>
       </c>
-      <c r="I28" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J28" s="19" t="inlineStr">
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J28" s="22" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/quantitative-investment-analyst-intern-at-tiger-brokers-singapore-4401843829?refId=LJ4PwcXqLhd1gtOBe9ZVig%3D%3D&amp;trackingId=oxh8Ol2m1QKvqfrvl10UqA%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K28" s="17" t="inlineStr">
+      <c r="K28" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-tiger-brokers-singapore-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L28" s="17" t="inlineStr">
+      <c r="L28" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-tiger-brokers-singapore-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M28" s="17" t="inlineStr"/>
+      <c r="M28" s="20" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>linkedin_4400148847</t>
         </is>
       </c>
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>Boomlet</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F29" s="17" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>Mumbai, Maharashtra, India</t>
         </is>
       </c>
-      <c r="G29" s="17" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H29" s="17" t="inlineStr">
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 05:24 UTC</t>
         </is>
       </c>
-      <c r="I29" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J29" s="19" t="inlineStr">
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J29" s="22" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-boomlet-4400148847?refId=vAgiKqchg4pd6EgGGQ%2FF%2FA%3D%3D&amp;trackingId=IoHiSd1L28nXXarEd4gYfw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K29" s="17" t="inlineStr">
+      <c r="K29" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boomlet-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L29" s="17" t="inlineStr">
+      <c r="L29" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boomlet-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M29" s="17" t="inlineStr"/>
+      <c r="M29" s="20" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>linkedin_4401844394</t>
         </is>
       </c>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>On-us</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>AI Business Analyst Summer Intern</t>
         </is>
       </c>
-      <c r="F30" s="17" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G30" s="17" t="inlineStr">
+      <c r="G30" s="20" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H30" s="17" t="inlineStr">
+      <c r="H30" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 04:56 UTC</t>
         </is>
       </c>
-      <c r="I30" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J30" s="19" t="inlineStr">
+      <c r="I30" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J30" s="22" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/ai-business-analyst-summer-intern-at-on-us-4401844394?refId=lslydLUu5l8kXOktysXYaw%3D%3D&amp;trackingId=BQ%2BoYgH5QtZKBWGZQgBfNQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K30" s="17" t="inlineStr">
+      <c r="K30" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-on-us-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L30" s="17" t="inlineStr">
+      <c r="L30" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-on-us-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M30" s="17" t="inlineStr"/>
+      <c r="M30" s="20" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>linkedin_4401837715</t>
         </is>
       </c>
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>Pathos Consultancy</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>Quantitative Research &amp; Development Internships</t>
         </is>
       </c>
-      <c r="F31" s="17" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G31" s="17" t="inlineStr">
+      <c r="G31" s="20" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H31" s="17" t="inlineStr">
+      <c r="H31" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 03:48 UTC</t>
         </is>
       </c>
-      <c r="I31" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J31" s="19" t="inlineStr">
+      <c r="I31" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J31" s="22" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/quantitative-research-development-internships-at-pathos-consultancy-4401837715?refId=KzaD5RMOfYQEZyaw6UmcpQ%3D%3D&amp;trackingId=eIGVr2dDtK%2F1o37C90xRoQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K31" s="17" t="inlineStr">
+      <c r="K31" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-pathos-consultancy-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L31" s="17" t="inlineStr">
+      <c r="L31" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-pathos-consultancy-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M31" s="17" t="inlineStr"/>
+      <c r="M31" s="20" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>linkedin_4402662606</t>
         </is>
       </c>
-      <c r="B32" s="17" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>Stripe</t>
         </is>
       </c>
-      <c r="E32" s="17" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>PhD Machine Learning Engineer, Intern</t>
         </is>
       </c>
-      <c r="F32" s="17" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G32" s="17" t="inlineStr">
+      <c r="G32" s="20" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H32" s="17" t="inlineStr">
+      <c r="H32" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 02:23 UTC</t>
         </is>
       </c>
-      <c r="I32" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J32" s="19" t="inlineStr">
+      <c r="I32" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J32" s="22" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-machine-learning-engineer-intern-at-stripe-4402662606?refId=vJILgNySaXYUQknbyaKZZQ%3D%3D&amp;trackingId=NDMzaPfHMoCKo5uxI3THcw%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K32" s="17" t="inlineStr">
+      <c r="K32" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L32" s="17" t="inlineStr">
+      <c r="L32" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M32" s="17" t="inlineStr"/>
+      <c r="M32" s="20" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>linkedin_4402953925</t>
         </is>
       </c>
-      <c r="B33" s="17" t="inlineStr">
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E33" s="17" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F33" s="17" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
-      <c r="G33" s="17" t="inlineStr">
+      <c r="G33" s="20" t="inlineStr">
         <is>
           <t>Middle_East</t>
         </is>
       </c>
-      <c r="H33" s="17" t="inlineStr">
+      <c r="H33" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 00:00 UTC</t>
         </is>
       </c>
-      <c r="I33" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J33" s="19" t="inlineStr">
+      <c r="I33" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J33" s="22" t="inlineStr">
         <is>
           <t>https://ae.linkedin.com/jobs/view/research-intern-at-skycliff-it-4402953925?refId=f%2BmSR6Ncm83dISKgoQTrbw%3D%3D&amp;trackingId=CdPOXElDD3wJKKeBZSdWsw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K33" s="17" t="inlineStr">
+      <c r="K33" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L33" s="17" t="inlineStr">
+      <c r="L33" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M33" s="17" t="inlineStr"/>
+      <c r="M33" s="20" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>linkedin_4402617206</t>
         </is>
       </c>
-      <c r="B34" s="17" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>Stripe</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr">
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>PhD Machine Learning Engineer, Intern</t>
         </is>
       </c>
-      <c r="F34" s="17" t="inlineStr">
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="G34" s="17" t="inlineStr">
+      <c r="G34" s="20" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H34" s="17" t="inlineStr">
+      <c r="H34" s="20" t="inlineStr">
         <is>
           <t>2026-04-15 20:25 UTC</t>
         </is>
       </c>
-      <c r="I34" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J34" s="19" t="inlineStr">
+      <c r="I34" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J34" s="22" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-machine-learning-engineer-intern-at-stripe-4402617206?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=yAc4U29LYJcrlQSUWWcubA%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K34" s="17" t="inlineStr">
+      <c r="K34" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L34" s="17" t="inlineStr">
+      <c r="L34" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M34" s="17" t="inlineStr"/>
+      <c r="M34" s="20" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>linkedin_4403183407</t>
         </is>
       </c>
-      <c r="B35" s="17" t="inlineStr">
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
         <is>
           <t>Hardware FYI</t>
         </is>
       </c>
-      <c r="E35" s="17" t="inlineStr">
+      <c r="E35" s="20" t="inlineStr">
         <is>
           <t>Robotics - Applied Scientist II Intern / Co-op - 2026 (Robotics, Manipulation, Perception, Motion Planning, Autonomous Mobile Robots, Computer Vision, Machine Learning, Controls, and more)</t>
         </is>
       </c>
-      <c r="F35" s="17" t="inlineStr">
+      <c r="F35" s="20" t="inlineStr">
         <is>
           <t>Boston, MA</t>
         </is>
       </c>
-      <c r="G35" s="17" t="inlineStr">
+      <c r="G35" s="20" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H35" s="17" t="inlineStr">
+      <c r="H35" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 04:31 UTC</t>
         </is>
       </c>
-      <c r="I35" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J35" s="19" t="inlineStr">
+      <c r="I35" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J35" s="22" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/robotics-applied-scientist-ii-intern-co-op-2026-robotics-manipulation-perception-motion-planning-autonomous-mobile-robots-computer-vision-machine-learning-controls-and-more-at-hardware-fyi-4403183407?refId=s5WxXRPJ8QU7G2WPi2yNiw%3D%3D&amp;trackingId=rjd%2F8qdM5kQMmADtGJgSSw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K35" s="17" t="inlineStr">
+      <c r="K35" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-hardware-fyi-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L35" s="17" t="inlineStr">
+      <c r="L35" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-hardware-fyi-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M35" s="17" t="inlineStr"/>
+      <c r="M35" s="20" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>linkedin_4403153262</t>
         </is>
       </c>
-      <c r="B36" s="17" t="inlineStr">
+      <c r="B36" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="inlineStr">
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
         <is>
           <t>Generali Malaysia</t>
         </is>
       </c>
-      <c r="E36" s="17" t="inlineStr">
+      <c r="E36" s="20" t="inlineStr">
         <is>
           <t>Intern, IT (AI Engineering)</t>
         </is>
       </c>
-      <c r="F36" s="17" t="inlineStr">
+      <c r="F36" s="20" t="inlineStr">
         <is>
           <t>Federal Territory of Kuala Lumpur, Malaysia</t>
         </is>
       </c>
-      <c r="G36" s="17" t="inlineStr">
+      <c r="G36" s="20" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H36" s="17" t="inlineStr">
+      <c r="H36" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 00:47 UTC</t>
         </is>
       </c>
-      <c r="I36" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J36" s="19" t="inlineStr">
+      <c r="I36" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J36" s="22" t="inlineStr">
         <is>
           <t>https://my.linkedin.com/jobs/view/intern-it-ai-engineering-at-generali-malaysia-4403153262?refId=h4J9hFjDRjjPW7bUqRcUZQ%3D%3D&amp;trackingId=WmqITEtGX486sbNH6b%2BYmA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K36" s="17" t="inlineStr">
+      <c r="K36" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-generali-malaysia-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L36" s="17" t="inlineStr">
+      <c r="L36" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-generali-malaysia-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M36" s="17" t="inlineStr"/>
+      <c r="M36" s="20" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>linkedin_4402311007</t>
         </is>
       </c>
-      <c r="B37" s="17" t="inlineStr">
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C37" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="inlineStr">
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E37" s="17" t="inlineStr">
+      <c r="E37" s="20" t="inlineStr">
         <is>
           <t>SAP iXp Intern - Customer Success Engineering, Operations &amp; AI Enablement [Boston]</t>
         </is>
       </c>
-      <c r="F37" s="17" t="inlineStr">
+      <c r="F37" s="20" t="inlineStr">
         <is>
           <t>Burlington, MA</t>
         </is>
       </c>
-      <c r="G37" s="17" t="inlineStr">
+      <c r="G37" s="20" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H37" s="17" t="inlineStr">
+      <c r="H37" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 21:40 UTC</t>
         </is>
       </c>
-      <c r="I37" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J37" s="19" t="inlineStr">
+      <c r="I37" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J37" s="22" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/sap-ixp-intern-%C2%A0customer-success-engineering-operations-ai-enablement-boston-at-sap-4402311007?refId=ofb0jzd8xWUoUtvr7A%2BwXQ%3D%3D&amp;trackingId=S%2Fo4FvRdeOcn00Jo5DVUBw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K37" s="17" t="inlineStr">
+      <c r="K37" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L37" s="17" t="inlineStr">
+      <c r="L37" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M37" s="17" t="inlineStr"/>
+      <c r="M37" s="20" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>linkedin_4403154707</t>
         </is>
       </c>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C38" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="inlineStr">
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E38" s="17" t="inlineStr">
+      <c r="E38" s="20" t="inlineStr">
         <is>
           <t>Software Engineer Intern, Perception Data</t>
         </is>
       </c>
-      <c r="F38" s="17" t="inlineStr">
+      <c r="F38" s="20" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G38" s="17" t="inlineStr">
+      <c r="G38" s="20" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H38" s="17" t="inlineStr">
+      <c r="H38" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 02:21 UTC</t>
         </is>
       </c>
-      <c r="I38" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J38" s="19" t="inlineStr">
+      <c r="I38" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J38" s="22" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/software-engineer-intern-perception-data-at-zoox-4403154707?refId=ON4L5FUhksKAgylRRsNllQ%3D%3D&amp;trackingId=1%2F3OkqP%2Bu0PqHp9bXnlS0A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K38" s="17" t="inlineStr">
+      <c r="K38" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L38" s="17" t="inlineStr">
+      <c r="L38" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M38" s="17" t="inlineStr"/>
+      <c r="M38" s="20" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>linkedin_4402947451</t>
         </is>
       </c>
-      <c r="B39" s="17" t="inlineStr">
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
         <is>
           <t>Rubrik</t>
         </is>
       </c>
-      <c r="E39" s="17" t="inlineStr">
+      <c r="E39" s="20" t="inlineStr">
         <is>
           <t>India Benefits &amp; AI Operations Intern</t>
         </is>
       </c>
-      <c r="F39" s="17" t="inlineStr">
+      <c r="F39" s="20" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G39" s="17" t="inlineStr">
+      <c r="G39" s="20" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H39" s="17" t="inlineStr">
+      <c r="H39" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 11:40 UTC</t>
         </is>
       </c>
-      <c r="I39" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J39" s="19" t="inlineStr">
+      <c r="I39" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J39" s="22" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/india-benefits-ai-operations-intern-at-rubrik-4402947451?refId=9u2uyUYzyMZimaTtDELDWg%3D%3D&amp;trackingId=BjOmyeYm6McmUpzLwcES9g%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K39" s="17" t="inlineStr">
+      <c r="K39" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-rubrik-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L39" s="17" t="inlineStr">
+      <c r="L39" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-rubrik-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M39" s="17" t="inlineStr"/>
+      <c r="M39" s="20" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>linkedin_4390354006</t>
         </is>
       </c>
-      <c r="B40" s="17" t="inlineStr">
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C40" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="inlineStr">
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
         <is>
           <t>Lila Sciences</t>
         </is>
       </c>
-      <c r="E40" s="17" t="inlineStr">
+      <c r="E40" s="20" t="inlineStr">
         <is>
           <t>Intern, Next Gen AI Robotics</t>
         </is>
       </c>
-      <c r="F40" s="17" t="inlineStr">
+      <c r="F40" s="20" t="inlineStr">
         <is>
           <t>Cambridge, MA</t>
         </is>
       </c>
-      <c r="G40" s="17" t="inlineStr">
+      <c r="G40" s="20" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H40" s="17" t="inlineStr">
+      <c r="H40" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 10:58 UTC</t>
         </is>
       </c>
-      <c r="I40" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J40" s="19" t="inlineStr">
+      <c r="I40" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J40" s="22" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/intern-next-gen-ai-robotics-at-lila-sciences-4390354006?refId=ZoXJQXesL%2FE%2B5EAGGzWfiA%3D%3D&amp;trackingId=FmSMwWhyyIaC52NsDwOCtw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K40" s="17" t="inlineStr">
+      <c r="K40" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-lila-sciences-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L40" s="17" t="inlineStr">
+      <c r="L40" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-lila-sciences-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M40" s="17" t="inlineStr"/>
+      <c r="M40" s="20" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>arbeitnow_ai-venture-development-tech-intern-berlin-100382</t>
         </is>
       </c>
-      <c r="B41" s="17" t="inlineStr">
+      <c r="B41" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C41" s="17" t="inlineStr">
+      <c r="C41" s="20" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="D41" s="17" t="inlineStr">
+      <c r="D41" s="20" t="inlineStr">
         <is>
           <t>Zeeg</t>
         </is>
       </c>
-      <c r="E41" s="17" t="inlineStr">
+      <c r="E41" s="20" t="inlineStr">
         <is>
           <t>AI &amp; Venture Development Tech Intern (w/m/d)</t>
         </is>
       </c>
-      <c r="F41" s="17" t="inlineStr">
+      <c r="F41" s="20" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="G41" s="17" t="inlineStr">
+      <c r="G41" s="20" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H41" s="17" t="inlineStr">
+      <c r="H41" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 10:30 UTC</t>
         </is>
       </c>
-      <c r="I41" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J41" s="19" t="inlineStr">
+      <c r="I41" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J41" s="22" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/zeeg/ai-venture-development-tech-intern-berlin-100382</t>
         </is>
       </c>
-      <c r="K41" s="17" t="inlineStr">
+      <c r="K41" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zeeg-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L41" s="17" t="inlineStr">
+      <c r="L41" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zeeg-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M41" s="17" t="inlineStr"/>
+      <c r="M41" s="20" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>linkedin_4391388054</t>
         </is>
       </c>
-      <c r="B42" s="17" t="inlineStr">
+      <c r="B42" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C42" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="inlineStr">
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
         <is>
           <t>Mackenzie Investments</t>
         </is>
       </c>
-      <c r="E42" s="17" t="inlineStr">
+      <c r="E42" s="20" t="inlineStr">
         <is>
           <t>Fall Intern 2026 - Data Science (Toronto Office)</t>
         </is>
       </c>
-      <c r="F42" s="17" t="inlineStr">
+      <c r="F42" s="20" t="inlineStr">
         <is>
           <t>Greater Toronto Area, Canada</t>
         </is>
       </c>
-      <c r="G42" s="17" t="inlineStr">
+      <c r="G42" s="20" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H42" s="17" t="inlineStr">
+      <c r="H42" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 14:00 UTC</t>
         </is>
       </c>
-      <c r="I42" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J42" s="19" t="inlineStr">
+      <c r="I42" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J42" s="22" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/fall-intern-2026-data-science-toronto-office-at-mackenzie-investments-4391388054?refId=ay8O%2Bgf7Gtfb1Rpr3XZOhg%3D%3D&amp;trackingId=O%2F%2FJTpCmUhvp4jSfNkV5bg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K42" s="17" t="inlineStr">
+      <c r="K42" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-mackenzie-investments-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L42" s="17" t="inlineStr">
+      <c r="L42" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-mackenzie-investments-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M42" s="17" t="inlineStr"/>
+      <c r="M42" s="20" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>linkedin_4390747937</t>
         </is>
       </c>
-      <c r="B43" s="17" t="inlineStr">
+      <c r="B43" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C43" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="inlineStr">
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
         <is>
           <t>BCG X</t>
         </is>
       </c>
-      <c r="E43" s="17" t="inlineStr">
+      <c r="E43" s="20" t="inlineStr">
         <is>
           <t>Visiting Forward Deployed AI Engineer, Internship, Germany - BCG X</t>
         </is>
       </c>
-      <c r="F43" s="17" t="inlineStr">
+      <c r="F43" s="20" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G43" s="17" t="inlineStr">
+      <c r="G43" s="20" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H43" s="17" t="inlineStr">
+      <c r="H43" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 13:51 UTC</t>
         </is>
       </c>
-      <c r="I43" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J43" s="19" t="inlineStr">
+      <c r="I43" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J43" s="22" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/visiting-forward-deployed-ai-engineer-internship-germany-bcg-x-at-bcg-x-4390747937?refId=1JxxxPqdlRpkbbaCzu2YGQ%3D%3D&amp;trackingId=7x%2BVQU%2BWOh9IPaVXWJkc5g%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K43" s="17" t="inlineStr">
+      <c r="K43" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bcg-x-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L43" s="17" t="inlineStr">
+      <c r="L43" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bcg-x-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M43" s="17" t="inlineStr"/>
+      <c r="M43" s="20" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="17" t="inlineStr">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>linkedin_4402726053</t>
         </is>
       </c>
-      <c r="B44" s="17" t="inlineStr">
+      <c r="B44" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C44" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D44" s="17" t="inlineStr">
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
         <is>
           <t>targetjobs UK</t>
         </is>
       </c>
-      <c r="E44" s="17" t="inlineStr">
+      <c r="E44" s="20" t="inlineStr">
         <is>
           <t>Internship: AI/ML for Ionospheric TEC Modelling</t>
         </is>
       </c>
-      <c r="F44" s="17" t="inlineStr">
+      <c r="F44" s="20" t="inlineStr">
         <is>
           <t>Reigate, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G44" s="17" t="inlineStr">
+      <c r="G44" s="20" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H44" s="17" t="inlineStr">
+      <c r="H44" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 14:25 UTC</t>
         </is>
       </c>
-      <c r="I44" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J44" s="19" t="inlineStr">
+      <c r="I44" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J44" s="22" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/internship-ai-ml-for-ionospheric-tec-modelling-at-targetjobs-uk-4402726053?refId=a1g6hMZsvI1y2Eje2OvLAA%3D%3D&amp;trackingId=IVJSJGE7Non8cohorDs%2F5A%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K44" s="17" t="inlineStr">
+      <c r="K44" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-targetjobs-uk-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L44" s="17" t="inlineStr">
+      <c r="L44" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-targetjobs-uk-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M44" s="17" t="inlineStr"/>
+      <c r="M44" s="20" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>linkedin_4400837114</t>
         </is>
       </c>
-      <c r="B45" s="17" t="inlineStr">
+      <c r="B45" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C45" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="inlineStr">
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
         <is>
           <t>Innovexis</t>
         </is>
       </c>
-      <c r="E45" s="17" t="inlineStr">
+      <c r="E45" s="20" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F45" s="17" t="inlineStr">
+      <c r="F45" s="20" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G45" s="17" t="inlineStr">
+      <c r="G45" s="20" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H45" s="17" t="inlineStr">
+      <c r="H45" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 13:04 UTC</t>
         </is>
       </c>
-      <c r="I45" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J45" s="19" t="inlineStr">
+      <c r="I45" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J45" s="22" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-innovexis-4400837114?refId=CVM89%2F3%2F%2BshqMJLc4IfFMg%3D%3D&amp;trackingId=j9WpQwI4k1ip7aRr%2Fv5Img%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K45" s="17" t="inlineStr">
+      <c r="K45" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-innovexis-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L45" s="17" t="inlineStr">
+      <c r="L45" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-innovexis-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M45" s="17" t="inlineStr"/>
+      <c r="M45" s="20" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="17" t="inlineStr">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>linkedin_4391074158</t>
         </is>
       </c>
-      <c r="B46" s="17" t="inlineStr">
+      <c r="B46" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C46" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D46" s="17" t="inlineStr">
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
         <is>
           <t>BMW Group</t>
         </is>
       </c>
-      <c r="E46" s="17" t="inlineStr">
+      <c r="E46" s="20" t="inlineStr">
         <is>
           <t>Intern IT Technology, Sales Volume Planning &amp; AI Support (f/m/x)</t>
         </is>
       </c>
-      <c r="F46" s="17" t="inlineStr">
+      <c r="F46" s="20" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G46" s="17" t="inlineStr">
+      <c r="G46" s="20" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H46" s="17" t="inlineStr">
+      <c r="H46" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 12:45 UTC</t>
         </is>
       </c>
-      <c r="I46" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J46" s="19" t="inlineStr">
+      <c r="I46" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J46" s="22" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/intern-it-technology-sales-volume-planning-ai-support-f-m-x-at-bmw-group-4391074158?refId=tHG5EqbLn3IDBqsSj%2FsUUg%3D%3D&amp;trackingId=OakOlgDcU0hWTRXcoLe3UA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K46" s="17" t="inlineStr">
+      <c r="K46" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bmw-group-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L46" s="17" t="inlineStr">
+      <c r="L46" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bmw-group-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M46" s="17" t="inlineStr"/>
+      <c r="M46" s="20" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="17" t="inlineStr">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>linkedin_4402725075</t>
         </is>
       </c>
-      <c r="B47" s="17" t="inlineStr">
+      <c r="B47" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C47" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D47" s="17" t="inlineStr">
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
         <is>
           <t>DARE</t>
         </is>
       </c>
-      <c r="E47" s="17" t="inlineStr">
+      <c r="E47" s="20" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F47" s="17" t="inlineStr">
+      <c r="F47" s="20" t="inlineStr">
         <is>
           <t>WP. Kuala Lumpur, Federal Territory of Kuala Lumpur, Malaysia</t>
         </is>
       </c>
-      <c r="G47" s="17" t="inlineStr">
+      <c r="G47" s="20" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H47" s="17" t="inlineStr">
+      <c r="H47" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 14:36 UTC</t>
         </is>
       </c>
-      <c r="I47" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J47" s="19" t="inlineStr">
+      <c r="I47" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J47" s="22" t="inlineStr">
         <is>
           <t>https://my.linkedin.com/jobs/view/research-intern-at-dare-4402725075?refId=xbzZXyF6FfcYy036eklDWw%3D%3D&amp;trackingId=QRt5DhbLSINvmHia0jEWIg%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K47" s="17" t="inlineStr">
+      <c r="K47" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dare-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L47" s="17" t="inlineStr">
+      <c r="L47" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dare-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M47" s="17" t="inlineStr"/>
+      <c r="M47" s="20" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="17" t="inlineStr">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>linkedin_4402745391</t>
         </is>
       </c>
-      <c r="B48" s="17" t="inlineStr">
+      <c r="B48" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C48" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D48" s="17" t="inlineStr">
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
         <is>
           <t>Huawei Technologies Research &amp; Development (UK) Ltd</t>
         </is>
       </c>
-      <c r="E48" s="17" t="inlineStr">
+      <c r="E48" s="20" t="inlineStr">
         <is>
           <t>Research Intern - Computer Vision</t>
         </is>
       </c>
-      <c r="F48" s="17" t="inlineStr">
+      <c r="F48" s="20" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G48" s="17" t="inlineStr">
+      <c r="G48" s="20" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H48" s="17" t="inlineStr">
+      <c r="H48" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 18:42 UTC</t>
         </is>
       </c>
-      <c r="I48" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J48" s="19" t="inlineStr">
+      <c r="I48" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J48" s="22" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/research-intern-computer-vision-at-huawei-technologies-research-development-uk-ltd-4402745391?refId=rRtCMQFBU%2FNi7vc62x5Nhg%3D%3D&amp;trackingId=%2Bt1We%2BmKhWHyXION%2FWwQVg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K48" s="17" t="inlineStr">
+      <c r="K48" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-huawei-technologies-research-development-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L48" s="17" t="inlineStr">
+      <c r="L48" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-huawei-technologies-research-development-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M48" s="17" t="inlineStr"/>
+      <c r="M48" s="20" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="17" t="inlineStr">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>linkedin_4402366780</t>
         </is>
       </c>
-      <c r="B49" s="17" t="inlineStr">
+      <c r="B49" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C49" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D49" s="17" t="inlineStr">
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
         <is>
           <t>Binance</t>
         </is>
       </c>
-      <c r="E49" s="17" t="inlineStr">
+      <c r="E49" s="20" t="inlineStr">
         <is>
           <t>Binance Accelerator Program - Data Scientist (LLM &amp; Trading)</t>
         </is>
       </c>
-      <c r="F49" s="17" t="inlineStr">
+      <c r="F49" s="20" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G49" s="17" t="inlineStr">
+      <c r="G49" s="20" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H49" s="17" t="inlineStr">
+      <c r="H49" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 09:43 UTC</t>
         </is>
       </c>
-      <c r="I49" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J49" s="19" t="inlineStr">
+      <c r="I49" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J49" s="22" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/binance-accelerator-program-data-scientist-llm-trading-at-binance-4402366780?refId=bc%2BXeBTeIKMQJTmlLFwbZQ%3D%3D&amp;trackingId=9UuyRRCEPapWNu6VKdZC5A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K49" s="17" t="inlineStr">
+      <c r="K49" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-binance-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L49" s="17" t="inlineStr">
+      <c r="L49" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-binance-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M49" s="17" t="inlineStr"/>
+      <c r="M49" s="20" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="inlineStr">
+      <c r="A50" s="20" t="inlineStr">
         <is>
           <t>linkedin_4382411039</t>
         </is>
       </c>
-      <c r="B50" s="17" t="inlineStr">
+      <c r="B50" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C50" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D50" s="17" t="inlineStr">
+      <c r="C50" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="inlineStr">
         <is>
           <t>The Walt Disney Company</t>
         </is>
       </c>
-      <c r="E50" s="17" t="inlineStr">
+      <c r="E50" s="20" t="inlineStr">
         <is>
           <t>Intern, APAC Data Analytics &amp; Insights (Content Analytics) -  Jul to Dec 2026</t>
         </is>
       </c>
-      <c r="F50" s="17" t="inlineStr">
+      <c r="F50" s="20" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G50" s="17" t="inlineStr">
+      <c r="G50" s="20" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H50" s="17" t="inlineStr">
+      <c r="H50" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 23:55 UTC</t>
         </is>
       </c>
-      <c r="I50" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J50" s="19" t="inlineStr">
+      <c r="I50" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J50" s="22" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/intern-apac-data-analytics-insights-content-analytics-jul-to-dec-2026-at-the-walt-disney-company-4382411039?refId=JBvXH2fNOamnO4WZI1Y0ew%3D%3D&amp;trackingId=Rs%2FdjczlbLYSYtCwY%2F%2FJyA%3D%3D&amp;position=7&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K50" s="17" t="inlineStr">
+      <c r="K50" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-the-walt-disney-company-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L50" s="17" t="inlineStr">
+      <c r="L50" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-the-walt-disney-company-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M50" s="17" t="inlineStr"/>
+      <c r="M50" s="20" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="17" t="inlineStr">
+      <c r="A51" s="20" t="inlineStr">
         <is>
           <t>linkedin_4402305263</t>
         </is>
       </c>
-      <c r="B51" s="17" t="inlineStr">
+      <c r="B51" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C51" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D51" s="17" t="inlineStr">
+      <c r="C51" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E51" s="17" t="inlineStr">
+      <c r="E51" s="20" t="inlineStr">
         <is>
           <t>SAP iXp Intern - Software Developer (Agentic AI &amp; LLM systems)</t>
         </is>
       </c>
-      <c r="F51" s="17" t="inlineStr">
+      <c r="F51" s="20" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G51" s="17" t="inlineStr">
+      <c r="G51" s="20" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H51" s="17" t="inlineStr">
+      <c r="H51" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 21:40 UTC</t>
         </is>
       </c>
-      <c r="I51" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J51" s="19" t="inlineStr">
+      <c r="I51" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J51" s="22" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/sap-ixp-intern-software-developer-agentic-ai-llm-systems-at-sap-4402305263?refId=zBXuSSlfFyuxcdEqyfeS8g%3D%3D&amp;trackingId=Imq%2FVHMQWkkoDZp5%2BnATSA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K51" s="17" t="inlineStr">
+      <c r="K51" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L51" s="17" t="inlineStr">
+      <c r="L51" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M51" s="17" t="inlineStr"/>
+      <c r="M51" s="20" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="17" t="inlineStr">
+      <c r="A52" s="20" t="inlineStr">
         <is>
           <t>linkedin_4400467080</t>
         </is>
       </c>
-      <c r="B52" s="17" t="inlineStr">
+      <c r="B52" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C52" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D52" s="17" t="inlineStr">
+      <c r="C52" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
         <is>
           <t>Saama</t>
         </is>
       </c>
-      <c r="E52" s="17" t="inlineStr">
+      <c r="E52" s="20" t="inlineStr">
         <is>
           <t>Intern for AI CoE</t>
         </is>
       </c>
-      <c r="F52" s="17" t="inlineStr">
+      <c r="F52" s="20" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G52" s="17" t="inlineStr">
+      <c r="G52" s="20" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H52" s="17" t="inlineStr">
+      <c r="H52" s="20" t="inlineStr">
         <is>
           <t>2026-04-16 19:45 UTC</t>
         </is>
       </c>
-      <c r="I52" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J52" s="19" t="inlineStr">
+      <c r="I52" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J52" s="22" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/intern-for-ai-coe-at-saama-4400467080?refId=7CvDuV2%2BR%2FzyGozq4UNPPw%3D%3D&amp;trackingId=Ls9yWFAC8lVRx8bmapJfLA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K52" s="17" t="inlineStr">
+      <c r="K52" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-saama-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L52" s="17" t="inlineStr">
+      <c r="L52" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-saama-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M52" s="17" t="inlineStr"/>
+      <c r="M52" s="20" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="17" t="inlineStr">
+      <c r="A53" s="20" t="inlineStr">
         <is>
           <t>linkedin_4400873418</t>
         </is>
       </c>
-      <c r="B53" s="17" t="inlineStr">
+      <c r="B53" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C53" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D53" s="17" t="inlineStr">
+      <c r="C53" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="inlineStr">
         <is>
           <t>SANOVIO</t>
         </is>
       </c>
-      <c r="E53" s="17" t="inlineStr">
+      <c r="E53" s="20" t="inlineStr">
         <is>
           <t>AI Engineering Intern</t>
         </is>
       </c>
-      <c r="F53" s="17" t="inlineStr">
+      <c r="F53" s="20" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G53" s="17" t="inlineStr">
+      <c r="G53" s="20" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H53" s="17" t="inlineStr">
+      <c r="H53" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 00:00 UTC</t>
         </is>
       </c>
-      <c r="I53" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J53" s="19" t="inlineStr">
+      <c r="I53" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J53" s="22" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/ai-engineering-intern-at-sanovio-4400873418?refId=egIYeNLcARu6P6oTIZ%2BHfA%3D%3D&amp;trackingId=c6wZ0DtTzvVZpTRC1l5tYQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K53" s="17" t="inlineStr">
+      <c r="K53" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sanovio-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L53" s="17" t="inlineStr">
+      <c r="L53" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sanovio-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M53" s="17" t="inlineStr"/>
+      <c r="M53" s="20" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="17" t="inlineStr">
+      <c r="A54" s="20" t="inlineStr">
         <is>
           <t>linkedin_4403524251</t>
         </is>
       </c>
-      <c r="B54" s="17" t="inlineStr">
+      <c r="B54" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C54" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D54" s="17" t="inlineStr">
+      <c r="C54" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D54" s="20" t="inlineStr">
         <is>
           <t>Nascent Markets</t>
         </is>
       </c>
-      <c r="E54" s="17" t="inlineStr">
+      <c r="E54" s="20" t="inlineStr">
         <is>
           <t>Agentic Systems Intern (Graduate Level)</t>
         </is>
       </c>
-      <c r="F54" s="17" t="inlineStr">
+      <c r="F54" s="20" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G54" s="17" t="inlineStr">
+      <c r="G54" s="20" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H54" s="17" t="inlineStr">
+      <c r="H54" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 19:53 UTC</t>
         </is>
       </c>
-      <c r="I54" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J54" s="19" t="inlineStr">
+      <c r="I54" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J54" s="22" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/agentic-systems-intern-graduate-level-at-nascent-markets-4403524251?refId=Ix0g0waARRaNpzTY4LxvsQ%3D%3D&amp;trackingId=RsqyOyJHkanw%2FTeHGUcadA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K54" s="17" t="inlineStr">
+      <c r="K54" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-nascent-markets-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L54" s="17" t="inlineStr">
+      <c r="L54" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-nascent-markets-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M54" s="17" t="inlineStr"/>
+      <c r="M54" s="20" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="17" t="inlineStr">
+      <c r="A55" s="20" t="inlineStr">
         <is>
           <t>linkedin_4402782985</t>
         </is>
       </c>
-      <c r="B55" s="17" t="inlineStr">
+      <c r="B55" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C55" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D55" s="17" t="inlineStr">
+      <c r="C55" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D55" s="20" t="inlineStr">
         <is>
           <t>Axiomatic_AI</t>
         </is>
       </c>
-      <c r="E55" s="17" t="inlineStr">
+      <c r="E55" s="20" t="inlineStr">
         <is>
           <t>Internship - Research Intern (Agentic Learning, Memory &amp; Neurosymbolic Reasoning)</t>
         </is>
       </c>
-      <c r="F55" s="17" t="inlineStr">
+      <c r="F55" s="20" t="inlineStr">
         <is>
           <t>Greater Barcelona Metropolitan Area</t>
         </is>
       </c>
-      <c r="G55" s="17" t="inlineStr">
+      <c r="G55" s="20" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H55" s="17" t="inlineStr">
+      <c r="H55" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 05:04 UTC</t>
         </is>
       </c>
-      <c r="I55" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J55" s="19" t="inlineStr">
+      <c r="I55" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J55" s="22" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/internship-research-intern-agentic-learning-memory-neurosymbolic-reasoning-at-axiomatic-ai-4402782985?refId=vm6No12NjZrg2BBV%2BnbuLQ%3D%3D&amp;trackingId=X9FXk%2FBDFftROMNo9Cr20g%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K55" s="17" t="inlineStr">
+      <c r="K55" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-axiomatic-ai-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L55" s="17" t="inlineStr">
+      <c r="L55" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-axiomatic-ai-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M55" s="17" t="inlineStr"/>
+      <c r="M55" s="20" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="17" t="inlineStr">
+      <c r="A56" s="20" t="inlineStr">
         <is>
           <t>linkedin_4309694978</t>
         </is>
       </c>
-      <c r="B56" s="17" t="inlineStr">
+      <c r="B56" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C56" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D56" s="17" t="inlineStr">
+      <c r="C56" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D56" s="20" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E56" s="17" t="inlineStr">
+      <c r="E56" s="20" t="inlineStr">
         <is>
           <t>Graduate Physics Research Intern</t>
         </is>
       </c>
-      <c r="F56" s="17" t="inlineStr">
+      <c r="F56" s="20" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
       </c>
-      <c r="G56" s="17" t="inlineStr">
+      <c r="G56" s="20" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H56" s="17" t="inlineStr">
+      <c r="H56" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 17:37 UTC</t>
         </is>
       </c>
-      <c r="I56" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J56" s="19" t="inlineStr">
+      <c r="I56" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J56" s="22" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/graduate-physics-research-intern-at-dataannotation-4309694978?refId=hlpC50hTZs9sJFHirXWMSg%3D%3D&amp;trackingId=1E0ixzzpb6MzeHKgxpE3Cw%3D%3D&amp;position=9&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K56" s="17" t="inlineStr">
+      <c r="K56" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L56" s="17" t="inlineStr">
+      <c r="L56" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M56" s="17" t="inlineStr"/>
+      <c r="M56" s="20" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="17" t="inlineStr">
+      <c r="A57" s="20" t="inlineStr">
         <is>
           <t>linkedin_4403562730</t>
         </is>
       </c>
-      <c r="B57" s="17" t="inlineStr">
+      <c r="B57" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C57" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D57" s="17" t="inlineStr">
+      <c r="C57" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D57" s="20" t="inlineStr">
         <is>
           <t>BNM Business Solutions LLP</t>
         </is>
       </c>
-      <c r="E57" s="17" t="inlineStr">
+      <c r="E57" s="20" t="inlineStr">
         <is>
           <t>Data Analyst Internship in Navi Mumbai, Mumbai</t>
         </is>
       </c>
-      <c r="F57" s="17" t="inlineStr">
+      <c r="F57" s="20" t="inlineStr">
         <is>
           <t>Mumbai Metropolitan Region</t>
         </is>
       </c>
-      <c r="G57" s="17" t="inlineStr">
+      <c r="G57" s="20" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H57" s="17" t="inlineStr">
+      <c r="H57" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 00:06 UTC</t>
         </is>
       </c>
-      <c r="I57" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J57" s="19" t="inlineStr">
+      <c r="I57" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J57" s="22" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-internship-in-navi-mumbai-mumbai-at-bnm-business-solutions-llp-4403562730?refId=1X9LgKP3%2FAPeJuhZVjyhxw%3D%3D&amp;trackingId=oFY9Z69ZBEGkNtq0cbBOMw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K57" s="17" t="inlineStr">
+      <c r="K57" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bnm-business-solutions-llp-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L57" s="17" t="inlineStr">
+      <c r="L57" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bnm-business-solutions-llp-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M57" s="17" t="inlineStr"/>
+      <c r="M57" s="20" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="17" t="inlineStr">
+      <c r="A58" s="20" t="inlineStr">
         <is>
           <t>linkedin_4309694917</t>
         </is>
       </c>
-      <c r="B58" s="17" t="inlineStr">
+      <c r="B58" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C58" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D58" s="17" t="inlineStr">
+      <c r="C58" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D58" s="20" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E58" s="17" t="inlineStr">
+      <c r="E58" s="20" t="inlineStr">
         <is>
           <t>Graduate Biology Research Intern</t>
         </is>
       </c>
-      <c r="F58" s="17" t="inlineStr">
+      <c r="F58" s="20" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
       </c>
-      <c r="G58" s="17" t="inlineStr">
+      <c r="G58" s="20" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H58" s="17" t="inlineStr">
+      <c r="H58" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 17:35 UTC</t>
         </is>
       </c>
-      <c r="I58" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J58" s="19" t="inlineStr">
+      <c r="I58" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J58" s="22" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/graduate-biology-research-intern-at-dataannotation-4309694917?refId=hlpC50hTZs9sJFHirXWMSg%3D%3D&amp;trackingId=BM%2FBx4ElnXDk5hEpiM0gzg%3D%3D&amp;position=8&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K58" s="17" t="inlineStr">
+      <c r="K58" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L58" s="17" t="inlineStr">
+      <c r="L58" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M58" s="17" t="inlineStr"/>
+      <c r="M58" s="20" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="17" t="inlineStr">
+      <c r="A59" s="20" t="inlineStr">
         <is>
           <t>linkedin_4346088677</t>
         </is>
       </c>
-      <c r="B59" s="17" t="inlineStr">
+      <c r="B59" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C59" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D59" s="17" t="inlineStr">
+      <c r="C59" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D59" s="20" t="inlineStr">
         <is>
           <t>revel8</t>
         </is>
       </c>
-      <c r="E59" s="17" t="inlineStr">
+      <c r="E59" s="20" t="inlineStr">
         <is>
           <t>Applied AI Engineer Intern (all genders)</t>
         </is>
       </c>
-      <c r="F59" s="17" t="inlineStr">
+      <c r="F59" s="20" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G59" s="17" t="inlineStr">
+      <c r="G59" s="20" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H59" s="17" t="inlineStr">
+      <c r="H59" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 22:38 UTC</t>
         </is>
       </c>
-      <c r="I59" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J59" s="19" t="inlineStr">
+      <c r="I59" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J59" s="22" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/applied-ai-engineer-intern-all-genders-at-revel8-4346088677?refId=FHQDN2Ta3J6B7WhWnDAuhQ%3D%3D&amp;trackingId=Pf%2Ftwn6H5Hrw8BKjPenbSQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K59" s="17" t="inlineStr">
+      <c r="K59" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-revel8-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L59" s="17" t="inlineStr">
+      <c r="L59" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-revel8-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M59" s="17" t="inlineStr"/>
+      <c r="M59" s="20" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="17" t="inlineStr">
+      <c r="A60" s="20" t="inlineStr">
         <is>
           <t>linkedin_4403475387</t>
         </is>
       </c>
-      <c r="B60" s="17" t="inlineStr">
+      <c r="B60" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C60" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D60" s="17" t="inlineStr">
+      <c r="C60" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D60" s="20" t="inlineStr">
         <is>
           <t>Inc42 Media</t>
         </is>
       </c>
-      <c r="E60" s="17" t="inlineStr">
+      <c r="E60" s="20" t="inlineStr">
         <is>
           <t>Operations Intern: Inc42 AI Summit 2026</t>
         </is>
       </c>
-      <c r="F60" s="17" t="inlineStr">
+      <c r="F60" s="20" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G60" s="17" t="inlineStr">
+      <c r="G60" s="20" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H60" s="17" t="inlineStr">
+      <c r="H60" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 16:23 UTC</t>
         </is>
       </c>
-      <c r="I60" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J60" s="19" t="inlineStr">
+      <c r="I60" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J60" s="22" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/operations-intern-inc42-ai-summit-2026-at-inc42-media-4403475387?refId=jyI2mJ9xFT%2BmdtkV0OCW0g%3D%3D&amp;trackingId=6sWKnvWNaTU69%2B7bcZNxLg%3D%3D&amp;position=10&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K60" s="17" t="inlineStr">
+      <c r="K60" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-inc42-media-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L60" s="17" t="inlineStr">
+      <c r="L60" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-inc42-media-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M60" s="17" t="inlineStr"/>
+      <c r="M60" s="20" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="17" t="inlineStr">
+      <c r="A61" s="20" t="inlineStr">
         <is>
           <t>linkedin_4403008384</t>
         </is>
       </c>
-      <c r="B61" s="17" t="inlineStr">
+      <c r="B61" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C61" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D61" s="17" t="inlineStr">
+      <c r="C61" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D61" s="20" t="inlineStr">
         <is>
           <t>VEDANTA MOBILITY</t>
         </is>
       </c>
-      <c r="E61" s="17" t="inlineStr">
+      <c r="E61" s="20" t="inlineStr">
         <is>
           <t>Founding Psychology Interns | AI Prototype (Govt Proposal – Dubai)</t>
         </is>
       </c>
-      <c r="F61" s="17" t="inlineStr">
+      <c r="F61" s="20" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G61" s="17" t="inlineStr">
+      <c r="G61" s="20" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H61" s="17" t="inlineStr">
+      <c r="H61" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 08:13 UTC</t>
         </is>
       </c>
-      <c r="I61" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J61" s="19" t="inlineStr">
+      <c r="I61" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J61" s="22" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/founding-psychology-interns-ai-prototype-govt-proposal-%E2%80%93-dubai-at-vedanta-mobility-4403008384?refId=moHjgKNH%2BrT9YT5JNnyyqw%3D%3D&amp;trackingId=RUjUOgXLH%2BLJwdPLtKtAMQ%3D%3D&amp;position=13&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K61" s="17" t="inlineStr">
+      <c r="K61" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-vedanta-mobility-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L61" s="17" t="inlineStr">
+      <c r="L61" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-vedanta-mobility-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M61" s="17" t="inlineStr"/>
+      <c r="M61" s="20" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="17" t="inlineStr">
+      <c r="A62" s="20" t="inlineStr">
         <is>
           <t>linkedin_4393616864</t>
         </is>
       </c>
-      <c r="B62" s="17" t="inlineStr">
+      <c r="B62" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C62" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D62" s="17" t="inlineStr">
+      <c r="C62" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D62" s="20" t="inlineStr">
         <is>
           <t>Medidata Solutions</t>
         </is>
       </c>
-      <c r="E62" s="17" t="inlineStr">
+      <c r="E62" s="20" t="inlineStr">
         <is>
           <t>Data Science Intern</t>
         </is>
       </c>
-      <c r="F62" s="17" t="inlineStr">
+      <c r="F62" s="20" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
       </c>
-      <c r="G62" s="17" t="inlineStr">
+      <c r="G62" s="20" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H62" s="17" t="inlineStr">
+      <c r="H62" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 13:13 UTC</t>
         </is>
       </c>
-      <c r="I62" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J62" s="19" t="inlineStr">
+      <c r="I62" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J62" s="22" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-science-intern-at-medidata-solutions-4393616864?refId=sPMU%2B0UtbDUVjDHc3gXCxA%3D%3D&amp;trackingId=%2BVrdVCzEYQ3jJQvUf4VUtA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K62" s="17" t="inlineStr">
+      <c r="K62" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-medidata-solutions-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L62" s="17" t="inlineStr">
+      <c r="L62" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-medidata-solutions-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M62" s="17" t="inlineStr"/>
+      <c r="M62" s="20" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="17" t="inlineStr">
+      <c r="A63" s="20" t="inlineStr">
         <is>
           <t>linkedin_4403819462</t>
         </is>
       </c>
-      <c r="B63" s="17" t="inlineStr">
+      <c r="B63" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C63" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D63" s="17" t="inlineStr">
+      <c r="C63" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D63" s="20" t="inlineStr">
         <is>
           <t>Calypso Commodities</t>
         </is>
       </c>
-      <c r="E63" s="17" t="inlineStr">
+      <c r="E63" s="20" t="inlineStr">
         <is>
           <t>Trading - Quant &amp; Engineering Intern (Client-Facing)</t>
         </is>
       </c>
-      <c r="F63" s="17" t="inlineStr">
+      <c r="F63" s="20" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="G63" s="17" t="inlineStr">
+      <c r="G63" s="20" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H63" s="17" t="inlineStr">
+      <c r="H63" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 12:44 UTC</t>
         </is>
       </c>
-      <c r="I63" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J63" s="19" t="inlineStr">
+      <c r="I63" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J63" s="22" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/trading-quant-engineering-intern-client-facing-at-calypso-commodities-4403819462?refId=wb%2BADKYeCTj8bBBZgf97xw%3D%3D&amp;trackingId=o0ZBUwzyVOiml0tJPOsNww%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K63" s="17" t="inlineStr">
+      <c r="K63" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-calypso-commodities-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L63" s="17" t="inlineStr">
+      <c r="L63" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-calypso-commodities-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M63" s="17" t="inlineStr"/>
+      <c r="M63" s="20" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="17" t="inlineStr">
+      <c r="A64" s="20" t="inlineStr">
         <is>
           <t>linkedin_4355269413</t>
         </is>
       </c>
-      <c r="B64" s="17" t="inlineStr">
+      <c r="B64" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C64" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D64" s="17" t="inlineStr">
+      <c r="C64" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D64" s="20" t="inlineStr">
         <is>
           <t>Temasek</t>
         </is>
       </c>
-      <c r="E64" s="17" t="inlineStr">
+      <c r="E64" s="20" t="inlineStr">
         <is>
           <t>Data Analytics/Science Intern, People Technology (Jun/Jul - Dec 2026)</t>
         </is>
       </c>
-      <c r="F64" s="17" t="inlineStr">
+      <c r="F64" s="20" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G64" s="17" t="inlineStr">
+      <c r="G64" s="20" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H64" s="17" t="inlineStr">
+      <c r="H64" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 10:35 UTC</t>
         </is>
       </c>
-      <c r="I64" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J64" s="19" t="inlineStr">
+      <c r="I64" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J64" s="22" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/data-analytics-science-intern-people-technology-jun-jul-dec-2026-at-temasek-4355269413?refId=emjtNEhTXLtOX%2BguWexSsg%3D%3D&amp;trackingId=DPHM%2FIJzKL0emfNJ1LMMoA%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K64" s="17" t="inlineStr">
+      <c r="K64" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-temasek-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L64" s="17" t="inlineStr">
+      <c r="L64" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-temasek-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M64" s="17" t="inlineStr"/>
+      <c r="M64" s="20" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="17" t="inlineStr">
+      <c r="A65" s="20" t="inlineStr">
         <is>
           <t>linkedin_4403065097</t>
         </is>
       </c>
-      <c r="B65" s="17" t="inlineStr">
+      <c r="B65" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C65" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D65" s="17" t="inlineStr">
+      <c r="C65" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D65" s="20" t="inlineStr">
         <is>
           <t>BLACK TREE GAMING LIMITED</t>
         </is>
       </c>
-      <c r="E65" s="17" t="inlineStr">
+      <c r="E65" s="20" t="inlineStr">
         <is>
           <t>Data Scientist (ML)</t>
         </is>
       </c>
-      <c r="F65" s="17" t="inlineStr">
+      <c r="F65" s="20" t="inlineStr">
         <is>
           <t>Greater London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G65" s="17" t="inlineStr">
+      <c r="G65" s="20" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H65" s="17" t="inlineStr">
+      <c r="H65" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 14:22 UTC</t>
         </is>
       </c>
-      <c r="I65" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J65" s="19" t="inlineStr">
+      <c r="I65" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J65" s="22" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/data-scientist-ml-at-black-tree-gaming-limited-4403065097?refId=X9Gb9UkVv%2BJtfDRc0dJPwA%3D%3D&amp;trackingId=Mfl%2BC%2FBN9DJehDmug19dGA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K65" s="17" t="inlineStr">
+      <c r="K65" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-black-tree-gaming-limited-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L65" s="17" t="inlineStr">
+      <c r="L65" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-black-tree-gaming-limited-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M65" s="17" t="inlineStr"/>
+      <c r="M65" s="20" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="17" t="inlineStr">
+      <c r="A66" s="20" t="inlineStr">
         <is>
           <t>linkedin_4291533663</t>
         </is>
       </c>
-      <c r="B66" s="17" t="inlineStr">
+      <c r="B66" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C66" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D66" s="17" t="inlineStr">
+      <c r="C66" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D66" s="20" t="inlineStr">
         <is>
           <t>McKinsey &amp; Company</t>
         </is>
       </c>
-      <c r="E66" s="17" t="inlineStr">
+      <c r="E66" s="20" t="inlineStr">
         <is>
           <t>Praktikum als Fellow Intern - Tech &amp; AI (m/w/d)</t>
         </is>
       </c>
-      <c r="F66" s="17" t="inlineStr">
+      <c r="F66" s="20" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G66" s="17" t="inlineStr">
+      <c r="G66" s="20" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H66" s="17" t="inlineStr">
+      <c r="H66" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 09:49 UTC</t>
         </is>
       </c>
-      <c r="I66" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J66" s="19" t="inlineStr">
+      <c r="I66" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J66" s="22" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/praktikum-als-fellow-intern-tech-ai-m-w-d-at-mckinsey-company-4291533663?refId=UmiOr88gcWDNbqipJy2ZTg%3D%3D&amp;trackingId=UvtRxMXKlReoOEeGgMaEfA%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K66" s="17" t="inlineStr">
+      <c r="K66" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-mckinsey-company-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L66" s="17" t="inlineStr">
+      <c r="L66" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-mckinsey-company-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M66" s="17" t="inlineStr"/>
+      <c r="M66" s="20" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="17" t="inlineStr">
+      <c r="A67" s="20" t="inlineStr">
         <is>
           <t>linkedin_4336838608</t>
         </is>
       </c>
-      <c r="B67" s="17" t="inlineStr">
+      <c r="B67" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C67" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D67" s="17" t="inlineStr">
+      <c r="C67" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D67" s="20" t="inlineStr">
         <is>
           <t>Sendbird</t>
         </is>
       </c>
-      <c r="E67" s="17" t="inlineStr">
+      <c r="E67" s="20" t="inlineStr">
         <is>
           <t>AI Agent Engineer, Intern</t>
         </is>
       </c>
-      <c r="F67" s="17" t="inlineStr">
+      <c r="F67" s="20" t="inlineStr">
         <is>
           <t>Seoul, Seoul, South Korea</t>
         </is>
       </c>
-      <c r="G67" s="17" t="inlineStr">
+      <c r="G67" s="20" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H67" s="17" t="inlineStr">
+      <c r="H67" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 13:46 UTC</t>
         </is>
       </c>
-      <c r="I67" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J67" s="19" t="inlineStr">
+      <c r="I67" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J67" s="22" t="inlineStr">
         <is>
           <t>https://kr.linkedin.com/jobs/view/ai-agent-engineer-intern-at-sendbird-4336838608?refId=%2F1qLChSVn3giUiiNusHaIQ%3D%3D&amp;trackingId=l6mUUvSfC97HjoyrA8uuqg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K67" s="17" t="inlineStr">
+      <c r="K67" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sendbird-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L67" s="17" t="inlineStr">
+      <c r="L67" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sendbird-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M67" s="17" t="inlineStr"/>
+      <c r="M67" s="20" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="17" t="inlineStr">
+      <c r="A68" s="20" t="inlineStr">
         <is>
           <t>linkedin_4372783510</t>
         </is>
       </c>
-      <c r="B68" s="17" t="inlineStr">
+      <c r="B68" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C68" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D68" s="17" t="inlineStr">
+      <c r="C68" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D68" s="20" t="inlineStr">
         <is>
           <t>42dot</t>
         </is>
       </c>
-      <c r="E68" s="17" t="inlineStr">
+      <c r="E68" s="20" t="inlineStr">
         <is>
           <t>[MS/PhD Intern] AI Engineer (정규직 전환형)</t>
         </is>
       </c>
-      <c r="F68" s="17" t="inlineStr">
+      <c r="F68" s="20" t="inlineStr">
         <is>
           <t>Seongnam, Gyeonggi, South Korea</t>
         </is>
       </c>
-      <c r="G68" s="17" t="inlineStr">
+      <c r="G68" s="20" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H68" s="17" t="inlineStr">
+      <c r="H68" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 15:08 UTC</t>
         </is>
       </c>
-      <c r="I68" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J68" s="19" t="inlineStr">
+      <c r="I68" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J68" s="22" t="inlineStr">
         <is>
           <t>https://kr.linkedin.com/jobs/view/ms-phd-intern-ai-engineer-%EC%A0%95%EA%B7%9C%EC%A7%81-%EC%A0%84%ED%99%98%ED%98%95-at-42dot-4372783510?refId=%2F1qLChSVn3giUiiNusHaIQ%3D%3D&amp;trackingId=TVYs5RWI1wgPuuVRiBioUA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K68" s="17" t="inlineStr">
+      <c r="K68" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-42dot-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L68" s="17" t="inlineStr">
+      <c r="L68" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-42dot-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M68" s="17" t="inlineStr"/>
+      <c r="M68" s="20" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="17" t="inlineStr">
+      <c r="A69" s="20" t="inlineStr">
         <is>
           <t>linkedin_4402753102</t>
         </is>
       </c>
-      <c r="B69" s="17" t="inlineStr">
+      <c r="B69" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C69" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D69" s="17" t="inlineStr">
+      <c r="C69" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D69" s="20" t="inlineStr">
         <is>
           <t>Five9</t>
         </is>
       </c>
-      <c r="E69" s="17" t="inlineStr">
+      <c r="E69" s="20" t="inlineStr">
         <is>
           <t>Software Developer AI Insights Intern</t>
         </is>
       </c>
-      <c r="F69" s="17" t="inlineStr">
+      <c r="F69" s="20" t="inlineStr">
         <is>
           <t>San Ramon, CA</t>
         </is>
       </c>
-      <c r="G69" s="17" t="inlineStr">
+      <c r="G69" s="20" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H69" s="17" t="inlineStr">
+      <c r="H69" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 20:56 UTC</t>
         </is>
       </c>
-      <c r="I69" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J69" s="19" t="inlineStr">
+      <c r="I69" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J69" s="22" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/software-developer-ai-insights-intern-at-five9-4402753102?refId=%2FiKmLsIvYp2TclUyf8MJwg%3D%3D&amp;trackingId=X2UMBr3jE86J9JmPv42B2w%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K69" s="17" t="inlineStr">
+      <c r="K69" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-five9-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L69" s="17" t="inlineStr">
+      <c r="L69" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-five9-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M69" s="17" t="inlineStr"/>
+      <c r="M69" s="20" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="17" t="inlineStr">
+      <c r="A70" s="20" t="inlineStr">
         <is>
           <t>linkedin_4403519373</t>
         </is>
       </c>
-      <c r="B70" s="17" t="inlineStr">
+      <c r="B70" s="20" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C70" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D70" s="17" t="inlineStr">
+      <c r="C70" s="20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D70" s="20" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E70" s="17" t="inlineStr">
+      <c r="E70" s="20" t="inlineStr">
         <is>
           <t>PhD Research Intern, Physical AI in Perception</t>
         </is>
       </c>
-      <c r="F70" s="17" t="inlineStr">
+      <c r="F70" s="20" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G70" s="17" t="inlineStr">
+      <c r="G70" s="20" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H70" s="17" t="inlineStr">
+      <c r="H70" s="20" t="inlineStr">
         <is>
           <t>2026-04-17 20:07 UTC</t>
         </is>
       </c>
-      <c r="I70" s="18" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J70" s="19" t="inlineStr">
+      <c r="I70" s="21" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J70" s="22" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-physical-ai-in-perception-at-zoox-4403519373?refId=LChV34e%2Bd7cvBpZ%2FbJAZjw%3D%3D&amp;trackingId=vlvuJ54NQfvZvNY3pNGqNw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K70" s="17" t="inlineStr">
+      <c r="K70" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L70" s="17" t="inlineStr">
+      <c r="L70" s="20" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M70" s="17" t="inlineStr"/>
+      <c r="M70" s="20" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="20" t="inlineStr">
@@ -5199,6 +5208,321 @@
         </is>
       </c>
       <c r="M74" s="20" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="23" t="inlineStr">
+        <is>
+          <t>linkedin_4391150969</t>
+        </is>
+      </c>
+      <c r="B75" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-19 19:54</t>
+        </is>
+      </c>
+      <c r="C75" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D75" s="23" t="inlineStr">
+        <is>
+          <t>Cartesian</t>
+        </is>
+      </c>
+      <c r="E75" s="23" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern (Summer/Fall 2026)</t>
+        </is>
+      </c>
+      <c r="F75" s="23" t="inlineStr">
+        <is>
+          <t>Cambridge, MA</t>
+        </is>
+      </c>
+      <c r="G75" s="23" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H75" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-18 23:08 UTC</t>
+        </is>
+      </c>
+      <c r="I75" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J75" s="25" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/software-engineering-intern-summer-fall-2026-at-cartesian-4391150969?refId=rXBEPoDKoHwUW%2BMU3mmCWA%3D%3D&amp;trackingId=03L6jyuSNG6Edf0%2FeXbj4w%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K75" s="23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-cartesian-2026-04-19.pdf</t>
+        </is>
+      </c>
+      <c r="L75" s="23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-cartesian-2026-04-19.pdf</t>
+        </is>
+      </c>
+      <c r="M75" s="23" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="23" t="inlineStr">
+        <is>
+          <t>linkedin_4401268516</t>
+        </is>
+      </c>
+      <c r="B76" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-19 19:54</t>
+        </is>
+      </c>
+      <c r="C76" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D76" s="23" t="inlineStr">
+        <is>
+          <t>Joveo Ai</t>
+        </is>
+      </c>
+      <c r="E76" s="23" t="inlineStr">
+        <is>
+          <t>Generative AI Intern</t>
+        </is>
+      </c>
+      <c r="F76" s="23" t="inlineStr">
+        <is>
+          <t>Bangalore Urban, Karnataka, India</t>
+        </is>
+      </c>
+      <c r="G76" s="23" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H76" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-19 16:33 UTC</t>
+        </is>
+      </c>
+      <c r="I76" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J76" s="25" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/generative-ai-intern-at-joveo-ai-4401268516?refId=AMRRU4%2FYzAhlhe1ad%2FYa%2Fw%3D%3D&amp;trackingId=lRpwTcswbLSpxr57DNyAvA%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K76" s="23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-joveo-ai-2026-04-19.pdf</t>
+        </is>
+      </c>
+      <c r="L76" s="23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-joveo-ai-2026-04-19.pdf</t>
+        </is>
+      </c>
+      <c r="M76" s="23" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="23" t="inlineStr">
+        <is>
+          <t>linkedin_4381330362</t>
+        </is>
+      </c>
+      <c r="B77" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-19 19:54</t>
+        </is>
+      </c>
+      <c r="C77" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D77" s="23" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="E77" s="23" t="inlineStr">
+        <is>
+          <t>Data Analyst Intern - Product Analysis, Regional Operations (Summer 2026)</t>
+        </is>
+      </c>
+      <c r="F77" s="23" t="inlineStr">
+        <is>
+          <t>Singapore, Singapore</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H77" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-19 13:47 UTC</t>
+        </is>
+      </c>
+      <c r="I77" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J77" s="25" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/data-analyst-intern-product-analysis-regional-operations-summer-2026-at-shopee-4381330362?refId=Mf9npsmRtScOZbkuOI7S2Q%3D%3D&amp;trackingId=qCnW3Di6Gcyx48NhCTpBLw%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K77" s="23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-shopee-2026-04-19.pdf</t>
+        </is>
+      </c>
+      <c r="L77" s="23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-shopee-2026-04-19.pdf</t>
+        </is>
+      </c>
+      <c r="M77" s="23" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="23" t="inlineStr">
+        <is>
+          <t>linkedin_4355297667</t>
+        </is>
+      </c>
+      <c r="B78" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-19 19:54</t>
+        </is>
+      </c>
+      <c r="C78" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D78" s="23" t="inlineStr">
+        <is>
+          <t>Temasek</t>
+        </is>
+      </c>
+      <c r="E78" s="23" t="inlineStr">
+        <is>
+          <t>Policy &amp; Research Intern, Workforce 4.0 (Jun/Jul - Dec 2026)</t>
+        </is>
+      </c>
+      <c r="F78" s="23" t="inlineStr">
+        <is>
+          <t>Singapore, Singapore</t>
+        </is>
+      </c>
+      <c r="G78" s="23" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H78" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-19 10:08 UTC</t>
+        </is>
+      </c>
+      <c r="I78" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J78" s="25" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/policy-research-intern-workforce-4-0-jun-jul-dec-2026-at-temasek-4355297667?refId=SZF%2BVbNMCE0h7Rloqm3lXQ%3D%3D&amp;trackingId=vK2euiis8CytJt264fhurw%3D%3D&amp;position=3&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K78" s="23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-temasek-2026-04-19.pdf</t>
+        </is>
+      </c>
+      <c r="L78" s="23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-temasek-2026-04-19.pdf</t>
+        </is>
+      </c>
+      <c r="M78" s="23" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="23" t="inlineStr">
+        <is>
+          <t>linkedin_4336865392</t>
+        </is>
+      </c>
+      <c r="B79" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-19 19:54</t>
+        </is>
+      </c>
+      <c r="C79" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D79" s="23" t="inlineStr">
+        <is>
+          <t>Zoox</t>
+        </is>
+      </c>
+      <c r="E79" s="23" t="inlineStr">
+        <is>
+          <t>PhD Research Intern, Visual Object Understanding</t>
+        </is>
+      </c>
+      <c r="F79" s="23" t="inlineStr">
+        <is>
+          <t>Foster City, CA</t>
+        </is>
+      </c>
+      <c r="G79" s="23" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H79" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-19 10:27 UTC</t>
+        </is>
+      </c>
+      <c r="I79" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J79" s="25" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/phd-research-intern-visual-object-understanding-at-zoox-4336865392?refId=gztZfDsooz7GE2iA6mPxjQ%3D%3D&amp;trackingId=%2F1kV0X%2F8hKCPhv0kD05v5Q%3D%3D&amp;position=3&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K79" s="23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-19.pdf</t>
+        </is>
+      </c>
+      <c r="L79" s="23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-19.pdf</t>
+        </is>
+      </c>
+      <c r="M79" s="23" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5275,6 +5599,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J72" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J73" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -83,10 +83,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -525,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -611,4603 +620,4603 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>linkedin_4401809501</t>
         </is>
       </c>
-      <c r="B2" s="20" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C2" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D2" s="20" t="inlineStr">
+      <c r="C2" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D2" s="23" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E2" s="20" t="inlineStr">
+      <c r="E2" s="23" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F2" s="20" t="inlineStr">
+      <c r="F2" s="23" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G2" s="20" t="inlineStr">
+      <c r="G2" s="23" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H2" s="20" t="inlineStr">
+      <c r="H2" s="23" t="inlineStr">
         <is>
           <t>2026-04-15 22:19 UTC</t>
         </is>
       </c>
-      <c r="I2" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J2" s="22" t="inlineStr">
+      <c r="I2" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J2" s="25" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/research-intern-at-skycliff-it-4401809501?refId=HHi6SaK1fggu3E9dI3MtVg%3D%3D&amp;trackingId=r33pSo29lHStfk9FH82pyw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K2" s="20" t="inlineStr">
+      <c r="K2" s="23" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L2" s="20" t="inlineStr">
+      <c r="L2" s="23" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M2" s="20" t="inlineStr"/>
+      <c r="M2" s="23" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>linkedin_4402568578</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C3" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D3" s="20" t="inlineStr">
+      <c r="C3" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t>Webs X UM</t>
         </is>
       </c>
-      <c r="E3" s="20" t="inlineStr">
+      <c r="E3" s="23" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F3" s="20" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G3" s="20" t="inlineStr">
+      <c r="G3" s="23" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H3" s="20" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t>2026-04-15 19:20 UTC</t>
         </is>
       </c>
-      <c r="I3" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J3" s="22" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J3" s="25" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-webs-x-um-4402568578?refId=g89JM6cY8EFeoLk6JL5tVg%3D%3D&amp;trackingId=uFZVJJX7SSI0XCPFIrLqmA%3D%3D&amp;position=19&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K3" s="20" t="inlineStr">
+      <c r="K3" s="23" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-webs-x-um-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L3" s="20" t="inlineStr">
+      <c r="L3" s="23" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-webs-x-um-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M3" s="20" t="inlineStr"/>
+      <c r="M3" s="23" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>linkedin_4399996740</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>SUN PHARMA</t>
         </is>
       </c>
-      <c r="E4" s="20" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>Becario</t>
         </is>
       </c>
-      <c r="F4" s="20" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t>Mexico City, Mexico</t>
         </is>
       </c>
-      <c r="G4" s="20" t="inlineStr">
+      <c r="G4" s="23" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H4" s="20" t="inlineStr">
+      <c r="H4" s="23" t="inlineStr">
         <is>
           <t>2026-04-15 17:59 UTC</t>
         </is>
       </c>
-      <c r="I4" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J4" s="22" t="inlineStr">
+      <c r="I4" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="inlineStr">
         <is>
           <t>https://mx.linkedin.com/jobs/view/becario-at-sun-pharma-4399996740?refId=g89JM6cY8EFeoLk6JL5tVg%3D%3D&amp;trackingId=sZ0Fkcf4RHuIpzXu4mJRNg%3D%3D&amp;position=22&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K4" s="20" t="inlineStr">
+      <c r="K4" s="23" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-sun-pharma-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L4" s="20" t="inlineStr">
+      <c r="L4" s="23" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-sun-pharma-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M4" s="20" t="inlineStr"/>
+      <c r="M4" s="23" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>linkedin_4399975959</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>LS Direct</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>Data Analytics Intern</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>Suffern, NY</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H5" s="20" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t>2026-04-15 14:26 UTC</t>
         </is>
       </c>
-      <c r="I5" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J5" s="22" t="inlineStr">
+      <c r="I5" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-analytics-intern-at-ls-direct-4399975959?refId=pg0ll3e89fatVyUznLcdpw%3D%3D&amp;trackingId=5b41IoyQfIfx3Tu42domiQ%3D%3D&amp;position=23&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K5" s="20" t="inlineStr">
+      <c r="K5" s="23" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-ls-direct-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="L5" s="23" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-ls-direct-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M5" s="20" t="inlineStr"/>
+      <c r="M5" s="23" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>linkedin_4370546718</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>Clarivate</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>Lead Data Scientist</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>Barcelona, Catalonia, Spain</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t>2026-04-15 12:16 UTC</t>
         </is>
       </c>
-      <c r="I6" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J6" s="25" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/lead-data-scientist-at-clarivate-4370546718?refId=FyyqQfduMQ8KZ7B5LeF0UQ%3D%3D&amp;trackingId=1i1kXdbV7SMunyFTiSJHJg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K6" s="20" t="inlineStr">
+      <c r="K6" s="23" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-clarivate-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L6" s="20" t="inlineStr">
+      <c r="L6" s="23" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-clarivate-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M6" s="20" t="inlineStr"/>
+      <c r="M6" s="23" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>linkedin_4389810164</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>Vitality</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>Senior Data Scientist - 12 Month FTC</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>2026-04-15 09:39 UTC</t>
         </is>
       </c>
-      <c r="I7" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J7" s="22" t="inlineStr">
+      <c r="I7" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J7" s="25" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/senior-data-scientist-12-month-ftc-at-vitality-4389810164?refId=FPz%2BrPoaQeqgXBm%2FfOzGGA%3D%3D&amp;trackingId=yVNh55t2X2xocDT4i6HDqQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K7" s="20" t="inlineStr">
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-vitality-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L7" s="20" t="inlineStr">
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-vitality-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M7" s="20" t="inlineStr"/>
+      <c r="M7" s="23" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>linkedin_4399952059</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>traide AI</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>AI Associate (f/m/x) (B2B SaaS Startup) - Intern/Working Student</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="G8" s="23" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t>2026-04-15 07:04 UTC</t>
         </is>
       </c>
-      <c r="I8" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J8" s="22" t="inlineStr">
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/ai-associate-f-m-x-b2b-saas-startup-intern-working-student-at-traide-ai-4399952059?refId=x0uIkl175n0hipT17L%2FGRw%3D%3D&amp;trackingId=8kdzUQgW%2B7rCk2pO2oIErg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K8" s="20" t="inlineStr">
+      <c r="K8" s="23" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-traide-ai-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L8" s="20" t="inlineStr">
+      <c r="L8" s="23" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-traide-ai-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M8" s="20" t="inlineStr"/>
+      <c r="M8" s="23" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>linkedin_4399933254</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>Briink</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>Growth Intern (Merantix AI Campus)</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t>2026-04-15 05:03 UTC</t>
         </is>
       </c>
-      <c r="I9" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J9" s="22" t="inlineStr">
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/growth-intern-merantix-ai-campus-at-briink-4399933254?refId=x0uIkl175n0hipT17L%2FGRw%3D%3D&amp;trackingId=qEKtyJNA03Kbr6AYDlhsBw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K9" s="20" t="inlineStr">
+      <c r="K9" s="23" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-briink-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L9" s="20" t="inlineStr">
+      <c r="L9" s="23" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-briink-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M9" s="20" t="inlineStr"/>
+      <c r="M9" s="23" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>linkedin_4400429367</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>Tata Consultancy Services</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>HR -Data Scientist</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>Renton, WA</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 16:56 UTC</t>
         </is>
       </c>
-      <c r="I10" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J10" s="22" t="inlineStr">
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/hr-data-scientist-at-tata-consultancy-services-4400429367?refId=vJILgNySaXYUQknbyaKZZQ%3D%3D&amp;trackingId=7cZ0KYh8Sv5%2Fh6%2FG86%2BLug%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K10" s="20" t="inlineStr">
+      <c r="K10" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-tata-consultancy-services-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L10" s="20" t="inlineStr">
+      <c r="L10" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-tata-consultancy-services-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M10" s="20" t="inlineStr"/>
+      <c r="M10" s="23" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>linkedin_4390814627</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>Criteo</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>Barcelona, Catalonia, Spain</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 12:19 UTC</t>
         </is>
       </c>
-      <c r="I11" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J11" s="22" t="inlineStr">
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/data-analyst-intern-at-criteo-4390814627?refId=PCZWvfzZIzNkx6giU9jTsA%3D%3D&amp;trackingId=T%2FMog6vtgG8P3ihAU9b1uQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K11" s="20" t="inlineStr">
+      <c r="K11" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-criteo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L11" s="20" t="inlineStr">
+      <c r="L11" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-criteo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M11" s="20" t="inlineStr"/>
+      <c r="M11" s="23" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>linkedin_4402983364</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>Brussels, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr">
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J12" s="22" t="inlineStr">
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402983364?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=zV4sJQyNyQg%2FS%2BYm6Ba9Eg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K12" s="20" t="inlineStr">
+      <c r="K12" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L12" s="20" t="inlineStr">
+      <c r="L12" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M12" s="20" t="inlineStr"/>
+      <c r="M12" s="23" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>linkedin_4390725142</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>Boston Consulting Group (BCG)</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>Forward Deployed AI Engineer, Internship, United Kingdom - BCG X</t>
         </is>
       </c>
-      <c r="F13" s="20" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G13" s="20" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr">
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 16:24 UTC</t>
         </is>
       </c>
-      <c r="I13" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J13" s="22" t="inlineStr">
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/forward-deployed-ai-engineer-internship-united-kingdom-bcg-x-at-boston-consulting-group-bcg-4390725142?refId=YHAZO5vAx9Qtg1RXMma%2F%2BA%3D%3D&amp;trackingId=E8kiSHzcdYe%2FH6s%2FCkGtMw%3D%3D&amp;position=7&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K13" s="20" t="inlineStr">
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L13" s="20" t="inlineStr">
+      <c r="L13" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M13" s="20" t="inlineStr"/>
+      <c r="M13" s="23" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>linkedin_4400428064</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>Fanatics</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G14" s="20" t="inlineStr">
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr">
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 16:16 UTC</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J14" s="22" t="inlineStr">
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/data-scientist-at-fanatics-4400428064?refId=SNMwEp9%2FBozAkX4FBnhJwQ%3D%3D&amp;trackingId=cAX0aKWV%2FBX1fvQzm%2FkEMg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K14" s="20" t="inlineStr">
+      <c r="K14" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-fanatics-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L14" s="20" t="inlineStr">
+      <c r="L14" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-fanatics-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M14" s="20" t="inlineStr"/>
+      <c r="M14" s="23" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>linkedin_4390730090</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>Boston Consulting Group (BCG)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>Forward Deployed AI Scientist, Internship, United Kingdom - BCG X</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G15" s="20" t="inlineStr">
+      <c r="G15" s="23" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H15" s="20" t="inlineStr">
+      <c r="H15" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 13:57 UTC</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J15" s="22" t="inlineStr">
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/forward-deployed-ai-scientist-internship-united-kingdom-bcg-x-at-boston-consulting-group-bcg-4390730090?refId=YHAZO5vAx9Qtg1RXMma%2F%2BA%3D%3D&amp;trackingId=m50MzwjbYzUmAv7nJVAKgA%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K15" s="20" t="inlineStr">
+      <c r="K15" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L15" s="20" t="inlineStr">
+      <c r="L15" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M15" s="20" t="inlineStr"/>
+      <c r="M15" s="23" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>linkedin_4402138096</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>Kelly Tutors</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>Research Intern (3-5hrs/week, flexible)</t>
         </is>
       </c>
-      <c r="F16" s="20" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G16" s="20" t="inlineStr">
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr">
+      <c r="H16" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 14:40 UTC</t>
         </is>
       </c>
-      <c r="I16" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J16" s="22" t="inlineStr">
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/research-intern-3-5hrs-week-flexible-at-kelly-tutors-4402138096?refId=HmOS2YEHUH3GOVent1txqw%3D%3D&amp;trackingId=3XBXMUoBdiHeRL4qw%2B2qRw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K16" s="20" t="inlineStr">
+      <c r="K16" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-kelly-tutors-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L16" s="20" t="inlineStr">
+      <c r="L16" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-kelly-tutors-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M16" s="20" t="inlineStr"/>
+      <c r="M16" s="23" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t>linkedin_4378557045</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>Fund for Public Health in NYC</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G17" s="20" t="inlineStr">
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H17" s="20" t="inlineStr">
+      <c r="H17" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 16:13 UTC</t>
         </is>
       </c>
-      <c r="I17" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J17" s="22" t="inlineStr">
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-scientist-at-fund-for-public-health-in-nyc-4378557045?refId=JsndNRa0tnfF7dsuxv62wA%3D%3D&amp;trackingId=Pmgt6JCxYmQun5Uv6%2BLbiQ%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K17" s="20" t="inlineStr">
+      <c r="K17" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-fund-for-public-health-in-nyc-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L17" s="20" t="inlineStr">
+      <c r="L17" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-fund-for-public-health-in-nyc-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M17" s="20" t="inlineStr"/>
+      <c r="M17" s="23" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t>linkedin_4402977457</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F18" s="20" t="inlineStr">
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>Brussels, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G18" s="20" t="inlineStr">
+      <c r="G18" s="23" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H18" s="20" t="inlineStr">
+      <c r="H18" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I18" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J18" s="22" t="inlineStr">
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402977457?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=gL9sbQh%2FaLMmzvXjuO71WQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K18" s="20" t="inlineStr">
+      <c r="K18" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L18" s="20" t="inlineStr">
+      <c r="L18" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M18" s="20" t="inlineStr"/>
+      <c r="M18" s="23" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="23" t="inlineStr">
         <is>
           <t>linkedin_4371210537</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>Gildan</t>
         </is>
       </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>Intern, ERP GenAI</t>
         </is>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G19" s="20" t="inlineStr">
+      <c r="G19" s="23" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H19" s="20" t="inlineStr">
+      <c r="H19" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 15:23 UTC</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J19" s="22" t="inlineStr">
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/intern-erp-genai-at-gildan-4371210537?refId=jteS%2Ft3Cmc2XLVMFToCpKw%3D%3D&amp;trackingId=OQGg%2Bob2m9u4kkbRcgWoUw%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K19" s="20" t="inlineStr">
+      <c r="K19" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-gildan-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L19" s="20" t="inlineStr">
+      <c r="L19" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-gildan-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M19" s="20" t="inlineStr"/>
+      <c r="M19" s="23" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>linkedin_4402974624</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E20" s="20" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>Uccle, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G20" s="20" t="inlineStr">
+      <c r="G20" s="23" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H20" s="20" t="inlineStr">
+      <c r="H20" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J20" s="22" t="inlineStr">
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402974624?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=RJfkVsuYxv4DqyEhPJ367g%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K20" s="20" t="inlineStr">
+      <c r="K20" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L20" s="20" t="inlineStr">
+      <c r="L20" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M20" s="20" t="inlineStr"/>
+      <c r="M20" s="23" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>linkedin_4402174633</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>Cloudera</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>AI Enablement Intern (Ireland Based)</t>
         </is>
       </c>
-      <c r="F21" s="20" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>Greater Dublin</t>
         </is>
       </c>
-      <c r="G21" s="20" t="inlineStr">
+      <c r="G21" s="23" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H21" s="20" t="inlineStr">
+      <c r="H21" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 18:24 UTC</t>
         </is>
       </c>
-      <c r="I21" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J21" s="22" t="inlineStr">
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="inlineStr">
         <is>
           <t>https://ie.linkedin.com/jobs/view/ai-enablement-intern-ireland-based-at-cloudera-4402174633?refId=d9iDz5spYJk0nIor701k5g%3D%3D&amp;trackingId=6OZvFiMQ12VqIzY6EqUe7A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K21" s="20" t="inlineStr">
+      <c r="K21" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-cloudera-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L21" s="20" t="inlineStr">
+      <c r="L21" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-cloudera-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M21" s="20" t="inlineStr"/>
+      <c r="M21" s="23" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>linkedin_4403115250</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>PhD Research Intern, Mapping Software</t>
         </is>
       </c>
-      <c r="F22" s="20" t="inlineStr">
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G22" s="20" t="inlineStr">
+      <c r="G22" s="23" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H22" s="20" t="inlineStr">
+      <c r="H22" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 19:55 UTC</t>
         </is>
       </c>
-      <c r="I22" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J22" s="22" t="inlineStr">
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-mapping-software-at-zoox-4403115250?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=67WsHxTIXiO%2ByWr0OYU7ug%3D%3D&amp;position=10&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K22" s="20" t="inlineStr">
+      <c r="K22" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L22" s="20" t="inlineStr">
+      <c r="L22" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M22" s="20" t="inlineStr"/>
+      <c r="M22" s="23" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="23" t="inlineStr">
         <is>
           <t>linkedin_4379373115</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>Woven by Toyota</t>
         </is>
       </c>
-      <c r="E23" s="20" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>Applied Scientist, Computer Vision and Generative Models, Vision AI (Internship)</t>
         </is>
       </c>
-      <c r="F23" s="20" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>Tokyo, Japan</t>
         </is>
       </c>
-      <c r="G23" s="20" t="inlineStr">
+      <c r="G23" s="23" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H23" s="20" t="inlineStr">
+      <c r="H23" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 14:55 UTC</t>
         </is>
       </c>
-      <c r="I23" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J23" s="22" t="inlineStr">
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="inlineStr">
         <is>
           <t>https://jp.linkedin.com/jobs/view/applied-scientist-computer-vision-and-generative-models-vision-ai-internship-at-woven-by-toyota-4379373115?refId=4q6ISAXJ%2BcfZsJD688QZWg%3D%3D&amp;trackingId=pUnO9OuzZx4G6BOukom%2FQQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K23" s="20" t="inlineStr">
+      <c r="K23" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-woven-by-toyota-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L23" s="20" t="inlineStr">
+      <c r="L23" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-woven-by-toyota-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M23" s="20" t="inlineStr"/>
+      <c r="M23" s="23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>linkedin_4325103488</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>Binance</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>Binance Accelerator Program - DevOps (Artificial Intelligence)</t>
         </is>
       </c>
-      <c r="F24" s="20" t="inlineStr">
+      <c r="F24" s="23" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G24" s="20" t="inlineStr">
+      <c r="G24" s="23" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H24" s="20" t="inlineStr">
+      <c r="H24" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 12:13 UTC</t>
         </is>
       </c>
-      <c r="I24" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J24" s="22" t="inlineStr">
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/binance-accelerator-program-devops-artificial-intelligence-at-binance-4325103488?refId=KzaD5RMOfYQEZyaw6UmcpQ%3D%3D&amp;trackingId=8R4okHiG3RYyjThXHAqxIQ%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K24" s="20" t="inlineStr">
+      <c r="K24" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-binance-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L24" s="20" t="inlineStr">
+      <c r="L24" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-binance-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M24" s="20" t="inlineStr"/>
+      <c r="M24" s="23" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>linkedin_4400563251</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>Aylo</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>Sr. Full-Stack Data Scientist - Data Services</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>Greater Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G25" s="20" t="inlineStr">
+      <c r="G25" s="23" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H25" s="20" t="inlineStr">
+      <c r="H25" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 12:01 UTC</t>
         </is>
       </c>
-      <c r="I25" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J25" s="22" t="inlineStr">
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/sr-full-stack-data-scientist-data-services-at-aylo-4400563251?refId=3X2hsLwn0XF5%2BC4ABneEzA%3D%3D&amp;trackingId=aJHp5psMKfAaMJdxBAz5Hw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K25" s="20" t="inlineStr">
+      <c r="K25" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-aylo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L25" s="20" t="inlineStr">
+      <c r="L25" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-aylo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M25" s="20" t="inlineStr"/>
+      <c r="M25" s="23" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>linkedin_4400403670</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>Schneider Electric</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>Internship in Global AI Sales Enablement &amp; Analytics</t>
         </is>
       </c>
-      <c r="F26" s="20" t="inlineStr">
+      <c r="F26" s="23" t="inlineStr">
         <is>
           <t>Warsaw, Mazowieckie, Poland</t>
         </is>
       </c>
-      <c r="G26" s="20" t="inlineStr">
+      <c r="G26" s="23" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H26" s="20" t="inlineStr">
+      <c r="H26" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 11:43 UTC</t>
         </is>
       </c>
-      <c r="I26" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J26" s="22" t="inlineStr">
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="inlineStr">
         <is>
           <t>https://pl.linkedin.com/jobs/view/internship-in-global-ai-sales-enablement-analytics-at-schneider-electric-4400403670?refId=0j6PfgagLJw81v3dQ49jXQ%3D%3D&amp;trackingId=ErR9yiUH1tcny4hRKbXl8A%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K26" s="20" t="inlineStr">
+      <c r="K26" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-schneider-electric-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L26" s="20" t="inlineStr">
+      <c r="L26" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-schneider-electric-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M26" s="20" t="inlineStr"/>
+      <c r="M26" s="23" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>linkedin_4297755027</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D27" s="20" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>Databricks</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>PhD GenAI Research Scientist Intern</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="F27" s="23" t="inlineStr">
         <is>
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="G27" s="20" t="inlineStr">
+      <c r="G27" s="23" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H27" s="20" t="inlineStr">
+      <c r="H27" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 10:31 UTC</t>
         </is>
       </c>
-      <c r="I27" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J27" s="22" t="inlineStr">
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-genai-research-scientist-intern-at-databricks-4297755027?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=UXoh9K97xsqO%2FzDhCy7Uug%3D%3D&amp;position=8&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K27" s="20" t="inlineStr">
+      <c r="K27" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-databricks-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L27" s="20" t="inlineStr">
+      <c r="L27" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-databricks-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M27" s="20" t="inlineStr"/>
+      <c r="M27" s="23" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>linkedin_4401843829</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>Tiger Brokers Singapore</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>Quantitative Investment Analyst Intern</t>
         </is>
       </c>
-      <c r="F28" s="20" t="inlineStr">
+      <c r="F28" s="23" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G28" s="20" t="inlineStr">
+      <c r="G28" s="23" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H28" s="20" t="inlineStr">
+      <c r="H28" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 06:09 UTC</t>
         </is>
       </c>
-      <c r="I28" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J28" s="22" t="inlineStr">
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J28" s="25" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/quantitative-investment-analyst-intern-at-tiger-brokers-singapore-4401843829?refId=LJ4PwcXqLhd1gtOBe9ZVig%3D%3D&amp;trackingId=oxh8Ol2m1QKvqfrvl10UqA%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K28" s="20" t="inlineStr">
+      <c r="K28" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-tiger-brokers-singapore-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L28" s="20" t="inlineStr">
+      <c r="L28" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-tiger-brokers-singapore-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M28" s="20" t="inlineStr"/>
+      <c r="M28" s="23" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>linkedin_4400148847</t>
         </is>
       </c>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C29" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D29" s="20" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>Boomlet</t>
         </is>
       </c>
-      <c r="E29" s="20" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F29" s="20" t="inlineStr">
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>Mumbai, Maharashtra, India</t>
         </is>
       </c>
-      <c r="G29" s="20" t="inlineStr">
+      <c r="G29" s="23" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H29" s="20" t="inlineStr">
+      <c r="H29" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 05:24 UTC</t>
         </is>
       </c>
-      <c r="I29" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J29" s="22" t="inlineStr">
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J29" s="25" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-boomlet-4400148847?refId=vAgiKqchg4pd6EgGGQ%2FF%2FA%3D%3D&amp;trackingId=IoHiSd1L28nXXarEd4gYfw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K29" s="20" t="inlineStr">
+      <c r="K29" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boomlet-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L29" s="20" t="inlineStr">
+      <c r="L29" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boomlet-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M29" s="20" t="inlineStr"/>
+      <c r="M29" s="23" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="23" t="inlineStr">
         <is>
           <t>linkedin_4401844394</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D30" s="20" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>On-us</t>
         </is>
       </c>
-      <c r="E30" s="20" t="inlineStr">
+      <c r="E30" s="23" t="inlineStr">
         <is>
           <t>AI Business Analyst Summer Intern</t>
         </is>
       </c>
-      <c r="F30" s="20" t="inlineStr">
+      <c r="F30" s="23" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G30" s="20" t="inlineStr">
+      <c r="G30" s="23" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H30" s="20" t="inlineStr">
+      <c r="H30" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 04:56 UTC</t>
         </is>
       </c>
-      <c r="I30" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J30" s="22" t="inlineStr">
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J30" s="25" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/ai-business-analyst-summer-intern-at-on-us-4401844394?refId=lslydLUu5l8kXOktysXYaw%3D%3D&amp;trackingId=BQ%2BoYgH5QtZKBWGZQgBfNQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K30" s="20" t="inlineStr">
+      <c r="K30" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-on-us-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L30" s="20" t="inlineStr">
+      <c r="L30" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-on-us-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M30" s="20" t="inlineStr"/>
+      <c r="M30" s="23" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="inlineStr">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t>linkedin_4401837715</t>
         </is>
       </c>
-      <c r="B31" s="20" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D31" s="20" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
         <is>
           <t>Pathos Consultancy</t>
         </is>
       </c>
-      <c r="E31" s="20" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>Quantitative Research &amp; Development Internships</t>
         </is>
       </c>
-      <c r="F31" s="20" t="inlineStr">
+      <c r="F31" s="23" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G31" s="20" t="inlineStr">
+      <c r="G31" s="23" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H31" s="20" t="inlineStr">
+      <c r="H31" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 03:48 UTC</t>
         </is>
       </c>
-      <c r="I31" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J31" s="22" t="inlineStr">
+      <c r="I31" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J31" s="25" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/quantitative-research-development-internships-at-pathos-consultancy-4401837715?refId=KzaD5RMOfYQEZyaw6UmcpQ%3D%3D&amp;trackingId=eIGVr2dDtK%2F1o37C90xRoQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K31" s="20" t="inlineStr">
+      <c r="K31" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-pathos-consultancy-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L31" s="20" t="inlineStr">
+      <c r="L31" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-pathos-consultancy-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M31" s="20" t="inlineStr"/>
+      <c r="M31" s="23" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A32" s="23" t="inlineStr">
         <is>
           <t>linkedin_4402662606</t>
         </is>
       </c>
-      <c r="B32" s="20" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C32" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D32" s="20" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>Stripe</t>
         </is>
       </c>
-      <c r="E32" s="20" t="inlineStr">
+      <c r="E32" s="23" t="inlineStr">
         <is>
           <t>PhD Machine Learning Engineer, Intern</t>
         </is>
       </c>
-      <c r="F32" s="20" t="inlineStr">
+      <c r="F32" s="23" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G32" s="20" t="inlineStr">
+      <c r="G32" s="23" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H32" s="20" t="inlineStr">
+      <c r="H32" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 02:23 UTC</t>
         </is>
       </c>
-      <c r="I32" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J32" s="22" t="inlineStr">
+      <c r="I32" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J32" s="25" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-machine-learning-engineer-intern-at-stripe-4402662606?refId=vJILgNySaXYUQknbyaKZZQ%3D%3D&amp;trackingId=NDMzaPfHMoCKo5uxI3THcw%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K32" s="20" t="inlineStr">
+      <c r="K32" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L32" s="20" t="inlineStr">
+      <c r="L32" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M32" s="20" t="inlineStr"/>
+      <c r="M32" s="23" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="23" t="inlineStr">
         <is>
           <t>linkedin_4402953925</t>
         </is>
       </c>
-      <c r="B33" s="20" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C33" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D33" s="20" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E33" s="20" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F33" s="20" t="inlineStr">
+      <c r="F33" s="23" t="inlineStr">
         <is>
           <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
-      <c r="G33" s="20" t="inlineStr">
+      <c r="G33" s="23" t="inlineStr">
         <is>
           <t>Middle_East</t>
         </is>
       </c>
-      <c r="H33" s="20" t="inlineStr">
+      <c r="H33" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 00:00 UTC</t>
         </is>
       </c>
-      <c r="I33" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J33" s="22" t="inlineStr">
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J33" s="25" t="inlineStr">
         <is>
           <t>https://ae.linkedin.com/jobs/view/research-intern-at-skycliff-it-4402953925?refId=f%2BmSR6Ncm83dISKgoQTrbw%3D%3D&amp;trackingId=CdPOXElDD3wJKKeBZSdWsw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K33" s="20" t="inlineStr">
+      <c r="K33" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L33" s="20" t="inlineStr">
+      <c r="L33" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M33" s="20" t="inlineStr"/>
+      <c r="M33" s="23" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="23" t="inlineStr">
         <is>
           <t>linkedin_4402617206</t>
         </is>
       </c>
-      <c r="B34" s="20" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C34" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D34" s="20" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>Stripe</t>
         </is>
       </c>
-      <c r="E34" s="20" t="inlineStr">
+      <c r="E34" s="23" t="inlineStr">
         <is>
           <t>PhD Machine Learning Engineer, Intern</t>
         </is>
       </c>
-      <c r="F34" s="20" t="inlineStr">
+      <c r="F34" s="23" t="inlineStr">
         <is>
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="G34" s="20" t="inlineStr">
+      <c r="G34" s="23" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H34" s="20" t="inlineStr">
+      <c r="H34" s="23" t="inlineStr">
         <is>
           <t>2026-04-15 20:25 UTC</t>
         </is>
       </c>
-      <c r="I34" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J34" s="22" t="inlineStr">
+      <c r="I34" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J34" s="25" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-machine-learning-engineer-intern-at-stripe-4402617206?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=yAc4U29LYJcrlQSUWWcubA%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K34" s="20" t="inlineStr">
+      <c r="K34" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L34" s="20" t="inlineStr">
+      <c r="L34" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M34" s="20" t="inlineStr"/>
+      <c r="M34" s="23" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+      <c r="A35" s="23" t="inlineStr">
         <is>
           <t>linkedin_4403183407</t>
         </is>
       </c>
-      <c r="B35" s="20" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C35" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D35" s="20" t="inlineStr">
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
         <is>
           <t>Hardware FYI</t>
         </is>
       </c>
-      <c r="E35" s="20" t="inlineStr">
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>Robotics - Applied Scientist II Intern / Co-op - 2026 (Robotics, Manipulation, Perception, Motion Planning, Autonomous Mobile Robots, Computer Vision, Machine Learning, Controls, and more)</t>
         </is>
       </c>
-      <c r="F35" s="20" t="inlineStr">
+      <c r="F35" s="23" t="inlineStr">
         <is>
           <t>Boston, MA</t>
         </is>
       </c>
-      <c r="G35" s="20" t="inlineStr">
+      <c r="G35" s="23" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H35" s="20" t="inlineStr">
+      <c r="H35" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 04:31 UTC</t>
         </is>
       </c>
-      <c r="I35" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J35" s="22" t="inlineStr">
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J35" s="25" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/robotics-applied-scientist-ii-intern-co-op-2026-robotics-manipulation-perception-motion-planning-autonomous-mobile-robots-computer-vision-machine-learning-controls-and-more-at-hardware-fyi-4403183407?refId=s5WxXRPJ8QU7G2WPi2yNiw%3D%3D&amp;trackingId=rjd%2F8qdM5kQMmADtGJgSSw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K35" s="20" t="inlineStr">
+      <c r="K35" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-hardware-fyi-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L35" s="20" t="inlineStr">
+      <c r="L35" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-hardware-fyi-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M35" s="20" t="inlineStr"/>
+      <c r="M35" s="23" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="20" t="inlineStr">
+      <c r="A36" s="23" t="inlineStr">
         <is>
           <t>linkedin_4403153262</t>
         </is>
       </c>
-      <c r="B36" s="20" t="inlineStr">
+      <c r="B36" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C36" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D36" s="20" t="inlineStr">
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
         <is>
           <t>Generali Malaysia</t>
         </is>
       </c>
-      <c r="E36" s="20" t="inlineStr">
+      <c r="E36" s="23" t="inlineStr">
         <is>
           <t>Intern, IT (AI Engineering)</t>
         </is>
       </c>
-      <c r="F36" s="20" t="inlineStr">
+      <c r="F36" s="23" t="inlineStr">
         <is>
           <t>Federal Territory of Kuala Lumpur, Malaysia</t>
         </is>
       </c>
-      <c r="G36" s="20" t="inlineStr">
+      <c r="G36" s="23" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H36" s="20" t="inlineStr">
+      <c r="H36" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 00:47 UTC</t>
         </is>
       </c>
-      <c r="I36" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J36" s="22" t="inlineStr">
+      <c r="I36" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J36" s="25" t="inlineStr">
         <is>
           <t>https://my.linkedin.com/jobs/view/intern-it-ai-engineering-at-generali-malaysia-4403153262?refId=h4J9hFjDRjjPW7bUqRcUZQ%3D%3D&amp;trackingId=WmqITEtGX486sbNH6b%2BYmA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K36" s="20" t="inlineStr">
+      <c r="K36" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-generali-malaysia-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L36" s="20" t="inlineStr">
+      <c r="L36" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-generali-malaysia-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M36" s="20" t="inlineStr"/>
+      <c r="M36" s="23" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="20" t="inlineStr">
+      <c r="A37" s="23" t="inlineStr">
         <is>
           <t>linkedin_4402311007</t>
         </is>
       </c>
-      <c r="B37" s="20" t="inlineStr">
+      <c r="B37" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C37" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D37" s="20" t="inlineStr">
+      <c r="C37" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E37" s="20" t="inlineStr">
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>SAP iXp Intern - Customer Success Engineering, Operations &amp; AI Enablement [Boston]</t>
         </is>
       </c>
-      <c r="F37" s="20" t="inlineStr">
+      <c r="F37" s="23" t="inlineStr">
         <is>
           <t>Burlington, MA</t>
         </is>
       </c>
-      <c r="G37" s="20" t="inlineStr">
+      <c r="G37" s="23" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H37" s="20" t="inlineStr">
+      <c r="H37" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 21:40 UTC</t>
         </is>
       </c>
-      <c r="I37" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J37" s="22" t="inlineStr">
+      <c r="I37" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J37" s="25" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/sap-ixp-intern-%C2%A0customer-success-engineering-operations-ai-enablement-boston-at-sap-4402311007?refId=ofb0jzd8xWUoUtvr7A%2BwXQ%3D%3D&amp;trackingId=S%2Fo4FvRdeOcn00Jo5DVUBw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K37" s="20" t="inlineStr">
+      <c r="K37" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L37" s="20" t="inlineStr">
+      <c r="L37" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M37" s="20" t="inlineStr"/>
+      <c r="M37" s="23" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+      <c r="A38" s="23" t="inlineStr">
         <is>
           <t>linkedin_4403154707</t>
         </is>
       </c>
-      <c r="B38" s="20" t="inlineStr">
+      <c r="B38" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C38" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D38" s="20" t="inlineStr">
+      <c r="C38" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E38" s="20" t="inlineStr">
+      <c r="E38" s="23" t="inlineStr">
         <is>
           <t>Software Engineer Intern, Perception Data</t>
         </is>
       </c>
-      <c r="F38" s="20" t="inlineStr">
+      <c r="F38" s="23" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G38" s="20" t="inlineStr">
+      <c r="G38" s="23" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H38" s="20" t="inlineStr">
+      <c r="H38" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 02:21 UTC</t>
         </is>
       </c>
-      <c r="I38" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J38" s="22" t="inlineStr">
+      <c r="I38" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J38" s="25" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/software-engineer-intern-perception-data-at-zoox-4403154707?refId=ON4L5FUhksKAgylRRsNllQ%3D%3D&amp;trackingId=1%2F3OkqP%2Bu0PqHp9bXnlS0A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K38" s="20" t="inlineStr">
+      <c r="K38" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L38" s="20" t="inlineStr">
+      <c r="L38" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M38" s="20" t="inlineStr"/>
+      <c r="M38" s="23" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="inlineStr">
+      <c r="A39" s="23" t="inlineStr">
         <is>
           <t>linkedin_4402947451</t>
         </is>
       </c>
-      <c r="B39" s="20" t="inlineStr">
+      <c r="B39" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C39" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D39" s="20" t="inlineStr">
+      <c r="C39" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D39" s="23" t="inlineStr">
         <is>
           <t>Rubrik</t>
         </is>
       </c>
-      <c r="E39" s="20" t="inlineStr">
+      <c r="E39" s="23" t="inlineStr">
         <is>
           <t>India Benefits &amp; AI Operations Intern</t>
         </is>
       </c>
-      <c r="F39" s="20" t="inlineStr">
+      <c r="F39" s="23" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G39" s="20" t="inlineStr">
+      <c r="G39" s="23" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H39" s="20" t="inlineStr">
+      <c r="H39" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 11:40 UTC</t>
         </is>
       </c>
-      <c r="I39" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J39" s="22" t="inlineStr">
+      <c r="I39" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J39" s="25" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/india-benefits-ai-operations-intern-at-rubrik-4402947451?refId=9u2uyUYzyMZimaTtDELDWg%3D%3D&amp;trackingId=BjOmyeYm6McmUpzLwcES9g%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K39" s="20" t="inlineStr">
+      <c r="K39" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-rubrik-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L39" s="20" t="inlineStr">
+      <c r="L39" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-rubrik-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M39" s="20" t="inlineStr"/>
+      <c r="M39" s="23" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="20" t="inlineStr">
+      <c r="A40" s="23" t="inlineStr">
         <is>
           <t>linkedin_4390354006</t>
         </is>
       </c>
-      <c r="B40" s="20" t="inlineStr">
+      <c r="B40" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C40" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D40" s="20" t="inlineStr">
+      <c r="C40" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="inlineStr">
         <is>
           <t>Lila Sciences</t>
         </is>
       </c>
-      <c r="E40" s="20" t="inlineStr">
+      <c r="E40" s="23" t="inlineStr">
         <is>
           <t>Intern, Next Gen AI Robotics</t>
         </is>
       </c>
-      <c r="F40" s="20" t="inlineStr">
+      <c r="F40" s="23" t="inlineStr">
         <is>
           <t>Cambridge, MA</t>
         </is>
       </c>
-      <c r="G40" s="20" t="inlineStr">
+      <c r="G40" s="23" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H40" s="20" t="inlineStr">
+      <c r="H40" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 10:58 UTC</t>
         </is>
       </c>
-      <c r="I40" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J40" s="22" t="inlineStr">
+      <c r="I40" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J40" s="25" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/intern-next-gen-ai-robotics-at-lila-sciences-4390354006?refId=ZoXJQXesL%2FE%2B5EAGGzWfiA%3D%3D&amp;trackingId=FmSMwWhyyIaC52NsDwOCtw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K40" s="20" t="inlineStr">
+      <c r="K40" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-lila-sciences-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L40" s="20" t="inlineStr">
+      <c r="L40" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-lila-sciences-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M40" s="20" t="inlineStr"/>
+      <c r="M40" s="23" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="20" t="inlineStr">
+      <c r="A41" s="23" t="inlineStr">
         <is>
           <t>arbeitnow_ai-venture-development-tech-intern-berlin-100382</t>
         </is>
       </c>
-      <c r="B41" s="20" t="inlineStr">
+      <c r="B41" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C41" s="20" t="inlineStr">
+      <c r="C41" s="23" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="D41" s="20" t="inlineStr">
+      <c r="D41" s="23" t="inlineStr">
         <is>
           <t>Zeeg</t>
         </is>
       </c>
-      <c r="E41" s="20" t="inlineStr">
+      <c r="E41" s="23" t="inlineStr">
         <is>
           <t>AI &amp; Venture Development Tech Intern (w/m/d)</t>
         </is>
       </c>
-      <c r="F41" s="20" t="inlineStr">
+      <c r="F41" s="23" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="G41" s="20" t="inlineStr">
+      <c r="G41" s="23" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H41" s="20" t="inlineStr">
+      <c r="H41" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 10:30 UTC</t>
         </is>
       </c>
-      <c r="I41" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J41" s="22" t="inlineStr">
+      <c r="I41" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J41" s="25" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/zeeg/ai-venture-development-tech-intern-berlin-100382</t>
         </is>
       </c>
-      <c r="K41" s="20" t="inlineStr">
+      <c r="K41" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zeeg-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L41" s="20" t="inlineStr">
+      <c r="L41" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zeeg-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M41" s="20" t="inlineStr"/>
+      <c r="M41" s="23" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="20" t="inlineStr">
+      <c r="A42" s="23" t="inlineStr">
         <is>
           <t>linkedin_4391388054</t>
         </is>
       </c>
-      <c r="B42" s="20" t="inlineStr">
+      <c r="B42" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C42" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D42" s="20" t="inlineStr">
+      <c r="C42" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="inlineStr">
         <is>
           <t>Mackenzie Investments</t>
         </is>
       </c>
-      <c r="E42" s="20" t="inlineStr">
+      <c r="E42" s="23" t="inlineStr">
         <is>
           <t>Fall Intern 2026 - Data Science (Toronto Office)</t>
         </is>
       </c>
-      <c r="F42" s="20" t="inlineStr">
+      <c r="F42" s="23" t="inlineStr">
         <is>
           <t>Greater Toronto Area, Canada</t>
         </is>
       </c>
-      <c r="G42" s="20" t="inlineStr">
+      <c r="G42" s="23" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H42" s="20" t="inlineStr">
+      <c r="H42" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 14:00 UTC</t>
         </is>
       </c>
-      <c r="I42" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J42" s="22" t="inlineStr">
+      <c r="I42" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J42" s="25" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/fall-intern-2026-data-science-toronto-office-at-mackenzie-investments-4391388054?refId=ay8O%2Bgf7Gtfb1Rpr3XZOhg%3D%3D&amp;trackingId=O%2F%2FJTpCmUhvp4jSfNkV5bg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K42" s="20" t="inlineStr">
+      <c r="K42" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-mackenzie-investments-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L42" s="20" t="inlineStr">
+      <c r="L42" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-mackenzie-investments-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M42" s="20" t="inlineStr"/>
+      <c r="M42" s="23" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="20" t="inlineStr">
+      <c r="A43" s="23" t="inlineStr">
         <is>
           <t>linkedin_4390747937</t>
         </is>
       </c>
-      <c r="B43" s="20" t="inlineStr">
+      <c r="B43" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C43" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D43" s="20" t="inlineStr">
+      <c r="C43" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="inlineStr">
         <is>
           <t>BCG X</t>
         </is>
       </c>
-      <c r="E43" s="20" t="inlineStr">
+      <c r="E43" s="23" t="inlineStr">
         <is>
           <t>Visiting Forward Deployed AI Engineer, Internship, Germany - BCG X</t>
         </is>
       </c>
-      <c r="F43" s="20" t="inlineStr">
+      <c r="F43" s="23" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G43" s="20" t="inlineStr">
+      <c r="G43" s="23" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H43" s="20" t="inlineStr">
+      <c r="H43" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 13:51 UTC</t>
         </is>
       </c>
-      <c r="I43" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J43" s="22" t="inlineStr">
+      <c r="I43" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J43" s="25" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/visiting-forward-deployed-ai-engineer-internship-germany-bcg-x-at-bcg-x-4390747937?refId=1JxxxPqdlRpkbbaCzu2YGQ%3D%3D&amp;trackingId=7x%2BVQU%2BWOh9IPaVXWJkc5g%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K43" s="20" t="inlineStr">
+      <c r="K43" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bcg-x-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L43" s="20" t="inlineStr">
+      <c r="L43" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bcg-x-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M43" s="20" t="inlineStr"/>
+      <c r="M43" s="23" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="20" t="inlineStr">
+      <c r="A44" s="23" t="inlineStr">
         <is>
           <t>linkedin_4402726053</t>
         </is>
       </c>
-      <c r="B44" s="20" t="inlineStr">
+      <c r="B44" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C44" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D44" s="20" t="inlineStr">
+      <c r="C44" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="inlineStr">
         <is>
           <t>targetjobs UK</t>
         </is>
       </c>
-      <c r="E44" s="20" t="inlineStr">
+      <c r="E44" s="23" t="inlineStr">
         <is>
           <t>Internship: AI/ML for Ionospheric TEC Modelling</t>
         </is>
       </c>
-      <c r="F44" s="20" t="inlineStr">
+      <c r="F44" s="23" t="inlineStr">
         <is>
           <t>Reigate, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G44" s="20" t="inlineStr">
+      <c r="G44" s="23" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H44" s="20" t="inlineStr">
+      <c r="H44" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 14:25 UTC</t>
         </is>
       </c>
-      <c r="I44" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J44" s="22" t="inlineStr">
+      <c r="I44" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J44" s="25" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/internship-ai-ml-for-ionospheric-tec-modelling-at-targetjobs-uk-4402726053?refId=a1g6hMZsvI1y2Eje2OvLAA%3D%3D&amp;trackingId=IVJSJGE7Non8cohorDs%2F5A%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K44" s="20" t="inlineStr">
+      <c r="K44" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-targetjobs-uk-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L44" s="20" t="inlineStr">
+      <c r="L44" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-targetjobs-uk-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M44" s="20" t="inlineStr"/>
+      <c r="M44" s="23" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="20" t="inlineStr">
+      <c r="A45" s="23" t="inlineStr">
         <is>
           <t>linkedin_4400837114</t>
         </is>
       </c>
-      <c r="B45" s="20" t="inlineStr">
+      <c r="B45" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C45" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D45" s="20" t="inlineStr">
+      <c r="C45" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D45" s="23" t="inlineStr">
         <is>
           <t>Innovexis</t>
         </is>
       </c>
-      <c r="E45" s="20" t="inlineStr">
+      <c r="E45" s="23" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F45" s="20" t="inlineStr">
+      <c r="F45" s="23" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G45" s="20" t="inlineStr">
+      <c r="G45" s="23" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H45" s="20" t="inlineStr">
+      <c r="H45" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 13:04 UTC</t>
         </is>
       </c>
-      <c r="I45" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J45" s="22" t="inlineStr">
+      <c r="I45" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J45" s="25" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-innovexis-4400837114?refId=CVM89%2F3%2F%2BshqMJLc4IfFMg%3D%3D&amp;trackingId=j9WpQwI4k1ip7aRr%2Fv5Img%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K45" s="20" t="inlineStr">
+      <c r="K45" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-innovexis-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L45" s="20" t="inlineStr">
+      <c r="L45" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-innovexis-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M45" s="20" t="inlineStr"/>
+      <c r="M45" s="23" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="20" t="inlineStr">
+      <c r="A46" s="23" t="inlineStr">
         <is>
           <t>linkedin_4391074158</t>
         </is>
       </c>
-      <c r="B46" s="20" t="inlineStr">
+      <c r="B46" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C46" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D46" s="20" t="inlineStr">
+      <c r="C46" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D46" s="23" t="inlineStr">
         <is>
           <t>BMW Group</t>
         </is>
       </c>
-      <c r="E46" s="20" t="inlineStr">
+      <c r="E46" s="23" t="inlineStr">
         <is>
           <t>Intern IT Technology, Sales Volume Planning &amp; AI Support (f/m/x)</t>
         </is>
       </c>
-      <c r="F46" s="20" t="inlineStr">
+      <c r="F46" s="23" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G46" s="20" t="inlineStr">
+      <c r="G46" s="23" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H46" s="20" t="inlineStr">
+      <c r="H46" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 12:45 UTC</t>
         </is>
       </c>
-      <c r="I46" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J46" s="22" t="inlineStr">
+      <c r="I46" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J46" s="25" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/intern-it-technology-sales-volume-planning-ai-support-f-m-x-at-bmw-group-4391074158?refId=tHG5EqbLn3IDBqsSj%2FsUUg%3D%3D&amp;trackingId=OakOlgDcU0hWTRXcoLe3UA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K46" s="20" t="inlineStr">
+      <c r="K46" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bmw-group-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L46" s="20" t="inlineStr">
+      <c r="L46" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bmw-group-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M46" s="20" t="inlineStr"/>
+      <c r="M46" s="23" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="20" t="inlineStr">
+      <c r="A47" s="23" t="inlineStr">
         <is>
           <t>linkedin_4402725075</t>
         </is>
       </c>
-      <c r="B47" s="20" t="inlineStr">
+      <c r="B47" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C47" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D47" s="20" t="inlineStr">
+      <c r="C47" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="inlineStr">
         <is>
           <t>DARE</t>
         </is>
       </c>
-      <c r="E47" s="20" t="inlineStr">
+      <c r="E47" s="23" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F47" s="20" t="inlineStr">
+      <c r="F47" s="23" t="inlineStr">
         <is>
           <t>WP. Kuala Lumpur, Federal Territory of Kuala Lumpur, Malaysia</t>
         </is>
       </c>
-      <c r="G47" s="20" t="inlineStr">
+      <c r="G47" s="23" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H47" s="20" t="inlineStr">
+      <c r="H47" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 14:36 UTC</t>
         </is>
       </c>
-      <c r="I47" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J47" s="22" t="inlineStr">
+      <c r="I47" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J47" s="25" t="inlineStr">
         <is>
           <t>https://my.linkedin.com/jobs/view/research-intern-at-dare-4402725075?refId=xbzZXyF6FfcYy036eklDWw%3D%3D&amp;trackingId=QRt5DhbLSINvmHia0jEWIg%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K47" s="20" t="inlineStr">
+      <c r="K47" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dare-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L47" s="20" t="inlineStr">
+      <c r="L47" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dare-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M47" s="20" t="inlineStr"/>
+      <c r="M47" s="23" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="20" t="inlineStr">
+      <c r="A48" s="23" t="inlineStr">
         <is>
           <t>linkedin_4402745391</t>
         </is>
       </c>
-      <c r="B48" s="20" t="inlineStr">
+      <c r="B48" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C48" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D48" s="20" t="inlineStr">
+      <c r="C48" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D48" s="23" t="inlineStr">
         <is>
           <t>Huawei Technologies Research &amp; Development (UK) Ltd</t>
         </is>
       </c>
-      <c r="E48" s="20" t="inlineStr">
+      <c r="E48" s="23" t="inlineStr">
         <is>
           <t>Research Intern - Computer Vision</t>
         </is>
       </c>
-      <c r="F48" s="20" t="inlineStr">
+      <c r="F48" s="23" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G48" s="20" t="inlineStr">
+      <c r="G48" s="23" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H48" s="20" t="inlineStr">
+      <c r="H48" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 18:42 UTC</t>
         </is>
       </c>
-      <c r="I48" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J48" s="22" t="inlineStr">
+      <c r="I48" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J48" s="25" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/research-intern-computer-vision-at-huawei-technologies-research-development-uk-ltd-4402745391?refId=rRtCMQFBU%2FNi7vc62x5Nhg%3D%3D&amp;trackingId=%2Bt1We%2BmKhWHyXION%2FWwQVg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K48" s="20" t="inlineStr">
+      <c r="K48" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-huawei-technologies-research-development-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L48" s="20" t="inlineStr">
+      <c r="L48" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-huawei-technologies-research-development-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M48" s="20" t="inlineStr"/>
+      <c r="M48" s="23" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="20" t="inlineStr">
+      <c r="A49" s="23" t="inlineStr">
         <is>
           <t>linkedin_4402366780</t>
         </is>
       </c>
-      <c r="B49" s="20" t="inlineStr">
+      <c r="B49" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C49" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D49" s="20" t="inlineStr">
+      <c r="C49" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D49" s="23" t="inlineStr">
         <is>
           <t>Binance</t>
         </is>
       </c>
-      <c r="E49" s="20" t="inlineStr">
+      <c r="E49" s="23" t="inlineStr">
         <is>
           <t>Binance Accelerator Program - Data Scientist (LLM &amp; Trading)</t>
         </is>
       </c>
-      <c r="F49" s="20" t="inlineStr">
+      <c r="F49" s="23" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G49" s="20" t="inlineStr">
+      <c r="G49" s="23" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H49" s="20" t="inlineStr">
+      <c r="H49" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 09:43 UTC</t>
         </is>
       </c>
-      <c r="I49" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J49" s="22" t="inlineStr">
+      <c r="I49" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J49" s="25" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/binance-accelerator-program-data-scientist-llm-trading-at-binance-4402366780?refId=bc%2BXeBTeIKMQJTmlLFwbZQ%3D%3D&amp;trackingId=9UuyRRCEPapWNu6VKdZC5A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K49" s="20" t="inlineStr">
+      <c r="K49" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-binance-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L49" s="20" t="inlineStr">
+      <c r="L49" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-binance-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M49" s="20" t="inlineStr"/>
+      <c r="M49" s="23" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="20" t="inlineStr">
+      <c r="A50" s="23" t="inlineStr">
         <is>
           <t>linkedin_4382411039</t>
         </is>
       </c>
-      <c r="B50" s="20" t="inlineStr">
+      <c r="B50" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C50" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D50" s="20" t="inlineStr">
+      <c r="C50" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D50" s="23" t="inlineStr">
         <is>
           <t>The Walt Disney Company</t>
         </is>
       </c>
-      <c r="E50" s="20" t="inlineStr">
+      <c r="E50" s="23" t="inlineStr">
         <is>
           <t>Intern, APAC Data Analytics &amp; Insights (Content Analytics) -  Jul to Dec 2026</t>
         </is>
       </c>
-      <c r="F50" s="20" t="inlineStr">
+      <c r="F50" s="23" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G50" s="20" t="inlineStr">
+      <c r="G50" s="23" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H50" s="20" t="inlineStr">
+      <c r="H50" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 23:55 UTC</t>
         </is>
       </c>
-      <c r="I50" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J50" s="22" t="inlineStr">
+      <c r="I50" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J50" s="25" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/intern-apac-data-analytics-insights-content-analytics-jul-to-dec-2026-at-the-walt-disney-company-4382411039?refId=JBvXH2fNOamnO4WZI1Y0ew%3D%3D&amp;trackingId=Rs%2FdjczlbLYSYtCwY%2F%2FJyA%3D%3D&amp;position=7&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K50" s="20" t="inlineStr">
+      <c r="K50" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-the-walt-disney-company-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L50" s="20" t="inlineStr">
+      <c r="L50" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-the-walt-disney-company-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M50" s="20" t="inlineStr"/>
+      <c r="M50" s="23" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="20" t="inlineStr">
+      <c r="A51" s="23" t="inlineStr">
         <is>
           <t>linkedin_4402305263</t>
         </is>
       </c>
-      <c r="B51" s="20" t="inlineStr">
+      <c r="B51" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C51" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D51" s="20" t="inlineStr">
+      <c r="C51" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D51" s="23" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E51" s="20" t="inlineStr">
+      <c r="E51" s="23" t="inlineStr">
         <is>
           <t>SAP iXp Intern - Software Developer (Agentic AI &amp; LLM systems)</t>
         </is>
       </c>
-      <c r="F51" s="20" t="inlineStr">
+      <c r="F51" s="23" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G51" s="20" t="inlineStr">
+      <c r="G51" s="23" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H51" s="20" t="inlineStr">
+      <c r="H51" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 21:40 UTC</t>
         </is>
       </c>
-      <c r="I51" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J51" s="22" t="inlineStr">
+      <c r="I51" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J51" s="25" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/sap-ixp-intern-software-developer-agentic-ai-llm-systems-at-sap-4402305263?refId=zBXuSSlfFyuxcdEqyfeS8g%3D%3D&amp;trackingId=Imq%2FVHMQWkkoDZp5%2BnATSA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K51" s="20" t="inlineStr">
+      <c r="K51" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L51" s="20" t="inlineStr">
+      <c r="L51" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M51" s="20" t="inlineStr"/>
+      <c r="M51" s="23" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="20" t="inlineStr">
+      <c r="A52" s="23" t="inlineStr">
         <is>
           <t>linkedin_4400467080</t>
         </is>
       </c>
-      <c r="B52" s="20" t="inlineStr">
+      <c r="B52" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C52" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D52" s="20" t="inlineStr">
+      <c r="C52" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D52" s="23" t="inlineStr">
         <is>
           <t>Saama</t>
         </is>
       </c>
-      <c r="E52" s="20" t="inlineStr">
+      <c r="E52" s="23" t="inlineStr">
         <is>
           <t>Intern for AI CoE</t>
         </is>
       </c>
-      <c r="F52" s="20" t="inlineStr">
+      <c r="F52" s="23" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G52" s="20" t="inlineStr">
+      <c r="G52" s="23" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H52" s="20" t="inlineStr">
+      <c r="H52" s="23" t="inlineStr">
         <is>
           <t>2026-04-16 19:45 UTC</t>
         </is>
       </c>
-      <c r="I52" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J52" s="22" t="inlineStr">
+      <c r="I52" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J52" s="25" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/intern-for-ai-coe-at-saama-4400467080?refId=7CvDuV2%2BR%2FzyGozq4UNPPw%3D%3D&amp;trackingId=Ls9yWFAC8lVRx8bmapJfLA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K52" s="20" t="inlineStr">
+      <c r="K52" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-saama-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L52" s="20" t="inlineStr">
+      <c r="L52" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-saama-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M52" s="20" t="inlineStr"/>
+      <c r="M52" s="23" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="20" t="inlineStr">
+      <c r="A53" s="23" t="inlineStr">
         <is>
           <t>linkedin_4400873418</t>
         </is>
       </c>
-      <c r="B53" s="20" t="inlineStr">
+      <c r="B53" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C53" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D53" s="20" t="inlineStr">
+      <c r="C53" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D53" s="23" t="inlineStr">
         <is>
           <t>SANOVIO</t>
         </is>
       </c>
-      <c r="E53" s="20" t="inlineStr">
+      <c r="E53" s="23" t="inlineStr">
         <is>
           <t>AI Engineering Intern</t>
         </is>
       </c>
-      <c r="F53" s="20" t="inlineStr">
+      <c r="F53" s="23" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G53" s="20" t="inlineStr">
+      <c r="G53" s="23" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H53" s="20" t="inlineStr">
+      <c r="H53" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 00:00 UTC</t>
         </is>
       </c>
-      <c r="I53" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J53" s="22" t="inlineStr">
+      <c r="I53" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J53" s="25" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/ai-engineering-intern-at-sanovio-4400873418?refId=egIYeNLcARu6P6oTIZ%2BHfA%3D%3D&amp;trackingId=c6wZ0DtTzvVZpTRC1l5tYQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K53" s="20" t="inlineStr">
+      <c r="K53" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sanovio-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L53" s="20" t="inlineStr">
+      <c r="L53" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sanovio-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M53" s="20" t="inlineStr"/>
+      <c r="M53" s="23" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="20" t="inlineStr">
+      <c r="A54" s="23" t="inlineStr">
         <is>
           <t>linkedin_4403524251</t>
         </is>
       </c>
-      <c r="B54" s="20" t="inlineStr">
+      <c r="B54" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C54" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D54" s="20" t="inlineStr">
+      <c r="C54" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D54" s="23" t="inlineStr">
         <is>
           <t>Nascent Markets</t>
         </is>
       </c>
-      <c r="E54" s="20" t="inlineStr">
+      <c r="E54" s="23" t="inlineStr">
         <is>
           <t>Agentic Systems Intern (Graduate Level)</t>
         </is>
       </c>
-      <c r="F54" s="20" t="inlineStr">
+      <c r="F54" s="23" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G54" s="20" t="inlineStr">
+      <c r="G54" s="23" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H54" s="20" t="inlineStr">
+      <c r="H54" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 19:53 UTC</t>
         </is>
       </c>
-      <c r="I54" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J54" s="22" t="inlineStr">
+      <c r="I54" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J54" s="25" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/agentic-systems-intern-graduate-level-at-nascent-markets-4403524251?refId=Ix0g0waARRaNpzTY4LxvsQ%3D%3D&amp;trackingId=RsqyOyJHkanw%2FTeHGUcadA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K54" s="20" t="inlineStr">
+      <c r="K54" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-nascent-markets-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L54" s="20" t="inlineStr">
+      <c r="L54" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-nascent-markets-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M54" s="20" t="inlineStr"/>
+      <c r="M54" s="23" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="20" t="inlineStr">
+      <c r="A55" s="23" t="inlineStr">
         <is>
           <t>linkedin_4402782985</t>
         </is>
       </c>
-      <c r="B55" s="20" t="inlineStr">
+      <c r="B55" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C55" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D55" s="20" t="inlineStr">
+      <c r="C55" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="inlineStr">
         <is>
           <t>Axiomatic_AI</t>
         </is>
       </c>
-      <c r="E55" s="20" t="inlineStr">
+      <c r="E55" s="23" t="inlineStr">
         <is>
           <t>Internship - Research Intern (Agentic Learning, Memory &amp; Neurosymbolic Reasoning)</t>
         </is>
       </c>
-      <c r="F55" s="20" t="inlineStr">
+      <c r="F55" s="23" t="inlineStr">
         <is>
           <t>Greater Barcelona Metropolitan Area</t>
         </is>
       </c>
-      <c r="G55" s="20" t="inlineStr">
+      <c r="G55" s="23" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H55" s="20" t="inlineStr">
+      <c r="H55" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 05:04 UTC</t>
         </is>
       </c>
-      <c r="I55" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J55" s="22" t="inlineStr">
+      <c r="I55" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J55" s="25" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/internship-research-intern-agentic-learning-memory-neurosymbolic-reasoning-at-axiomatic-ai-4402782985?refId=vm6No12NjZrg2BBV%2BnbuLQ%3D%3D&amp;trackingId=X9FXk%2FBDFftROMNo9Cr20g%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K55" s="20" t="inlineStr">
+      <c r="K55" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-axiomatic-ai-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L55" s="20" t="inlineStr">
+      <c r="L55" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-axiomatic-ai-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M55" s="20" t="inlineStr"/>
+      <c r="M55" s="23" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="20" t="inlineStr">
+      <c r="A56" s="23" t="inlineStr">
         <is>
           <t>linkedin_4309694978</t>
         </is>
       </c>
-      <c r="B56" s="20" t="inlineStr">
+      <c r="B56" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C56" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D56" s="20" t="inlineStr">
+      <c r="C56" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D56" s="23" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E56" s="20" t="inlineStr">
+      <c r="E56" s="23" t="inlineStr">
         <is>
           <t>Graduate Physics Research Intern</t>
         </is>
       </c>
-      <c r="F56" s="20" t="inlineStr">
+      <c r="F56" s="23" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
       </c>
-      <c r="G56" s="20" t="inlineStr">
+      <c r="G56" s="23" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H56" s="20" t="inlineStr">
+      <c r="H56" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 17:37 UTC</t>
         </is>
       </c>
-      <c r="I56" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J56" s="22" t="inlineStr">
+      <c r="I56" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J56" s="25" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/graduate-physics-research-intern-at-dataannotation-4309694978?refId=hlpC50hTZs9sJFHirXWMSg%3D%3D&amp;trackingId=1E0ixzzpb6MzeHKgxpE3Cw%3D%3D&amp;position=9&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K56" s="20" t="inlineStr">
+      <c r="K56" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L56" s="20" t="inlineStr">
+      <c r="L56" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M56" s="20" t="inlineStr"/>
+      <c r="M56" s="23" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="20" t="inlineStr">
+      <c r="A57" s="23" t="inlineStr">
         <is>
           <t>linkedin_4403562730</t>
         </is>
       </c>
-      <c r="B57" s="20" t="inlineStr">
+      <c r="B57" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C57" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D57" s="20" t="inlineStr">
+      <c r="C57" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D57" s="23" t="inlineStr">
         <is>
           <t>BNM Business Solutions LLP</t>
         </is>
       </c>
-      <c r="E57" s="20" t="inlineStr">
+      <c r="E57" s="23" t="inlineStr">
         <is>
           <t>Data Analyst Internship in Navi Mumbai, Mumbai</t>
         </is>
       </c>
-      <c r="F57" s="20" t="inlineStr">
+      <c r="F57" s="23" t="inlineStr">
         <is>
           <t>Mumbai Metropolitan Region</t>
         </is>
       </c>
-      <c r="G57" s="20" t="inlineStr">
+      <c r="G57" s="23" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H57" s="20" t="inlineStr">
+      <c r="H57" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 00:06 UTC</t>
         </is>
       </c>
-      <c r="I57" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J57" s="22" t="inlineStr">
+      <c r="I57" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J57" s="25" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-internship-in-navi-mumbai-mumbai-at-bnm-business-solutions-llp-4403562730?refId=1X9LgKP3%2FAPeJuhZVjyhxw%3D%3D&amp;trackingId=oFY9Z69ZBEGkNtq0cbBOMw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K57" s="20" t="inlineStr">
+      <c r="K57" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bnm-business-solutions-llp-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L57" s="20" t="inlineStr">
+      <c r="L57" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bnm-business-solutions-llp-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M57" s="20" t="inlineStr"/>
+      <c r="M57" s="23" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="20" t="inlineStr">
+      <c r="A58" s="23" t="inlineStr">
         <is>
           <t>linkedin_4309694917</t>
         </is>
       </c>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B58" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C58" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D58" s="20" t="inlineStr">
+      <c r="C58" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D58" s="23" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E58" s="20" t="inlineStr">
+      <c r="E58" s="23" t="inlineStr">
         <is>
           <t>Graduate Biology Research Intern</t>
         </is>
       </c>
-      <c r="F58" s="20" t="inlineStr">
+      <c r="F58" s="23" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
       </c>
-      <c r="G58" s="20" t="inlineStr">
+      <c r="G58" s="23" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H58" s="20" t="inlineStr">
+      <c r="H58" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 17:35 UTC</t>
         </is>
       </c>
-      <c r="I58" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J58" s="22" t="inlineStr">
+      <c r="I58" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J58" s="25" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/graduate-biology-research-intern-at-dataannotation-4309694917?refId=hlpC50hTZs9sJFHirXWMSg%3D%3D&amp;trackingId=BM%2FBx4ElnXDk5hEpiM0gzg%3D%3D&amp;position=8&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K58" s="20" t="inlineStr">
+      <c r="K58" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L58" s="20" t="inlineStr">
+      <c r="L58" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M58" s="20" t="inlineStr"/>
+      <c r="M58" s="23" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="20" t="inlineStr">
+      <c r="A59" s="23" t="inlineStr">
         <is>
           <t>linkedin_4346088677</t>
         </is>
       </c>
-      <c r="B59" s="20" t="inlineStr">
+      <c r="B59" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C59" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D59" s="20" t="inlineStr">
+      <c r="C59" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D59" s="23" t="inlineStr">
         <is>
           <t>revel8</t>
         </is>
       </c>
-      <c r="E59" s="20" t="inlineStr">
+      <c r="E59" s="23" t="inlineStr">
         <is>
           <t>Applied AI Engineer Intern (all genders)</t>
         </is>
       </c>
-      <c r="F59" s="20" t="inlineStr">
+      <c r="F59" s="23" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G59" s="20" t="inlineStr">
+      <c r="G59" s="23" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H59" s="20" t="inlineStr">
+      <c r="H59" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 22:38 UTC</t>
         </is>
       </c>
-      <c r="I59" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J59" s="22" t="inlineStr">
+      <c r="I59" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J59" s="25" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/applied-ai-engineer-intern-all-genders-at-revel8-4346088677?refId=FHQDN2Ta3J6B7WhWnDAuhQ%3D%3D&amp;trackingId=Pf%2Ftwn6H5Hrw8BKjPenbSQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K59" s="20" t="inlineStr">
+      <c r="K59" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-revel8-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L59" s="20" t="inlineStr">
+      <c r="L59" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-revel8-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M59" s="20" t="inlineStr"/>
+      <c r="M59" s="23" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="20" t="inlineStr">
+      <c r="A60" s="23" t="inlineStr">
         <is>
           <t>linkedin_4403475387</t>
         </is>
       </c>
-      <c r="B60" s="20" t="inlineStr">
+      <c r="B60" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C60" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D60" s="20" t="inlineStr">
+      <c r="C60" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D60" s="23" t="inlineStr">
         <is>
           <t>Inc42 Media</t>
         </is>
       </c>
-      <c r="E60" s="20" t="inlineStr">
+      <c r="E60" s="23" t="inlineStr">
         <is>
           <t>Operations Intern: Inc42 AI Summit 2026</t>
         </is>
       </c>
-      <c r="F60" s="20" t="inlineStr">
+      <c r="F60" s="23" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G60" s="20" t="inlineStr">
+      <c r="G60" s="23" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H60" s="20" t="inlineStr">
+      <c r="H60" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 16:23 UTC</t>
         </is>
       </c>
-      <c r="I60" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J60" s="22" t="inlineStr">
+      <c r="I60" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J60" s="25" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/operations-intern-inc42-ai-summit-2026-at-inc42-media-4403475387?refId=jyI2mJ9xFT%2BmdtkV0OCW0g%3D%3D&amp;trackingId=6sWKnvWNaTU69%2B7bcZNxLg%3D%3D&amp;position=10&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K60" s="20" t="inlineStr">
+      <c r="K60" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-inc42-media-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L60" s="20" t="inlineStr">
+      <c r="L60" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-inc42-media-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M60" s="20" t="inlineStr"/>
+      <c r="M60" s="23" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="20" t="inlineStr">
+      <c r="A61" s="23" t="inlineStr">
         <is>
           <t>linkedin_4403008384</t>
         </is>
       </c>
-      <c r="B61" s="20" t="inlineStr">
+      <c r="B61" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C61" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D61" s="20" t="inlineStr">
+      <c r="C61" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D61" s="23" t="inlineStr">
         <is>
           <t>VEDANTA MOBILITY</t>
         </is>
       </c>
-      <c r="E61" s="20" t="inlineStr">
+      <c r="E61" s="23" t="inlineStr">
         <is>
           <t>Founding Psychology Interns | AI Prototype (Govt Proposal – Dubai)</t>
         </is>
       </c>
-      <c r="F61" s="20" t="inlineStr">
+      <c r="F61" s="23" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G61" s="20" t="inlineStr">
+      <c r="G61" s="23" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H61" s="20" t="inlineStr">
+      <c r="H61" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 08:13 UTC</t>
         </is>
       </c>
-      <c r="I61" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J61" s="22" t="inlineStr">
+      <c r="I61" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J61" s="25" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/founding-psychology-interns-ai-prototype-govt-proposal-%E2%80%93-dubai-at-vedanta-mobility-4403008384?refId=moHjgKNH%2BrT9YT5JNnyyqw%3D%3D&amp;trackingId=RUjUOgXLH%2BLJwdPLtKtAMQ%3D%3D&amp;position=13&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K61" s="20" t="inlineStr">
+      <c r="K61" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-vedanta-mobility-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L61" s="20" t="inlineStr">
+      <c r="L61" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-vedanta-mobility-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M61" s="20" t="inlineStr"/>
+      <c r="M61" s="23" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="20" t="inlineStr">
+      <c r="A62" s="23" t="inlineStr">
         <is>
           <t>linkedin_4393616864</t>
         </is>
       </c>
-      <c r="B62" s="20" t="inlineStr">
+      <c r="B62" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C62" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D62" s="20" t="inlineStr">
+      <c r="C62" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D62" s="23" t="inlineStr">
         <is>
           <t>Medidata Solutions</t>
         </is>
       </c>
-      <c r="E62" s="20" t="inlineStr">
+      <c r="E62" s="23" t="inlineStr">
         <is>
           <t>Data Science Intern</t>
         </is>
       </c>
-      <c r="F62" s="20" t="inlineStr">
+      <c r="F62" s="23" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
       </c>
-      <c r="G62" s="20" t="inlineStr">
+      <c r="G62" s="23" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H62" s="20" t="inlineStr">
+      <c r="H62" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 13:13 UTC</t>
         </is>
       </c>
-      <c r="I62" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J62" s="22" t="inlineStr">
+      <c r="I62" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J62" s="25" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-science-intern-at-medidata-solutions-4393616864?refId=sPMU%2B0UtbDUVjDHc3gXCxA%3D%3D&amp;trackingId=%2BVrdVCzEYQ3jJQvUf4VUtA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K62" s="20" t="inlineStr">
+      <c r="K62" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-medidata-solutions-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L62" s="20" t="inlineStr">
+      <c r="L62" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-medidata-solutions-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M62" s="20" t="inlineStr"/>
+      <c r="M62" s="23" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="20" t="inlineStr">
+      <c r="A63" s="23" t="inlineStr">
         <is>
           <t>linkedin_4403819462</t>
         </is>
       </c>
-      <c r="B63" s="20" t="inlineStr">
+      <c r="B63" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C63" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D63" s="20" t="inlineStr">
+      <c r="C63" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D63" s="23" t="inlineStr">
         <is>
           <t>Calypso Commodities</t>
         </is>
       </c>
-      <c r="E63" s="20" t="inlineStr">
+      <c r="E63" s="23" t="inlineStr">
         <is>
           <t>Trading - Quant &amp; Engineering Intern (Client-Facing)</t>
         </is>
       </c>
-      <c r="F63" s="20" t="inlineStr">
+      <c r="F63" s="23" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="G63" s="20" t="inlineStr">
+      <c r="G63" s="23" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H63" s="20" t="inlineStr">
+      <c r="H63" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 12:44 UTC</t>
         </is>
       </c>
-      <c r="I63" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J63" s="22" t="inlineStr">
+      <c r="I63" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J63" s="25" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/trading-quant-engineering-intern-client-facing-at-calypso-commodities-4403819462?refId=wb%2BADKYeCTj8bBBZgf97xw%3D%3D&amp;trackingId=o0ZBUwzyVOiml0tJPOsNww%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K63" s="20" t="inlineStr">
+      <c r="K63" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-calypso-commodities-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L63" s="20" t="inlineStr">
+      <c r="L63" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-calypso-commodities-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M63" s="20" t="inlineStr"/>
+      <c r="M63" s="23" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="20" t="inlineStr">
+      <c r="A64" s="23" t="inlineStr">
         <is>
           <t>linkedin_4355269413</t>
         </is>
       </c>
-      <c r="B64" s="20" t="inlineStr">
+      <c r="B64" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C64" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D64" s="20" t="inlineStr">
+      <c r="C64" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D64" s="23" t="inlineStr">
         <is>
           <t>Temasek</t>
         </is>
       </c>
-      <c r="E64" s="20" t="inlineStr">
+      <c r="E64" s="23" t="inlineStr">
         <is>
           <t>Data Analytics/Science Intern, People Technology (Jun/Jul - Dec 2026)</t>
         </is>
       </c>
-      <c r="F64" s="20" t="inlineStr">
+      <c r="F64" s="23" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G64" s="20" t="inlineStr">
+      <c r="G64" s="23" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H64" s="20" t="inlineStr">
+      <c r="H64" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 10:35 UTC</t>
         </is>
       </c>
-      <c r="I64" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J64" s="22" t="inlineStr">
+      <c r="I64" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J64" s="25" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/data-analytics-science-intern-people-technology-jun-jul-dec-2026-at-temasek-4355269413?refId=emjtNEhTXLtOX%2BguWexSsg%3D%3D&amp;trackingId=DPHM%2FIJzKL0emfNJ1LMMoA%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K64" s="20" t="inlineStr">
+      <c r="K64" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-temasek-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L64" s="20" t="inlineStr">
+      <c r="L64" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-temasek-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M64" s="20" t="inlineStr"/>
+      <c r="M64" s="23" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="20" t="inlineStr">
+      <c r="A65" s="23" t="inlineStr">
         <is>
           <t>linkedin_4403065097</t>
         </is>
       </c>
-      <c r="B65" s="20" t="inlineStr">
+      <c r="B65" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C65" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D65" s="20" t="inlineStr">
+      <c r="C65" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D65" s="23" t="inlineStr">
         <is>
           <t>BLACK TREE GAMING LIMITED</t>
         </is>
       </c>
-      <c r="E65" s="20" t="inlineStr">
+      <c r="E65" s="23" t="inlineStr">
         <is>
           <t>Data Scientist (ML)</t>
         </is>
       </c>
-      <c r="F65" s="20" t="inlineStr">
+      <c r="F65" s="23" t="inlineStr">
         <is>
           <t>Greater London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G65" s="20" t="inlineStr">
+      <c r="G65" s="23" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H65" s="20" t="inlineStr">
+      <c r="H65" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 14:22 UTC</t>
         </is>
       </c>
-      <c r="I65" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J65" s="22" t="inlineStr">
+      <c r="I65" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J65" s="25" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/data-scientist-ml-at-black-tree-gaming-limited-4403065097?refId=X9Gb9UkVv%2BJtfDRc0dJPwA%3D%3D&amp;trackingId=Mfl%2BC%2FBN9DJehDmug19dGA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K65" s="20" t="inlineStr">
+      <c r="K65" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-black-tree-gaming-limited-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L65" s="20" t="inlineStr">
+      <c r="L65" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-black-tree-gaming-limited-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M65" s="20" t="inlineStr"/>
+      <c r="M65" s="23" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="20" t="inlineStr">
+      <c r="A66" s="23" t="inlineStr">
         <is>
           <t>linkedin_4291533663</t>
         </is>
       </c>
-      <c r="B66" s="20" t="inlineStr">
+      <c r="B66" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C66" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D66" s="20" t="inlineStr">
+      <c r="C66" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D66" s="23" t="inlineStr">
         <is>
           <t>McKinsey &amp; Company</t>
         </is>
       </c>
-      <c r="E66" s="20" t="inlineStr">
+      <c r="E66" s="23" t="inlineStr">
         <is>
           <t>Praktikum als Fellow Intern - Tech &amp; AI (m/w/d)</t>
         </is>
       </c>
-      <c r="F66" s="20" t="inlineStr">
+      <c r="F66" s="23" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G66" s="20" t="inlineStr">
+      <c r="G66" s="23" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H66" s="20" t="inlineStr">
+      <c r="H66" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 09:49 UTC</t>
         </is>
       </c>
-      <c r="I66" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J66" s="22" t="inlineStr">
+      <c r="I66" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J66" s="25" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/praktikum-als-fellow-intern-tech-ai-m-w-d-at-mckinsey-company-4291533663?refId=UmiOr88gcWDNbqipJy2ZTg%3D%3D&amp;trackingId=UvtRxMXKlReoOEeGgMaEfA%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K66" s="20" t="inlineStr">
+      <c r="K66" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-mckinsey-company-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L66" s="20" t="inlineStr">
+      <c r="L66" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-mckinsey-company-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M66" s="20" t="inlineStr"/>
+      <c r="M66" s="23" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="20" t="inlineStr">
+      <c r="A67" s="23" t="inlineStr">
         <is>
           <t>linkedin_4336838608</t>
         </is>
       </c>
-      <c r="B67" s="20" t="inlineStr">
+      <c r="B67" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C67" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D67" s="20" t="inlineStr">
+      <c r="C67" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D67" s="23" t="inlineStr">
         <is>
           <t>Sendbird</t>
         </is>
       </c>
-      <c r="E67" s="20" t="inlineStr">
+      <c r="E67" s="23" t="inlineStr">
         <is>
           <t>AI Agent Engineer, Intern</t>
         </is>
       </c>
-      <c r="F67" s="20" t="inlineStr">
+      <c r="F67" s="23" t="inlineStr">
         <is>
           <t>Seoul, Seoul, South Korea</t>
         </is>
       </c>
-      <c r="G67" s="20" t="inlineStr">
+      <c r="G67" s="23" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H67" s="20" t="inlineStr">
+      <c r="H67" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 13:46 UTC</t>
         </is>
       </c>
-      <c r="I67" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J67" s="22" t="inlineStr">
+      <c r="I67" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J67" s="25" t="inlineStr">
         <is>
           <t>https://kr.linkedin.com/jobs/view/ai-agent-engineer-intern-at-sendbird-4336838608?refId=%2F1qLChSVn3giUiiNusHaIQ%3D%3D&amp;trackingId=l6mUUvSfC97HjoyrA8uuqg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K67" s="20" t="inlineStr">
+      <c r="K67" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sendbird-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L67" s="20" t="inlineStr">
+      <c r="L67" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sendbird-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M67" s="20" t="inlineStr"/>
+      <c r="M67" s="23" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="20" t="inlineStr">
+      <c r="A68" s="23" t="inlineStr">
         <is>
           <t>linkedin_4372783510</t>
         </is>
       </c>
-      <c r="B68" s="20" t="inlineStr">
+      <c r="B68" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C68" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D68" s="20" t="inlineStr">
+      <c r="C68" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D68" s="23" t="inlineStr">
         <is>
           <t>42dot</t>
         </is>
       </c>
-      <c r="E68" s="20" t="inlineStr">
+      <c r="E68" s="23" t="inlineStr">
         <is>
           <t>[MS/PhD Intern] AI Engineer (정규직 전환형)</t>
         </is>
       </c>
-      <c r="F68" s="20" t="inlineStr">
+      <c r="F68" s="23" t="inlineStr">
         <is>
           <t>Seongnam, Gyeonggi, South Korea</t>
         </is>
       </c>
-      <c r="G68" s="20" t="inlineStr">
+      <c r="G68" s="23" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H68" s="20" t="inlineStr">
+      <c r="H68" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 15:08 UTC</t>
         </is>
       </c>
-      <c r="I68" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J68" s="22" t="inlineStr">
+      <c r="I68" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J68" s="25" t="inlineStr">
         <is>
           <t>https://kr.linkedin.com/jobs/view/ms-phd-intern-ai-engineer-%EC%A0%95%EA%B7%9C%EC%A7%81-%EC%A0%84%ED%99%98%ED%98%95-at-42dot-4372783510?refId=%2F1qLChSVn3giUiiNusHaIQ%3D%3D&amp;trackingId=TVYs5RWI1wgPuuVRiBioUA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K68" s="20" t="inlineStr">
+      <c r="K68" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-42dot-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L68" s="20" t="inlineStr">
+      <c r="L68" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-42dot-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M68" s="20" t="inlineStr"/>
+      <c r="M68" s="23" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="20" t="inlineStr">
+      <c r="A69" s="23" t="inlineStr">
         <is>
           <t>linkedin_4402753102</t>
         </is>
       </c>
-      <c r="B69" s="20" t="inlineStr">
+      <c r="B69" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C69" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D69" s="20" t="inlineStr">
+      <c r="C69" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D69" s="23" t="inlineStr">
         <is>
           <t>Five9</t>
         </is>
       </c>
-      <c r="E69" s="20" t="inlineStr">
+      <c r="E69" s="23" t="inlineStr">
         <is>
           <t>Software Developer AI Insights Intern</t>
         </is>
       </c>
-      <c r="F69" s="20" t="inlineStr">
+      <c r="F69" s="23" t="inlineStr">
         <is>
           <t>San Ramon, CA</t>
         </is>
       </c>
-      <c r="G69" s="20" t="inlineStr">
+      <c r="G69" s="23" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H69" s="20" t="inlineStr">
+      <c r="H69" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 20:56 UTC</t>
         </is>
       </c>
-      <c r="I69" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J69" s="22" t="inlineStr">
+      <c r="I69" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J69" s="25" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/software-developer-ai-insights-intern-at-five9-4402753102?refId=%2FiKmLsIvYp2TclUyf8MJwg%3D%3D&amp;trackingId=X2UMBr3jE86J9JmPv42B2w%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K69" s="20" t="inlineStr">
+      <c r="K69" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-five9-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L69" s="20" t="inlineStr">
+      <c r="L69" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-five9-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M69" s="20" t="inlineStr"/>
+      <c r="M69" s="23" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="20" t="inlineStr">
+      <c r="A70" s="23" t="inlineStr">
         <is>
           <t>linkedin_4403519373</t>
         </is>
       </c>
-      <c r="B70" s="20" t="inlineStr">
+      <c r="B70" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C70" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D70" s="20" t="inlineStr">
+      <c r="C70" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D70" s="23" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E70" s="20" t="inlineStr">
+      <c r="E70" s="23" t="inlineStr">
         <is>
           <t>PhD Research Intern, Physical AI in Perception</t>
         </is>
       </c>
-      <c r="F70" s="20" t="inlineStr">
+      <c r="F70" s="23" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G70" s="20" t="inlineStr">
+      <c r="G70" s="23" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H70" s="20" t="inlineStr">
+      <c r="H70" s="23" t="inlineStr">
         <is>
           <t>2026-04-17 20:07 UTC</t>
         </is>
       </c>
-      <c r="I70" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J70" s="22" t="inlineStr">
+      <c r="I70" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J70" s="25" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-physical-ai-in-perception-at-zoox-4403519373?refId=LChV34e%2Bd7cvBpZ%2FbJAZjw%3D%3D&amp;trackingId=vlvuJ54NQfvZvNY3pNGqNw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K70" s="20" t="inlineStr">
+      <c r="K70" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L70" s="20" t="inlineStr">
+      <c r="L70" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M70" s="20" t="inlineStr"/>
+      <c r="M70" s="23" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="20" t="inlineStr">
+      <c r="A71" s="23" t="inlineStr">
         <is>
           <t>linkedin_4403095692</t>
         </is>
       </c>
-      <c r="B71" s="20" t="inlineStr">
+      <c r="B71" s="23" t="inlineStr">
         <is>
           <t>2026-04-19 08:24</t>
         </is>
       </c>
-      <c r="C71" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D71" s="20" t="inlineStr">
+      <c r="C71" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D71" s="23" t="inlineStr">
         <is>
           <t>Starrycraze Technology</t>
         </is>
       </c>
-      <c r="E71" s="20" t="inlineStr">
+      <c r="E71" s="23" t="inlineStr">
         <is>
           <t>Data Scientist Intern</t>
         </is>
       </c>
-      <c r="F71" s="20" t="inlineStr">
+      <c r="F71" s="23" t="inlineStr">
         <is>
           <t>Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G71" s="20" t="inlineStr">
+      <c r="G71" s="23" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H71" s="20" t="inlineStr">
+      <c r="H71" s="23" t="inlineStr">
         <is>
           <t>2026-04-19 04:58 UTC</t>
         </is>
       </c>
-      <c r="I71" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J71" s="22" t="inlineStr">
+      <c r="I71" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J71" s="25" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/data-scientist-intern-at-starrycraze-technology-4403095692?refId=TVQyGaR78N78VqNo32HHeA%3D%3D&amp;trackingId=iTU%2BdVDc304eRUiD2UiVkA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K71" s="20" t="inlineStr">
+      <c r="K71" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-starrycraze-technology-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L71" s="20" t="inlineStr">
+      <c r="L71" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-starrycraze-technology-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M71" s="20" t="inlineStr"/>
+      <c r="M71" s="23" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="20" t="inlineStr">
+      <c r="A72" s="23" t="inlineStr">
         <is>
           <t>linkedin_4403848986</t>
         </is>
       </c>
-      <c r="B72" s="20" t="inlineStr">
+      <c r="B72" s="23" t="inlineStr">
         <is>
           <t>2026-04-19 08:24</t>
         </is>
       </c>
-      <c r="C72" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D72" s="20" t="inlineStr">
+      <c r="C72" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D72" s="23" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E72" s="20" t="inlineStr">
+      <c r="E72" s="23" t="inlineStr">
         <is>
           <t>PhD Research Intern, Offline Driving Intelligence</t>
         </is>
       </c>
-      <c r="F72" s="20" t="inlineStr">
+      <c r="F72" s="23" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G72" s="20" t="inlineStr">
+      <c r="G72" s="23" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H72" s="20" t="inlineStr">
+      <c r="H72" s="23" t="inlineStr">
         <is>
           <t>2026-04-19 02:06 UTC</t>
         </is>
       </c>
-      <c r="I72" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J72" s="22" t="inlineStr">
+      <c r="I72" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J72" s="25" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-offline-driving-intelligence-at-zoox-4403848986?refId=5ydRxcXuf5aHqLJVjey87Q%3D%3D&amp;trackingId=FWtGym5%2BhCmPjiMPBVYS7w%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K72" s="20" t="inlineStr">
+      <c r="K72" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L72" s="20" t="inlineStr">
+      <c r="L72" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M72" s="20" t="inlineStr"/>
+      <c r="M72" s="23" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="20" t="inlineStr">
+      <c r="A73" s="23" t="inlineStr">
         <is>
           <t>linkedin_4371758156</t>
         </is>
       </c>
-      <c r="B73" s="20" t="inlineStr">
+      <c r="B73" s="23" t="inlineStr">
         <is>
           <t>2026-04-19 08:24</t>
         </is>
       </c>
-      <c r="C73" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D73" s="20" t="inlineStr">
+      <c r="C73" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D73" s="23" t="inlineStr">
         <is>
           <t>Lowe's India</t>
         </is>
       </c>
-      <c r="E73" s="20" t="inlineStr">
+      <c r="E73" s="23" t="inlineStr">
         <is>
           <t>DIH Intern, Data Engineering</t>
         </is>
       </c>
-      <c r="F73" s="20" t="inlineStr">
+      <c r="F73" s="23" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G73" s="20" t="inlineStr">
+      <c r="G73" s="23" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H73" s="20" t="inlineStr">
+      <c r="H73" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 10:48 UTC</t>
         </is>
       </c>
-      <c r="I73" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J73" s="22" t="inlineStr">
+      <c r="I73" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J73" s="25" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/dih-intern-data-engineering-at-lowe-s-india-4371758156?refId=1mgTdTTgR1UncTTJ8Ts5OA%3D%3D&amp;trackingId=7HYWBNU0zclnyp9qIoW2Jw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K73" s="20" t="inlineStr">
+      <c r="K73" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-lowes-india-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L73" s="20" t="inlineStr">
+      <c r="L73" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-lowes-india-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M73" s="20" t="inlineStr"/>
+      <c r="M73" s="23" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="20" t="inlineStr">
+      <c r="A74" s="23" t="inlineStr">
         <is>
           <t>linkedin_4327191639</t>
         </is>
       </c>
-      <c r="B74" s="20" t="inlineStr">
+      <c r="B74" s="23" t="inlineStr">
         <is>
           <t>2026-04-19 08:24</t>
         </is>
       </c>
-      <c r="C74" s="20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D74" s="20" t="inlineStr">
+      <c r="C74" s="23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D74" s="23" t="inlineStr">
         <is>
           <t>Whatnot</t>
         </is>
       </c>
-      <c r="E74" s="20" t="inlineStr">
+      <c r="E74" s="23" t="inlineStr">
         <is>
           <t>Data Scientist, Product Analytics</t>
         </is>
       </c>
-      <c r="F74" s="20" t="inlineStr">
+      <c r="F74" s="23" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G74" s="20" t="inlineStr">
+      <c r="G74" s="23" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H74" s="20" t="inlineStr">
+      <c r="H74" s="23" t="inlineStr">
         <is>
           <t>2026-04-18 13:22 UTC</t>
         </is>
       </c>
-      <c r="I74" s="21" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J74" s="22" t="inlineStr">
+      <c r="I74" s="24" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J74" s="25" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-scientist-product-analytics-at-whatnot-4327191639?refId=mfQJnJ6mRr3La1qB9YnNGA%3D%3D&amp;trackingId=k4mLJmsHD9wYHSZlc4RA%2Fw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K74" s="20" t="inlineStr">
+      <c r="K74" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-whatnot-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L74" s="20" t="inlineStr">
+      <c r="L74" s="23" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-whatnot-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M74" s="20" t="inlineStr"/>
+      <c r="M74" s="23" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="23" t="inlineStr">
@@ -5523,6 +5532,510 @@
         </is>
       </c>
       <c r="M79" s="23" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="26" t="inlineStr">
+        <is>
+          <t>linkedin_4404025051</t>
+        </is>
+      </c>
+      <c r="B80" s="26" t="inlineStr">
+        <is>
+          <t>2026-04-20 09:16</t>
+        </is>
+      </c>
+      <c r="C80" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D80" s="26" t="inlineStr">
+        <is>
+          <t>Dassault Systèmes</t>
+        </is>
+      </c>
+      <c r="E80" s="26" t="inlineStr">
+        <is>
+          <t>INTERNSHIP: Data Science (6mo June 2026)</t>
+        </is>
+      </c>
+      <c r="F80" s="26" t="inlineStr">
+        <is>
+          <t>Waltham, MA</t>
+        </is>
+      </c>
+      <c r="G80" s="26" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H80" s="26" t="inlineStr">
+        <is>
+          <t>2026-04-19 23:38 UTC</t>
+        </is>
+      </c>
+      <c r="I80" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J80" s="28" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/internship-data-science-6mo-june-2026-at-dassault-syst%C3%A8mes-4404025051?refId=S4wy0FwbzbiuPwYYk2m0dw%3D%3D&amp;trackingId=RGARwF5XkYgBTfpY7DrrZg%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K80" s="26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dassault-systèmes-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="L80" s="26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dassault-systèmes-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="M80" s="26" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="26" t="inlineStr">
+        <is>
+          <t>linkedin_4403368519</t>
+        </is>
+      </c>
+      <c r="B81" s="26" t="inlineStr">
+        <is>
+          <t>2026-04-20 09:16</t>
+        </is>
+      </c>
+      <c r="C81" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D81" s="26" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="E81" s="26" t="inlineStr">
+        <is>
+          <t>Risk Control Algorithm Engineer Intern</t>
+        </is>
+      </c>
+      <c r="F81" s="26" t="inlineStr">
+        <is>
+          <t>Hong Kong, Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="G81" s="26" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H81" s="26" t="inlineStr">
+        <is>
+          <t>2026-04-20 08:20 UTC</t>
+        </is>
+      </c>
+      <c r="I81" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J81" s="28" t="inlineStr">
+        <is>
+          <t>https://hk.linkedin.com/jobs/view/risk-control-algorithm-engineer-intern-at-bybit-4403368519?refId=9jFaGeHrGBqPLrXTIfcNwA%3D%3D&amp;trackingId=glTg%2F1p9B2dY4YX59MH9DA%3D%3D&amp;position=2&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K81" s="26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bybit-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="L81" s="26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bybit-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="M81" s="26" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="26" t="inlineStr">
+        <is>
+          <t>linkedin_4403320381</t>
+        </is>
+      </c>
+      <c r="B82" s="26" t="inlineStr">
+        <is>
+          <t>2026-04-20 09:16</t>
+        </is>
+      </c>
+      <c r="C82" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D82" s="26" t="inlineStr">
+        <is>
+          <t>Digitomics AI</t>
+        </is>
+      </c>
+      <c r="E82" s="26" t="inlineStr">
+        <is>
+          <t>AI Engineering Intern</t>
+        </is>
+      </c>
+      <c r="F82" s="26" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India</t>
+        </is>
+      </c>
+      <c r="G82" s="26" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H82" s="26" t="inlineStr">
+        <is>
+          <t>2026-04-20 08:43 UTC</t>
+        </is>
+      </c>
+      <c r="I82" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J82" s="28" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ai-engineering-intern-at-digitomics-ai-4403320381?refId=0fRwalKs7ueOf%2FH7m6U26Q%3D%3D&amp;trackingId=zbHZrmgemJdB%2BlQYFw7geg%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K82" s="26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-digitomics-ai-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="L82" s="26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-digitomics-ai-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="M82" s="26" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="26" t="inlineStr">
+        <is>
+          <t>linkedin_4403358236</t>
+        </is>
+      </c>
+      <c r="B83" s="26" t="inlineStr">
+        <is>
+          <t>2026-04-20 09:16</t>
+        </is>
+      </c>
+      <c r="C83" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D83" s="26" t="inlineStr">
+        <is>
+          <t>InMobi</t>
+        </is>
+      </c>
+      <c r="E83" s="26" t="inlineStr">
+        <is>
+          <t>Intern - Industrial Trainee</t>
+        </is>
+      </c>
+      <c r="F83" s="26" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India</t>
+        </is>
+      </c>
+      <c r="G83" s="26" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H83" s="26" t="inlineStr">
+        <is>
+          <t>2026-04-20 06:44 UTC</t>
+        </is>
+      </c>
+      <c r="I83" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J83" s="28" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/intern-industrial-trainee-at-inmobi-4403358236?refId=Hz8z0MLJ0gvG3WjNfG9q9Q%3D%3D&amp;trackingId=uO3LmXVsff1dJma3y3w5Gg%3D%3D&amp;position=8&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K83" s="26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-inmobi-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="L83" s="26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-inmobi-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="M83" s="26" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="26" t="inlineStr">
+        <is>
+          <t>linkedin_4403359204</t>
+        </is>
+      </c>
+      <c r="B84" s="26" t="inlineStr">
+        <is>
+          <t>2026-04-20 09:16</t>
+        </is>
+      </c>
+      <c r="C84" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D84" s="26" t="inlineStr">
+        <is>
+          <t>TakedaPharmaceutical Nordics AB</t>
+        </is>
+      </c>
+      <c r="E84" s="26" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="F84" s="26" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="G84" s="26" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H84" s="26" t="inlineStr">
+        <is>
+          <t>2026-04-20 06:45 UTC</t>
+        </is>
+      </c>
+      <c r="I84" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J84" s="28" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-data-scientist-at-takedapharmaceutical-nordics-ab-4403359204?refId=S4wy0FwbzbiuPwYYk2m0dw%3D%3D&amp;trackingId=zfL5isOE6jcFxwuJQPpkyA%3D%3D&amp;position=2&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K84" s="26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-takedapharmaceutical-nordics-ab-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="L84" s="26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-takedapharmaceutical-nordics-ab-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="M84" s="26" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="26" t="inlineStr">
+        <is>
+          <t>linkedin_4403353339</t>
+        </is>
+      </c>
+      <c r="B85" s="26" t="inlineStr">
+        <is>
+          <t>2026-04-20 09:16</t>
+        </is>
+      </c>
+      <c r="C85" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D85" s="26" t="inlineStr">
+        <is>
+          <t>Kuku</t>
+        </is>
+      </c>
+      <c r="E85" s="26" t="inlineStr">
+        <is>
+          <t>AI Intern</t>
+        </is>
+      </c>
+      <c r="F85" s="26" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India</t>
+        </is>
+      </c>
+      <c r="G85" s="26" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H85" s="26" t="inlineStr">
+        <is>
+          <t>2026-04-20 07:10 UTC</t>
+        </is>
+      </c>
+      <c r="I85" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J85" s="28" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ai-intern-at-kuku-4403353339?refId=Hz8z0MLJ0gvG3WjNfG9q9Q%3D%3D&amp;trackingId=HENEvtuPxzCTSc47zwTLxw%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K85" s="26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-kuku-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="L85" s="26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-kuku-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="M85" s="26" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="26" t="inlineStr">
+        <is>
+          <t>linkedin_4403306789</t>
+        </is>
+      </c>
+      <c r="B86" s="26" t="inlineStr">
+        <is>
+          <t>2026-04-20 09:16</t>
+        </is>
+      </c>
+      <c r="C86" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D86" s="26" t="inlineStr">
+        <is>
+          <t>Skycliff IT</t>
+        </is>
+      </c>
+      <c r="E86" s="26" t="inlineStr">
+        <is>
+          <t>Research Intern</t>
+        </is>
+      </c>
+      <c r="F86" s="26" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India</t>
+        </is>
+      </c>
+      <c r="G86" s="26" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H86" s="26" t="inlineStr">
+        <is>
+          <t>2026-04-19 22:21 UTC</t>
+        </is>
+      </c>
+      <c r="I86" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J86" s="28" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/research-intern-at-skycliff-it-4403306789?refId=KN18fO0braE9qgElBP9zEg%3D%3D&amp;trackingId=%2Bm9LCS%2BxHyH7O3sA%2BvKB2A%3D%3D&amp;position=5&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K86" s="26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="L86" s="26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="M86" s="26" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="26" t="inlineStr">
+        <is>
+          <t>linkedin_4336984951</t>
+        </is>
+      </c>
+      <c r="B87" s="26" t="inlineStr">
+        <is>
+          <t>2026-04-20 09:16</t>
+        </is>
+      </c>
+      <c r="C87" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D87" s="26" t="inlineStr">
+        <is>
+          <t>Zoox</t>
+        </is>
+      </c>
+      <c r="E87" s="26" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer Intern, Simulation</t>
+        </is>
+      </c>
+      <c r="F87" s="26" t="inlineStr">
+        <is>
+          <t>Foster City, CA</t>
+        </is>
+      </c>
+      <c r="G87" s="26" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H87" s="26" t="inlineStr">
+        <is>
+          <t>2026-04-19 09:41 UTC</t>
+        </is>
+      </c>
+      <c r="I87" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J87" s="28" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/machine-learning-engineer-intern-simulation-at-zoox-4336984951?refId=kzdKy3lQPz5ITmALB3aiLA%3D%3D&amp;trackingId=TBJ5wFzjDmfdPFnmhbpCvA%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K87" s="26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="L87" s="26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="M87" s="26" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5604,6 +6117,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -83,10 +83,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -534,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -620,4918 +629,4918 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>linkedin_4401809501</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C2" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="C2" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D2" s="26" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E2" s="23" t="inlineStr">
+      <c r="E2" s="26" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F2" s="23" t="inlineStr">
+      <c r="F2" s="26" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G2" s="23" t="inlineStr">
+      <c r="G2" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H2" s="23" t="inlineStr">
+      <c r="H2" s="26" t="inlineStr">
         <is>
           <t>2026-04-15 22:19 UTC</t>
         </is>
       </c>
-      <c r="I2" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J2" s="25" t="inlineStr">
+      <c r="I2" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/research-intern-at-skycliff-it-4401809501?refId=HHi6SaK1fggu3E9dI3MtVg%3D%3D&amp;trackingId=r33pSo29lHStfk9FH82pyw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K2" s="23" t="inlineStr">
+      <c r="K2" s="26" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L2" s="23" t="inlineStr">
+      <c r="L2" s="26" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M2" s="23" t="inlineStr"/>
+      <c r="M2" s="26" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>linkedin_4402568578</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C3" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>Webs X UM</t>
         </is>
       </c>
-      <c r="E3" s="23" t="inlineStr">
+      <c r="E3" s="26" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F3" s="23" t="inlineStr">
+      <c r="F3" s="26" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G3" s="23" t="inlineStr">
+      <c r="G3" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H3" s="23" t="inlineStr">
+      <c r="H3" s="26" t="inlineStr">
         <is>
           <t>2026-04-15 19:20 UTC</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J3" s="25" t="inlineStr">
+      <c r="I3" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-webs-x-um-4402568578?refId=g89JM6cY8EFeoLk6JL5tVg%3D%3D&amp;trackingId=uFZVJJX7SSI0XCPFIrLqmA%3D%3D&amp;position=19&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K3" s="23" t="inlineStr">
+      <c r="K3" s="26" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-webs-x-um-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L3" s="23" t="inlineStr">
+      <c r="L3" s="26" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-webs-x-um-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M3" s="23" t="inlineStr"/>
+      <c r="M3" s="26" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>linkedin_4399996740</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="C4" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>SUN PHARMA</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="26" t="inlineStr">
         <is>
           <t>Becario</t>
         </is>
       </c>
-      <c r="F4" s="23" t="inlineStr">
+      <c r="F4" s="26" t="inlineStr">
         <is>
           <t>Mexico City, Mexico</t>
         </is>
       </c>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="G4" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H4" s="23" t="inlineStr">
+      <c r="H4" s="26" t="inlineStr">
         <is>
           <t>2026-04-15 17:59 UTC</t>
         </is>
       </c>
-      <c r="I4" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J4" s="25" t="inlineStr">
+      <c r="I4" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
         <is>
           <t>https://mx.linkedin.com/jobs/view/becario-at-sun-pharma-4399996740?refId=g89JM6cY8EFeoLk6JL5tVg%3D%3D&amp;trackingId=sZ0Fkcf4RHuIpzXu4mJRNg%3D%3D&amp;position=22&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K4" s="23" t="inlineStr">
+      <c r="K4" s="26" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-sun-pharma-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L4" s="23" t="inlineStr">
+      <c r="L4" s="26" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-sun-pharma-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M4" s="23" t="inlineStr"/>
+      <c r="M4" s="26" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>linkedin_4399975959</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>LS Direct</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>Data Analytics Intern</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="F5" s="26" t="inlineStr">
         <is>
           <t>Suffern, NY</t>
         </is>
       </c>
-      <c r="G5" s="23" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H5" s="23" t="inlineStr">
+      <c r="H5" s="26" t="inlineStr">
         <is>
           <t>2026-04-15 14:26 UTC</t>
         </is>
       </c>
-      <c r="I5" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-analytics-intern-at-ls-direct-4399975959?refId=pg0ll3e89fatVyUznLcdpw%3D%3D&amp;trackingId=5b41IoyQfIfx3Tu42domiQ%3D%3D&amp;position=23&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K5" s="23" t="inlineStr">
+      <c r="K5" s="26" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-ls-direct-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L5" s="23" t="inlineStr">
+      <c r="L5" s="26" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-ls-direct-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M5" s="23" t="inlineStr"/>
+      <c r="M5" s="26" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>linkedin_4370546718</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>Clarivate</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>Lead Data Scientist</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="26" t="inlineStr">
         <is>
           <t>Barcelona, Catalonia, Spain</t>
         </is>
       </c>
-      <c r="G6" s="23" t="inlineStr">
+      <c r="G6" s="26" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="H6" s="26" t="inlineStr">
         <is>
           <t>2026-04-15 12:16 UTC</t>
         </is>
       </c>
-      <c r="I6" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J6" s="25" t="inlineStr">
+      <c r="I6" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/lead-data-scientist-at-clarivate-4370546718?refId=FyyqQfduMQ8KZ7B5LeF0UQ%3D%3D&amp;trackingId=1i1kXdbV7SMunyFTiSJHJg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K6" s="23" t="inlineStr">
+      <c r="K6" s="26" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-clarivate-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L6" s="23" t="inlineStr">
+      <c r="L6" s="26" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-clarivate-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M6" s="23" t="inlineStr"/>
+      <c r="M6" s="26" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>linkedin_4389810164</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>Vitality</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t>Senior Data Scientist - 12 Month FTC</t>
         </is>
       </c>
-      <c r="F7" s="23" t="inlineStr">
+      <c r="F7" s="26" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G7" s="23" t="inlineStr">
+      <c r="G7" s="26" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H7" s="23" t="inlineStr">
+      <c r="H7" s="26" t="inlineStr">
         <is>
           <t>2026-04-15 09:39 UTC</t>
         </is>
       </c>
-      <c r="I7" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J7" s="25" t="inlineStr">
+      <c r="I7" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J7" s="28" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/senior-data-scientist-12-month-ftc-at-vitality-4389810164?refId=FPz%2BrPoaQeqgXBm%2FfOzGGA%3D%3D&amp;trackingId=yVNh55t2X2xocDT4i6HDqQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K7" s="23" t="inlineStr">
+      <c r="K7" s="26" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-vitality-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L7" s="23" t="inlineStr">
+      <c r="L7" s="26" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-vitality-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M7" s="23" t="inlineStr"/>
+      <c r="M7" s="26" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>linkedin_4399952059</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>traide AI</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>AI Associate (f/m/x) (B2B SaaS Startup) - Intern/Working Student</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="26" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="G8" s="26" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
+      <c r="H8" s="26" t="inlineStr">
         <is>
           <t>2026-04-15 07:04 UTC</t>
         </is>
       </c>
-      <c r="I8" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J8" s="25" t="inlineStr">
+      <c r="I8" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J8" s="28" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/ai-associate-f-m-x-b2b-saas-startup-intern-working-student-at-traide-ai-4399952059?refId=x0uIkl175n0hipT17L%2FGRw%3D%3D&amp;trackingId=8kdzUQgW%2B7rCk2pO2oIErg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K8" s="23" t="inlineStr">
+      <c r="K8" s="26" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-traide-ai-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L8" s="23" t="inlineStr">
+      <c r="L8" s="26" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-traide-ai-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M8" s="23" t="inlineStr"/>
+      <c r="M8" s="26" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>linkedin_4399933254</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="inlineStr">
         <is>
           <t>Briink</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="26" t="inlineStr">
         <is>
           <t>Growth Intern (Merantix AI Campus)</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="26" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G9" s="26" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="H9" s="26" t="inlineStr">
         <is>
           <t>2026-04-15 05:03 UTC</t>
         </is>
       </c>
-      <c r="I9" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J9" s="25" t="inlineStr">
+      <c r="I9" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J9" s="28" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/growth-intern-merantix-ai-campus-at-briink-4399933254?refId=x0uIkl175n0hipT17L%2FGRw%3D%3D&amp;trackingId=qEKtyJNA03Kbr6AYDlhsBw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K9" s="23" t="inlineStr">
+      <c r="K9" s="26" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-briink-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L9" s="23" t="inlineStr">
+      <c r="L9" s="26" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-briink-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M9" s="23" t="inlineStr"/>
+      <c r="M9" s="26" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>linkedin_4400429367</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>Tata Consultancy Services</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t>HR -Data Scientist</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F10" s="26" t="inlineStr">
         <is>
           <t>Renton, WA</t>
         </is>
       </c>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G10" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H10" s="23" t="inlineStr">
+      <c r="H10" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 16:56 UTC</t>
         </is>
       </c>
-      <c r="I10" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J10" s="25" t="inlineStr">
+      <c r="I10" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J10" s="28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/hr-data-scientist-at-tata-consultancy-services-4400429367?refId=vJILgNySaXYUQknbyaKZZQ%3D%3D&amp;trackingId=7cZ0KYh8Sv5%2Fh6%2FG86%2BLug%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K10" s="23" t="inlineStr">
+      <c r="K10" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-tata-consultancy-services-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L10" s="23" t="inlineStr">
+      <c r="L10" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-tata-consultancy-services-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M10" s="23" t="inlineStr"/>
+      <c r="M10" s="26" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>linkedin_4390814627</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>Criteo</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F11" s="26" t="inlineStr">
         <is>
           <t>Barcelona, Catalonia, Spain</t>
         </is>
       </c>
-      <c r="G11" s="23" t="inlineStr">
+      <c r="G11" s="26" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H11" s="23" t="inlineStr">
+      <c r="H11" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 12:19 UTC</t>
         </is>
       </c>
-      <c r="I11" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J11" s="25" t="inlineStr">
+      <c r="I11" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J11" s="28" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/data-analyst-intern-at-criteo-4390814627?refId=PCZWvfzZIzNkx6giU9jTsA%3D%3D&amp;trackingId=T%2FMog6vtgG8P3ihAU9b1uQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K11" s="23" t="inlineStr">
+      <c r="K11" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-criteo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L11" s="23" t="inlineStr">
+      <c r="L11" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-criteo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M11" s="23" t="inlineStr"/>
+      <c r="M11" s="26" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>linkedin_4402983364</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="26" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F12" s="26" t="inlineStr">
         <is>
           <t>Brussels, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G12" s="23" t="inlineStr">
+      <c r="G12" s="26" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H12" s="23" t="inlineStr">
+      <c r="H12" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I12" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J12" s="25" t="inlineStr">
+      <c r="I12" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J12" s="28" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402983364?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=zV4sJQyNyQg%2FS%2BYm6Ba9Eg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K12" s="23" t="inlineStr">
+      <c r="K12" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L12" s="23" t="inlineStr">
+      <c r="L12" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M12" s="23" t="inlineStr"/>
+      <c r="M12" s="26" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>linkedin_4390725142</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="inlineStr">
         <is>
           <t>Boston Consulting Group (BCG)</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="26" t="inlineStr">
         <is>
           <t>Forward Deployed AI Engineer, Internship, United Kingdom - BCG X</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F13" s="26" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G13" s="23" t="inlineStr">
+      <c r="G13" s="26" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H13" s="23" t="inlineStr">
+      <c r="H13" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 16:24 UTC</t>
         </is>
       </c>
-      <c r="I13" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J13" s="25" t="inlineStr">
+      <c r="I13" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J13" s="28" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/forward-deployed-ai-engineer-internship-united-kingdom-bcg-x-at-boston-consulting-group-bcg-4390725142?refId=YHAZO5vAx9Qtg1RXMma%2F%2BA%3D%3D&amp;trackingId=E8kiSHzcdYe%2FH6s%2FCkGtMw%3D%3D&amp;position=7&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K13" s="23" t="inlineStr">
+      <c r="K13" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L13" s="23" t="inlineStr">
+      <c r="L13" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M13" s="23" t="inlineStr"/>
+      <c r="M13" s="26" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>linkedin_4400428064</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
         <is>
           <t>Fanatics</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="26" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="F14" s="26" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G14" s="23" t="inlineStr">
+      <c r="G14" s="26" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H14" s="23" t="inlineStr">
+      <c r="H14" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 16:16 UTC</t>
         </is>
       </c>
-      <c r="I14" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J14" s="25" t="inlineStr">
+      <c r="I14" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J14" s="28" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/data-scientist-at-fanatics-4400428064?refId=SNMwEp9%2FBozAkX4FBnhJwQ%3D%3D&amp;trackingId=cAX0aKWV%2FBX1fvQzm%2FkEMg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K14" s="23" t="inlineStr">
+      <c r="K14" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-fanatics-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L14" s="23" t="inlineStr">
+      <c r="L14" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-fanatics-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M14" s="23" t="inlineStr"/>
+      <c r="M14" s="26" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="26" t="inlineStr">
         <is>
           <t>linkedin_4390730090</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
         <is>
           <t>Boston Consulting Group (BCG)</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="26" t="inlineStr">
         <is>
           <t>Forward Deployed AI Scientist, Internship, United Kingdom - BCG X</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
+      <c r="F15" s="26" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G15" s="23" t="inlineStr">
+      <c r="G15" s="26" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H15" s="23" t="inlineStr">
+      <c r="H15" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 13:57 UTC</t>
         </is>
       </c>
-      <c r="I15" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J15" s="25" t="inlineStr">
+      <c r="I15" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J15" s="28" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/forward-deployed-ai-scientist-internship-united-kingdom-bcg-x-at-boston-consulting-group-bcg-4390730090?refId=YHAZO5vAx9Qtg1RXMma%2F%2BA%3D%3D&amp;trackingId=m50MzwjbYzUmAv7nJVAKgA%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K15" s="23" t="inlineStr">
+      <c r="K15" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L15" s="23" t="inlineStr">
+      <c r="L15" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M15" s="23" t="inlineStr"/>
+      <c r="M15" s="26" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>linkedin_4402138096</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="inlineStr">
         <is>
           <t>Kelly Tutors</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E16" s="26" t="inlineStr">
         <is>
           <t>Research Intern (3-5hrs/week, flexible)</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F16" s="26" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="G16" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H16" s="23" t="inlineStr">
+      <c r="H16" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 14:40 UTC</t>
         </is>
       </c>
-      <c r="I16" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J16" s="25" t="inlineStr">
+      <c r="I16" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J16" s="28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/research-intern-3-5hrs-week-flexible-at-kelly-tutors-4402138096?refId=HmOS2YEHUH3GOVent1txqw%3D%3D&amp;trackingId=3XBXMUoBdiHeRL4qw%2B2qRw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K16" s="23" t="inlineStr">
+      <c r="K16" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-kelly-tutors-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L16" s="23" t="inlineStr">
+      <c r="L16" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-kelly-tutors-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M16" s="23" t="inlineStr"/>
+      <c r="M16" s="26" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="26" t="inlineStr">
         <is>
           <t>linkedin_4378557045</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="inlineStr">
         <is>
           <t>Fund for Public Health in NYC</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="26" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="F17" s="26" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G17" s="23" t="inlineStr">
+      <c r="G17" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H17" s="23" t="inlineStr">
+      <c r="H17" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 16:13 UTC</t>
         </is>
       </c>
-      <c r="I17" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J17" s="25" t="inlineStr">
+      <c r="I17" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J17" s="28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-scientist-at-fund-for-public-health-in-nyc-4378557045?refId=JsndNRa0tnfF7dsuxv62wA%3D%3D&amp;trackingId=Pmgt6JCxYmQun5Uv6%2BLbiQ%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K17" s="23" t="inlineStr">
+      <c r="K17" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-fund-for-public-health-in-nyc-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L17" s="23" t="inlineStr">
+      <c r="L17" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-fund-for-public-health-in-nyc-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M17" s="23" t="inlineStr"/>
+      <c r="M17" s="26" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t>linkedin_4402977457</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D18" s="26" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="26" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
+      <c r="F18" s="26" t="inlineStr">
         <is>
           <t>Brussels, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G18" s="23" t="inlineStr">
+      <c r="G18" s="26" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H18" s="23" t="inlineStr">
+      <c r="H18" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I18" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J18" s="25" t="inlineStr">
+      <c r="I18" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J18" s="28" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402977457?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=gL9sbQh%2FaLMmzvXjuO71WQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K18" s="23" t="inlineStr">
+      <c r="K18" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L18" s="23" t="inlineStr">
+      <c r="L18" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M18" s="23" t="inlineStr"/>
+      <c r="M18" s="26" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="26" t="inlineStr">
         <is>
           <t>linkedin_4371210537</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="inlineStr">
         <is>
           <t>Gildan</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="26" t="inlineStr">
         <is>
           <t>Intern, ERP GenAI</t>
         </is>
       </c>
-      <c r="F19" s="23" t="inlineStr">
+      <c r="F19" s="26" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G19" s="23" t="inlineStr">
+      <c r="G19" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H19" s="23" t="inlineStr">
+      <c r="H19" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 15:23 UTC</t>
         </is>
       </c>
-      <c r="I19" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J19" s="25" t="inlineStr">
+      <c r="I19" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J19" s="28" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/intern-erp-genai-at-gildan-4371210537?refId=jteS%2Ft3Cmc2XLVMFToCpKw%3D%3D&amp;trackingId=OQGg%2Bob2m9u4kkbRcgWoUw%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K19" s="23" t="inlineStr">
+      <c r="K19" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-gildan-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L19" s="23" t="inlineStr">
+      <c r="L19" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-gildan-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M19" s="23" t="inlineStr"/>
+      <c r="M19" s="26" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t>linkedin_4402974624</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D20" s="26" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="26" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
+      <c r="F20" s="26" t="inlineStr">
         <is>
           <t>Uccle, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G20" s="23" t="inlineStr">
+      <c r="G20" s="26" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H20" s="23" t="inlineStr">
+      <c r="H20" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I20" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J20" s="25" t="inlineStr">
+      <c r="I20" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J20" s="28" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402974624?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=RJfkVsuYxv4DqyEhPJ367g%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K20" s="23" t="inlineStr">
+      <c r="K20" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L20" s="23" t="inlineStr">
+      <c r="L20" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M20" s="23" t="inlineStr"/>
+      <c r="M20" s="26" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>linkedin_4402174633</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D21" s="26" t="inlineStr">
         <is>
           <t>Cloudera</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="26" t="inlineStr">
         <is>
           <t>AI Enablement Intern (Ireland Based)</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr">
+      <c r="F21" s="26" t="inlineStr">
         <is>
           <t>Greater Dublin</t>
         </is>
       </c>
-      <c r="G21" s="23" t="inlineStr">
+      <c r="G21" s="26" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H21" s="23" t="inlineStr">
+      <c r="H21" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 18:24 UTC</t>
         </is>
       </c>
-      <c r="I21" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J21" s="25" t="inlineStr">
+      <c r="I21" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J21" s="28" t="inlineStr">
         <is>
           <t>https://ie.linkedin.com/jobs/view/ai-enablement-intern-ireland-based-at-cloudera-4402174633?refId=d9iDz5spYJk0nIor701k5g%3D%3D&amp;trackingId=6OZvFiMQ12VqIzY6EqUe7A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K21" s="23" t="inlineStr">
+      <c r="K21" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-cloudera-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L21" s="23" t="inlineStr">
+      <c r="L21" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-cloudera-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M21" s="23" t="inlineStr"/>
+      <c r="M21" s="26" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t>linkedin_4403115250</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D22" s="26" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E22" s="26" t="inlineStr">
         <is>
           <t>PhD Research Intern, Mapping Software</t>
         </is>
       </c>
-      <c r="F22" s="23" t="inlineStr">
+      <c r="F22" s="26" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G22" s="23" t="inlineStr">
+      <c r="G22" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H22" s="23" t="inlineStr">
+      <c r="H22" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 19:55 UTC</t>
         </is>
       </c>
-      <c r="I22" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J22" s="25" t="inlineStr">
+      <c r="I22" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J22" s="28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-mapping-software-at-zoox-4403115250?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=67WsHxTIXiO%2ByWr0OYU7ug%3D%3D&amp;position=10&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K22" s="23" t="inlineStr">
+      <c r="K22" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L22" s="23" t="inlineStr">
+      <c r="L22" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M22" s="23" t="inlineStr"/>
+      <c r="M22" s="26" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="23" t="inlineStr">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t>linkedin_4379373115</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D23" s="26" t="inlineStr">
         <is>
           <t>Woven by Toyota</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E23" s="26" t="inlineStr">
         <is>
           <t>Applied Scientist, Computer Vision and Generative Models, Vision AI (Internship)</t>
         </is>
       </c>
-      <c r="F23" s="23" t="inlineStr">
+      <c r="F23" s="26" t="inlineStr">
         <is>
           <t>Tokyo, Japan</t>
         </is>
       </c>
-      <c r="G23" s="23" t="inlineStr">
+      <c r="G23" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H23" s="23" t="inlineStr">
+      <c r="H23" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 14:55 UTC</t>
         </is>
       </c>
-      <c r="I23" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J23" s="25" t="inlineStr">
+      <c r="I23" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J23" s="28" t="inlineStr">
         <is>
           <t>https://jp.linkedin.com/jobs/view/applied-scientist-computer-vision-and-generative-models-vision-ai-internship-at-woven-by-toyota-4379373115?refId=4q6ISAXJ%2BcfZsJD688QZWg%3D%3D&amp;trackingId=pUnO9OuzZx4G6BOukom%2FQQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K23" s="23" t="inlineStr">
+      <c r="K23" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-woven-by-toyota-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L23" s="23" t="inlineStr">
+      <c r="L23" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-woven-by-toyota-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M23" s="23" t="inlineStr"/>
+      <c r="M23" s="26" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t>linkedin_4325103488</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D24" s="26" t="inlineStr">
         <is>
           <t>Binance</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E24" s="26" t="inlineStr">
         <is>
           <t>Binance Accelerator Program - DevOps (Artificial Intelligence)</t>
         </is>
       </c>
-      <c r="F24" s="23" t="inlineStr">
+      <c r="F24" s="26" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G24" s="23" t="inlineStr">
+      <c r="G24" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H24" s="23" t="inlineStr">
+      <c r="H24" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 12:13 UTC</t>
         </is>
       </c>
-      <c r="I24" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J24" s="25" t="inlineStr">
+      <c r="I24" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J24" s="28" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/binance-accelerator-program-devops-artificial-intelligence-at-binance-4325103488?refId=KzaD5RMOfYQEZyaw6UmcpQ%3D%3D&amp;trackingId=8R4okHiG3RYyjThXHAqxIQ%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K24" s="23" t="inlineStr">
+      <c r="K24" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-binance-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L24" s="23" t="inlineStr">
+      <c r="L24" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-binance-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M24" s="23" t="inlineStr"/>
+      <c r="M24" s="26" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="23" t="inlineStr">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t>linkedin_4400563251</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D25" s="23" t="inlineStr">
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D25" s="26" t="inlineStr">
         <is>
           <t>Aylo</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E25" s="26" t="inlineStr">
         <is>
           <t>Sr. Full-Stack Data Scientist - Data Services</t>
         </is>
       </c>
-      <c r="F25" s="23" t="inlineStr">
+      <c r="F25" s="26" t="inlineStr">
         <is>
           <t>Greater Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G25" s="23" t="inlineStr">
+      <c r="G25" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H25" s="23" t="inlineStr">
+      <c r="H25" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 12:01 UTC</t>
         </is>
       </c>
-      <c r="I25" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J25" s="25" t="inlineStr">
+      <c r="I25" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J25" s="28" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/sr-full-stack-data-scientist-data-services-at-aylo-4400563251?refId=3X2hsLwn0XF5%2BC4ABneEzA%3D%3D&amp;trackingId=aJHp5psMKfAaMJdxBAz5Hw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K25" s="23" t="inlineStr">
+      <c r="K25" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-aylo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L25" s="23" t="inlineStr">
+      <c r="L25" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-aylo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M25" s="23" t="inlineStr"/>
+      <c r="M25" s="26" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t>linkedin_4400403670</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
         <is>
           <t>Schneider Electric</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E26" s="26" t="inlineStr">
         <is>
           <t>Internship in Global AI Sales Enablement &amp; Analytics</t>
         </is>
       </c>
-      <c r="F26" s="23" t="inlineStr">
+      <c r="F26" s="26" t="inlineStr">
         <is>
           <t>Warsaw, Mazowieckie, Poland</t>
         </is>
       </c>
-      <c r="G26" s="23" t="inlineStr">
+      <c r="G26" s="26" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H26" s="23" t="inlineStr">
+      <c r="H26" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 11:43 UTC</t>
         </is>
       </c>
-      <c r="I26" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J26" s="25" t="inlineStr">
+      <c r="I26" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J26" s="28" t="inlineStr">
         <is>
           <t>https://pl.linkedin.com/jobs/view/internship-in-global-ai-sales-enablement-analytics-at-schneider-electric-4400403670?refId=0j6PfgagLJw81v3dQ49jXQ%3D%3D&amp;trackingId=ErR9yiUH1tcny4hRKbXl8A%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K26" s="23" t="inlineStr">
+      <c r="K26" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-schneider-electric-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L26" s="23" t="inlineStr">
+      <c r="L26" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-schneider-electric-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M26" s="23" t="inlineStr"/>
+      <c r="M26" s="26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="23" t="inlineStr">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>linkedin_4297755027</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="inlineStr">
         <is>
           <t>Databricks</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E27" s="26" t="inlineStr">
         <is>
           <t>PhD GenAI Research Scientist Intern</t>
         </is>
       </c>
-      <c r="F27" s="23" t="inlineStr">
+      <c r="F27" s="26" t="inlineStr">
         <is>
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="G27" s="23" t="inlineStr">
+      <c r="G27" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H27" s="23" t="inlineStr">
+      <c r="H27" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 10:31 UTC</t>
         </is>
       </c>
-      <c r="I27" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J27" s="25" t="inlineStr">
+      <c r="I27" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J27" s="28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-genai-research-scientist-intern-at-databricks-4297755027?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=UXoh9K97xsqO%2FzDhCy7Uug%3D%3D&amp;position=8&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K27" s="23" t="inlineStr">
+      <c r="K27" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-databricks-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L27" s="23" t="inlineStr">
+      <c r="L27" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-databricks-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M27" s="23" t="inlineStr"/>
+      <c r="M27" s="26" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="23" t="inlineStr">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>linkedin_4401843829</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D28" s="26" t="inlineStr">
         <is>
           <t>Tiger Brokers Singapore</t>
         </is>
       </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E28" s="26" t="inlineStr">
         <is>
           <t>Quantitative Investment Analyst Intern</t>
         </is>
       </c>
-      <c r="F28" s="23" t="inlineStr">
+      <c r="F28" s="26" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G28" s="23" t="inlineStr">
+      <c r="G28" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H28" s="23" t="inlineStr">
+      <c r="H28" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 06:09 UTC</t>
         </is>
       </c>
-      <c r="I28" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J28" s="25" t="inlineStr">
+      <c r="I28" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J28" s="28" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/quantitative-investment-analyst-intern-at-tiger-brokers-singapore-4401843829?refId=LJ4PwcXqLhd1gtOBe9ZVig%3D%3D&amp;trackingId=oxh8Ol2m1QKvqfrvl10UqA%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K28" s="23" t="inlineStr">
+      <c r="K28" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-tiger-brokers-singapore-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L28" s="23" t="inlineStr">
+      <c r="L28" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-tiger-brokers-singapore-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M28" s="23" t="inlineStr"/>
+      <c r="M28" s="26" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t>linkedin_4400148847</t>
         </is>
       </c>
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B29" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C29" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D29" s="23" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D29" s="26" t="inlineStr">
         <is>
           <t>Boomlet</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E29" s="26" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F29" s="23" t="inlineStr">
+      <c r="F29" s="26" t="inlineStr">
         <is>
           <t>Mumbai, Maharashtra, India</t>
         </is>
       </c>
-      <c r="G29" s="23" t="inlineStr">
+      <c r="G29" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H29" s="23" t="inlineStr">
+      <c r="H29" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 05:24 UTC</t>
         </is>
       </c>
-      <c r="I29" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J29" s="25" t="inlineStr">
+      <c r="I29" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J29" s="28" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-boomlet-4400148847?refId=vAgiKqchg4pd6EgGGQ%2FF%2FA%3D%3D&amp;trackingId=IoHiSd1L28nXXarEd4gYfw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K29" s="23" t="inlineStr">
+      <c r="K29" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boomlet-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L29" s="23" t="inlineStr">
+      <c r="L29" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boomlet-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M29" s="23" t="inlineStr"/>
+      <c r="M29" s="26" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="23" t="inlineStr">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>linkedin_4401844394</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D30" s="26" t="inlineStr">
         <is>
           <t>On-us</t>
         </is>
       </c>
-      <c r="E30" s="23" t="inlineStr">
+      <c r="E30" s="26" t="inlineStr">
         <is>
           <t>AI Business Analyst Summer Intern</t>
         </is>
       </c>
-      <c r="F30" s="23" t="inlineStr">
+      <c r="F30" s="26" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G30" s="23" t="inlineStr">
+      <c r="G30" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H30" s="23" t="inlineStr">
+      <c r="H30" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 04:56 UTC</t>
         </is>
       </c>
-      <c r="I30" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J30" s="25" t="inlineStr">
+      <c r="I30" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J30" s="28" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/ai-business-analyst-summer-intern-at-on-us-4401844394?refId=lslydLUu5l8kXOktysXYaw%3D%3D&amp;trackingId=BQ%2BoYgH5QtZKBWGZQgBfNQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K30" s="23" t="inlineStr">
+      <c r="K30" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-on-us-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L30" s="23" t="inlineStr">
+      <c r="L30" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-on-us-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M30" s="23" t="inlineStr"/>
+      <c r="M30" s="26" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="23" t="inlineStr">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t>linkedin_4401837715</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D31" s="23" t="inlineStr">
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D31" s="26" t="inlineStr">
         <is>
           <t>Pathos Consultancy</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E31" s="26" t="inlineStr">
         <is>
           <t>Quantitative Research &amp; Development Internships</t>
         </is>
       </c>
-      <c r="F31" s="23" t="inlineStr">
+      <c r="F31" s="26" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G31" s="23" t="inlineStr">
+      <c r="G31" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H31" s="23" t="inlineStr">
+      <c r="H31" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 03:48 UTC</t>
         </is>
       </c>
-      <c r="I31" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J31" s="25" t="inlineStr">
+      <c r="I31" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J31" s="28" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/quantitative-research-development-internships-at-pathos-consultancy-4401837715?refId=KzaD5RMOfYQEZyaw6UmcpQ%3D%3D&amp;trackingId=eIGVr2dDtK%2F1o37C90xRoQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K31" s="23" t="inlineStr">
+      <c r="K31" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-pathos-consultancy-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L31" s="23" t="inlineStr">
+      <c r="L31" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-pathos-consultancy-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M31" s="23" t="inlineStr"/>
+      <c r="M31" s="26" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="23" t="inlineStr">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t>linkedin_4402662606</t>
         </is>
       </c>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="B32" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C32" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D32" s="26" t="inlineStr">
         <is>
           <t>Stripe</t>
         </is>
       </c>
-      <c r="E32" s="23" t="inlineStr">
+      <c r="E32" s="26" t="inlineStr">
         <is>
           <t>PhD Machine Learning Engineer, Intern</t>
         </is>
       </c>
-      <c r="F32" s="23" t="inlineStr">
+      <c r="F32" s="26" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G32" s="23" t="inlineStr">
+      <c r="G32" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H32" s="23" t="inlineStr">
+      <c r="H32" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 02:23 UTC</t>
         </is>
       </c>
-      <c r="I32" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J32" s="25" t="inlineStr">
+      <c r="I32" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J32" s="28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-machine-learning-engineer-intern-at-stripe-4402662606?refId=vJILgNySaXYUQknbyaKZZQ%3D%3D&amp;trackingId=NDMzaPfHMoCKo5uxI3THcw%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K32" s="23" t="inlineStr">
+      <c r="K32" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L32" s="23" t="inlineStr">
+      <c r="L32" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M32" s="23" t="inlineStr"/>
+      <c r="M32" s="26" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="23" t="inlineStr">
+      <c r="A33" s="26" t="inlineStr">
         <is>
           <t>linkedin_4402953925</t>
         </is>
       </c>
-      <c r="B33" s="23" t="inlineStr">
+      <c r="B33" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C33" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D33" s="23" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D33" s="26" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="E33" s="26" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F33" s="23" t="inlineStr">
+      <c r="F33" s="26" t="inlineStr">
         <is>
           <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
-      <c r="G33" s="23" t="inlineStr">
+      <c r="G33" s="26" t="inlineStr">
         <is>
           <t>Middle_East</t>
         </is>
       </c>
-      <c r="H33" s="23" t="inlineStr">
+      <c r="H33" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 00:00 UTC</t>
         </is>
       </c>
-      <c r="I33" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J33" s="25" t="inlineStr">
+      <c r="I33" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J33" s="28" t="inlineStr">
         <is>
           <t>https://ae.linkedin.com/jobs/view/research-intern-at-skycliff-it-4402953925?refId=f%2BmSR6Ncm83dISKgoQTrbw%3D%3D&amp;trackingId=CdPOXElDD3wJKKeBZSdWsw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K33" s="23" t="inlineStr">
+      <c r="K33" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L33" s="23" t="inlineStr">
+      <c r="L33" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M33" s="23" t="inlineStr"/>
+      <c r="M33" s="26" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="23" t="inlineStr">
+      <c r="A34" s="26" t="inlineStr">
         <is>
           <t>linkedin_4402617206</t>
         </is>
       </c>
-      <c r="B34" s="23" t="inlineStr">
+      <c r="B34" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C34" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D34" s="23" t="inlineStr">
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D34" s="26" t="inlineStr">
         <is>
           <t>Stripe</t>
         </is>
       </c>
-      <c r="E34" s="23" t="inlineStr">
+      <c r="E34" s="26" t="inlineStr">
         <is>
           <t>PhD Machine Learning Engineer, Intern</t>
         </is>
       </c>
-      <c r="F34" s="23" t="inlineStr">
+      <c r="F34" s="26" t="inlineStr">
         <is>
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="G34" s="23" t="inlineStr">
+      <c r="G34" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H34" s="23" t="inlineStr">
+      <c r="H34" s="26" t="inlineStr">
         <is>
           <t>2026-04-15 20:25 UTC</t>
         </is>
       </c>
-      <c r="I34" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J34" s="25" t="inlineStr">
+      <c r="I34" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J34" s="28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-machine-learning-engineer-intern-at-stripe-4402617206?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=yAc4U29LYJcrlQSUWWcubA%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K34" s="23" t="inlineStr">
+      <c r="K34" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L34" s="23" t="inlineStr">
+      <c r="L34" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M34" s="23" t="inlineStr"/>
+      <c r="M34" s="26" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="23" t="inlineStr">
+      <c r="A35" s="26" t="inlineStr">
         <is>
           <t>linkedin_4403183407</t>
         </is>
       </c>
-      <c r="B35" s="23" t="inlineStr">
+      <c r="B35" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C35" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D35" s="23" t="inlineStr">
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D35" s="26" t="inlineStr">
         <is>
           <t>Hardware FYI</t>
         </is>
       </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="E35" s="26" t="inlineStr">
         <is>
           <t>Robotics - Applied Scientist II Intern / Co-op - 2026 (Robotics, Manipulation, Perception, Motion Planning, Autonomous Mobile Robots, Computer Vision, Machine Learning, Controls, and more)</t>
         </is>
       </c>
-      <c r="F35" s="23" t="inlineStr">
+      <c r="F35" s="26" t="inlineStr">
         <is>
           <t>Boston, MA</t>
         </is>
       </c>
-      <c r="G35" s="23" t="inlineStr">
+      <c r="G35" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H35" s="23" t="inlineStr">
+      <c r="H35" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 04:31 UTC</t>
         </is>
       </c>
-      <c r="I35" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J35" s="25" t="inlineStr">
+      <c r="I35" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J35" s="28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/robotics-applied-scientist-ii-intern-co-op-2026-robotics-manipulation-perception-motion-planning-autonomous-mobile-robots-computer-vision-machine-learning-controls-and-more-at-hardware-fyi-4403183407?refId=s5WxXRPJ8QU7G2WPi2yNiw%3D%3D&amp;trackingId=rjd%2F8qdM5kQMmADtGJgSSw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K35" s="23" t="inlineStr">
+      <c r="K35" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-hardware-fyi-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L35" s="23" t="inlineStr">
+      <c r="L35" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-hardware-fyi-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M35" s="23" t="inlineStr"/>
+      <c r="M35" s="26" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="23" t="inlineStr">
+      <c r="A36" s="26" t="inlineStr">
         <is>
           <t>linkedin_4403153262</t>
         </is>
       </c>
-      <c r="B36" s="23" t="inlineStr">
+      <c r="B36" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C36" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D36" s="23" t="inlineStr">
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D36" s="26" t="inlineStr">
         <is>
           <t>Generali Malaysia</t>
         </is>
       </c>
-      <c r="E36" s="23" t="inlineStr">
+      <c r="E36" s="26" t="inlineStr">
         <is>
           <t>Intern, IT (AI Engineering)</t>
         </is>
       </c>
-      <c r="F36" s="23" t="inlineStr">
+      <c r="F36" s="26" t="inlineStr">
         <is>
           <t>Federal Territory of Kuala Lumpur, Malaysia</t>
         </is>
       </c>
-      <c r="G36" s="23" t="inlineStr">
+      <c r="G36" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H36" s="23" t="inlineStr">
+      <c r="H36" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 00:47 UTC</t>
         </is>
       </c>
-      <c r="I36" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J36" s="25" t="inlineStr">
+      <c r="I36" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J36" s="28" t="inlineStr">
         <is>
           <t>https://my.linkedin.com/jobs/view/intern-it-ai-engineering-at-generali-malaysia-4403153262?refId=h4J9hFjDRjjPW7bUqRcUZQ%3D%3D&amp;trackingId=WmqITEtGX486sbNH6b%2BYmA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K36" s="23" t="inlineStr">
+      <c r="K36" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-generali-malaysia-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L36" s="23" t="inlineStr">
+      <c r="L36" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-generali-malaysia-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M36" s="23" t="inlineStr"/>
+      <c r="M36" s="26" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="23" t="inlineStr">
+      <c r="A37" s="26" t="inlineStr">
         <is>
           <t>linkedin_4402311007</t>
         </is>
       </c>
-      <c r="B37" s="23" t="inlineStr">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C37" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D37" s="23" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D37" s="26" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="E37" s="26" t="inlineStr">
         <is>
           <t>SAP iXp Intern - Customer Success Engineering, Operations &amp; AI Enablement [Boston]</t>
         </is>
       </c>
-      <c r="F37" s="23" t="inlineStr">
+      <c r="F37" s="26" t="inlineStr">
         <is>
           <t>Burlington, MA</t>
         </is>
       </c>
-      <c r="G37" s="23" t="inlineStr">
+      <c r="G37" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H37" s="23" t="inlineStr">
+      <c r="H37" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 21:40 UTC</t>
         </is>
       </c>
-      <c r="I37" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J37" s="25" t="inlineStr">
+      <c r="I37" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J37" s="28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/sap-ixp-intern-%C2%A0customer-success-engineering-operations-ai-enablement-boston-at-sap-4402311007?refId=ofb0jzd8xWUoUtvr7A%2BwXQ%3D%3D&amp;trackingId=S%2Fo4FvRdeOcn00Jo5DVUBw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K37" s="23" t="inlineStr">
+      <c r="K37" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L37" s="23" t="inlineStr">
+      <c r="L37" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M37" s="23" t="inlineStr"/>
+      <c r="M37" s="26" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="23" t="inlineStr">
+      <c r="A38" s="26" t="inlineStr">
         <is>
           <t>linkedin_4403154707</t>
         </is>
       </c>
-      <c r="B38" s="23" t="inlineStr">
+      <c r="B38" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C38" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D38" s="23" t="inlineStr">
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D38" s="26" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E38" s="23" t="inlineStr">
+      <c r="E38" s="26" t="inlineStr">
         <is>
           <t>Software Engineer Intern, Perception Data</t>
         </is>
       </c>
-      <c r="F38" s="23" t="inlineStr">
+      <c r="F38" s="26" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G38" s="23" t="inlineStr">
+      <c r="G38" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H38" s="23" t="inlineStr">
+      <c r="H38" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 02:21 UTC</t>
         </is>
       </c>
-      <c r="I38" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J38" s="25" t="inlineStr">
+      <c r="I38" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J38" s="28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/software-engineer-intern-perception-data-at-zoox-4403154707?refId=ON4L5FUhksKAgylRRsNllQ%3D%3D&amp;trackingId=1%2F3OkqP%2Bu0PqHp9bXnlS0A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K38" s="23" t="inlineStr">
+      <c r="K38" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L38" s="23" t="inlineStr">
+      <c r="L38" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M38" s="23" t="inlineStr"/>
+      <c r="M38" s="26" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="23" t="inlineStr">
+      <c r="A39" s="26" t="inlineStr">
         <is>
           <t>linkedin_4402947451</t>
         </is>
       </c>
-      <c r="B39" s="23" t="inlineStr">
+      <c r="B39" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C39" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D39" s="23" t="inlineStr">
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D39" s="26" t="inlineStr">
         <is>
           <t>Rubrik</t>
         </is>
       </c>
-      <c r="E39" s="23" t="inlineStr">
+      <c r="E39" s="26" t="inlineStr">
         <is>
           <t>India Benefits &amp; AI Operations Intern</t>
         </is>
       </c>
-      <c r="F39" s="23" t="inlineStr">
+      <c r="F39" s="26" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G39" s="23" t="inlineStr">
+      <c r="G39" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H39" s="23" t="inlineStr">
+      <c r="H39" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 11:40 UTC</t>
         </is>
       </c>
-      <c r="I39" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J39" s="25" t="inlineStr">
+      <c r="I39" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J39" s="28" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/india-benefits-ai-operations-intern-at-rubrik-4402947451?refId=9u2uyUYzyMZimaTtDELDWg%3D%3D&amp;trackingId=BjOmyeYm6McmUpzLwcES9g%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K39" s="23" t="inlineStr">
+      <c r="K39" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-rubrik-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L39" s="23" t="inlineStr">
+      <c r="L39" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-rubrik-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M39" s="23" t="inlineStr"/>
+      <c r="M39" s="26" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="23" t="inlineStr">
+      <c r="A40" s="26" t="inlineStr">
         <is>
           <t>linkedin_4390354006</t>
         </is>
       </c>
-      <c r="B40" s="23" t="inlineStr">
+      <c r="B40" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C40" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D40" s="23" t="inlineStr">
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="inlineStr">
         <is>
           <t>Lila Sciences</t>
         </is>
       </c>
-      <c r="E40" s="23" t="inlineStr">
+      <c r="E40" s="26" t="inlineStr">
         <is>
           <t>Intern, Next Gen AI Robotics</t>
         </is>
       </c>
-      <c r="F40" s="23" t="inlineStr">
+      <c r="F40" s="26" t="inlineStr">
         <is>
           <t>Cambridge, MA</t>
         </is>
       </c>
-      <c r="G40" s="23" t="inlineStr">
+      <c r="G40" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H40" s="23" t="inlineStr">
+      <c r="H40" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 10:58 UTC</t>
         </is>
       </c>
-      <c r="I40" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J40" s="25" t="inlineStr">
+      <c r="I40" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J40" s="28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/intern-next-gen-ai-robotics-at-lila-sciences-4390354006?refId=ZoXJQXesL%2FE%2B5EAGGzWfiA%3D%3D&amp;trackingId=FmSMwWhyyIaC52NsDwOCtw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K40" s="23" t="inlineStr">
+      <c r="K40" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-lila-sciences-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L40" s="23" t="inlineStr">
+      <c r="L40" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-lila-sciences-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M40" s="23" t="inlineStr"/>
+      <c r="M40" s="26" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="23" t="inlineStr">
+      <c r="A41" s="26" t="inlineStr">
         <is>
           <t>arbeitnow_ai-venture-development-tech-intern-berlin-100382</t>
         </is>
       </c>
-      <c r="B41" s="23" t="inlineStr">
+      <c r="B41" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C41" s="23" t="inlineStr">
+      <c r="C41" s="26" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="D41" s="23" t="inlineStr">
+      <c r="D41" s="26" t="inlineStr">
         <is>
           <t>Zeeg</t>
         </is>
       </c>
-      <c r="E41" s="23" t="inlineStr">
+      <c r="E41" s="26" t="inlineStr">
         <is>
           <t>AI &amp; Venture Development Tech Intern (w/m/d)</t>
         </is>
       </c>
-      <c r="F41" s="23" t="inlineStr">
+      <c r="F41" s="26" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="G41" s="23" t="inlineStr">
+      <c r="G41" s="26" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H41" s="23" t="inlineStr">
+      <c r="H41" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 10:30 UTC</t>
         </is>
       </c>
-      <c r="I41" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J41" s="25" t="inlineStr">
+      <c r="I41" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J41" s="28" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/zeeg/ai-venture-development-tech-intern-berlin-100382</t>
         </is>
       </c>
-      <c r="K41" s="23" t="inlineStr">
+      <c r="K41" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zeeg-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L41" s="23" t="inlineStr">
+      <c r="L41" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zeeg-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M41" s="23" t="inlineStr"/>
+      <c r="M41" s="26" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="23" t="inlineStr">
+      <c r="A42" s="26" t="inlineStr">
         <is>
           <t>linkedin_4391388054</t>
         </is>
       </c>
-      <c r="B42" s="23" t="inlineStr">
+      <c r="B42" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C42" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D42" s="23" t="inlineStr">
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D42" s="26" t="inlineStr">
         <is>
           <t>Mackenzie Investments</t>
         </is>
       </c>
-      <c r="E42" s="23" t="inlineStr">
+      <c r="E42" s="26" t="inlineStr">
         <is>
           <t>Fall Intern 2026 - Data Science (Toronto Office)</t>
         </is>
       </c>
-      <c r="F42" s="23" t="inlineStr">
+      <c r="F42" s="26" t="inlineStr">
         <is>
           <t>Greater Toronto Area, Canada</t>
         </is>
       </c>
-      <c r="G42" s="23" t="inlineStr">
+      <c r="G42" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H42" s="23" t="inlineStr">
+      <c r="H42" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 14:00 UTC</t>
         </is>
       </c>
-      <c r="I42" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J42" s="25" t="inlineStr">
+      <c r="I42" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J42" s="28" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/fall-intern-2026-data-science-toronto-office-at-mackenzie-investments-4391388054?refId=ay8O%2Bgf7Gtfb1Rpr3XZOhg%3D%3D&amp;trackingId=O%2F%2FJTpCmUhvp4jSfNkV5bg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K42" s="23" t="inlineStr">
+      <c r="K42" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-mackenzie-investments-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L42" s="23" t="inlineStr">
+      <c r="L42" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-mackenzie-investments-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M42" s="23" t="inlineStr"/>
+      <c r="M42" s="26" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="23" t="inlineStr">
+      <c r="A43" s="26" t="inlineStr">
         <is>
           <t>linkedin_4390747937</t>
         </is>
       </c>
-      <c r="B43" s="23" t="inlineStr">
+      <c r="B43" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C43" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D43" s="23" t="inlineStr">
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D43" s="26" t="inlineStr">
         <is>
           <t>BCG X</t>
         </is>
       </c>
-      <c r="E43" s="23" t="inlineStr">
+      <c r="E43" s="26" t="inlineStr">
         <is>
           <t>Visiting Forward Deployed AI Engineer, Internship, Germany - BCG X</t>
         </is>
       </c>
-      <c r="F43" s="23" t="inlineStr">
+      <c r="F43" s="26" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G43" s="23" t="inlineStr">
+      <c r="G43" s="26" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H43" s="23" t="inlineStr">
+      <c r="H43" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 13:51 UTC</t>
         </is>
       </c>
-      <c r="I43" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J43" s="25" t="inlineStr">
+      <c r="I43" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J43" s="28" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/visiting-forward-deployed-ai-engineer-internship-germany-bcg-x-at-bcg-x-4390747937?refId=1JxxxPqdlRpkbbaCzu2YGQ%3D%3D&amp;trackingId=7x%2BVQU%2BWOh9IPaVXWJkc5g%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K43" s="23" t="inlineStr">
+      <c r="K43" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bcg-x-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L43" s="23" t="inlineStr">
+      <c r="L43" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bcg-x-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M43" s="23" t="inlineStr"/>
+      <c r="M43" s="26" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="23" t="inlineStr">
+      <c r="A44" s="26" t="inlineStr">
         <is>
           <t>linkedin_4402726053</t>
         </is>
       </c>
-      <c r="B44" s="23" t="inlineStr">
+      <c r="B44" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C44" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D44" s="23" t="inlineStr">
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D44" s="26" t="inlineStr">
         <is>
           <t>targetjobs UK</t>
         </is>
       </c>
-      <c r="E44" s="23" t="inlineStr">
+      <c r="E44" s="26" t="inlineStr">
         <is>
           <t>Internship: AI/ML for Ionospheric TEC Modelling</t>
         </is>
       </c>
-      <c r="F44" s="23" t="inlineStr">
+      <c r="F44" s="26" t="inlineStr">
         <is>
           <t>Reigate, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G44" s="23" t="inlineStr">
+      <c r="G44" s="26" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H44" s="23" t="inlineStr">
+      <c r="H44" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 14:25 UTC</t>
         </is>
       </c>
-      <c r="I44" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J44" s="25" t="inlineStr">
+      <c r="I44" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J44" s="28" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/internship-ai-ml-for-ionospheric-tec-modelling-at-targetjobs-uk-4402726053?refId=a1g6hMZsvI1y2Eje2OvLAA%3D%3D&amp;trackingId=IVJSJGE7Non8cohorDs%2F5A%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K44" s="23" t="inlineStr">
+      <c r="K44" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-targetjobs-uk-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L44" s="23" t="inlineStr">
+      <c r="L44" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-targetjobs-uk-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M44" s="23" t="inlineStr"/>
+      <c r="M44" s="26" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="23" t="inlineStr">
+      <c r="A45" s="26" t="inlineStr">
         <is>
           <t>linkedin_4400837114</t>
         </is>
       </c>
-      <c r="B45" s="23" t="inlineStr">
+      <c r="B45" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C45" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D45" s="23" t="inlineStr">
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D45" s="26" t="inlineStr">
         <is>
           <t>Innovexis</t>
         </is>
       </c>
-      <c r="E45" s="23" t="inlineStr">
+      <c r="E45" s="26" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F45" s="23" t="inlineStr">
+      <c r="F45" s="26" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G45" s="23" t="inlineStr">
+      <c r="G45" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H45" s="23" t="inlineStr">
+      <c r="H45" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 13:04 UTC</t>
         </is>
       </c>
-      <c r="I45" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J45" s="25" t="inlineStr">
+      <c r="I45" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J45" s="28" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-innovexis-4400837114?refId=CVM89%2F3%2F%2BshqMJLc4IfFMg%3D%3D&amp;trackingId=j9WpQwI4k1ip7aRr%2Fv5Img%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K45" s="23" t="inlineStr">
+      <c r="K45" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-innovexis-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L45" s="23" t="inlineStr">
+      <c r="L45" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-innovexis-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M45" s="23" t="inlineStr"/>
+      <c r="M45" s="26" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="23" t="inlineStr">
+      <c r="A46" s="26" t="inlineStr">
         <is>
           <t>linkedin_4391074158</t>
         </is>
       </c>
-      <c r="B46" s="23" t="inlineStr">
+      <c r="B46" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C46" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D46" s="23" t="inlineStr">
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D46" s="26" t="inlineStr">
         <is>
           <t>BMW Group</t>
         </is>
       </c>
-      <c r="E46" s="23" t="inlineStr">
+      <c r="E46" s="26" t="inlineStr">
         <is>
           <t>Intern IT Technology, Sales Volume Planning &amp; AI Support (f/m/x)</t>
         </is>
       </c>
-      <c r="F46" s="23" t="inlineStr">
+      <c r="F46" s="26" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G46" s="23" t="inlineStr">
+      <c r="G46" s="26" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H46" s="23" t="inlineStr">
+      <c r="H46" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 12:45 UTC</t>
         </is>
       </c>
-      <c r="I46" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J46" s="25" t="inlineStr">
+      <c r="I46" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J46" s="28" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/intern-it-technology-sales-volume-planning-ai-support-f-m-x-at-bmw-group-4391074158?refId=tHG5EqbLn3IDBqsSj%2FsUUg%3D%3D&amp;trackingId=OakOlgDcU0hWTRXcoLe3UA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K46" s="23" t="inlineStr">
+      <c r="K46" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bmw-group-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L46" s="23" t="inlineStr">
+      <c r="L46" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bmw-group-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M46" s="23" t="inlineStr"/>
+      <c r="M46" s="26" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="23" t="inlineStr">
+      <c r="A47" s="26" t="inlineStr">
         <is>
           <t>linkedin_4402725075</t>
         </is>
       </c>
-      <c r="B47" s="23" t="inlineStr">
+      <c r="B47" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C47" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D47" s="23" t="inlineStr">
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="inlineStr">
         <is>
           <t>DARE</t>
         </is>
       </c>
-      <c r="E47" s="23" t="inlineStr">
+      <c r="E47" s="26" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F47" s="23" t="inlineStr">
+      <c r="F47" s="26" t="inlineStr">
         <is>
           <t>WP. Kuala Lumpur, Federal Territory of Kuala Lumpur, Malaysia</t>
         </is>
       </c>
-      <c r="G47" s="23" t="inlineStr">
+      <c r="G47" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H47" s="23" t="inlineStr">
+      <c r="H47" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 14:36 UTC</t>
         </is>
       </c>
-      <c r="I47" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J47" s="25" t="inlineStr">
+      <c r="I47" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J47" s="28" t="inlineStr">
         <is>
           <t>https://my.linkedin.com/jobs/view/research-intern-at-dare-4402725075?refId=xbzZXyF6FfcYy036eklDWw%3D%3D&amp;trackingId=QRt5DhbLSINvmHia0jEWIg%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K47" s="23" t="inlineStr">
+      <c r="K47" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dare-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L47" s="23" t="inlineStr">
+      <c r="L47" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dare-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M47" s="23" t="inlineStr"/>
+      <c r="M47" s="26" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="23" t="inlineStr">
+      <c r="A48" s="26" t="inlineStr">
         <is>
           <t>linkedin_4402745391</t>
         </is>
       </c>
-      <c r="B48" s="23" t="inlineStr">
+      <c r="B48" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C48" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D48" s="23" t="inlineStr">
+      <c r="C48" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D48" s="26" t="inlineStr">
         <is>
           <t>Huawei Technologies Research &amp; Development (UK) Ltd</t>
         </is>
       </c>
-      <c r="E48" s="23" t="inlineStr">
+      <c r="E48" s="26" t="inlineStr">
         <is>
           <t>Research Intern - Computer Vision</t>
         </is>
       </c>
-      <c r="F48" s="23" t="inlineStr">
+      <c r="F48" s="26" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G48" s="23" t="inlineStr">
+      <c r="G48" s="26" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H48" s="23" t="inlineStr">
+      <c r="H48" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 18:42 UTC</t>
         </is>
       </c>
-      <c r="I48" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J48" s="25" t="inlineStr">
+      <c r="I48" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J48" s="28" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/research-intern-computer-vision-at-huawei-technologies-research-development-uk-ltd-4402745391?refId=rRtCMQFBU%2FNi7vc62x5Nhg%3D%3D&amp;trackingId=%2Bt1We%2BmKhWHyXION%2FWwQVg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K48" s="23" t="inlineStr">
+      <c r="K48" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-huawei-technologies-research-development-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L48" s="23" t="inlineStr">
+      <c r="L48" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-huawei-technologies-research-development-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M48" s="23" t="inlineStr"/>
+      <c r="M48" s="26" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="23" t="inlineStr">
+      <c r="A49" s="26" t="inlineStr">
         <is>
           <t>linkedin_4402366780</t>
         </is>
       </c>
-      <c r="B49" s="23" t="inlineStr">
+      <c r="B49" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C49" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D49" s="23" t="inlineStr">
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D49" s="26" t="inlineStr">
         <is>
           <t>Binance</t>
         </is>
       </c>
-      <c r="E49" s="23" t="inlineStr">
+      <c r="E49" s="26" t="inlineStr">
         <is>
           <t>Binance Accelerator Program - Data Scientist (LLM &amp; Trading)</t>
         </is>
       </c>
-      <c r="F49" s="23" t="inlineStr">
+      <c r="F49" s="26" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G49" s="23" t="inlineStr">
+      <c r="G49" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H49" s="23" t="inlineStr">
+      <c r="H49" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 09:43 UTC</t>
         </is>
       </c>
-      <c r="I49" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J49" s="25" t="inlineStr">
+      <c r="I49" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J49" s="28" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/binance-accelerator-program-data-scientist-llm-trading-at-binance-4402366780?refId=bc%2BXeBTeIKMQJTmlLFwbZQ%3D%3D&amp;trackingId=9UuyRRCEPapWNu6VKdZC5A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K49" s="23" t="inlineStr">
+      <c r="K49" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-binance-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L49" s="23" t="inlineStr">
+      <c r="L49" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-binance-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M49" s="23" t="inlineStr"/>
+      <c r="M49" s="26" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="23" t="inlineStr">
+      <c r="A50" s="26" t="inlineStr">
         <is>
           <t>linkedin_4382411039</t>
         </is>
       </c>
-      <c r="B50" s="23" t="inlineStr">
+      <c r="B50" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C50" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D50" s="23" t="inlineStr">
+      <c r="C50" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D50" s="26" t="inlineStr">
         <is>
           <t>The Walt Disney Company</t>
         </is>
       </c>
-      <c r="E50" s="23" t="inlineStr">
+      <c r="E50" s="26" t="inlineStr">
         <is>
           <t>Intern, APAC Data Analytics &amp; Insights (Content Analytics) -  Jul to Dec 2026</t>
         </is>
       </c>
-      <c r="F50" s="23" t="inlineStr">
+      <c r="F50" s="26" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G50" s="23" t="inlineStr">
+      <c r="G50" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H50" s="23" t="inlineStr">
+      <c r="H50" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 23:55 UTC</t>
         </is>
       </c>
-      <c r="I50" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J50" s="25" t="inlineStr">
+      <c r="I50" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J50" s="28" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/intern-apac-data-analytics-insights-content-analytics-jul-to-dec-2026-at-the-walt-disney-company-4382411039?refId=JBvXH2fNOamnO4WZI1Y0ew%3D%3D&amp;trackingId=Rs%2FdjczlbLYSYtCwY%2F%2FJyA%3D%3D&amp;position=7&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K50" s="23" t="inlineStr">
+      <c r="K50" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-the-walt-disney-company-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L50" s="23" t="inlineStr">
+      <c r="L50" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-the-walt-disney-company-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M50" s="23" t="inlineStr"/>
+      <c r="M50" s="26" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="23" t="inlineStr">
+      <c r="A51" s="26" t="inlineStr">
         <is>
           <t>linkedin_4402305263</t>
         </is>
       </c>
-      <c r="B51" s="23" t="inlineStr">
+      <c r="B51" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C51" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D51" s="23" t="inlineStr">
+      <c r="C51" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D51" s="26" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E51" s="23" t="inlineStr">
+      <c r="E51" s="26" t="inlineStr">
         <is>
           <t>SAP iXp Intern - Software Developer (Agentic AI &amp; LLM systems)</t>
         </is>
       </c>
-      <c r="F51" s="23" t="inlineStr">
+      <c r="F51" s="26" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G51" s="23" t="inlineStr">
+      <c r="G51" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H51" s="23" t="inlineStr">
+      <c r="H51" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 21:40 UTC</t>
         </is>
       </c>
-      <c r="I51" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J51" s="25" t="inlineStr">
+      <c r="I51" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J51" s="28" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/sap-ixp-intern-software-developer-agentic-ai-llm-systems-at-sap-4402305263?refId=zBXuSSlfFyuxcdEqyfeS8g%3D%3D&amp;trackingId=Imq%2FVHMQWkkoDZp5%2BnATSA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K51" s="23" t="inlineStr">
+      <c r="K51" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L51" s="23" t="inlineStr">
+      <c r="L51" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M51" s="23" t="inlineStr"/>
+      <c r="M51" s="26" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="23" t="inlineStr">
+      <c r="A52" s="26" t="inlineStr">
         <is>
           <t>linkedin_4400467080</t>
         </is>
       </c>
-      <c r="B52" s="23" t="inlineStr">
+      <c r="B52" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C52" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D52" s="23" t="inlineStr">
+      <c r="C52" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D52" s="26" t="inlineStr">
         <is>
           <t>Saama</t>
         </is>
       </c>
-      <c r="E52" s="23" t="inlineStr">
+      <c r="E52" s="26" t="inlineStr">
         <is>
           <t>Intern for AI CoE</t>
         </is>
       </c>
-      <c r="F52" s="23" t="inlineStr">
+      <c r="F52" s="26" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G52" s="23" t="inlineStr">
+      <c r="G52" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H52" s="23" t="inlineStr">
+      <c r="H52" s="26" t="inlineStr">
         <is>
           <t>2026-04-16 19:45 UTC</t>
         </is>
       </c>
-      <c r="I52" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J52" s="25" t="inlineStr">
+      <c r="I52" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J52" s="28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/intern-for-ai-coe-at-saama-4400467080?refId=7CvDuV2%2BR%2FzyGozq4UNPPw%3D%3D&amp;trackingId=Ls9yWFAC8lVRx8bmapJfLA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K52" s="23" t="inlineStr">
+      <c r="K52" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-saama-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L52" s="23" t="inlineStr">
+      <c r="L52" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-saama-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M52" s="23" t="inlineStr"/>
+      <c r="M52" s="26" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="23" t="inlineStr">
+      <c r="A53" s="26" t="inlineStr">
         <is>
           <t>linkedin_4400873418</t>
         </is>
       </c>
-      <c r="B53" s="23" t="inlineStr">
+      <c r="B53" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C53" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D53" s="23" t="inlineStr">
+      <c r="C53" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D53" s="26" t="inlineStr">
         <is>
           <t>SANOVIO</t>
         </is>
       </c>
-      <c r="E53" s="23" t="inlineStr">
+      <c r="E53" s="26" t="inlineStr">
         <is>
           <t>AI Engineering Intern</t>
         </is>
       </c>
-      <c r="F53" s="23" t="inlineStr">
+      <c r="F53" s="26" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G53" s="23" t="inlineStr">
+      <c r="G53" s="26" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H53" s="23" t="inlineStr">
+      <c r="H53" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 00:00 UTC</t>
         </is>
       </c>
-      <c r="I53" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J53" s="25" t="inlineStr">
+      <c r="I53" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J53" s="28" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/ai-engineering-intern-at-sanovio-4400873418?refId=egIYeNLcARu6P6oTIZ%2BHfA%3D%3D&amp;trackingId=c6wZ0DtTzvVZpTRC1l5tYQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K53" s="23" t="inlineStr">
+      <c r="K53" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sanovio-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L53" s="23" t="inlineStr">
+      <c r="L53" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sanovio-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M53" s="23" t="inlineStr"/>
+      <c r="M53" s="26" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="23" t="inlineStr">
+      <c r="A54" s="26" t="inlineStr">
         <is>
           <t>linkedin_4403524251</t>
         </is>
       </c>
-      <c r="B54" s="23" t="inlineStr">
+      <c r="B54" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C54" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D54" s="23" t="inlineStr">
+      <c r="C54" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D54" s="26" t="inlineStr">
         <is>
           <t>Nascent Markets</t>
         </is>
       </c>
-      <c r="E54" s="23" t="inlineStr">
+      <c r="E54" s="26" t="inlineStr">
         <is>
           <t>Agentic Systems Intern (Graduate Level)</t>
         </is>
       </c>
-      <c r="F54" s="23" t="inlineStr">
+      <c r="F54" s="26" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G54" s="23" t="inlineStr">
+      <c r="G54" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H54" s="23" t="inlineStr">
+      <c r="H54" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 19:53 UTC</t>
         </is>
       </c>
-      <c r="I54" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J54" s="25" t="inlineStr">
+      <c r="I54" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J54" s="28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/agentic-systems-intern-graduate-level-at-nascent-markets-4403524251?refId=Ix0g0waARRaNpzTY4LxvsQ%3D%3D&amp;trackingId=RsqyOyJHkanw%2FTeHGUcadA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K54" s="23" t="inlineStr">
+      <c r="K54" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-nascent-markets-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L54" s="23" t="inlineStr">
+      <c r="L54" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-nascent-markets-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M54" s="23" t="inlineStr"/>
+      <c r="M54" s="26" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="23" t="inlineStr">
+      <c r="A55" s="26" t="inlineStr">
         <is>
           <t>linkedin_4402782985</t>
         </is>
       </c>
-      <c r="B55" s="23" t="inlineStr">
+      <c r="B55" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C55" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D55" s="23" t="inlineStr">
+      <c r="C55" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D55" s="26" t="inlineStr">
         <is>
           <t>Axiomatic_AI</t>
         </is>
       </c>
-      <c r="E55" s="23" t="inlineStr">
+      <c r="E55" s="26" t="inlineStr">
         <is>
           <t>Internship - Research Intern (Agentic Learning, Memory &amp; Neurosymbolic Reasoning)</t>
         </is>
       </c>
-      <c r="F55" s="23" t="inlineStr">
+      <c r="F55" s="26" t="inlineStr">
         <is>
           <t>Greater Barcelona Metropolitan Area</t>
         </is>
       </c>
-      <c r="G55" s="23" t="inlineStr">
+      <c r="G55" s="26" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H55" s="23" t="inlineStr">
+      <c r="H55" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 05:04 UTC</t>
         </is>
       </c>
-      <c r="I55" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J55" s="25" t="inlineStr">
+      <c r="I55" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J55" s="28" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/internship-research-intern-agentic-learning-memory-neurosymbolic-reasoning-at-axiomatic-ai-4402782985?refId=vm6No12NjZrg2BBV%2BnbuLQ%3D%3D&amp;trackingId=X9FXk%2FBDFftROMNo9Cr20g%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K55" s="23" t="inlineStr">
+      <c r="K55" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-axiomatic-ai-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L55" s="23" t="inlineStr">
+      <c r="L55" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-axiomatic-ai-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M55" s="23" t="inlineStr"/>
+      <c r="M55" s="26" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="23" t="inlineStr">
+      <c r="A56" s="26" t="inlineStr">
         <is>
           <t>linkedin_4309694978</t>
         </is>
       </c>
-      <c r="B56" s="23" t="inlineStr">
+      <c r="B56" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C56" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D56" s="23" t="inlineStr">
+      <c r="C56" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D56" s="26" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E56" s="23" t="inlineStr">
+      <c r="E56" s="26" t="inlineStr">
         <is>
           <t>Graduate Physics Research Intern</t>
         </is>
       </c>
-      <c r="F56" s="23" t="inlineStr">
+      <c r="F56" s="26" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
       </c>
-      <c r="G56" s="23" t="inlineStr">
+      <c r="G56" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H56" s="23" t="inlineStr">
+      <c r="H56" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 17:37 UTC</t>
         </is>
       </c>
-      <c r="I56" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J56" s="25" t="inlineStr">
+      <c r="I56" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J56" s="28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/graduate-physics-research-intern-at-dataannotation-4309694978?refId=hlpC50hTZs9sJFHirXWMSg%3D%3D&amp;trackingId=1E0ixzzpb6MzeHKgxpE3Cw%3D%3D&amp;position=9&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K56" s="23" t="inlineStr">
+      <c r="K56" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L56" s="23" t="inlineStr">
+      <c r="L56" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M56" s="23" t="inlineStr"/>
+      <c r="M56" s="26" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="23" t="inlineStr">
+      <c r="A57" s="26" t="inlineStr">
         <is>
           <t>linkedin_4403562730</t>
         </is>
       </c>
-      <c r="B57" s="23" t="inlineStr">
+      <c r="B57" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C57" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D57" s="23" t="inlineStr">
+      <c r="C57" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D57" s="26" t="inlineStr">
         <is>
           <t>BNM Business Solutions LLP</t>
         </is>
       </c>
-      <c r="E57" s="23" t="inlineStr">
+      <c r="E57" s="26" t="inlineStr">
         <is>
           <t>Data Analyst Internship in Navi Mumbai, Mumbai</t>
         </is>
       </c>
-      <c r="F57" s="23" t="inlineStr">
+      <c r="F57" s="26" t="inlineStr">
         <is>
           <t>Mumbai Metropolitan Region</t>
         </is>
       </c>
-      <c r="G57" s="23" t="inlineStr">
+      <c r="G57" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H57" s="23" t="inlineStr">
+      <c r="H57" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 00:06 UTC</t>
         </is>
       </c>
-      <c r="I57" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J57" s="25" t="inlineStr">
+      <c r="I57" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J57" s="28" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-internship-in-navi-mumbai-mumbai-at-bnm-business-solutions-llp-4403562730?refId=1X9LgKP3%2FAPeJuhZVjyhxw%3D%3D&amp;trackingId=oFY9Z69ZBEGkNtq0cbBOMw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K57" s="23" t="inlineStr">
+      <c r="K57" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bnm-business-solutions-llp-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L57" s="23" t="inlineStr">
+      <c r="L57" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bnm-business-solutions-llp-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M57" s="23" t="inlineStr"/>
+      <c r="M57" s="26" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="23" t="inlineStr">
+      <c r="A58" s="26" t="inlineStr">
         <is>
           <t>linkedin_4309694917</t>
         </is>
       </c>
-      <c r="B58" s="23" t="inlineStr">
+      <c r="B58" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C58" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D58" s="23" t="inlineStr">
+      <c r="C58" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D58" s="26" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E58" s="23" t="inlineStr">
+      <c r="E58" s="26" t="inlineStr">
         <is>
           <t>Graduate Biology Research Intern</t>
         </is>
       </c>
-      <c r="F58" s="23" t="inlineStr">
+      <c r="F58" s="26" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
       </c>
-      <c r="G58" s="23" t="inlineStr">
+      <c r="G58" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H58" s="23" t="inlineStr">
+      <c r="H58" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 17:35 UTC</t>
         </is>
       </c>
-      <c r="I58" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J58" s="25" t="inlineStr">
+      <c r="I58" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J58" s="28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/graduate-biology-research-intern-at-dataannotation-4309694917?refId=hlpC50hTZs9sJFHirXWMSg%3D%3D&amp;trackingId=BM%2FBx4ElnXDk5hEpiM0gzg%3D%3D&amp;position=8&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K58" s="23" t="inlineStr">
+      <c r="K58" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L58" s="23" t="inlineStr">
+      <c r="L58" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M58" s="23" t="inlineStr"/>
+      <c r="M58" s="26" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="23" t="inlineStr">
+      <c r="A59" s="26" t="inlineStr">
         <is>
           <t>linkedin_4346088677</t>
         </is>
       </c>
-      <c r="B59" s="23" t="inlineStr">
+      <c r="B59" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C59" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D59" s="23" t="inlineStr">
+      <c r="C59" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D59" s="26" t="inlineStr">
         <is>
           <t>revel8</t>
         </is>
       </c>
-      <c r="E59" s="23" t="inlineStr">
+      <c r="E59" s="26" t="inlineStr">
         <is>
           <t>Applied AI Engineer Intern (all genders)</t>
         </is>
       </c>
-      <c r="F59" s="23" t="inlineStr">
+      <c r="F59" s="26" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G59" s="23" t="inlineStr">
+      <c r="G59" s="26" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H59" s="23" t="inlineStr">
+      <c r="H59" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 22:38 UTC</t>
         </is>
       </c>
-      <c r="I59" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J59" s="25" t="inlineStr">
+      <c r="I59" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J59" s="28" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/applied-ai-engineer-intern-all-genders-at-revel8-4346088677?refId=FHQDN2Ta3J6B7WhWnDAuhQ%3D%3D&amp;trackingId=Pf%2Ftwn6H5Hrw8BKjPenbSQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K59" s="23" t="inlineStr">
+      <c r="K59" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-revel8-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L59" s="23" t="inlineStr">
+      <c r="L59" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-revel8-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M59" s="23" t="inlineStr"/>
+      <c r="M59" s="26" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="23" t="inlineStr">
+      <c r="A60" s="26" t="inlineStr">
         <is>
           <t>linkedin_4403475387</t>
         </is>
       </c>
-      <c r="B60" s="23" t="inlineStr">
+      <c r="B60" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C60" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D60" s="23" t="inlineStr">
+      <c r="C60" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D60" s="26" t="inlineStr">
         <is>
           <t>Inc42 Media</t>
         </is>
       </c>
-      <c r="E60" s="23" t="inlineStr">
+      <c r="E60" s="26" t="inlineStr">
         <is>
           <t>Operations Intern: Inc42 AI Summit 2026</t>
         </is>
       </c>
-      <c r="F60" s="23" t="inlineStr">
+      <c r="F60" s="26" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G60" s="23" t="inlineStr">
+      <c r="G60" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H60" s="23" t="inlineStr">
+      <c r="H60" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 16:23 UTC</t>
         </is>
       </c>
-      <c r="I60" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J60" s="25" t="inlineStr">
+      <c r="I60" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J60" s="28" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/operations-intern-inc42-ai-summit-2026-at-inc42-media-4403475387?refId=jyI2mJ9xFT%2BmdtkV0OCW0g%3D%3D&amp;trackingId=6sWKnvWNaTU69%2B7bcZNxLg%3D%3D&amp;position=10&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K60" s="23" t="inlineStr">
+      <c r="K60" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-inc42-media-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L60" s="23" t="inlineStr">
+      <c r="L60" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-inc42-media-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M60" s="23" t="inlineStr"/>
+      <c r="M60" s="26" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="23" t="inlineStr">
+      <c r="A61" s="26" t="inlineStr">
         <is>
           <t>linkedin_4403008384</t>
         </is>
       </c>
-      <c r="B61" s="23" t="inlineStr">
+      <c r="B61" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C61" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D61" s="23" t="inlineStr">
+      <c r="C61" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D61" s="26" t="inlineStr">
         <is>
           <t>VEDANTA MOBILITY</t>
         </is>
       </c>
-      <c r="E61" s="23" t="inlineStr">
+      <c r="E61" s="26" t="inlineStr">
         <is>
           <t>Founding Psychology Interns | AI Prototype (Govt Proposal – Dubai)</t>
         </is>
       </c>
-      <c r="F61" s="23" t="inlineStr">
+      <c r="F61" s="26" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G61" s="23" t="inlineStr">
+      <c r="G61" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H61" s="23" t="inlineStr">
+      <c r="H61" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 08:13 UTC</t>
         </is>
       </c>
-      <c r="I61" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J61" s="25" t="inlineStr">
+      <c r="I61" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J61" s="28" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/founding-psychology-interns-ai-prototype-govt-proposal-%E2%80%93-dubai-at-vedanta-mobility-4403008384?refId=moHjgKNH%2BrT9YT5JNnyyqw%3D%3D&amp;trackingId=RUjUOgXLH%2BLJwdPLtKtAMQ%3D%3D&amp;position=13&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K61" s="23" t="inlineStr">
+      <c r="K61" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-vedanta-mobility-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L61" s="23" t="inlineStr">
+      <c r="L61" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-vedanta-mobility-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M61" s="23" t="inlineStr"/>
+      <c r="M61" s="26" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="23" t="inlineStr">
+      <c r="A62" s="26" t="inlineStr">
         <is>
           <t>linkedin_4393616864</t>
         </is>
       </c>
-      <c r="B62" s="23" t="inlineStr">
+      <c r="B62" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C62" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D62" s="23" t="inlineStr">
+      <c r="C62" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D62" s="26" t="inlineStr">
         <is>
           <t>Medidata Solutions</t>
         </is>
       </c>
-      <c r="E62" s="23" t="inlineStr">
+      <c r="E62" s="26" t="inlineStr">
         <is>
           <t>Data Science Intern</t>
         </is>
       </c>
-      <c r="F62" s="23" t="inlineStr">
+      <c r="F62" s="26" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
       </c>
-      <c r="G62" s="23" t="inlineStr">
+      <c r="G62" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H62" s="23" t="inlineStr">
+      <c r="H62" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 13:13 UTC</t>
         </is>
       </c>
-      <c r="I62" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J62" s="25" t="inlineStr">
+      <c r="I62" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J62" s="28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-science-intern-at-medidata-solutions-4393616864?refId=sPMU%2B0UtbDUVjDHc3gXCxA%3D%3D&amp;trackingId=%2BVrdVCzEYQ3jJQvUf4VUtA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K62" s="23" t="inlineStr">
+      <c r="K62" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-medidata-solutions-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L62" s="23" t="inlineStr">
+      <c r="L62" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-medidata-solutions-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M62" s="23" t="inlineStr"/>
+      <c r="M62" s="26" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="23" t="inlineStr">
+      <c r="A63" s="26" t="inlineStr">
         <is>
           <t>linkedin_4403819462</t>
         </is>
       </c>
-      <c r="B63" s="23" t="inlineStr">
+      <c r="B63" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C63" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D63" s="23" t="inlineStr">
+      <c r="C63" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D63" s="26" t="inlineStr">
         <is>
           <t>Calypso Commodities</t>
         </is>
       </c>
-      <c r="E63" s="23" t="inlineStr">
+      <c r="E63" s="26" t="inlineStr">
         <is>
           <t>Trading - Quant &amp; Engineering Intern (Client-Facing)</t>
         </is>
       </c>
-      <c r="F63" s="23" t="inlineStr">
+      <c r="F63" s="26" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="G63" s="23" t="inlineStr">
+      <c r="G63" s="26" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H63" s="23" t="inlineStr">
+      <c r="H63" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 12:44 UTC</t>
         </is>
       </c>
-      <c r="I63" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J63" s="25" t="inlineStr">
+      <c r="I63" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J63" s="28" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/trading-quant-engineering-intern-client-facing-at-calypso-commodities-4403819462?refId=wb%2BADKYeCTj8bBBZgf97xw%3D%3D&amp;trackingId=o0ZBUwzyVOiml0tJPOsNww%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K63" s="23" t="inlineStr">
+      <c r="K63" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-calypso-commodities-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L63" s="23" t="inlineStr">
+      <c r="L63" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-calypso-commodities-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M63" s="23" t="inlineStr"/>
+      <c r="M63" s="26" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="23" t="inlineStr">
+      <c r="A64" s="26" t="inlineStr">
         <is>
           <t>linkedin_4355269413</t>
         </is>
       </c>
-      <c r="B64" s="23" t="inlineStr">
+      <c r="B64" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C64" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D64" s="23" t="inlineStr">
+      <c r="C64" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D64" s="26" t="inlineStr">
         <is>
           <t>Temasek</t>
         </is>
       </c>
-      <c r="E64" s="23" t="inlineStr">
+      <c r="E64" s="26" t="inlineStr">
         <is>
           <t>Data Analytics/Science Intern, People Technology (Jun/Jul - Dec 2026)</t>
         </is>
       </c>
-      <c r="F64" s="23" t="inlineStr">
+      <c r="F64" s="26" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G64" s="23" t="inlineStr">
+      <c r="G64" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H64" s="23" t="inlineStr">
+      <c r="H64" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 10:35 UTC</t>
         </is>
       </c>
-      <c r="I64" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J64" s="25" t="inlineStr">
+      <c r="I64" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J64" s="28" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/data-analytics-science-intern-people-technology-jun-jul-dec-2026-at-temasek-4355269413?refId=emjtNEhTXLtOX%2BguWexSsg%3D%3D&amp;trackingId=DPHM%2FIJzKL0emfNJ1LMMoA%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K64" s="23" t="inlineStr">
+      <c r="K64" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-temasek-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L64" s="23" t="inlineStr">
+      <c r="L64" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-temasek-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M64" s="23" t="inlineStr"/>
+      <c r="M64" s="26" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="23" t="inlineStr">
+      <c r="A65" s="26" t="inlineStr">
         <is>
           <t>linkedin_4403065097</t>
         </is>
       </c>
-      <c r="B65" s="23" t="inlineStr">
+      <c r="B65" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C65" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D65" s="23" t="inlineStr">
+      <c r="C65" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D65" s="26" t="inlineStr">
         <is>
           <t>BLACK TREE GAMING LIMITED</t>
         </is>
       </c>
-      <c r="E65" s="23" t="inlineStr">
+      <c r="E65" s="26" t="inlineStr">
         <is>
           <t>Data Scientist (ML)</t>
         </is>
       </c>
-      <c r="F65" s="23" t="inlineStr">
+      <c r="F65" s="26" t="inlineStr">
         <is>
           <t>Greater London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G65" s="23" t="inlineStr">
+      <c r="G65" s="26" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H65" s="23" t="inlineStr">
+      <c r="H65" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 14:22 UTC</t>
         </is>
       </c>
-      <c r="I65" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J65" s="25" t="inlineStr">
+      <c r="I65" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J65" s="28" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/data-scientist-ml-at-black-tree-gaming-limited-4403065097?refId=X9Gb9UkVv%2BJtfDRc0dJPwA%3D%3D&amp;trackingId=Mfl%2BC%2FBN9DJehDmug19dGA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K65" s="23" t="inlineStr">
+      <c r="K65" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-black-tree-gaming-limited-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L65" s="23" t="inlineStr">
+      <c r="L65" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-black-tree-gaming-limited-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M65" s="23" t="inlineStr"/>
+      <c r="M65" s="26" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="23" t="inlineStr">
+      <c r="A66" s="26" t="inlineStr">
         <is>
           <t>linkedin_4291533663</t>
         </is>
       </c>
-      <c r="B66" s="23" t="inlineStr">
+      <c r="B66" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C66" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D66" s="23" t="inlineStr">
+      <c r="C66" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D66" s="26" t="inlineStr">
         <is>
           <t>McKinsey &amp; Company</t>
         </is>
       </c>
-      <c r="E66" s="23" t="inlineStr">
+      <c r="E66" s="26" t="inlineStr">
         <is>
           <t>Praktikum als Fellow Intern - Tech &amp; AI (m/w/d)</t>
         </is>
       </c>
-      <c r="F66" s="23" t="inlineStr">
+      <c r="F66" s="26" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G66" s="23" t="inlineStr">
+      <c r="G66" s="26" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H66" s="23" t="inlineStr">
+      <c r="H66" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 09:49 UTC</t>
         </is>
       </c>
-      <c r="I66" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J66" s="25" t="inlineStr">
+      <c r="I66" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J66" s="28" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/praktikum-als-fellow-intern-tech-ai-m-w-d-at-mckinsey-company-4291533663?refId=UmiOr88gcWDNbqipJy2ZTg%3D%3D&amp;trackingId=UvtRxMXKlReoOEeGgMaEfA%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K66" s="23" t="inlineStr">
+      <c r="K66" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-mckinsey-company-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L66" s="23" t="inlineStr">
+      <c r="L66" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-mckinsey-company-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M66" s="23" t="inlineStr"/>
+      <c r="M66" s="26" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="23" t="inlineStr">
+      <c r="A67" s="26" t="inlineStr">
         <is>
           <t>linkedin_4336838608</t>
         </is>
       </c>
-      <c r="B67" s="23" t="inlineStr">
+      <c r="B67" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C67" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D67" s="23" t="inlineStr">
+      <c r="C67" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D67" s="26" t="inlineStr">
         <is>
           <t>Sendbird</t>
         </is>
       </c>
-      <c r="E67" s="23" t="inlineStr">
+      <c r="E67" s="26" t="inlineStr">
         <is>
           <t>AI Agent Engineer, Intern</t>
         </is>
       </c>
-      <c r="F67" s="23" t="inlineStr">
+      <c r="F67" s="26" t="inlineStr">
         <is>
           <t>Seoul, Seoul, South Korea</t>
         </is>
       </c>
-      <c r="G67" s="23" t="inlineStr">
+      <c r="G67" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H67" s="23" t="inlineStr">
+      <c r="H67" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 13:46 UTC</t>
         </is>
       </c>
-      <c r="I67" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J67" s="25" t="inlineStr">
+      <c r="I67" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J67" s="28" t="inlineStr">
         <is>
           <t>https://kr.linkedin.com/jobs/view/ai-agent-engineer-intern-at-sendbird-4336838608?refId=%2F1qLChSVn3giUiiNusHaIQ%3D%3D&amp;trackingId=l6mUUvSfC97HjoyrA8uuqg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K67" s="23" t="inlineStr">
+      <c r="K67" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sendbird-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L67" s="23" t="inlineStr">
+      <c r="L67" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sendbird-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M67" s="23" t="inlineStr"/>
+      <c r="M67" s="26" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="23" t="inlineStr">
+      <c r="A68" s="26" t="inlineStr">
         <is>
           <t>linkedin_4372783510</t>
         </is>
       </c>
-      <c r="B68" s="23" t="inlineStr">
+      <c r="B68" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C68" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D68" s="23" t="inlineStr">
+      <c r="C68" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D68" s="26" t="inlineStr">
         <is>
           <t>42dot</t>
         </is>
       </c>
-      <c r="E68" s="23" t="inlineStr">
+      <c r="E68" s="26" t="inlineStr">
         <is>
           <t>[MS/PhD Intern] AI Engineer (정규직 전환형)</t>
         </is>
       </c>
-      <c r="F68" s="23" t="inlineStr">
+      <c r="F68" s="26" t="inlineStr">
         <is>
           <t>Seongnam, Gyeonggi, South Korea</t>
         </is>
       </c>
-      <c r="G68" s="23" t="inlineStr">
+      <c r="G68" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H68" s="23" t="inlineStr">
+      <c r="H68" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 15:08 UTC</t>
         </is>
       </c>
-      <c r="I68" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J68" s="25" t="inlineStr">
+      <c r="I68" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J68" s="28" t="inlineStr">
         <is>
           <t>https://kr.linkedin.com/jobs/view/ms-phd-intern-ai-engineer-%EC%A0%95%EA%B7%9C%EC%A7%81-%EC%A0%84%ED%99%98%ED%98%95-at-42dot-4372783510?refId=%2F1qLChSVn3giUiiNusHaIQ%3D%3D&amp;trackingId=TVYs5RWI1wgPuuVRiBioUA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K68" s="23" t="inlineStr">
+      <c r="K68" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-42dot-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L68" s="23" t="inlineStr">
+      <c r="L68" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-42dot-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M68" s="23" t="inlineStr"/>
+      <c r="M68" s="26" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="23" t="inlineStr">
+      <c r="A69" s="26" t="inlineStr">
         <is>
           <t>linkedin_4402753102</t>
         </is>
       </c>
-      <c r="B69" s="23" t="inlineStr">
+      <c r="B69" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C69" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D69" s="23" t="inlineStr">
+      <c r="C69" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D69" s="26" t="inlineStr">
         <is>
           <t>Five9</t>
         </is>
       </c>
-      <c r="E69" s="23" t="inlineStr">
+      <c r="E69" s="26" t="inlineStr">
         <is>
           <t>Software Developer AI Insights Intern</t>
         </is>
       </c>
-      <c r="F69" s="23" t="inlineStr">
+      <c r="F69" s="26" t="inlineStr">
         <is>
           <t>San Ramon, CA</t>
         </is>
       </c>
-      <c r="G69" s="23" t="inlineStr">
+      <c r="G69" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H69" s="23" t="inlineStr">
+      <c r="H69" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 20:56 UTC</t>
         </is>
       </c>
-      <c r="I69" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J69" s="25" t="inlineStr">
+      <c r="I69" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J69" s="28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/software-developer-ai-insights-intern-at-five9-4402753102?refId=%2FiKmLsIvYp2TclUyf8MJwg%3D%3D&amp;trackingId=X2UMBr3jE86J9JmPv42B2w%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K69" s="23" t="inlineStr">
+      <c r="K69" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-five9-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L69" s="23" t="inlineStr">
+      <c r="L69" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-five9-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M69" s="23" t="inlineStr"/>
+      <c r="M69" s="26" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="23" t="inlineStr">
+      <c r="A70" s="26" t="inlineStr">
         <is>
           <t>linkedin_4403519373</t>
         </is>
       </c>
-      <c r="B70" s="23" t="inlineStr">
+      <c r="B70" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C70" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D70" s="23" t="inlineStr">
+      <c r="C70" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D70" s="26" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E70" s="23" t="inlineStr">
+      <c r="E70" s="26" t="inlineStr">
         <is>
           <t>PhD Research Intern, Physical AI in Perception</t>
         </is>
       </c>
-      <c r="F70" s="23" t="inlineStr">
+      <c r="F70" s="26" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G70" s="23" t="inlineStr">
+      <c r="G70" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H70" s="23" t="inlineStr">
+      <c r="H70" s="26" t="inlineStr">
         <is>
           <t>2026-04-17 20:07 UTC</t>
         </is>
       </c>
-      <c r="I70" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J70" s="25" t="inlineStr">
+      <c r="I70" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J70" s="28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-physical-ai-in-perception-at-zoox-4403519373?refId=LChV34e%2Bd7cvBpZ%2FbJAZjw%3D%3D&amp;trackingId=vlvuJ54NQfvZvNY3pNGqNw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K70" s="23" t="inlineStr">
+      <c r="K70" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L70" s="23" t="inlineStr">
+      <c r="L70" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M70" s="23" t="inlineStr"/>
+      <c r="M70" s="26" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="23" t="inlineStr">
+      <c r="A71" s="26" t="inlineStr">
         <is>
           <t>linkedin_4403095692</t>
         </is>
       </c>
-      <c r="B71" s="23" t="inlineStr">
+      <c r="B71" s="26" t="inlineStr">
         <is>
           <t>2026-04-19 08:24</t>
         </is>
       </c>
-      <c r="C71" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D71" s="23" t="inlineStr">
+      <c r="C71" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D71" s="26" t="inlineStr">
         <is>
           <t>Starrycraze Technology</t>
         </is>
       </c>
-      <c r="E71" s="23" t="inlineStr">
+      <c r="E71" s="26" t="inlineStr">
         <is>
           <t>Data Scientist Intern</t>
         </is>
       </c>
-      <c r="F71" s="23" t="inlineStr">
+      <c r="F71" s="26" t="inlineStr">
         <is>
           <t>Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G71" s="23" t="inlineStr">
+      <c r="G71" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H71" s="23" t="inlineStr">
+      <c r="H71" s="26" t="inlineStr">
         <is>
           <t>2026-04-19 04:58 UTC</t>
         </is>
       </c>
-      <c r="I71" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J71" s="25" t="inlineStr">
+      <c r="I71" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J71" s="28" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/data-scientist-intern-at-starrycraze-technology-4403095692?refId=TVQyGaR78N78VqNo32HHeA%3D%3D&amp;trackingId=iTU%2BdVDc304eRUiD2UiVkA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K71" s="23" t="inlineStr">
+      <c r="K71" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-starrycraze-technology-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L71" s="23" t="inlineStr">
+      <c r="L71" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-starrycraze-technology-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M71" s="23" t="inlineStr"/>
+      <c r="M71" s="26" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="23" t="inlineStr">
+      <c r="A72" s="26" t="inlineStr">
         <is>
           <t>linkedin_4403848986</t>
         </is>
       </c>
-      <c r="B72" s="23" t="inlineStr">
+      <c r="B72" s="26" t="inlineStr">
         <is>
           <t>2026-04-19 08:24</t>
         </is>
       </c>
-      <c r="C72" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D72" s="23" t="inlineStr">
+      <c r="C72" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D72" s="26" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E72" s="23" t="inlineStr">
+      <c r="E72" s="26" t="inlineStr">
         <is>
           <t>PhD Research Intern, Offline Driving Intelligence</t>
         </is>
       </c>
-      <c r="F72" s="23" t="inlineStr">
+      <c r="F72" s="26" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G72" s="23" t="inlineStr">
+      <c r="G72" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H72" s="23" t="inlineStr">
+      <c r="H72" s="26" t="inlineStr">
         <is>
           <t>2026-04-19 02:06 UTC</t>
         </is>
       </c>
-      <c r="I72" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J72" s="25" t="inlineStr">
+      <c r="I72" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J72" s="28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-offline-driving-intelligence-at-zoox-4403848986?refId=5ydRxcXuf5aHqLJVjey87Q%3D%3D&amp;trackingId=FWtGym5%2BhCmPjiMPBVYS7w%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K72" s="23" t="inlineStr">
+      <c r="K72" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L72" s="23" t="inlineStr">
+      <c r="L72" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M72" s="23" t="inlineStr"/>
+      <c r="M72" s="26" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="23" t="inlineStr">
+      <c r="A73" s="26" t="inlineStr">
         <is>
           <t>linkedin_4371758156</t>
         </is>
       </c>
-      <c r="B73" s="23" t="inlineStr">
+      <c r="B73" s="26" t="inlineStr">
         <is>
           <t>2026-04-19 08:24</t>
         </is>
       </c>
-      <c r="C73" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D73" s="23" t="inlineStr">
+      <c r="C73" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D73" s="26" t="inlineStr">
         <is>
           <t>Lowe's India</t>
         </is>
       </c>
-      <c r="E73" s="23" t="inlineStr">
+      <c r="E73" s="26" t="inlineStr">
         <is>
           <t>DIH Intern, Data Engineering</t>
         </is>
       </c>
-      <c r="F73" s="23" t="inlineStr">
+      <c r="F73" s="26" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G73" s="23" t="inlineStr">
+      <c r="G73" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H73" s="23" t="inlineStr">
+      <c r="H73" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 10:48 UTC</t>
         </is>
       </c>
-      <c r="I73" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J73" s="25" t="inlineStr">
+      <c r="I73" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J73" s="28" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/dih-intern-data-engineering-at-lowe-s-india-4371758156?refId=1mgTdTTgR1UncTTJ8Ts5OA%3D%3D&amp;trackingId=7HYWBNU0zclnyp9qIoW2Jw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K73" s="23" t="inlineStr">
+      <c r="K73" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-lowes-india-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L73" s="23" t="inlineStr">
+      <c r="L73" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-lowes-india-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M73" s="23" t="inlineStr"/>
+      <c r="M73" s="26" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="23" t="inlineStr">
+      <c r="A74" s="26" t="inlineStr">
         <is>
           <t>linkedin_4327191639</t>
         </is>
       </c>
-      <c r="B74" s="23" t="inlineStr">
+      <c r="B74" s="26" t="inlineStr">
         <is>
           <t>2026-04-19 08:24</t>
         </is>
       </c>
-      <c r="C74" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D74" s="23" t="inlineStr">
+      <c r="C74" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D74" s="26" t="inlineStr">
         <is>
           <t>Whatnot</t>
         </is>
       </c>
-      <c r="E74" s="23" t="inlineStr">
+      <c r="E74" s="26" t="inlineStr">
         <is>
           <t>Data Scientist, Product Analytics</t>
         </is>
       </c>
-      <c r="F74" s="23" t="inlineStr">
+      <c r="F74" s="26" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G74" s="23" t="inlineStr">
+      <c r="G74" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H74" s="23" t="inlineStr">
+      <c r="H74" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 13:22 UTC</t>
         </is>
       </c>
-      <c r="I74" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J74" s="25" t="inlineStr">
+      <c r="I74" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J74" s="28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-scientist-product-analytics-at-whatnot-4327191639?refId=mfQJnJ6mRr3La1qB9YnNGA%3D%3D&amp;trackingId=k4mLJmsHD9wYHSZlc4RA%2Fw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K74" s="23" t="inlineStr">
+      <c r="K74" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-whatnot-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L74" s="23" t="inlineStr">
+      <c r="L74" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-whatnot-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M74" s="23" t="inlineStr"/>
+      <c r="M74" s="26" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="23" t="inlineStr">
+      <c r="A75" s="26" t="inlineStr">
         <is>
           <t>linkedin_4391150969</t>
         </is>
       </c>
-      <c r="B75" s="23" t="inlineStr">
+      <c r="B75" s="26" t="inlineStr">
         <is>
           <t>2026-04-19 19:54</t>
         </is>
       </c>
-      <c r="C75" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D75" s="23" t="inlineStr">
+      <c r="C75" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D75" s="26" t="inlineStr">
         <is>
           <t>Cartesian</t>
         </is>
       </c>
-      <c r="E75" s="23" t="inlineStr">
+      <c r="E75" s="26" t="inlineStr">
         <is>
           <t>Software Engineering Intern (Summer/Fall 2026)</t>
         </is>
       </c>
-      <c r="F75" s="23" t="inlineStr">
+      <c r="F75" s="26" t="inlineStr">
         <is>
           <t>Cambridge, MA</t>
         </is>
       </c>
-      <c r="G75" s="23" t="inlineStr">
+      <c r="G75" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H75" s="23" t="inlineStr">
+      <c r="H75" s="26" t="inlineStr">
         <is>
           <t>2026-04-18 23:08 UTC</t>
         </is>
       </c>
-      <c r="I75" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J75" s="25" t="inlineStr">
+      <c r="I75" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J75" s="28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/software-engineering-intern-summer-fall-2026-at-cartesian-4391150969?refId=rXBEPoDKoHwUW%2BMU3mmCWA%3D%3D&amp;trackingId=03L6jyuSNG6Edf0%2FeXbj4w%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K75" s="23" t="inlineStr">
+      <c r="K75" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-cartesian-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L75" s="23" t="inlineStr">
+      <c r="L75" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-cartesian-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M75" s="23" t="inlineStr"/>
+      <c r="M75" s="26" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="23" t="inlineStr">
+      <c r="A76" s="26" t="inlineStr">
         <is>
           <t>linkedin_4401268516</t>
         </is>
       </c>
-      <c r="B76" s="23" t="inlineStr">
+      <c r="B76" s="26" t="inlineStr">
         <is>
           <t>2026-04-19 19:54</t>
         </is>
       </c>
-      <c r="C76" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D76" s="23" t="inlineStr">
+      <c r="C76" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D76" s="26" t="inlineStr">
         <is>
           <t>Joveo Ai</t>
         </is>
       </c>
-      <c r="E76" s="23" t="inlineStr">
+      <c r="E76" s="26" t="inlineStr">
         <is>
           <t>Generative AI Intern</t>
         </is>
       </c>
-      <c r="F76" s="23" t="inlineStr">
+      <c r="F76" s="26" t="inlineStr">
         <is>
           <t>Bangalore Urban, Karnataka, India</t>
         </is>
       </c>
-      <c r="G76" s="23" t="inlineStr">
+      <c r="G76" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H76" s="23" t="inlineStr">
+      <c r="H76" s="26" t="inlineStr">
         <is>
           <t>2026-04-19 16:33 UTC</t>
         </is>
       </c>
-      <c r="I76" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J76" s="25" t="inlineStr">
+      <c r="I76" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J76" s="28" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/generative-ai-intern-at-joveo-ai-4401268516?refId=AMRRU4%2FYzAhlhe1ad%2FYa%2Fw%3D%3D&amp;trackingId=lRpwTcswbLSpxr57DNyAvA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K76" s="23" t="inlineStr">
+      <c r="K76" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-joveo-ai-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L76" s="23" t="inlineStr">
+      <c r="L76" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-joveo-ai-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M76" s="23" t="inlineStr"/>
+      <c r="M76" s="26" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="23" t="inlineStr">
+      <c r="A77" s="26" t="inlineStr">
         <is>
           <t>linkedin_4381330362</t>
         </is>
       </c>
-      <c r="B77" s="23" t="inlineStr">
+      <c r="B77" s="26" t="inlineStr">
         <is>
           <t>2026-04-19 19:54</t>
         </is>
       </c>
-      <c r="C77" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D77" s="23" t="inlineStr">
+      <c r="C77" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D77" s="26" t="inlineStr">
         <is>
           <t>Shopee</t>
         </is>
       </c>
-      <c r="E77" s="23" t="inlineStr">
+      <c r="E77" s="26" t="inlineStr">
         <is>
           <t>Data Analyst Intern - Product Analysis, Regional Operations (Summer 2026)</t>
         </is>
       </c>
-      <c r="F77" s="23" t="inlineStr">
+      <c r="F77" s="26" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G77" s="23" t="inlineStr">
+      <c r="G77" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H77" s="23" t="inlineStr">
+      <c r="H77" s="26" t="inlineStr">
         <is>
           <t>2026-04-19 13:47 UTC</t>
         </is>
       </c>
-      <c r="I77" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J77" s="25" t="inlineStr">
+      <c r="I77" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J77" s="28" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/data-analyst-intern-product-analysis-regional-operations-summer-2026-at-shopee-4381330362?refId=Mf9npsmRtScOZbkuOI7S2Q%3D%3D&amp;trackingId=qCnW3Di6Gcyx48NhCTpBLw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K77" s="23" t="inlineStr">
+      <c r="K77" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-shopee-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L77" s="23" t="inlineStr">
+      <c r="L77" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-shopee-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M77" s="23" t="inlineStr"/>
+      <c r="M77" s="26" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="23" t="inlineStr">
+      <c r="A78" s="26" t="inlineStr">
         <is>
           <t>linkedin_4355297667</t>
         </is>
       </c>
-      <c r="B78" s="23" t="inlineStr">
+      <c r="B78" s="26" t="inlineStr">
         <is>
           <t>2026-04-19 19:54</t>
         </is>
       </c>
-      <c r="C78" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D78" s="23" t="inlineStr">
+      <c r="C78" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D78" s="26" t="inlineStr">
         <is>
           <t>Temasek</t>
         </is>
       </c>
-      <c r="E78" s="23" t="inlineStr">
+      <c r="E78" s="26" t="inlineStr">
         <is>
           <t>Policy &amp; Research Intern, Workforce 4.0 (Jun/Jul - Dec 2026)</t>
         </is>
       </c>
-      <c r="F78" s="23" t="inlineStr">
+      <c r="F78" s="26" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G78" s="23" t="inlineStr">
+      <c r="G78" s="26" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H78" s="23" t="inlineStr">
+      <c r="H78" s="26" t="inlineStr">
         <is>
           <t>2026-04-19 10:08 UTC</t>
         </is>
       </c>
-      <c r="I78" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J78" s="25" t="inlineStr">
+      <c r="I78" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J78" s="28" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/policy-research-intern-workforce-4-0-jun-jul-dec-2026-at-temasek-4355297667?refId=SZF%2BVbNMCE0h7Rloqm3lXQ%3D%3D&amp;trackingId=vK2euiis8CytJt264fhurw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K78" s="23" t="inlineStr">
+      <c r="K78" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-temasek-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L78" s="23" t="inlineStr">
+      <c r="L78" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-temasek-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M78" s="23" t="inlineStr"/>
+      <c r="M78" s="26" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="23" t="inlineStr">
+      <c r="A79" s="26" t="inlineStr">
         <is>
           <t>linkedin_4336865392</t>
         </is>
       </c>
-      <c r="B79" s="23" t="inlineStr">
+      <c r="B79" s="26" t="inlineStr">
         <is>
           <t>2026-04-19 19:54</t>
         </is>
       </c>
-      <c r="C79" s="23" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D79" s="23" t="inlineStr">
+      <c r="C79" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D79" s="26" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E79" s="23" t="inlineStr">
+      <c r="E79" s="26" t="inlineStr">
         <is>
           <t>PhD Research Intern, Visual Object Understanding</t>
         </is>
       </c>
-      <c r="F79" s="23" t="inlineStr">
+      <c r="F79" s="26" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G79" s="23" t="inlineStr">
+      <c r="G79" s="26" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H79" s="23" t="inlineStr">
+      <c r="H79" s="26" t="inlineStr">
         <is>
           <t>2026-04-19 10:27 UTC</t>
         </is>
       </c>
-      <c r="I79" s="24" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J79" s="25" t="inlineStr">
+      <c r="I79" s="27" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J79" s="28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-visual-object-understanding-at-zoox-4336865392?refId=gztZfDsooz7GE2iA6mPxjQ%3D%3D&amp;trackingId=%2F1kV0X%2F8hKCPhv0kD05v5Q%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K79" s="23" t="inlineStr">
+      <c r="K79" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L79" s="23" t="inlineStr">
+      <c r="L79" s="26" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M79" s="23" t="inlineStr"/>
+      <c r="M79" s="26" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="26" t="inlineStr">
@@ -6036,6 +6045,384 @@
         </is>
       </c>
       <c r="M87" s="26" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="29" t="inlineStr">
+        <is>
+          <t>linkedin_4323554488</t>
+        </is>
+      </c>
+      <c r="B88" s="29" t="inlineStr">
+        <is>
+          <t>2026-04-20 20:02</t>
+        </is>
+      </c>
+      <c r="C88" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D88" s="29" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="E88" s="29" t="inlineStr">
+        <is>
+          <t>Data Analyst Intern, Buyer &amp; Marketing - Business Intelligence (Jan- Apr 2026)</t>
+        </is>
+      </c>
+      <c r="F88" s="29" t="inlineStr">
+        <is>
+          <t>Singapore, Singapore</t>
+        </is>
+      </c>
+      <c r="G88" s="29" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H88" s="29" t="inlineStr">
+        <is>
+          <t>2026-04-20 13:19 UTC</t>
+        </is>
+      </c>
+      <c r="I88" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J88" s="31" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/data-analyst-intern-buyer-marketing-business-intelligence-jan-apr-2026-at-shopee-4323554488?refId=7F9xR8A2ceTxeNHc8C48Lw%3D%3D&amp;trackingId=yyqxH6uqfdMekl83OKdeng%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K88" s="29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-shopee-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="L88" s="29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-shopee-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="M88" s="29" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="29" t="inlineStr">
+        <is>
+          <t>linkedin_4403602536</t>
+        </is>
+      </c>
+      <c r="B89" s="29" t="inlineStr">
+        <is>
+          <t>2026-04-20 20:02</t>
+        </is>
+      </c>
+      <c r="C89" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D89" s="29" t="inlineStr">
+        <is>
+          <t>Matter</t>
+        </is>
+      </c>
+      <c r="E89" s="29" t="inlineStr">
+        <is>
+          <t>ESG Data Intern</t>
+        </is>
+      </c>
+      <c r="F89" s="29" t="inlineStr">
+        <is>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+        </is>
+      </c>
+      <c r="G89" s="29" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H89" s="29" t="inlineStr">
+        <is>
+          <t>2026-04-20 13:42 UTC</t>
+        </is>
+      </c>
+      <c r="I89" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J89" s="31" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/jobs/view/esg-data-intern-at-matter-4403602536?refId=AE%2FVzoOpycEQ7%2F%2BJ0DeSEg%3D%3D&amp;trackingId=KDyRT7oadVzItXO7Z6Fndw%3D%3D&amp;position=2&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K89" s="29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-matter-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="L89" s="29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-matter-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="M89" s="29" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="29" t="inlineStr">
+        <is>
+          <t>linkedin_4403625335</t>
+        </is>
+      </c>
+      <c r="B90" s="29" t="inlineStr">
+        <is>
+          <t>2026-04-20 20:02</t>
+        </is>
+      </c>
+      <c r="C90" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D90" s="29" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="E90" s="29" t="inlineStr">
+        <is>
+          <t>Binance Accelerator Program - Applied Data Scientist</t>
+        </is>
+      </c>
+      <c r="F90" s="29" t="inlineStr">
+        <is>
+          <t>Singapore, Singapore</t>
+        </is>
+      </c>
+      <c r="G90" s="29" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H90" s="29" t="inlineStr">
+        <is>
+          <t>2026-04-20 15:53 UTC</t>
+        </is>
+      </c>
+      <c r="I90" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J90" s="31" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/binance-accelerator-program-applied-data-scientist-at-binance-4403625335?refId=RjWLz09J3iQbgIc%2B%2Farrcg%3D%3D&amp;trackingId=DNLE3AfRN1YFc4qeIspU0w%3D%3D&amp;position=5&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K90" s="29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-binance-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="L90" s="29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-binance-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="M90" s="29" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="29" t="inlineStr">
+        <is>
+          <t>linkedin_4401462467</t>
+        </is>
+      </c>
+      <c r="B91" s="29" t="inlineStr">
+        <is>
+          <t>2026-04-20 20:02</t>
+        </is>
+      </c>
+      <c r="C91" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D91" s="29" t="inlineStr">
+        <is>
+          <t>Henning Larsen</t>
+        </is>
+      </c>
+      <c r="E91" s="29" t="inlineStr">
+        <is>
+          <t>Business Development Intern – AI and IT focus</t>
+        </is>
+      </c>
+      <c r="F91" s="29" t="inlineStr">
+        <is>
+          <t>Copenhagen, Capital Region of Denmark, Denmark</t>
+        </is>
+      </c>
+      <c r="G91" s="29" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H91" s="29" t="inlineStr">
+        <is>
+          <t>2026-04-20 14:23 UTC</t>
+        </is>
+      </c>
+      <c r="I91" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J91" s="31" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/jobs/view/business-development-intern-%E2%80%93-ai-and-it-focus-at-henning-larsen-4401462467?refId=AE%2FVzoOpycEQ7%2F%2BJ0DeSEg%3D%3D&amp;trackingId=a6kSBIKrUbVcoZ6e1VKmqQ%3D%3D&amp;position=1&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K91" s="29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-henning-larsen-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="L91" s="29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-henning-larsen-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="M91" s="29" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="29" t="inlineStr">
+        <is>
+          <t>linkedin_3694731755</t>
+        </is>
+      </c>
+      <c r="B92" s="29" t="inlineStr">
+        <is>
+          <t>2026-04-20 20:02</t>
+        </is>
+      </c>
+      <c r="C92" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D92" s="29" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="E92" s="29" t="inlineStr">
+        <is>
+          <t>Data Analyst Intern - Warehouse Operations, Regional Operations (Spring 2025)</t>
+        </is>
+      </c>
+      <c r="F92" s="29" t="inlineStr">
+        <is>
+          <t>Singapore, Singapore</t>
+        </is>
+      </c>
+      <c r="G92" s="29" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H92" s="29" t="inlineStr">
+        <is>
+          <t>2026-04-20 13:27 UTC</t>
+        </is>
+      </c>
+      <c r="I92" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J92" s="31" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/data-analyst-intern-warehouse-operations-regional-operations-spring-2025-at-shopee-3694731755?refId=7F9xR8A2ceTxeNHc8C48Lw%3D%3D&amp;trackingId=Z5%2FGgcVQ%2FHnhfRD8%2FEOmvw%3D%3D&amp;position=2&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K92" s="29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-shopee-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="L92" s="29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-shopee-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="M92" s="29" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="29" t="inlineStr">
+        <is>
+          <t>linkedin_4401618037</t>
+        </is>
+      </c>
+      <c r="B93" s="29" t="inlineStr">
+        <is>
+          <t>2026-04-20 20:02</t>
+        </is>
+      </c>
+      <c r="C93" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D93" s="29" t="inlineStr">
+        <is>
+          <t>Superhuman</t>
+        </is>
+      </c>
+      <c r="E93" s="29" t="inlineStr">
+        <is>
+          <t>Applied Research Intern (Summer 2026)</t>
+        </is>
+      </c>
+      <c r="F93" s="29" t="inlineStr">
+        <is>
+          <t>Berlin, Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="G93" s="29" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H93" s="29" t="inlineStr">
+        <is>
+          <t>2026-04-20 09:39 UTC</t>
+        </is>
+      </c>
+      <c r="I93" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J93" s="31" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/applied-research-intern-summer-2026-at-superhuman-4401618037?refId=QaSuTZCPNmMWLvSVLYxnBg%3D%3D&amp;trackingId=VlqyKWxk2dgOXzUfhtaiGQ%3D%3D&amp;position=2&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K93" s="29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-superhuman-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="L93" s="29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-superhuman-2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="M93" s="29" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6125,6 +6512,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J86" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J93" r:id="rId92"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -83,10 +83,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -543,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M93"/>
+  <dimension ref="A1:M95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -629,5422 +638,5422 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>linkedin_4401809501</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C2" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D2" s="26" t="inlineStr">
+      <c r="C2" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D2" s="29" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E2" s="26" t="inlineStr">
+      <c r="E2" s="29" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F2" s="26" t="inlineStr">
+      <c r="F2" s="29" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G2" s="26" t="inlineStr">
+      <c r="G2" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H2" s="26" t="inlineStr">
+      <c r="H2" s="29" t="inlineStr">
         <is>
           <t>2026-04-15 22:19 UTC</t>
         </is>
       </c>
-      <c r="I2" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J2" s="28" t="inlineStr">
+      <c r="I2" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J2" s="31" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/research-intern-at-skycliff-it-4401809501?refId=HHi6SaK1fggu3E9dI3MtVg%3D%3D&amp;trackingId=r33pSo29lHStfk9FH82pyw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K2" s="26" t="inlineStr">
+      <c r="K2" s="29" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L2" s="26" t="inlineStr">
+      <c r="L2" s="29" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M2" s="26" t="inlineStr"/>
+      <c r="M2" s="29" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>linkedin_4402568578</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D3" s="29" t="inlineStr">
         <is>
           <t>Webs X UM</t>
         </is>
       </c>
-      <c r="E3" s="26" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F3" s="26" t="inlineStr">
+      <c r="F3" s="29" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G3" s="26" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H3" s="26" t="inlineStr">
+      <c r="H3" s="29" t="inlineStr">
         <is>
           <t>2026-04-15 19:20 UTC</t>
         </is>
       </c>
-      <c r="I3" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J3" s="28" t="inlineStr">
+      <c r="I3" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J3" s="31" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-webs-x-um-4402568578?refId=g89JM6cY8EFeoLk6JL5tVg%3D%3D&amp;trackingId=uFZVJJX7SSI0XCPFIrLqmA%3D%3D&amp;position=19&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K3" s="26" t="inlineStr">
+      <c r="K3" s="29" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-webs-x-um-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L3" s="26" t="inlineStr">
+      <c r="L3" s="29" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-webs-x-um-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M3" s="26" t="inlineStr"/>
+      <c r="M3" s="29" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>linkedin_4399996740</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D4" s="26" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>SUN PHARMA</t>
         </is>
       </c>
-      <c r="E4" s="26" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>Becario</t>
         </is>
       </c>
-      <c r="F4" s="26" t="inlineStr">
+      <c r="F4" s="29" t="inlineStr">
         <is>
           <t>Mexico City, Mexico</t>
         </is>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H4" s="26" t="inlineStr">
+      <c r="H4" s="29" t="inlineStr">
         <is>
           <t>2026-04-15 17:59 UTC</t>
         </is>
       </c>
-      <c r="I4" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J4" s="28" t="inlineStr">
+      <c r="I4" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J4" s="31" t="inlineStr">
         <is>
           <t>https://mx.linkedin.com/jobs/view/becario-at-sun-pharma-4399996740?refId=g89JM6cY8EFeoLk6JL5tVg%3D%3D&amp;trackingId=sZ0Fkcf4RHuIpzXu4mJRNg%3D%3D&amp;position=22&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K4" s="26" t="inlineStr">
+      <c r="K4" s="29" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-sun-pharma-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L4" s="26" t="inlineStr">
+      <c r="L4" s="29" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-sun-pharma-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M4" s="26" t="inlineStr"/>
+      <c r="M4" s="29" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>linkedin_4399975959</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D5" s="29" t="inlineStr">
         <is>
           <t>LS Direct</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="29" t="inlineStr">
         <is>
           <t>Data Analytics Intern</t>
         </is>
       </c>
-      <c r="F5" s="26" t="inlineStr">
+      <c r="F5" s="29" t="inlineStr">
         <is>
           <t>Suffern, NY</t>
         </is>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H5" s="26" t="inlineStr">
+      <c r="H5" s="29" t="inlineStr">
         <is>
           <t>2026-04-15 14:26 UTC</t>
         </is>
       </c>
-      <c r="I5" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J5" s="28" t="inlineStr">
+      <c r="I5" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J5" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-analytics-intern-at-ls-direct-4399975959?refId=pg0ll3e89fatVyUznLcdpw%3D%3D&amp;trackingId=5b41IoyQfIfx3Tu42domiQ%3D%3D&amp;position=23&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K5" s="26" t="inlineStr">
+      <c r="K5" s="29" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-ls-direct-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L5" s="26" t="inlineStr">
+      <c r="L5" s="29" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-ls-direct-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M5" s="26" t="inlineStr"/>
+      <c r="M5" s="29" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>linkedin_4370546718</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>Clarivate</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>Lead Data Scientist</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="F6" s="29" t="inlineStr">
         <is>
           <t>Barcelona, Catalonia, Spain</t>
         </is>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H6" s="26" t="inlineStr">
+      <c r="H6" s="29" t="inlineStr">
         <is>
           <t>2026-04-15 12:16 UTC</t>
         </is>
       </c>
-      <c r="I6" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J6" s="28" t="inlineStr">
+      <c r="I6" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J6" s="31" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/lead-data-scientist-at-clarivate-4370546718?refId=FyyqQfduMQ8KZ7B5LeF0UQ%3D%3D&amp;trackingId=1i1kXdbV7SMunyFTiSJHJg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K6" s="26" t="inlineStr">
+      <c r="K6" s="29" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-clarivate-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L6" s="26" t="inlineStr">
+      <c r="L6" s="29" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-clarivate-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M6" s="26" t="inlineStr"/>
+      <c r="M6" s="29" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>linkedin_4389810164</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>Vitality</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>Senior Data Scientist - 12 Month FTC</t>
         </is>
       </c>
-      <c r="F7" s="26" t="inlineStr">
+      <c r="F7" s="29" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H7" s="26" t="inlineStr">
+      <c r="H7" s="29" t="inlineStr">
         <is>
           <t>2026-04-15 09:39 UTC</t>
         </is>
       </c>
-      <c r="I7" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J7" s="28" t="inlineStr">
+      <c r="I7" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J7" s="31" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/senior-data-scientist-12-month-ftc-at-vitality-4389810164?refId=FPz%2BrPoaQeqgXBm%2FfOzGGA%3D%3D&amp;trackingId=yVNh55t2X2xocDT4i6HDqQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K7" s="26" t="inlineStr">
+      <c r="K7" s="29" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-vitality-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L7" s="26" t="inlineStr">
+      <c r="L7" s="29" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-vitality-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M7" s="26" t="inlineStr"/>
+      <c r="M7" s="29" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>linkedin_4399952059</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>traide AI</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>AI Associate (f/m/x) (B2B SaaS Startup) - Intern/Working Student</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="29" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="29" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H8" s="26" t="inlineStr">
+      <c r="H8" s="29" t="inlineStr">
         <is>
           <t>2026-04-15 07:04 UTC</t>
         </is>
       </c>
-      <c r="I8" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J8" s="28" t="inlineStr">
+      <c r="I8" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J8" s="31" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/ai-associate-f-m-x-b2b-saas-startup-intern-working-student-at-traide-ai-4399952059?refId=x0uIkl175n0hipT17L%2FGRw%3D%3D&amp;trackingId=8kdzUQgW%2B7rCk2pO2oIErg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K8" s="26" t="inlineStr">
+      <c r="K8" s="29" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-traide-ai-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L8" s="26" t="inlineStr">
+      <c r="L8" s="29" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-traide-ai-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M8" s="26" t="inlineStr"/>
+      <c r="M8" s="29" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>linkedin_4399933254</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Briink</t>
         </is>
       </c>
-      <c r="E9" s="26" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>Growth Intern (Merantix AI Campus)</t>
         </is>
       </c>
-      <c r="F9" s="26" t="inlineStr">
+      <c r="F9" s="29" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G9" s="26" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H9" s="26" t="inlineStr">
+      <c r="H9" s="29" t="inlineStr">
         <is>
           <t>2026-04-15 05:03 UTC</t>
         </is>
       </c>
-      <c r="I9" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J9" s="28" t="inlineStr">
+      <c r="I9" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J9" s="31" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/growth-intern-merantix-ai-campus-at-briink-4399933254?refId=x0uIkl175n0hipT17L%2FGRw%3D%3D&amp;trackingId=qEKtyJNA03Kbr6AYDlhsBw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K9" s="26" t="inlineStr">
+      <c r="K9" s="29" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-briink-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L9" s="26" t="inlineStr">
+      <c r="L9" s="29" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-briink-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M9" s="26" t="inlineStr"/>
+      <c r="M9" s="29" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>linkedin_4400429367</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>Tata Consultancy Services</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>HR -Data Scientist</t>
         </is>
       </c>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="F10" s="29" t="inlineStr">
         <is>
           <t>Renton, WA</t>
         </is>
       </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="G10" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H10" s="26" t="inlineStr">
+      <c r="H10" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 16:56 UTC</t>
         </is>
       </c>
-      <c r="I10" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J10" s="28" t="inlineStr">
+      <c r="I10" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J10" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/hr-data-scientist-at-tata-consultancy-services-4400429367?refId=vJILgNySaXYUQknbyaKZZQ%3D%3D&amp;trackingId=7cZ0KYh8Sv5%2Fh6%2FG86%2BLug%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K10" s="26" t="inlineStr">
+      <c r="K10" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-tata-consultancy-services-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L10" s="26" t="inlineStr">
+      <c r="L10" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-tata-consultancy-services-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M10" s="26" t="inlineStr"/>
+      <c r="M10" s="29" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>linkedin_4390814627</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>Criteo</t>
         </is>
       </c>
-      <c r="E11" s="26" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F11" s="26" t="inlineStr">
+      <c r="F11" s="29" t="inlineStr">
         <is>
           <t>Barcelona, Catalonia, Spain</t>
         </is>
       </c>
-      <c r="G11" s="26" t="inlineStr">
+      <c r="G11" s="29" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H11" s="26" t="inlineStr">
+      <c r="H11" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 12:19 UTC</t>
         </is>
       </c>
-      <c r="I11" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J11" s="28" t="inlineStr">
+      <c r="I11" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J11" s="31" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/data-analyst-intern-at-criteo-4390814627?refId=PCZWvfzZIzNkx6giU9jTsA%3D%3D&amp;trackingId=T%2FMog6vtgG8P3ihAU9b1uQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K11" s="26" t="inlineStr">
+      <c r="K11" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-criteo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L11" s="26" t="inlineStr">
+      <c r="L11" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-criteo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M11" s="26" t="inlineStr"/>
+      <c r="M11" s="29" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>linkedin_4402983364</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F12" s="26" t="inlineStr">
+      <c r="F12" s="29" t="inlineStr">
         <is>
           <t>Brussels, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G12" s="26" t="inlineStr">
+      <c r="G12" s="29" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H12" s="26" t="inlineStr">
+      <c r="H12" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I12" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J12" s="28" t="inlineStr">
+      <c r="I12" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J12" s="31" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402983364?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=zV4sJQyNyQg%2FS%2BYm6Ba9Eg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K12" s="26" t="inlineStr">
+      <c r="K12" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L12" s="26" t="inlineStr">
+      <c r="L12" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M12" s="26" t="inlineStr"/>
+      <c r="M12" s="29" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>linkedin_4390725142</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D13" s="26" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>Boston Consulting Group (BCG)</t>
         </is>
       </c>
-      <c r="E13" s="26" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>Forward Deployed AI Engineer, Internship, United Kingdom - BCG X</t>
         </is>
       </c>
-      <c r="F13" s="26" t="inlineStr">
+      <c r="F13" s="29" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G13" s="26" t="inlineStr">
+      <c r="G13" s="29" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H13" s="26" t="inlineStr">
+      <c r="H13" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 16:24 UTC</t>
         </is>
       </c>
-      <c r="I13" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J13" s="28" t="inlineStr">
+      <c r="I13" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J13" s="31" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/forward-deployed-ai-engineer-internship-united-kingdom-bcg-x-at-boston-consulting-group-bcg-4390725142?refId=YHAZO5vAx9Qtg1RXMma%2F%2BA%3D%3D&amp;trackingId=E8kiSHzcdYe%2FH6s%2FCkGtMw%3D%3D&amp;position=7&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K13" s="26" t="inlineStr">
+      <c r="K13" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L13" s="26" t="inlineStr">
+      <c r="L13" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M13" s="26" t="inlineStr"/>
+      <c r="M13" s="29" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="29" t="inlineStr">
         <is>
           <t>linkedin_4400428064</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>Fanatics</t>
         </is>
       </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="F14" s="26" t="inlineStr">
+      <c r="F14" s="29" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G14" s="26" t="inlineStr">
+      <c r="G14" s="29" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H14" s="26" t="inlineStr">
+      <c r="H14" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 16:16 UTC</t>
         </is>
       </c>
-      <c r="I14" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J14" s="28" t="inlineStr">
+      <c r="I14" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J14" s="31" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/data-scientist-at-fanatics-4400428064?refId=SNMwEp9%2FBozAkX4FBnhJwQ%3D%3D&amp;trackingId=cAX0aKWV%2FBX1fvQzm%2FkEMg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K14" s="26" t="inlineStr">
+      <c r="K14" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-fanatics-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L14" s="26" t="inlineStr">
+      <c r="L14" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-fanatics-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M14" s="26" t="inlineStr"/>
+      <c r="M14" s="29" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>linkedin_4390730090</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>Boston Consulting Group (BCG)</t>
         </is>
       </c>
-      <c r="E15" s="26" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>Forward Deployed AI Scientist, Internship, United Kingdom - BCG X</t>
         </is>
       </c>
-      <c r="F15" s="26" t="inlineStr">
+      <c r="F15" s="29" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G15" s="26" t="inlineStr">
+      <c r="G15" s="29" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H15" s="26" t="inlineStr">
+      <c r="H15" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 13:57 UTC</t>
         </is>
       </c>
-      <c r="I15" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J15" s="28" t="inlineStr">
+      <c r="I15" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J15" s="31" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/forward-deployed-ai-scientist-internship-united-kingdom-bcg-x-at-boston-consulting-group-bcg-4390730090?refId=YHAZO5vAx9Qtg1RXMma%2F%2BA%3D%3D&amp;trackingId=m50MzwjbYzUmAv7nJVAKgA%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K15" s="26" t="inlineStr">
+      <c r="K15" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L15" s="26" t="inlineStr">
+      <c r="L15" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M15" s="26" t="inlineStr"/>
+      <c r="M15" s="29" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>linkedin_4402138096</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D16" s="29" t="inlineStr">
         <is>
           <t>Kelly Tutors</t>
         </is>
       </c>
-      <c r="E16" s="26" t="inlineStr">
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>Research Intern (3-5hrs/week, flexible)</t>
         </is>
       </c>
-      <c r="F16" s="26" t="inlineStr">
+      <c r="F16" s="29" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G16" s="26" t="inlineStr">
+      <c r="G16" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H16" s="26" t="inlineStr">
+      <c r="H16" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 14:40 UTC</t>
         </is>
       </c>
-      <c r="I16" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J16" s="28" t="inlineStr">
+      <c r="I16" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J16" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/research-intern-3-5hrs-week-flexible-at-kelly-tutors-4402138096?refId=HmOS2YEHUH3GOVent1txqw%3D%3D&amp;trackingId=3XBXMUoBdiHeRL4qw%2B2qRw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K16" s="26" t="inlineStr">
+      <c r="K16" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-kelly-tutors-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L16" s="26" t="inlineStr">
+      <c r="L16" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-kelly-tutors-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M16" s="26" t="inlineStr"/>
+      <c r="M16" s="29" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>linkedin_4378557045</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D17" s="26" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>Fund for Public Health in NYC</t>
         </is>
       </c>
-      <c r="E17" s="26" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="F17" s="26" t="inlineStr">
+      <c r="F17" s="29" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G17" s="26" t="inlineStr">
+      <c r="G17" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H17" s="26" t="inlineStr">
+      <c r="H17" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 16:13 UTC</t>
         </is>
       </c>
-      <c r="I17" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J17" s="28" t="inlineStr">
+      <c r="I17" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J17" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-scientist-at-fund-for-public-health-in-nyc-4378557045?refId=JsndNRa0tnfF7dsuxv62wA%3D%3D&amp;trackingId=Pmgt6JCxYmQun5Uv6%2BLbiQ%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K17" s="26" t="inlineStr">
+      <c r="K17" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-fund-for-public-health-in-nyc-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L17" s="26" t="inlineStr">
+      <c r="L17" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-fund-for-public-health-in-nyc-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M17" s="26" t="inlineStr"/>
+      <c r="M17" s="29" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="29" t="inlineStr">
         <is>
           <t>linkedin_4402977457</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D18" s="26" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E18" s="26" t="inlineStr">
+      <c r="E18" s="29" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F18" s="26" t="inlineStr">
+      <c r="F18" s="29" t="inlineStr">
         <is>
           <t>Brussels, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G18" s="26" t="inlineStr">
+      <c r="G18" s="29" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H18" s="26" t="inlineStr">
+      <c r="H18" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I18" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J18" s="28" t="inlineStr">
+      <c r="I18" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J18" s="31" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402977457?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=gL9sbQh%2FaLMmzvXjuO71WQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K18" s="26" t="inlineStr">
+      <c r="K18" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L18" s="26" t="inlineStr">
+      <c r="L18" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M18" s="26" t="inlineStr"/>
+      <c r="M18" s="29" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="A19" s="29" t="inlineStr">
         <is>
           <t>linkedin_4371210537</t>
         </is>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D19" s="26" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D19" s="29" t="inlineStr">
         <is>
           <t>Gildan</t>
         </is>
       </c>
-      <c r="E19" s="26" t="inlineStr">
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>Intern, ERP GenAI</t>
         </is>
       </c>
-      <c r="F19" s="26" t="inlineStr">
+      <c r="F19" s="29" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G19" s="26" t="inlineStr">
+      <c r="G19" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H19" s="26" t="inlineStr">
+      <c r="H19" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 15:23 UTC</t>
         </is>
       </c>
-      <c r="I19" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J19" s="28" t="inlineStr">
+      <c r="I19" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J19" s="31" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/intern-erp-genai-at-gildan-4371210537?refId=jteS%2Ft3Cmc2XLVMFToCpKw%3D%3D&amp;trackingId=OQGg%2Bob2m9u4kkbRcgWoUw%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K19" s="26" t="inlineStr">
+      <c r="K19" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-gildan-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L19" s="26" t="inlineStr">
+      <c r="L19" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-gildan-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M19" s="26" t="inlineStr"/>
+      <c r="M19" s="29" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>linkedin_4402974624</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D20" s="29" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E20" s="26" t="inlineStr">
+      <c r="E20" s="29" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F20" s="26" t="inlineStr">
+      <c r="F20" s="29" t="inlineStr">
         <is>
           <t>Uccle, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G20" s="26" t="inlineStr">
+      <c r="G20" s="29" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H20" s="26" t="inlineStr">
+      <c r="H20" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I20" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J20" s="28" t="inlineStr">
+      <c r="I20" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J20" s="31" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402974624?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=RJfkVsuYxv4DqyEhPJ367g%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K20" s="26" t="inlineStr">
+      <c r="K20" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L20" s="26" t="inlineStr">
+      <c r="L20" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M20" s="26" t="inlineStr"/>
+      <c r="M20" s="29" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>linkedin_4402174633</t>
         </is>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D21" s="26" t="inlineStr">
+      <c r="C21" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D21" s="29" t="inlineStr">
         <is>
           <t>Cloudera</t>
         </is>
       </c>
-      <c r="E21" s="26" t="inlineStr">
+      <c r="E21" s="29" t="inlineStr">
         <is>
           <t>AI Enablement Intern (Ireland Based)</t>
         </is>
       </c>
-      <c r="F21" s="26" t="inlineStr">
+      <c r="F21" s="29" t="inlineStr">
         <is>
           <t>Greater Dublin</t>
         </is>
       </c>
-      <c r="G21" s="26" t="inlineStr">
+      <c r="G21" s="29" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H21" s="26" t="inlineStr">
+      <c r="H21" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 18:24 UTC</t>
         </is>
       </c>
-      <c r="I21" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J21" s="28" t="inlineStr">
+      <c r="I21" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J21" s="31" t="inlineStr">
         <is>
           <t>https://ie.linkedin.com/jobs/view/ai-enablement-intern-ireland-based-at-cloudera-4402174633?refId=d9iDz5spYJk0nIor701k5g%3D%3D&amp;trackingId=6OZvFiMQ12VqIzY6EqUe7A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K21" s="26" t="inlineStr">
+      <c r="K21" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-cloudera-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L21" s="26" t="inlineStr">
+      <c r="L21" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-cloudera-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M21" s="26" t="inlineStr"/>
+      <c r="M21" s="29" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="29" t="inlineStr">
         <is>
           <t>linkedin_4403115250</t>
         </is>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B22" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D22" s="26" t="inlineStr">
+      <c r="C22" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D22" s="29" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E22" s="26" t="inlineStr">
+      <c r="E22" s="29" t="inlineStr">
         <is>
           <t>PhD Research Intern, Mapping Software</t>
         </is>
       </c>
-      <c r="F22" s="26" t="inlineStr">
+      <c r="F22" s="29" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G22" s="26" t="inlineStr">
+      <c r="G22" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H22" s="26" t="inlineStr">
+      <c r="H22" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 19:55 UTC</t>
         </is>
       </c>
-      <c r="I22" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J22" s="28" t="inlineStr">
+      <c r="I22" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J22" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-mapping-software-at-zoox-4403115250?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=67WsHxTIXiO%2ByWr0OYU7ug%3D%3D&amp;position=10&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K22" s="26" t="inlineStr">
+      <c r="K22" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L22" s="26" t="inlineStr">
+      <c r="L22" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M22" s="26" t="inlineStr"/>
+      <c r="M22" s="29" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>linkedin_4379373115</t>
         </is>
       </c>
-      <c r="B23" s="26" t="inlineStr">
+      <c r="B23" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D23" s="26" t="inlineStr">
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D23" s="29" t="inlineStr">
         <is>
           <t>Woven by Toyota</t>
         </is>
       </c>
-      <c r="E23" s="26" t="inlineStr">
+      <c r="E23" s="29" t="inlineStr">
         <is>
           <t>Applied Scientist, Computer Vision and Generative Models, Vision AI (Internship)</t>
         </is>
       </c>
-      <c r="F23" s="26" t="inlineStr">
+      <c r="F23" s="29" t="inlineStr">
         <is>
           <t>Tokyo, Japan</t>
         </is>
       </c>
-      <c r="G23" s="26" t="inlineStr">
+      <c r="G23" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H23" s="26" t="inlineStr">
+      <c r="H23" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 14:55 UTC</t>
         </is>
       </c>
-      <c r="I23" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J23" s="28" t="inlineStr">
+      <c r="I23" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J23" s="31" t="inlineStr">
         <is>
           <t>https://jp.linkedin.com/jobs/view/applied-scientist-computer-vision-and-generative-models-vision-ai-internship-at-woven-by-toyota-4379373115?refId=4q6ISAXJ%2BcfZsJD688QZWg%3D%3D&amp;trackingId=pUnO9OuzZx4G6BOukom%2FQQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K23" s="26" t="inlineStr">
+      <c r="K23" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-woven-by-toyota-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L23" s="26" t="inlineStr">
+      <c r="L23" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-woven-by-toyota-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M23" s="26" t="inlineStr"/>
+      <c r="M23" s="29" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="29" t="inlineStr">
         <is>
           <t>linkedin_4325103488</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D24" s="26" t="inlineStr">
+      <c r="C24" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D24" s="29" t="inlineStr">
         <is>
           <t>Binance</t>
         </is>
       </c>
-      <c r="E24" s="26" t="inlineStr">
+      <c r="E24" s="29" t="inlineStr">
         <is>
           <t>Binance Accelerator Program - DevOps (Artificial Intelligence)</t>
         </is>
       </c>
-      <c r="F24" s="26" t="inlineStr">
+      <c r="F24" s="29" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G24" s="26" t="inlineStr">
+      <c r="G24" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H24" s="26" t="inlineStr">
+      <c r="H24" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 12:13 UTC</t>
         </is>
       </c>
-      <c r="I24" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J24" s="28" t="inlineStr">
+      <c r="I24" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J24" s="31" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/binance-accelerator-program-devops-artificial-intelligence-at-binance-4325103488?refId=KzaD5RMOfYQEZyaw6UmcpQ%3D%3D&amp;trackingId=8R4okHiG3RYyjThXHAqxIQ%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K24" s="26" t="inlineStr">
+      <c r="K24" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-binance-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L24" s="26" t="inlineStr">
+      <c r="L24" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-binance-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M24" s="26" t="inlineStr"/>
+      <c r="M24" s="29" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="29" t="inlineStr">
         <is>
           <t>linkedin_4400563251</t>
         </is>
       </c>
-      <c r="B25" s="26" t="inlineStr">
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D25" s="26" t="inlineStr">
+      <c r="C25" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D25" s="29" t="inlineStr">
         <is>
           <t>Aylo</t>
         </is>
       </c>
-      <c r="E25" s="26" t="inlineStr">
+      <c r="E25" s="29" t="inlineStr">
         <is>
           <t>Sr. Full-Stack Data Scientist - Data Services</t>
         </is>
       </c>
-      <c r="F25" s="26" t="inlineStr">
+      <c r="F25" s="29" t="inlineStr">
         <is>
           <t>Greater Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G25" s="26" t="inlineStr">
+      <c r="G25" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H25" s="26" t="inlineStr">
+      <c r="H25" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 12:01 UTC</t>
         </is>
       </c>
-      <c r="I25" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J25" s="28" t="inlineStr">
+      <c r="I25" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J25" s="31" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/sr-full-stack-data-scientist-data-services-at-aylo-4400563251?refId=3X2hsLwn0XF5%2BC4ABneEzA%3D%3D&amp;trackingId=aJHp5psMKfAaMJdxBAz5Hw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K25" s="26" t="inlineStr">
+      <c r="K25" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-aylo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L25" s="26" t="inlineStr">
+      <c r="L25" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-aylo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M25" s="26" t="inlineStr"/>
+      <c r="M25" s="29" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="29" t="inlineStr">
         <is>
           <t>linkedin_4400403670</t>
         </is>
       </c>
-      <c r="B26" s="26" t="inlineStr">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C26" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D26" s="26" t="inlineStr">
+      <c r="C26" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D26" s="29" t="inlineStr">
         <is>
           <t>Schneider Electric</t>
         </is>
       </c>
-      <c r="E26" s="26" t="inlineStr">
+      <c r="E26" s="29" t="inlineStr">
         <is>
           <t>Internship in Global AI Sales Enablement &amp; Analytics</t>
         </is>
       </c>
-      <c r="F26" s="26" t="inlineStr">
+      <c r="F26" s="29" t="inlineStr">
         <is>
           <t>Warsaw, Mazowieckie, Poland</t>
         </is>
       </c>
-      <c r="G26" s="26" t="inlineStr">
+      <c r="G26" s="29" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H26" s="26" t="inlineStr">
+      <c r="H26" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 11:43 UTC</t>
         </is>
       </c>
-      <c r="I26" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J26" s="28" t="inlineStr">
+      <c r="I26" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J26" s="31" t="inlineStr">
         <is>
           <t>https://pl.linkedin.com/jobs/view/internship-in-global-ai-sales-enablement-analytics-at-schneider-electric-4400403670?refId=0j6PfgagLJw81v3dQ49jXQ%3D%3D&amp;trackingId=ErR9yiUH1tcny4hRKbXl8A%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K26" s="26" t="inlineStr">
+      <c r="K26" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-schneider-electric-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L26" s="26" t="inlineStr">
+      <c r="L26" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-schneider-electric-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M26" s="26" t="inlineStr"/>
+      <c r="M26" s="29" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="26" t="inlineStr">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>linkedin_4297755027</t>
         </is>
       </c>
-      <c r="B27" s="26" t="inlineStr">
+      <c r="B27" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D27" s="26" t="inlineStr">
+      <c r="C27" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D27" s="29" t="inlineStr">
         <is>
           <t>Databricks</t>
         </is>
       </c>
-      <c r="E27" s="26" t="inlineStr">
+      <c r="E27" s="29" t="inlineStr">
         <is>
           <t>PhD GenAI Research Scientist Intern</t>
         </is>
       </c>
-      <c r="F27" s="26" t="inlineStr">
+      <c r="F27" s="29" t="inlineStr">
         <is>
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="G27" s="26" t="inlineStr">
+      <c r="G27" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H27" s="26" t="inlineStr">
+      <c r="H27" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 10:31 UTC</t>
         </is>
       </c>
-      <c r="I27" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J27" s="28" t="inlineStr">
+      <c r="I27" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J27" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-genai-research-scientist-intern-at-databricks-4297755027?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=UXoh9K97xsqO%2FzDhCy7Uug%3D%3D&amp;position=8&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K27" s="26" t="inlineStr">
+      <c r="K27" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-databricks-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L27" s="26" t="inlineStr">
+      <c r="L27" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-databricks-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M27" s="26" t="inlineStr"/>
+      <c r="M27" s="29" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="29" t="inlineStr">
         <is>
           <t>linkedin_4401843829</t>
         </is>
       </c>
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B28" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D28" s="26" t="inlineStr">
+      <c r="C28" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D28" s="29" t="inlineStr">
         <is>
           <t>Tiger Brokers Singapore</t>
         </is>
       </c>
-      <c r="E28" s="26" t="inlineStr">
+      <c r="E28" s="29" t="inlineStr">
         <is>
           <t>Quantitative Investment Analyst Intern</t>
         </is>
       </c>
-      <c r="F28" s="26" t="inlineStr">
+      <c r="F28" s="29" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G28" s="26" t="inlineStr">
+      <c r="G28" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H28" s="26" t="inlineStr">
+      <c r="H28" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 06:09 UTC</t>
         </is>
       </c>
-      <c r="I28" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J28" s="28" t="inlineStr">
+      <c r="I28" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J28" s="31" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/quantitative-investment-analyst-intern-at-tiger-brokers-singapore-4401843829?refId=LJ4PwcXqLhd1gtOBe9ZVig%3D%3D&amp;trackingId=oxh8Ol2m1QKvqfrvl10UqA%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K28" s="26" t="inlineStr">
+      <c r="K28" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-tiger-brokers-singapore-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L28" s="26" t="inlineStr">
+      <c r="L28" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-tiger-brokers-singapore-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M28" s="26" t="inlineStr"/>
+      <c r="M28" s="29" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="26" t="inlineStr">
+      <c r="A29" s="29" t="inlineStr">
         <is>
           <t>linkedin_4400148847</t>
         </is>
       </c>
-      <c r="B29" s="26" t="inlineStr">
+      <c r="B29" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C29" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D29" s="26" t="inlineStr">
+      <c r="C29" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D29" s="29" t="inlineStr">
         <is>
           <t>Boomlet</t>
         </is>
       </c>
-      <c r="E29" s="26" t="inlineStr">
+      <c r="E29" s="29" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F29" s="26" t="inlineStr">
+      <c r="F29" s="29" t="inlineStr">
         <is>
           <t>Mumbai, Maharashtra, India</t>
         </is>
       </c>
-      <c r="G29" s="26" t="inlineStr">
+      <c r="G29" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H29" s="26" t="inlineStr">
+      <c r="H29" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 05:24 UTC</t>
         </is>
       </c>
-      <c r="I29" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J29" s="28" t="inlineStr">
+      <c r="I29" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J29" s="31" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-boomlet-4400148847?refId=vAgiKqchg4pd6EgGGQ%2FF%2FA%3D%3D&amp;trackingId=IoHiSd1L28nXXarEd4gYfw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K29" s="26" t="inlineStr">
+      <c r="K29" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boomlet-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L29" s="26" t="inlineStr">
+      <c r="L29" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boomlet-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M29" s="26" t="inlineStr"/>
+      <c r="M29" s="29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" s="29" t="inlineStr">
         <is>
           <t>linkedin_4401844394</t>
         </is>
       </c>
-      <c r="B30" s="26" t="inlineStr">
+      <c r="B30" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D30" s="26" t="inlineStr">
+      <c r="C30" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D30" s="29" t="inlineStr">
         <is>
           <t>On-us</t>
         </is>
       </c>
-      <c r="E30" s="26" t="inlineStr">
+      <c r="E30" s="29" t="inlineStr">
         <is>
           <t>AI Business Analyst Summer Intern</t>
         </is>
       </c>
-      <c r="F30" s="26" t="inlineStr">
+      <c r="F30" s="29" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G30" s="26" t="inlineStr">
+      <c r="G30" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H30" s="26" t="inlineStr">
+      <c r="H30" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 04:56 UTC</t>
         </is>
       </c>
-      <c r="I30" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J30" s="28" t="inlineStr">
+      <c r="I30" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J30" s="31" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/ai-business-analyst-summer-intern-at-on-us-4401844394?refId=lslydLUu5l8kXOktysXYaw%3D%3D&amp;trackingId=BQ%2BoYgH5QtZKBWGZQgBfNQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K30" s="26" t="inlineStr">
+      <c r="K30" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-on-us-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L30" s="26" t="inlineStr">
+      <c r="L30" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-on-us-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M30" s="26" t="inlineStr"/>
+      <c r="M30" s="29" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t>linkedin_4401837715</t>
         </is>
       </c>
-      <c r="B31" s="26" t="inlineStr">
+      <c r="B31" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C31" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D31" s="26" t="inlineStr">
+      <c r="C31" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D31" s="29" t="inlineStr">
         <is>
           <t>Pathos Consultancy</t>
         </is>
       </c>
-      <c r="E31" s="26" t="inlineStr">
+      <c r="E31" s="29" t="inlineStr">
         <is>
           <t>Quantitative Research &amp; Development Internships</t>
         </is>
       </c>
-      <c r="F31" s="26" t="inlineStr">
+      <c r="F31" s="29" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G31" s="26" t="inlineStr">
+      <c r="G31" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H31" s="26" t="inlineStr">
+      <c r="H31" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 03:48 UTC</t>
         </is>
       </c>
-      <c r="I31" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J31" s="28" t="inlineStr">
+      <c r="I31" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J31" s="31" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/quantitative-research-development-internships-at-pathos-consultancy-4401837715?refId=KzaD5RMOfYQEZyaw6UmcpQ%3D%3D&amp;trackingId=eIGVr2dDtK%2F1o37C90xRoQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K31" s="26" t="inlineStr">
+      <c r="K31" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-pathos-consultancy-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L31" s="26" t="inlineStr">
+      <c r="L31" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-pathos-consultancy-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M31" s="26" t="inlineStr"/>
+      <c r="M31" s="29" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="29" t="inlineStr">
         <is>
           <t>linkedin_4402662606</t>
         </is>
       </c>
-      <c r="B32" s="26" t="inlineStr">
+      <c r="B32" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C32" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D32" s="26" t="inlineStr">
+      <c r="C32" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D32" s="29" t="inlineStr">
         <is>
           <t>Stripe</t>
         </is>
       </c>
-      <c r="E32" s="26" t="inlineStr">
+      <c r="E32" s="29" t="inlineStr">
         <is>
           <t>PhD Machine Learning Engineer, Intern</t>
         </is>
       </c>
-      <c r="F32" s="26" t="inlineStr">
+      <c r="F32" s="29" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G32" s="26" t="inlineStr">
+      <c r="G32" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H32" s="26" t="inlineStr">
+      <c r="H32" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 02:23 UTC</t>
         </is>
       </c>
-      <c r="I32" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J32" s="28" t="inlineStr">
+      <c r="I32" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J32" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-machine-learning-engineer-intern-at-stripe-4402662606?refId=vJILgNySaXYUQknbyaKZZQ%3D%3D&amp;trackingId=NDMzaPfHMoCKo5uxI3THcw%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K32" s="26" t="inlineStr">
+      <c r="K32" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L32" s="26" t="inlineStr">
+      <c r="L32" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M32" s="26" t="inlineStr"/>
+      <c r="M32" s="29" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="26" t="inlineStr">
+      <c r="A33" s="29" t="inlineStr">
         <is>
           <t>linkedin_4402953925</t>
         </is>
       </c>
-      <c r="B33" s="26" t="inlineStr">
+      <c r="B33" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C33" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D33" s="26" t="inlineStr">
+      <c r="C33" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D33" s="29" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E33" s="26" t="inlineStr">
+      <c r="E33" s="29" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F33" s="26" t="inlineStr">
+      <c r="F33" s="29" t="inlineStr">
         <is>
           <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
-      <c r="G33" s="26" t="inlineStr">
+      <c r="G33" s="29" t="inlineStr">
         <is>
           <t>Middle_East</t>
         </is>
       </c>
-      <c r="H33" s="26" t="inlineStr">
+      <c r="H33" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 00:00 UTC</t>
         </is>
       </c>
-      <c r="I33" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J33" s="28" t="inlineStr">
+      <c r="I33" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J33" s="31" t="inlineStr">
         <is>
           <t>https://ae.linkedin.com/jobs/view/research-intern-at-skycliff-it-4402953925?refId=f%2BmSR6Ncm83dISKgoQTrbw%3D%3D&amp;trackingId=CdPOXElDD3wJKKeBZSdWsw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K33" s="26" t="inlineStr">
+      <c r="K33" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L33" s="26" t="inlineStr">
+      <c r="L33" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M33" s="26" t="inlineStr"/>
+      <c r="M33" s="29" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="26" t="inlineStr">
+      <c r="A34" s="29" t="inlineStr">
         <is>
           <t>linkedin_4402617206</t>
         </is>
       </c>
-      <c r="B34" s="26" t="inlineStr">
+      <c r="B34" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C34" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D34" s="26" t="inlineStr">
+      <c r="C34" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D34" s="29" t="inlineStr">
         <is>
           <t>Stripe</t>
         </is>
       </c>
-      <c r="E34" s="26" t="inlineStr">
+      <c r="E34" s="29" t="inlineStr">
         <is>
           <t>PhD Machine Learning Engineer, Intern</t>
         </is>
       </c>
-      <c r="F34" s="26" t="inlineStr">
+      <c r="F34" s="29" t="inlineStr">
         <is>
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="G34" s="26" t="inlineStr">
+      <c r="G34" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H34" s="26" t="inlineStr">
+      <c r="H34" s="29" t="inlineStr">
         <is>
           <t>2026-04-15 20:25 UTC</t>
         </is>
       </c>
-      <c r="I34" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J34" s="28" t="inlineStr">
+      <c r="I34" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J34" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-machine-learning-engineer-intern-at-stripe-4402617206?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=yAc4U29LYJcrlQSUWWcubA%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K34" s="26" t="inlineStr">
+      <c r="K34" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L34" s="26" t="inlineStr">
+      <c r="L34" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M34" s="26" t="inlineStr"/>
+      <c r="M34" s="29" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="26" t="inlineStr">
+      <c r="A35" s="29" t="inlineStr">
         <is>
           <t>linkedin_4403183407</t>
         </is>
       </c>
-      <c r="B35" s="26" t="inlineStr">
+      <c r="B35" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C35" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D35" s="26" t="inlineStr">
+      <c r="C35" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D35" s="29" t="inlineStr">
         <is>
           <t>Hardware FYI</t>
         </is>
       </c>
-      <c r="E35" s="26" t="inlineStr">
+      <c r="E35" s="29" t="inlineStr">
         <is>
           <t>Robotics - Applied Scientist II Intern / Co-op - 2026 (Robotics, Manipulation, Perception, Motion Planning, Autonomous Mobile Robots, Computer Vision, Machine Learning, Controls, and more)</t>
         </is>
       </c>
-      <c r="F35" s="26" t="inlineStr">
+      <c r="F35" s="29" t="inlineStr">
         <is>
           <t>Boston, MA</t>
         </is>
       </c>
-      <c r="G35" s="26" t="inlineStr">
+      <c r="G35" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H35" s="26" t="inlineStr">
+      <c r="H35" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 04:31 UTC</t>
         </is>
       </c>
-      <c r="I35" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J35" s="28" t="inlineStr">
+      <c r="I35" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J35" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/robotics-applied-scientist-ii-intern-co-op-2026-robotics-manipulation-perception-motion-planning-autonomous-mobile-robots-computer-vision-machine-learning-controls-and-more-at-hardware-fyi-4403183407?refId=s5WxXRPJ8QU7G2WPi2yNiw%3D%3D&amp;trackingId=rjd%2F8qdM5kQMmADtGJgSSw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K35" s="26" t="inlineStr">
+      <c r="K35" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-hardware-fyi-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L35" s="26" t="inlineStr">
+      <c r="L35" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-hardware-fyi-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M35" s="26" t="inlineStr"/>
+      <c r="M35" s="29" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="26" t="inlineStr">
+      <c r="A36" s="29" t="inlineStr">
         <is>
           <t>linkedin_4403153262</t>
         </is>
       </c>
-      <c r="B36" s="26" t="inlineStr">
+      <c r="B36" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D36" s="26" t="inlineStr">
+      <c r="C36" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D36" s="29" t="inlineStr">
         <is>
           <t>Generali Malaysia</t>
         </is>
       </c>
-      <c r="E36" s="26" t="inlineStr">
+      <c r="E36" s="29" t="inlineStr">
         <is>
           <t>Intern, IT (AI Engineering)</t>
         </is>
       </c>
-      <c r="F36" s="26" t="inlineStr">
+      <c r="F36" s="29" t="inlineStr">
         <is>
           <t>Federal Territory of Kuala Lumpur, Malaysia</t>
         </is>
       </c>
-      <c r="G36" s="26" t="inlineStr">
+      <c r="G36" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H36" s="26" t="inlineStr">
+      <c r="H36" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 00:47 UTC</t>
         </is>
       </c>
-      <c r="I36" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J36" s="28" t="inlineStr">
+      <c r="I36" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J36" s="31" t="inlineStr">
         <is>
           <t>https://my.linkedin.com/jobs/view/intern-it-ai-engineering-at-generali-malaysia-4403153262?refId=h4J9hFjDRjjPW7bUqRcUZQ%3D%3D&amp;trackingId=WmqITEtGX486sbNH6b%2BYmA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K36" s="26" t="inlineStr">
+      <c r="K36" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-generali-malaysia-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L36" s="26" t="inlineStr">
+      <c r="L36" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-generali-malaysia-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M36" s="26" t="inlineStr"/>
+      <c r="M36" s="29" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="26" t="inlineStr">
+      <c r="A37" s="29" t="inlineStr">
         <is>
           <t>linkedin_4402311007</t>
         </is>
       </c>
-      <c r="B37" s="26" t="inlineStr">
+      <c r="B37" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C37" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D37" s="26" t="inlineStr">
+      <c r="C37" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D37" s="29" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E37" s="26" t="inlineStr">
+      <c r="E37" s="29" t="inlineStr">
         <is>
           <t>SAP iXp Intern - Customer Success Engineering, Operations &amp; AI Enablement [Boston]</t>
         </is>
       </c>
-      <c r="F37" s="26" t="inlineStr">
+      <c r="F37" s="29" t="inlineStr">
         <is>
           <t>Burlington, MA</t>
         </is>
       </c>
-      <c r="G37" s="26" t="inlineStr">
+      <c r="G37" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H37" s="26" t="inlineStr">
+      <c r="H37" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 21:40 UTC</t>
         </is>
       </c>
-      <c r="I37" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J37" s="28" t="inlineStr">
+      <c r="I37" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J37" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/sap-ixp-intern-%C2%A0customer-success-engineering-operations-ai-enablement-boston-at-sap-4402311007?refId=ofb0jzd8xWUoUtvr7A%2BwXQ%3D%3D&amp;trackingId=S%2Fo4FvRdeOcn00Jo5DVUBw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K37" s="26" t="inlineStr">
+      <c r="K37" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L37" s="26" t="inlineStr">
+      <c r="L37" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M37" s="26" t="inlineStr"/>
+      <c r="M37" s="29" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="26" t="inlineStr">
+      <c r="A38" s="29" t="inlineStr">
         <is>
           <t>linkedin_4403154707</t>
         </is>
       </c>
-      <c r="B38" s="26" t="inlineStr">
+      <c r="B38" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C38" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D38" s="26" t="inlineStr">
+      <c r="C38" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D38" s="29" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E38" s="26" t="inlineStr">
+      <c r="E38" s="29" t="inlineStr">
         <is>
           <t>Software Engineer Intern, Perception Data</t>
         </is>
       </c>
-      <c r="F38" s="26" t="inlineStr">
+      <c r="F38" s="29" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G38" s="26" t="inlineStr">
+      <c r="G38" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H38" s="26" t="inlineStr">
+      <c r="H38" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 02:21 UTC</t>
         </is>
       </c>
-      <c r="I38" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J38" s="28" t="inlineStr">
+      <c r="I38" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J38" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/software-engineer-intern-perception-data-at-zoox-4403154707?refId=ON4L5FUhksKAgylRRsNllQ%3D%3D&amp;trackingId=1%2F3OkqP%2Bu0PqHp9bXnlS0A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K38" s="26" t="inlineStr">
+      <c r="K38" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L38" s="26" t="inlineStr">
+      <c r="L38" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M38" s="26" t="inlineStr"/>
+      <c r="M38" s="29" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="26" t="inlineStr">
+      <c r="A39" s="29" t="inlineStr">
         <is>
           <t>linkedin_4402947451</t>
         </is>
       </c>
-      <c r="B39" s="26" t="inlineStr">
+      <c r="B39" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C39" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D39" s="26" t="inlineStr">
+      <c r="C39" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D39" s="29" t="inlineStr">
         <is>
           <t>Rubrik</t>
         </is>
       </c>
-      <c r="E39" s="26" t="inlineStr">
+      <c r="E39" s="29" t="inlineStr">
         <is>
           <t>India Benefits &amp; AI Operations Intern</t>
         </is>
       </c>
-      <c r="F39" s="26" t="inlineStr">
+      <c r="F39" s="29" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G39" s="26" t="inlineStr">
+      <c r="G39" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H39" s="26" t="inlineStr">
+      <c r="H39" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 11:40 UTC</t>
         </is>
       </c>
-      <c r="I39" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J39" s="28" t="inlineStr">
+      <c r="I39" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J39" s="31" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/india-benefits-ai-operations-intern-at-rubrik-4402947451?refId=9u2uyUYzyMZimaTtDELDWg%3D%3D&amp;trackingId=BjOmyeYm6McmUpzLwcES9g%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K39" s="26" t="inlineStr">
+      <c r="K39" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-rubrik-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L39" s="26" t="inlineStr">
+      <c r="L39" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-rubrik-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M39" s="26" t="inlineStr"/>
+      <c r="M39" s="29" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="26" t="inlineStr">
+      <c r="A40" s="29" t="inlineStr">
         <is>
           <t>linkedin_4390354006</t>
         </is>
       </c>
-      <c r="B40" s="26" t="inlineStr">
+      <c r="B40" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C40" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D40" s="26" t="inlineStr">
+      <c r="C40" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D40" s="29" t="inlineStr">
         <is>
           <t>Lila Sciences</t>
         </is>
       </c>
-      <c r="E40" s="26" t="inlineStr">
+      <c r="E40" s="29" t="inlineStr">
         <is>
           <t>Intern, Next Gen AI Robotics</t>
         </is>
       </c>
-      <c r="F40" s="26" t="inlineStr">
+      <c r="F40" s="29" t="inlineStr">
         <is>
           <t>Cambridge, MA</t>
         </is>
       </c>
-      <c r="G40" s="26" t="inlineStr">
+      <c r="G40" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H40" s="26" t="inlineStr">
+      <c r="H40" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 10:58 UTC</t>
         </is>
       </c>
-      <c r="I40" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J40" s="28" t="inlineStr">
+      <c r="I40" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J40" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/intern-next-gen-ai-robotics-at-lila-sciences-4390354006?refId=ZoXJQXesL%2FE%2B5EAGGzWfiA%3D%3D&amp;trackingId=FmSMwWhyyIaC52NsDwOCtw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K40" s="26" t="inlineStr">
+      <c r="K40" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-lila-sciences-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L40" s="26" t="inlineStr">
+      <c r="L40" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-lila-sciences-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M40" s="26" t="inlineStr"/>
+      <c r="M40" s="29" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="26" t="inlineStr">
+      <c r="A41" s="29" t="inlineStr">
         <is>
           <t>arbeitnow_ai-venture-development-tech-intern-berlin-100382</t>
         </is>
       </c>
-      <c r="B41" s="26" t="inlineStr">
+      <c r="B41" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C41" s="26" t="inlineStr">
+      <c r="C41" s="29" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="D41" s="26" t="inlineStr">
+      <c r="D41" s="29" t="inlineStr">
         <is>
           <t>Zeeg</t>
         </is>
       </c>
-      <c r="E41" s="26" t="inlineStr">
+      <c r="E41" s="29" t="inlineStr">
         <is>
           <t>AI &amp; Venture Development Tech Intern (w/m/d)</t>
         </is>
       </c>
-      <c r="F41" s="26" t="inlineStr">
+      <c r="F41" s="29" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="G41" s="26" t="inlineStr">
+      <c r="G41" s="29" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H41" s="26" t="inlineStr">
+      <c r="H41" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 10:30 UTC</t>
         </is>
       </c>
-      <c r="I41" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J41" s="28" t="inlineStr">
+      <c r="I41" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J41" s="31" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/zeeg/ai-venture-development-tech-intern-berlin-100382</t>
         </is>
       </c>
-      <c r="K41" s="26" t="inlineStr">
+      <c r="K41" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zeeg-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L41" s="26" t="inlineStr">
+      <c r="L41" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zeeg-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M41" s="26" t="inlineStr"/>
+      <c r="M41" s="29" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="26" t="inlineStr">
+      <c r="A42" s="29" t="inlineStr">
         <is>
           <t>linkedin_4391388054</t>
         </is>
       </c>
-      <c r="B42" s="26" t="inlineStr">
+      <c r="B42" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C42" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D42" s="26" t="inlineStr">
+      <c r="C42" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D42" s="29" t="inlineStr">
         <is>
           <t>Mackenzie Investments</t>
         </is>
       </c>
-      <c r="E42" s="26" t="inlineStr">
+      <c r="E42" s="29" t="inlineStr">
         <is>
           <t>Fall Intern 2026 - Data Science (Toronto Office)</t>
         </is>
       </c>
-      <c r="F42" s="26" t="inlineStr">
+      <c r="F42" s="29" t="inlineStr">
         <is>
           <t>Greater Toronto Area, Canada</t>
         </is>
       </c>
-      <c r="G42" s="26" t="inlineStr">
+      <c r="G42" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H42" s="26" t="inlineStr">
+      <c r="H42" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 14:00 UTC</t>
         </is>
       </c>
-      <c r="I42" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J42" s="28" t="inlineStr">
+      <c r="I42" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J42" s="31" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/fall-intern-2026-data-science-toronto-office-at-mackenzie-investments-4391388054?refId=ay8O%2Bgf7Gtfb1Rpr3XZOhg%3D%3D&amp;trackingId=O%2F%2FJTpCmUhvp4jSfNkV5bg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K42" s="26" t="inlineStr">
+      <c r="K42" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-mackenzie-investments-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L42" s="26" t="inlineStr">
+      <c r="L42" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-mackenzie-investments-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M42" s="26" t="inlineStr"/>
+      <c r="M42" s="29" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="26" t="inlineStr">
+      <c r="A43" s="29" t="inlineStr">
         <is>
           <t>linkedin_4390747937</t>
         </is>
       </c>
-      <c r="B43" s="26" t="inlineStr">
+      <c r="B43" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C43" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D43" s="26" t="inlineStr">
+      <c r="C43" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D43" s="29" t="inlineStr">
         <is>
           <t>BCG X</t>
         </is>
       </c>
-      <c r="E43" s="26" t="inlineStr">
+      <c r="E43" s="29" t="inlineStr">
         <is>
           <t>Visiting Forward Deployed AI Engineer, Internship, Germany - BCG X</t>
         </is>
       </c>
-      <c r="F43" s="26" t="inlineStr">
+      <c r="F43" s="29" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G43" s="26" t="inlineStr">
+      <c r="G43" s="29" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H43" s="26" t="inlineStr">
+      <c r="H43" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 13:51 UTC</t>
         </is>
       </c>
-      <c r="I43" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J43" s="28" t="inlineStr">
+      <c r="I43" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J43" s="31" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/visiting-forward-deployed-ai-engineer-internship-germany-bcg-x-at-bcg-x-4390747937?refId=1JxxxPqdlRpkbbaCzu2YGQ%3D%3D&amp;trackingId=7x%2BVQU%2BWOh9IPaVXWJkc5g%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K43" s="26" t="inlineStr">
+      <c r="K43" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bcg-x-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L43" s="26" t="inlineStr">
+      <c r="L43" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bcg-x-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M43" s="26" t="inlineStr"/>
+      <c r="M43" s="29" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="26" t="inlineStr">
+      <c r="A44" s="29" t="inlineStr">
         <is>
           <t>linkedin_4402726053</t>
         </is>
       </c>
-      <c r="B44" s="26" t="inlineStr">
+      <c r="B44" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C44" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D44" s="26" t="inlineStr">
+      <c r="C44" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D44" s="29" t="inlineStr">
         <is>
           <t>targetjobs UK</t>
         </is>
       </c>
-      <c r="E44" s="26" t="inlineStr">
+      <c r="E44" s="29" t="inlineStr">
         <is>
           <t>Internship: AI/ML for Ionospheric TEC Modelling</t>
         </is>
       </c>
-      <c r="F44" s="26" t="inlineStr">
+      <c r="F44" s="29" t="inlineStr">
         <is>
           <t>Reigate, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G44" s="26" t="inlineStr">
+      <c r="G44" s="29" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H44" s="26" t="inlineStr">
+      <c r="H44" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 14:25 UTC</t>
         </is>
       </c>
-      <c r="I44" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J44" s="28" t="inlineStr">
+      <c r="I44" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J44" s="31" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/internship-ai-ml-for-ionospheric-tec-modelling-at-targetjobs-uk-4402726053?refId=a1g6hMZsvI1y2Eje2OvLAA%3D%3D&amp;trackingId=IVJSJGE7Non8cohorDs%2F5A%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K44" s="26" t="inlineStr">
+      <c r="K44" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-targetjobs-uk-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L44" s="26" t="inlineStr">
+      <c r="L44" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-targetjobs-uk-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M44" s="26" t="inlineStr"/>
+      <c r="M44" s="29" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="26" t="inlineStr">
+      <c r="A45" s="29" t="inlineStr">
         <is>
           <t>linkedin_4400837114</t>
         </is>
       </c>
-      <c r="B45" s="26" t="inlineStr">
+      <c r="B45" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C45" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D45" s="26" t="inlineStr">
+      <c r="C45" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D45" s="29" t="inlineStr">
         <is>
           <t>Innovexis</t>
         </is>
       </c>
-      <c r="E45" s="26" t="inlineStr">
+      <c r="E45" s="29" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F45" s="26" t="inlineStr">
+      <c r="F45" s="29" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G45" s="26" t="inlineStr">
+      <c r="G45" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H45" s="26" t="inlineStr">
+      <c r="H45" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 13:04 UTC</t>
         </is>
       </c>
-      <c r="I45" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J45" s="28" t="inlineStr">
+      <c r="I45" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J45" s="31" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-innovexis-4400837114?refId=CVM89%2F3%2F%2BshqMJLc4IfFMg%3D%3D&amp;trackingId=j9WpQwI4k1ip7aRr%2Fv5Img%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K45" s="26" t="inlineStr">
+      <c r="K45" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-innovexis-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L45" s="26" t="inlineStr">
+      <c r="L45" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-innovexis-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M45" s="26" t="inlineStr"/>
+      <c r="M45" s="29" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="26" t="inlineStr">
+      <c r="A46" s="29" t="inlineStr">
         <is>
           <t>linkedin_4391074158</t>
         </is>
       </c>
-      <c r="B46" s="26" t="inlineStr">
+      <c r="B46" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C46" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D46" s="26" t="inlineStr">
+      <c r="C46" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D46" s="29" t="inlineStr">
         <is>
           <t>BMW Group</t>
         </is>
       </c>
-      <c r="E46" s="26" t="inlineStr">
+      <c r="E46" s="29" t="inlineStr">
         <is>
           <t>Intern IT Technology, Sales Volume Planning &amp; AI Support (f/m/x)</t>
         </is>
       </c>
-      <c r="F46" s="26" t="inlineStr">
+      <c r="F46" s="29" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G46" s="26" t="inlineStr">
+      <c r="G46" s="29" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H46" s="26" t="inlineStr">
+      <c r="H46" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 12:45 UTC</t>
         </is>
       </c>
-      <c r="I46" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J46" s="28" t="inlineStr">
+      <c r="I46" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J46" s="31" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/intern-it-technology-sales-volume-planning-ai-support-f-m-x-at-bmw-group-4391074158?refId=tHG5EqbLn3IDBqsSj%2FsUUg%3D%3D&amp;trackingId=OakOlgDcU0hWTRXcoLe3UA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K46" s="26" t="inlineStr">
+      <c r="K46" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bmw-group-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L46" s="26" t="inlineStr">
+      <c r="L46" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bmw-group-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M46" s="26" t="inlineStr"/>
+      <c r="M46" s="29" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="26" t="inlineStr">
+      <c r="A47" s="29" t="inlineStr">
         <is>
           <t>linkedin_4402725075</t>
         </is>
       </c>
-      <c r="B47" s="26" t="inlineStr">
+      <c r="B47" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C47" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D47" s="26" t="inlineStr">
+      <c r="C47" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D47" s="29" t="inlineStr">
         <is>
           <t>DARE</t>
         </is>
       </c>
-      <c r="E47" s="26" t="inlineStr">
+      <c r="E47" s="29" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F47" s="26" t="inlineStr">
+      <c r="F47" s="29" t="inlineStr">
         <is>
           <t>WP. Kuala Lumpur, Federal Territory of Kuala Lumpur, Malaysia</t>
         </is>
       </c>
-      <c r="G47" s="26" t="inlineStr">
+      <c r="G47" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H47" s="26" t="inlineStr">
+      <c r="H47" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 14:36 UTC</t>
         </is>
       </c>
-      <c r="I47" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J47" s="28" t="inlineStr">
+      <c r="I47" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J47" s="31" t="inlineStr">
         <is>
           <t>https://my.linkedin.com/jobs/view/research-intern-at-dare-4402725075?refId=xbzZXyF6FfcYy036eklDWw%3D%3D&amp;trackingId=QRt5DhbLSINvmHia0jEWIg%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K47" s="26" t="inlineStr">
+      <c r="K47" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dare-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L47" s="26" t="inlineStr">
+      <c r="L47" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dare-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M47" s="26" t="inlineStr"/>
+      <c r="M47" s="29" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="26" t="inlineStr">
+      <c r="A48" s="29" t="inlineStr">
         <is>
           <t>linkedin_4402745391</t>
         </is>
       </c>
-      <c r="B48" s="26" t="inlineStr">
+      <c r="B48" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C48" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D48" s="26" t="inlineStr">
+      <c r="C48" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D48" s="29" t="inlineStr">
         <is>
           <t>Huawei Technologies Research &amp; Development (UK) Ltd</t>
         </is>
       </c>
-      <c r="E48" s="26" t="inlineStr">
+      <c r="E48" s="29" t="inlineStr">
         <is>
           <t>Research Intern - Computer Vision</t>
         </is>
       </c>
-      <c r="F48" s="26" t="inlineStr">
+      <c r="F48" s="29" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G48" s="26" t="inlineStr">
+      <c r="G48" s="29" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H48" s="26" t="inlineStr">
+      <c r="H48" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 18:42 UTC</t>
         </is>
       </c>
-      <c r="I48" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J48" s="28" t="inlineStr">
+      <c r="I48" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J48" s="31" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/research-intern-computer-vision-at-huawei-technologies-research-development-uk-ltd-4402745391?refId=rRtCMQFBU%2FNi7vc62x5Nhg%3D%3D&amp;trackingId=%2Bt1We%2BmKhWHyXION%2FWwQVg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K48" s="26" t="inlineStr">
+      <c r="K48" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-huawei-technologies-research-development-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L48" s="26" t="inlineStr">
+      <c r="L48" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-huawei-technologies-research-development-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M48" s="26" t="inlineStr"/>
+      <c r="M48" s="29" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="26" t="inlineStr">
+      <c r="A49" s="29" t="inlineStr">
         <is>
           <t>linkedin_4402366780</t>
         </is>
       </c>
-      <c r="B49" s="26" t="inlineStr">
+      <c r="B49" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C49" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D49" s="26" t="inlineStr">
+      <c r="C49" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D49" s="29" t="inlineStr">
         <is>
           <t>Binance</t>
         </is>
       </c>
-      <c r="E49" s="26" t="inlineStr">
+      <c r="E49" s="29" t="inlineStr">
         <is>
           <t>Binance Accelerator Program - Data Scientist (LLM &amp; Trading)</t>
         </is>
       </c>
-      <c r="F49" s="26" t="inlineStr">
+      <c r="F49" s="29" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G49" s="26" t="inlineStr">
+      <c r="G49" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H49" s="26" t="inlineStr">
+      <c r="H49" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 09:43 UTC</t>
         </is>
       </c>
-      <c r="I49" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J49" s="28" t="inlineStr">
+      <c r="I49" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J49" s="31" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/binance-accelerator-program-data-scientist-llm-trading-at-binance-4402366780?refId=bc%2BXeBTeIKMQJTmlLFwbZQ%3D%3D&amp;trackingId=9UuyRRCEPapWNu6VKdZC5A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K49" s="26" t="inlineStr">
+      <c r="K49" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-binance-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L49" s="26" t="inlineStr">
+      <c r="L49" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-binance-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M49" s="26" t="inlineStr"/>
+      <c r="M49" s="29" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="26" t="inlineStr">
+      <c r="A50" s="29" t="inlineStr">
         <is>
           <t>linkedin_4382411039</t>
         </is>
       </c>
-      <c r="B50" s="26" t="inlineStr">
+      <c r="B50" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C50" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D50" s="26" t="inlineStr">
+      <c r="C50" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D50" s="29" t="inlineStr">
         <is>
           <t>The Walt Disney Company</t>
         </is>
       </c>
-      <c r="E50" s="26" t="inlineStr">
+      <c r="E50" s="29" t="inlineStr">
         <is>
           <t>Intern, APAC Data Analytics &amp; Insights (Content Analytics) -  Jul to Dec 2026</t>
         </is>
       </c>
-      <c r="F50" s="26" t="inlineStr">
+      <c r="F50" s="29" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G50" s="26" t="inlineStr">
+      <c r="G50" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H50" s="26" t="inlineStr">
+      <c r="H50" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 23:55 UTC</t>
         </is>
       </c>
-      <c r="I50" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J50" s="28" t="inlineStr">
+      <c r="I50" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J50" s="31" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/intern-apac-data-analytics-insights-content-analytics-jul-to-dec-2026-at-the-walt-disney-company-4382411039?refId=JBvXH2fNOamnO4WZI1Y0ew%3D%3D&amp;trackingId=Rs%2FdjczlbLYSYtCwY%2F%2FJyA%3D%3D&amp;position=7&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K50" s="26" t="inlineStr">
+      <c r="K50" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-the-walt-disney-company-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L50" s="26" t="inlineStr">
+      <c r="L50" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-the-walt-disney-company-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M50" s="26" t="inlineStr"/>
+      <c r="M50" s="29" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="26" t="inlineStr">
+      <c r="A51" s="29" t="inlineStr">
         <is>
           <t>linkedin_4402305263</t>
         </is>
       </c>
-      <c r="B51" s="26" t="inlineStr">
+      <c r="B51" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C51" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D51" s="26" t="inlineStr">
+      <c r="C51" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D51" s="29" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E51" s="26" t="inlineStr">
+      <c r="E51" s="29" t="inlineStr">
         <is>
           <t>SAP iXp Intern - Software Developer (Agentic AI &amp; LLM systems)</t>
         </is>
       </c>
-      <c r="F51" s="26" t="inlineStr">
+      <c r="F51" s="29" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G51" s="26" t="inlineStr">
+      <c r="G51" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H51" s="26" t="inlineStr">
+      <c r="H51" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 21:40 UTC</t>
         </is>
       </c>
-      <c r="I51" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J51" s="28" t="inlineStr">
+      <c r="I51" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J51" s="31" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/sap-ixp-intern-software-developer-agentic-ai-llm-systems-at-sap-4402305263?refId=zBXuSSlfFyuxcdEqyfeS8g%3D%3D&amp;trackingId=Imq%2FVHMQWkkoDZp5%2BnATSA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K51" s="26" t="inlineStr">
+      <c r="K51" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L51" s="26" t="inlineStr">
+      <c r="L51" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M51" s="26" t="inlineStr"/>
+      <c r="M51" s="29" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="26" t="inlineStr">
+      <c r="A52" s="29" t="inlineStr">
         <is>
           <t>linkedin_4400467080</t>
         </is>
       </c>
-      <c r="B52" s="26" t="inlineStr">
+      <c r="B52" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C52" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D52" s="26" t="inlineStr">
+      <c r="C52" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D52" s="29" t="inlineStr">
         <is>
           <t>Saama</t>
         </is>
       </c>
-      <c r="E52" s="26" t="inlineStr">
+      <c r="E52" s="29" t="inlineStr">
         <is>
           <t>Intern for AI CoE</t>
         </is>
       </c>
-      <c r="F52" s="26" t="inlineStr">
+      <c r="F52" s="29" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G52" s="26" t="inlineStr">
+      <c r="G52" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H52" s="26" t="inlineStr">
+      <c r="H52" s="29" t="inlineStr">
         <is>
           <t>2026-04-16 19:45 UTC</t>
         </is>
       </c>
-      <c r="I52" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J52" s="28" t="inlineStr">
+      <c r="I52" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J52" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/intern-for-ai-coe-at-saama-4400467080?refId=7CvDuV2%2BR%2FzyGozq4UNPPw%3D%3D&amp;trackingId=Ls9yWFAC8lVRx8bmapJfLA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K52" s="26" t="inlineStr">
+      <c r="K52" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-saama-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L52" s="26" t="inlineStr">
+      <c r="L52" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-saama-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M52" s="26" t="inlineStr"/>
+      <c r="M52" s="29" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="26" t="inlineStr">
+      <c r="A53" s="29" t="inlineStr">
         <is>
           <t>linkedin_4400873418</t>
         </is>
       </c>
-      <c r="B53" s="26" t="inlineStr">
+      <c r="B53" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C53" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D53" s="26" t="inlineStr">
+      <c r="C53" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D53" s="29" t="inlineStr">
         <is>
           <t>SANOVIO</t>
         </is>
       </c>
-      <c r="E53" s="26" t="inlineStr">
+      <c r="E53" s="29" t="inlineStr">
         <is>
           <t>AI Engineering Intern</t>
         </is>
       </c>
-      <c r="F53" s="26" t="inlineStr">
+      <c r="F53" s="29" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G53" s="26" t="inlineStr">
+      <c r="G53" s="29" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H53" s="26" t="inlineStr">
+      <c r="H53" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 00:00 UTC</t>
         </is>
       </c>
-      <c r="I53" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J53" s="28" t="inlineStr">
+      <c r="I53" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J53" s="31" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/ai-engineering-intern-at-sanovio-4400873418?refId=egIYeNLcARu6P6oTIZ%2BHfA%3D%3D&amp;trackingId=c6wZ0DtTzvVZpTRC1l5tYQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K53" s="26" t="inlineStr">
+      <c r="K53" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sanovio-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L53" s="26" t="inlineStr">
+      <c r="L53" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sanovio-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M53" s="26" t="inlineStr"/>
+      <c r="M53" s="29" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="26" t="inlineStr">
+      <c r="A54" s="29" t="inlineStr">
         <is>
           <t>linkedin_4403524251</t>
         </is>
       </c>
-      <c r="B54" s="26" t="inlineStr">
+      <c r="B54" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C54" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D54" s="26" t="inlineStr">
+      <c r="C54" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D54" s="29" t="inlineStr">
         <is>
           <t>Nascent Markets</t>
         </is>
       </c>
-      <c r="E54" s="26" t="inlineStr">
+      <c r="E54" s="29" t="inlineStr">
         <is>
           <t>Agentic Systems Intern (Graduate Level)</t>
         </is>
       </c>
-      <c r="F54" s="26" t="inlineStr">
+      <c r="F54" s="29" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G54" s="26" t="inlineStr">
+      <c r="G54" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H54" s="26" t="inlineStr">
+      <c r="H54" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 19:53 UTC</t>
         </is>
       </c>
-      <c r="I54" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J54" s="28" t="inlineStr">
+      <c r="I54" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J54" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/agentic-systems-intern-graduate-level-at-nascent-markets-4403524251?refId=Ix0g0waARRaNpzTY4LxvsQ%3D%3D&amp;trackingId=RsqyOyJHkanw%2FTeHGUcadA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K54" s="26" t="inlineStr">
+      <c r="K54" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-nascent-markets-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L54" s="26" t="inlineStr">
+      <c r="L54" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-nascent-markets-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M54" s="26" t="inlineStr"/>
+      <c r="M54" s="29" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="26" t="inlineStr">
+      <c r="A55" s="29" t="inlineStr">
         <is>
           <t>linkedin_4402782985</t>
         </is>
       </c>
-      <c r="B55" s="26" t="inlineStr">
+      <c r="B55" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C55" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D55" s="26" t="inlineStr">
+      <c r="C55" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D55" s="29" t="inlineStr">
         <is>
           <t>Axiomatic_AI</t>
         </is>
       </c>
-      <c r="E55" s="26" t="inlineStr">
+      <c r="E55" s="29" t="inlineStr">
         <is>
           <t>Internship - Research Intern (Agentic Learning, Memory &amp; Neurosymbolic Reasoning)</t>
         </is>
       </c>
-      <c r="F55" s="26" t="inlineStr">
+      <c r="F55" s="29" t="inlineStr">
         <is>
           <t>Greater Barcelona Metropolitan Area</t>
         </is>
       </c>
-      <c r="G55" s="26" t="inlineStr">
+      <c r="G55" s="29" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H55" s="26" t="inlineStr">
+      <c r="H55" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 05:04 UTC</t>
         </is>
       </c>
-      <c r="I55" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J55" s="28" t="inlineStr">
+      <c r="I55" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J55" s="31" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/internship-research-intern-agentic-learning-memory-neurosymbolic-reasoning-at-axiomatic-ai-4402782985?refId=vm6No12NjZrg2BBV%2BnbuLQ%3D%3D&amp;trackingId=X9FXk%2FBDFftROMNo9Cr20g%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K55" s="26" t="inlineStr">
+      <c r="K55" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-axiomatic-ai-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L55" s="26" t="inlineStr">
+      <c r="L55" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-axiomatic-ai-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M55" s="26" t="inlineStr"/>
+      <c r="M55" s="29" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="26" t="inlineStr">
+      <c r="A56" s="29" t="inlineStr">
         <is>
           <t>linkedin_4309694978</t>
         </is>
       </c>
-      <c r="B56" s="26" t="inlineStr">
+      <c r="B56" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C56" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D56" s="26" t="inlineStr">
+      <c r="C56" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D56" s="29" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E56" s="26" t="inlineStr">
+      <c r="E56" s="29" t="inlineStr">
         <is>
           <t>Graduate Physics Research Intern</t>
         </is>
       </c>
-      <c r="F56" s="26" t="inlineStr">
+      <c r="F56" s="29" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
       </c>
-      <c r="G56" s="26" t="inlineStr">
+      <c r="G56" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H56" s="26" t="inlineStr">
+      <c r="H56" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 17:37 UTC</t>
         </is>
       </c>
-      <c r="I56" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J56" s="28" t="inlineStr">
+      <c r="I56" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J56" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/graduate-physics-research-intern-at-dataannotation-4309694978?refId=hlpC50hTZs9sJFHirXWMSg%3D%3D&amp;trackingId=1E0ixzzpb6MzeHKgxpE3Cw%3D%3D&amp;position=9&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K56" s="26" t="inlineStr">
+      <c r="K56" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L56" s="26" t="inlineStr">
+      <c r="L56" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M56" s="26" t="inlineStr"/>
+      <c r="M56" s="29" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="26" t="inlineStr">
+      <c r="A57" s="29" t="inlineStr">
         <is>
           <t>linkedin_4403562730</t>
         </is>
       </c>
-      <c r="B57" s="26" t="inlineStr">
+      <c r="B57" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C57" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D57" s="26" t="inlineStr">
+      <c r="C57" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D57" s="29" t="inlineStr">
         <is>
           <t>BNM Business Solutions LLP</t>
         </is>
       </c>
-      <c r="E57" s="26" t="inlineStr">
+      <c r="E57" s="29" t="inlineStr">
         <is>
           <t>Data Analyst Internship in Navi Mumbai, Mumbai</t>
         </is>
       </c>
-      <c r="F57" s="26" t="inlineStr">
+      <c r="F57" s="29" t="inlineStr">
         <is>
           <t>Mumbai Metropolitan Region</t>
         </is>
       </c>
-      <c r="G57" s="26" t="inlineStr">
+      <c r="G57" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H57" s="26" t="inlineStr">
+      <c r="H57" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 00:06 UTC</t>
         </is>
       </c>
-      <c r="I57" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J57" s="28" t="inlineStr">
+      <c r="I57" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J57" s="31" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-internship-in-navi-mumbai-mumbai-at-bnm-business-solutions-llp-4403562730?refId=1X9LgKP3%2FAPeJuhZVjyhxw%3D%3D&amp;trackingId=oFY9Z69ZBEGkNtq0cbBOMw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K57" s="26" t="inlineStr">
+      <c r="K57" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bnm-business-solutions-llp-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L57" s="26" t="inlineStr">
+      <c r="L57" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bnm-business-solutions-llp-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M57" s="26" t="inlineStr"/>
+      <c r="M57" s="29" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="26" t="inlineStr">
+      <c r="A58" s="29" t="inlineStr">
         <is>
           <t>linkedin_4309694917</t>
         </is>
       </c>
-      <c r="B58" s="26" t="inlineStr">
+      <c r="B58" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C58" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D58" s="26" t="inlineStr">
+      <c r="C58" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D58" s="29" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E58" s="26" t="inlineStr">
+      <c r="E58" s="29" t="inlineStr">
         <is>
           <t>Graduate Biology Research Intern</t>
         </is>
       </c>
-      <c r="F58" s="26" t="inlineStr">
+      <c r="F58" s="29" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
       </c>
-      <c r="G58" s="26" t="inlineStr">
+      <c r="G58" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H58" s="26" t="inlineStr">
+      <c r="H58" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 17:35 UTC</t>
         </is>
       </c>
-      <c r="I58" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J58" s="28" t="inlineStr">
+      <c r="I58" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J58" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/graduate-biology-research-intern-at-dataannotation-4309694917?refId=hlpC50hTZs9sJFHirXWMSg%3D%3D&amp;trackingId=BM%2FBx4ElnXDk5hEpiM0gzg%3D%3D&amp;position=8&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K58" s="26" t="inlineStr">
+      <c r="K58" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L58" s="26" t="inlineStr">
+      <c r="L58" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M58" s="26" t="inlineStr"/>
+      <c r="M58" s="29" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="26" t="inlineStr">
+      <c r="A59" s="29" t="inlineStr">
         <is>
           <t>linkedin_4346088677</t>
         </is>
       </c>
-      <c r="B59" s="26" t="inlineStr">
+      <c r="B59" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C59" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D59" s="26" t="inlineStr">
+      <c r="C59" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D59" s="29" t="inlineStr">
         <is>
           <t>revel8</t>
         </is>
       </c>
-      <c r="E59" s="26" t="inlineStr">
+      <c r="E59" s="29" t="inlineStr">
         <is>
           <t>Applied AI Engineer Intern (all genders)</t>
         </is>
       </c>
-      <c r="F59" s="26" t="inlineStr">
+      <c r="F59" s="29" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G59" s="26" t="inlineStr">
+      <c r="G59" s="29" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H59" s="26" t="inlineStr">
+      <c r="H59" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 22:38 UTC</t>
         </is>
       </c>
-      <c r="I59" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J59" s="28" t="inlineStr">
+      <c r="I59" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J59" s="31" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/applied-ai-engineer-intern-all-genders-at-revel8-4346088677?refId=FHQDN2Ta3J6B7WhWnDAuhQ%3D%3D&amp;trackingId=Pf%2Ftwn6H5Hrw8BKjPenbSQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K59" s="26" t="inlineStr">
+      <c r="K59" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-revel8-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L59" s="26" t="inlineStr">
+      <c r="L59" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-revel8-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M59" s="26" t="inlineStr"/>
+      <c r="M59" s="29" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="26" t="inlineStr">
+      <c r="A60" s="29" t="inlineStr">
         <is>
           <t>linkedin_4403475387</t>
         </is>
       </c>
-      <c r="B60" s="26" t="inlineStr">
+      <c r="B60" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C60" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D60" s="26" t="inlineStr">
+      <c r="C60" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D60" s="29" t="inlineStr">
         <is>
           <t>Inc42 Media</t>
         </is>
       </c>
-      <c r="E60" s="26" t="inlineStr">
+      <c r="E60" s="29" t="inlineStr">
         <is>
           <t>Operations Intern: Inc42 AI Summit 2026</t>
         </is>
       </c>
-      <c r="F60" s="26" t="inlineStr">
+      <c r="F60" s="29" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G60" s="26" t="inlineStr">
+      <c r="G60" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H60" s="26" t="inlineStr">
+      <c r="H60" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 16:23 UTC</t>
         </is>
       </c>
-      <c r="I60" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J60" s="28" t="inlineStr">
+      <c r="I60" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J60" s="31" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/operations-intern-inc42-ai-summit-2026-at-inc42-media-4403475387?refId=jyI2mJ9xFT%2BmdtkV0OCW0g%3D%3D&amp;trackingId=6sWKnvWNaTU69%2B7bcZNxLg%3D%3D&amp;position=10&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K60" s="26" t="inlineStr">
+      <c r="K60" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-inc42-media-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L60" s="26" t="inlineStr">
+      <c r="L60" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-inc42-media-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M60" s="26" t="inlineStr"/>
+      <c r="M60" s="29" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="26" t="inlineStr">
+      <c r="A61" s="29" t="inlineStr">
         <is>
           <t>linkedin_4403008384</t>
         </is>
       </c>
-      <c r="B61" s="26" t="inlineStr">
+      <c r="B61" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C61" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D61" s="26" t="inlineStr">
+      <c r="C61" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D61" s="29" t="inlineStr">
         <is>
           <t>VEDANTA MOBILITY</t>
         </is>
       </c>
-      <c r="E61" s="26" t="inlineStr">
+      <c r="E61" s="29" t="inlineStr">
         <is>
           <t>Founding Psychology Interns | AI Prototype (Govt Proposal – Dubai)</t>
         </is>
       </c>
-      <c r="F61" s="26" t="inlineStr">
+      <c r="F61" s="29" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G61" s="26" t="inlineStr">
+      <c r="G61" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H61" s="26" t="inlineStr">
+      <c r="H61" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 08:13 UTC</t>
         </is>
       </c>
-      <c r="I61" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J61" s="28" t="inlineStr">
+      <c r="I61" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J61" s="31" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/founding-psychology-interns-ai-prototype-govt-proposal-%E2%80%93-dubai-at-vedanta-mobility-4403008384?refId=moHjgKNH%2BrT9YT5JNnyyqw%3D%3D&amp;trackingId=RUjUOgXLH%2BLJwdPLtKtAMQ%3D%3D&amp;position=13&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K61" s="26" t="inlineStr">
+      <c r="K61" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-vedanta-mobility-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L61" s="26" t="inlineStr">
+      <c r="L61" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-vedanta-mobility-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M61" s="26" t="inlineStr"/>
+      <c r="M61" s="29" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="26" t="inlineStr">
+      <c r="A62" s="29" t="inlineStr">
         <is>
           <t>linkedin_4393616864</t>
         </is>
       </c>
-      <c r="B62" s="26" t="inlineStr">
+      <c r="B62" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C62" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D62" s="26" t="inlineStr">
+      <c r="C62" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D62" s="29" t="inlineStr">
         <is>
           <t>Medidata Solutions</t>
         </is>
       </c>
-      <c r="E62" s="26" t="inlineStr">
+      <c r="E62" s="29" t="inlineStr">
         <is>
           <t>Data Science Intern</t>
         </is>
       </c>
-      <c r="F62" s="26" t="inlineStr">
+      <c r="F62" s="29" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
       </c>
-      <c r="G62" s="26" t="inlineStr">
+      <c r="G62" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H62" s="26" t="inlineStr">
+      <c r="H62" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 13:13 UTC</t>
         </is>
       </c>
-      <c r="I62" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J62" s="28" t="inlineStr">
+      <c r="I62" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J62" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-science-intern-at-medidata-solutions-4393616864?refId=sPMU%2B0UtbDUVjDHc3gXCxA%3D%3D&amp;trackingId=%2BVrdVCzEYQ3jJQvUf4VUtA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K62" s="26" t="inlineStr">
+      <c r="K62" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-medidata-solutions-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L62" s="26" t="inlineStr">
+      <c r="L62" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-medidata-solutions-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M62" s="26" t="inlineStr"/>
+      <c r="M62" s="29" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="26" t="inlineStr">
+      <c r="A63" s="29" t="inlineStr">
         <is>
           <t>linkedin_4403819462</t>
         </is>
       </c>
-      <c r="B63" s="26" t="inlineStr">
+      <c r="B63" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C63" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D63" s="26" t="inlineStr">
+      <c r="C63" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D63" s="29" t="inlineStr">
         <is>
           <t>Calypso Commodities</t>
         </is>
       </c>
-      <c r="E63" s="26" t="inlineStr">
+      <c r="E63" s="29" t="inlineStr">
         <is>
           <t>Trading - Quant &amp; Engineering Intern (Client-Facing)</t>
         </is>
       </c>
-      <c r="F63" s="26" t="inlineStr">
+      <c r="F63" s="29" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="G63" s="26" t="inlineStr">
+      <c r="G63" s="29" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H63" s="26" t="inlineStr">
+      <c r="H63" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 12:44 UTC</t>
         </is>
       </c>
-      <c r="I63" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J63" s="28" t="inlineStr">
+      <c r="I63" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J63" s="31" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/trading-quant-engineering-intern-client-facing-at-calypso-commodities-4403819462?refId=wb%2BADKYeCTj8bBBZgf97xw%3D%3D&amp;trackingId=o0ZBUwzyVOiml0tJPOsNww%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K63" s="26" t="inlineStr">
+      <c r="K63" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-calypso-commodities-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L63" s="26" t="inlineStr">
+      <c r="L63" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-calypso-commodities-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M63" s="26" t="inlineStr"/>
+      <c r="M63" s="29" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="26" t="inlineStr">
+      <c r="A64" s="29" t="inlineStr">
         <is>
           <t>linkedin_4355269413</t>
         </is>
       </c>
-      <c r="B64" s="26" t="inlineStr">
+      <c r="B64" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C64" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D64" s="26" t="inlineStr">
+      <c r="C64" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D64" s="29" t="inlineStr">
         <is>
           <t>Temasek</t>
         </is>
       </c>
-      <c r="E64" s="26" t="inlineStr">
+      <c r="E64" s="29" t="inlineStr">
         <is>
           <t>Data Analytics/Science Intern, People Technology (Jun/Jul - Dec 2026)</t>
         </is>
       </c>
-      <c r="F64" s="26" t="inlineStr">
+      <c r="F64" s="29" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G64" s="26" t="inlineStr">
+      <c r="G64" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H64" s="26" t="inlineStr">
+      <c r="H64" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 10:35 UTC</t>
         </is>
       </c>
-      <c r="I64" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J64" s="28" t="inlineStr">
+      <c r="I64" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J64" s="31" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/data-analytics-science-intern-people-technology-jun-jul-dec-2026-at-temasek-4355269413?refId=emjtNEhTXLtOX%2BguWexSsg%3D%3D&amp;trackingId=DPHM%2FIJzKL0emfNJ1LMMoA%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K64" s="26" t="inlineStr">
+      <c r="K64" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-temasek-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L64" s="26" t="inlineStr">
+      <c r="L64" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-temasek-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M64" s="26" t="inlineStr"/>
+      <c r="M64" s="29" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="26" t="inlineStr">
+      <c r="A65" s="29" t="inlineStr">
         <is>
           <t>linkedin_4403065097</t>
         </is>
       </c>
-      <c r="B65" s="26" t="inlineStr">
+      <c r="B65" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C65" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D65" s="26" t="inlineStr">
+      <c r="C65" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D65" s="29" t="inlineStr">
         <is>
           <t>BLACK TREE GAMING LIMITED</t>
         </is>
       </c>
-      <c r="E65" s="26" t="inlineStr">
+      <c r="E65" s="29" t="inlineStr">
         <is>
           <t>Data Scientist (ML)</t>
         </is>
       </c>
-      <c r="F65" s="26" t="inlineStr">
+      <c r="F65" s="29" t="inlineStr">
         <is>
           <t>Greater London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G65" s="26" t="inlineStr">
+      <c r="G65" s="29" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H65" s="26" t="inlineStr">
+      <c r="H65" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 14:22 UTC</t>
         </is>
       </c>
-      <c r="I65" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J65" s="28" t="inlineStr">
+      <c r="I65" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J65" s="31" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/data-scientist-ml-at-black-tree-gaming-limited-4403065097?refId=X9Gb9UkVv%2BJtfDRc0dJPwA%3D%3D&amp;trackingId=Mfl%2BC%2FBN9DJehDmug19dGA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K65" s="26" t="inlineStr">
+      <c r="K65" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-black-tree-gaming-limited-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L65" s="26" t="inlineStr">
+      <c r="L65" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-black-tree-gaming-limited-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M65" s="26" t="inlineStr"/>
+      <c r="M65" s="29" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="26" t="inlineStr">
+      <c r="A66" s="29" t="inlineStr">
         <is>
           <t>linkedin_4291533663</t>
         </is>
       </c>
-      <c r="B66" s="26" t="inlineStr">
+      <c r="B66" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C66" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D66" s="26" t="inlineStr">
+      <c r="C66" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D66" s="29" t="inlineStr">
         <is>
           <t>McKinsey &amp; Company</t>
         </is>
       </c>
-      <c r="E66" s="26" t="inlineStr">
+      <c r="E66" s="29" t="inlineStr">
         <is>
           <t>Praktikum als Fellow Intern - Tech &amp; AI (m/w/d)</t>
         </is>
       </c>
-      <c r="F66" s="26" t="inlineStr">
+      <c r="F66" s="29" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G66" s="26" t="inlineStr">
+      <c r="G66" s="29" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H66" s="26" t="inlineStr">
+      <c r="H66" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 09:49 UTC</t>
         </is>
       </c>
-      <c r="I66" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J66" s="28" t="inlineStr">
+      <c r="I66" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J66" s="31" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/praktikum-als-fellow-intern-tech-ai-m-w-d-at-mckinsey-company-4291533663?refId=UmiOr88gcWDNbqipJy2ZTg%3D%3D&amp;trackingId=UvtRxMXKlReoOEeGgMaEfA%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K66" s="26" t="inlineStr">
+      <c r="K66" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-mckinsey-company-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L66" s="26" t="inlineStr">
+      <c r="L66" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-mckinsey-company-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M66" s="26" t="inlineStr"/>
+      <c r="M66" s="29" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="26" t="inlineStr">
+      <c r="A67" s="29" t="inlineStr">
         <is>
           <t>linkedin_4336838608</t>
         </is>
       </c>
-      <c r="B67" s="26" t="inlineStr">
+      <c r="B67" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C67" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D67" s="26" t="inlineStr">
+      <c r="C67" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D67" s="29" t="inlineStr">
         <is>
           <t>Sendbird</t>
         </is>
       </c>
-      <c r="E67" s="26" t="inlineStr">
+      <c r="E67" s="29" t="inlineStr">
         <is>
           <t>AI Agent Engineer, Intern</t>
         </is>
       </c>
-      <c r="F67" s="26" t="inlineStr">
+      <c r="F67" s="29" t="inlineStr">
         <is>
           <t>Seoul, Seoul, South Korea</t>
         </is>
       </c>
-      <c r="G67" s="26" t="inlineStr">
+      <c r="G67" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H67" s="26" t="inlineStr">
+      <c r="H67" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 13:46 UTC</t>
         </is>
       </c>
-      <c r="I67" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J67" s="28" t="inlineStr">
+      <c r="I67" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J67" s="31" t="inlineStr">
         <is>
           <t>https://kr.linkedin.com/jobs/view/ai-agent-engineer-intern-at-sendbird-4336838608?refId=%2F1qLChSVn3giUiiNusHaIQ%3D%3D&amp;trackingId=l6mUUvSfC97HjoyrA8uuqg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K67" s="26" t="inlineStr">
+      <c r="K67" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sendbird-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L67" s="26" t="inlineStr">
+      <c r="L67" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sendbird-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M67" s="26" t="inlineStr"/>
+      <c r="M67" s="29" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="26" t="inlineStr">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>linkedin_4372783510</t>
         </is>
       </c>
-      <c r="B68" s="26" t="inlineStr">
+      <c r="B68" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C68" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D68" s="26" t="inlineStr">
+      <c r="C68" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D68" s="29" t="inlineStr">
         <is>
           <t>42dot</t>
         </is>
       </c>
-      <c r="E68" s="26" t="inlineStr">
+      <c r="E68" s="29" t="inlineStr">
         <is>
           <t>[MS/PhD Intern] AI Engineer (정규직 전환형)</t>
         </is>
       </c>
-      <c r="F68" s="26" t="inlineStr">
+      <c r="F68" s="29" t="inlineStr">
         <is>
           <t>Seongnam, Gyeonggi, South Korea</t>
         </is>
       </c>
-      <c r="G68" s="26" t="inlineStr">
+      <c r="G68" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H68" s="26" t="inlineStr">
+      <c r="H68" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 15:08 UTC</t>
         </is>
       </c>
-      <c r="I68" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J68" s="28" t="inlineStr">
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J68" s="31" t="inlineStr">
         <is>
           <t>https://kr.linkedin.com/jobs/view/ms-phd-intern-ai-engineer-%EC%A0%95%EA%B7%9C%EC%A7%81-%EC%A0%84%ED%99%98%ED%98%95-at-42dot-4372783510?refId=%2F1qLChSVn3giUiiNusHaIQ%3D%3D&amp;trackingId=TVYs5RWI1wgPuuVRiBioUA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K68" s="26" t="inlineStr">
+      <c r="K68" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-42dot-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L68" s="26" t="inlineStr">
+      <c r="L68" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-42dot-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M68" s="26" t="inlineStr"/>
+      <c r="M68" s="29" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="26" t="inlineStr">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>linkedin_4402753102</t>
         </is>
       </c>
-      <c r="B69" s="26" t="inlineStr">
+      <c r="B69" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C69" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D69" s="26" t="inlineStr">
+      <c r="C69" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D69" s="29" t="inlineStr">
         <is>
           <t>Five9</t>
         </is>
       </c>
-      <c r="E69" s="26" t="inlineStr">
+      <c r="E69" s="29" t="inlineStr">
         <is>
           <t>Software Developer AI Insights Intern</t>
         </is>
       </c>
-      <c r="F69" s="26" t="inlineStr">
+      <c r="F69" s="29" t="inlineStr">
         <is>
           <t>San Ramon, CA</t>
         </is>
       </c>
-      <c r="G69" s="26" t="inlineStr">
+      <c r="G69" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H69" s="26" t="inlineStr">
+      <c r="H69" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 20:56 UTC</t>
         </is>
       </c>
-      <c r="I69" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J69" s="28" t="inlineStr">
+      <c r="I69" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J69" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/software-developer-ai-insights-intern-at-five9-4402753102?refId=%2FiKmLsIvYp2TclUyf8MJwg%3D%3D&amp;trackingId=X2UMBr3jE86J9JmPv42B2w%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K69" s="26" t="inlineStr">
+      <c r="K69" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-five9-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L69" s="26" t="inlineStr">
+      <c r="L69" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-five9-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M69" s="26" t="inlineStr"/>
+      <c r="M69" s="29" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="26" t="inlineStr">
+      <c r="A70" s="29" t="inlineStr">
         <is>
           <t>linkedin_4403519373</t>
         </is>
       </c>
-      <c r="B70" s="26" t="inlineStr">
+      <c r="B70" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C70" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D70" s="26" t="inlineStr">
+      <c r="C70" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D70" s="29" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E70" s="26" t="inlineStr">
+      <c r="E70" s="29" t="inlineStr">
         <is>
           <t>PhD Research Intern, Physical AI in Perception</t>
         </is>
       </c>
-      <c r="F70" s="26" t="inlineStr">
+      <c r="F70" s="29" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G70" s="26" t="inlineStr">
+      <c r="G70" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H70" s="26" t="inlineStr">
+      <c r="H70" s="29" t="inlineStr">
         <is>
           <t>2026-04-17 20:07 UTC</t>
         </is>
       </c>
-      <c r="I70" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J70" s="28" t="inlineStr">
+      <c r="I70" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J70" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-physical-ai-in-perception-at-zoox-4403519373?refId=LChV34e%2Bd7cvBpZ%2FbJAZjw%3D%3D&amp;trackingId=vlvuJ54NQfvZvNY3pNGqNw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K70" s="26" t="inlineStr">
+      <c r="K70" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L70" s="26" t="inlineStr">
+      <c r="L70" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M70" s="26" t="inlineStr"/>
+      <c r="M70" s="29" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="26" t="inlineStr">
+      <c r="A71" s="29" t="inlineStr">
         <is>
           <t>linkedin_4403095692</t>
         </is>
       </c>
-      <c r="B71" s="26" t="inlineStr">
+      <c r="B71" s="29" t="inlineStr">
         <is>
           <t>2026-04-19 08:24</t>
         </is>
       </c>
-      <c r="C71" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D71" s="26" t="inlineStr">
+      <c r="C71" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D71" s="29" t="inlineStr">
         <is>
           <t>Starrycraze Technology</t>
         </is>
       </c>
-      <c r="E71" s="26" t="inlineStr">
+      <c r="E71" s="29" t="inlineStr">
         <is>
           <t>Data Scientist Intern</t>
         </is>
       </c>
-      <c r="F71" s="26" t="inlineStr">
+      <c r="F71" s="29" t="inlineStr">
         <is>
           <t>Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G71" s="26" t="inlineStr">
+      <c r="G71" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H71" s="26" t="inlineStr">
+      <c r="H71" s="29" t="inlineStr">
         <is>
           <t>2026-04-19 04:58 UTC</t>
         </is>
       </c>
-      <c r="I71" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J71" s="28" t="inlineStr">
+      <c r="I71" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J71" s="31" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/data-scientist-intern-at-starrycraze-technology-4403095692?refId=TVQyGaR78N78VqNo32HHeA%3D%3D&amp;trackingId=iTU%2BdVDc304eRUiD2UiVkA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K71" s="26" t="inlineStr">
+      <c r="K71" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-starrycraze-technology-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L71" s="26" t="inlineStr">
+      <c r="L71" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-starrycraze-technology-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M71" s="26" t="inlineStr"/>
+      <c r="M71" s="29" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="26" t="inlineStr">
+      <c r="A72" s="29" t="inlineStr">
         <is>
           <t>linkedin_4403848986</t>
         </is>
       </c>
-      <c r="B72" s="26" t="inlineStr">
+      <c r="B72" s="29" t="inlineStr">
         <is>
           <t>2026-04-19 08:24</t>
         </is>
       </c>
-      <c r="C72" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D72" s="26" t="inlineStr">
+      <c r="C72" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D72" s="29" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E72" s="26" t="inlineStr">
+      <c r="E72" s="29" t="inlineStr">
         <is>
           <t>PhD Research Intern, Offline Driving Intelligence</t>
         </is>
       </c>
-      <c r="F72" s="26" t="inlineStr">
+      <c r="F72" s="29" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G72" s="26" t="inlineStr">
+      <c r="G72" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H72" s="26" t="inlineStr">
+      <c r="H72" s="29" t="inlineStr">
         <is>
           <t>2026-04-19 02:06 UTC</t>
         </is>
       </c>
-      <c r="I72" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J72" s="28" t="inlineStr">
+      <c r="I72" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J72" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-offline-driving-intelligence-at-zoox-4403848986?refId=5ydRxcXuf5aHqLJVjey87Q%3D%3D&amp;trackingId=FWtGym5%2BhCmPjiMPBVYS7w%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K72" s="26" t="inlineStr">
+      <c r="K72" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L72" s="26" t="inlineStr">
+      <c r="L72" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M72" s="26" t="inlineStr"/>
+      <c r="M72" s="29" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="26" t="inlineStr">
+      <c r="A73" s="29" t="inlineStr">
         <is>
           <t>linkedin_4371758156</t>
         </is>
       </c>
-      <c r="B73" s="26" t="inlineStr">
+      <c r="B73" s="29" t="inlineStr">
         <is>
           <t>2026-04-19 08:24</t>
         </is>
       </c>
-      <c r="C73" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D73" s="26" t="inlineStr">
+      <c r="C73" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D73" s="29" t="inlineStr">
         <is>
           <t>Lowe's India</t>
         </is>
       </c>
-      <c r="E73" s="26" t="inlineStr">
+      <c r="E73" s="29" t="inlineStr">
         <is>
           <t>DIH Intern, Data Engineering</t>
         </is>
       </c>
-      <c r="F73" s="26" t="inlineStr">
+      <c r="F73" s="29" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G73" s="26" t="inlineStr">
+      <c r="G73" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H73" s="26" t="inlineStr">
+      <c r="H73" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 10:48 UTC</t>
         </is>
       </c>
-      <c r="I73" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J73" s="28" t="inlineStr">
+      <c r="I73" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J73" s="31" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/dih-intern-data-engineering-at-lowe-s-india-4371758156?refId=1mgTdTTgR1UncTTJ8Ts5OA%3D%3D&amp;trackingId=7HYWBNU0zclnyp9qIoW2Jw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K73" s="26" t="inlineStr">
+      <c r="K73" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-lowes-india-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L73" s="26" t="inlineStr">
+      <c r="L73" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-lowes-india-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M73" s="26" t="inlineStr"/>
+      <c r="M73" s="29" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="26" t="inlineStr">
+      <c r="A74" s="29" t="inlineStr">
         <is>
           <t>linkedin_4327191639</t>
         </is>
       </c>
-      <c r="B74" s="26" t="inlineStr">
+      <c r="B74" s="29" t="inlineStr">
         <is>
           <t>2026-04-19 08:24</t>
         </is>
       </c>
-      <c r="C74" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D74" s="26" t="inlineStr">
+      <c r="C74" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D74" s="29" t="inlineStr">
         <is>
           <t>Whatnot</t>
         </is>
       </c>
-      <c r="E74" s="26" t="inlineStr">
+      <c r="E74" s="29" t="inlineStr">
         <is>
           <t>Data Scientist, Product Analytics</t>
         </is>
       </c>
-      <c r="F74" s="26" t="inlineStr">
+      <c r="F74" s="29" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G74" s="26" t="inlineStr">
+      <c r="G74" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H74" s="26" t="inlineStr">
+      <c r="H74" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 13:22 UTC</t>
         </is>
       </c>
-      <c r="I74" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J74" s="28" t="inlineStr">
+      <c r="I74" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J74" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-scientist-product-analytics-at-whatnot-4327191639?refId=mfQJnJ6mRr3La1qB9YnNGA%3D%3D&amp;trackingId=k4mLJmsHD9wYHSZlc4RA%2Fw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K74" s="26" t="inlineStr">
+      <c r="K74" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-whatnot-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L74" s="26" t="inlineStr">
+      <c r="L74" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-whatnot-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M74" s="26" t="inlineStr"/>
+      <c r="M74" s="29" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="26" t="inlineStr">
+      <c r="A75" s="29" t="inlineStr">
         <is>
           <t>linkedin_4391150969</t>
         </is>
       </c>
-      <c r="B75" s="26" t="inlineStr">
+      <c r="B75" s="29" t="inlineStr">
         <is>
           <t>2026-04-19 19:54</t>
         </is>
       </c>
-      <c r="C75" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D75" s="26" t="inlineStr">
+      <c r="C75" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D75" s="29" t="inlineStr">
         <is>
           <t>Cartesian</t>
         </is>
       </c>
-      <c r="E75" s="26" t="inlineStr">
+      <c r="E75" s="29" t="inlineStr">
         <is>
           <t>Software Engineering Intern (Summer/Fall 2026)</t>
         </is>
       </c>
-      <c r="F75" s="26" t="inlineStr">
+      <c r="F75" s="29" t="inlineStr">
         <is>
           <t>Cambridge, MA</t>
         </is>
       </c>
-      <c r="G75" s="26" t="inlineStr">
+      <c r="G75" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H75" s="26" t="inlineStr">
+      <c r="H75" s="29" t="inlineStr">
         <is>
           <t>2026-04-18 23:08 UTC</t>
         </is>
       </c>
-      <c r="I75" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J75" s="28" t="inlineStr">
+      <c r="I75" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J75" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/software-engineering-intern-summer-fall-2026-at-cartesian-4391150969?refId=rXBEPoDKoHwUW%2BMU3mmCWA%3D%3D&amp;trackingId=03L6jyuSNG6Edf0%2FeXbj4w%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K75" s="26" t="inlineStr">
+      <c r="K75" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-cartesian-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L75" s="26" t="inlineStr">
+      <c r="L75" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-cartesian-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M75" s="26" t="inlineStr"/>
+      <c r="M75" s="29" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="26" t="inlineStr">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>linkedin_4401268516</t>
         </is>
       </c>
-      <c r="B76" s="26" t="inlineStr">
+      <c r="B76" s="29" t="inlineStr">
         <is>
           <t>2026-04-19 19:54</t>
         </is>
       </c>
-      <c r="C76" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D76" s="26" t="inlineStr">
+      <c r="C76" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D76" s="29" t="inlineStr">
         <is>
           <t>Joveo Ai</t>
         </is>
       </c>
-      <c r="E76" s="26" t="inlineStr">
+      <c r="E76" s="29" t="inlineStr">
         <is>
           <t>Generative AI Intern</t>
         </is>
       </c>
-      <c r="F76" s="26" t="inlineStr">
+      <c r="F76" s="29" t="inlineStr">
         <is>
           <t>Bangalore Urban, Karnataka, India</t>
         </is>
       </c>
-      <c r="G76" s="26" t="inlineStr">
+      <c r="G76" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H76" s="26" t="inlineStr">
+      <c r="H76" s="29" t="inlineStr">
         <is>
           <t>2026-04-19 16:33 UTC</t>
         </is>
       </c>
-      <c r="I76" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J76" s="28" t="inlineStr">
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J76" s="31" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/generative-ai-intern-at-joveo-ai-4401268516?refId=AMRRU4%2FYzAhlhe1ad%2FYa%2Fw%3D%3D&amp;trackingId=lRpwTcswbLSpxr57DNyAvA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K76" s="26" t="inlineStr">
+      <c r="K76" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-joveo-ai-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L76" s="26" t="inlineStr">
+      <c r="L76" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-joveo-ai-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M76" s="26" t="inlineStr"/>
+      <c r="M76" s="29" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="26" t="inlineStr">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>linkedin_4381330362</t>
         </is>
       </c>
-      <c r="B77" s="26" t="inlineStr">
+      <c r="B77" s="29" t="inlineStr">
         <is>
           <t>2026-04-19 19:54</t>
         </is>
       </c>
-      <c r="C77" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D77" s="26" t="inlineStr">
+      <c r="C77" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D77" s="29" t="inlineStr">
         <is>
           <t>Shopee</t>
         </is>
       </c>
-      <c r="E77" s="26" t="inlineStr">
+      <c r="E77" s="29" t="inlineStr">
         <is>
           <t>Data Analyst Intern - Product Analysis, Regional Operations (Summer 2026)</t>
         </is>
       </c>
-      <c r="F77" s="26" t="inlineStr">
+      <c r="F77" s="29" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G77" s="26" t="inlineStr">
+      <c r="G77" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H77" s="26" t="inlineStr">
+      <c r="H77" s="29" t="inlineStr">
         <is>
           <t>2026-04-19 13:47 UTC</t>
         </is>
       </c>
-      <c r="I77" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J77" s="28" t="inlineStr">
+      <c r="I77" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J77" s="31" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/data-analyst-intern-product-analysis-regional-operations-summer-2026-at-shopee-4381330362?refId=Mf9npsmRtScOZbkuOI7S2Q%3D%3D&amp;trackingId=qCnW3Di6Gcyx48NhCTpBLw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K77" s="26" t="inlineStr">
+      <c r="K77" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-shopee-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L77" s="26" t="inlineStr">
+      <c r="L77" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-shopee-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M77" s="26" t="inlineStr"/>
+      <c r="M77" s="29" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="26" t="inlineStr">
+      <c r="A78" s="29" t="inlineStr">
         <is>
           <t>linkedin_4355297667</t>
         </is>
       </c>
-      <c r="B78" s="26" t="inlineStr">
+      <c r="B78" s="29" t="inlineStr">
         <is>
           <t>2026-04-19 19:54</t>
         </is>
       </c>
-      <c r="C78" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D78" s="26" t="inlineStr">
+      <c r="C78" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D78" s="29" t="inlineStr">
         <is>
           <t>Temasek</t>
         </is>
       </c>
-      <c r="E78" s="26" t="inlineStr">
+      <c r="E78" s="29" t="inlineStr">
         <is>
           <t>Policy &amp; Research Intern, Workforce 4.0 (Jun/Jul - Dec 2026)</t>
         </is>
       </c>
-      <c r="F78" s="26" t="inlineStr">
+      <c r="F78" s="29" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G78" s="26" t="inlineStr">
+      <c r="G78" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H78" s="26" t="inlineStr">
+      <c r="H78" s="29" t="inlineStr">
         <is>
           <t>2026-04-19 10:08 UTC</t>
         </is>
       </c>
-      <c r="I78" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J78" s="28" t="inlineStr">
+      <c r="I78" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J78" s="31" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/policy-research-intern-workforce-4-0-jun-jul-dec-2026-at-temasek-4355297667?refId=SZF%2BVbNMCE0h7Rloqm3lXQ%3D%3D&amp;trackingId=vK2euiis8CytJt264fhurw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K78" s="26" t="inlineStr">
+      <c r="K78" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-temasek-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L78" s="26" t="inlineStr">
+      <c r="L78" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-temasek-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M78" s="26" t="inlineStr"/>
+      <c r="M78" s="29" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="26" t="inlineStr">
+      <c r="A79" s="29" t="inlineStr">
         <is>
           <t>linkedin_4336865392</t>
         </is>
       </c>
-      <c r="B79" s="26" t="inlineStr">
+      <c r="B79" s="29" t="inlineStr">
         <is>
           <t>2026-04-19 19:54</t>
         </is>
       </c>
-      <c r="C79" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D79" s="26" t="inlineStr">
+      <c r="C79" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D79" s="29" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E79" s="26" t="inlineStr">
+      <c r="E79" s="29" t="inlineStr">
         <is>
           <t>PhD Research Intern, Visual Object Understanding</t>
         </is>
       </c>
-      <c r="F79" s="26" t="inlineStr">
+      <c r="F79" s="29" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G79" s="26" t="inlineStr">
+      <c r="G79" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H79" s="26" t="inlineStr">
+      <c r="H79" s="29" t="inlineStr">
         <is>
           <t>2026-04-19 10:27 UTC</t>
         </is>
       </c>
-      <c r="I79" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J79" s="28" t="inlineStr">
+      <c r="I79" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J79" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-visual-object-understanding-at-zoox-4336865392?refId=gztZfDsooz7GE2iA6mPxjQ%3D%3D&amp;trackingId=%2F1kV0X%2F8hKCPhv0kD05v5Q%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K79" s="26" t="inlineStr">
+      <c r="K79" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L79" s="26" t="inlineStr">
+      <c r="L79" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M79" s="26" t="inlineStr"/>
+      <c r="M79" s="29" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="26" t="inlineStr">
+      <c r="A80" s="29" t="inlineStr">
         <is>
           <t>linkedin_4404025051</t>
         </is>
       </c>
-      <c r="B80" s="26" t="inlineStr">
+      <c r="B80" s="29" t="inlineStr">
         <is>
           <t>2026-04-20 09:16</t>
         </is>
       </c>
-      <c r="C80" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D80" s="26" t="inlineStr">
+      <c r="C80" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D80" s="29" t="inlineStr">
         <is>
           <t>Dassault Systèmes</t>
         </is>
       </c>
-      <c r="E80" s="26" t="inlineStr">
+      <c r="E80" s="29" t="inlineStr">
         <is>
           <t>INTERNSHIP: Data Science (6mo June 2026)</t>
         </is>
       </c>
-      <c r="F80" s="26" t="inlineStr">
+      <c r="F80" s="29" t="inlineStr">
         <is>
           <t>Waltham, MA</t>
         </is>
       </c>
-      <c r="G80" s="26" t="inlineStr">
+      <c r="G80" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H80" s="26" t="inlineStr">
+      <c r="H80" s="29" t="inlineStr">
         <is>
           <t>2026-04-19 23:38 UTC</t>
         </is>
       </c>
-      <c r="I80" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J80" s="28" t="inlineStr">
+      <c r="I80" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J80" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/internship-data-science-6mo-june-2026-at-dassault-syst%C3%A8mes-4404025051?refId=S4wy0FwbzbiuPwYYk2m0dw%3D%3D&amp;trackingId=RGARwF5XkYgBTfpY7DrrZg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K80" s="26" t="inlineStr">
+      <c r="K80" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dassault-systèmes-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L80" s="26" t="inlineStr">
+      <c r="L80" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dassault-systèmes-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M80" s="26" t="inlineStr"/>
+      <c r="M80" s="29" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="26" t="inlineStr">
+      <c r="A81" s="29" t="inlineStr">
         <is>
           <t>linkedin_4403368519</t>
         </is>
       </c>
-      <c r="B81" s="26" t="inlineStr">
+      <c r="B81" s="29" t="inlineStr">
         <is>
           <t>2026-04-20 09:16</t>
         </is>
       </c>
-      <c r="C81" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D81" s="26" t="inlineStr">
+      <c r="C81" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D81" s="29" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="E81" s="26" t="inlineStr">
+      <c r="E81" s="29" t="inlineStr">
         <is>
           <t>Risk Control Algorithm Engineer Intern</t>
         </is>
       </c>
-      <c r="F81" s="26" t="inlineStr">
+      <c r="F81" s="29" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G81" s="26" t="inlineStr">
+      <c r="G81" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H81" s="26" t="inlineStr">
+      <c r="H81" s="29" t="inlineStr">
         <is>
           <t>2026-04-20 08:20 UTC</t>
         </is>
       </c>
-      <c r="I81" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J81" s="28" t="inlineStr">
+      <c r="I81" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J81" s="31" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/risk-control-algorithm-engineer-intern-at-bybit-4403368519?refId=9jFaGeHrGBqPLrXTIfcNwA%3D%3D&amp;trackingId=glTg%2F1p9B2dY4YX59MH9DA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K81" s="26" t="inlineStr">
+      <c r="K81" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bybit-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L81" s="26" t="inlineStr">
+      <c r="L81" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bybit-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M81" s="26" t="inlineStr"/>
+      <c r="M81" s="29" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="26" t="inlineStr">
+      <c r="A82" s="29" t="inlineStr">
         <is>
           <t>linkedin_4403320381</t>
         </is>
       </c>
-      <c r="B82" s="26" t="inlineStr">
+      <c r="B82" s="29" t="inlineStr">
         <is>
           <t>2026-04-20 09:16</t>
         </is>
       </c>
-      <c r="C82" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D82" s="26" t="inlineStr">
+      <c r="C82" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D82" s="29" t="inlineStr">
         <is>
           <t>Digitomics AI</t>
         </is>
       </c>
-      <c r="E82" s="26" t="inlineStr">
+      <c r="E82" s="29" t="inlineStr">
         <is>
           <t>AI Engineering Intern</t>
         </is>
       </c>
-      <c r="F82" s="26" t="inlineStr">
+      <c r="F82" s="29" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G82" s="26" t="inlineStr">
+      <c r="G82" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H82" s="26" t="inlineStr">
+      <c r="H82" s="29" t="inlineStr">
         <is>
           <t>2026-04-20 08:43 UTC</t>
         </is>
       </c>
-      <c r="I82" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J82" s="28" t="inlineStr">
+      <c r="I82" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J82" s="31" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/ai-engineering-intern-at-digitomics-ai-4403320381?refId=0fRwalKs7ueOf%2FH7m6U26Q%3D%3D&amp;trackingId=zbHZrmgemJdB%2BlQYFw7geg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K82" s="26" t="inlineStr">
+      <c r="K82" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-digitomics-ai-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L82" s="26" t="inlineStr">
+      <c r="L82" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-digitomics-ai-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M82" s="26" t="inlineStr"/>
+      <c r="M82" s="29" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="26" t="inlineStr">
+      <c r="A83" s="29" t="inlineStr">
         <is>
           <t>linkedin_4403358236</t>
         </is>
       </c>
-      <c r="B83" s="26" t="inlineStr">
+      <c r="B83" s="29" t="inlineStr">
         <is>
           <t>2026-04-20 09:16</t>
         </is>
       </c>
-      <c r="C83" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D83" s="26" t="inlineStr">
+      <c r="C83" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D83" s="29" t="inlineStr">
         <is>
           <t>InMobi</t>
         </is>
       </c>
-      <c r="E83" s="26" t="inlineStr">
+      <c r="E83" s="29" t="inlineStr">
         <is>
           <t>Intern - Industrial Trainee</t>
         </is>
       </c>
-      <c r="F83" s="26" t="inlineStr">
+      <c r="F83" s="29" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G83" s="26" t="inlineStr">
+      <c r="G83" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H83" s="26" t="inlineStr">
+      <c r="H83" s="29" t="inlineStr">
         <is>
           <t>2026-04-20 06:44 UTC</t>
         </is>
       </c>
-      <c r="I83" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J83" s="28" t="inlineStr">
+      <c r="I83" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J83" s="31" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/intern-industrial-trainee-at-inmobi-4403358236?refId=Hz8z0MLJ0gvG3WjNfG9q9Q%3D%3D&amp;trackingId=uO3LmXVsff1dJma3y3w5Gg%3D%3D&amp;position=8&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K83" s="26" t="inlineStr">
+      <c r="K83" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-inmobi-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L83" s="26" t="inlineStr">
+      <c r="L83" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-inmobi-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M83" s="26" t="inlineStr"/>
+      <c r="M83" s="29" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="26" t="inlineStr">
+      <c r="A84" s="29" t="inlineStr">
         <is>
           <t>linkedin_4403359204</t>
         </is>
       </c>
-      <c r="B84" s="26" t="inlineStr">
+      <c r="B84" s="29" t="inlineStr">
         <is>
           <t>2026-04-20 09:16</t>
         </is>
       </c>
-      <c r="C84" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D84" s="26" t="inlineStr">
+      <c r="C84" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D84" s="29" t="inlineStr">
         <is>
           <t>TakedaPharmaceutical Nordics AB</t>
         </is>
       </c>
-      <c r="E84" s="26" t="inlineStr">
+      <c r="E84" s="29" t="inlineStr">
         <is>
           <t>Senior Data Scientist</t>
         </is>
       </c>
-      <c r="F84" s="26" t="inlineStr">
+      <c r="F84" s="29" t="inlineStr">
         <is>
           <t>Boston, MA</t>
         </is>
       </c>
-      <c r="G84" s="26" t="inlineStr">
+      <c r="G84" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H84" s="26" t="inlineStr">
+      <c r="H84" s="29" t="inlineStr">
         <is>
           <t>2026-04-20 06:45 UTC</t>
         </is>
       </c>
-      <c r="I84" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J84" s="28" t="inlineStr">
+      <c r="I84" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J84" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/senior-data-scientist-at-takedapharmaceutical-nordics-ab-4403359204?refId=S4wy0FwbzbiuPwYYk2m0dw%3D%3D&amp;trackingId=zfL5isOE6jcFxwuJQPpkyA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K84" s="26" t="inlineStr">
+      <c r="K84" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-takedapharmaceutical-nordics-ab-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L84" s="26" t="inlineStr">
+      <c r="L84" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-takedapharmaceutical-nordics-ab-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M84" s="26" t="inlineStr"/>
+      <c r="M84" s="29" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="26" t="inlineStr">
+      <c r="A85" s="29" t="inlineStr">
         <is>
           <t>linkedin_4403353339</t>
         </is>
       </c>
-      <c r="B85" s="26" t="inlineStr">
+      <c r="B85" s="29" t="inlineStr">
         <is>
           <t>2026-04-20 09:16</t>
         </is>
       </c>
-      <c r="C85" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D85" s="26" t="inlineStr">
+      <c r="C85" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D85" s="29" t="inlineStr">
         <is>
           <t>Kuku</t>
         </is>
       </c>
-      <c r="E85" s="26" t="inlineStr">
+      <c r="E85" s="29" t="inlineStr">
         <is>
           <t>AI Intern</t>
         </is>
       </c>
-      <c r="F85" s="26" t="inlineStr">
+      <c r="F85" s="29" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G85" s="26" t="inlineStr">
+      <c r="G85" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H85" s="26" t="inlineStr">
+      <c r="H85" s="29" t="inlineStr">
         <is>
           <t>2026-04-20 07:10 UTC</t>
         </is>
       </c>
-      <c r="I85" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J85" s="28" t="inlineStr">
+      <c r="I85" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J85" s="31" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/ai-intern-at-kuku-4403353339?refId=Hz8z0MLJ0gvG3WjNfG9q9Q%3D%3D&amp;trackingId=HENEvtuPxzCTSc47zwTLxw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K85" s="26" t="inlineStr">
+      <c r="K85" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-kuku-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L85" s="26" t="inlineStr">
+      <c r="L85" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-kuku-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M85" s="26" t="inlineStr"/>
+      <c r="M85" s="29" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="26" t="inlineStr">
+      <c r="A86" s="29" t="inlineStr">
         <is>
           <t>linkedin_4403306789</t>
         </is>
       </c>
-      <c r="B86" s="26" t="inlineStr">
+      <c r="B86" s="29" t="inlineStr">
         <is>
           <t>2026-04-20 09:16</t>
         </is>
       </c>
-      <c r="C86" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D86" s="26" t="inlineStr">
+      <c r="C86" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D86" s="29" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E86" s="26" t="inlineStr">
+      <c r="E86" s="29" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F86" s="26" t="inlineStr">
+      <c r="F86" s="29" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G86" s="26" t="inlineStr">
+      <c r="G86" s="29" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H86" s="26" t="inlineStr">
+      <c r="H86" s="29" t="inlineStr">
         <is>
           <t>2026-04-19 22:21 UTC</t>
         </is>
       </c>
-      <c r="I86" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J86" s="28" t="inlineStr">
+      <c r="I86" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J86" s="31" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/research-intern-at-skycliff-it-4403306789?refId=KN18fO0braE9qgElBP9zEg%3D%3D&amp;trackingId=%2Bm9LCS%2BxHyH7O3sA%2BvKB2A%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K86" s="26" t="inlineStr">
+      <c r="K86" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L86" s="26" t="inlineStr">
+      <c r="L86" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M86" s="26" t="inlineStr"/>
+      <c r="M86" s="29" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="26" t="inlineStr">
+      <c r="A87" s="29" t="inlineStr">
         <is>
           <t>linkedin_4336984951</t>
         </is>
       </c>
-      <c r="B87" s="26" t="inlineStr">
+      <c r="B87" s="29" t="inlineStr">
         <is>
           <t>2026-04-20 09:16</t>
         </is>
       </c>
-      <c r="C87" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D87" s="26" t="inlineStr">
+      <c r="C87" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D87" s="29" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E87" s="26" t="inlineStr">
+      <c r="E87" s="29" t="inlineStr">
         <is>
           <t>Machine Learning Engineer Intern, Simulation</t>
         </is>
       </c>
-      <c r="F87" s="26" t="inlineStr">
+      <c r="F87" s="29" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G87" s="26" t="inlineStr">
+      <c r="G87" s="29" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H87" s="26" t="inlineStr">
+      <c r="H87" s="29" t="inlineStr">
         <is>
           <t>2026-04-19 09:41 UTC</t>
         </is>
       </c>
-      <c r="I87" s="27" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J87" s="28" t="inlineStr">
+      <c r="I87" s="30" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J87" s="31" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/machine-learning-engineer-intern-simulation-at-zoox-4336984951?refId=kzdKy3lQPz5ITmALB3aiLA%3D%3D&amp;trackingId=TBJ5wFzjDmfdPFnmhbpCvA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K87" s="26" t="inlineStr">
+      <c r="K87" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L87" s="26" t="inlineStr">
+      <c r="L87" s="29" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M87" s="26" t="inlineStr"/>
+      <c r="M87" s="29" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="29" t="inlineStr">
@@ -6423,6 +6432,132 @@
         </is>
       </c>
       <c r="M93" s="29" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="32" t="inlineStr">
+        <is>
+          <t>linkedin_4404365794</t>
+        </is>
+      </c>
+      <c r="B94" s="32" t="inlineStr">
+        <is>
+          <t>2026-04-21 08:59</t>
+        </is>
+      </c>
+      <c r="C94" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D94" s="32" t="inlineStr">
+        <is>
+          <t>Zoox</t>
+        </is>
+      </c>
+      <c r="E94" s="32" t="inlineStr">
+        <is>
+          <t>PhD Research Intern, Vision Language Action Models</t>
+        </is>
+      </c>
+      <c r="F94" s="32" t="inlineStr">
+        <is>
+          <t>Foster City, CA</t>
+        </is>
+      </c>
+      <c r="G94" s="32" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H94" s="32" t="inlineStr">
+        <is>
+          <t>2026-04-20 20:15 UTC</t>
+        </is>
+      </c>
+      <c r="I94" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J94" s="34" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/phd-research-intern-vision-language-action-models-at-zoox-4404365794?refId=uXGDZFbr7zJfdUDLc3YoBA%3D%3D&amp;trackingId=VzDGaTfSup4x8BX36ZTRMw%3D%3D&amp;position=7&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K94" s="32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-21.pdf</t>
+        </is>
+      </c>
+      <c r="L94" s="32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-21.pdf</t>
+        </is>
+      </c>
+      <c r="M94" s="32" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="32" t="inlineStr">
+        <is>
+          <t>linkedin_4401665722</t>
+        </is>
+      </c>
+      <c r="B95" s="32" t="inlineStr">
+        <is>
+          <t>2026-04-21 08:59</t>
+        </is>
+      </c>
+      <c r="C95" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D95" s="32" t="inlineStr">
+        <is>
+          <t>BMW Group</t>
+        </is>
+      </c>
+      <c r="E95" s="32" t="inlineStr">
+        <is>
+          <t>Intern LLM-enhanced in-vehicle personal assistants (f/m/x)</t>
+        </is>
+      </c>
+      <c r="F95" s="32" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G95" s="32" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H95" s="32" t="inlineStr">
+        <is>
+          <t>2026-04-20 21:46 UTC</t>
+        </is>
+      </c>
+      <c r="I95" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J95" s="34" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/intern-llm-enhanced-in-vehicle-personal-assistants-f-m-x-at-bmw-group-4401665722?refId=eLXGs4VRP9DfKl0tb9vatg%3D%3D&amp;trackingId=ng0wN9P80Kinot8zi8AH9g%3D%3D&amp;position=8&amp;pageNum=0</t>
+        </is>
+      </c>
+      <c r="K95" s="32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bmw-group-2026-04-21.pdf</t>
+        </is>
+      </c>
+      <c r="L95" s="32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bmw-group-2026-04-21.pdf</t>
+        </is>
+      </c>
+      <c r="M95" s="32" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6518,6 +6653,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J91" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J92" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J95" r:id="rId94"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Internship Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,7 +39,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF9C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -185,6 +190,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -638,5800 +646,5804 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>linkedin_4401809501</t>
         </is>
       </c>
-      <c r="B2" s="29" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C2" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D2" s="29" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D2" s="32" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E2" s="29" t="inlineStr">
+      <c r="E2" s="32" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F2" s="29" t="inlineStr">
+      <c r="F2" s="32" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G2" s="29" t="inlineStr">
+      <c r="G2" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H2" s="29" t="inlineStr">
+      <c r="H2" s="32" t="inlineStr">
         <is>
           <t>2026-04-15 22:19 UTC</t>
         </is>
       </c>
-      <c r="I2" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J2" s="31" t="inlineStr">
+      <c r="I2" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J2" s="34" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/research-intern-at-skycliff-it-4401809501?refId=HHi6SaK1fggu3E9dI3MtVg%3D%3D&amp;trackingId=r33pSo29lHStfk9FH82pyw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K2" s="29" t="inlineStr">
+      <c r="K2" s="32" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L2" s="29" t="inlineStr">
+      <c r="L2" s="32" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M2" s="29" t="inlineStr"/>
+      <c r="M2" s="32" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>linkedin_4402568578</t>
         </is>
       </c>
-      <c r="B3" s="29" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C3" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D3" s="29" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D3" s="32" t="inlineStr">
         <is>
           <t>Webs X UM</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="32" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F3" s="29" t="inlineStr">
+      <c r="F3" s="32" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G3" s="29" t="inlineStr">
+      <c r="G3" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H3" s="29" t="inlineStr">
+      <c r="H3" s="32" t="inlineStr">
         <is>
           <t>2026-04-15 19:20 UTC</t>
         </is>
       </c>
-      <c r="I3" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J3" s="31" t="inlineStr">
+      <c r="I3" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J3" s="34" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-webs-x-um-4402568578?refId=g89JM6cY8EFeoLk6JL5tVg%3D%3D&amp;trackingId=uFZVJJX7SSI0XCPFIrLqmA%3D%3D&amp;position=19&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K3" s="29" t="inlineStr">
+      <c r="K3" s="32" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-webs-x-um-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L3" s="29" t="inlineStr">
+      <c r="L3" s="32" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-webs-x-um-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M3" s="29" t="inlineStr"/>
+      <c r="M3" s="32" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="32" t="inlineStr">
         <is>
           <t>linkedin_4399996740</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>SUN PHARMA</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="32" t="inlineStr">
         <is>
           <t>Becario</t>
         </is>
       </c>
-      <c r="F4" s="29" t="inlineStr">
+      <c r="F4" s="32" t="inlineStr">
         <is>
           <t>Mexico City, Mexico</t>
         </is>
       </c>
-      <c r="G4" s="29" t="inlineStr">
+      <c r="G4" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H4" s="29" t="inlineStr">
+      <c r="H4" s="32" t="inlineStr">
         <is>
           <t>2026-04-15 17:59 UTC</t>
         </is>
       </c>
-      <c r="I4" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J4" s="31" t="inlineStr">
+      <c r="I4" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J4" s="34" t="inlineStr">
         <is>
           <t>https://mx.linkedin.com/jobs/view/becario-at-sun-pharma-4399996740?refId=g89JM6cY8EFeoLk6JL5tVg%3D%3D&amp;trackingId=sZ0Fkcf4RHuIpzXu4mJRNg%3D%3D&amp;position=22&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K4" s="29" t="inlineStr">
+      <c r="K4" s="32" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-sun-pharma-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L4" s="29" t="inlineStr">
+      <c r="L4" s="32" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-sun-pharma-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M4" s="29" t="inlineStr"/>
+      <c r="M4" s="32" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>linkedin_4399975959</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D5" s="29" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
         <is>
           <t>LS Direct</t>
         </is>
       </c>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t>Data Analytics Intern</t>
         </is>
       </c>
-      <c r="F5" s="29" t="inlineStr">
+      <c r="F5" s="32" t="inlineStr">
         <is>
           <t>Suffern, NY</t>
         </is>
       </c>
-      <c r="G5" s="29" t="inlineStr">
+      <c r="G5" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H5" s="29" t="inlineStr">
+      <c r="H5" s="32" t="inlineStr">
         <is>
           <t>2026-04-15 14:26 UTC</t>
         </is>
       </c>
-      <c r="I5" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J5" s="31" t="inlineStr">
+      <c r="I5" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J5" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-analytics-intern-at-ls-direct-4399975959?refId=pg0ll3e89fatVyUznLcdpw%3D%3D&amp;trackingId=5b41IoyQfIfx3Tu42domiQ%3D%3D&amp;position=23&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K5" s="29" t="inlineStr">
+      <c r="K5" s="32" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-ls-direct-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L5" s="29" t="inlineStr">
+      <c r="L5" s="32" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-ls-direct-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M5" s="29" t="inlineStr"/>
+      <c r="M5" s="32" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t>linkedin_4370546718</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D6" s="29" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D6" s="32" t="inlineStr">
         <is>
           <t>Clarivate</t>
         </is>
       </c>
-      <c r="E6" s="29" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t>Lead Data Scientist</t>
         </is>
       </c>
-      <c r="F6" s="29" t="inlineStr">
+      <c r="F6" s="32" t="inlineStr">
         <is>
           <t>Barcelona, Catalonia, Spain</t>
         </is>
       </c>
-      <c r="G6" s="29" t="inlineStr">
+      <c r="G6" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H6" s="29" t="inlineStr">
+      <c r="H6" s="32" t="inlineStr">
         <is>
           <t>2026-04-15 12:16 UTC</t>
         </is>
       </c>
-      <c r="I6" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J6" s="31" t="inlineStr">
+      <c r="I6" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J6" s="34" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/lead-data-scientist-at-clarivate-4370546718?refId=FyyqQfduMQ8KZ7B5LeF0UQ%3D%3D&amp;trackingId=1i1kXdbV7SMunyFTiSJHJg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K6" s="29" t="inlineStr">
+      <c r="K6" s="32" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-clarivate-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L6" s="29" t="inlineStr">
+      <c r="L6" s="32" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-clarivate-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M6" s="29" t="inlineStr"/>
+      <c r="M6" s="32" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>linkedin_4389810164</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D7" s="29" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
         <is>
           <t>Vitality</t>
         </is>
       </c>
-      <c r="E7" s="29" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>Senior Data Scientist - 12 Month FTC</t>
         </is>
       </c>
-      <c r="F7" s="29" t="inlineStr">
+      <c r="F7" s="32" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G7" s="29" t="inlineStr">
+      <c r="G7" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H7" s="29" t="inlineStr">
+      <c r="H7" s="32" t="inlineStr">
         <is>
           <t>2026-04-15 09:39 UTC</t>
         </is>
       </c>
-      <c r="I7" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J7" s="31" t="inlineStr">
+      <c r="I7" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J7" s="34" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/senior-data-scientist-12-month-ftc-at-vitality-4389810164?refId=FPz%2BrPoaQeqgXBm%2FfOzGGA%3D%3D&amp;trackingId=yVNh55t2X2xocDT4i6HDqQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K7" s="29" t="inlineStr">
+      <c r="K7" s="32" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-vitality-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L7" s="29" t="inlineStr">
+      <c r="L7" s="32" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-vitality-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M7" s="29" t="inlineStr"/>
+      <c r="M7" s="32" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>linkedin_4399952059</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D8" s="29" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="inlineStr">
         <is>
           <t>traide AI</t>
         </is>
       </c>
-      <c r="E8" s="29" t="inlineStr">
+      <c r="E8" s="32" t="inlineStr">
         <is>
           <t>AI Associate (f/m/x) (B2B SaaS Startup) - Intern/Working Student</t>
         </is>
       </c>
-      <c r="F8" s="29" t="inlineStr">
+      <c r="F8" s="32" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G8" s="29" t="inlineStr">
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H8" s="29" t="inlineStr">
+      <c r="H8" s="32" t="inlineStr">
         <is>
           <t>2026-04-15 07:04 UTC</t>
         </is>
       </c>
-      <c r="I8" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J8" s="31" t="inlineStr">
+      <c r="I8" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J8" s="34" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/ai-associate-f-m-x-b2b-saas-startup-intern-working-student-at-traide-ai-4399952059?refId=x0uIkl175n0hipT17L%2FGRw%3D%3D&amp;trackingId=8kdzUQgW%2B7rCk2pO2oIErg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K8" s="29" t="inlineStr">
+      <c r="K8" s="32" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-traide-ai-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L8" s="29" t="inlineStr">
+      <c r="L8" s="32" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-traide-ai-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M8" s="29" t="inlineStr"/>
+      <c r="M8" s="32" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>linkedin_4399933254</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D9" s="29" t="inlineStr">
+      <c r="C9" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
         <is>
           <t>Briink</t>
         </is>
       </c>
-      <c r="E9" s="29" t="inlineStr">
+      <c r="E9" s="32" t="inlineStr">
         <is>
           <t>Growth Intern (Merantix AI Campus)</t>
         </is>
       </c>
-      <c r="F9" s="29" t="inlineStr">
+      <c r="F9" s="32" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G9" s="29" t="inlineStr">
+      <c r="G9" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H9" s="29" t="inlineStr">
+      <c r="H9" s="32" t="inlineStr">
         <is>
           <t>2026-04-15 05:03 UTC</t>
         </is>
       </c>
-      <c r="I9" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J9" s="31" t="inlineStr">
+      <c r="I9" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J9" s="34" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/growth-intern-merantix-ai-campus-at-briink-4399933254?refId=x0uIkl175n0hipT17L%2FGRw%3D%3D&amp;trackingId=qEKtyJNA03Kbr6AYDlhsBw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K9" s="29" t="inlineStr">
+      <c r="K9" s="32" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-briink-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L9" s="29" t="inlineStr">
+      <c r="L9" s="32" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-briink-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M9" s="29" t="inlineStr"/>
+      <c r="M9" s="32" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>linkedin_4400429367</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C10" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D10" s="29" t="inlineStr">
+      <c r="C10" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr">
         <is>
           <t>Tata Consultancy Services</t>
         </is>
       </c>
-      <c r="E10" s="29" t="inlineStr">
+      <c r="E10" s="32" t="inlineStr">
         <is>
           <t>HR -Data Scientist</t>
         </is>
       </c>
-      <c r="F10" s="29" t="inlineStr">
+      <c r="F10" s="32" t="inlineStr">
         <is>
           <t>Renton, WA</t>
         </is>
       </c>
-      <c r="G10" s="29" t="inlineStr">
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H10" s="29" t="inlineStr">
+      <c r="H10" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 16:56 UTC</t>
         </is>
       </c>
-      <c r="I10" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J10" s="31" t="inlineStr">
+      <c r="I10" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J10" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/hr-data-scientist-at-tata-consultancy-services-4400429367?refId=vJILgNySaXYUQknbyaKZZQ%3D%3D&amp;trackingId=7cZ0KYh8Sv5%2Fh6%2FG86%2BLug%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K10" s="29" t="inlineStr">
+      <c r="K10" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-tata-consultancy-services-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L10" s="29" t="inlineStr">
+      <c r="L10" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-tata-consultancy-services-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M10" s="29" t="inlineStr"/>
+      <c r="M10" s="32" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>linkedin_4390814627</t>
         </is>
       </c>
-      <c r="B11" s="29" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C11" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D11" s="29" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
         <is>
           <t>Criteo</t>
         </is>
       </c>
-      <c r="E11" s="29" t="inlineStr">
+      <c r="E11" s="32" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F11" s="29" t="inlineStr">
+      <c r="F11" s="32" t="inlineStr">
         <is>
           <t>Barcelona, Catalonia, Spain</t>
         </is>
       </c>
-      <c r="G11" s="29" t="inlineStr">
+      <c r="G11" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H11" s="29" t="inlineStr">
+      <c r="H11" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 12:19 UTC</t>
         </is>
       </c>
-      <c r="I11" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J11" s="31" t="inlineStr">
+      <c r="I11" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J11" s="34" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/data-analyst-intern-at-criteo-4390814627?refId=PCZWvfzZIzNkx6giU9jTsA%3D%3D&amp;trackingId=T%2FMog6vtgG8P3ihAU9b1uQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K11" s="29" t="inlineStr">
+      <c r="K11" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-criteo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L11" s="29" t="inlineStr">
+      <c r="L11" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-criteo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M11" s="29" t="inlineStr"/>
+      <c r="M11" s="32" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>linkedin_4402983364</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C12" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D12" s="29" t="inlineStr">
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E12" s="29" t="inlineStr">
+      <c r="E12" s="32" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F12" s="29" t="inlineStr">
+      <c r="F12" s="32" t="inlineStr">
         <is>
           <t>Brussels, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G12" s="29" t="inlineStr">
+      <c r="G12" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H12" s="29" t="inlineStr">
+      <c r="H12" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I12" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J12" s="31" t="inlineStr">
+      <c r="I12" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J12" s="34" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402983364?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=zV4sJQyNyQg%2FS%2BYm6Ba9Eg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K12" s="29" t="inlineStr">
+      <c r="K12" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L12" s="29" t="inlineStr">
+      <c r="L12" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M12" s="29" t="inlineStr"/>
+      <c r="M12" s="32" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>linkedin_4390725142</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C13" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D13" s="29" t="inlineStr">
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
         <is>
           <t>Boston Consulting Group (BCG)</t>
         </is>
       </c>
-      <c r="E13" s="29" t="inlineStr">
+      <c r="E13" s="32" t="inlineStr">
         <is>
           <t>Forward Deployed AI Engineer, Internship, United Kingdom - BCG X</t>
         </is>
       </c>
-      <c r="F13" s="29" t="inlineStr">
+      <c r="F13" s="32" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G13" s="29" t="inlineStr">
+      <c r="G13" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H13" s="29" t="inlineStr">
+      <c r="H13" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 16:24 UTC</t>
         </is>
       </c>
-      <c r="I13" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J13" s="31" t="inlineStr">
+      <c r="I13" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J13" s="34" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/forward-deployed-ai-engineer-internship-united-kingdom-bcg-x-at-boston-consulting-group-bcg-4390725142?refId=YHAZO5vAx9Qtg1RXMma%2F%2BA%3D%3D&amp;trackingId=E8kiSHzcdYe%2FH6s%2FCkGtMw%3D%3D&amp;position=7&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K13" s="29" t="inlineStr">
+      <c r="K13" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L13" s="29" t="inlineStr">
+      <c r="L13" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M13" s="29" t="inlineStr"/>
+      <c r="M13" s="32" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="inlineStr">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>linkedin_4400428064</t>
         </is>
       </c>
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C14" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D14" s="29" t="inlineStr">
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
         <is>
           <t>Fanatics</t>
         </is>
       </c>
-      <c r="E14" s="29" t="inlineStr">
+      <c r="E14" s="32" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="F14" s="29" t="inlineStr">
+      <c r="F14" s="32" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G14" s="29" t="inlineStr">
+      <c r="G14" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H14" s="29" t="inlineStr">
+      <c r="H14" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 16:16 UTC</t>
         </is>
       </c>
-      <c r="I14" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J14" s="31" t="inlineStr">
+      <c r="I14" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J14" s="34" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/data-scientist-at-fanatics-4400428064?refId=SNMwEp9%2FBozAkX4FBnhJwQ%3D%3D&amp;trackingId=cAX0aKWV%2FBX1fvQzm%2FkEMg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K14" s="29" t="inlineStr">
+      <c r="K14" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-fanatics-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L14" s="29" t="inlineStr">
+      <c r="L14" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-fanatics-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M14" s="29" t="inlineStr"/>
+      <c r="M14" s="32" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>linkedin_4390730090</t>
         </is>
       </c>
-      <c r="B15" s="29" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C15" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D15" s="29" t="inlineStr">
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
         <is>
           <t>Boston Consulting Group (BCG)</t>
         </is>
       </c>
-      <c r="E15" s="29" t="inlineStr">
+      <c r="E15" s="32" t="inlineStr">
         <is>
           <t>Forward Deployed AI Scientist, Internship, United Kingdom - BCG X</t>
         </is>
       </c>
-      <c r="F15" s="29" t="inlineStr">
+      <c r="F15" s="32" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G15" s="29" t="inlineStr">
+      <c r="G15" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H15" s="29" t="inlineStr">
+      <c r="H15" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 13:57 UTC</t>
         </is>
       </c>
-      <c r="I15" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J15" s="31" t="inlineStr">
+      <c r="I15" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J15" s="34" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/forward-deployed-ai-scientist-internship-united-kingdom-bcg-x-at-boston-consulting-group-bcg-4390730090?refId=YHAZO5vAx9Qtg1RXMma%2F%2BA%3D%3D&amp;trackingId=m50MzwjbYzUmAv7nJVAKgA%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K15" s="29" t="inlineStr">
+      <c r="K15" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L15" s="29" t="inlineStr">
+      <c r="L15" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M15" s="29" t="inlineStr"/>
+      <c r="M15" s="32" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="29" t="inlineStr">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>linkedin_4402138096</t>
         </is>
       </c>
-      <c r="B16" s="29" t="inlineStr">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C16" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D16" s="29" t="inlineStr">
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="inlineStr">
         <is>
           <t>Kelly Tutors</t>
         </is>
       </c>
-      <c r="E16" s="29" t="inlineStr">
+      <c r="E16" s="32" t="inlineStr">
         <is>
           <t>Research Intern (3-5hrs/week, flexible)</t>
         </is>
       </c>
-      <c r="F16" s="29" t="inlineStr">
+      <c r="F16" s="32" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G16" s="29" t="inlineStr">
+      <c r="G16" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H16" s="29" t="inlineStr">
+      <c r="H16" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 14:40 UTC</t>
         </is>
       </c>
-      <c r="I16" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J16" s="31" t="inlineStr">
+      <c r="I16" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J16" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/research-intern-3-5hrs-week-flexible-at-kelly-tutors-4402138096?refId=HmOS2YEHUH3GOVent1txqw%3D%3D&amp;trackingId=3XBXMUoBdiHeRL4qw%2B2qRw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K16" s="29" t="inlineStr">
+      <c r="K16" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-kelly-tutors-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L16" s="29" t="inlineStr">
+      <c r="L16" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-kelly-tutors-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M16" s="29" t="inlineStr"/>
+      <c r="M16" s="32" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="29" t="inlineStr">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>linkedin_4378557045</t>
         </is>
       </c>
-      <c r="B17" s="29" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C17" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D17" s="29" t="inlineStr">
+      <c r="C17" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="inlineStr">
         <is>
           <t>Fund for Public Health in NYC</t>
         </is>
       </c>
-      <c r="E17" s="29" t="inlineStr">
+      <c r="E17" s="32" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="F17" s="29" t="inlineStr">
+      <c r="F17" s="32" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G17" s="29" t="inlineStr">
+      <c r="G17" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H17" s="29" t="inlineStr">
+      <c r="H17" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 16:13 UTC</t>
         </is>
       </c>
-      <c r="I17" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J17" s="31" t="inlineStr">
+      <c r="I17" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J17" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-scientist-at-fund-for-public-health-in-nyc-4378557045?refId=JsndNRa0tnfF7dsuxv62wA%3D%3D&amp;trackingId=Pmgt6JCxYmQun5Uv6%2BLbiQ%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K17" s="29" t="inlineStr">
+      <c r="K17" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-fund-for-public-health-in-nyc-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L17" s="29" t="inlineStr">
+      <c r="L17" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-fund-for-public-health-in-nyc-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M17" s="29" t="inlineStr"/>
+      <c r="M17" s="32" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="A18" s="32" t="inlineStr">
         <is>
           <t>linkedin_4402977457</t>
         </is>
       </c>
-      <c r="B18" s="29" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C18" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D18" s="29" t="inlineStr">
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E18" s="29" t="inlineStr">
+      <c r="E18" s="32" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F18" s="29" t="inlineStr">
+      <c r="F18" s="32" t="inlineStr">
         <is>
           <t>Brussels, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G18" s="29" t="inlineStr">
+      <c r="G18" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H18" s="29" t="inlineStr">
+      <c r="H18" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I18" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J18" s="31" t="inlineStr">
+      <c r="I18" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J18" s="34" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402977457?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=gL9sbQh%2FaLMmzvXjuO71WQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K18" s="29" t="inlineStr">
+      <c r="K18" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L18" s="29" t="inlineStr">
+      <c r="L18" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M18" s="29" t="inlineStr"/>
+      <c r="M18" s="32" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>linkedin_4371210537</t>
         </is>
       </c>
-      <c r="B19" s="29" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C19" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D19" s="29" t="inlineStr">
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="inlineStr">
         <is>
           <t>Gildan</t>
         </is>
       </c>
-      <c r="E19" s="29" t="inlineStr">
+      <c r="E19" s="32" t="inlineStr">
         <is>
           <t>Intern, ERP GenAI</t>
         </is>
       </c>
-      <c r="F19" s="29" t="inlineStr">
+      <c r="F19" s="32" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G19" s="29" t="inlineStr">
+      <c r="G19" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H19" s="29" t="inlineStr">
+      <c r="H19" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 15:23 UTC</t>
         </is>
       </c>
-      <c r="I19" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J19" s="31" t="inlineStr">
+      <c r="I19" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J19" s="34" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/intern-erp-genai-at-gildan-4371210537?refId=jteS%2Ft3Cmc2XLVMFToCpKw%3D%3D&amp;trackingId=OQGg%2Bob2m9u4kkbRcgWoUw%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K19" s="29" t="inlineStr">
+      <c r="K19" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-gildan-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L19" s="29" t="inlineStr">
+      <c r="L19" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-gildan-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M19" s="29" t="inlineStr"/>
+      <c r="M19" s="32" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t>linkedin_4402974624</t>
         </is>
       </c>
-      <c r="B20" s="29" t="inlineStr">
+      <c r="B20" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C20" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D20" s="29" t="inlineStr">
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E20" s="29" t="inlineStr">
+      <c r="E20" s="32" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F20" s="29" t="inlineStr">
+      <c r="F20" s="32" t="inlineStr">
         <is>
           <t>Uccle, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G20" s="29" t="inlineStr">
+      <c r="G20" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H20" s="29" t="inlineStr">
+      <c r="H20" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I20" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J20" s="31" t="inlineStr">
+      <c r="I20" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J20" s="34" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402974624?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=RJfkVsuYxv4DqyEhPJ367g%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K20" s="29" t="inlineStr">
+      <c r="K20" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L20" s="29" t="inlineStr">
+      <c r="L20" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M20" s="29" t="inlineStr"/>
+      <c r="M20" s="32" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="32" t="inlineStr">
         <is>
           <t>linkedin_4402174633</t>
         </is>
       </c>
-      <c r="B21" s="29" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C21" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D21" s="29" t="inlineStr">
+      <c r="C21" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
         <is>
           <t>Cloudera</t>
         </is>
       </c>
-      <c r="E21" s="29" t="inlineStr">
+      <c r="E21" s="32" t="inlineStr">
         <is>
           <t>AI Enablement Intern (Ireland Based)</t>
         </is>
       </c>
-      <c r="F21" s="29" t="inlineStr">
+      <c r="F21" s="32" t="inlineStr">
         <is>
           <t>Greater Dublin</t>
         </is>
       </c>
-      <c r="G21" s="29" t="inlineStr">
+      <c r="G21" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H21" s="29" t="inlineStr">
+      <c r="H21" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 18:24 UTC</t>
         </is>
       </c>
-      <c r="I21" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J21" s="31" t="inlineStr">
+      <c r="I21" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J21" s="34" t="inlineStr">
         <is>
           <t>https://ie.linkedin.com/jobs/view/ai-enablement-intern-ireland-based-at-cloudera-4402174633?refId=d9iDz5spYJk0nIor701k5g%3D%3D&amp;trackingId=6OZvFiMQ12VqIzY6EqUe7A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K21" s="29" t="inlineStr">
+      <c r="K21" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-cloudera-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L21" s="29" t="inlineStr">
+      <c r="L21" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-cloudera-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M21" s="29" t="inlineStr"/>
+      <c r="M21" s="32" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="29" t="inlineStr">
+      <c r="A22" s="32" t="inlineStr">
         <is>
           <t>linkedin_4403115250</t>
         </is>
       </c>
-      <c r="B22" s="29" t="inlineStr">
+      <c r="B22" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C22" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D22" s="29" t="inlineStr">
+      <c r="C22" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D22" s="32" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E22" s="29" t="inlineStr">
+      <c r="E22" s="32" t="inlineStr">
         <is>
           <t>PhD Research Intern, Mapping Software</t>
         </is>
       </c>
-      <c r="F22" s="29" t="inlineStr">
+      <c r="F22" s="32" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G22" s="29" t="inlineStr">
+      <c r="G22" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H22" s="29" t="inlineStr">
+      <c r="H22" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 19:55 UTC</t>
         </is>
       </c>
-      <c r="I22" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J22" s="31" t="inlineStr">
+      <c r="I22" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J22" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-mapping-software-at-zoox-4403115250?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=67WsHxTIXiO%2ByWr0OYU7ug%3D%3D&amp;position=10&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K22" s="29" t="inlineStr">
+      <c r="K22" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L22" s="29" t="inlineStr">
+      <c r="L22" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M22" s="29" t="inlineStr"/>
+      <c r="M22" s="32" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="inlineStr">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>linkedin_4379373115</t>
         </is>
       </c>
-      <c r="B23" s="29" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C23" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D23" s="29" t="inlineStr">
+      <c r="C23" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D23" s="32" t="inlineStr">
         <is>
           <t>Woven by Toyota</t>
         </is>
       </c>
-      <c r="E23" s="29" t="inlineStr">
+      <c r="E23" s="32" t="inlineStr">
         <is>
           <t>Applied Scientist, Computer Vision and Generative Models, Vision AI (Internship)</t>
         </is>
       </c>
-      <c r="F23" s="29" t="inlineStr">
+      <c r="F23" s="32" t="inlineStr">
         <is>
           <t>Tokyo, Japan</t>
         </is>
       </c>
-      <c r="G23" s="29" t="inlineStr">
+      <c r="G23" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H23" s="29" t="inlineStr">
+      <c r="H23" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 14:55 UTC</t>
         </is>
       </c>
-      <c r="I23" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J23" s="31" t="inlineStr">
+      <c r="I23" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J23" s="34" t="inlineStr">
         <is>
           <t>https://jp.linkedin.com/jobs/view/applied-scientist-computer-vision-and-generative-models-vision-ai-internship-at-woven-by-toyota-4379373115?refId=4q6ISAXJ%2BcfZsJD688QZWg%3D%3D&amp;trackingId=pUnO9OuzZx4G6BOukom%2FQQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K23" s="29" t="inlineStr">
+      <c r="K23" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-woven-by-toyota-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L23" s="29" t="inlineStr">
+      <c r="L23" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-woven-by-toyota-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M23" s="29" t="inlineStr"/>
+      <c r="M23" s="32" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="29" t="inlineStr">
+      <c r="A24" s="32" t="inlineStr">
         <is>
           <t>linkedin_4325103488</t>
         </is>
       </c>
-      <c r="B24" s="29" t="inlineStr">
+      <c r="B24" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C24" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D24" s="29" t="inlineStr">
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D24" s="32" t="inlineStr">
         <is>
           <t>Binance</t>
         </is>
       </c>
-      <c r="E24" s="29" t="inlineStr">
+      <c r="E24" s="32" t="inlineStr">
         <is>
           <t>Binance Accelerator Program - DevOps (Artificial Intelligence)</t>
         </is>
       </c>
-      <c r="F24" s="29" t="inlineStr">
+      <c r="F24" s="32" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G24" s="29" t="inlineStr">
+      <c r="G24" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H24" s="29" t="inlineStr">
+      <c r="H24" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 12:13 UTC</t>
         </is>
       </c>
-      <c r="I24" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J24" s="31" t="inlineStr">
+      <c r="I24" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J24" s="34" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/binance-accelerator-program-devops-artificial-intelligence-at-binance-4325103488?refId=KzaD5RMOfYQEZyaw6UmcpQ%3D%3D&amp;trackingId=8R4okHiG3RYyjThXHAqxIQ%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K24" s="29" t="inlineStr">
+      <c r="K24" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-binance-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L24" s="29" t="inlineStr">
+      <c r="L24" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-binance-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M24" s="29" t="inlineStr"/>
+      <c r="M24" s="32" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="29" t="inlineStr">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>linkedin_4400563251</t>
         </is>
       </c>
-      <c r="B25" s="29" t="inlineStr">
+      <c r="B25" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C25" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D25" s="29" t="inlineStr">
+      <c r="C25" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D25" s="32" t="inlineStr">
         <is>
           <t>Aylo</t>
         </is>
       </c>
-      <c r="E25" s="29" t="inlineStr">
+      <c r="E25" s="32" t="inlineStr">
         <is>
           <t>Sr. Full-Stack Data Scientist - Data Services</t>
         </is>
       </c>
-      <c r="F25" s="29" t="inlineStr">
+      <c r="F25" s="32" t="inlineStr">
         <is>
           <t>Greater Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G25" s="29" t="inlineStr">
+      <c r="G25" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H25" s="29" t="inlineStr">
+      <c r="H25" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 12:01 UTC</t>
         </is>
       </c>
-      <c r="I25" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J25" s="31" t="inlineStr">
+      <c r="I25" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J25" s="34" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/sr-full-stack-data-scientist-data-services-at-aylo-4400563251?refId=3X2hsLwn0XF5%2BC4ABneEzA%3D%3D&amp;trackingId=aJHp5psMKfAaMJdxBAz5Hw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K25" s="29" t="inlineStr">
+      <c r="K25" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-aylo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L25" s="29" t="inlineStr">
+      <c r="L25" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-aylo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M25" s="29" t="inlineStr"/>
+      <c r="M25" s="32" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="A26" s="32" t="inlineStr">
         <is>
           <t>linkedin_4400403670</t>
         </is>
       </c>
-      <c r="B26" s="29" t="inlineStr">
+      <c r="B26" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C26" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D26" s="29" t="inlineStr">
+      <c r="C26" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D26" s="32" t="inlineStr">
         <is>
           <t>Schneider Electric</t>
         </is>
       </c>
-      <c r="E26" s="29" t="inlineStr">
+      <c r="E26" s="32" t="inlineStr">
         <is>
           <t>Internship in Global AI Sales Enablement &amp; Analytics</t>
         </is>
       </c>
-      <c r="F26" s="29" t="inlineStr">
+      <c r="F26" s="32" t="inlineStr">
         <is>
           <t>Warsaw, Mazowieckie, Poland</t>
         </is>
       </c>
-      <c r="G26" s="29" t="inlineStr">
+      <c r="G26" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H26" s="29" t="inlineStr">
+      <c r="H26" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 11:43 UTC</t>
         </is>
       </c>
-      <c r="I26" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J26" s="31" t="inlineStr">
+      <c r="I26" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J26" s="34" t="inlineStr">
         <is>
           <t>https://pl.linkedin.com/jobs/view/internship-in-global-ai-sales-enablement-analytics-at-schneider-electric-4400403670?refId=0j6PfgagLJw81v3dQ49jXQ%3D%3D&amp;trackingId=ErR9yiUH1tcny4hRKbXl8A%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K26" s="29" t="inlineStr">
+      <c r="K26" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-schneider-electric-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L26" s="29" t="inlineStr">
+      <c r="L26" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-schneider-electric-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M26" s="29" t="inlineStr"/>
+      <c r="M26" s="32" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="29" t="inlineStr">
+      <c r="A27" s="32" t="inlineStr">
         <is>
           <t>linkedin_4297755027</t>
         </is>
       </c>
-      <c r="B27" s="29" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C27" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D27" s="29" t="inlineStr">
+      <c r="C27" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D27" s="32" t="inlineStr">
         <is>
           <t>Databricks</t>
         </is>
       </c>
-      <c r="E27" s="29" t="inlineStr">
+      <c r="E27" s="32" t="inlineStr">
         <is>
           <t>PhD GenAI Research Scientist Intern</t>
         </is>
       </c>
-      <c r="F27" s="29" t="inlineStr">
+      <c r="F27" s="32" t="inlineStr">
         <is>
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="G27" s="29" t="inlineStr">
+      <c r="G27" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H27" s="29" t="inlineStr">
+      <c r="H27" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 10:31 UTC</t>
         </is>
       </c>
-      <c r="I27" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J27" s="31" t="inlineStr">
+      <c r="I27" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J27" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-genai-research-scientist-intern-at-databricks-4297755027?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=UXoh9K97xsqO%2FzDhCy7Uug%3D%3D&amp;position=8&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K27" s="29" t="inlineStr">
+      <c r="K27" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-databricks-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L27" s="29" t="inlineStr">
+      <c r="L27" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-databricks-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M27" s="29" t="inlineStr"/>
+      <c r="M27" s="32" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="29" t="inlineStr">
+      <c r="A28" s="32" t="inlineStr">
         <is>
           <t>linkedin_4401843829</t>
         </is>
       </c>
-      <c r="B28" s="29" t="inlineStr">
+      <c r="B28" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C28" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D28" s="29" t="inlineStr">
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D28" s="32" t="inlineStr">
         <is>
           <t>Tiger Brokers Singapore</t>
         </is>
       </c>
-      <c r="E28" s="29" t="inlineStr">
+      <c r="E28" s="32" t="inlineStr">
         <is>
           <t>Quantitative Investment Analyst Intern</t>
         </is>
       </c>
-      <c r="F28" s="29" t="inlineStr">
+      <c r="F28" s="32" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G28" s="29" t="inlineStr">
+      <c r="G28" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H28" s="29" t="inlineStr">
+      <c r="H28" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 06:09 UTC</t>
         </is>
       </c>
-      <c r="I28" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J28" s="31" t="inlineStr">
+      <c r="I28" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J28" s="34" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/quantitative-investment-analyst-intern-at-tiger-brokers-singapore-4401843829?refId=LJ4PwcXqLhd1gtOBe9ZVig%3D%3D&amp;trackingId=oxh8Ol2m1QKvqfrvl10UqA%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K28" s="29" t="inlineStr">
+      <c r="K28" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-tiger-brokers-singapore-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L28" s="29" t="inlineStr">
+      <c r="L28" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-tiger-brokers-singapore-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M28" s="29" t="inlineStr"/>
+      <c r="M28" s="32" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="29" t="inlineStr">
+      <c r="A29" s="32" t="inlineStr">
         <is>
           <t>linkedin_4400148847</t>
         </is>
       </c>
-      <c r="B29" s="29" t="inlineStr">
+      <c r="B29" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C29" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D29" s="29" t="inlineStr">
+      <c r="C29" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D29" s="32" t="inlineStr">
         <is>
           <t>Boomlet</t>
         </is>
       </c>
-      <c r="E29" s="29" t="inlineStr">
+      <c r="E29" s="32" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F29" s="29" t="inlineStr">
+      <c r="F29" s="32" t="inlineStr">
         <is>
           <t>Mumbai, Maharashtra, India</t>
         </is>
       </c>
-      <c r="G29" s="29" t="inlineStr">
+      <c r="G29" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H29" s="29" t="inlineStr">
+      <c r="H29" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 05:24 UTC</t>
         </is>
       </c>
-      <c r="I29" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J29" s="31" t="inlineStr">
+      <c r="I29" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J29" s="34" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-boomlet-4400148847?refId=vAgiKqchg4pd6EgGGQ%2FF%2FA%3D%3D&amp;trackingId=IoHiSd1L28nXXarEd4gYfw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K29" s="29" t="inlineStr">
+      <c r="K29" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boomlet-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L29" s="29" t="inlineStr">
+      <c r="L29" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boomlet-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M29" s="29" t="inlineStr"/>
+      <c r="M29" s="32" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="29" t="inlineStr">
+      <c r="A30" s="32" t="inlineStr">
         <is>
           <t>linkedin_4401844394</t>
         </is>
       </c>
-      <c r="B30" s="29" t="inlineStr">
+      <c r="B30" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C30" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D30" s="29" t="inlineStr">
+      <c r="C30" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D30" s="32" t="inlineStr">
         <is>
           <t>On-us</t>
         </is>
       </c>
-      <c r="E30" s="29" t="inlineStr">
+      <c r="E30" s="32" t="inlineStr">
         <is>
           <t>AI Business Analyst Summer Intern</t>
         </is>
       </c>
-      <c r="F30" s="29" t="inlineStr">
+      <c r="F30" s="32" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G30" s="29" t="inlineStr">
+      <c r="G30" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H30" s="29" t="inlineStr">
+      <c r="H30" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 04:56 UTC</t>
         </is>
       </c>
-      <c r="I30" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J30" s="31" t="inlineStr">
+      <c r="I30" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J30" s="34" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/ai-business-analyst-summer-intern-at-on-us-4401844394?refId=lslydLUu5l8kXOktysXYaw%3D%3D&amp;trackingId=BQ%2BoYgH5QtZKBWGZQgBfNQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K30" s="29" t="inlineStr">
+      <c r="K30" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-on-us-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L30" s="29" t="inlineStr">
+      <c r="L30" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-on-us-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M30" s="29" t="inlineStr"/>
+      <c r="M30" s="32" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="inlineStr">
+      <c r="A31" s="32" t="inlineStr">
         <is>
           <t>linkedin_4401837715</t>
         </is>
       </c>
-      <c r="B31" s="29" t="inlineStr">
+      <c r="B31" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C31" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D31" s="29" t="inlineStr">
+      <c r="C31" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D31" s="32" t="inlineStr">
         <is>
           <t>Pathos Consultancy</t>
         </is>
       </c>
-      <c r="E31" s="29" t="inlineStr">
+      <c r="E31" s="32" t="inlineStr">
         <is>
           <t>Quantitative Research &amp; Development Internships</t>
         </is>
       </c>
-      <c r="F31" s="29" t="inlineStr">
+      <c r="F31" s="32" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G31" s="29" t="inlineStr">
+      <c r="G31" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H31" s="29" t="inlineStr">
+      <c r="H31" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 03:48 UTC</t>
         </is>
       </c>
-      <c r="I31" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J31" s="31" t="inlineStr">
+      <c r="I31" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J31" s="34" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/quantitative-research-development-internships-at-pathos-consultancy-4401837715?refId=KzaD5RMOfYQEZyaw6UmcpQ%3D%3D&amp;trackingId=eIGVr2dDtK%2F1o37C90xRoQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K31" s="29" t="inlineStr">
+      <c r="K31" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-pathos-consultancy-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L31" s="29" t="inlineStr">
+      <c r="L31" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-pathos-consultancy-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M31" s="29" t="inlineStr"/>
+      <c r="M31" s="32" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="29" t="inlineStr">
+      <c r="A32" s="32" t="inlineStr">
         <is>
           <t>linkedin_4402662606</t>
         </is>
       </c>
-      <c r="B32" s="29" t="inlineStr">
+      <c r="B32" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C32" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D32" s="29" t="inlineStr">
+      <c r="C32" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D32" s="32" t="inlineStr">
         <is>
           <t>Stripe</t>
         </is>
       </c>
-      <c r="E32" s="29" t="inlineStr">
+      <c r="E32" s="32" t="inlineStr">
         <is>
           <t>PhD Machine Learning Engineer, Intern</t>
         </is>
       </c>
-      <c r="F32" s="29" t="inlineStr">
+      <c r="F32" s="32" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G32" s="29" t="inlineStr">
+      <c r="G32" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H32" s="29" t="inlineStr">
+      <c r="H32" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 02:23 UTC</t>
         </is>
       </c>
-      <c r="I32" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J32" s="31" t="inlineStr">
+      <c r="I32" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J32" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-machine-learning-engineer-intern-at-stripe-4402662606?refId=vJILgNySaXYUQknbyaKZZQ%3D%3D&amp;trackingId=NDMzaPfHMoCKo5uxI3THcw%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K32" s="29" t="inlineStr">
+      <c r="K32" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L32" s="29" t="inlineStr">
+      <c r="L32" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M32" s="29" t="inlineStr"/>
+      <c r="M32" s="32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="29" t="inlineStr">
+      <c r="A33" s="32" t="inlineStr">
         <is>
           <t>linkedin_4402953925</t>
         </is>
       </c>
-      <c r="B33" s="29" t="inlineStr">
+      <c r="B33" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C33" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D33" s="29" t="inlineStr">
+      <c r="C33" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D33" s="32" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E33" s="29" t="inlineStr">
+      <c r="E33" s="32" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F33" s="29" t="inlineStr">
+      <c r="F33" s="32" t="inlineStr">
         <is>
           <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
-      <c r="G33" s="29" t="inlineStr">
+      <c r="G33" s="32" t="inlineStr">
         <is>
           <t>Middle_East</t>
         </is>
       </c>
-      <c r="H33" s="29" t="inlineStr">
+      <c r="H33" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 00:00 UTC</t>
         </is>
       </c>
-      <c r="I33" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J33" s="31" t="inlineStr">
+      <c r="I33" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J33" s="34" t="inlineStr">
         <is>
           <t>https://ae.linkedin.com/jobs/view/research-intern-at-skycliff-it-4402953925?refId=f%2BmSR6Ncm83dISKgoQTrbw%3D%3D&amp;trackingId=CdPOXElDD3wJKKeBZSdWsw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K33" s="29" t="inlineStr">
+      <c r="K33" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L33" s="29" t="inlineStr">
+      <c r="L33" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M33" s="29" t="inlineStr"/>
+      <c r="M33" s="32" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="29" t="inlineStr">
+      <c r="A34" s="32" t="inlineStr">
         <is>
           <t>linkedin_4402617206</t>
         </is>
       </c>
-      <c r="B34" s="29" t="inlineStr">
+      <c r="B34" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C34" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D34" s="29" t="inlineStr">
+      <c r="C34" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D34" s="32" t="inlineStr">
         <is>
           <t>Stripe</t>
         </is>
       </c>
-      <c r="E34" s="29" t="inlineStr">
+      <c r="E34" s="32" t="inlineStr">
         <is>
           <t>PhD Machine Learning Engineer, Intern</t>
         </is>
       </c>
-      <c r="F34" s="29" t="inlineStr">
+      <c r="F34" s="32" t="inlineStr">
         <is>
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="G34" s="29" t="inlineStr">
+      <c r="G34" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H34" s="29" t="inlineStr">
+      <c r="H34" s="32" t="inlineStr">
         <is>
           <t>2026-04-15 20:25 UTC</t>
         </is>
       </c>
-      <c r="I34" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J34" s="31" t="inlineStr">
+      <c r="I34" s="35" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="J34" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-machine-learning-engineer-intern-at-stripe-4402617206?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=yAc4U29LYJcrlQSUWWcubA%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K34" s="29" t="inlineStr">
+      <c r="K34" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L34" s="29" t="inlineStr">
+      <c r="L34" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M34" s="29" t="inlineStr"/>
+      <c r="M34" s="32" t="inlineStr">
+        <is>
+          <t>Status set via Telegram command</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="29" t="inlineStr">
+      <c r="A35" s="32" t="inlineStr">
         <is>
           <t>linkedin_4403183407</t>
         </is>
       </c>
-      <c r="B35" s="29" t="inlineStr">
+      <c r="B35" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C35" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D35" s="29" t="inlineStr">
+      <c r="C35" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D35" s="32" t="inlineStr">
         <is>
           <t>Hardware FYI</t>
         </is>
       </c>
-      <c r="E35" s="29" t="inlineStr">
+      <c r="E35" s="32" t="inlineStr">
         <is>
           <t>Robotics - Applied Scientist II Intern / Co-op - 2026 (Robotics, Manipulation, Perception, Motion Planning, Autonomous Mobile Robots, Computer Vision, Machine Learning, Controls, and more)</t>
         </is>
       </c>
-      <c r="F35" s="29" t="inlineStr">
+      <c r="F35" s="32" t="inlineStr">
         <is>
           <t>Boston, MA</t>
         </is>
       </c>
-      <c r="G35" s="29" t="inlineStr">
+      <c r="G35" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H35" s="29" t="inlineStr">
+      <c r="H35" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 04:31 UTC</t>
         </is>
       </c>
-      <c r="I35" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J35" s="31" t="inlineStr">
+      <c r="I35" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J35" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/robotics-applied-scientist-ii-intern-co-op-2026-robotics-manipulation-perception-motion-planning-autonomous-mobile-robots-computer-vision-machine-learning-controls-and-more-at-hardware-fyi-4403183407?refId=s5WxXRPJ8QU7G2WPi2yNiw%3D%3D&amp;trackingId=rjd%2F8qdM5kQMmADtGJgSSw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K35" s="29" t="inlineStr">
+      <c r="K35" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-hardware-fyi-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L35" s="29" t="inlineStr">
+      <c r="L35" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-hardware-fyi-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M35" s="29" t="inlineStr"/>
+      <c r="M35" s="32" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="29" t="inlineStr">
+      <c r="A36" s="32" t="inlineStr">
         <is>
           <t>linkedin_4403153262</t>
         </is>
       </c>
-      <c r="B36" s="29" t="inlineStr">
+      <c r="B36" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C36" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D36" s="29" t="inlineStr">
+      <c r="C36" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D36" s="32" t="inlineStr">
         <is>
           <t>Generali Malaysia</t>
         </is>
       </c>
-      <c r="E36" s="29" t="inlineStr">
+      <c r="E36" s="32" t="inlineStr">
         <is>
           <t>Intern, IT (AI Engineering)</t>
         </is>
       </c>
-      <c r="F36" s="29" t="inlineStr">
+      <c r="F36" s="32" t="inlineStr">
         <is>
           <t>Federal Territory of Kuala Lumpur, Malaysia</t>
         </is>
       </c>
-      <c r="G36" s="29" t="inlineStr">
+      <c r="G36" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H36" s="29" t="inlineStr">
+      <c r="H36" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 00:47 UTC</t>
         </is>
       </c>
-      <c r="I36" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J36" s="31" t="inlineStr">
+      <c r="I36" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J36" s="34" t="inlineStr">
         <is>
           <t>https://my.linkedin.com/jobs/view/intern-it-ai-engineering-at-generali-malaysia-4403153262?refId=h4J9hFjDRjjPW7bUqRcUZQ%3D%3D&amp;trackingId=WmqITEtGX486sbNH6b%2BYmA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K36" s="29" t="inlineStr">
+      <c r="K36" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-generali-malaysia-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L36" s="29" t="inlineStr">
+      <c r="L36" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-generali-malaysia-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M36" s="29" t="inlineStr"/>
+      <c r="M36" s="32" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="29" t="inlineStr">
+      <c r="A37" s="32" t="inlineStr">
         <is>
           <t>linkedin_4402311007</t>
         </is>
       </c>
-      <c r="B37" s="29" t="inlineStr">
+      <c r="B37" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C37" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D37" s="29" t="inlineStr">
+      <c r="C37" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D37" s="32" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E37" s="29" t="inlineStr">
+      <c r="E37" s="32" t="inlineStr">
         <is>
           <t>SAP iXp Intern - Customer Success Engineering, Operations &amp; AI Enablement [Boston]</t>
         </is>
       </c>
-      <c r="F37" s="29" t="inlineStr">
+      <c r="F37" s="32" t="inlineStr">
         <is>
           <t>Burlington, MA</t>
         </is>
       </c>
-      <c r="G37" s="29" t="inlineStr">
+      <c r="G37" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H37" s="29" t="inlineStr">
+      <c r="H37" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 21:40 UTC</t>
         </is>
       </c>
-      <c r="I37" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J37" s="31" t="inlineStr">
+      <c r="I37" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J37" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/sap-ixp-intern-%C2%A0customer-success-engineering-operations-ai-enablement-boston-at-sap-4402311007?refId=ofb0jzd8xWUoUtvr7A%2BwXQ%3D%3D&amp;trackingId=S%2Fo4FvRdeOcn00Jo5DVUBw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K37" s="29" t="inlineStr">
+      <c r="K37" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L37" s="29" t="inlineStr">
+      <c r="L37" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M37" s="29" t="inlineStr"/>
+      <c r="M37" s="32" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="29" t="inlineStr">
+      <c r="A38" s="32" t="inlineStr">
         <is>
           <t>linkedin_4403154707</t>
         </is>
       </c>
-      <c r="B38" s="29" t="inlineStr">
+      <c r="B38" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C38" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D38" s="29" t="inlineStr">
+      <c r="C38" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D38" s="32" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E38" s="29" t="inlineStr">
+      <c r="E38" s="32" t="inlineStr">
         <is>
           <t>Software Engineer Intern, Perception Data</t>
         </is>
       </c>
-      <c r="F38" s="29" t="inlineStr">
+      <c r="F38" s="32" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G38" s="29" t="inlineStr">
+      <c r="G38" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H38" s="29" t="inlineStr">
+      <c r="H38" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 02:21 UTC</t>
         </is>
       </c>
-      <c r="I38" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J38" s="31" t="inlineStr">
+      <c r="I38" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J38" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/software-engineer-intern-perception-data-at-zoox-4403154707?refId=ON4L5FUhksKAgylRRsNllQ%3D%3D&amp;trackingId=1%2F3OkqP%2Bu0PqHp9bXnlS0A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K38" s="29" t="inlineStr">
+      <c r="K38" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L38" s="29" t="inlineStr">
+      <c r="L38" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M38" s="29" t="inlineStr"/>
+      <c r="M38" s="32" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="29" t="inlineStr">
+      <c r="A39" s="32" t="inlineStr">
         <is>
           <t>linkedin_4402947451</t>
         </is>
       </c>
-      <c r="B39" s="29" t="inlineStr">
+      <c r="B39" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C39" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D39" s="29" t="inlineStr">
+      <c r="C39" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D39" s="32" t="inlineStr">
         <is>
           <t>Rubrik</t>
         </is>
       </c>
-      <c r="E39" s="29" t="inlineStr">
+      <c r="E39" s="32" t="inlineStr">
         <is>
           <t>India Benefits &amp; AI Operations Intern</t>
         </is>
       </c>
-      <c r="F39" s="29" t="inlineStr">
+      <c r="F39" s="32" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G39" s="29" t="inlineStr">
+      <c r="G39" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H39" s="29" t="inlineStr">
+      <c r="H39" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 11:40 UTC</t>
         </is>
       </c>
-      <c r="I39" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J39" s="31" t="inlineStr">
+      <c r="I39" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J39" s="34" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/india-benefits-ai-operations-intern-at-rubrik-4402947451?refId=9u2uyUYzyMZimaTtDELDWg%3D%3D&amp;trackingId=BjOmyeYm6McmUpzLwcES9g%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K39" s="29" t="inlineStr">
+      <c r="K39" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-rubrik-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L39" s="29" t="inlineStr">
+      <c r="L39" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-rubrik-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M39" s="29" t="inlineStr"/>
+      <c r="M39" s="32" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="29" t="inlineStr">
+      <c r="A40" s="32" t="inlineStr">
         <is>
           <t>linkedin_4390354006</t>
         </is>
       </c>
-      <c r="B40" s="29" t="inlineStr">
+      <c r="B40" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C40" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D40" s="29" t="inlineStr">
+      <c r="C40" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D40" s="32" t="inlineStr">
         <is>
           <t>Lila Sciences</t>
         </is>
       </c>
-      <c r="E40" s="29" t="inlineStr">
+      <c r="E40" s="32" t="inlineStr">
         <is>
           <t>Intern, Next Gen AI Robotics</t>
         </is>
       </c>
-      <c r="F40" s="29" t="inlineStr">
+      <c r="F40" s="32" t="inlineStr">
         <is>
           <t>Cambridge, MA</t>
         </is>
       </c>
-      <c r="G40" s="29" t="inlineStr">
+      <c r="G40" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H40" s="29" t="inlineStr">
+      <c r="H40" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 10:58 UTC</t>
         </is>
       </c>
-      <c r="I40" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J40" s="31" t="inlineStr">
+      <c r="I40" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J40" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/intern-next-gen-ai-robotics-at-lila-sciences-4390354006?refId=ZoXJQXesL%2FE%2B5EAGGzWfiA%3D%3D&amp;trackingId=FmSMwWhyyIaC52NsDwOCtw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K40" s="29" t="inlineStr">
+      <c r="K40" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-lila-sciences-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L40" s="29" t="inlineStr">
+      <c r="L40" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-lila-sciences-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M40" s="29" t="inlineStr"/>
+      <c r="M40" s="32" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="29" t="inlineStr">
+      <c r="A41" s="32" t="inlineStr">
         <is>
           <t>arbeitnow_ai-venture-development-tech-intern-berlin-100382</t>
         </is>
       </c>
-      <c r="B41" s="29" t="inlineStr">
+      <c r="B41" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C41" s="29" t="inlineStr">
+      <c r="C41" s="32" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="D41" s="29" t="inlineStr">
+      <c r="D41" s="32" t="inlineStr">
         <is>
           <t>Zeeg</t>
         </is>
       </c>
-      <c r="E41" s="29" t="inlineStr">
+      <c r="E41" s="32" t="inlineStr">
         <is>
           <t>AI &amp; Venture Development Tech Intern (w/m/d)</t>
         </is>
       </c>
-      <c r="F41" s="29" t="inlineStr">
+      <c r="F41" s="32" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="G41" s="29" t="inlineStr">
+      <c r="G41" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H41" s="29" t="inlineStr">
+      <c r="H41" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 10:30 UTC</t>
         </is>
       </c>
-      <c r="I41" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J41" s="31" t="inlineStr">
+      <c r="I41" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J41" s="34" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/zeeg/ai-venture-development-tech-intern-berlin-100382</t>
         </is>
       </c>
-      <c r="K41" s="29" t="inlineStr">
+      <c r="K41" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zeeg-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L41" s="29" t="inlineStr">
+      <c r="L41" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zeeg-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M41" s="29" t="inlineStr"/>
+      <c r="M41" s="32" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="29" t="inlineStr">
+      <c r="A42" s="32" t="inlineStr">
         <is>
           <t>linkedin_4391388054</t>
         </is>
       </c>
-      <c r="B42" s="29" t="inlineStr">
+      <c r="B42" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C42" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D42" s="29" t="inlineStr">
+      <c r="C42" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D42" s="32" t="inlineStr">
         <is>
           <t>Mackenzie Investments</t>
         </is>
       </c>
-      <c r="E42" s="29" t="inlineStr">
+      <c r="E42" s="32" t="inlineStr">
         <is>
           <t>Fall Intern 2026 - Data Science (Toronto Office)</t>
         </is>
       </c>
-      <c r="F42" s="29" t="inlineStr">
+      <c r="F42" s="32" t="inlineStr">
         <is>
           <t>Greater Toronto Area, Canada</t>
         </is>
       </c>
-      <c r="G42" s="29" t="inlineStr">
+      <c r="G42" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H42" s="29" t="inlineStr">
+      <c r="H42" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 14:00 UTC</t>
         </is>
       </c>
-      <c r="I42" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J42" s="31" t="inlineStr">
+      <c r="I42" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J42" s="34" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/fall-intern-2026-data-science-toronto-office-at-mackenzie-investments-4391388054?refId=ay8O%2Bgf7Gtfb1Rpr3XZOhg%3D%3D&amp;trackingId=O%2F%2FJTpCmUhvp4jSfNkV5bg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K42" s="29" t="inlineStr">
+      <c r="K42" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-mackenzie-investments-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L42" s="29" t="inlineStr">
+      <c r="L42" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-mackenzie-investments-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M42" s="29" t="inlineStr"/>
+      <c r="M42" s="32" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="inlineStr">
+      <c r="A43" s="32" t="inlineStr">
         <is>
           <t>linkedin_4390747937</t>
         </is>
       </c>
-      <c r="B43" s="29" t="inlineStr">
+      <c r="B43" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C43" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D43" s="29" t="inlineStr">
+      <c r="C43" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D43" s="32" t="inlineStr">
         <is>
           <t>BCG X</t>
         </is>
       </c>
-      <c r="E43" s="29" t="inlineStr">
+      <c r="E43" s="32" t="inlineStr">
         <is>
           <t>Visiting Forward Deployed AI Engineer, Internship, Germany - BCG X</t>
         </is>
       </c>
-      <c r="F43" s="29" t="inlineStr">
+      <c r="F43" s="32" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G43" s="29" t="inlineStr">
+      <c r="G43" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H43" s="29" t="inlineStr">
+      <c r="H43" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 13:51 UTC</t>
         </is>
       </c>
-      <c r="I43" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J43" s="31" t="inlineStr">
+      <c r="I43" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J43" s="34" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/visiting-forward-deployed-ai-engineer-internship-germany-bcg-x-at-bcg-x-4390747937?refId=1JxxxPqdlRpkbbaCzu2YGQ%3D%3D&amp;trackingId=7x%2BVQU%2BWOh9IPaVXWJkc5g%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K43" s="29" t="inlineStr">
+      <c r="K43" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bcg-x-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L43" s="29" t="inlineStr">
+      <c r="L43" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bcg-x-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M43" s="29" t="inlineStr"/>
+      <c r="M43" s="32" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="29" t="inlineStr">
+      <c r="A44" s="32" t="inlineStr">
         <is>
           <t>linkedin_4402726053</t>
         </is>
       </c>
-      <c r="B44" s="29" t="inlineStr">
+      <c r="B44" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C44" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D44" s="29" t="inlineStr">
+      <c r="C44" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D44" s="32" t="inlineStr">
         <is>
           <t>targetjobs UK</t>
         </is>
       </c>
-      <c r="E44" s="29" t="inlineStr">
+      <c r="E44" s="32" t="inlineStr">
         <is>
           <t>Internship: AI/ML for Ionospheric TEC Modelling</t>
         </is>
       </c>
-      <c r="F44" s="29" t="inlineStr">
+      <c r="F44" s="32" t="inlineStr">
         <is>
           <t>Reigate, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G44" s="29" t="inlineStr">
+      <c r="G44" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H44" s="29" t="inlineStr">
+      <c r="H44" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 14:25 UTC</t>
         </is>
       </c>
-      <c r="I44" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J44" s="31" t="inlineStr">
+      <c r="I44" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J44" s="34" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/internship-ai-ml-for-ionospheric-tec-modelling-at-targetjobs-uk-4402726053?refId=a1g6hMZsvI1y2Eje2OvLAA%3D%3D&amp;trackingId=IVJSJGE7Non8cohorDs%2F5A%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K44" s="29" t="inlineStr">
+      <c r="K44" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-targetjobs-uk-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L44" s="29" t="inlineStr">
+      <c r="L44" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-targetjobs-uk-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M44" s="29" t="inlineStr"/>
+      <c r="M44" s="32" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="29" t="inlineStr">
+      <c r="A45" s="32" t="inlineStr">
         <is>
           <t>linkedin_4400837114</t>
         </is>
       </c>
-      <c r="B45" s="29" t="inlineStr">
+      <c r="B45" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C45" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D45" s="29" t="inlineStr">
+      <c r="C45" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D45" s="32" t="inlineStr">
         <is>
           <t>Innovexis</t>
         </is>
       </c>
-      <c r="E45" s="29" t="inlineStr">
+      <c r="E45" s="32" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F45" s="29" t="inlineStr">
+      <c r="F45" s="32" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G45" s="29" t="inlineStr">
+      <c r="G45" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H45" s="29" t="inlineStr">
+      <c r="H45" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 13:04 UTC</t>
         </is>
       </c>
-      <c r="I45" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J45" s="31" t="inlineStr">
+      <c r="I45" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J45" s="34" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-innovexis-4400837114?refId=CVM89%2F3%2F%2BshqMJLc4IfFMg%3D%3D&amp;trackingId=j9WpQwI4k1ip7aRr%2Fv5Img%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K45" s="29" t="inlineStr">
+      <c r="K45" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-innovexis-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L45" s="29" t="inlineStr">
+      <c r="L45" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-innovexis-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M45" s="29" t="inlineStr"/>
+      <c r="M45" s="32" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="29" t="inlineStr">
+      <c r="A46" s="32" t="inlineStr">
         <is>
           <t>linkedin_4391074158</t>
         </is>
       </c>
-      <c r="B46" s="29" t="inlineStr">
+      <c r="B46" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C46" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D46" s="29" t="inlineStr">
+      <c r="C46" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D46" s="32" t="inlineStr">
         <is>
           <t>BMW Group</t>
         </is>
       </c>
-      <c r="E46" s="29" t="inlineStr">
+      <c r="E46" s="32" t="inlineStr">
         <is>
           <t>Intern IT Technology, Sales Volume Planning &amp; AI Support (f/m/x)</t>
         </is>
       </c>
-      <c r="F46" s="29" t="inlineStr">
+      <c r="F46" s="32" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G46" s="29" t="inlineStr">
+      <c r="G46" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H46" s="29" t="inlineStr">
+      <c r="H46" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 12:45 UTC</t>
         </is>
       </c>
-      <c r="I46" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J46" s="31" t="inlineStr">
+      <c r="I46" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J46" s="34" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/intern-it-technology-sales-volume-planning-ai-support-f-m-x-at-bmw-group-4391074158?refId=tHG5EqbLn3IDBqsSj%2FsUUg%3D%3D&amp;trackingId=OakOlgDcU0hWTRXcoLe3UA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K46" s="29" t="inlineStr">
+      <c r="K46" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bmw-group-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L46" s="29" t="inlineStr">
+      <c r="L46" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bmw-group-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M46" s="29" t="inlineStr"/>
+      <c r="M46" s="32" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="29" t="inlineStr">
+      <c r="A47" s="32" t="inlineStr">
         <is>
           <t>linkedin_4402725075</t>
         </is>
       </c>
-      <c r="B47" s="29" t="inlineStr">
+      <c r="B47" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C47" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D47" s="29" t="inlineStr">
+      <c r="C47" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D47" s="32" t="inlineStr">
         <is>
           <t>DARE</t>
         </is>
       </c>
-      <c r="E47" s="29" t="inlineStr">
+      <c r="E47" s="32" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F47" s="29" t="inlineStr">
+      <c r="F47" s="32" t="inlineStr">
         <is>
           <t>WP. Kuala Lumpur, Federal Territory of Kuala Lumpur, Malaysia</t>
         </is>
       </c>
-      <c r="G47" s="29" t="inlineStr">
+      <c r="G47" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H47" s="29" t="inlineStr">
+      <c r="H47" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 14:36 UTC</t>
         </is>
       </c>
-      <c r="I47" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J47" s="31" t="inlineStr">
+      <c r="I47" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J47" s="34" t="inlineStr">
         <is>
           <t>https://my.linkedin.com/jobs/view/research-intern-at-dare-4402725075?refId=xbzZXyF6FfcYy036eklDWw%3D%3D&amp;trackingId=QRt5DhbLSINvmHia0jEWIg%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K47" s="29" t="inlineStr">
+      <c r="K47" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dare-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L47" s="29" t="inlineStr">
+      <c r="L47" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dare-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M47" s="29" t="inlineStr"/>
+      <c r="M47" s="32" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="29" t="inlineStr">
+      <c r="A48" s="32" t="inlineStr">
         <is>
           <t>linkedin_4402745391</t>
         </is>
       </c>
-      <c r="B48" s="29" t="inlineStr">
+      <c r="B48" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C48" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D48" s="29" t="inlineStr">
+      <c r="C48" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D48" s="32" t="inlineStr">
         <is>
           <t>Huawei Technologies Research &amp; Development (UK) Ltd</t>
         </is>
       </c>
-      <c r="E48" s="29" t="inlineStr">
+      <c r="E48" s="32" t="inlineStr">
         <is>
           <t>Research Intern - Computer Vision</t>
         </is>
       </c>
-      <c r="F48" s="29" t="inlineStr">
+      <c r="F48" s="32" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G48" s="29" t="inlineStr">
+      <c r="G48" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H48" s="29" t="inlineStr">
+      <c r="H48" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 18:42 UTC</t>
         </is>
       </c>
-      <c r="I48" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J48" s="31" t="inlineStr">
+      <c r="I48" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J48" s="34" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/research-intern-computer-vision-at-huawei-technologies-research-development-uk-ltd-4402745391?refId=rRtCMQFBU%2FNi7vc62x5Nhg%3D%3D&amp;trackingId=%2Bt1We%2BmKhWHyXION%2FWwQVg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K48" s="29" t="inlineStr">
+      <c r="K48" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-huawei-technologies-research-development-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L48" s="29" t="inlineStr">
+      <c r="L48" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-huawei-technologies-research-development-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M48" s="29" t="inlineStr"/>
+      <c r="M48" s="32" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="29" t="inlineStr">
+      <c r="A49" s="32" t="inlineStr">
         <is>
           <t>linkedin_4402366780</t>
         </is>
       </c>
-      <c r="B49" s="29" t="inlineStr">
+      <c r="B49" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C49" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D49" s="29" t="inlineStr">
+      <c r="C49" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D49" s="32" t="inlineStr">
         <is>
           <t>Binance</t>
         </is>
       </c>
-      <c r="E49" s="29" t="inlineStr">
+      <c r="E49" s="32" t="inlineStr">
         <is>
           <t>Binance Accelerator Program - Data Scientist (LLM &amp; Trading)</t>
         </is>
       </c>
-      <c r="F49" s="29" t="inlineStr">
+      <c r="F49" s="32" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G49" s="29" t="inlineStr">
+      <c r="G49" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H49" s="29" t="inlineStr">
+      <c r="H49" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 09:43 UTC</t>
         </is>
       </c>
-      <c r="I49" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J49" s="31" t="inlineStr">
+      <c r="I49" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J49" s="34" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/binance-accelerator-program-data-scientist-llm-trading-at-binance-4402366780?refId=bc%2BXeBTeIKMQJTmlLFwbZQ%3D%3D&amp;trackingId=9UuyRRCEPapWNu6VKdZC5A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K49" s="29" t="inlineStr">
+      <c r="K49" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-binance-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L49" s="29" t="inlineStr">
+      <c r="L49" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-binance-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M49" s="29" t="inlineStr"/>
+      <c r="M49" s="32" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="29" t="inlineStr">
+      <c r="A50" s="32" t="inlineStr">
         <is>
           <t>linkedin_4382411039</t>
         </is>
       </c>
-      <c r="B50" s="29" t="inlineStr">
+      <c r="B50" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C50" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D50" s="29" t="inlineStr">
+      <c r="C50" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D50" s="32" t="inlineStr">
         <is>
           <t>The Walt Disney Company</t>
         </is>
       </c>
-      <c r="E50" s="29" t="inlineStr">
+      <c r="E50" s="32" t="inlineStr">
         <is>
           <t>Intern, APAC Data Analytics &amp; Insights (Content Analytics) -  Jul to Dec 2026</t>
         </is>
       </c>
-      <c r="F50" s="29" t="inlineStr">
+      <c r="F50" s="32" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G50" s="29" t="inlineStr">
+      <c r="G50" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H50" s="29" t="inlineStr">
+      <c r="H50" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 23:55 UTC</t>
         </is>
       </c>
-      <c r="I50" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J50" s="31" t="inlineStr">
+      <c r="I50" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J50" s="34" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/intern-apac-data-analytics-insights-content-analytics-jul-to-dec-2026-at-the-walt-disney-company-4382411039?refId=JBvXH2fNOamnO4WZI1Y0ew%3D%3D&amp;trackingId=Rs%2FdjczlbLYSYtCwY%2F%2FJyA%3D%3D&amp;position=7&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K50" s="29" t="inlineStr">
+      <c r="K50" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-the-walt-disney-company-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L50" s="29" t="inlineStr">
+      <c r="L50" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-the-walt-disney-company-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M50" s="29" t="inlineStr"/>
+      <c r="M50" s="32" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="29" t="inlineStr">
+      <c r="A51" s="32" t="inlineStr">
         <is>
           <t>linkedin_4402305263</t>
         </is>
       </c>
-      <c r="B51" s="29" t="inlineStr">
+      <c r="B51" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C51" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D51" s="29" t="inlineStr">
+      <c r="C51" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D51" s="32" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E51" s="29" t="inlineStr">
+      <c r="E51" s="32" t="inlineStr">
         <is>
           <t>SAP iXp Intern - Software Developer (Agentic AI &amp; LLM systems)</t>
         </is>
       </c>
-      <c r="F51" s="29" t="inlineStr">
+      <c r="F51" s="32" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G51" s="29" t="inlineStr">
+      <c r="G51" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H51" s="29" t="inlineStr">
+      <c r="H51" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 21:40 UTC</t>
         </is>
       </c>
-      <c r="I51" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J51" s="31" t="inlineStr">
+      <c r="I51" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J51" s="34" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/sap-ixp-intern-software-developer-agentic-ai-llm-systems-at-sap-4402305263?refId=zBXuSSlfFyuxcdEqyfeS8g%3D%3D&amp;trackingId=Imq%2FVHMQWkkoDZp5%2BnATSA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K51" s="29" t="inlineStr">
+      <c r="K51" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L51" s="29" t="inlineStr">
+      <c r="L51" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M51" s="29" t="inlineStr"/>
+      <c r="M51" s="32" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="29" t="inlineStr">
+      <c r="A52" s="32" t="inlineStr">
         <is>
           <t>linkedin_4400467080</t>
         </is>
       </c>
-      <c r="B52" s="29" t="inlineStr">
+      <c r="B52" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C52" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D52" s="29" t="inlineStr">
+      <c r="C52" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D52" s="32" t="inlineStr">
         <is>
           <t>Saama</t>
         </is>
       </c>
-      <c r="E52" s="29" t="inlineStr">
+      <c r="E52" s="32" t="inlineStr">
         <is>
           <t>Intern for AI CoE</t>
         </is>
       </c>
-      <c r="F52" s="29" t="inlineStr">
+      <c r="F52" s="32" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G52" s="29" t="inlineStr">
+      <c r="G52" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H52" s="29" t="inlineStr">
+      <c r="H52" s="32" t="inlineStr">
         <is>
           <t>2026-04-16 19:45 UTC</t>
         </is>
       </c>
-      <c r="I52" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J52" s="31" t="inlineStr">
+      <c r="I52" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J52" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/intern-for-ai-coe-at-saama-4400467080?refId=7CvDuV2%2BR%2FzyGozq4UNPPw%3D%3D&amp;trackingId=Ls9yWFAC8lVRx8bmapJfLA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K52" s="29" t="inlineStr">
+      <c r="K52" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-saama-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L52" s="29" t="inlineStr">
+      <c r="L52" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-saama-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M52" s="29" t="inlineStr"/>
+      <c r="M52" s="32" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="29" t="inlineStr">
+      <c r="A53" s="32" t="inlineStr">
         <is>
           <t>linkedin_4400873418</t>
         </is>
       </c>
-      <c r="B53" s="29" t="inlineStr">
+      <c r="B53" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C53" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D53" s="29" t="inlineStr">
+      <c r="C53" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D53" s="32" t="inlineStr">
         <is>
           <t>SANOVIO</t>
         </is>
       </c>
-      <c r="E53" s="29" t="inlineStr">
+      <c r="E53" s="32" t="inlineStr">
         <is>
           <t>AI Engineering Intern</t>
         </is>
       </c>
-      <c r="F53" s="29" t="inlineStr">
+      <c r="F53" s="32" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G53" s="29" t="inlineStr">
+      <c r="G53" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H53" s="29" t="inlineStr">
+      <c r="H53" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 00:00 UTC</t>
         </is>
       </c>
-      <c r="I53" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J53" s="31" t="inlineStr">
+      <c r="I53" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J53" s="34" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/ai-engineering-intern-at-sanovio-4400873418?refId=egIYeNLcARu6P6oTIZ%2BHfA%3D%3D&amp;trackingId=c6wZ0DtTzvVZpTRC1l5tYQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K53" s="29" t="inlineStr">
+      <c r="K53" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sanovio-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L53" s="29" t="inlineStr">
+      <c r="L53" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sanovio-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M53" s="29" t="inlineStr"/>
+      <c r="M53" s="32" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="29" t="inlineStr">
+      <c r="A54" s="32" t="inlineStr">
         <is>
           <t>linkedin_4403524251</t>
         </is>
       </c>
-      <c r="B54" s="29" t="inlineStr">
+      <c r="B54" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C54" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D54" s="29" t="inlineStr">
+      <c r="C54" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D54" s="32" t="inlineStr">
         <is>
           <t>Nascent Markets</t>
         </is>
       </c>
-      <c r="E54" s="29" t="inlineStr">
+      <c r="E54" s="32" t="inlineStr">
         <is>
           <t>Agentic Systems Intern (Graduate Level)</t>
         </is>
       </c>
-      <c r="F54" s="29" t="inlineStr">
+      <c r="F54" s="32" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G54" s="29" t="inlineStr">
+      <c r="G54" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H54" s="29" t="inlineStr">
+      <c r="H54" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 19:53 UTC</t>
         </is>
       </c>
-      <c r="I54" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J54" s="31" t="inlineStr">
+      <c r="I54" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J54" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/agentic-systems-intern-graduate-level-at-nascent-markets-4403524251?refId=Ix0g0waARRaNpzTY4LxvsQ%3D%3D&amp;trackingId=RsqyOyJHkanw%2FTeHGUcadA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K54" s="29" t="inlineStr">
+      <c r="K54" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-nascent-markets-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L54" s="29" t="inlineStr">
+      <c r="L54" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-nascent-markets-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M54" s="29" t="inlineStr"/>
+      <c r="M54" s="32" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="29" t="inlineStr">
+      <c r="A55" s="32" t="inlineStr">
         <is>
           <t>linkedin_4402782985</t>
         </is>
       </c>
-      <c r="B55" s="29" t="inlineStr">
+      <c r="B55" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C55" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D55" s="29" t="inlineStr">
+      <c r="C55" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D55" s="32" t="inlineStr">
         <is>
           <t>Axiomatic_AI</t>
         </is>
       </c>
-      <c r="E55" s="29" t="inlineStr">
+      <c r="E55" s="32" t="inlineStr">
         <is>
           <t>Internship - Research Intern (Agentic Learning, Memory &amp; Neurosymbolic Reasoning)</t>
         </is>
       </c>
-      <c r="F55" s="29" t="inlineStr">
+      <c r="F55" s="32" t="inlineStr">
         <is>
           <t>Greater Barcelona Metropolitan Area</t>
         </is>
       </c>
-      <c r="G55" s="29" t="inlineStr">
+      <c r="G55" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H55" s="29" t="inlineStr">
+      <c r="H55" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 05:04 UTC</t>
         </is>
       </c>
-      <c r="I55" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J55" s="31" t="inlineStr">
+      <c r="I55" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J55" s="34" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/internship-research-intern-agentic-learning-memory-neurosymbolic-reasoning-at-axiomatic-ai-4402782985?refId=vm6No12NjZrg2BBV%2BnbuLQ%3D%3D&amp;trackingId=X9FXk%2FBDFftROMNo9Cr20g%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K55" s="29" t="inlineStr">
+      <c r="K55" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-axiomatic-ai-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L55" s="29" t="inlineStr">
+      <c r="L55" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-axiomatic-ai-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M55" s="29" t="inlineStr"/>
+      <c r="M55" s="32" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="29" t="inlineStr">
+      <c r="A56" s="32" t="inlineStr">
         <is>
           <t>linkedin_4309694978</t>
         </is>
       </c>
-      <c r="B56" s="29" t="inlineStr">
+      <c r="B56" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C56" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D56" s="29" t="inlineStr">
+      <c r="C56" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D56" s="32" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E56" s="29" t="inlineStr">
+      <c r="E56" s="32" t="inlineStr">
         <is>
           <t>Graduate Physics Research Intern</t>
         </is>
       </c>
-      <c r="F56" s="29" t="inlineStr">
+      <c r="F56" s="32" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
       </c>
-      <c r="G56" s="29" t="inlineStr">
+      <c r="G56" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H56" s="29" t="inlineStr">
+      <c r="H56" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 17:37 UTC</t>
         </is>
       </c>
-      <c r="I56" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J56" s="31" t="inlineStr">
+      <c r="I56" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J56" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/graduate-physics-research-intern-at-dataannotation-4309694978?refId=hlpC50hTZs9sJFHirXWMSg%3D%3D&amp;trackingId=1E0ixzzpb6MzeHKgxpE3Cw%3D%3D&amp;position=9&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K56" s="29" t="inlineStr">
+      <c r="K56" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L56" s="29" t="inlineStr">
+      <c r="L56" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M56" s="29" t="inlineStr"/>
+      <c r="M56" s="32" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="29" t="inlineStr">
+      <c r="A57" s="32" t="inlineStr">
         <is>
           <t>linkedin_4403562730</t>
         </is>
       </c>
-      <c r="B57" s="29" t="inlineStr">
+      <c r="B57" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C57" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D57" s="29" t="inlineStr">
+      <c r="C57" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D57" s="32" t="inlineStr">
         <is>
           <t>BNM Business Solutions LLP</t>
         </is>
       </c>
-      <c r="E57" s="29" t="inlineStr">
+      <c r="E57" s="32" t="inlineStr">
         <is>
           <t>Data Analyst Internship in Navi Mumbai, Mumbai</t>
         </is>
       </c>
-      <c r="F57" s="29" t="inlineStr">
+      <c r="F57" s="32" t="inlineStr">
         <is>
           <t>Mumbai Metropolitan Region</t>
         </is>
       </c>
-      <c r="G57" s="29" t="inlineStr">
+      <c r="G57" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H57" s="29" t="inlineStr">
+      <c r="H57" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 00:06 UTC</t>
         </is>
       </c>
-      <c r="I57" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J57" s="31" t="inlineStr">
+      <c r="I57" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J57" s="34" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-internship-in-navi-mumbai-mumbai-at-bnm-business-solutions-llp-4403562730?refId=1X9LgKP3%2FAPeJuhZVjyhxw%3D%3D&amp;trackingId=oFY9Z69ZBEGkNtq0cbBOMw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K57" s="29" t="inlineStr">
+      <c r="K57" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bnm-business-solutions-llp-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L57" s="29" t="inlineStr">
+      <c r="L57" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bnm-business-solutions-llp-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M57" s="29" t="inlineStr"/>
+      <c r="M57" s="32" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="29" t="inlineStr">
+      <c r="A58" s="32" t="inlineStr">
         <is>
           <t>linkedin_4309694917</t>
         </is>
       </c>
-      <c r="B58" s="29" t="inlineStr">
+      <c r="B58" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C58" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D58" s="29" t="inlineStr">
+      <c r="C58" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D58" s="32" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E58" s="29" t="inlineStr">
+      <c r="E58" s="32" t="inlineStr">
         <is>
           <t>Graduate Biology Research Intern</t>
         </is>
       </c>
-      <c r="F58" s="29" t="inlineStr">
+      <c r="F58" s="32" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
       </c>
-      <c r="G58" s="29" t="inlineStr">
+      <c r="G58" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H58" s="29" t="inlineStr">
+      <c r="H58" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 17:35 UTC</t>
         </is>
       </c>
-      <c r="I58" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J58" s="31" t="inlineStr">
+      <c r="I58" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J58" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/graduate-biology-research-intern-at-dataannotation-4309694917?refId=hlpC50hTZs9sJFHirXWMSg%3D%3D&amp;trackingId=BM%2FBx4ElnXDk5hEpiM0gzg%3D%3D&amp;position=8&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K58" s="29" t="inlineStr">
+      <c r="K58" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L58" s="29" t="inlineStr">
+      <c r="L58" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M58" s="29" t="inlineStr"/>
+      <c r="M58" s="32" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="29" t="inlineStr">
+      <c r="A59" s="32" t="inlineStr">
         <is>
           <t>linkedin_4346088677</t>
         </is>
       </c>
-      <c r="B59" s="29" t="inlineStr">
+      <c r="B59" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C59" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D59" s="29" t="inlineStr">
+      <c r="C59" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D59" s="32" t="inlineStr">
         <is>
           <t>revel8</t>
         </is>
       </c>
-      <c r="E59" s="29" t="inlineStr">
+      <c r="E59" s="32" t="inlineStr">
         <is>
           <t>Applied AI Engineer Intern (all genders)</t>
         </is>
       </c>
-      <c r="F59" s="29" t="inlineStr">
+      <c r="F59" s="32" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G59" s="29" t="inlineStr">
+      <c r="G59" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H59" s="29" t="inlineStr">
+      <c r="H59" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 22:38 UTC</t>
         </is>
       </c>
-      <c r="I59" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J59" s="31" t="inlineStr">
+      <c r="I59" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J59" s="34" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/applied-ai-engineer-intern-all-genders-at-revel8-4346088677?refId=FHQDN2Ta3J6B7WhWnDAuhQ%3D%3D&amp;trackingId=Pf%2Ftwn6H5Hrw8BKjPenbSQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K59" s="29" t="inlineStr">
+      <c r="K59" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-revel8-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L59" s="29" t="inlineStr">
+      <c r="L59" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-revel8-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M59" s="29" t="inlineStr"/>
+      <c r="M59" s="32" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="29" t="inlineStr">
+      <c r="A60" s="32" t="inlineStr">
         <is>
           <t>linkedin_4403475387</t>
         </is>
       </c>
-      <c r="B60" s="29" t="inlineStr">
+      <c r="B60" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C60" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D60" s="29" t="inlineStr">
+      <c r="C60" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D60" s="32" t="inlineStr">
         <is>
           <t>Inc42 Media</t>
         </is>
       </c>
-      <c r="E60" s="29" t="inlineStr">
+      <c r="E60" s="32" t="inlineStr">
         <is>
           <t>Operations Intern: Inc42 AI Summit 2026</t>
         </is>
       </c>
-      <c r="F60" s="29" t="inlineStr">
+      <c r="F60" s="32" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G60" s="29" t="inlineStr">
+      <c r="G60" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H60" s="29" t="inlineStr">
+      <c r="H60" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 16:23 UTC</t>
         </is>
       </c>
-      <c r="I60" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J60" s="31" t="inlineStr">
+      <c r="I60" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J60" s="34" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/operations-intern-inc42-ai-summit-2026-at-inc42-media-4403475387?refId=jyI2mJ9xFT%2BmdtkV0OCW0g%3D%3D&amp;trackingId=6sWKnvWNaTU69%2B7bcZNxLg%3D%3D&amp;position=10&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K60" s="29" t="inlineStr">
+      <c r="K60" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-inc42-media-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L60" s="29" t="inlineStr">
+      <c r="L60" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-inc42-media-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M60" s="29" t="inlineStr"/>
+      <c r="M60" s="32" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="29" t="inlineStr">
+      <c r="A61" s="32" t="inlineStr">
         <is>
           <t>linkedin_4403008384</t>
         </is>
       </c>
-      <c r="B61" s="29" t="inlineStr">
+      <c r="B61" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C61" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D61" s="29" t="inlineStr">
+      <c r="C61" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D61" s="32" t="inlineStr">
         <is>
           <t>VEDANTA MOBILITY</t>
         </is>
       </c>
-      <c r="E61" s="29" t="inlineStr">
+      <c r="E61" s="32" t="inlineStr">
         <is>
           <t>Founding Psychology Interns | AI Prototype (Govt Proposal – Dubai)</t>
         </is>
       </c>
-      <c r="F61" s="29" t="inlineStr">
+      <c r="F61" s="32" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G61" s="29" t="inlineStr">
+      <c r="G61" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H61" s="29" t="inlineStr">
+      <c r="H61" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 08:13 UTC</t>
         </is>
       </c>
-      <c r="I61" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J61" s="31" t="inlineStr">
+      <c r="I61" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J61" s="34" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/founding-psychology-interns-ai-prototype-govt-proposal-%E2%80%93-dubai-at-vedanta-mobility-4403008384?refId=moHjgKNH%2BrT9YT5JNnyyqw%3D%3D&amp;trackingId=RUjUOgXLH%2BLJwdPLtKtAMQ%3D%3D&amp;position=13&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K61" s="29" t="inlineStr">
+      <c r="K61" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-vedanta-mobility-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L61" s="29" t="inlineStr">
+      <c r="L61" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-vedanta-mobility-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M61" s="29" t="inlineStr"/>
+      <c r="M61" s="32" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="29" t="inlineStr">
+      <c r="A62" s="32" t="inlineStr">
         <is>
           <t>linkedin_4393616864</t>
         </is>
       </c>
-      <c r="B62" s="29" t="inlineStr">
+      <c r="B62" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C62" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D62" s="29" t="inlineStr">
+      <c r="C62" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D62" s="32" t="inlineStr">
         <is>
           <t>Medidata Solutions</t>
         </is>
       </c>
-      <c r="E62" s="29" t="inlineStr">
+      <c r="E62" s="32" t="inlineStr">
         <is>
           <t>Data Science Intern</t>
         </is>
       </c>
-      <c r="F62" s="29" t="inlineStr">
+      <c r="F62" s="32" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
       </c>
-      <c r="G62" s="29" t="inlineStr">
+      <c r="G62" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H62" s="29" t="inlineStr">
+      <c r="H62" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 13:13 UTC</t>
         </is>
       </c>
-      <c r="I62" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J62" s="31" t="inlineStr">
+      <c r="I62" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J62" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-science-intern-at-medidata-solutions-4393616864?refId=sPMU%2B0UtbDUVjDHc3gXCxA%3D%3D&amp;trackingId=%2BVrdVCzEYQ3jJQvUf4VUtA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K62" s="29" t="inlineStr">
+      <c r="K62" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-medidata-solutions-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L62" s="29" t="inlineStr">
+      <c r="L62" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-medidata-solutions-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M62" s="29" t="inlineStr"/>
+      <c r="M62" s="32" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="29" t="inlineStr">
+      <c r="A63" s="32" t="inlineStr">
         <is>
           <t>linkedin_4403819462</t>
         </is>
       </c>
-      <c r="B63" s="29" t="inlineStr">
+      <c r="B63" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C63" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D63" s="29" t="inlineStr">
+      <c r="C63" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D63" s="32" t="inlineStr">
         <is>
           <t>Calypso Commodities</t>
         </is>
       </c>
-      <c r="E63" s="29" t="inlineStr">
+      <c r="E63" s="32" t="inlineStr">
         <is>
           <t>Trading - Quant &amp; Engineering Intern (Client-Facing)</t>
         </is>
       </c>
-      <c r="F63" s="29" t="inlineStr">
+      <c r="F63" s="32" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="G63" s="29" t="inlineStr">
+      <c r="G63" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H63" s="29" t="inlineStr">
+      <c r="H63" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 12:44 UTC</t>
         </is>
       </c>
-      <c r="I63" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J63" s="31" t="inlineStr">
+      <c r="I63" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J63" s="34" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/trading-quant-engineering-intern-client-facing-at-calypso-commodities-4403819462?refId=wb%2BADKYeCTj8bBBZgf97xw%3D%3D&amp;trackingId=o0ZBUwzyVOiml0tJPOsNww%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K63" s="29" t="inlineStr">
+      <c r="K63" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-calypso-commodities-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L63" s="29" t="inlineStr">
+      <c r="L63" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-calypso-commodities-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M63" s="29" t="inlineStr"/>
+      <c r="M63" s="32" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="29" t="inlineStr">
+      <c r="A64" s="32" t="inlineStr">
         <is>
           <t>linkedin_4355269413</t>
         </is>
       </c>
-      <c r="B64" s="29" t="inlineStr">
+      <c r="B64" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C64" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D64" s="29" t="inlineStr">
+      <c r="C64" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D64" s="32" t="inlineStr">
         <is>
           <t>Temasek</t>
         </is>
       </c>
-      <c r="E64" s="29" t="inlineStr">
+      <c r="E64" s="32" t="inlineStr">
         <is>
           <t>Data Analytics/Science Intern, People Technology (Jun/Jul - Dec 2026)</t>
         </is>
       </c>
-      <c r="F64" s="29" t="inlineStr">
+      <c r="F64" s="32" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G64" s="29" t="inlineStr">
+      <c r="G64" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H64" s="29" t="inlineStr">
+      <c r="H64" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 10:35 UTC</t>
         </is>
       </c>
-      <c r="I64" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J64" s="31" t="inlineStr">
+      <c r="I64" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J64" s="34" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/data-analytics-science-intern-people-technology-jun-jul-dec-2026-at-temasek-4355269413?refId=emjtNEhTXLtOX%2BguWexSsg%3D%3D&amp;trackingId=DPHM%2FIJzKL0emfNJ1LMMoA%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K64" s="29" t="inlineStr">
+      <c r="K64" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-temasek-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L64" s="29" t="inlineStr">
+      <c r="L64" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-temasek-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M64" s="29" t="inlineStr"/>
+      <c r="M64" s="32" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="29" t="inlineStr">
+      <c r="A65" s="32" t="inlineStr">
         <is>
           <t>linkedin_4403065097</t>
         </is>
       </c>
-      <c r="B65" s="29" t="inlineStr">
+      <c r="B65" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C65" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D65" s="29" t="inlineStr">
+      <c r="C65" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D65" s="32" t="inlineStr">
         <is>
           <t>BLACK TREE GAMING LIMITED</t>
         </is>
       </c>
-      <c r="E65" s="29" t="inlineStr">
+      <c r="E65" s="32" t="inlineStr">
         <is>
           <t>Data Scientist (ML)</t>
         </is>
       </c>
-      <c r="F65" s="29" t="inlineStr">
+      <c r="F65" s="32" t="inlineStr">
         <is>
           <t>Greater London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G65" s="29" t="inlineStr">
+      <c r="G65" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H65" s="29" t="inlineStr">
+      <c r="H65" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 14:22 UTC</t>
         </is>
       </c>
-      <c r="I65" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J65" s="31" t="inlineStr">
+      <c r="I65" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J65" s="34" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/data-scientist-ml-at-black-tree-gaming-limited-4403065097?refId=X9Gb9UkVv%2BJtfDRc0dJPwA%3D%3D&amp;trackingId=Mfl%2BC%2FBN9DJehDmug19dGA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K65" s="29" t="inlineStr">
+      <c r="K65" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-black-tree-gaming-limited-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L65" s="29" t="inlineStr">
+      <c r="L65" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-black-tree-gaming-limited-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M65" s="29" t="inlineStr"/>
+      <c r="M65" s="32" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="29" t="inlineStr">
+      <c r="A66" s="32" t="inlineStr">
         <is>
           <t>linkedin_4291533663</t>
         </is>
       </c>
-      <c r="B66" s="29" t="inlineStr">
+      <c r="B66" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C66" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D66" s="29" t="inlineStr">
+      <c r="C66" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D66" s="32" t="inlineStr">
         <is>
           <t>McKinsey &amp; Company</t>
         </is>
       </c>
-      <c r="E66" s="29" t="inlineStr">
+      <c r="E66" s="32" t="inlineStr">
         <is>
           <t>Praktikum als Fellow Intern - Tech &amp; AI (m/w/d)</t>
         </is>
       </c>
-      <c r="F66" s="29" t="inlineStr">
+      <c r="F66" s="32" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G66" s="29" t="inlineStr">
+      <c r="G66" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H66" s="29" t="inlineStr">
+      <c r="H66" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 09:49 UTC</t>
         </is>
       </c>
-      <c r="I66" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J66" s="31" t="inlineStr">
+      <c r="I66" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J66" s="34" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/praktikum-als-fellow-intern-tech-ai-m-w-d-at-mckinsey-company-4291533663?refId=UmiOr88gcWDNbqipJy2ZTg%3D%3D&amp;trackingId=UvtRxMXKlReoOEeGgMaEfA%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K66" s="29" t="inlineStr">
+      <c r="K66" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-mckinsey-company-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L66" s="29" t="inlineStr">
+      <c r="L66" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-mckinsey-company-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M66" s="29" t="inlineStr"/>
+      <c r="M66" s="32" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="29" t="inlineStr">
+      <c r="A67" s="32" t="inlineStr">
         <is>
           <t>linkedin_4336838608</t>
         </is>
       </c>
-      <c r="B67" s="29" t="inlineStr">
+      <c r="B67" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C67" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D67" s="29" t="inlineStr">
+      <c r="C67" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D67" s="32" t="inlineStr">
         <is>
           <t>Sendbird</t>
         </is>
       </c>
-      <c r="E67" s="29" t="inlineStr">
+      <c r="E67" s="32" t="inlineStr">
         <is>
           <t>AI Agent Engineer, Intern</t>
         </is>
       </c>
-      <c r="F67" s="29" t="inlineStr">
+      <c r="F67" s="32" t="inlineStr">
         <is>
           <t>Seoul, Seoul, South Korea</t>
         </is>
       </c>
-      <c r="G67" s="29" t="inlineStr">
+      <c r="G67" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H67" s="29" t="inlineStr">
+      <c r="H67" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 13:46 UTC</t>
         </is>
       </c>
-      <c r="I67" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J67" s="31" t="inlineStr">
+      <c r="I67" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J67" s="34" t="inlineStr">
         <is>
           <t>https://kr.linkedin.com/jobs/view/ai-agent-engineer-intern-at-sendbird-4336838608?refId=%2F1qLChSVn3giUiiNusHaIQ%3D%3D&amp;trackingId=l6mUUvSfC97HjoyrA8uuqg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K67" s="29" t="inlineStr">
+      <c r="K67" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sendbird-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L67" s="29" t="inlineStr">
+      <c r="L67" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sendbird-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M67" s="29" t="inlineStr"/>
+      <c r="M67" s="32" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+      <c r="A68" s="32" t="inlineStr">
         <is>
           <t>linkedin_4372783510</t>
         </is>
       </c>
-      <c r="B68" s="29" t="inlineStr">
+      <c r="B68" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C68" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D68" s="29" t="inlineStr">
+      <c r="C68" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D68" s="32" t="inlineStr">
         <is>
           <t>42dot</t>
         </is>
       </c>
-      <c r="E68" s="29" t="inlineStr">
+      <c r="E68" s="32" t="inlineStr">
         <is>
           <t>[MS/PhD Intern] AI Engineer (정규직 전환형)</t>
         </is>
       </c>
-      <c r="F68" s="29" t="inlineStr">
+      <c r="F68" s="32" t="inlineStr">
         <is>
           <t>Seongnam, Gyeonggi, South Korea</t>
         </is>
       </c>
-      <c r="G68" s="29" t="inlineStr">
+      <c r="G68" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H68" s="29" t="inlineStr">
+      <c r="H68" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 15:08 UTC</t>
         </is>
       </c>
-      <c r="I68" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J68" s="31" t="inlineStr">
+      <c r="I68" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J68" s="34" t="inlineStr">
         <is>
           <t>https://kr.linkedin.com/jobs/view/ms-phd-intern-ai-engineer-%EC%A0%95%EA%B7%9C%EC%A7%81-%EC%A0%84%ED%99%98%ED%98%95-at-42dot-4372783510?refId=%2F1qLChSVn3giUiiNusHaIQ%3D%3D&amp;trackingId=TVYs5RWI1wgPuuVRiBioUA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K68" s="29" t="inlineStr">
+      <c r="K68" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-42dot-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L68" s="29" t="inlineStr">
+      <c r="L68" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-42dot-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M68" s="29" t="inlineStr"/>
+      <c r="M68" s="32" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
+      <c r="A69" s="32" t="inlineStr">
         <is>
           <t>linkedin_4402753102</t>
         </is>
       </c>
-      <c r="B69" s="29" t="inlineStr">
+      <c r="B69" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C69" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D69" s="29" t="inlineStr">
+      <c r="C69" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D69" s="32" t="inlineStr">
         <is>
           <t>Five9</t>
         </is>
       </c>
-      <c r="E69" s="29" t="inlineStr">
+      <c r="E69" s="32" t="inlineStr">
         <is>
           <t>Software Developer AI Insights Intern</t>
         </is>
       </c>
-      <c r="F69" s="29" t="inlineStr">
+      <c r="F69" s="32" t="inlineStr">
         <is>
           <t>San Ramon, CA</t>
         </is>
       </c>
-      <c r="G69" s="29" t="inlineStr">
+      <c r="G69" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H69" s="29" t="inlineStr">
+      <c r="H69" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 20:56 UTC</t>
         </is>
       </c>
-      <c r="I69" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J69" s="31" t="inlineStr">
+      <c r="I69" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J69" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/software-developer-ai-insights-intern-at-five9-4402753102?refId=%2FiKmLsIvYp2TclUyf8MJwg%3D%3D&amp;trackingId=X2UMBr3jE86J9JmPv42B2w%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K69" s="29" t="inlineStr">
+      <c r="K69" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-five9-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L69" s="29" t="inlineStr">
+      <c r="L69" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-five9-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M69" s="29" t="inlineStr"/>
+      <c r="M69" s="32" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="29" t="inlineStr">
+      <c r="A70" s="32" t="inlineStr">
         <is>
           <t>linkedin_4403519373</t>
         </is>
       </c>
-      <c r="B70" s="29" t="inlineStr">
+      <c r="B70" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C70" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D70" s="29" t="inlineStr">
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E70" s="29" t="inlineStr">
+      <c r="E70" s="32" t="inlineStr">
         <is>
           <t>PhD Research Intern, Physical AI in Perception</t>
         </is>
       </c>
-      <c r="F70" s="29" t="inlineStr">
+      <c r="F70" s="32" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G70" s="29" t="inlineStr">
+      <c r="G70" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H70" s="29" t="inlineStr">
+      <c r="H70" s="32" t="inlineStr">
         <is>
           <t>2026-04-17 20:07 UTC</t>
         </is>
       </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J70" s="31" t="inlineStr">
+      <c r="I70" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J70" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-physical-ai-in-perception-at-zoox-4403519373?refId=LChV34e%2Bd7cvBpZ%2FbJAZjw%3D%3D&amp;trackingId=vlvuJ54NQfvZvNY3pNGqNw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K70" s="29" t="inlineStr">
+      <c r="K70" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L70" s="29" t="inlineStr">
+      <c r="L70" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M70" s="29" t="inlineStr"/>
+      <c r="M70" s="32" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="29" t="inlineStr">
+      <c r="A71" s="32" t="inlineStr">
         <is>
           <t>linkedin_4403095692</t>
         </is>
       </c>
-      <c r="B71" s="29" t="inlineStr">
+      <c r="B71" s="32" t="inlineStr">
         <is>
           <t>2026-04-19 08:24</t>
         </is>
       </c>
-      <c r="C71" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D71" s="29" t="inlineStr">
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
         <is>
           <t>Starrycraze Technology</t>
         </is>
       </c>
-      <c r="E71" s="29" t="inlineStr">
+      <c r="E71" s="32" t="inlineStr">
         <is>
           <t>Data Scientist Intern</t>
         </is>
       </c>
-      <c r="F71" s="29" t="inlineStr">
+      <c r="F71" s="32" t="inlineStr">
         <is>
           <t>Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G71" s="29" t="inlineStr">
+      <c r="G71" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H71" s="29" t="inlineStr">
+      <c r="H71" s="32" t="inlineStr">
         <is>
           <t>2026-04-19 04:58 UTC</t>
         </is>
       </c>
-      <c r="I71" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J71" s="31" t="inlineStr">
+      <c r="I71" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J71" s="34" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/data-scientist-intern-at-starrycraze-technology-4403095692?refId=TVQyGaR78N78VqNo32HHeA%3D%3D&amp;trackingId=iTU%2BdVDc304eRUiD2UiVkA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K71" s="29" t="inlineStr">
+      <c r="K71" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-starrycraze-technology-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L71" s="29" t="inlineStr">
+      <c r="L71" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-starrycraze-technology-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M71" s="29" t="inlineStr"/>
+      <c r="M71" s="32" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="29" t="inlineStr">
+      <c r="A72" s="32" t="inlineStr">
         <is>
           <t>linkedin_4403848986</t>
         </is>
       </c>
-      <c r="B72" s="29" t="inlineStr">
+      <c r="B72" s="32" t="inlineStr">
         <is>
           <t>2026-04-19 08:24</t>
         </is>
       </c>
-      <c r="C72" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D72" s="29" t="inlineStr">
+      <c r="C72" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E72" s="29" t="inlineStr">
+      <c r="E72" s="32" t="inlineStr">
         <is>
           <t>PhD Research Intern, Offline Driving Intelligence</t>
         </is>
       </c>
-      <c r="F72" s="29" t="inlineStr">
+      <c r="F72" s="32" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G72" s="29" t="inlineStr">
+      <c r="G72" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H72" s="29" t="inlineStr">
+      <c r="H72" s="32" t="inlineStr">
         <is>
           <t>2026-04-19 02:06 UTC</t>
         </is>
       </c>
-      <c r="I72" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J72" s="31" t="inlineStr">
+      <c r="I72" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J72" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-offline-driving-intelligence-at-zoox-4403848986?refId=5ydRxcXuf5aHqLJVjey87Q%3D%3D&amp;trackingId=FWtGym5%2BhCmPjiMPBVYS7w%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K72" s="29" t="inlineStr">
+      <c r="K72" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L72" s="29" t="inlineStr">
+      <c r="L72" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M72" s="29" t="inlineStr"/>
+      <c r="M72" s="32" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="29" t="inlineStr">
+      <c r="A73" s="32" t="inlineStr">
         <is>
           <t>linkedin_4371758156</t>
         </is>
       </c>
-      <c r="B73" s="29" t="inlineStr">
+      <c r="B73" s="32" t="inlineStr">
         <is>
           <t>2026-04-19 08:24</t>
         </is>
       </c>
-      <c r="C73" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D73" s="29" t="inlineStr">
+      <c r="C73" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
         <is>
           <t>Lowe's India</t>
         </is>
       </c>
-      <c r="E73" s="29" t="inlineStr">
+      <c r="E73" s="32" t="inlineStr">
         <is>
           <t>DIH Intern, Data Engineering</t>
         </is>
       </c>
-      <c r="F73" s="29" t="inlineStr">
+      <c r="F73" s="32" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G73" s="29" t="inlineStr">
+      <c r="G73" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H73" s="29" t="inlineStr">
+      <c r="H73" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 10:48 UTC</t>
         </is>
       </c>
-      <c r="I73" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J73" s="31" t="inlineStr">
+      <c r="I73" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J73" s="34" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/dih-intern-data-engineering-at-lowe-s-india-4371758156?refId=1mgTdTTgR1UncTTJ8Ts5OA%3D%3D&amp;trackingId=7HYWBNU0zclnyp9qIoW2Jw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K73" s="29" t="inlineStr">
+      <c r="K73" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-lowes-india-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L73" s="29" t="inlineStr">
+      <c r="L73" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-lowes-india-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M73" s="29" t="inlineStr"/>
+      <c r="M73" s="32" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="29" t="inlineStr">
+      <c r="A74" s="32" t="inlineStr">
         <is>
           <t>linkedin_4327191639</t>
         </is>
       </c>
-      <c r="B74" s="29" t="inlineStr">
+      <c r="B74" s="32" t="inlineStr">
         <is>
           <t>2026-04-19 08:24</t>
         </is>
       </c>
-      <c r="C74" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D74" s="29" t="inlineStr">
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
         <is>
           <t>Whatnot</t>
         </is>
       </c>
-      <c r="E74" s="29" t="inlineStr">
+      <c r="E74" s="32" t="inlineStr">
         <is>
           <t>Data Scientist, Product Analytics</t>
         </is>
       </c>
-      <c r="F74" s="29" t="inlineStr">
+      <c r="F74" s="32" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G74" s="29" t="inlineStr">
+      <c r="G74" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H74" s="29" t="inlineStr">
+      <c r="H74" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 13:22 UTC</t>
         </is>
       </c>
-      <c r="I74" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J74" s="31" t="inlineStr">
+      <c r="I74" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J74" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-scientist-product-analytics-at-whatnot-4327191639?refId=mfQJnJ6mRr3La1qB9YnNGA%3D%3D&amp;trackingId=k4mLJmsHD9wYHSZlc4RA%2Fw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K74" s="29" t="inlineStr">
+      <c r="K74" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-whatnot-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L74" s="29" t="inlineStr">
+      <c r="L74" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-whatnot-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M74" s="29" t="inlineStr"/>
+      <c r="M74" s="32" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="29" t="inlineStr">
+      <c r="A75" s="32" t="inlineStr">
         <is>
           <t>linkedin_4391150969</t>
         </is>
       </c>
-      <c r="B75" s="29" t="inlineStr">
+      <c r="B75" s="32" t="inlineStr">
         <is>
           <t>2026-04-19 19:54</t>
         </is>
       </c>
-      <c r="C75" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D75" s="29" t="inlineStr">
+      <c r="C75" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D75" s="32" t="inlineStr">
         <is>
           <t>Cartesian</t>
         </is>
       </c>
-      <c r="E75" s="29" t="inlineStr">
+      <c r="E75" s="32" t="inlineStr">
         <is>
           <t>Software Engineering Intern (Summer/Fall 2026)</t>
         </is>
       </c>
-      <c r="F75" s="29" t="inlineStr">
+      <c r="F75" s="32" t="inlineStr">
         <is>
           <t>Cambridge, MA</t>
         </is>
       </c>
-      <c r="G75" s="29" t="inlineStr">
+      <c r="G75" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H75" s="29" t="inlineStr">
+      <c r="H75" s="32" t="inlineStr">
         <is>
           <t>2026-04-18 23:08 UTC</t>
         </is>
       </c>
-      <c r="I75" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J75" s="31" t="inlineStr">
+      <c r="I75" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J75" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/software-engineering-intern-summer-fall-2026-at-cartesian-4391150969?refId=rXBEPoDKoHwUW%2BMU3mmCWA%3D%3D&amp;trackingId=03L6jyuSNG6Edf0%2FeXbj4w%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K75" s="29" t="inlineStr">
+      <c r="K75" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-cartesian-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L75" s="29" t="inlineStr">
+      <c r="L75" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-cartesian-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M75" s="29" t="inlineStr"/>
+      <c r="M75" s="32" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+      <c r="A76" s="32" t="inlineStr">
         <is>
           <t>linkedin_4401268516</t>
         </is>
       </c>
-      <c r="B76" s="29" t="inlineStr">
+      <c r="B76" s="32" t="inlineStr">
         <is>
           <t>2026-04-19 19:54</t>
         </is>
       </c>
-      <c r="C76" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D76" s="29" t="inlineStr">
+      <c r="C76" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D76" s="32" t="inlineStr">
         <is>
           <t>Joveo Ai</t>
         </is>
       </c>
-      <c r="E76" s="29" t="inlineStr">
+      <c r="E76" s="32" t="inlineStr">
         <is>
           <t>Generative AI Intern</t>
         </is>
       </c>
-      <c r="F76" s="29" t="inlineStr">
+      <c r="F76" s="32" t="inlineStr">
         <is>
           <t>Bangalore Urban, Karnataka, India</t>
         </is>
       </c>
-      <c r="G76" s="29" t="inlineStr">
+      <c r="G76" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H76" s="29" t="inlineStr">
+      <c r="H76" s="32" t="inlineStr">
         <is>
           <t>2026-04-19 16:33 UTC</t>
         </is>
       </c>
-      <c r="I76" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J76" s="31" t="inlineStr">
+      <c r="I76" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J76" s="34" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/generative-ai-intern-at-joveo-ai-4401268516?refId=AMRRU4%2FYzAhlhe1ad%2FYa%2Fw%3D%3D&amp;trackingId=lRpwTcswbLSpxr57DNyAvA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K76" s="29" t="inlineStr">
+      <c r="K76" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-joveo-ai-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L76" s="29" t="inlineStr">
+      <c r="L76" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-joveo-ai-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M76" s="29" t="inlineStr"/>
+      <c r="M76" s="32" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="29" t="inlineStr">
+      <c r="A77" s="32" t="inlineStr">
         <is>
           <t>linkedin_4381330362</t>
         </is>
       </c>
-      <c r="B77" s="29" t="inlineStr">
+      <c r="B77" s="32" t="inlineStr">
         <is>
           <t>2026-04-19 19:54</t>
         </is>
       </c>
-      <c r="C77" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D77" s="29" t="inlineStr">
+      <c r="C77" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D77" s="32" t="inlineStr">
         <is>
           <t>Shopee</t>
         </is>
       </c>
-      <c r="E77" s="29" t="inlineStr">
+      <c r="E77" s="32" t="inlineStr">
         <is>
           <t>Data Analyst Intern - Product Analysis, Regional Operations (Summer 2026)</t>
         </is>
       </c>
-      <c r="F77" s="29" t="inlineStr">
+      <c r="F77" s="32" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G77" s="29" t="inlineStr">
+      <c r="G77" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H77" s="29" t="inlineStr">
+      <c r="H77" s="32" t="inlineStr">
         <is>
           <t>2026-04-19 13:47 UTC</t>
         </is>
       </c>
-      <c r="I77" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J77" s="31" t="inlineStr">
+      <c r="I77" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J77" s="34" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/data-analyst-intern-product-analysis-regional-operations-summer-2026-at-shopee-4381330362?refId=Mf9npsmRtScOZbkuOI7S2Q%3D%3D&amp;trackingId=qCnW3Di6Gcyx48NhCTpBLw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K77" s="29" t="inlineStr">
+      <c r="K77" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-shopee-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L77" s="29" t="inlineStr">
+      <c r="L77" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-shopee-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M77" s="29" t="inlineStr"/>
+      <c r="M77" s="32" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="29" t="inlineStr">
+      <c r="A78" s="32" t="inlineStr">
         <is>
           <t>linkedin_4355297667</t>
         </is>
       </c>
-      <c r="B78" s="29" t="inlineStr">
+      <c r="B78" s="32" t="inlineStr">
         <is>
           <t>2026-04-19 19:54</t>
         </is>
       </c>
-      <c r="C78" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D78" s="29" t="inlineStr">
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
         <is>
           <t>Temasek</t>
         </is>
       </c>
-      <c r="E78" s="29" t="inlineStr">
+      <c r="E78" s="32" t="inlineStr">
         <is>
           <t>Policy &amp; Research Intern, Workforce 4.0 (Jun/Jul - Dec 2026)</t>
         </is>
       </c>
-      <c r="F78" s="29" t="inlineStr">
+      <c r="F78" s="32" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G78" s="29" t="inlineStr">
+      <c r="G78" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H78" s="29" t="inlineStr">
+      <c r="H78" s="32" t="inlineStr">
         <is>
           <t>2026-04-19 10:08 UTC</t>
         </is>
       </c>
-      <c r="I78" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J78" s="31" t="inlineStr">
+      <c r="I78" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J78" s="34" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/policy-research-intern-workforce-4-0-jun-jul-dec-2026-at-temasek-4355297667?refId=SZF%2BVbNMCE0h7Rloqm3lXQ%3D%3D&amp;trackingId=vK2euiis8CytJt264fhurw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K78" s="29" t="inlineStr">
+      <c r="K78" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-temasek-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L78" s="29" t="inlineStr">
+      <c r="L78" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-temasek-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M78" s="29" t="inlineStr"/>
+      <c r="M78" s="32" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="29" t="inlineStr">
+      <c r="A79" s="32" t="inlineStr">
         <is>
           <t>linkedin_4336865392</t>
         </is>
       </c>
-      <c r="B79" s="29" t="inlineStr">
+      <c r="B79" s="32" t="inlineStr">
         <is>
           <t>2026-04-19 19:54</t>
         </is>
       </c>
-      <c r="C79" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D79" s="29" t="inlineStr">
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E79" s="29" t="inlineStr">
+      <c r="E79" s="32" t="inlineStr">
         <is>
           <t>PhD Research Intern, Visual Object Understanding</t>
         </is>
       </c>
-      <c r="F79" s="29" t="inlineStr">
+      <c r="F79" s="32" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G79" s="29" t="inlineStr">
+      <c r="G79" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H79" s="29" t="inlineStr">
+      <c r="H79" s="32" t="inlineStr">
         <is>
           <t>2026-04-19 10:27 UTC</t>
         </is>
       </c>
-      <c r="I79" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J79" s="31" t="inlineStr">
+      <c r="I79" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J79" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-visual-object-understanding-at-zoox-4336865392?refId=gztZfDsooz7GE2iA6mPxjQ%3D%3D&amp;trackingId=%2F1kV0X%2F8hKCPhv0kD05v5Q%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K79" s="29" t="inlineStr">
+      <c r="K79" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L79" s="29" t="inlineStr">
+      <c r="L79" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M79" s="29" t="inlineStr"/>
+      <c r="M79" s="32" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="29" t="inlineStr">
+      <c r="A80" s="32" t="inlineStr">
         <is>
           <t>linkedin_4404025051</t>
         </is>
       </c>
-      <c r="B80" s="29" t="inlineStr">
+      <c r="B80" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 09:16</t>
         </is>
       </c>
-      <c r="C80" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D80" s="29" t="inlineStr">
+      <c r="C80" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
         <is>
           <t>Dassault Systèmes</t>
         </is>
       </c>
-      <c r="E80" s="29" t="inlineStr">
+      <c r="E80" s="32" t="inlineStr">
         <is>
           <t>INTERNSHIP: Data Science (6mo June 2026)</t>
         </is>
       </c>
-      <c r="F80" s="29" t="inlineStr">
+      <c r="F80" s="32" t="inlineStr">
         <is>
           <t>Waltham, MA</t>
         </is>
       </c>
-      <c r="G80" s="29" t="inlineStr">
+      <c r="G80" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H80" s="29" t="inlineStr">
+      <c r="H80" s="32" t="inlineStr">
         <is>
           <t>2026-04-19 23:38 UTC</t>
         </is>
       </c>
-      <c r="I80" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J80" s="31" t="inlineStr">
+      <c r="I80" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J80" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/internship-data-science-6mo-june-2026-at-dassault-syst%C3%A8mes-4404025051?refId=S4wy0FwbzbiuPwYYk2m0dw%3D%3D&amp;trackingId=RGARwF5XkYgBTfpY7DrrZg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K80" s="29" t="inlineStr">
+      <c r="K80" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dassault-systèmes-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L80" s="29" t="inlineStr">
+      <c r="L80" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dassault-systèmes-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M80" s="29" t="inlineStr"/>
+      <c r="M80" s="32" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="29" t="inlineStr">
+      <c r="A81" s="32" t="inlineStr">
         <is>
           <t>linkedin_4403368519</t>
         </is>
       </c>
-      <c r="B81" s="29" t="inlineStr">
+      <c r="B81" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 09:16</t>
         </is>
       </c>
-      <c r="C81" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D81" s="29" t="inlineStr">
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="E81" s="29" t="inlineStr">
+      <c r="E81" s="32" t="inlineStr">
         <is>
           <t>Risk Control Algorithm Engineer Intern</t>
         </is>
       </c>
-      <c r="F81" s="29" t="inlineStr">
+      <c r="F81" s="32" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G81" s="29" t="inlineStr">
+      <c r="G81" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H81" s="29" t="inlineStr">
+      <c r="H81" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 08:20 UTC</t>
         </is>
       </c>
-      <c r="I81" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J81" s="31" t="inlineStr">
+      <c r="I81" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J81" s="34" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/risk-control-algorithm-engineer-intern-at-bybit-4403368519?refId=9jFaGeHrGBqPLrXTIfcNwA%3D%3D&amp;trackingId=glTg%2F1p9B2dY4YX59MH9DA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K81" s="29" t="inlineStr">
+      <c r="K81" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bybit-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L81" s="29" t="inlineStr">
+      <c r="L81" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bybit-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M81" s="29" t="inlineStr"/>
+      <c r="M81" s="32" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="29" t="inlineStr">
+      <c r="A82" s="32" t="inlineStr">
         <is>
           <t>linkedin_4403320381</t>
         </is>
       </c>
-      <c r="B82" s="29" t="inlineStr">
+      <c r="B82" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 09:16</t>
         </is>
       </c>
-      <c r="C82" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D82" s="29" t="inlineStr">
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
         <is>
           <t>Digitomics AI</t>
         </is>
       </c>
-      <c r="E82" s="29" t="inlineStr">
+      <c r="E82" s="32" t="inlineStr">
         <is>
           <t>AI Engineering Intern</t>
         </is>
       </c>
-      <c r="F82" s="29" t="inlineStr">
+      <c r="F82" s="32" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G82" s="29" t="inlineStr">
+      <c r="G82" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H82" s="29" t="inlineStr">
+      <c r="H82" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 08:43 UTC</t>
         </is>
       </c>
-      <c r="I82" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J82" s="31" t="inlineStr">
+      <c r="I82" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J82" s="34" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/ai-engineering-intern-at-digitomics-ai-4403320381?refId=0fRwalKs7ueOf%2FH7m6U26Q%3D%3D&amp;trackingId=zbHZrmgemJdB%2BlQYFw7geg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K82" s="29" t="inlineStr">
+      <c r="K82" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-digitomics-ai-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L82" s="29" t="inlineStr">
+      <c r="L82" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-digitomics-ai-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M82" s="29" t="inlineStr"/>
+      <c r="M82" s="32" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="29" t="inlineStr">
+      <c r="A83" s="32" t="inlineStr">
         <is>
           <t>linkedin_4403358236</t>
         </is>
       </c>
-      <c r="B83" s="29" t="inlineStr">
+      <c r="B83" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 09:16</t>
         </is>
       </c>
-      <c r="C83" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D83" s="29" t="inlineStr">
+      <c r="C83" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D83" s="32" t="inlineStr">
         <is>
           <t>InMobi</t>
         </is>
       </c>
-      <c r="E83" s="29" t="inlineStr">
+      <c r="E83" s="32" t="inlineStr">
         <is>
           <t>Intern - Industrial Trainee</t>
         </is>
       </c>
-      <c r="F83" s="29" t="inlineStr">
+      <c r="F83" s="32" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G83" s="29" t="inlineStr">
+      <c r="G83" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H83" s="29" t="inlineStr">
+      <c r="H83" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 06:44 UTC</t>
         </is>
       </c>
-      <c r="I83" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J83" s="31" t="inlineStr">
+      <c r="I83" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J83" s="34" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/intern-industrial-trainee-at-inmobi-4403358236?refId=Hz8z0MLJ0gvG3WjNfG9q9Q%3D%3D&amp;trackingId=uO3LmXVsff1dJma3y3w5Gg%3D%3D&amp;position=8&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K83" s="29" t="inlineStr">
+      <c r="K83" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-inmobi-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L83" s="29" t="inlineStr">
+      <c r="L83" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-inmobi-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M83" s="29" t="inlineStr"/>
+      <c r="M83" s="32" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="29" t="inlineStr">
+      <c r="A84" s="32" t="inlineStr">
         <is>
           <t>linkedin_4403359204</t>
         </is>
       </c>
-      <c r="B84" s="29" t="inlineStr">
+      <c r="B84" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 09:16</t>
         </is>
       </c>
-      <c r="C84" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D84" s="29" t="inlineStr">
+      <c r="C84" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D84" s="32" t="inlineStr">
         <is>
           <t>TakedaPharmaceutical Nordics AB</t>
         </is>
       </c>
-      <c r="E84" s="29" t="inlineStr">
+      <c r="E84" s="32" t="inlineStr">
         <is>
           <t>Senior Data Scientist</t>
         </is>
       </c>
-      <c r="F84" s="29" t="inlineStr">
+      <c r="F84" s="32" t="inlineStr">
         <is>
           <t>Boston, MA</t>
         </is>
       </c>
-      <c r="G84" s="29" t="inlineStr">
+      <c r="G84" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H84" s="29" t="inlineStr">
+      <c r="H84" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 06:45 UTC</t>
         </is>
       </c>
-      <c r="I84" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J84" s="31" t="inlineStr">
+      <c r="I84" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J84" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/senior-data-scientist-at-takedapharmaceutical-nordics-ab-4403359204?refId=S4wy0FwbzbiuPwYYk2m0dw%3D%3D&amp;trackingId=zfL5isOE6jcFxwuJQPpkyA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K84" s="29" t="inlineStr">
+      <c r="K84" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-takedapharmaceutical-nordics-ab-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L84" s="29" t="inlineStr">
+      <c r="L84" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-takedapharmaceutical-nordics-ab-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M84" s="29" t="inlineStr"/>
+      <c r="M84" s="32" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="29" t="inlineStr">
+      <c r="A85" s="32" t="inlineStr">
         <is>
           <t>linkedin_4403353339</t>
         </is>
       </c>
-      <c r="B85" s="29" t="inlineStr">
+      <c r="B85" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 09:16</t>
         </is>
       </c>
-      <c r="C85" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D85" s="29" t="inlineStr">
+      <c r="C85" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D85" s="32" t="inlineStr">
         <is>
           <t>Kuku</t>
         </is>
       </c>
-      <c r="E85" s="29" t="inlineStr">
+      <c r="E85" s="32" t="inlineStr">
         <is>
           <t>AI Intern</t>
         </is>
       </c>
-      <c r="F85" s="29" t="inlineStr">
+      <c r="F85" s="32" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G85" s="29" t="inlineStr">
+      <c r="G85" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H85" s="29" t="inlineStr">
+      <c r="H85" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 07:10 UTC</t>
         </is>
       </c>
-      <c r="I85" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J85" s="31" t="inlineStr">
+      <c r="I85" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J85" s="34" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/ai-intern-at-kuku-4403353339?refId=Hz8z0MLJ0gvG3WjNfG9q9Q%3D%3D&amp;trackingId=HENEvtuPxzCTSc47zwTLxw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K85" s="29" t="inlineStr">
+      <c r="K85" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-kuku-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L85" s="29" t="inlineStr">
+      <c r="L85" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-kuku-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M85" s="29" t="inlineStr"/>
+      <c r="M85" s="32" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="29" t="inlineStr">
+      <c r="A86" s="32" t="inlineStr">
         <is>
           <t>linkedin_4403306789</t>
         </is>
       </c>
-      <c r="B86" s="29" t="inlineStr">
+      <c r="B86" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 09:16</t>
         </is>
       </c>
-      <c r="C86" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D86" s="29" t="inlineStr">
+      <c r="C86" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D86" s="32" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E86" s="29" t="inlineStr">
+      <c r="E86" s="32" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F86" s="29" t="inlineStr">
+      <c r="F86" s="32" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G86" s="29" t="inlineStr">
+      <c r="G86" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H86" s="29" t="inlineStr">
+      <c r="H86" s="32" t="inlineStr">
         <is>
           <t>2026-04-19 22:21 UTC</t>
         </is>
       </c>
-      <c r="I86" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J86" s="31" t="inlineStr">
+      <c r="I86" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J86" s="34" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/research-intern-at-skycliff-it-4403306789?refId=KN18fO0braE9qgElBP9zEg%3D%3D&amp;trackingId=%2Bm9LCS%2BxHyH7O3sA%2BvKB2A%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K86" s="29" t="inlineStr">
+      <c r="K86" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L86" s="29" t="inlineStr">
+      <c r="L86" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M86" s="29" t="inlineStr"/>
+      <c r="M86" s="32" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="29" t="inlineStr">
+      <c r="A87" s="32" t="inlineStr">
         <is>
           <t>linkedin_4336984951</t>
         </is>
       </c>
-      <c r="B87" s="29" t="inlineStr">
+      <c r="B87" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 09:16</t>
         </is>
       </c>
-      <c r="C87" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D87" s="29" t="inlineStr">
+      <c r="C87" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D87" s="32" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E87" s="29" t="inlineStr">
+      <c r="E87" s="32" t="inlineStr">
         <is>
           <t>Machine Learning Engineer Intern, Simulation</t>
         </is>
       </c>
-      <c r="F87" s="29" t="inlineStr">
+      <c r="F87" s="32" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G87" s="29" t="inlineStr">
+      <c r="G87" s="32" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H87" s="29" t="inlineStr">
+      <c r="H87" s="32" t="inlineStr">
         <is>
           <t>2026-04-19 09:41 UTC</t>
         </is>
       </c>
-      <c r="I87" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J87" s="31" t="inlineStr">
+      <c r="I87" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J87" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/machine-learning-engineer-intern-simulation-at-zoox-4336984951?refId=kzdKy3lQPz5ITmALB3aiLA%3D%3D&amp;trackingId=TBJ5wFzjDmfdPFnmhbpCvA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K87" s="29" t="inlineStr">
+      <c r="K87" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L87" s="29" t="inlineStr">
+      <c r="L87" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M87" s="29" t="inlineStr"/>
+      <c r="M87" s="32" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="29" t="inlineStr">
+      <c r="A88" s="32" t="inlineStr">
         <is>
           <t>linkedin_4323554488</t>
         </is>
       </c>
-      <c r="B88" s="29" t="inlineStr">
+      <c r="B88" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 20:02</t>
         </is>
       </c>
-      <c r="C88" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D88" s="29" t="inlineStr">
+      <c r="C88" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D88" s="32" t="inlineStr">
         <is>
           <t>Shopee</t>
         </is>
       </c>
-      <c r="E88" s="29" t="inlineStr">
+      <c r="E88" s="32" t="inlineStr">
         <is>
           <t>Data Analyst Intern, Buyer &amp; Marketing - Business Intelligence (Jan- Apr 2026)</t>
         </is>
       </c>
-      <c r="F88" s="29" t="inlineStr">
+      <c r="F88" s="32" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G88" s="29" t="inlineStr">
+      <c r="G88" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H88" s="29" t="inlineStr">
+      <c r="H88" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 13:19 UTC</t>
         </is>
       </c>
-      <c r="I88" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J88" s="31" t="inlineStr">
+      <c r="I88" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J88" s="34" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/data-analyst-intern-buyer-marketing-business-intelligence-jan-apr-2026-at-shopee-4323554488?refId=7F9xR8A2ceTxeNHc8C48Lw%3D%3D&amp;trackingId=yyqxH6uqfdMekl83OKdeng%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K88" s="29" t="inlineStr">
+      <c r="K88" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-shopee-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L88" s="29" t="inlineStr">
+      <c r="L88" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-shopee-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M88" s="29" t="inlineStr"/>
+      <c r="M88" s="32" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="29" t="inlineStr">
+      <c r="A89" s="32" t="inlineStr">
         <is>
           <t>linkedin_4403602536</t>
         </is>
       </c>
-      <c r="B89" s="29" t="inlineStr">
+      <c r="B89" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 20:02</t>
         </is>
       </c>
-      <c r="C89" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D89" s="29" t="inlineStr">
+      <c r="C89" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D89" s="32" t="inlineStr">
         <is>
           <t>Matter</t>
         </is>
       </c>
-      <c r="E89" s="29" t="inlineStr">
+      <c r="E89" s="32" t="inlineStr">
         <is>
           <t>ESG Data Intern</t>
         </is>
       </c>
-      <c r="F89" s="29" t="inlineStr">
+      <c r="F89" s="32" t="inlineStr">
         <is>
           <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
-      <c r="G89" s="29" t="inlineStr">
+      <c r="G89" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H89" s="29" t="inlineStr">
+      <c r="H89" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 13:42 UTC</t>
         </is>
       </c>
-      <c r="I89" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J89" s="31" t="inlineStr">
+      <c r="I89" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J89" s="34" t="inlineStr">
         <is>
           <t>https://dk.linkedin.com/jobs/view/esg-data-intern-at-matter-4403602536?refId=AE%2FVzoOpycEQ7%2F%2BJ0DeSEg%3D%3D&amp;trackingId=KDyRT7oadVzItXO7Z6Fndw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K89" s="29" t="inlineStr">
+      <c r="K89" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-matter-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L89" s="29" t="inlineStr">
+      <c r="L89" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-matter-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M89" s="29" t="inlineStr"/>
+      <c r="M89" s="32" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="29" t="inlineStr">
+      <c r="A90" s="32" t="inlineStr">
         <is>
           <t>linkedin_4403625335</t>
         </is>
       </c>
-      <c r="B90" s="29" t="inlineStr">
+      <c r="B90" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 20:02</t>
         </is>
       </c>
-      <c r="C90" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D90" s="29" t="inlineStr">
+      <c r="C90" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D90" s="32" t="inlineStr">
         <is>
           <t>Binance</t>
         </is>
       </c>
-      <c r="E90" s="29" t="inlineStr">
+      <c r="E90" s="32" t="inlineStr">
         <is>
           <t>Binance Accelerator Program - Applied Data Scientist</t>
         </is>
       </c>
-      <c r="F90" s="29" t="inlineStr">
+      <c r="F90" s="32" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G90" s="29" t="inlineStr">
+      <c r="G90" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H90" s="29" t="inlineStr">
+      <c r="H90" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 15:53 UTC</t>
         </is>
       </c>
-      <c r="I90" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J90" s="31" t="inlineStr">
+      <c r="I90" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J90" s="34" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/binance-accelerator-program-applied-data-scientist-at-binance-4403625335?refId=RjWLz09J3iQbgIc%2B%2Farrcg%3D%3D&amp;trackingId=DNLE3AfRN1YFc4qeIspU0w%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K90" s="29" t="inlineStr">
+      <c r="K90" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-binance-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L90" s="29" t="inlineStr">
+      <c r="L90" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-binance-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M90" s="29" t="inlineStr"/>
+      <c r="M90" s="32" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="29" t="inlineStr">
+      <c r="A91" s="32" t="inlineStr">
         <is>
           <t>linkedin_4401462467</t>
         </is>
       </c>
-      <c r="B91" s="29" t="inlineStr">
+      <c r="B91" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 20:02</t>
         </is>
       </c>
-      <c r="C91" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D91" s="29" t="inlineStr">
+      <c r="C91" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D91" s="32" t="inlineStr">
         <is>
           <t>Henning Larsen</t>
         </is>
       </c>
-      <c r="E91" s="29" t="inlineStr">
+      <c r="E91" s="32" t="inlineStr">
         <is>
           <t>Business Development Intern – AI and IT focus</t>
         </is>
       </c>
-      <c r="F91" s="29" t="inlineStr">
+      <c r="F91" s="32" t="inlineStr">
         <is>
           <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
-      <c r="G91" s="29" t="inlineStr">
+      <c r="G91" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H91" s="29" t="inlineStr">
+      <c r="H91" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 14:23 UTC</t>
         </is>
       </c>
-      <c r="I91" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J91" s="31" t="inlineStr">
+      <c r="I91" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J91" s="34" t="inlineStr">
         <is>
           <t>https://dk.linkedin.com/jobs/view/business-development-intern-%E2%80%93-ai-and-it-focus-at-henning-larsen-4401462467?refId=AE%2FVzoOpycEQ7%2F%2BJ0DeSEg%3D%3D&amp;trackingId=a6kSBIKrUbVcoZ6e1VKmqQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K91" s="29" t="inlineStr">
+      <c r="K91" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-henning-larsen-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L91" s="29" t="inlineStr">
+      <c r="L91" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-henning-larsen-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M91" s="29" t="inlineStr"/>
+      <c r="M91" s="32" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="29" t="inlineStr">
+      <c r="A92" s="32" t="inlineStr">
         <is>
           <t>linkedin_3694731755</t>
         </is>
       </c>
-      <c r="B92" s="29" t="inlineStr">
+      <c r="B92" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 20:02</t>
         </is>
       </c>
-      <c r="C92" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D92" s="29" t="inlineStr">
+      <c r="C92" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D92" s="32" t="inlineStr">
         <is>
           <t>Shopee</t>
         </is>
       </c>
-      <c r="E92" s="29" t="inlineStr">
+      <c r="E92" s="32" t="inlineStr">
         <is>
           <t>Data Analyst Intern - Warehouse Operations, Regional Operations (Spring 2025)</t>
         </is>
       </c>
-      <c r="F92" s="29" t="inlineStr">
+      <c r="F92" s="32" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G92" s="29" t="inlineStr">
+      <c r="G92" s="32" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H92" s="29" t="inlineStr">
+      <c r="H92" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 13:27 UTC</t>
         </is>
       </c>
-      <c r="I92" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J92" s="31" t="inlineStr">
+      <c r="I92" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J92" s="34" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/data-analyst-intern-warehouse-operations-regional-operations-spring-2025-at-shopee-3694731755?refId=7F9xR8A2ceTxeNHc8C48Lw%3D%3D&amp;trackingId=Z5%2FGgcVQ%2FHnhfRD8%2FEOmvw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K92" s="29" t="inlineStr">
+      <c r="K92" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-shopee-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L92" s="29" t="inlineStr">
+      <c r="L92" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-shopee-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M92" s="29" t="inlineStr"/>
+      <c r="M92" s="32" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="29" t="inlineStr">
+      <c r="A93" s="32" t="inlineStr">
         <is>
           <t>linkedin_4401618037</t>
         </is>
       </c>
-      <c r="B93" s="29" t="inlineStr">
+      <c r="B93" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 20:02</t>
         </is>
       </c>
-      <c r="C93" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D93" s="29" t="inlineStr">
+      <c r="C93" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D93" s="32" t="inlineStr">
         <is>
           <t>Superhuman</t>
         </is>
       </c>
-      <c r="E93" s="29" t="inlineStr">
+      <c r="E93" s="32" t="inlineStr">
         <is>
           <t>Applied Research Intern (Summer 2026)</t>
         </is>
       </c>
-      <c r="F93" s="29" t="inlineStr">
+      <c r="F93" s="32" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G93" s="29" t="inlineStr">
+      <c r="G93" s="32" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H93" s="29" t="inlineStr">
+      <c r="H93" s="32" t="inlineStr">
         <is>
           <t>2026-04-20 09:39 UTC</t>
         </is>
       </c>
-      <c r="I93" s="30" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J93" s="31" t="inlineStr">
+      <c r="I93" s="33" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J93" s="34" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/applied-research-intern-summer-2026-at-superhuman-4401618037?refId=QaSuTZCPNmMWLvSVLYxnBg%3D%3D&amp;trackingId=VlqyKWxk2dgOXzUfhtaiGQ%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K93" s="29" t="inlineStr">
+      <c r="K93" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-superhuman-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L93" s="29" t="inlineStr">
+      <c r="L93" s="32" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-superhuman-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M93" s="29" t="inlineStr"/>
+      <c r="M93" s="32" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="32" t="inlineStr">

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Internship Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1505,9 +1505,9 @@
           <t>2026-04-16 13:57 UTC</t>
         </is>
       </c>
-      <c r="I15" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
+      <c r="I15" s="35" t="inlineStr">
+        <is>
+          <t>Applied</t>
         </is>
       </c>
       <c r="J15" s="34" t="inlineStr">
@@ -1525,7 +1525,11 @@
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M15" s="32" t="inlineStr"/>
+      <c r="M15" s="32" t="inlineStr">
+        <is>
+          <t>Auto-detected via Gmail: 'Thank you for applying'  [Auto-detected via Gmail: 'Thank you for your application, Aymane AIT DADS']</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="32" t="inlineStr">

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,6 +193,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -560,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M95"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6574,6 +6583,1014 @@
         </is>
       </c>
       <c r="M95" s="32" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="36" t="inlineStr">
+        <is>
+          <t>adzuna_5714403026</t>
+        </is>
+      </c>
+      <c r="B96" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:06</t>
+        </is>
+      </c>
+      <c r="C96" s="36" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="D96" s="36" t="inlineStr">
+        <is>
+          <t>Halliburton</t>
+        </is>
+      </c>
+      <c r="E96" s="36" t="inlineStr">
+        <is>
+          <t>Abingdon_Computer Science/Data Science/Artificial Intelligence Intern</t>
+        </is>
+      </c>
+      <c r="F96" s="36" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G96" s="36" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H96" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-30 09:58 UTC</t>
+        </is>
+      </c>
+      <c r="I96" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J96" s="38" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5714403026?utm_medium=api&amp;utm_source=9f5acb07</t>
+        </is>
+      </c>
+      <c r="K96" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-halliburton-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L96" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-halliburton-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M96" s="36" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="36" t="inlineStr">
+        <is>
+          <t>indeed_10418a615827b4d1</t>
+        </is>
+      </c>
+      <c r="B97" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:06</t>
+        </is>
+      </c>
+      <c r="C97" s="36" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="D97" s="36" t="inlineStr">
+        <is>
+          <t>Cynapse</t>
+        </is>
+      </c>
+      <c r="E97" s="36" t="inlineStr">
+        <is>
+          <t>AI Research &amp; Development Intern</t>
+        </is>
+      </c>
+      <c r="F97" s="36" t="inlineStr">
+        <is>
+          <t>Queenstown, S00, SG</t>
+        </is>
+      </c>
+      <c r="G97" s="36" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H97" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-30 00:00 UTC</t>
+        </is>
+      </c>
+      <c r="I97" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J97" s="38" t="inlineStr">
+        <is>
+          <t>https://sg.indeed.com/viewjob?jk=9016a93caf115b35</t>
+        </is>
+      </c>
+      <c r="K97" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-cynapse-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L97" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-cynapse-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M97" s="36" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="36" t="inlineStr">
+        <is>
+          <t>adzuna_5714041814</t>
+        </is>
+      </c>
+      <c r="B98" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:06</t>
+        </is>
+      </c>
+      <c r="C98" s="36" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="D98" s="36" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="E98" s="36" t="inlineStr">
+        <is>
+          <t>Intern - AI Research</t>
+        </is>
+      </c>
+      <c r="F98" s="36" t="inlineStr">
+        <is>
+          <t>Cambridge, Cambridgeshire</t>
+        </is>
+      </c>
+      <c r="G98" s="36" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H98" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-30 01:49 UTC</t>
+        </is>
+      </c>
+      <c r="I98" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J98" s="38" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5714041814?utm_medium=api&amp;utm_source=9f5acb07</t>
+        </is>
+      </c>
+      <c r="K98" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-samsung-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L98" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-samsung-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M98" s="36" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="36" t="inlineStr">
+        <is>
+          <t>indeed_0b71b590119343e5</t>
+        </is>
+      </c>
+      <c r="B99" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:06</t>
+        </is>
+      </c>
+      <c r="C99" s="36" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="D99" s="36" t="inlineStr">
+        <is>
+          <t>HASKONING</t>
+        </is>
+      </c>
+      <c r="E99" s="36" t="inlineStr">
+        <is>
+          <t>MSc thesis assignment: Machine Learning Fusion of Sentinel 2 and ICESat-2 data for Satellite Derived Bathymetry (SDB)</t>
+        </is>
+      </c>
+      <c r="F99" s="36" t="inlineStr">
+        <is>
+          <t>Amersfoort, UT, NL</t>
+        </is>
+      </c>
+      <c r="G99" s="36" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H99" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-29 00:00 UTC</t>
+        </is>
+      </c>
+      <c r="I99" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J99" s="38" t="inlineStr">
+        <is>
+          <t>https://nl.indeed.com/viewjob?jk=dd7e04db6c3db1c6</t>
+        </is>
+      </c>
+      <c r="K99" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-haskoning-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L99" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-haskoning-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M99" s="36" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="36" t="inlineStr">
+        <is>
+          <t>adzuna_5713201869</t>
+        </is>
+      </c>
+      <c r="B100" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:06</t>
+        </is>
+      </c>
+      <c r="C100" s="36" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="D100" s="36" t="inlineStr">
+        <is>
+          <t>Perspectum</t>
+        </is>
+      </c>
+      <c r="E100" s="36" t="inlineStr">
+        <is>
+          <t>Data Science (Cardiac) Intern</t>
+        </is>
+      </c>
+      <c r="F100" s="36" t="inlineStr">
+        <is>
+          <t>Cowley, Oxford</t>
+        </is>
+      </c>
+      <c r="G100" s="36" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H100" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-29 02:48 UTC</t>
+        </is>
+      </c>
+      <c r="I100" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J100" s="38" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/details/5713201869?utm_medium=api&amp;utm_source=9f5acb07</t>
+        </is>
+      </c>
+      <c r="K100" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-perspectum-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L100" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-perspectum-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M100" s="36" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="36" t="inlineStr">
+        <is>
+          <t>indeed_565e4fa6caafce9b</t>
+        </is>
+      </c>
+      <c r="B101" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:06</t>
+        </is>
+      </c>
+      <c r="C101" s="36" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="D101" s="36" t="inlineStr">
+        <is>
+          <t>Bosch</t>
+        </is>
+      </c>
+      <c r="E101" s="36" t="inlineStr">
+        <is>
+          <t>Intern, Multimodal Sensing for Smart Home Applications</t>
+        </is>
+      </c>
+      <c r="F101" s="36" t="inlineStr">
+        <is>
+          <t>Singapore, S00, SG</t>
+        </is>
+      </c>
+      <c r="G101" s="36" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H101" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-29 00:00 UTC</t>
+        </is>
+      </c>
+      <c r="I101" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J101" s="38" t="inlineStr">
+        <is>
+          <t>https://sg.indeed.com/viewjob?jk=2e98197cd87ac155</t>
+        </is>
+      </c>
+      <c r="K101" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bosch-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L101" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bosch-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M101" s="36" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="36" t="inlineStr">
+        <is>
+          <t>adzuna_5713673495</t>
+        </is>
+      </c>
+      <c r="B102" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:06</t>
+        </is>
+      </c>
+      <c r="C102" s="36" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="D102" s="36" t="inlineStr">
+        <is>
+          <t>RedTech Recruitment</t>
+        </is>
+      </c>
+      <c r="E102" s="36" t="inlineStr">
+        <is>
+          <t>Machine Vision Intern</t>
+        </is>
+      </c>
+      <c r="F102" s="36" t="inlineStr">
+        <is>
+          <t>Saffron Walden, Essex</t>
+        </is>
+      </c>
+      <c r="G102" s="36" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H102" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:12 UTC</t>
+        </is>
+      </c>
+      <c r="I102" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J102" s="38" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.co.uk/jobs/land/ad/5713673495?se=toyBeJpE8RGfkIjwp6H8IA&amp;utm_medium=api&amp;utm_source=9f5acb07&amp;v=DACC8611F87C88CEC7F988F72F79B7D44B82C3DD</t>
+        </is>
+      </c>
+      <c r="K102" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-redtech-recruitment-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L102" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-redtech-recruitment-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M102" s="36" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="36" t="inlineStr">
+        <is>
+          <t>indeed_1e67f37e2f52e0d5</t>
+        </is>
+      </c>
+      <c r="B103" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:06</t>
+        </is>
+      </c>
+      <c r="C103" s="36" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="D103" s="36" t="inlineStr">
+        <is>
+          <t>Applied Materials</t>
+        </is>
+      </c>
+      <c r="E103" s="36" t="inlineStr">
+        <is>
+          <t>Algorithm Developer Intern</t>
+        </is>
+      </c>
+      <c r="F103" s="36" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US</t>
+        </is>
+      </c>
+      <c r="G103" s="36" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H103" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-29 00:00 UTC</t>
+        </is>
+      </c>
+      <c r="I103" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J103" s="38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d1a28167b9346db</t>
+        </is>
+      </c>
+      <c r="K103" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-applied-materials-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L103" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-applied-materials-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M103" s="36" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="36" t="inlineStr">
+        <is>
+          <t>indeed_f4d1adf6f64078cf</t>
+        </is>
+      </c>
+      <c r="B104" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:06</t>
+        </is>
+      </c>
+      <c r="C104" s="36" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="D104" s="36" t="inlineStr">
+        <is>
+          <t>d-Matrix</t>
+        </is>
+      </c>
+      <c r="E104" s="36" t="inlineStr">
+        <is>
+          <t>Applied AI Engineering Intern</t>
+        </is>
+      </c>
+      <c r="F104" s="36" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US</t>
+        </is>
+      </c>
+      <c r="G104" s="36" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H104" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-29 00:00 UTC</t>
+        </is>
+      </c>
+      <c r="I104" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J104" s="38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31f3e6e263943a73</t>
+        </is>
+      </c>
+      <c r="K104" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-d-matrix-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L104" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-d-matrix-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M104" s="36" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="36" t="inlineStr">
+        <is>
+          <t>adzuna_5713106974</t>
+        </is>
+      </c>
+      <c r="B105" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:06</t>
+        </is>
+      </c>
+      <c r="C105" s="36" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="D105" s="36" t="inlineStr">
+        <is>
+          <t>Kogan.com</t>
+        </is>
+      </c>
+      <c r="E105" s="36" t="inlineStr">
+        <is>
+          <t>Data &amp; ML Intern</t>
+        </is>
+      </c>
+      <c r="F105" s="36" t="inlineStr">
+        <is>
+          <t>Melbourne Region, Victoria</t>
+        </is>
+      </c>
+      <c r="G105" s="36" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H105" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-29 10:24 UTC</t>
+        </is>
+      </c>
+      <c r="I105" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J105" s="38" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.com.au/details/5713106974?utm_medium=api&amp;utm_source=9f5acb07</t>
+        </is>
+      </c>
+      <c r="K105" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-kogancom-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L105" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-kogancom-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M105" s="36" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="36" t="inlineStr">
+        <is>
+          <t>adzuna_5712356957</t>
+        </is>
+      </c>
+      <c r="B106" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:06</t>
+        </is>
+      </c>
+      <c r="C106" s="36" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="D106" s="36" t="inlineStr">
+        <is>
+          <t>Kogan</t>
+        </is>
+      </c>
+      <c r="E106" s="36" t="inlineStr">
+        <is>
+          <t>Data &amp; ML Intern</t>
+        </is>
+      </c>
+      <c r="F106" s="36" t="inlineStr">
+        <is>
+          <t>Hampton East, Bayside Area</t>
+        </is>
+      </c>
+      <c r="G106" s="36" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H106" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-28 13:09 UTC</t>
+        </is>
+      </c>
+      <c r="I106" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J106" s="38" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.com.au/details/5712356957?utm_medium=api&amp;utm_source=9f5acb07</t>
+        </is>
+      </c>
+      <c r="K106" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-kogan-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L106" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-kogan-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M106" s="36" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="36" t="inlineStr">
+        <is>
+          <t>indeed_21b0670ed62ff422</t>
+        </is>
+      </c>
+      <c r="B107" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:06</t>
+        </is>
+      </c>
+      <c r="C107" s="36" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="D107" s="36" t="inlineStr">
+        <is>
+          <t>Gravis Robotics</t>
+        </is>
+      </c>
+      <c r="E107" s="36" t="inlineStr">
+        <is>
+          <t>Software Engineer Internship</t>
+        </is>
+      </c>
+      <c r="F107" s="36" t="inlineStr">
+        <is>
+          <t>Zürich, ZH, CH</t>
+        </is>
+      </c>
+      <c r="G107" s="36" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H107" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-28 00:00 UTC</t>
+        </is>
+      </c>
+      <c r="I107" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J107" s="38" t="inlineStr">
+        <is>
+          <t>https://ch.indeed.com/viewjob?jk=0695eda2d1ac6a35</t>
+        </is>
+      </c>
+      <c r="K107" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-gravis-robotics-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L107" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-gravis-robotics-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M107" s="36" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="36" t="inlineStr">
+        <is>
+          <t>indeed_a38f3c916c81d004</t>
+        </is>
+      </c>
+      <c r="B108" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:06</t>
+        </is>
+      </c>
+      <c r="C108" s="36" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="D108" s="36" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="E108" s="36" t="inlineStr">
+        <is>
+          <t>SAP Intern - Generative AI Engineer</t>
+        </is>
+      </c>
+      <c r="F108" s="36" t="inlineStr">
+        <is>
+          <t>Queenstown, S00, SG</t>
+        </is>
+      </c>
+      <c r="G108" s="36" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H108" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-28 00:00 UTC</t>
+        </is>
+      </c>
+      <c r="I108" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J108" s="38" t="inlineStr">
+        <is>
+          <t>https://sg.indeed.com/viewjob?jk=2658d6b6cb3c1b2a</t>
+        </is>
+      </c>
+      <c r="K108" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sap-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L108" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sap-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M108" s="36" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="36" t="inlineStr">
+        <is>
+          <t>indeed_05cf42f3ff44f48a</t>
+        </is>
+      </c>
+      <c r="B109" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:06</t>
+        </is>
+      </c>
+      <c r="C109" s="36" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="D109" s="36" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="E109" s="36" t="inlineStr">
+        <is>
+          <t>Summer 2026 Intern - AI &amp; Data Science Analyst</t>
+        </is>
+      </c>
+      <c r="F109" s="36" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US</t>
+        </is>
+      </c>
+      <c r="G109" s="36" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H109" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-28 00:00 UTC</t>
+        </is>
+      </c>
+      <c r="I109" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J109" s="38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e14e3dd4da069b0</t>
+        </is>
+      </c>
+      <c r="K109" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-salesforce-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L109" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-salesforce-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M109" s="36" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="36" t="inlineStr">
+        <is>
+          <t>indeed_43a454755db5b829</t>
+        </is>
+      </c>
+      <c r="B110" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:06</t>
+        </is>
+      </c>
+      <c r="C110" s="36" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="D110" s="36" t="inlineStr">
+        <is>
+          <t>BillionToOne</t>
+        </is>
+      </c>
+      <c r="E110" s="36" t="inlineStr">
+        <is>
+          <t>Data Science and AI Intern</t>
+        </is>
+      </c>
+      <c r="F110" s="36" t="inlineStr">
+        <is>
+          <t>Menlo Park, CA, US</t>
+        </is>
+      </c>
+      <c r="G110" s="36" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H110" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-28 00:00 UTC</t>
+        </is>
+      </c>
+      <c r="I110" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J110" s="38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7dd1b465ada114e</t>
+        </is>
+      </c>
+      <c r="K110" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-billiontoone-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L110" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-billiontoone-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M110" s="36" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="36" t="inlineStr">
+        <is>
+          <t>adzuna_5712574176</t>
+        </is>
+      </c>
+      <c r="B111" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:06</t>
+        </is>
+      </c>
+      <c r="C111" s="36" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="D111" s="36" t="inlineStr">
+        <is>
+          <t>RooflineAI GmbH</t>
+        </is>
+      </c>
+      <c r="E111" s="36" t="inlineStr">
+        <is>
+          <t>Intern Software Engineer - Edge AI Engineering</t>
+        </is>
+      </c>
+      <c r="F111" s="36" t="inlineStr">
+        <is>
+          <t>Altstadt-Nord, Köln</t>
+        </is>
+      </c>
+      <c r="G111" s="36" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H111" s="36" t="inlineStr">
+        <is>
+          <t>2026-04-28 10:25 UTC</t>
+        </is>
+      </c>
+      <c r="I111" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J111" s="38" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.de/details/5712574176?utm_medium=api&amp;utm_source=9f5acb07</t>
+        </is>
+      </c>
+      <c r="K111" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-rooflineai-gmbh-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L111" s="36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-rooflineai-gmbh-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M111" s="36" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6671,6 +7688,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J93" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J94" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J111" r:id="rId110"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Internship Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -655,861 +655,861 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="32" t="inlineStr">
+      <c r="A2" s="36" t="inlineStr">
         <is>
           <t>linkedin_4401809501</t>
         </is>
       </c>
-      <c r="B2" s="32" t="inlineStr">
+      <c r="B2" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D2" s="32" t="inlineStr">
+      <c r="C2" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D2" s="36" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E2" s="32" t="inlineStr">
+      <c r="E2" s="36" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F2" s="32" t="inlineStr">
+      <c r="F2" s="36" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G2" s="32" t="inlineStr">
+      <c r="G2" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H2" s="32" t="inlineStr">
+      <c r="H2" s="36" t="inlineStr">
         <is>
           <t>2026-04-15 22:19 UTC</t>
         </is>
       </c>
-      <c r="I2" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J2" s="34" t="inlineStr">
+      <c r="I2" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J2" s="38" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/research-intern-at-skycliff-it-4401809501?refId=HHi6SaK1fggu3E9dI3MtVg%3D%3D&amp;trackingId=r33pSo29lHStfk9FH82pyw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K2" s="32" t="inlineStr">
+      <c r="K2" s="36" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L2" s="32" t="inlineStr">
+      <c r="L2" s="36" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M2" s="32" t="inlineStr"/>
+      <c r="M2" s="36" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="36" t="inlineStr">
         <is>
           <t>linkedin_4402568578</t>
         </is>
       </c>
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D3" s="32" t="inlineStr">
+      <c r="C3" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D3" s="36" t="inlineStr">
         <is>
           <t>Webs X UM</t>
         </is>
       </c>
-      <c r="E3" s="32" t="inlineStr">
+      <c r="E3" s="36" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F3" s="32" t="inlineStr">
+      <c r="F3" s="36" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G3" s="32" t="inlineStr">
+      <c r="G3" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H3" s="32" t="inlineStr">
+      <c r="H3" s="36" t="inlineStr">
         <is>
           <t>2026-04-15 19:20 UTC</t>
         </is>
       </c>
-      <c r="I3" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J3" s="34" t="inlineStr">
+      <c r="I3" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J3" s="38" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-webs-x-um-4402568578?refId=g89JM6cY8EFeoLk6JL5tVg%3D%3D&amp;trackingId=uFZVJJX7SSI0XCPFIrLqmA%3D%3D&amp;position=19&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K3" s="32" t="inlineStr">
+      <c r="K3" s="36" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-webs-x-um-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L3" s="32" t="inlineStr">
+      <c r="L3" s="36" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-webs-x-um-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M3" s="32" t="inlineStr"/>
+      <c r="M3" s="36" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>linkedin_4399996740</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="C4" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D4" s="36" t="inlineStr">
         <is>
           <t>SUN PHARMA</t>
         </is>
       </c>
-      <c r="E4" s="32" t="inlineStr">
+      <c r="E4" s="36" t="inlineStr">
         <is>
           <t>Becario</t>
         </is>
       </c>
-      <c r="F4" s="32" t="inlineStr">
+      <c r="F4" s="36" t="inlineStr">
         <is>
           <t>Mexico City, Mexico</t>
         </is>
       </c>
-      <c r="G4" s="32" t="inlineStr">
+      <c r="G4" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H4" s="32" t="inlineStr">
+      <c r="H4" s="36" t="inlineStr">
         <is>
           <t>2026-04-15 17:59 UTC</t>
         </is>
       </c>
-      <c r="I4" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J4" s="34" t="inlineStr">
+      <c r="I4" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J4" s="38" t="inlineStr">
         <is>
           <t>https://mx.linkedin.com/jobs/view/becario-at-sun-pharma-4399996740?refId=g89JM6cY8EFeoLk6JL5tVg%3D%3D&amp;trackingId=sZ0Fkcf4RHuIpzXu4mJRNg%3D%3D&amp;position=22&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K4" s="32" t="inlineStr">
+      <c r="K4" s="36" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-sun-pharma-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L4" s="32" t="inlineStr">
+      <c r="L4" s="36" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-sun-pharma-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M4" s="32" t="inlineStr"/>
+      <c r="M4" s="36" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>linkedin_4399975959</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D5" s="32" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>LS Direct</t>
         </is>
       </c>
-      <c r="E5" s="32" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>Data Analytics Intern</t>
         </is>
       </c>
-      <c r="F5" s="32" t="inlineStr">
+      <c r="F5" s="36" t="inlineStr">
         <is>
           <t>Suffern, NY</t>
         </is>
       </c>
-      <c r="G5" s="32" t="inlineStr">
+      <c r="G5" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H5" s="32" t="inlineStr">
+      <c r="H5" s="36" t="inlineStr">
         <is>
           <t>2026-04-15 14:26 UTC</t>
         </is>
       </c>
-      <c r="I5" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J5" s="34" t="inlineStr">
+      <c r="I5" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J5" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-analytics-intern-at-ls-direct-4399975959?refId=pg0ll3e89fatVyUznLcdpw%3D%3D&amp;trackingId=5b41IoyQfIfx3Tu42domiQ%3D%3D&amp;position=23&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K5" s="32" t="inlineStr">
+      <c r="K5" s="36" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-ls-direct-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L5" s="32" t="inlineStr">
+      <c r="L5" s="36" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-ls-direct-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M5" s="32" t="inlineStr"/>
+      <c r="M5" s="36" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>linkedin_4370546718</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D6" s="32" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>Clarivate</t>
         </is>
       </c>
-      <c r="E6" s="32" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>Lead Data Scientist</t>
         </is>
       </c>
-      <c r="F6" s="32" t="inlineStr">
+      <c r="F6" s="36" t="inlineStr">
         <is>
           <t>Barcelona, Catalonia, Spain</t>
         </is>
       </c>
-      <c r="G6" s="32" t="inlineStr">
+      <c r="G6" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H6" s="32" t="inlineStr">
+      <c r="H6" s="36" t="inlineStr">
         <is>
           <t>2026-04-15 12:16 UTC</t>
         </is>
       </c>
-      <c r="I6" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J6" s="34" t="inlineStr">
+      <c r="I6" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J6" s="38" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/lead-data-scientist-at-clarivate-4370546718?refId=FyyqQfduMQ8KZ7B5LeF0UQ%3D%3D&amp;trackingId=1i1kXdbV7SMunyFTiSJHJg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K6" s="32" t="inlineStr">
+      <c r="K6" s="36" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-clarivate-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L6" s="32" t="inlineStr">
+      <c r="L6" s="36" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-clarivate-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M6" s="32" t="inlineStr"/>
+      <c r="M6" s="36" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>linkedin_4389810164</t>
         </is>
       </c>
-      <c r="B7" s="32" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C7" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D7" s="32" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>Vitality</t>
         </is>
       </c>
-      <c r="E7" s="32" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t>Senior Data Scientist - 12 Month FTC</t>
         </is>
       </c>
-      <c r="F7" s="32" t="inlineStr">
+      <c r="F7" s="36" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G7" s="32" t="inlineStr">
+      <c r="G7" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H7" s="32" t="inlineStr">
+      <c r="H7" s="36" t="inlineStr">
         <is>
           <t>2026-04-15 09:39 UTC</t>
         </is>
       </c>
-      <c r="I7" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J7" s="34" t="inlineStr">
+      <c r="I7" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J7" s="38" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/senior-data-scientist-12-month-ftc-at-vitality-4389810164?refId=FPz%2BrPoaQeqgXBm%2FfOzGGA%3D%3D&amp;trackingId=yVNh55t2X2xocDT4i6HDqQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K7" s="32" t="inlineStr">
+      <c r="K7" s="36" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-vitality-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L7" s="32" t="inlineStr">
+      <c r="L7" s="36" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-vitality-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M7" s="32" t="inlineStr"/>
+      <c r="M7" s="36" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>linkedin_4399952059</t>
         </is>
       </c>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C8" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D8" s="32" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>traide AI</t>
         </is>
       </c>
-      <c r="E8" s="32" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>AI Associate (f/m/x) (B2B SaaS Startup) - Intern/Working Student</t>
         </is>
       </c>
-      <c r="F8" s="32" t="inlineStr">
+      <c r="F8" s="36" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G8" s="32" t="inlineStr">
+      <c r="G8" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H8" s="32" t="inlineStr">
+      <c r="H8" s="36" t="inlineStr">
         <is>
           <t>2026-04-15 07:04 UTC</t>
         </is>
       </c>
-      <c r="I8" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J8" s="34" t="inlineStr">
+      <c r="I8" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J8" s="38" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/ai-associate-f-m-x-b2b-saas-startup-intern-working-student-at-traide-ai-4399952059?refId=x0uIkl175n0hipT17L%2FGRw%3D%3D&amp;trackingId=8kdzUQgW%2B7rCk2pO2oIErg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K8" s="32" t="inlineStr">
+      <c r="K8" s="36" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-traide-ai-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L8" s="32" t="inlineStr">
+      <c r="L8" s="36" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-traide-ai-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M8" s="32" t="inlineStr"/>
+      <c r="M8" s="36" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>linkedin_4399933254</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C9" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>Briink</t>
         </is>
       </c>
-      <c r="E9" s="32" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>Growth Intern (Merantix AI Campus)</t>
         </is>
       </c>
-      <c r="F9" s="32" t="inlineStr">
+      <c r="F9" s="36" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G9" s="32" t="inlineStr">
+      <c r="G9" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H9" s="32" t="inlineStr">
+      <c r="H9" s="36" t="inlineStr">
         <is>
           <t>2026-04-15 05:03 UTC</t>
         </is>
       </c>
-      <c r="I9" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J9" s="34" t="inlineStr">
+      <c r="I9" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J9" s="38" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/growth-intern-merantix-ai-campus-at-briink-4399933254?refId=x0uIkl175n0hipT17L%2FGRw%3D%3D&amp;trackingId=qEKtyJNA03Kbr6AYDlhsBw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K9" s="32" t="inlineStr">
+      <c r="K9" s="36" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-briink-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L9" s="32" t="inlineStr">
+      <c r="L9" s="36" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-briink-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M9" s="32" t="inlineStr"/>
+      <c r="M9" s="36" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>linkedin_4400429367</t>
         </is>
       </c>
-      <c r="B10" s="32" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C10" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D10" s="32" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>Tata Consultancy Services</t>
         </is>
       </c>
-      <c r="E10" s="32" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>HR -Data Scientist</t>
         </is>
       </c>
-      <c r="F10" s="32" t="inlineStr">
+      <c r="F10" s="36" t="inlineStr">
         <is>
           <t>Renton, WA</t>
         </is>
       </c>
-      <c r="G10" s="32" t="inlineStr">
+      <c r="G10" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H10" s="32" t="inlineStr">
+      <c r="H10" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 16:56 UTC</t>
         </is>
       </c>
-      <c r="I10" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J10" s="34" t="inlineStr">
+      <c r="I10" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J10" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/hr-data-scientist-at-tata-consultancy-services-4400429367?refId=vJILgNySaXYUQknbyaKZZQ%3D%3D&amp;trackingId=7cZ0KYh8Sv5%2Fh6%2FG86%2BLug%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K10" s="32" t="inlineStr">
+      <c r="K10" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-tata-consultancy-services-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L10" s="32" t="inlineStr">
+      <c r="L10" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-tata-consultancy-services-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M10" s="32" t="inlineStr"/>
+      <c r="M10" s="36" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>linkedin_4390814627</t>
         </is>
       </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C11" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D11" s="32" t="inlineStr">
+      <c r="C11" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D11" s="36" t="inlineStr">
         <is>
           <t>Criteo</t>
         </is>
       </c>
-      <c r="E11" s="32" t="inlineStr">
+      <c r="E11" s="36" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F11" s="32" t="inlineStr">
+      <c r="F11" s="36" t="inlineStr">
         <is>
           <t>Barcelona, Catalonia, Spain</t>
         </is>
       </c>
-      <c r="G11" s="32" t="inlineStr">
+      <c r="G11" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H11" s="32" t="inlineStr">
+      <c r="H11" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 12:19 UTC</t>
         </is>
       </c>
-      <c r="I11" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J11" s="34" t="inlineStr">
+      <c r="I11" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J11" s="38" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/data-analyst-intern-at-criteo-4390814627?refId=PCZWvfzZIzNkx6giU9jTsA%3D%3D&amp;trackingId=T%2FMog6vtgG8P3ihAU9b1uQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K11" s="32" t="inlineStr">
+      <c r="K11" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-criteo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L11" s="32" t="inlineStr">
+      <c r="L11" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-criteo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M11" s="32" t="inlineStr"/>
+      <c r="M11" s="36" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>linkedin_4402983364</t>
         </is>
       </c>
-      <c r="B12" s="32" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C12" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D12" s="32" t="inlineStr">
+      <c r="C12" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E12" s="32" t="inlineStr">
+      <c r="E12" s="36" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F12" s="32" t="inlineStr">
+      <c r="F12" s="36" t="inlineStr">
         <is>
           <t>Brussels, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G12" s="32" t="inlineStr">
+      <c r="G12" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H12" s="32" t="inlineStr">
+      <c r="H12" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I12" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J12" s="34" t="inlineStr">
+      <c r="I12" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J12" s="38" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402983364?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=zV4sJQyNyQg%2FS%2BYm6Ba9Eg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K12" s="32" t="inlineStr">
+      <c r="K12" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L12" s="32" t="inlineStr">
+      <c r="L12" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M12" s="32" t="inlineStr"/>
+      <c r="M12" s="36" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>linkedin_4390725142</t>
         </is>
       </c>
-      <c r="B13" s="32" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C13" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D13" s="32" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D13" s="36" t="inlineStr">
         <is>
           <t>Boston Consulting Group (BCG)</t>
         </is>
       </c>
-      <c r="E13" s="32" t="inlineStr">
+      <c r="E13" s="36" t="inlineStr">
         <is>
           <t>Forward Deployed AI Engineer, Internship, United Kingdom - BCG X</t>
         </is>
       </c>
-      <c r="F13" s="32" t="inlineStr">
+      <c r="F13" s="36" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G13" s="32" t="inlineStr">
+      <c r="G13" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H13" s="32" t="inlineStr">
+      <c r="H13" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 16:24 UTC</t>
         </is>
       </c>
-      <c r="I13" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J13" s="34" t="inlineStr">
+      <c r="I13" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J13" s="38" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/forward-deployed-ai-engineer-internship-united-kingdom-bcg-x-at-boston-consulting-group-bcg-4390725142?refId=YHAZO5vAx9Qtg1RXMma%2F%2BA%3D%3D&amp;trackingId=E8kiSHzcdYe%2FH6s%2FCkGtMw%3D%3D&amp;position=7&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K13" s="32" t="inlineStr">
+      <c r="K13" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L13" s="32" t="inlineStr">
+      <c r="L13" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M13" s="32" t="inlineStr"/>
+      <c r="M13" s="36" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>linkedin_4400428064</t>
         </is>
       </c>
-      <c r="B14" s="32" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C14" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D14" s="32" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D14" s="36" t="inlineStr">
         <is>
           <t>Fanatics</t>
         </is>
       </c>
-      <c r="E14" s="32" t="inlineStr">
+      <c r="E14" s="36" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="F14" s="32" t="inlineStr">
+      <c r="F14" s="36" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G14" s="32" t="inlineStr">
+      <c r="G14" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H14" s="32" t="inlineStr">
+      <c r="H14" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 16:16 UTC</t>
         </is>
       </c>
-      <c r="I14" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J14" s="34" t="inlineStr">
+      <c r="I14" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J14" s="38" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/data-scientist-at-fanatics-4400428064?refId=SNMwEp9%2FBozAkX4FBnhJwQ%3D%3D&amp;trackingId=cAX0aKWV%2FBX1fvQzm%2FkEMg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K14" s="32" t="inlineStr">
+      <c r="K14" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-fanatics-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L14" s="32" t="inlineStr">
+      <c r="L14" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-fanatics-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M14" s="32" t="inlineStr"/>
+      <c r="M14" s="36" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>linkedin_4390730090</t>
         </is>
       </c>
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C15" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D15" s="32" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D15" s="36" t="inlineStr">
         <is>
           <t>Boston Consulting Group (BCG)</t>
         </is>
       </c>
-      <c r="E15" s="32" t="inlineStr">
+      <c r="E15" s="36" t="inlineStr">
         <is>
           <t>Forward Deployed AI Scientist, Internship, United Kingdom - BCG X</t>
         </is>
       </c>
-      <c r="F15" s="32" t="inlineStr">
+      <c r="F15" s="36" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G15" s="32" t="inlineStr">
+      <c r="G15" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H15" s="32" t="inlineStr">
+      <c r="H15" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 13:57 UTC</t>
         </is>
@@ -1519,1198 +1519,1198 @@
           <t>Applied</t>
         </is>
       </c>
-      <c r="J15" s="34" t="inlineStr">
+      <c r="J15" s="38" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/forward-deployed-ai-scientist-internship-united-kingdom-bcg-x-at-boston-consulting-group-bcg-4390730090?refId=YHAZO5vAx9Qtg1RXMma%2F%2BA%3D%3D&amp;trackingId=m50MzwjbYzUmAv7nJVAKgA%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K15" s="32" t="inlineStr">
+      <c r="K15" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L15" s="32" t="inlineStr">
+      <c r="L15" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M15" s="32" t="inlineStr">
+      <c r="M15" s="36" t="inlineStr">
         <is>
           <t>Auto-detected via Gmail: 'Thank you for applying'  [Auto-detected via Gmail: 'Thank you for your application, Aymane AIT DADS']</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>linkedin_4402138096</t>
         </is>
       </c>
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C16" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D16" s="32" t="inlineStr">
+      <c r="C16" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D16" s="36" t="inlineStr">
         <is>
           <t>Kelly Tutors</t>
         </is>
       </c>
-      <c r="E16" s="32" t="inlineStr">
+      <c r="E16" s="36" t="inlineStr">
         <is>
           <t>Research Intern (3-5hrs/week, flexible)</t>
         </is>
       </c>
-      <c r="F16" s="32" t="inlineStr">
+      <c r="F16" s="36" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G16" s="32" t="inlineStr">
+      <c r="G16" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H16" s="32" t="inlineStr">
+      <c r="H16" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 14:40 UTC</t>
         </is>
       </c>
-      <c r="I16" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J16" s="34" t="inlineStr">
+      <c r="I16" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J16" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/research-intern-3-5hrs-week-flexible-at-kelly-tutors-4402138096?refId=HmOS2YEHUH3GOVent1txqw%3D%3D&amp;trackingId=3XBXMUoBdiHeRL4qw%2B2qRw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K16" s="32" t="inlineStr">
+      <c r="K16" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-kelly-tutors-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L16" s="32" t="inlineStr">
+      <c r="L16" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-kelly-tutors-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M16" s="32" t="inlineStr"/>
+      <c r="M16" s="36" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>linkedin_4378557045</t>
         </is>
       </c>
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C17" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D17" s="32" t="inlineStr">
+      <c r="C17" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D17" s="36" t="inlineStr">
         <is>
           <t>Fund for Public Health in NYC</t>
         </is>
       </c>
-      <c r="E17" s="32" t="inlineStr">
+      <c r="E17" s="36" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="F17" s="32" t="inlineStr">
+      <c r="F17" s="36" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G17" s="32" t="inlineStr">
+      <c r="G17" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H17" s="32" t="inlineStr">
+      <c r="H17" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 16:13 UTC</t>
         </is>
       </c>
-      <c r="I17" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J17" s="34" t="inlineStr">
+      <c r="I17" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J17" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-scientist-at-fund-for-public-health-in-nyc-4378557045?refId=JsndNRa0tnfF7dsuxv62wA%3D%3D&amp;trackingId=Pmgt6JCxYmQun5Uv6%2BLbiQ%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K17" s="32" t="inlineStr">
+      <c r="K17" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-fund-for-public-health-in-nyc-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L17" s="32" t="inlineStr">
+      <c r="L17" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-fund-for-public-health-in-nyc-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M17" s="32" t="inlineStr"/>
+      <c r="M17" s="36" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="32" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>linkedin_4402977457</t>
         </is>
       </c>
-      <c r="B18" s="32" t="inlineStr">
+      <c r="B18" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C18" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D18" s="32" t="inlineStr">
+      <c r="C18" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D18" s="36" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E18" s="32" t="inlineStr">
+      <c r="E18" s="36" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F18" s="32" t="inlineStr">
+      <c r="F18" s="36" t="inlineStr">
         <is>
           <t>Brussels, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G18" s="32" t="inlineStr">
+      <c r="G18" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H18" s="32" t="inlineStr">
+      <c r="H18" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I18" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J18" s="34" t="inlineStr">
+      <c r="I18" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J18" s="38" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402977457?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=gL9sbQh%2FaLMmzvXjuO71WQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K18" s="32" t="inlineStr">
+      <c r="K18" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L18" s="32" t="inlineStr">
+      <c r="L18" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M18" s="32" t="inlineStr"/>
+      <c r="M18" s="36" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="32" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>linkedin_4371210537</t>
         </is>
       </c>
-      <c r="B19" s="32" t="inlineStr">
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C19" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D19" s="32" t="inlineStr">
+      <c r="C19" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D19" s="36" t="inlineStr">
         <is>
           <t>Gildan</t>
         </is>
       </c>
-      <c r="E19" s="32" t="inlineStr">
+      <c r="E19" s="36" t="inlineStr">
         <is>
           <t>Intern, ERP GenAI</t>
         </is>
       </c>
-      <c r="F19" s="32" t="inlineStr">
+      <c r="F19" s="36" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G19" s="32" t="inlineStr">
+      <c r="G19" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H19" s="32" t="inlineStr">
+      <c r="H19" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 15:23 UTC</t>
         </is>
       </c>
-      <c r="I19" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J19" s="34" t="inlineStr">
+      <c r="I19" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J19" s="38" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/intern-erp-genai-at-gildan-4371210537?refId=jteS%2Ft3Cmc2XLVMFToCpKw%3D%3D&amp;trackingId=OQGg%2Bob2m9u4kkbRcgWoUw%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K19" s="32" t="inlineStr">
+      <c r="K19" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-gildan-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L19" s="32" t="inlineStr">
+      <c r="L19" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-gildan-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M19" s="32" t="inlineStr"/>
+      <c r="M19" s="36" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="32" t="inlineStr">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>linkedin_4402974624</t>
         </is>
       </c>
-      <c r="B20" s="32" t="inlineStr">
+      <c r="B20" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C20" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D20" s="32" t="inlineStr">
+      <c r="C20" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D20" s="36" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E20" s="32" t="inlineStr">
+      <c r="E20" s="36" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F20" s="32" t="inlineStr">
+      <c r="F20" s="36" t="inlineStr">
         <is>
           <t>Uccle, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G20" s="32" t="inlineStr">
+      <c r="G20" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H20" s="32" t="inlineStr">
+      <c r="H20" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I20" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J20" s="34" t="inlineStr">
+      <c r="I20" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J20" s="38" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402974624?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=RJfkVsuYxv4DqyEhPJ367g%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K20" s="32" t="inlineStr">
+      <c r="K20" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L20" s="32" t="inlineStr">
+      <c r="L20" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M20" s="32" t="inlineStr"/>
+      <c r="M20" s="36" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="32" t="inlineStr">
+      <c r="A21" s="36" t="inlineStr">
         <is>
           <t>linkedin_4402174633</t>
         </is>
       </c>
-      <c r="B21" s="32" t="inlineStr">
+      <c r="B21" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C21" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D21" s="32" t="inlineStr">
+      <c r="C21" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D21" s="36" t="inlineStr">
         <is>
           <t>Cloudera</t>
         </is>
       </c>
-      <c r="E21" s="32" t="inlineStr">
+      <c r="E21" s="36" t="inlineStr">
         <is>
           <t>AI Enablement Intern (Ireland Based)</t>
         </is>
       </c>
-      <c r="F21" s="32" t="inlineStr">
+      <c r="F21" s="36" t="inlineStr">
         <is>
           <t>Greater Dublin</t>
         </is>
       </c>
-      <c r="G21" s="32" t="inlineStr">
+      <c r="G21" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H21" s="32" t="inlineStr">
+      <c r="H21" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 18:24 UTC</t>
         </is>
       </c>
-      <c r="I21" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J21" s="34" t="inlineStr">
+      <c r="I21" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J21" s="38" t="inlineStr">
         <is>
           <t>https://ie.linkedin.com/jobs/view/ai-enablement-intern-ireland-based-at-cloudera-4402174633?refId=d9iDz5spYJk0nIor701k5g%3D%3D&amp;trackingId=6OZvFiMQ12VqIzY6EqUe7A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K21" s="32" t="inlineStr">
+      <c r="K21" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-cloudera-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L21" s="32" t="inlineStr">
+      <c r="L21" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-cloudera-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M21" s="32" t="inlineStr"/>
+      <c r="M21" s="36" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="32" t="inlineStr">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>linkedin_4403115250</t>
         </is>
       </c>
-      <c r="B22" s="32" t="inlineStr">
+      <c r="B22" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C22" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D22" s="32" t="inlineStr">
+      <c r="C22" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D22" s="36" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E22" s="32" t="inlineStr">
+      <c r="E22" s="36" t="inlineStr">
         <is>
           <t>PhD Research Intern, Mapping Software</t>
         </is>
       </c>
-      <c r="F22" s="32" t="inlineStr">
+      <c r="F22" s="36" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G22" s="32" t="inlineStr">
+      <c r="G22" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H22" s="32" t="inlineStr">
+      <c r="H22" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 19:55 UTC</t>
         </is>
       </c>
-      <c r="I22" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J22" s="34" t="inlineStr">
+      <c r="I22" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J22" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-mapping-software-at-zoox-4403115250?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=67WsHxTIXiO%2ByWr0OYU7ug%3D%3D&amp;position=10&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K22" s="32" t="inlineStr">
+      <c r="K22" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L22" s="32" t="inlineStr">
+      <c r="L22" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M22" s="32" t="inlineStr"/>
+      <c r="M22" s="36" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="32" t="inlineStr">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>linkedin_4379373115</t>
         </is>
       </c>
-      <c r="B23" s="32" t="inlineStr">
+      <c r="B23" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C23" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D23" s="32" t="inlineStr">
+      <c r="C23" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D23" s="36" t="inlineStr">
         <is>
           <t>Woven by Toyota</t>
         </is>
       </c>
-      <c r="E23" s="32" t="inlineStr">
+      <c r="E23" s="36" t="inlineStr">
         <is>
           <t>Applied Scientist, Computer Vision and Generative Models, Vision AI (Internship)</t>
         </is>
       </c>
-      <c r="F23" s="32" t="inlineStr">
+      <c r="F23" s="36" t="inlineStr">
         <is>
           <t>Tokyo, Japan</t>
         </is>
       </c>
-      <c r="G23" s="32" t="inlineStr">
+      <c r="G23" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H23" s="32" t="inlineStr">
+      <c r="H23" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 14:55 UTC</t>
         </is>
       </c>
-      <c r="I23" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J23" s="34" t="inlineStr">
+      <c r="I23" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J23" s="38" t="inlineStr">
         <is>
           <t>https://jp.linkedin.com/jobs/view/applied-scientist-computer-vision-and-generative-models-vision-ai-internship-at-woven-by-toyota-4379373115?refId=4q6ISAXJ%2BcfZsJD688QZWg%3D%3D&amp;trackingId=pUnO9OuzZx4G6BOukom%2FQQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K23" s="32" t="inlineStr">
+      <c r="K23" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-woven-by-toyota-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L23" s="32" t="inlineStr">
+      <c r="L23" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-woven-by-toyota-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M23" s="32" t="inlineStr"/>
+      <c r="M23" s="36" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="32" t="inlineStr">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>linkedin_4325103488</t>
         </is>
       </c>
-      <c r="B24" s="32" t="inlineStr">
+      <c r="B24" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C24" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D24" s="32" t="inlineStr">
+      <c r="C24" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D24" s="36" t="inlineStr">
         <is>
           <t>Binance</t>
         </is>
       </c>
-      <c r="E24" s="32" t="inlineStr">
+      <c r="E24" s="36" t="inlineStr">
         <is>
           <t>Binance Accelerator Program - DevOps (Artificial Intelligence)</t>
         </is>
       </c>
-      <c r="F24" s="32" t="inlineStr">
+      <c r="F24" s="36" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G24" s="32" t="inlineStr">
+      <c r="G24" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H24" s="32" t="inlineStr">
+      <c r="H24" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 12:13 UTC</t>
         </is>
       </c>
-      <c r="I24" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J24" s="34" t="inlineStr">
+      <c r="I24" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J24" s="38" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/binance-accelerator-program-devops-artificial-intelligence-at-binance-4325103488?refId=KzaD5RMOfYQEZyaw6UmcpQ%3D%3D&amp;trackingId=8R4okHiG3RYyjThXHAqxIQ%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K24" s="32" t="inlineStr">
+      <c r="K24" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-binance-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L24" s="32" t="inlineStr">
+      <c r="L24" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-binance-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M24" s="32" t="inlineStr"/>
+      <c r="M24" s="36" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="32" t="inlineStr">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>linkedin_4400563251</t>
         </is>
       </c>
-      <c r="B25" s="32" t="inlineStr">
+      <c r="B25" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C25" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D25" s="32" t="inlineStr">
+      <c r="C25" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D25" s="36" t="inlineStr">
         <is>
           <t>Aylo</t>
         </is>
       </c>
-      <c r="E25" s="32" t="inlineStr">
+      <c r="E25" s="36" t="inlineStr">
         <is>
           <t>Sr. Full-Stack Data Scientist - Data Services</t>
         </is>
       </c>
-      <c r="F25" s="32" t="inlineStr">
+      <c r="F25" s="36" t="inlineStr">
         <is>
           <t>Greater Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G25" s="32" t="inlineStr">
+      <c r="G25" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H25" s="32" t="inlineStr">
+      <c r="H25" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 12:01 UTC</t>
         </is>
       </c>
-      <c r="I25" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J25" s="34" t="inlineStr">
+      <c r="I25" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J25" s="38" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/sr-full-stack-data-scientist-data-services-at-aylo-4400563251?refId=3X2hsLwn0XF5%2BC4ABneEzA%3D%3D&amp;trackingId=aJHp5psMKfAaMJdxBAz5Hw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K25" s="32" t="inlineStr">
+      <c r="K25" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-aylo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L25" s="32" t="inlineStr">
+      <c r="L25" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-aylo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M25" s="32" t="inlineStr"/>
+      <c r="M25" s="36" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="32" t="inlineStr">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>linkedin_4400403670</t>
         </is>
       </c>
-      <c r="B26" s="32" t="inlineStr">
+      <c r="B26" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C26" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D26" s="32" t="inlineStr">
+      <c r="C26" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D26" s="36" t="inlineStr">
         <is>
           <t>Schneider Electric</t>
         </is>
       </c>
-      <c r="E26" s="32" t="inlineStr">
+      <c r="E26" s="36" t="inlineStr">
         <is>
           <t>Internship in Global AI Sales Enablement &amp; Analytics</t>
         </is>
       </c>
-      <c r="F26" s="32" t="inlineStr">
+      <c r="F26" s="36" t="inlineStr">
         <is>
           <t>Warsaw, Mazowieckie, Poland</t>
         </is>
       </c>
-      <c r="G26" s="32" t="inlineStr">
+      <c r="G26" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H26" s="32" t="inlineStr">
+      <c r="H26" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 11:43 UTC</t>
         </is>
       </c>
-      <c r="I26" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J26" s="34" t="inlineStr">
+      <c r="I26" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J26" s="38" t="inlineStr">
         <is>
           <t>https://pl.linkedin.com/jobs/view/internship-in-global-ai-sales-enablement-analytics-at-schneider-electric-4400403670?refId=0j6PfgagLJw81v3dQ49jXQ%3D%3D&amp;trackingId=ErR9yiUH1tcny4hRKbXl8A%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K26" s="32" t="inlineStr">
+      <c r="K26" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-schneider-electric-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L26" s="32" t="inlineStr">
+      <c r="L26" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-schneider-electric-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M26" s="32" t="inlineStr"/>
+      <c r="M26" s="36" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="32" t="inlineStr">
+      <c r="A27" s="36" t="inlineStr">
         <is>
           <t>linkedin_4297755027</t>
         </is>
       </c>
-      <c r="B27" s="32" t="inlineStr">
+      <c r="B27" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C27" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D27" s="32" t="inlineStr">
+      <c r="C27" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D27" s="36" t="inlineStr">
         <is>
           <t>Databricks</t>
         </is>
       </c>
-      <c r="E27" s="32" t="inlineStr">
+      <c r="E27" s="36" t="inlineStr">
         <is>
           <t>PhD GenAI Research Scientist Intern</t>
         </is>
       </c>
-      <c r="F27" s="32" t="inlineStr">
+      <c r="F27" s="36" t="inlineStr">
         <is>
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="G27" s="32" t="inlineStr">
+      <c r="G27" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H27" s="32" t="inlineStr">
+      <c r="H27" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 10:31 UTC</t>
         </is>
       </c>
-      <c r="I27" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J27" s="34" t="inlineStr">
+      <c r="I27" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J27" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-genai-research-scientist-intern-at-databricks-4297755027?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=UXoh9K97xsqO%2FzDhCy7Uug%3D%3D&amp;position=8&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K27" s="32" t="inlineStr">
+      <c r="K27" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-databricks-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L27" s="32" t="inlineStr">
+      <c r="L27" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-databricks-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M27" s="32" t="inlineStr"/>
+      <c r="M27" s="36" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="32" t="inlineStr">
+      <c r="A28" s="36" t="inlineStr">
         <is>
           <t>linkedin_4401843829</t>
         </is>
       </c>
-      <c r="B28" s="32" t="inlineStr">
+      <c r="B28" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C28" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D28" s="32" t="inlineStr">
+      <c r="C28" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D28" s="36" t="inlineStr">
         <is>
           <t>Tiger Brokers Singapore</t>
         </is>
       </c>
-      <c r="E28" s="32" t="inlineStr">
+      <c r="E28" s="36" t="inlineStr">
         <is>
           <t>Quantitative Investment Analyst Intern</t>
         </is>
       </c>
-      <c r="F28" s="32" t="inlineStr">
+      <c r="F28" s="36" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G28" s="32" t="inlineStr">
+      <c r="G28" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H28" s="32" t="inlineStr">
+      <c r="H28" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 06:09 UTC</t>
         </is>
       </c>
-      <c r="I28" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J28" s="34" t="inlineStr">
+      <c r="I28" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J28" s="38" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/quantitative-investment-analyst-intern-at-tiger-brokers-singapore-4401843829?refId=LJ4PwcXqLhd1gtOBe9ZVig%3D%3D&amp;trackingId=oxh8Ol2m1QKvqfrvl10UqA%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K28" s="32" t="inlineStr">
+      <c r="K28" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-tiger-brokers-singapore-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L28" s="32" t="inlineStr">
+      <c r="L28" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-tiger-brokers-singapore-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M28" s="32" t="inlineStr"/>
+      <c r="M28" s="36" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="32" t="inlineStr">
+      <c r="A29" s="36" t="inlineStr">
         <is>
           <t>linkedin_4400148847</t>
         </is>
       </c>
-      <c r="B29" s="32" t="inlineStr">
+      <c r="B29" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C29" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D29" s="32" t="inlineStr">
+      <c r="C29" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D29" s="36" t="inlineStr">
         <is>
           <t>Boomlet</t>
         </is>
       </c>
-      <c r="E29" s="32" t="inlineStr">
+      <c r="E29" s="36" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F29" s="32" t="inlineStr">
+      <c r="F29" s="36" t="inlineStr">
         <is>
           <t>Mumbai, Maharashtra, India</t>
         </is>
       </c>
-      <c r="G29" s="32" t="inlineStr">
+      <c r="G29" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H29" s="32" t="inlineStr">
+      <c r="H29" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 05:24 UTC</t>
         </is>
       </c>
-      <c r="I29" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J29" s="34" t="inlineStr">
+      <c r="I29" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J29" s="38" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-boomlet-4400148847?refId=vAgiKqchg4pd6EgGGQ%2FF%2FA%3D%3D&amp;trackingId=IoHiSd1L28nXXarEd4gYfw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K29" s="32" t="inlineStr">
+      <c r="K29" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boomlet-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L29" s="32" t="inlineStr">
+      <c r="L29" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boomlet-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M29" s="32" t="inlineStr"/>
+      <c r="M29" s="36" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="32" t="inlineStr">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>linkedin_4401844394</t>
         </is>
       </c>
-      <c r="B30" s="32" t="inlineStr">
+      <c r="B30" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C30" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D30" s="32" t="inlineStr">
+      <c r="C30" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D30" s="36" t="inlineStr">
         <is>
           <t>On-us</t>
         </is>
       </c>
-      <c r="E30" s="32" t="inlineStr">
+      <c r="E30" s="36" t="inlineStr">
         <is>
           <t>AI Business Analyst Summer Intern</t>
         </is>
       </c>
-      <c r="F30" s="32" t="inlineStr">
+      <c r="F30" s="36" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G30" s="32" t="inlineStr">
+      <c r="G30" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H30" s="32" t="inlineStr">
+      <c r="H30" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 04:56 UTC</t>
         </is>
       </c>
-      <c r="I30" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J30" s="34" t="inlineStr">
+      <c r="I30" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J30" s="38" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/ai-business-analyst-summer-intern-at-on-us-4401844394?refId=lslydLUu5l8kXOktysXYaw%3D%3D&amp;trackingId=BQ%2BoYgH5QtZKBWGZQgBfNQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K30" s="32" t="inlineStr">
+      <c r="K30" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-on-us-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L30" s="32" t="inlineStr">
+      <c r="L30" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-on-us-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M30" s="32" t="inlineStr"/>
+      <c r="M30" s="36" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="32" t="inlineStr">
+      <c r="A31" s="36" t="inlineStr">
         <is>
           <t>linkedin_4401837715</t>
         </is>
       </c>
-      <c r="B31" s="32" t="inlineStr">
+      <c r="B31" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C31" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D31" s="32" t="inlineStr">
+      <c r="C31" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D31" s="36" t="inlineStr">
         <is>
           <t>Pathos Consultancy</t>
         </is>
       </c>
-      <c r="E31" s="32" t="inlineStr">
+      <c r="E31" s="36" t="inlineStr">
         <is>
           <t>Quantitative Research &amp; Development Internships</t>
         </is>
       </c>
-      <c r="F31" s="32" t="inlineStr">
+      <c r="F31" s="36" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G31" s="32" t="inlineStr">
+      <c r="G31" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H31" s="32" t="inlineStr">
+      <c r="H31" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 03:48 UTC</t>
         </is>
       </c>
-      <c r="I31" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J31" s="34" t="inlineStr">
+      <c r="I31" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J31" s="38" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/quantitative-research-development-internships-at-pathos-consultancy-4401837715?refId=KzaD5RMOfYQEZyaw6UmcpQ%3D%3D&amp;trackingId=eIGVr2dDtK%2F1o37C90xRoQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K31" s="32" t="inlineStr">
+      <c r="K31" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-pathos-consultancy-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L31" s="32" t="inlineStr">
+      <c r="L31" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-pathos-consultancy-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M31" s="32" t="inlineStr"/>
+      <c r="M31" s="36" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="32" t="inlineStr">
+      <c r="A32" s="36" t="inlineStr">
         <is>
           <t>linkedin_4402662606</t>
         </is>
       </c>
-      <c r="B32" s="32" t="inlineStr">
+      <c r="B32" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C32" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D32" s="32" t="inlineStr">
+      <c r="C32" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D32" s="36" t="inlineStr">
         <is>
           <t>Stripe</t>
         </is>
       </c>
-      <c r="E32" s="32" t="inlineStr">
+      <c r="E32" s="36" t="inlineStr">
         <is>
           <t>PhD Machine Learning Engineer, Intern</t>
         </is>
       </c>
-      <c r="F32" s="32" t="inlineStr">
+      <c r="F32" s="36" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G32" s="32" t="inlineStr">
+      <c r="G32" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H32" s="32" t="inlineStr">
+      <c r="H32" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 02:23 UTC</t>
         </is>
       </c>
-      <c r="I32" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J32" s="34" t="inlineStr">
+      <c r="I32" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J32" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-machine-learning-engineer-intern-at-stripe-4402662606?refId=vJILgNySaXYUQknbyaKZZQ%3D%3D&amp;trackingId=NDMzaPfHMoCKo5uxI3THcw%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K32" s="32" t="inlineStr">
+      <c r="K32" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L32" s="32" t="inlineStr">
+      <c r="L32" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M32" s="32" t="inlineStr"/>
+      <c r="M32" s="36" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="32" t="inlineStr">
+      <c r="A33" s="36" t="inlineStr">
         <is>
           <t>linkedin_4402953925</t>
         </is>
       </c>
-      <c r="B33" s="32" t="inlineStr">
+      <c r="B33" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C33" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D33" s="32" t="inlineStr">
+      <c r="C33" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D33" s="36" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E33" s="32" t="inlineStr">
+      <c r="E33" s="36" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F33" s="32" t="inlineStr">
+      <c r="F33" s="36" t="inlineStr">
         <is>
           <t>Dubai, Dubai, United Arab Emirates</t>
         </is>
       </c>
-      <c r="G33" s="32" t="inlineStr">
+      <c r="G33" s="36" t="inlineStr">
         <is>
           <t>Middle_East</t>
         </is>
       </c>
-      <c r="H33" s="32" t="inlineStr">
+      <c r="H33" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 00:00 UTC</t>
         </is>
       </c>
-      <c r="I33" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J33" s="34" t="inlineStr">
+      <c r="I33" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J33" s="38" t="inlineStr">
         <is>
           <t>https://ae.linkedin.com/jobs/view/research-intern-at-skycliff-it-4402953925?refId=f%2BmSR6Ncm83dISKgoQTrbw%3D%3D&amp;trackingId=CdPOXElDD3wJKKeBZSdWsw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K33" s="32" t="inlineStr">
+      <c r="K33" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L33" s="32" t="inlineStr">
+      <c r="L33" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M33" s="32" t="inlineStr"/>
+      <c r="M33" s="36" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="32" t="inlineStr">
+      <c r="A34" s="36" t="inlineStr">
         <is>
           <t>linkedin_4402617206</t>
         </is>
       </c>
-      <c r="B34" s="32" t="inlineStr">
+      <c r="B34" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C34" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D34" s="32" t="inlineStr">
+      <c r="C34" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D34" s="36" t="inlineStr">
         <is>
           <t>Stripe</t>
         </is>
       </c>
-      <c r="E34" s="32" t="inlineStr">
+      <c r="E34" s="36" t="inlineStr">
         <is>
           <t>PhD Machine Learning Engineer, Intern</t>
         </is>
       </c>
-      <c r="F34" s="32" t="inlineStr">
+      <c r="F34" s="36" t="inlineStr">
         <is>
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="G34" s="32" t="inlineStr">
+      <c r="G34" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H34" s="32" t="inlineStr">
+      <c r="H34" s="36" t="inlineStr">
         <is>
           <t>2026-04-15 20:25 UTC</t>
         </is>
@@ -2720,3869 +2720,3869 @@
           <t>Applied</t>
         </is>
       </c>
-      <c r="J34" s="34" t="inlineStr">
+      <c r="J34" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-machine-learning-engineer-intern-at-stripe-4402617206?refId=zKUzVrf7g9pFvKbgWIK%2FsA%3D%3D&amp;trackingId=yAc4U29LYJcrlQSUWWcubA%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K34" s="32" t="inlineStr">
+      <c r="K34" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L34" s="32" t="inlineStr">
+      <c r="L34" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-stripe-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M34" s="32" t="inlineStr">
+      <c r="M34" s="36" t="inlineStr">
         <is>
           <t>Status set via Telegram command</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="32" t="inlineStr">
+      <c r="A35" s="36" t="inlineStr">
         <is>
           <t>linkedin_4403183407</t>
         </is>
       </c>
-      <c r="B35" s="32" t="inlineStr">
+      <c r="B35" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C35" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D35" s="32" t="inlineStr">
+      <c r="C35" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D35" s="36" t="inlineStr">
         <is>
           <t>Hardware FYI</t>
         </is>
       </c>
-      <c r="E35" s="32" t="inlineStr">
+      <c r="E35" s="36" t="inlineStr">
         <is>
           <t>Robotics - Applied Scientist II Intern / Co-op - 2026 (Robotics, Manipulation, Perception, Motion Planning, Autonomous Mobile Robots, Computer Vision, Machine Learning, Controls, and more)</t>
         </is>
       </c>
-      <c r="F35" s="32" t="inlineStr">
+      <c r="F35" s="36" t="inlineStr">
         <is>
           <t>Boston, MA</t>
         </is>
       </c>
-      <c r="G35" s="32" t="inlineStr">
+      <c r="G35" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H35" s="32" t="inlineStr">
+      <c r="H35" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 04:31 UTC</t>
         </is>
       </c>
-      <c r="I35" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J35" s="34" t="inlineStr">
+      <c r="I35" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J35" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/robotics-applied-scientist-ii-intern-co-op-2026-robotics-manipulation-perception-motion-planning-autonomous-mobile-robots-computer-vision-machine-learning-controls-and-more-at-hardware-fyi-4403183407?refId=s5WxXRPJ8QU7G2WPi2yNiw%3D%3D&amp;trackingId=rjd%2F8qdM5kQMmADtGJgSSw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K35" s="32" t="inlineStr">
+      <c r="K35" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-hardware-fyi-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L35" s="32" t="inlineStr">
+      <c r="L35" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-hardware-fyi-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M35" s="32" t="inlineStr"/>
+      <c r="M35" s="36" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="32" t="inlineStr">
+      <c r="A36" s="36" t="inlineStr">
         <is>
           <t>linkedin_4403153262</t>
         </is>
       </c>
-      <c r="B36" s="32" t="inlineStr">
+      <c r="B36" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C36" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D36" s="32" t="inlineStr">
+      <c r="C36" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D36" s="36" t="inlineStr">
         <is>
           <t>Generali Malaysia</t>
         </is>
       </c>
-      <c r="E36" s="32" t="inlineStr">
+      <c r="E36" s="36" t="inlineStr">
         <is>
           <t>Intern, IT (AI Engineering)</t>
         </is>
       </c>
-      <c r="F36" s="32" t="inlineStr">
+      <c r="F36" s="36" t="inlineStr">
         <is>
           <t>Federal Territory of Kuala Lumpur, Malaysia</t>
         </is>
       </c>
-      <c r="G36" s="32" t="inlineStr">
+      <c r="G36" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H36" s="32" t="inlineStr">
+      <c r="H36" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 00:47 UTC</t>
         </is>
       </c>
-      <c r="I36" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J36" s="34" t="inlineStr">
+      <c r="I36" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J36" s="38" t="inlineStr">
         <is>
           <t>https://my.linkedin.com/jobs/view/intern-it-ai-engineering-at-generali-malaysia-4403153262?refId=h4J9hFjDRjjPW7bUqRcUZQ%3D%3D&amp;trackingId=WmqITEtGX486sbNH6b%2BYmA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K36" s="32" t="inlineStr">
+      <c r="K36" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-generali-malaysia-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L36" s="32" t="inlineStr">
+      <c r="L36" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-generali-malaysia-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M36" s="32" t="inlineStr"/>
+      <c r="M36" s="36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="32" t="inlineStr">
+      <c r="A37" s="36" t="inlineStr">
         <is>
           <t>linkedin_4402311007</t>
         </is>
       </c>
-      <c r="B37" s="32" t="inlineStr">
+      <c r="B37" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C37" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D37" s="32" t="inlineStr">
+      <c r="C37" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D37" s="36" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E37" s="32" t="inlineStr">
+      <c r="E37" s="36" t="inlineStr">
         <is>
           <t>SAP iXp Intern - Customer Success Engineering, Operations &amp; AI Enablement [Boston]</t>
         </is>
       </c>
-      <c r="F37" s="32" t="inlineStr">
+      <c r="F37" s="36" t="inlineStr">
         <is>
           <t>Burlington, MA</t>
         </is>
       </c>
-      <c r="G37" s="32" t="inlineStr">
+      <c r="G37" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H37" s="32" t="inlineStr">
+      <c r="H37" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 21:40 UTC</t>
         </is>
       </c>
-      <c r="I37" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J37" s="34" t="inlineStr">
+      <c r="I37" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J37" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/sap-ixp-intern-%C2%A0customer-success-engineering-operations-ai-enablement-boston-at-sap-4402311007?refId=ofb0jzd8xWUoUtvr7A%2BwXQ%3D%3D&amp;trackingId=S%2Fo4FvRdeOcn00Jo5DVUBw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K37" s="32" t="inlineStr">
+      <c r="K37" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L37" s="32" t="inlineStr">
+      <c r="L37" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M37" s="32" t="inlineStr"/>
+      <c r="M37" s="36" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="32" t="inlineStr">
+      <c r="A38" s="36" t="inlineStr">
         <is>
           <t>linkedin_4403154707</t>
         </is>
       </c>
-      <c r="B38" s="32" t="inlineStr">
+      <c r="B38" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C38" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D38" s="32" t="inlineStr">
+      <c r="C38" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D38" s="36" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E38" s="32" t="inlineStr">
+      <c r="E38" s="36" t="inlineStr">
         <is>
           <t>Software Engineer Intern, Perception Data</t>
         </is>
       </c>
-      <c r="F38" s="32" t="inlineStr">
+      <c r="F38" s="36" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G38" s="32" t="inlineStr">
+      <c r="G38" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H38" s="32" t="inlineStr">
+      <c r="H38" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 02:21 UTC</t>
         </is>
       </c>
-      <c r="I38" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J38" s="34" t="inlineStr">
+      <c r="I38" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J38" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/software-engineer-intern-perception-data-at-zoox-4403154707?refId=ON4L5FUhksKAgylRRsNllQ%3D%3D&amp;trackingId=1%2F3OkqP%2Bu0PqHp9bXnlS0A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K38" s="32" t="inlineStr">
+      <c r="K38" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L38" s="32" t="inlineStr">
+      <c r="L38" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M38" s="32" t="inlineStr"/>
+      <c r="M38" s="36" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="32" t="inlineStr">
+      <c r="A39" s="36" t="inlineStr">
         <is>
           <t>linkedin_4402947451</t>
         </is>
       </c>
-      <c r="B39" s="32" t="inlineStr">
+      <c r="B39" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C39" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D39" s="32" t="inlineStr">
+      <c r="C39" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D39" s="36" t="inlineStr">
         <is>
           <t>Rubrik</t>
         </is>
       </c>
-      <c r="E39" s="32" t="inlineStr">
+      <c r="E39" s="36" t="inlineStr">
         <is>
           <t>India Benefits &amp; AI Operations Intern</t>
         </is>
       </c>
-      <c r="F39" s="32" t="inlineStr">
+      <c r="F39" s="36" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G39" s="32" t="inlineStr">
+      <c r="G39" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H39" s="32" t="inlineStr">
+      <c r="H39" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 11:40 UTC</t>
         </is>
       </c>
-      <c r="I39" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J39" s="34" t="inlineStr">
+      <c r="I39" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J39" s="38" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/india-benefits-ai-operations-intern-at-rubrik-4402947451?refId=9u2uyUYzyMZimaTtDELDWg%3D%3D&amp;trackingId=BjOmyeYm6McmUpzLwcES9g%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K39" s="32" t="inlineStr">
+      <c r="K39" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-rubrik-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L39" s="32" t="inlineStr">
+      <c r="L39" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-rubrik-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M39" s="32" t="inlineStr"/>
+      <c r="M39" s="36" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="32" t="inlineStr">
+      <c r="A40" s="36" t="inlineStr">
         <is>
           <t>linkedin_4390354006</t>
         </is>
       </c>
-      <c r="B40" s="32" t="inlineStr">
+      <c r="B40" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C40" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D40" s="32" t="inlineStr">
+      <c r="C40" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D40" s="36" t="inlineStr">
         <is>
           <t>Lila Sciences</t>
         </is>
       </c>
-      <c r="E40" s="32" t="inlineStr">
+      <c r="E40" s="36" t="inlineStr">
         <is>
           <t>Intern, Next Gen AI Robotics</t>
         </is>
       </c>
-      <c r="F40" s="32" t="inlineStr">
+      <c r="F40" s="36" t="inlineStr">
         <is>
           <t>Cambridge, MA</t>
         </is>
       </c>
-      <c r="G40" s="32" t="inlineStr">
+      <c r="G40" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H40" s="32" t="inlineStr">
+      <c r="H40" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 10:58 UTC</t>
         </is>
       </c>
-      <c r="I40" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J40" s="34" t="inlineStr">
+      <c r="I40" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J40" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/intern-next-gen-ai-robotics-at-lila-sciences-4390354006?refId=ZoXJQXesL%2FE%2B5EAGGzWfiA%3D%3D&amp;trackingId=FmSMwWhyyIaC52NsDwOCtw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K40" s="32" t="inlineStr">
+      <c r="K40" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-lila-sciences-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L40" s="32" t="inlineStr">
+      <c r="L40" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-lila-sciences-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M40" s="32" t="inlineStr"/>
+      <c r="M40" s="36" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="32" t="inlineStr">
+      <c r="A41" s="36" t="inlineStr">
         <is>
           <t>arbeitnow_ai-venture-development-tech-intern-berlin-100382</t>
         </is>
       </c>
-      <c r="B41" s="32" t="inlineStr">
+      <c r="B41" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 08:58</t>
         </is>
       </c>
-      <c r="C41" s="32" t="inlineStr">
+      <c r="C41" s="36" t="inlineStr">
         <is>
           <t>Arbeitnow</t>
         </is>
       </c>
-      <c r="D41" s="32" t="inlineStr">
+      <c r="D41" s="36" t="inlineStr">
         <is>
           <t>Zeeg</t>
         </is>
       </c>
-      <c r="E41" s="32" t="inlineStr">
+      <c r="E41" s="36" t="inlineStr">
         <is>
           <t>AI &amp; Venture Development Tech Intern (w/m/d)</t>
         </is>
       </c>
-      <c r="F41" s="32" t="inlineStr">
+      <c r="F41" s="36" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="G41" s="32" t="inlineStr">
+      <c r="G41" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H41" s="32" t="inlineStr">
+      <c r="H41" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 10:30 UTC</t>
         </is>
       </c>
-      <c r="I41" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J41" s="34" t="inlineStr">
+      <c r="I41" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J41" s="38" t="inlineStr">
         <is>
           <t>https://www.arbeitnow.com/jobs/companies/zeeg/ai-venture-development-tech-intern-berlin-100382</t>
         </is>
       </c>
-      <c r="K41" s="32" t="inlineStr">
+      <c r="K41" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zeeg-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L41" s="32" t="inlineStr">
+      <c r="L41" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zeeg-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M41" s="32" t="inlineStr"/>
+      <c r="M41" s="36" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="32" t="inlineStr">
+      <c r="A42" s="36" t="inlineStr">
         <is>
           <t>linkedin_4391388054</t>
         </is>
       </c>
-      <c r="B42" s="32" t="inlineStr">
+      <c r="B42" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C42" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D42" s="32" t="inlineStr">
+      <c r="C42" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D42" s="36" t="inlineStr">
         <is>
           <t>Mackenzie Investments</t>
         </is>
       </c>
-      <c r="E42" s="32" t="inlineStr">
+      <c r="E42" s="36" t="inlineStr">
         <is>
           <t>Fall Intern 2026 - Data Science (Toronto Office)</t>
         </is>
       </c>
-      <c r="F42" s="32" t="inlineStr">
+      <c r="F42" s="36" t="inlineStr">
         <is>
           <t>Greater Toronto Area, Canada</t>
         </is>
       </c>
-      <c r="G42" s="32" t="inlineStr">
+      <c r="G42" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H42" s="32" t="inlineStr">
+      <c r="H42" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 14:00 UTC</t>
         </is>
       </c>
-      <c r="I42" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J42" s="34" t="inlineStr">
+      <c r="I42" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J42" s="38" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/fall-intern-2026-data-science-toronto-office-at-mackenzie-investments-4391388054?refId=ay8O%2Bgf7Gtfb1Rpr3XZOhg%3D%3D&amp;trackingId=O%2F%2FJTpCmUhvp4jSfNkV5bg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K42" s="32" t="inlineStr">
+      <c r="K42" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-mackenzie-investments-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L42" s="32" t="inlineStr">
+      <c r="L42" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-mackenzie-investments-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M42" s="32" t="inlineStr"/>
+      <c r="M42" s="36" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="32" t="inlineStr">
+      <c r="A43" s="36" t="inlineStr">
         <is>
           <t>linkedin_4390747937</t>
         </is>
       </c>
-      <c r="B43" s="32" t="inlineStr">
+      <c r="B43" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C43" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D43" s="32" t="inlineStr">
+      <c r="C43" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D43" s="36" t="inlineStr">
         <is>
           <t>BCG X</t>
         </is>
       </c>
-      <c r="E43" s="32" t="inlineStr">
+      <c r="E43" s="36" t="inlineStr">
         <is>
           <t>Visiting Forward Deployed AI Engineer, Internship, Germany - BCG X</t>
         </is>
       </c>
-      <c r="F43" s="32" t="inlineStr">
+      <c r="F43" s="36" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G43" s="32" t="inlineStr">
+      <c r="G43" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H43" s="32" t="inlineStr">
+      <c r="H43" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 13:51 UTC</t>
         </is>
       </c>
-      <c r="I43" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J43" s="34" t="inlineStr">
+      <c r="I43" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J43" s="38" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/visiting-forward-deployed-ai-engineer-internship-germany-bcg-x-at-bcg-x-4390747937?refId=1JxxxPqdlRpkbbaCzu2YGQ%3D%3D&amp;trackingId=7x%2BVQU%2BWOh9IPaVXWJkc5g%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K43" s="32" t="inlineStr">
+      <c r="K43" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bcg-x-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L43" s="32" t="inlineStr">
+      <c r="L43" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bcg-x-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M43" s="32" t="inlineStr"/>
+      <c r="M43" s="36" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="32" t="inlineStr">
+      <c r="A44" s="36" t="inlineStr">
         <is>
           <t>linkedin_4402726053</t>
         </is>
       </c>
-      <c r="B44" s="32" t="inlineStr">
+      <c r="B44" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C44" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D44" s="32" t="inlineStr">
+      <c r="C44" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D44" s="36" t="inlineStr">
         <is>
           <t>targetjobs UK</t>
         </is>
       </c>
-      <c r="E44" s="32" t="inlineStr">
+      <c r="E44" s="36" t="inlineStr">
         <is>
           <t>Internship: AI/ML for Ionospheric TEC Modelling</t>
         </is>
       </c>
-      <c r="F44" s="32" t="inlineStr">
+      <c r="F44" s="36" t="inlineStr">
         <is>
           <t>Reigate, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G44" s="32" t="inlineStr">
+      <c r="G44" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H44" s="32" t="inlineStr">
+      <c r="H44" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 14:25 UTC</t>
         </is>
       </c>
-      <c r="I44" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J44" s="34" t="inlineStr">
+      <c r="I44" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J44" s="38" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/internship-ai-ml-for-ionospheric-tec-modelling-at-targetjobs-uk-4402726053?refId=a1g6hMZsvI1y2Eje2OvLAA%3D%3D&amp;trackingId=IVJSJGE7Non8cohorDs%2F5A%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K44" s="32" t="inlineStr">
+      <c r="K44" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-targetjobs-uk-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L44" s="32" t="inlineStr">
+      <c r="L44" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-targetjobs-uk-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M44" s="32" t="inlineStr"/>
+      <c r="M44" s="36" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="32" t="inlineStr">
+      <c r="A45" s="36" t="inlineStr">
         <is>
           <t>linkedin_4400837114</t>
         </is>
       </c>
-      <c r="B45" s="32" t="inlineStr">
+      <c r="B45" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C45" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D45" s="32" t="inlineStr">
+      <c r="C45" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D45" s="36" t="inlineStr">
         <is>
           <t>Innovexis</t>
         </is>
       </c>
-      <c r="E45" s="32" t="inlineStr">
+      <c r="E45" s="36" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F45" s="32" t="inlineStr">
+      <c r="F45" s="36" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G45" s="32" t="inlineStr">
+      <c r="G45" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H45" s="32" t="inlineStr">
+      <c r="H45" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 13:04 UTC</t>
         </is>
       </c>
-      <c r="I45" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J45" s="34" t="inlineStr">
+      <c r="I45" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J45" s="38" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-innovexis-4400837114?refId=CVM89%2F3%2F%2BshqMJLc4IfFMg%3D%3D&amp;trackingId=j9WpQwI4k1ip7aRr%2Fv5Img%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K45" s="32" t="inlineStr">
+      <c r="K45" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-innovexis-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L45" s="32" t="inlineStr">
+      <c r="L45" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-innovexis-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M45" s="32" t="inlineStr"/>
+      <c r="M45" s="36" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="32" t="inlineStr">
+      <c r="A46" s="36" t="inlineStr">
         <is>
           <t>linkedin_4391074158</t>
         </is>
       </c>
-      <c r="B46" s="32" t="inlineStr">
+      <c r="B46" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C46" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D46" s="32" t="inlineStr">
+      <c r="C46" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D46" s="36" t="inlineStr">
         <is>
           <t>BMW Group</t>
         </is>
       </c>
-      <c r="E46" s="32" t="inlineStr">
+      <c r="E46" s="36" t="inlineStr">
         <is>
           <t>Intern IT Technology, Sales Volume Planning &amp; AI Support (f/m/x)</t>
         </is>
       </c>
-      <c r="F46" s="32" t="inlineStr">
+      <c r="F46" s="36" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G46" s="32" t="inlineStr">
+      <c r="G46" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H46" s="32" t="inlineStr">
+      <c r="H46" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 12:45 UTC</t>
         </is>
       </c>
-      <c r="I46" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J46" s="34" t="inlineStr">
+      <c r="I46" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J46" s="38" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/intern-it-technology-sales-volume-planning-ai-support-f-m-x-at-bmw-group-4391074158?refId=tHG5EqbLn3IDBqsSj%2FsUUg%3D%3D&amp;trackingId=OakOlgDcU0hWTRXcoLe3UA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K46" s="32" t="inlineStr">
+      <c r="K46" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bmw-group-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L46" s="32" t="inlineStr">
+      <c r="L46" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bmw-group-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M46" s="32" t="inlineStr"/>
+      <c r="M46" s="36" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="32" t="inlineStr">
+      <c r="A47" s="36" t="inlineStr">
         <is>
           <t>linkedin_4402725075</t>
         </is>
       </c>
-      <c r="B47" s="32" t="inlineStr">
+      <c r="B47" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C47" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D47" s="32" t="inlineStr">
+      <c r="C47" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D47" s="36" t="inlineStr">
         <is>
           <t>DARE</t>
         </is>
       </c>
-      <c r="E47" s="32" t="inlineStr">
+      <c r="E47" s="36" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F47" s="32" t="inlineStr">
+      <c r="F47" s="36" t="inlineStr">
         <is>
           <t>WP. Kuala Lumpur, Federal Territory of Kuala Lumpur, Malaysia</t>
         </is>
       </c>
-      <c r="G47" s="32" t="inlineStr">
+      <c r="G47" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H47" s="32" t="inlineStr">
+      <c r="H47" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 14:36 UTC</t>
         </is>
       </c>
-      <c r="I47" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J47" s="34" t="inlineStr">
+      <c r="I47" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J47" s="38" t="inlineStr">
         <is>
           <t>https://my.linkedin.com/jobs/view/research-intern-at-dare-4402725075?refId=xbzZXyF6FfcYy036eklDWw%3D%3D&amp;trackingId=QRt5DhbLSINvmHia0jEWIg%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K47" s="32" t="inlineStr">
+      <c r="K47" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dare-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L47" s="32" t="inlineStr">
+      <c r="L47" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dare-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M47" s="32" t="inlineStr"/>
+      <c r="M47" s="36" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="32" t="inlineStr">
+      <c r="A48" s="36" t="inlineStr">
         <is>
           <t>linkedin_4402745391</t>
         </is>
       </c>
-      <c r="B48" s="32" t="inlineStr">
+      <c r="B48" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C48" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D48" s="32" t="inlineStr">
+      <c r="C48" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D48" s="36" t="inlineStr">
         <is>
           <t>Huawei Technologies Research &amp; Development (UK) Ltd</t>
         </is>
       </c>
-      <c r="E48" s="32" t="inlineStr">
+      <c r="E48" s="36" t="inlineStr">
         <is>
           <t>Research Intern - Computer Vision</t>
         </is>
       </c>
-      <c r="F48" s="32" t="inlineStr">
+      <c r="F48" s="36" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G48" s="32" t="inlineStr">
+      <c r="G48" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H48" s="32" t="inlineStr">
+      <c r="H48" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 18:42 UTC</t>
         </is>
       </c>
-      <c r="I48" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J48" s="34" t="inlineStr">
+      <c r="I48" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J48" s="38" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/research-intern-computer-vision-at-huawei-technologies-research-development-uk-ltd-4402745391?refId=rRtCMQFBU%2FNi7vc62x5Nhg%3D%3D&amp;trackingId=%2Bt1We%2BmKhWHyXION%2FWwQVg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K48" s="32" t="inlineStr">
+      <c r="K48" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-huawei-technologies-research-development-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L48" s="32" t="inlineStr">
+      <c r="L48" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-huawei-technologies-research-development-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M48" s="32" t="inlineStr"/>
+      <c r="M48" s="36" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="32" t="inlineStr">
+      <c r="A49" s="36" t="inlineStr">
         <is>
           <t>linkedin_4402366780</t>
         </is>
       </c>
-      <c r="B49" s="32" t="inlineStr">
+      <c r="B49" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C49" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D49" s="32" t="inlineStr">
+      <c r="C49" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D49" s="36" t="inlineStr">
         <is>
           <t>Binance</t>
         </is>
       </c>
-      <c r="E49" s="32" t="inlineStr">
+      <c r="E49" s="36" t="inlineStr">
         <is>
           <t>Binance Accelerator Program - Data Scientist (LLM &amp; Trading)</t>
         </is>
       </c>
-      <c r="F49" s="32" t="inlineStr">
+      <c r="F49" s="36" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G49" s="32" t="inlineStr">
+      <c r="G49" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H49" s="32" t="inlineStr">
+      <c r="H49" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 09:43 UTC</t>
         </is>
       </c>
-      <c r="I49" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J49" s="34" t="inlineStr">
+      <c r="I49" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J49" s="38" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/binance-accelerator-program-data-scientist-llm-trading-at-binance-4402366780?refId=bc%2BXeBTeIKMQJTmlLFwbZQ%3D%3D&amp;trackingId=9UuyRRCEPapWNu6VKdZC5A%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K49" s="32" t="inlineStr">
+      <c r="K49" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-binance-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L49" s="32" t="inlineStr">
+      <c r="L49" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-binance-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M49" s="32" t="inlineStr"/>
+      <c r="M49" s="36" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="32" t="inlineStr">
+      <c r="A50" s="36" t="inlineStr">
         <is>
           <t>linkedin_4382411039</t>
         </is>
       </c>
-      <c r="B50" s="32" t="inlineStr">
+      <c r="B50" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C50" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D50" s="32" t="inlineStr">
+      <c r="C50" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D50" s="36" t="inlineStr">
         <is>
           <t>The Walt Disney Company</t>
         </is>
       </c>
-      <c r="E50" s="32" t="inlineStr">
+      <c r="E50" s="36" t="inlineStr">
         <is>
           <t>Intern, APAC Data Analytics &amp; Insights (Content Analytics) -  Jul to Dec 2026</t>
         </is>
       </c>
-      <c r="F50" s="32" t="inlineStr">
+      <c r="F50" s="36" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G50" s="32" t="inlineStr">
+      <c r="G50" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H50" s="32" t="inlineStr">
+      <c r="H50" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 23:55 UTC</t>
         </is>
       </c>
-      <c r="I50" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J50" s="34" t="inlineStr">
+      <c r="I50" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J50" s="38" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/intern-apac-data-analytics-insights-content-analytics-jul-to-dec-2026-at-the-walt-disney-company-4382411039?refId=JBvXH2fNOamnO4WZI1Y0ew%3D%3D&amp;trackingId=Rs%2FdjczlbLYSYtCwY%2F%2FJyA%3D%3D&amp;position=7&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K50" s="32" t="inlineStr">
+      <c r="K50" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-the-walt-disney-company-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L50" s="32" t="inlineStr">
+      <c r="L50" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-the-walt-disney-company-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M50" s="32" t="inlineStr"/>
+      <c r="M50" s="36" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="32" t="inlineStr">
+      <c r="A51" s="36" t="inlineStr">
         <is>
           <t>linkedin_4402305263</t>
         </is>
       </c>
-      <c r="B51" s="32" t="inlineStr">
+      <c r="B51" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C51" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D51" s="32" t="inlineStr">
+      <c r="C51" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D51" s="36" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E51" s="32" t="inlineStr">
+      <c r="E51" s="36" t="inlineStr">
         <is>
           <t>SAP iXp Intern - Software Developer (Agentic AI &amp; LLM systems)</t>
         </is>
       </c>
-      <c r="F51" s="32" t="inlineStr">
+      <c r="F51" s="36" t="inlineStr">
         <is>
           <t>Montreal, Quebec, Canada</t>
         </is>
       </c>
-      <c r="G51" s="32" t="inlineStr">
+      <c r="G51" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H51" s="32" t="inlineStr">
+      <c r="H51" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 21:40 UTC</t>
         </is>
       </c>
-      <c r="I51" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J51" s="34" t="inlineStr">
+      <c r="I51" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J51" s="38" t="inlineStr">
         <is>
           <t>https://ca.linkedin.com/jobs/view/sap-ixp-intern-software-developer-agentic-ai-llm-systems-at-sap-4402305263?refId=zBXuSSlfFyuxcdEqyfeS8g%3D%3D&amp;trackingId=Imq%2FVHMQWkkoDZp5%2BnATSA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K51" s="32" t="inlineStr">
+      <c r="K51" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L51" s="32" t="inlineStr">
+      <c r="L51" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sap-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M51" s="32" t="inlineStr"/>
+      <c r="M51" s="36" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="32" t="inlineStr">
+      <c r="A52" s="36" t="inlineStr">
         <is>
           <t>linkedin_4400467080</t>
         </is>
       </c>
-      <c r="B52" s="32" t="inlineStr">
+      <c r="B52" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 20:18</t>
         </is>
       </c>
-      <c r="C52" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D52" s="32" t="inlineStr">
+      <c r="C52" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D52" s="36" t="inlineStr">
         <is>
           <t>Saama</t>
         </is>
       </c>
-      <c r="E52" s="32" t="inlineStr">
+      <c r="E52" s="36" t="inlineStr">
         <is>
           <t>Intern for AI CoE</t>
         </is>
       </c>
-      <c r="F52" s="32" t="inlineStr">
+      <c r="F52" s="36" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G52" s="32" t="inlineStr">
+      <c r="G52" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H52" s="32" t="inlineStr">
+      <c r="H52" s="36" t="inlineStr">
         <is>
           <t>2026-04-16 19:45 UTC</t>
         </is>
       </c>
-      <c r="I52" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J52" s="34" t="inlineStr">
+      <c r="I52" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J52" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/intern-for-ai-coe-at-saama-4400467080?refId=7CvDuV2%2BR%2FzyGozq4UNPPw%3D%3D&amp;trackingId=Ls9yWFAC8lVRx8bmapJfLA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K52" s="32" t="inlineStr">
+      <c r="K52" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-saama-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="L52" s="32" t="inlineStr">
+      <c r="L52" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-saama-2026-04-17.pdf</t>
         </is>
       </c>
-      <c r="M52" s="32" t="inlineStr"/>
+      <c r="M52" s="36" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="32" t="inlineStr">
+      <c r="A53" s="36" t="inlineStr">
         <is>
           <t>linkedin_4400873418</t>
         </is>
       </c>
-      <c r="B53" s="32" t="inlineStr">
+      <c r="B53" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C53" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D53" s="32" t="inlineStr">
+      <c r="C53" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D53" s="36" t="inlineStr">
         <is>
           <t>SANOVIO</t>
         </is>
       </c>
-      <c r="E53" s="32" t="inlineStr">
+      <c r="E53" s="36" t="inlineStr">
         <is>
           <t>AI Engineering Intern</t>
         </is>
       </c>
-      <c r="F53" s="32" t="inlineStr">
+      <c r="F53" s="36" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G53" s="32" t="inlineStr">
+      <c r="G53" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H53" s="32" t="inlineStr">
+      <c r="H53" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 00:00 UTC</t>
         </is>
       </c>
-      <c r="I53" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J53" s="34" t="inlineStr">
+      <c r="I53" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J53" s="38" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/ai-engineering-intern-at-sanovio-4400873418?refId=egIYeNLcARu6P6oTIZ%2BHfA%3D%3D&amp;trackingId=c6wZ0DtTzvVZpTRC1l5tYQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K53" s="32" t="inlineStr">
+      <c r="K53" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sanovio-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L53" s="32" t="inlineStr">
+      <c r="L53" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sanovio-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M53" s="32" t="inlineStr"/>
+      <c r="M53" s="36" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="32" t="inlineStr">
+      <c r="A54" s="36" t="inlineStr">
         <is>
           <t>linkedin_4403524251</t>
         </is>
       </c>
-      <c r="B54" s="32" t="inlineStr">
+      <c r="B54" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C54" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D54" s="32" t="inlineStr">
+      <c r="C54" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D54" s="36" t="inlineStr">
         <is>
           <t>Nascent Markets</t>
         </is>
       </c>
-      <c r="E54" s="32" t="inlineStr">
+      <c r="E54" s="36" t="inlineStr">
         <is>
           <t>Agentic Systems Intern (Graduate Level)</t>
         </is>
       </c>
-      <c r="F54" s="32" t="inlineStr">
+      <c r="F54" s="36" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
       </c>
-      <c r="G54" s="32" t="inlineStr">
+      <c r="G54" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H54" s="32" t="inlineStr">
+      <c r="H54" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 19:53 UTC</t>
         </is>
       </c>
-      <c r="I54" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J54" s="34" t="inlineStr">
+      <c r="I54" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J54" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/agentic-systems-intern-graduate-level-at-nascent-markets-4403524251?refId=Ix0g0waARRaNpzTY4LxvsQ%3D%3D&amp;trackingId=RsqyOyJHkanw%2FTeHGUcadA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K54" s="32" t="inlineStr">
+      <c r="K54" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-nascent-markets-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L54" s="32" t="inlineStr">
+      <c r="L54" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-nascent-markets-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M54" s="32" t="inlineStr"/>
+      <c r="M54" s="36" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="32" t="inlineStr">
+      <c r="A55" s="36" t="inlineStr">
         <is>
           <t>linkedin_4402782985</t>
         </is>
       </c>
-      <c r="B55" s="32" t="inlineStr">
+      <c r="B55" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C55" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D55" s="32" t="inlineStr">
+      <c r="C55" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D55" s="36" t="inlineStr">
         <is>
           <t>Axiomatic_AI</t>
         </is>
       </c>
-      <c r="E55" s="32" t="inlineStr">
+      <c r="E55" s="36" t="inlineStr">
         <is>
           <t>Internship - Research Intern (Agentic Learning, Memory &amp; Neurosymbolic Reasoning)</t>
         </is>
       </c>
-      <c r="F55" s="32" t="inlineStr">
+      <c r="F55" s="36" t="inlineStr">
         <is>
           <t>Greater Barcelona Metropolitan Area</t>
         </is>
       </c>
-      <c r="G55" s="32" t="inlineStr">
+      <c r="G55" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H55" s="32" t="inlineStr">
+      <c r="H55" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 05:04 UTC</t>
         </is>
       </c>
-      <c r="I55" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J55" s="34" t="inlineStr">
+      <c r="I55" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J55" s="38" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/internship-research-intern-agentic-learning-memory-neurosymbolic-reasoning-at-axiomatic-ai-4402782985?refId=vm6No12NjZrg2BBV%2BnbuLQ%3D%3D&amp;trackingId=X9FXk%2FBDFftROMNo9Cr20g%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K55" s="32" t="inlineStr">
+      <c r="K55" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-axiomatic-ai-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L55" s="32" t="inlineStr">
+      <c r="L55" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-axiomatic-ai-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M55" s="32" t="inlineStr"/>
+      <c r="M55" s="36" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="32" t="inlineStr">
+      <c r="A56" s="36" t="inlineStr">
         <is>
           <t>linkedin_4309694978</t>
         </is>
       </c>
-      <c r="B56" s="32" t="inlineStr">
+      <c r="B56" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C56" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D56" s="32" t="inlineStr">
+      <c r="C56" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D56" s="36" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E56" s="32" t="inlineStr">
+      <c r="E56" s="36" t="inlineStr">
         <is>
           <t>Graduate Physics Research Intern</t>
         </is>
       </c>
-      <c r="F56" s="32" t="inlineStr">
+      <c r="F56" s="36" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
       </c>
-      <c r="G56" s="32" t="inlineStr">
+      <c r="G56" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H56" s="32" t="inlineStr">
+      <c r="H56" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 17:37 UTC</t>
         </is>
       </c>
-      <c r="I56" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J56" s="34" t="inlineStr">
+      <c r="I56" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J56" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/graduate-physics-research-intern-at-dataannotation-4309694978?refId=hlpC50hTZs9sJFHirXWMSg%3D%3D&amp;trackingId=1E0ixzzpb6MzeHKgxpE3Cw%3D%3D&amp;position=9&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K56" s="32" t="inlineStr">
+      <c r="K56" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L56" s="32" t="inlineStr">
+      <c r="L56" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M56" s="32" t="inlineStr"/>
+      <c r="M56" s="36" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="32" t="inlineStr">
+      <c r="A57" s="36" t="inlineStr">
         <is>
           <t>linkedin_4403562730</t>
         </is>
       </c>
-      <c r="B57" s="32" t="inlineStr">
+      <c r="B57" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C57" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D57" s="32" t="inlineStr">
+      <c r="C57" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D57" s="36" t="inlineStr">
         <is>
           <t>BNM Business Solutions LLP</t>
         </is>
       </c>
-      <c r="E57" s="32" t="inlineStr">
+      <c r="E57" s="36" t="inlineStr">
         <is>
           <t>Data Analyst Internship in Navi Mumbai, Mumbai</t>
         </is>
       </c>
-      <c r="F57" s="32" t="inlineStr">
+      <c r="F57" s="36" t="inlineStr">
         <is>
           <t>Mumbai Metropolitan Region</t>
         </is>
       </c>
-      <c r="G57" s="32" t="inlineStr">
+      <c r="G57" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H57" s="32" t="inlineStr">
+      <c r="H57" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 00:06 UTC</t>
         </is>
       </c>
-      <c r="I57" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J57" s="34" t="inlineStr">
+      <c r="I57" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J57" s="38" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-internship-in-navi-mumbai-mumbai-at-bnm-business-solutions-llp-4403562730?refId=1X9LgKP3%2FAPeJuhZVjyhxw%3D%3D&amp;trackingId=oFY9Z69ZBEGkNtq0cbBOMw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K57" s="32" t="inlineStr">
+      <c r="K57" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bnm-business-solutions-llp-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L57" s="32" t="inlineStr">
+      <c r="L57" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bnm-business-solutions-llp-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M57" s="32" t="inlineStr"/>
+      <c r="M57" s="36" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="32" t="inlineStr">
+      <c r="A58" s="36" t="inlineStr">
         <is>
           <t>linkedin_4309694917</t>
         </is>
       </c>
-      <c r="B58" s="32" t="inlineStr">
+      <c r="B58" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C58" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D58" s="32" t="inlineStr">
+      <c r="C58" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D58" s="36" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E58" s="32" t="inlineStr">
+      <c r="E58" s="36" t="inlineStr">
         <is>
           <t>Graduate Biology Research Intern</t>
         </is>
       </c>
-      <c r="F58" s="32" t="inlineStr">
+      <c r="F58" s="36" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
       </c>
-      <c r="G58" s="32" t="inlineStr">
+      <c r="G58" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H58" s="32" t="inlineStr">
+      <c r="H58" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 17:35 UTC</t>
         </is>
       </c>
-      <c r="I58" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J58" s="34" t="inlineStr">
+      <c r="I58" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J58" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/graduate-biology-research-intern-at-dataannotation-4309694917?refId=hlpC50hTZs9sJFHirXWMSg%3D%3D&amp;trackingId=BM%2FBx4ElnXDk5hEpiM0gzg%3D%3D&amp;position=8&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K58" s="32" t="inlineStr">
+      <c r="K58" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L58" s="32" t="inlineStr">
+      <c r="L58" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dataannotation-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M58" s="32" t="inlineStr"/>
+      <c r="M58" s="36" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="32" t="inlineStr">
+      <c r="A59" s="36" t="inlineStr">
         <is>
           <t>linkedin_4346088677</t>
         </is>
       </c>
-      <c r="B59" s="32" t="inlineStr">
+      <c r="B59" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C59" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D59" s="32" t="inlineStr">
+      <c r="C59" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D59" s="36" t="inlineStr">
         <is>
           <t>revel8</t>
         </is>
       </c>
-      <c r="E59" s="32" t="inlineStr">
+      <c r="E59" s="36" t="inlineStr">
         <is>
           <t>Applied AI Engineer Intern (all genders)</t>
         </is>
       </c>
-      <c r="F59" s="32" t="inlineStr">
+      <c r="F59" s="36" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G59" s="32" t="inlineStr">
+      <c r="G59" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H59" s="32" t="inlineStr">
+      <c r="H59" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 22:38 UTC</t>
         </is>
       </c>
-      <c r="I59" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J59" s="34" t="inlineStr">
+      <c r="I59" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J59" s="38" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/applied-ai-engineer-intern-all-genders-at-revel8-4346088677?refId=FHQDN2Ta3J6B7WhWnDAuhQ%3D%3D&amp;trackingId=Pf%2Ftwn6H5Hrw8BKjPenbSQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K59" s="32" t="inlineStr">
+      <c r="K59" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-revel8-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L59" s="32" t="inlineStr">
+      <c r="L59" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-revel8-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M59" s="32" t="inlineStr"/>
+      <c r="M59" s="36" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="32" t="inlineStr">
+      <c r="A60" s="36" t="inlineStr">
         <is>
           <t>linkedin_4403475387</t>
         </is>
       </c>
-      <c r="B60" s="32" t="inlineStr">
+      <c r="B60" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 08:17</t>
         </is>
       </c>
-      <c r="C60" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D60" s="32" t="inlineStr">
+      <c r="C60" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D60" s="36" t="inlineStr">
         <is>
           <t>Inc42 Media</t>
         </is>
       </c>
-      <c r="E60" s="32" t="inlineStr">
+      <c r="E60" s="36" t="inlineStr">
         <is>
           <t>Operations Intern: Inc42 AI Summit 2026</t>
         </is>
       </c>
-      <c r="F60" s="32" t="inlineStr">
+      <c r="F60" s="36" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G60" s="32" t="inlineStr">
+      <c r="G60" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H60" s="32" t="inlineStr">
+      <c r="H60" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 16:23 UTC</t>
         </is>
       </c>
-      <c r="I60" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J60" s="34" t="inlineStr">
+      <c r="I60" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J60" s="38" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/operations-intern-inc42-ai-summit-2026-at-inc42-media-4403475387?refId=jyI2mJ9xFT%2BmdtkV0OCW0g%3D%3D&amp;trackingId=6sWKnvWNaTU69%2B7bcZNxLg%3D%3D&amp;position=10&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K60" s="32" t="inlineStr">
+      <c r="K60" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-inc42-media-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L60" s="32" t="inlineStr">
+      <c r="L60" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-inc42-media-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M60" s="32" t="inlineStr"/>
+      <c r="M60" s="36" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="32" t="inlineStr">
+      <c r="A61" s="36" t="inlineStr">
         <is>
           <t>linkedin_4403008384</t>
         </is>
       </c>
-      <c r="B61" s="32" t="inlineStr">
+      <c r="B61" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C61" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D61" s="32" t="inlineStr">
+      <c r="C61" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D61" s="36" t="inlineStr">
         <is>
           <t>VEDANTA MOBILITY</t>
         </is>
       </c>
-      <c r="E61" s="32" t="inlineStr">
+      <c r="E61" s="36" t="inlineStr">
         <is>
           <t>Founding Psychology Interns | AI Prototype (Govt Proposal – Dubai)</t>
         </is>
       </c>
-      <c r="F61" s="32" t="inlineStr">
+      <c r="F61" s="36" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G61" s="32" t="inlineStr">
+      <c r="G61" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H61" s="32" t="inlineStr">
+      <c r="H61" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 08:13 UTC</t>
         </is>
       </c>
-      <c r="I61" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J61" s="34" t="inlineStr">
+      <c r="I61" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J61" s="38" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/founding-psychology-interns-ai-prototype-govt-proposal-%E2%80%93-dubai-at-vedanta-mobility-4403008384?refId=moHjgKNH%2BrT9YT5JNnyyqw%3D%3D&amp;trackingId=RUjUOgXLH%2BLJwdPLtKtAMQ%3D%3D&amp;position=13&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K61" s="32" t="inlineStr">
+      <c r="K61" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-vedanta-mobility-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L61" s="32" t="inlineStr">
+      <c r="L61" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-vedanta-mobility-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M61" s="32" t="inlineStr"/>
+      <c r="M61" s="36" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="32" t="inlineStr">
+      <c r="A62" s="36" t="inlineStr">
         <is>
           <t>linkedin_4393616864</t>
         </is>
       </c>
-      <c r="B62" s="32" t="inlineStr">
+      <c r="B62" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C62" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D62" s="32" t="inlineStr">
+      <c r="C62" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D62" s="36" t="inlineStr">
         <is>
           <t>Medidata Solutions</t>
         </is>
       </c>
-      <c r="E62" s="32" t="inlineStr">
+      <c r="E62" s="36" t="inlineStr">
         <is>
           <t>Data Science Intern</t>
         </is>
       </c>
-      <c r="F62" s="32" t="inlineStr">
+      <c r="F62" s="36" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
       </c>
-      <c r="G62" s="32" t="inlineStr">
+      <c r="G62" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H62" s="32" t="inlineStr">
+      <c r="H62" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 13:13 UTC</t>
         </is>
       </c>
-      <c r="I62" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J62" s="34" t="inlineStr">
+      <c r="I62" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J62" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-science-intern-at-medidata-solutions-4393616864?refId=sPMU%2B0UtbDUVjDHc3gXCxA%3D%3D&amp;trackingId=%2BVrdVCzEYQ3jJQvUf4VUtA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K62" s="32" t="inlineStr">
+      <c r="K62" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-medidata-solutions-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L62" s="32" t="inlineStr">
+      <c r="L62" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-medidata-solutions-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M62" s="32" t="inlineStr"/>
+      <c r="M62" s="36" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="32" t="inlineStr">
+      <c r="A63" s="36" t="inlineStr">
         <is>
           <t>linkedin_4403819462</t>
         </is>
       </c>
-      <c r="B63" s="32" t="inlineStr">
+      <c r="B63" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C63" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D63" s="32" t="inlineStr">
+      <c r="C63" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D63" s="36" t="inlineStr">
         <is>
           <t>Calypso Commodities</t>
         </is>
       </c>
-      <c r="E63" s="32" t="inlineStr">
+      <c r="E63" s="36" t="inlineStr">
         <is>
           <t>Trading - Quant &amp; Engineering Intern (Client-Facing)</t>
         </is>
       </c>
-      <c r="F63" s="32" t="inlineStr">
+      <c r="F63" s="36" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="G63" s="32" t="inlineStr">
+      <c r="G63" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H63" s="32" t="inlineStr">
+      <c r="H63" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 12:44 UTC</t>
         </is>
       </c>
-      <c r="I63" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J63" s="34" t="inlineStr">
+      <c r="I63" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J63" s="38" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/trading-quant-engineering-intern-client-facing-at-calypso-commodities-4403819462?refId=wb%2BADKYeCTj8bBBZgf97xw%3D%3D&amp;trackingId=o0ZBUwzyVOiml0tJPOsNww%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K63" s="32" t="inlineStr">
+      <c r="K63" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-calypso-commodities-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L63" s="32" t="inlineStr">
+      <c r="L63" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-calypso-commodities-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M63" s="32" t="inlineStr"/>
+      <c r="M63" s="36" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="32" t="inlineStr">
+      <c r="A64" s="36" t="inlineStr">
         <is>
           <t>linkedin_4355269413</t>
         </is>
       </c>
-      <c r="B64" s="32" t="inlineStr">
+      <c r="B64" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C64" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D64" s="32" t="inlineStr">
+      <c r="C64" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D64" s="36" t="inlineStr">
         <is>
           <t>Temasek</t>
         </is>
       </c>
-      <c r="E64" s="32" t="inlineStr">
+      <c r="E64" s="36" t="inlineStr">
         <is>
           <t>Data Analytics/Science Intern, People Technology (Jun/Jul - Dec 2026)</t>
         </is>
       </c>
-      <c r="F64" s="32" t="inlineStr">
+      <c r="F64" s="36" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G64" s="32" t="inlineStr">
+      <c r="G64" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H64" s="32" t="inlineStr">
+      <c r="H64" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 10:35 UTC</t>
         </is>
       </c>
-      <c r="I64" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J64" s="34" t="inlineStr">
+      <c r="I64" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J64" s="38" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/data-analytics-science-intern-people-technology-jun-jul-dec-2026-at-temasek-4355269413?refId=emjtNEhTXLtOX%2BguWexSsg%3D%3D&amp;trackingId=DPHM%2FIJzKL0emfNJ1LMMoA%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K64" s="32" t="inlineStr">
+      <c r="K64" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-temasek-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L64" s="32" t="inlineStr">
+      <c r="L64" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-temasek-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M64" s="32" t="inlineStr"/>
+      <c r="M64" s="36" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="32" t="inlineStr">
+      <c r="A65" s="36" t="inlineStr">
         <is>
           <t>linkedin_4403065097</t>
         </is>
       </c>
-      <c r="B65" s="32" t="inlineStr">
+      <c r="B65" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C65" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D65" s="32" t="inlineStr">
+      <c r="C65" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D65" s="36" t="inlineStr">
         <is>
           <t>BLACK TREE GAMING LIMITED</t>
         </is>
       </c>
-      <c r="E65" s="32" t="inlineStr">
+      <c r="E65" s="36" t="inlineStr">
         <is>
           <t>Data Scientist (ML)</t>
         </is>
       </c>
-      <c r="F65" s="32" t="inlineStr">
+      <c r="F65" s="36" t="inlineStr">
         <is>
           <t>Greater London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G65" s="32" t="inlineStr">
+      <c r="G65" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H65" s="32" t="inlineStr">
+      <c r="H65" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 14:22 UTC</t>
         </is>
       </c>
-      <c r="I65" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J65" s="34" t="inlineStr">
+      <c r="I65" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J65" s="38" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/data-scientist-ml-at-black-tree-gaming-limited-4403065097?refId=X9Gb9UkVv%2BJtfDRc0dJPwA%3D%3D&amp;trackingId=Mfl%2BC%2FBN9DJehDmug19dGA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K65" s="32" t="inlineStr">
+      <c r="K65" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-black-tree-gaming-limited-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L65" s="32" t="inlineStr">
+      <c r="L65" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-black-tree-gaming-limited-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M65" s="32" t="inlineStr"/>
+      <c r="M65" s="36" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="32" t="inlineStr">
+      <c r="A66" s="36" t="inlineStr">
         <is>
           <t>linkedin_4291533663</t>
         </is>
       </c>
-      <c r="B66" s="32" t="inlineStr">
+      <c r="B66" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C66" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D66" s="32" t="inlineStr">
+      <c r="C66" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D66" s="36" t="inlineStr">
         <is>
           <t>McKinsey &amp; Company</t>
         </is>
       </c>
-      <c r="E66" s="32" t="inlineStr">
+      <c r="E66" s="36" t="inlineStr">
         <is>
           <t>Praktikum als Fellow Intern - Tech &amp; AI (m/w/d)</t>
         </is>
       </c>
-      <c r="F66" s="32" t="inlineStr">
+      <c r="F66" s="36" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G66" s="32" t="inlineStr">
+      <c r="G66" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H66" s="32" t="inlineStr">
+      <c r="H66" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 09:49 UTC</t>
         </is>
       </c>
-      <c r="I66" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J66" s="34" t="inlineStr">
+      <c r="I66" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J66" s="38" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/praktikum-als-fellow-intern-tech-ai-m-w-d-at-mckinsey-company-4291533663?refId=UmiOr88gcWDNbqipJy2ZTg%3D%3D&amp;trackingId=UvtRxMXKlReoOEeGgMaEfA%3D%3D&amp;position=4&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K66" s="32" t="inlineStr">
+      <c r="K66" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-mckinsey-company-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L66" s="32" t="inlineStr">
+      <c r="L66" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-mckinsey-company-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M66" s="32" t="inlineStr"/>
+      <c r="M66" s="36" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="32" t="inlineStr">
+      <c r="A67" s="36" t="inlineStr">
         <is>
           <t>linkedin_4336838608</t>
         </is>
       </c>
-      <c r="B67" s="32" t="inlineStr">
+      <c r="B67" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C67" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D67" s="32" t="inlineStr">
+      <c r="C67" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D67" s="36" t="inlineStr">
         <is>
           <t>Sendbird</t>
         </is>
       </c>
-      <c r="E67" s="32" t="inlineStr">
+      <c r="E67" s="36" t="inlineStr">
         <is>
           <t>AI Agent Engineer, Intern</t>
         </is>
       </c>
-      <c r="F67" s="32" t="inlineStr">
+      <c r="F67" s="36" t="inlineStr">
         <is>
           <t>Seoul, Seoul, South Korea</t>
         </is>
       </c>
-      <c r="G67" s="32" t="inlineStr">
+      <c r="G67" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H67" s="32" t="inlineStr">
+      <c r="H67" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 13:46 UTC</t>
         </is>
       </c>
-      <c r="I67" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J67" s="34" t="inlineStr">
+      <c r="I67" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J67" s="38" t="inlineStr">
         <is>
           <t>https://kr.linkedin.com/jobs/view/ai-agent-engineer-intern-at-sendbird-4336838608?refId=%2F1qLChSVn3giUiiNusHaIQ%3D%3D&amp;trackingId=l6mUUvSfC97HjoyrA8uuqg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K67" s="32" t="inlineStr">
+      <c r="K67" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sendbird-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L67" s="32" t="inlineStr">
+      <c r="L67" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sendbird-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M67" s="32" t="inlineStr"/>
+      <c r="M67" s="36" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="32" t="inlineStr">
+      <c r="A68" s="36" t="inlineStr">
         <is>
           <t>linkedin_4372783510</t>
         </is>
       </c>
-      <c r="B68" s="32" t="inlineStr">
+      <c r="B68" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C68" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D68" s="32" t="inlineStr">
+      <c r="C68" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D68" s="36" t="inlineStr">
         <is>
           <t>42dot</t>
         </is>
       </c>
-      <c r="E68" s="32" t="inlineStr">
+      <c r="E68" s="36" t="inlineStr">
         <is>
           <t>[MS/PhD Intern] AI Engineer (정규직 전환형)</t>
         </is>
       </c>
-      <c r="F68" s="32" t="inlineStr">
+      <c r="F68" s="36" t="inlineStr">
         <is>
           <t>Seongnam, Gyeonggi, South Korea</t>
         </is>
       </c>
-      <c r="G68" s="32" t="inlineStr">
+      <c r="G68" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H68" s="32" t="inlineStr">
+      <c r="H68" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 15:08 UTC</t>
         </is>
       </c>
-      <c r="I68" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J68" s="34" t="inlineStr">
+      <c r="I68" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J68" s="38" t="inlineStr">
         <is>
           <t>https://kr.linkedin.com/jobs/view/ms-phd-intern-ai-engineer-%EC%A0%95%EA%B7%9C%EC%A7%81-%EC%A0%84%ED%99%98%ED%98%95-at-42dot-4372783510?refId=%2F1qLChSVn3giUiiNusHaIQ%3D%3D&amp;trackingId=TVYs5RWI1wgPuuVRiBioUA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K68" s="32" t="inlineStr">
+      <c r="K68" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-42dot-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L68" s="32" t="inlineStr">
+      <c r="L68" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-42dot-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M68" s="32" t="inlineStr"/>
+      <c r="M68" s="36" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="32" t="inlineStr">
+      <c r="A69" s="36" t="inlineStr">
         <is>
           <t>linkedin_4402753102</t>
         </is>
       </c>
-      <c r="B69" s="32" t="inlineStr">
+      <c r="B69" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C69" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D69" s="32" t="inlineStr">
+      <c r="C69" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D69" s="36" t="inlineStr">
         <is>
           <t>Five9</t>
         </is>
       </c>
-      <c r="E69" s="32" t="inlineStr">
+      <c r="E69" s="36" t="inlineStr">
         <is>
           <t>Software Developer AI Insights Intern</t>
         </is>
       </c>
-      <c r="F69" s="32" t="inlineStr">
+      <c r="F69" s="36" t="inlineStr">
         <is>
           <t>San Ramon, CA</t>
         </is>
       </c>
-      <c r="G69" s="32" t="inlineStr">
+      <c r="G69" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H69" s="32" t="inlineStr">
+      <c r="H69" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 20:56 UTC</t>
         </is>
       </c>
-      <c r="I69" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J69" s="34" t="inlineStr">
+      <c r="I69" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J69" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/software-developer-ai-insights-intern-at-five9-4402753102?refId=%2FiKmLsIvYp2TclUyf8MJwg%3D%3D&amp;trackingId=X2UMBr3jE86J9JmPv42B2w%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K69" s="32" t="inlineStr">
+      <c r="K69" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-five9-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L69" s="32" t="inlineStr">
+      <c r="L69" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-five9-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M69" s="32" t="inlineStr"/>
+      <c r="M69" s="36" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="32" t="inlineStr">
+      <c r="A70" s="36" t="inlineStr">
         <is>
           <t>linkedin_4403519373</t>
         </is>
       </c>
-      <c r="B70" s="32" t="inlineStr">
+      <c r="B70" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 19:59</t>
         </is>
       </c>
-      <c r="C70" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
+      <c r="C70" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D70" s="36" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E70" s="32" t="inlineStr">
+      <c r="E70" s="36" t="inlineStr">
         <is>
           <t>PhD Research Intern, Physical AI in Perception</t>
         </is>
       </c>
-      <c r="F70" s="32" t="inlineStr">
+      <c r="F70" s="36" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G70" s="32" t="inlineStr">
+      <c r="G70" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H70" s="32" t="inlineStr">
+      <c r="H70" s="36" t="inlineStr">
         <is>
           <t>2026-04-17 20:07 UTC</t>
         </is>
       </c>
-      <c r="I70" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J70" s="34" t="inlineStr">
+      <c r="I70" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J70" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-physical-ai-in-perception-at-zoox-4403519373?refId=LChV34e%2Bd7cvBpZ%2FbJAZjw%3D%3D&amp;trackingId=vlvuJ54NQfvZvNY3pNGqNw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K70" s="32" t="inlineStr">
+      <c r="K70" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="L70" s="32" t="inlineStr">
+      <c r="L70" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-18.pdf</t>
         </is>
       </c>
-      <c r="M70" s="32" t="inlineStr"/>
+      <c r="M70" s="36" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="32" t="inlineStr">
+      <c r="A71" s="36" t="inlineStr">
         <is>
           <t>linkedin_4403095692</t>
         </is>
       </c>
-      <c r="B71" s="32" t="inlineStr">
+      <c r="B71" s="36" t="inlineStr">
         <is>
           <t>2026-04-19 08:24</t>
         </is>
       </c>
-      <c r="C71" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
+      <c r="C71" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D71" s="36" t="inlineStr">
         <is>
           <t>Starrycraze Technology</t>
         </is>
       </c>
-      <c r="E71" s="32" t="inlineStr">
+      <c r="E71" s="36" t="inlineStr">
         <is>
           <t>Data Scientist Intern</t>
         </is>
       </c>
-      <c r="F71" s="32" t="inlineStr">
+      <c r="F71" s="36" t="inlineStr">
         <is>
           <t>Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G71" s="32" t="inlineStr">
+      <c r="G71" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H71" s="32" t="inlineStr">
+      <c r="H71" s="36" t="inlineStr">
         <is>
           <t>2026-04-19 04:58 UTC</t>
         </is>
       </c>
-      <c r="I71" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J71" s="34" t="inlineStr">
+      <c r="I71" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J71" s="38" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/data-scientist-intern-at-starrycraze-technology-4403095692?refId=TVQyGaR78N78VqNo32HHeA%3D%3D&amp;trackingId=iTU%2BdVDc304eRUiD2UiVkA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K71" s="32" t="inlineStr">
+      <c r="K71" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-starrycraze-technology-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L71" s="32" t="inlineStr">
+      <c r="L71" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-starrycraze-technology-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M71" s="32" t="inlineStr"/>
+      <c r="M71" s="36" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="32" t="inlineStr">
+      <c r="A72" s="36" t="inlineStr">
         <is>
           <t>linkedin_4403848986</t>
         </is>
       </c>
-      <c r="B72" s="32" t="inlineStr">
+      <c r="B72" s="36" t="inlineStr">
         <is>
           <t>2026-04-19 08:24</t>
         </is>
       </c>
-      <c r="C72" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D72" s="32" t="inlineStr">
+      <c r="C72" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D72" s="36" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E72" s="32" t="inlineStr">
+      <c r="E72" s="36" t="inlineStr">
         <is>
           <t>PhD Research Intern, Offline Driving Intelligence</t>
         </is>
       </c>
-      <c r="F72" s="32" t="inlineStr">
+      <c r="F72" s="36" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G72" s="32" t="inlineStr">
+      <c r="G72" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H72" s="32" t="inlineStr">
+      <c r="H72" s="36" t="inlineStr">
         <is>
           <t>2026-04-19 02:06 UTC</t>
         </is>
       </c>
-      <c r="I72" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J72" s="34" t="inlineStr">
+      <c r="I72" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J72" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-offline-driving-intelligence-at-zoox-4403848986?refId=5ydRxcXuf5aHqLJVjey87Q%3D%3D&amp;trackingId=FWtGym5%2BhCmPjiMPBVYS7w%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K72" s="32" t="inlineStr">
+      <c r="K72" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L72" s="32" t="inlineStr">
+      <c r="L72" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M72" s="32" t="inlineStr"/>
+      <c r="M72" s="36" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="32" t="inlineStr">
+      <c r="A73" s="36" t="inlineStr">
         <is>
           <t>linkedin_4371758156</t>
         </is>
       </c>
-      <c r="B73" s="32" t="inlineStr">
+      <c r="B73" s="36" t="inlineStr">
         <is>
           <t>2026-04-19 08:24</t>
         </is>
       </c>
-      <c r="C73" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
+      <c r="C73" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D73" s="36" t="inlineStr">
         <is>
           <t>Lowe's India</t>
         </is>
       </c>
-      <c r="E73" s="32" t="inlineStr">
+      <c r="E73" s="36" t="inlineStr">
         <is>
           <t>DIH Intern, Data Engineering</t>
         </is>
       </c>
-      <c r="F73" s="32" t="inlineStr">
+      <c r="F73" s="36" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G73" s="32" t="inlineStr">
+      <c r="G73" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H73" s="32" t="inlineStr">
+      <c r="H73" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 10:48 UTC</t>
         </is>
       </c>
-      <c r="I73" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J73" s="34" t="inlineStr">
+      <c r="I73" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J73" s="38" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/dih-intern-data-engineering-at-lowe-s-india-4371758156?refId=1mgTdTTgR1UncTTJ8Ts5OA%3D%3D&amp;trackingId=7HYWBNU0zclnyp9qIoW2Jw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K73" s="32" t="inlineStr">
+      <c r="K73" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-lowes-india-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L73" s="32" t="inlineStr">
+      <c r="L73" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-lowes-india-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M73" s="32" t="inlineStr"/>
+      <c r="M73" s="36" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="32" t="inlineStr">
+      <c r="A74" s="36" t="inlineStr">
         <is>
           <t>linkedin_4327191639</t>
         </is>
       </c>
-      <c r="B74" s="32" t="inlineStr">
+      <c r="B74" s="36" t="inlineStr">
         <is>
           <t>2026-04-19 08:24</t>
         </is>
       </c>
-      <c r="C74" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
+      <c r="C74" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D74" s="36" t="inlineStr">
         <is>
           <t>Whatnot</t>
         </is>
       </c>
-      <c r="E74" s="32" t="inlineStr">
+      <c r="E74" s="36" t="inlineStr">
         <is>
           <t>Data Scientist, Product Analytics</t>
         </is>
       </c>
-      <c r="F74" s="32" t="inlineStr">
+      <c r="F74" s="36" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="G74" s="32" t="inlineStr">
+      <c r="G74" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H74" s="32" t="inlineStr">
+      <c r="H74" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 13:22 UTC</t>
         </is>
       </c>
-      <c r="I74" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J74" s="34" t="inlineStr">
+      <c r="I74" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J74" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-scientist-product-analytics-at-whatnot-4327191639?refId=mfQJnJ6mRr3La1qB9YnNGA%3D%3D&amp;trackingId=k4mLJmsHD9wYHSZlc4RA%2Fw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K74" s="32" t="inlineStr">
+      <c r="K74" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-whatnot-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L74" s="32" t="inlineStr">
+      <c r="L74" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-whatnot-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M74" s="32" t="inlineStr"/>
+      <c r="M74" s="36" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="32" t="inlineStr">
+      <c r="A75" s="36" t="inlineStr">
         <is>
           <t>linkedin_4391150969</t>
         </is>
       </c>
-      <c r="B75" s="32" t="inlineStr">
+      <c r="B75" s="36" t="inlineStr">
         <is>
           <t>2026-04-19 19:54</t>
         </is>
       </c>
-      <c r="C75" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D75" s="32" t="inlineStr">
+      <c r="C75" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D75" s="36" t="inlineStr">
         <is>
           <t>Cartesian</t>
         </is>
       </c>
-      <c r="E75" s="32" t="inlineStr">
+      <c r="E75" s="36" t="inlineStr">
         <is>
           <t>Software Engineering Intern (Summer/Fall 2026)</t>
         </is>
       </c>
-      <c r="F75" s="32" t="inlineStr">
+      <c r="F75" s="36" t="inlineStr">
         <is>
           <t>Cambridge, MA</t>
         </is>
       </c>
-      <c r="G75" s="32" t="inlineStr">
+      <c r="G75" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H75" s="32" t="inlineStr">
+      <c r="H75" s="36" t="inlineStr">
         <is>
           <t>2026-04-18 23:08 UTC</t>
         </is>
       </c>
-      <c r="I75" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J75" s="34" t="inlineStr">
+      <c r="I75" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J75" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/software-engineering-intern-summer-fall-2026-at-cartesian-4391150969?refId=rXBEPoDKoHwUW%2BMU3mmCWA%3D%3D&amp;trackingId=03L6jyuSNG6Edf0%2FeXbj4w%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K75" s="32" t="inlineStr">
+      <c r="K75" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-cartesian-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L75" s="32" t="inlineStr">
+      <c r="L75" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-cartesian-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M75" s="32" t="inlineStr"/>
+      <c r="M75" s="36" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="32" t="inlineStr">
+      <c r="A76" s="36" t="inlineStr">
         <is>
           <t>linkedin_4401268516</t>
         </is>
       </c>
-      <c r="B76" s="32" t="inlineStr">
+      <c r="B76" s="36" t="inlineStr">
         <is>
           <t>2026-04-19 19:54</t>
         </is>
       </c>
-      <c r="C76" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D76" s="32" t="inlineStr">
+      <c r="C76" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D76" s="36" t="inlineStr">
         <is>
           <t>Joveo Ai</t>
         </is>
       </c>
-      <c r="E76" s="32" t="inlineStr">
+      <c r="E76" s="36" t="inlineStr">
         <is>
           <t>Generative AI Intern</t>
         </is>
       </c>
-      <c r="F76" s="32" t="inlineStr">
+      <c r="F76" s="36" t="inlineStr">
         <is>
           <t>Bangalore Urban, Karnataka, India</t>
         </is>
       </c>
-      <c r="G76" s="32" t="inlineStr">
+      <c r="G76" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H76" s="32" t="inlineStr">
+      <c r="H76" s="36" t="inlineStr">
         <is>
           <t>2026-04-19 16:33 UTC</t>
         </is>
       </c>
-      <c r="I76" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J76" s="34" t="inlineStr">
+      <c r="I76" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J76" s="38" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/generative-ai-intern-at-joveo-ai-4401268516?refId=AMRRU4%2FYzAhlhe1ad%2FYa%2Fw%3D%3D&amp;trackingId=lRpwTcswbLSpxr57DNyAvA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K76" s="32" t="inlineStr">
+      <c r="K76" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-joveo-ai-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L76" s="32" t="inlineStr">
+      <c r="L76" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-joveo-ai-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M76" s="32" t="inlineStr"/>
+      <c r="M76" s="36" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="32" t="inlineStr">
+      <c r="A77" s="36" t="inlineStr">
         <is>
           <t>linkedin_4381330362</t>
         </is>
       </c>
-      <c r="B77" s="32" t="inlineStr">
+      <c r="B77" s="36" t="inlineStr">
         <is>
           <t>2026-04-19 19:54</t>
         </is>
       </c>
-      <c r="C77" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D77" s="32" t="inlineStr">
+      <c r="C77" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D77" s="36" t="inlineStr">
         <is>
           <t>Shopee</t>
         </is>
       </c>
-      <c r="E77" s="32" t="inlineStr">
+      <c r="E77" s="36" t="inlineStr">
         <is>
           <t>Data Analyst Intern - Product Analysis, Regional Operations (Summer 2026)</t>
         </is>
       </c>
-      <c r="F77" s="32" t="inlineStr">
+      <c r="F77" s="36" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G77" s="32" t="inlineStr">
+      <c r="G77" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H77" s="32" t="inlineStr">
+      <c r="H77" s="36" t="inlineStr">
         <is>
           <t>2026-04-19 13:47 UTC</t>
         </is>
       </c>
-      <c r="I77" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J77" s="34" t="inlineStr">
+      <c r="I77" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J77" s="38" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/data-analyst-intern-product-analysis-regional-operations-summer-2026-at-shopee-4381330362?refId=Mf9npsmRtScOZbkuOI7S2Q%3D%3D&amp;trackingId=qCnW3Di6Gcyx48NhCTpBLw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K77" s="32" t="inlineStr">
+      <c r="K77" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-shopee-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L77" s="32" t="inlineStr">
+      <c r="L77" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-shopee-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M77" s="32" t="inlineStr"/>
+      <c r="M77" s="36" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="32" t="inlineStr">
+      <c r="A78" s="36" t="inlineStr">
         <is>
           <t>linkedin_4355297667</t>
         </is>
       </c>
-      <c r="B78" s="32" t="inlineStr">
+      <c r="B78" s="36" t="inlineStr">
         <is>
           <t>2026-04-19 19:54</t>
         </is>
       </c>
-      <c r="C78" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
+      <c r="C78" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D78" s="36" t="inlineStr">
         <is>
           <t>Temasek</t>
         </is>
       </c>
-      <c r="E78" s="32" t="inlineStr">
+      <c r="E78" s="36" t="inlineStr">
         <is>
           <t>Policy &amp; Research Intern, Workforce 4.0 (Jun/Jul - Dec 2026)</t>
         </is>
       </c>
-      <c r="F78" s="32" t="inlineStr">
+      <c r="F78" s="36" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G78" s="32" t="inlineStr">
+      <c r="G78" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H78" s="32" t="inlineStr">
+      <c r="H78" s="36" t="inlineStr">
         <is>
           <t>2026-04-19 10:08 UTC</t>
         </is>
       </c>
-      <c r="I78" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J78" s="34" t="inlineStr">
+      <c r="I78" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J78" s="38" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/policy-research-intern-workforce-4-0-jun-jul-dec-2026-at-temasek-4355297667?refId=SZF%2BVbNMCE0h7Rloqm3lXQ%3D%3D&amp;trackingId=vK2euiis8CytJt264fhurw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K78" s="32" t="inlineStr">
+      <c r="K78" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-temasek-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L78" s="32" t="inlineStr">
+      <c r="L78" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-temasek-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M78" s="32" t="inlineStr"/>
+      <c r="M78" s="36" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="32" t="inlineStr">
+      <c r="A79" s="36" t="inlineStr">
         <is>
           <t>linkedin_4336865392</t>
         </is>
       </c>
-      <c r="B79" s="32" t="inlineStr">
+      <c r="B79" s="36" t="inlineStr">
         <is>
           <t>2026-04-19 19:54</t>
         </is>
       </c>
-      <c r="C79" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
+      <c r="C79" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D79" s="36" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E79" s="32" t="inlineStr">
+      <c r="E79" s="36" t="inlineStr">
         <is>
           <t>PhD Research Intern, Visual Object Understanding</t>
         </is>
       </c>
-      <c r="F79" s="32" t="inlineStr">
+      <c r="F79" s="36" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G79" s="32" t="inlineStr">
+      <c r="G79" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H79" s="32" t="inlineStr">
+      <c r="H79" s="36" t="inlineStr">
         <is>
           <t>2026-04-19 10:27 UTC</t>
         </is>
       </c>
-      <c r="I79" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J79" s="34" t="inlineStr">
+      <c r="I79" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J79" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-visual-object-understanding-at-zoox-4336865392?refId=gztZfDsooz7GE2iA6mPxjQ%3D%3D&amp;trackingId=%2F1kV0X%2F8hKCPhv0kD05v5Q%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K79" s="32" t="inlineStr">
+      <c r="K79" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="L79" s="32" t="inlineStr">
+      <c r="L79" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-19.pdf</t>
         </is>
       </c>
-      <c r="M79" s="32" t="inlineStr"/>
+      <c r="M79" s="36" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="32" t="inlineStr">
+      <c r="A80" s="36" t="inlineStr">
         <is>
           <t>linkedin_4404025051</t>
         </is>
       </c>
-      <c r="B80" s="32" t="inlineStr">
+      <c r="B80" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 09:16</t>
         </is>
       </c>
-      <c r="C80" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D80" s="32" t="inlineStr">
+      <c r="C80" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D80" s="36" t="inlineStr">
         <is>
           <t>Dassault Systèmes</t>
         </is>
       </c>
-      <c r="E80" s="32" t="inlineStr">
+      <c r="E80" s="36" t="inlineStr">
         <is>
           <t>INTERNSHIP: Data Science (6mo June 2026)</t>
         </is>
       </c>
-      <c r="F80" s="32" t="inlineStr">
+      <c r="F80" s="36" t="inlineStr">
         <is>
           <t>Waltham, MA</t>
         </is>
       </c>
-      <c r="G80" s="32" t="inlineStr">
+      <c r="G80" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H80" s="32" t="inlineStr">
+      <c r="H80" s="36" t="inlineStr">
         <is>
           <t>2026-04-19 23:38 UTC</t>
         </is>
       </c>
-      <c r="I80" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J80" s="34" t="inlineStr">
+      <c r="I80" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J80" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/internship-data-science-6mo-june-2026-at-dassault-syst%C3%A8mes-4404025051?refId=S4wy0FwbzbiuPwYYk2m0dw%3D%3D&amp;trackingId=RGARwF5XkYgBTfpY7DrrZg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K80" s="32" t="inlineStr">
+      <c r="K80" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-dassault-systèmes-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L80" s="32" t="inlineStr">
+      <c r="L80" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-dassault-systèmes-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M80" s="32" t="inlineStr"/>
+      <c r="M80" s="36" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="32" t="inlineStr">
+      <c r="A81" s="36" t="inlineStr">
         <is>
           <t>linkedin_4403368519</t>
         </is>
       </c>
-      <c r="B81" s="32" t="inlineStr">
+      <c r="B81" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 09:16</t>
         </is>
       </c>
-      <c r="C81" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
+      <c r="C81" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D81" s="36" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="E81" s="32" t="inlineStr">
+      <c r="E81" s="36" t="inlineStr">
         <is>
           <t>Risk Control Algorithm Engineer Intern</t>
         </is>
       </c>
-      <c r="F81" s="32" t="inlineStr">
+      <c r="F81" s="36" t="inlineStr">
         <is>
           <t>Hong Kong, Hong Kong SAR</t>
         </is>
       </c>
-      <c r="G81" s="32" t="inlineStr">
+      <c r="G81" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H81" s="32" t="inlineStr">
+      <c r="H81" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 08:20 UTC</t>
         </is>
       </c>
-      <c r="I81" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J81" s="34" t="inlineStr">
+      <c r="I81" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J81" s="38" t="inlineStr">
         <is>
           <t>https://hk.linkedin.com/jobs/view/risk-control-algorithm-engineer-intern-at-bybit-4403368519?refId=9jFaGeHrGBqPLrXTIfcNwA%3D%3D&amp;trackingId=glTg%2F1p9B2dY4YX59MH9DA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K81" s="32" t="inlineStr">
+      <c r="K81" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bybit-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L81" s="32" t="inlineStr">
+      <c r="L81" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bybit-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M81" s="32" t="inlineStr"/>
+      <c r="M81" s="36" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="32" t="inlineStr">
+      <c r="A82" s="36" t="inlineStr">
         <is>
           <t>linkedin_4403320381</t>
         </is>
       </c>
-      <c r="B82" s="32" t="inlineStr">
+      <c r="B82" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 09:16</t>
         </is>
       </c>
-      <c r="C82" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
+      <c r="C82" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D82" s="36" t="inlineStr">
         <is>
           <t>Digitomics AI</t>
         </is>
       </c>
-      <c r="E82" s="32" t="inlineStr">
+      <c r="E82" s="36" t="inlineStr">
         <is>
           <t>AI Engineering Intern</t>
         </is>
       </c>
-      <c r="F82" s="32" t="inlineStr">
+      <c r="F82" s="36" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G82" s="32" t="inlineStr">
+      <c r="G82" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H82" s="32" t="inlineStr">
+      <c r="H82" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 08:43 UTC</t>
         </is>
       </c>
-      <c r="I82" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J82" s="34" t="inlineStr">
+      <c r="I82" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J82" s="38" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/ai-engineering-intern-at-digitomics-ai-4403320381?refId=0fRwalKs7ueOf%2FH7m6U26Q%3D%3D&amp;trackingId=zbHZrmgemJdB%2BlQYFw7geg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K82" s="32" t="inlineStr">
+      <c r="K82" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-digitomics-ai-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L82" s="32" t="inlineStr">
+      <c r="L82" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-digitomics-ai-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M82" s="32" t="inlineStr"/>
+      <c r="M82" s="36" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="32" t="inlineStr">
+      <c r="A83" s="36" t="inlineStr">
         <is>
           <t>linkedin_4403358236</t>
         </is>
       </c>
-      <c r="B83" s="32" t="inlineStr">
+      <c r="B83" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 09:16</t>
         </is>
       </c>
-      <c r="C83" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D83" s="32" t="inlineStr">
+      <c r="C83" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D83" s="36" t="inlineStr">
         <is>
           <t>InMobi</t>
         </is>
       </c>
-      <c r="E83" s="32" t="inlineStr">
+      <c r="E83" s="36" t="inlineStr">
         <is>
           <t>Intern - Industrial Trainee</t>
         </is>
       </c>
-      <c r="F83" s="32" t="inlineStr">
+      <c r="F83" s="36" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G83" s="32" t="inlineStr">
+      <c r="G83" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H83" s="32" t="inlineStr">
+      <c r="H83" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 06:44 UTC</t>
         </is>
       </c>
-      <c r="I83" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J83" s="34" t="inlineStr">
+      <c r="I83" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J83" s="38" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/intern-industrial-trainee-at-inmobi-4403358236?refId=Hz8z0MLJ0gvG3WjNfG9q9Q%3D%3D&amp;trackingId=uO3LmXVsff1dJma3y3w5Gg%3D%3D&amp;position=8&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K83" s="32" t="inlineStr">
+      <c r="K83" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-inmobi-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L83" s="32" t="inlineStr">
+      <c r="L83" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-inmobi-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M83" s="32" t="inlineStr"/>
+      <c r="M83" s="36" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="32" t="inlineStr">
+      <c r="A84" s="36" t="inlineStr">
         <is>
           <t>linkedin_4403359204</t>
         </is>
       </c>
-      <c r="B84" s="32" t="inlineStr">
+      <c r="B84" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 09:16</t>
         </is>
       </c>
-      <c r="C84" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D84" s="32" t="inlineStr">
+      <c r="C84" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D84" s="36" t="inlineStr">
         <is>
           <t>TakedaPharmaceutical Nordics AB</t>
         </is>
       </c>
-      <c r="E84" s="32" t="inlineStr">
+      <c r="E84" s="36" t="inlineStr">
         <is>
           <t>Senior Data Scientist</t>
         </is>
       </c>
-      <c r="F84" s="32" t="inlineStr">
+      <c r="F84" s="36" t="inlineStr">
         <is>
           <t>Boston, MA</t>
         </is>
       </c>
-      <c r="G84" s="32" t="inlineStr">
+      <c r="G84" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H84" s="32" t="inlineStr">
+      <c r="H84" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 06:45 UTC</t>
         </is>
       </c>
-      <c r="I84" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J84" s="34" t="inlineStr">
+      <c r="I84" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J84" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/senior-data-scientist-at-takedapharmaceutical-nordics-ab-4403359204?refId=S4wy0FwbzbiuPwYYk2m0dw%3D%3D&amp;trackingId=zfL5isOE6jcFxwuJQPpkyA%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K84" s="32" t="inlineStr">
+      <c r="K84" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-takedapharmaceutical-nordics-ab-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L84" s="32" t="inlineStr">
+      <c r="L84" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-takedapharmaceutical-nordics-ab-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M84" s="32" t="inlineStr"/>
+      <c r="M84" s="36" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="32" t="inlineStr">
+      <c r="A85" s="36" t="inlineStr">
         <is>
           <t>linkedin_4403353339</t>
         </is>
       </c>
-      <c r="B85" s="32" t="inlineStr">
+      <c r="B85" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 09:16</t>
         </is>
       </c>
-      <c r="C85" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D85" s="32" t="inlineStr">
+      <c r="C85" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D85" s="36" t="inlineStr">
         <is>
           <t>Kuku</t>
         </is>
       </c>
-      <c r="E85" s="32" t="inlineStr">
+      <c r="E85" s="36" t="inlineStr">
         <is>
           <t>AI Intern</t>
         </is>
       </c>
-      <c r="F85" s="32" t="inlineStr">
+      <c r="F85" s="36" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G85" s="32" t="inlineStr">
+      <c r="G85" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H85" s="32" t="inlineStr">
+      <c r="H85" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 07:10 UTC</t>
         </is>
       </c>
-      <c r="I85" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J85" s="34" t="inlineStr">
+      <c r="I85" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J85" s="38" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/ai-intern-at-kuku-4403353339?refId=Hz8z0MLJ0gvG3WjNfG9q9Q%3D%3D&amp;trackingId=HENEvtuPxzCTSc47zwTLxw%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K85" s="32" t="inlineStr">
+      <c r="K85" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-kuku-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L85" s="32" t="inlineStr">
+      <c r="L85" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-kuku-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M85" s="32" t="inlineStr"/>
+      <c r="M85" s="36" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="32" t="inlineStr">
+      <c r="A86" s="36" t="inlineStr">
         <is>
           <t>linkedin_4403306789</t>
         </is>
       </c>
-      <c r="B86" s="32" t="inlineStr">
+      <c r="B86" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 09:16</t>
         </is>
       </c>
-      <c r="C86" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D86" s="32" t="inlineStr">
+      <c r="C86" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D86" s="36" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E86" s="32" t="inlineStr">
+      <c r="E86" s="36" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F86" s="32" t="inlineStr">
+      <c r="F86" s="36" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G86" s="32" t="inlineStr">
+      <c r="G86" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H86" s="32" t="inlineStr">
+      <c r="H86" s="36" t="inlineStr">
         <is>
           <t>2026-04-19 22:21 UTC</t>
         </is>
       </c>
-      <c r="I86" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J86" s="34" t="inlineStr">
+      <c r="I86" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J86" s="38" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/research-intern-at-skycliff-it-4403306789?refId=KN18fO0braE9qgElBP9zEg%3D%3D&amp;trackingId=%2Bm9LCS%2BxHyH7O3sA%2BvKB2A%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K86" s="32" t="inlineStr">
+      <c r="K86" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L86" s="32" t="inlineStr">
+      <c r="L86" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M86" s="32" t="inlineStr"/>
+      <c r="M86" s="36" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="32" t="inlineStr">
+      <c r="A87" s="36" t="inlineStr">
         <is>
           <t>linkedin_4336984951</t>
         </is>
       </c>
-      <c r="B87" s="32" t="inlineStr">
+      <c r="B87" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 09:16</t>
         </is>
       </c>
-      <c r="C87" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D87" s="32" t="inlineStr">
+      <c r="C87" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D87" s="36" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E87" s="32" t="inlineStr">
+      <c r="E87" s="36" t="inlineStr">
         <is>
           <t>Machine Learning Engineer Intern, Simulation</t>
         </is>
       </c>
-      <c r="F87" s="32" t="inlineStr">
+      <c r="F87" s="36" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G87" s="32" t="inlineStr">
+      <c r="G87" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H87" s="32" t="inlineStr">
+      <c r="H87" s="36" t="inlineStr">
         <is>
           <t>2026-04-19 09:41 UTC</t>
         </is>
       </c>
-      <c r="I87" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J87" s="34" t="inlineStr">
+      <c r="I87" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J87" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/machine-learning-engineer-intern-simulation-at-zoox-4336984951?refId=kzdKy3lQPz5ITmALB3aiLA%3D%3D&amp;trackingId=TBJ5wFzjDmfdPFnmhbpCvA%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K87" s="32" t="inlineStr">
+      <c r="K87" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L87" s="32" t="inlineStr">
+      <c r="L87" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M87" s="32" t="inlineStr"/>
+      <c r="M87" s="36" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="32" t="inlineStr">
+      <c r="A88" s="36" t="inlineStr">
         <is>
           <t>linkedin_4323554488</t>
         </is>
       </c>
-      <c r="B88" s="32" t="inlineStr">
+      <c r="B88" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 20:02</t>
         </is>
       </c>
-      <c r="C88" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D88" s="32" t="inlineStr">
+      <c r="C88" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D88" s="36" t="inlineStr">
         <is>
           <t>Shopee</t>
         </is>
       </c>
-      <c r="E88" s="32" t="inlineStr">
+      <c r="E88" s="36" t="inlineStr">
         <is>
           <t>Data Analyst Intern, Buyer &amp; Marketing - Business Intelligence (Jan- Apr 2026)</t>
         </is>
       </c>
-      <c r="F88" s="32" t="inlineStr">
+      <c r="F88" s="36" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G88" s="32" t="inlineStr">
+      <c r="G88" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H88" s="32" t="inlineStr">
+      <c r="H88" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 13:19 UTC</t>
         </is>
       </c>
-      <c r="I88" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J88" s="34" t="inlineStr">
+      <c r="I88" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J88" s="38" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/data-analyst-intern-buyer-marketing-business-intelligence-jan-apr-2026-at-shopee-4323554488?refId=7F9xR8A2ceTxeNHc8C48Lw%3D%3D&amp;trackingId=yyqxH6uqfdMekl83OKdeng%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K88" s="32" t="inlineStr">
+      <c r="K88" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-shopee-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L88" s="32" t="inlineStr">
+      <c r="L88" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-shopee-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M88" s="32" t="inlineStr"/>
+      <c r="M88" s="36" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="32" t="inlineStr">
+      <c r="A89" s="36" t="inlineStr">
         <is>
           <t>linkedin_4403602536</t>
         </is>
       </c>
-      <c r="B89" s="32" t="inlineStr">
+      <c r="B89" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 20:02</t>
         </is>
       </c>
-      <c r="C89" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D89" s="32" t="inlineStr">
+      <c r="C89" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D89" s="36" t="inlineStr">
         <is>
           <t>Matter</t>
         </is>
       </c>
-      <c r="E89" s="32" t="inlineStr">
+      <c r="E89" s="36" t="inlineStr">
         <is>
           <t>ESG Data Intern</t>
         </is>
       </c>
-      <c r="F89" s="32" t="inlineStr">
+      <c r="F89" s="36" t="inlineStr">
         <is>
           <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
-      <c r="G89" s="32" t="inlineStr">
+      <c r="G89" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H89" s="32" t="inlineStr">
+      <c r="H89" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 13:42 UTC</t>
         </is>
       </c>
-      <c r="I89" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J89" s="34" t="inlineStr">
+      <c r="I89" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J89" s="38" t="inlineStr">
         <is>
           <t>https://dk.linkedin.com/jobs/view/esg-data-intern-at-matter-4403602536?refId=AE%2FVzoOpycEQ7%2F%2BJ0DeSEg%3D%3D&amp;trackingId=KDyRT7oadVzItXO7Z6Fndw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K89" s="32" t="inlineStr">
+      <c r="K89" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-matter-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L89" s="32" t="inlineStr">
+      <c r="L89" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-matter-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M89" s="32" t="inlineStr"/>
+      <c r="M89" s="36" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="32" t="inlineStr">
+      <c r="A90" s="36" t="inlineStr">
         <is>
           <t>linkedin_4403625335</t>
         </is>
       </c>
-      <c r="B90" s="32" t="inlineStr">
+      <c r="B90" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 20:02</t>
         </is>
       </c>
-      <c r="C90" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D90" s="32" t="inlineStr">
+      <c r="C90" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D90" s="36" t="inlineStr">
         <is>
           <t>Binance</t>
         </is>
       </c>
-      <c r="E90" s="32" t="inlineStr">
+      <c r="E90" s="36" t="inlineStr">
         <is>
           <t>Binance Accelerator Program - Applied Data Scientist</t>
         </is>
       </c>
-      <c r="F90" s="32" t="inlineStr">
+      <c r="F90" s="36" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G90" s="32" t="inlineStr">
+      <c r="G90" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H90" s="32" t="inlineStr">
+      <c r="H90" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 15:53 UTC</t>
         </is>
       </c>
-      <c r="I90" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J90" s="34" t="inlineStr">
+      <c r="I90" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J90" s="38" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/binance-accelerator-program-applied-data-scientist-at-binance-4403625335?refId=RjWLz09J3iQbgIc%2B%2Farrcg%3D%3D&amp;trackingId=DNLE3AfRN1YFc4qeIspU0w%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K90" s="32" t="inlineStr">
+      <c r="K90" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-binance-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L90" s="32" t="inlineStr">
+      <c r="L90" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-binance-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M90" s="32" t="inlineStr"/>
+      <c r="M90" s="36" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="32" t="inlineStr">
+      <c r="A91" s="36" t="inlineStr">
         <is>
           <t>linkedin_4401462467</t>
         </is>
       </c>
-      <c r="B91" s="32" t="inlineStr">
+      <c r="B91" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 20:02</t>
         </is>
       </c>
-      <c r="C91" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D91" s="32" t="inlineStr">
+      <c r="C91" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D91" s="36" t="inlineStr">
         <is>
           <t>Henning Larsen</t>
         </is>
       </c>
-      <c r="E91" s="32" t="inlineStr">
+      <c r="E91" s="36" t="inlineStr">
         <is>
           <t>Business Development Intern – AI and IT focus</t>
         </is>
       </c>
-      <c r="F91" s="32" t="inlineStr">
+      <c r="F91" s="36" t="inlineStr">
         <is>
           <t>Copenhagen, Capital Region of Denmark, Denmark</t>
         </is>
       </c>
-      <c r="G91" s="32" t="inlineStr">
+      <c r="G91" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H91" s="32" t="inlineStr">
+      <c r="H91" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 14:23 UTC</t>
         </is>
       </c>
-      <c r="I91" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J91" s="34" t="inlineStr">
+      <c r="I91" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J91" s="38" t="inlineStr">
         <is>
           <t>https://dk.linkedin.com/jobs/view/business-development-intern-%E2%80%93-ai-and-it-focus-at-henning-larsen-4401462467?refId=AE%2FVzoOpycEQ7%2F%2BJ0DeSEg%3D%3D&amp;trackingId=a6kSBIKrUbVcoZ6e1VKmqQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K91" s="32" t="inlineStr">
+      <c r="K91" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-henning-larsen-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L91" s="32" t="inlineStr">
+      <c r="L91" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-henning-larsen-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M91" s="32" t="inlineStr"/>
+      <c r="M91" s="36" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="32" t="inlineStr">
+      <c r="A92" s="36" t="inlineStr">
         <is>
           <t>linkedin_3694731755</t>
         </is>
       </c>
-      <c r="B92" s="32" t="inlineStr">
+      <c r="B92" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 20:02</t>
         </is>
       </c>
-      <c r="C92" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D92" s="32" t="inlineStr">
+      <c r="C92" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D92" s="36" t="inlineStr">
         <is>
           <t>Shopee</t>
         </is>
       </c>
-      <c r="E92" s="32" t="inlineStr">
+      <c r="E92" s="36" t="inlineStr">
         <is>
           <t>Data Analyst Intern - Warehouse Operations, Regional Operations (Spring 2025)</t>
         </is>
       </c>
-      <c r="F92" s="32" t="inlineStr">
+      <c r="F92" s="36" t="inlineStr">
         <is>
           <t>Singapore, Singapore</t>
         </is>
       </c>
-      <c r="G92" s="32" t="inlineStr">
+      <c r="G92" s="36" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H92" s="32" t="inlineStr">
+      <c r="H92" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 13:27 UTC</t>
         </is>
       </c>
-      <c r="I92" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J92" s="34" t="inlineStr">
+      <c r="I92" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J92" s="38" t="inlineStr">
         <is>
           <t>https://sg.linkedin.com/jobs/view/data-analyst-intern-warehouse-operations-regional-operations-spring-2025-at-shopee-3694731755?refId=7F9xR8A2ceTxeNHc8C48Lw%3D%3D&amp;trackingId=Z5%2FGgcVQ%2FHnhfRD8%2FEOmvw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K92" s="32" t="inlineStr">
+      <c r="K92" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-shopee-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L92" s="32" t="inlineStr">
+      <c r="L92" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-shopee-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M92" s="32" t="inlineStr"/>
+      <c r="M92" s="36" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="32" t="inlineStr">
+      <c r="A93" s="36" t="inlineStr">
         <is>
           <t>linkedin_4401618037</t>
         </is>
       </c>
-      <c r="B93" s="32" t="inlineStr">
+      <c r="B93" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 20:02</t>
         </is>
       </c>
-      <c r="C93" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D93" s="32" t="inlineStr">
+      <c r="C93" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D93" s="36" t="inlineStr">
         <is>
           <t>Superhuman</t>
         </is>
       </c>
-      <c r="E93" s="32" t="inlineStr">
+      <c r="E93" s="36" t="inlineStr">
         <is>
           <t>Applied Research Intern (Summer 2026)</t>
         </is>
       </c>
-      <c r="F93" s="32" t="inlineStr">
+      <c r="F93" s="36" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G93" s="32" t="inlineStr">
+      <c r="G93" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H93" s="32" t="inlineStr">
+      <c r="H93" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 09:39 UTC</t>
         </is>
       </c>
-      <c r="I93" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J93" s="34" t="inlineStr">
+      <c r="I93" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J93" s="38" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/applied-research-intern-summer-2026-at-superhuman-4401618037?refId=QaSuTZCPNmMWLvSVLYxnBg%3D%3D&amp;trackingId=VlqyKWxk2dgOXzUfhtaiGQ%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K93" s="32" t="inlineStr">
+      <c r="K93" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-superhuman-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="L93" s="32" t="inlineStr">
+      <c r="L93" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-superhuman-2026-04-20.pdf</t>
         </is>
       </c>
-      <c r="M93" s="32" t="inlineStr"/>
+      <c r="M93" s="36" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="32" t="inlineStr">
+      <c r="A94" s="36" t="inlineStr">
         <is>
           <t>linkedin_4404365794</t>
         </is>
       </c>
-      <c r="B94" s="32" t="inlineStr">
+      <c r="B94" s="36" t="inlineStr">
         <is>
           <t>2026-04-21 08:59</t>
         </is>
       </c>
-      <c r="C94" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D94" s="32" t="inlineStr">
+      <c r="C94" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D94" s="36" t="inlineStr">
         <is>
           <t>Zoox</t>
         </is>
       </c>
-      <c r="E94" s="32" t="inlineStr">
+      <c r="E94" s="36" t="inlineStr">
         <is>
           <t>PhD Research Intern, Vision Language Action Models</t>
         </is>
       </c>
-      <c r="F94" s="32" t="inlineStr">
+      <c r="F94" s="36" t="inlineStr">
         <is>
           <t>Foster City, CA</t>
         </is>
       </c>
-      <c r="G94" s="32" t="inlineStr">
+      <c r="G94" s="36" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H94" s="32" t="inlineStr">
+      <c r="H94" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 20:15 UTC</t>
         </is>
       </c>
-      <c r="I94" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J94" s="34" t="inlineStr">
+      <c r="I94" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J94" s="38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/phd-research-intern-vision-language-action-models-at-zoox-4404365794?refId=uXGDZFbr7zJfdUDLc3YoBA%3D%3D&amp;trackingId=VzDGaTfSup4x8BX36ZTRMw%3D%3D&amp;position=7&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K94" s="32" t="inlineStr">
+      <c r="K94" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-zoox-2026-04-21.pdf</t>
         </is>
       </c>
-      <c r="L94" s="32" t="inlineStr">
+      <c r="L94" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-zoox-2026-04-21.pdf</t>
         </is>
       </c>
-      <c r="M94" s="32" t="inlineStr"/>
+      <c r="M94" s="36" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="32" t="inlineStr">
+      <c r="A95" s="36" t="inlineStr">
         <is>
           <t>linkedin_4401665722</t>
         </is>
       </c>
-      <c r="B95" s="32" t="inlineStr">
+      <c r="B95" s="36" t="inlineStr">
         <is>
           <t>2026-04-21 08:59</t>
         </is>
       </c>
-      <c r="C95" s="32" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D95" s="32" t="inlineStr">
+      <c r="C95" s="36" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D95" s="36" t="inlineStr">
         <is>
           <t>BMW Group</t>
         </is>
       </c>
-      <c r="E95" s="32" t="inlineStr">
+      <c r="E95" s="36" t="inlineStr">
         <is>
           <t>Intern LLM-enhanced in-vehicle personal assistants (f/m/x)</t>
         </is>
       </c>
-      <c r="F95" s="32" t="inlineStr">
+      <c r="F95" s="36" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G95" s="32" t="inlineStr">
+      <c r="G95" s="36" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H95" s="32" t="inlineStr">
+      <c r="H95" s="36" t="inlineStr">
         <is>
           <t>2026-04-20 21:46 UTC</t>
         </is>
       </c>
-      <c r="I95" s="33" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J95" s="34" t="inlineStr">
+      <c r="I95" s="37" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J95" s="38" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/intern-llm-enhanced-in-vehicle-personal-assistants-f-m-x-at-bmw-group-4401665722?refId=eLXGs4VRP9DfKl0tb9vatg%3D%3D&amp;trackingId=ng0wN9P80Kinot8zi8AH9g%3D%3D&amp;position=8&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K95" s="32" t="inlineStr">
+      <c r="K95" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-bmw-group-2026-04-21.pdf</t>
         </is>
       </c>
-      <c r="L95" s="32" t="inlineStr">
+      <c r="L95" s="36" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bmw-group-2026-04-21.pdf</t>
         </is>
       </c>
-      <c r="M95" s="32" t="inlineStr"/>
+      <c r="M95" s="36" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="36" t="inlineStr">
@@ -6625,9 +6625,9 @@
           <t>2026-04-30 09:58 UTC</t>
         </is>
       </c>
-      <c r="I96" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
+      <c r="I96" s="35" t="inlineStr">
+        <is>
+          <t>Applied</t>
         </is>
       </c>
       <c r="J96" s="38" t="inlineStr">
@@ -6645,7 +6645,11 @@
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-halliburton-2026-04-30.pdf</t>
         </is>
       </c>
-      <c r="M96" s="36" t="inlineStr"/>
+      <c r="M96" s="36" t="inlineStr">
+        <is>
+          <t>Status set via Telegram command</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="36" t="inlineStr">
@@ -6688,9 +6692,9 @@
           <t>2026-04-30 00:00 UTC</t>
         </is>
       </c>
-      <c r="I97" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
+      <c r="I97" s="35" t="inlineStr">
+        <is>
+          <t>Applied</t>
         </is>
       </c>
       <c r="J97" s="38" t="inlineStr">
@@ -6708,7 +6712,11 @@
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-cynapse-2026-04-30.pdf</t>
         </is>
       </c>
-      <c r="M97" s="36" t="inlineStr"/>
+      <c r="M97" s="36" t="inlineStr">
+        <is>
+          <t>Status set via Telegram command</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="36" t="inlineStr">
@@ -6751,9 +6759,9 @@
           <t>2026-04-30 01:49 UTC</t>
         </is>
       </c>
-      <c r="I98" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
+      <c r="I98" s="35" t="inlineStr">
+        <is>
+          <t>Applied</t>
         </is>
       </c>
       <c r="J98" s="38" t="inlineStr">
@@ -6771,7 +6779,11 @@
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-samsung-2026-04-30.pdf</t>
         </is>
       </c>
-      <c r="M98" s="36" t="inlineStr"/>
+      <c r="M98" s="36" t="inlineStr">
+        <is>
+          <t>Status set via Telegram command</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="36" t="inlineStr">
@@ -6814,9 +6826,9 @@
           <t>2026-04-29 00:00 UTC</t>
         </is>
       </c>
-      <c r="I99" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
+      <c r="I99" s="35" t="inlineStr">
+        <is>
+          <t>Applied</t>
         </is>
       </c>
       <c r="J99" s="38" t="inlineStr">
@@ -6834,7 +6846,11 @@
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-haskoning-2026-04-30.pdf</t>
         </is>
       </c>
-      <c r="M99" s="36" t="inlineStr"/>
+      <c r="M99" s="36" t="inlineStr">
+        <is>
+          <t>Status set via Telegram command  [Status set via Telegram command]</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="36" t="inlineStr">
@@ -6940,9 +6956,9 @@
           <t>2026-04-29 00:00 UTC</t>
         </is>
       </c>
-      <c r="I101" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
+      <c r="I101" s="35" t="inlineStr">
+        <is>
+          <t>Applied</t>
         </is>
       </c>
       <c r="J101" s="38" t="inlineStr">
@@ -6960,7 +6976,11 @@
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-bosch-2026-04-30.pdf</t>
         </is>
       </c>
-      <c r="M101" s="36" t="inlineStr"/>
+      <c r="M101" s="36" t="inlineStr">
+        <is>
+          <t>Status set via Telegram command</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="36" t="inlineStr">
@@ -7066,9 +7086,9 @@
           <t>2026-04-29 00:00 UTC</t>
         </is>
       </c>
-      <c r="I103" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
+      <c r="I103" s="35" t="inlineStr">
+        <is>
+          <t>Applied</t>
         </is>
       </c>
       <c r="J103" s="38" t="inlineStr">
@@ -7086,7 +7106,11 @@
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-applied-materials-2026-04-30.pdf</t>
         </is>
       </c>
-      <c r="M103" s="36" t="inlineStr"/>
+      <c r="M103" s="36" t="inlineStr">
+        <is>
+          <t>Status set via Telegram command</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="36" t="inlineStr">
@@ -7129,9 +7153,9 @@
           <t>2026-04-29 00:00 UTC</t>
         </is>
       </c>
-      <c r="I104" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
+      <c r="I104" s="35" t="inlineStr">
+        <is>
+          <t>Applied</t>
         </is>
       </c>
       <c r="J104" s="38" t="inlineStr">
@@ -7149,7 +7173,11 @@
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-d-matrix-2026-04-30.pdf</t>
         </is>
       </c>
-      <c r="M104" s="36" t="inlineStr"/>
+      <c r="M104" s="36" t="inlineStr">
+        <is>
+          <t>Status set via Telegram command</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="36" t="inlineStr">
@@ -7192,9 +7220,9 @@
           <t>2026-04-29 10:24 UTC</t>
         </is>
       </c>
-      <c r="I105" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
+      <c r="I105" s="35" t="inlineStr">
+        <is>
+          <t>Applied</t>
         </is>
       </c>
       <c r="J105" s="38" t="inlineStr">
@@ -7212,7 +7240,11 @@
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-kogancom-2026-04-30.pdf</t>
         </is>
       </c>
-      <c r="M105" s="36" t="inlineStr"/>
+      <c r="M105" s="36" t="inlineStr">
+        <is>
+          <t>Status set via Telegram command</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="36" t="inlineStr">
@@ -7255,9 +7287,9 @@
           <t>2026-04-28 13:09 UTC</t>
         </is>
       </c>
-      <c r="I106" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
+      <c r="I106" s="35" t="inlineStr">
+        <is>
+          <t>Applied</t>
         </is>
       </c>
       <c r="J106" s="38" t="inlineStr">
@@ -7275,7 +7307,11 @@
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-kogan-2026-04-30.pdf</t>
         </is>
       </c>
-      <c r="M106" s="36" t="inlineStr"/>
+      <c r="M106" s="36" t="inlineStr">
+        <is>
+          <t>Status set via Telegram command</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="36" t="inlineStr">
@@ -7381,9 +7417,9 @@
           <t>2026-04-28 00:00 UTC</t>
         </is>
       </c>
-      <c r="I108" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
+      <c r="I108" s="35" t="inlineStr">
+        <is>
+          <t>Applied</t>
         </is>
       </c>
       <c r="J108" s="38" t="inlineStr">
@@ -7401,7 +7437,11 @@
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sap-2026-04-30.pdf</t>
         </is>
       </c>
-      <c r="M108" s="36" t="inlineStr"/>
+      <c r="M108" s="36" t="inlineStr">
+        <is>
+          <t>Status set via Telegram command</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="36" t="inlineStr">
@@ -7444,9 +7484,9 @@
           <t>2026-04-28 00:00 UTC</t>
         </is>
       </c>
-      <c r="I109" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
+      <c r="I109" s="35" t="inlineStr">
+        <is>
+          <t>Applied</t>
         </is>
       </c>
       <c r="J109" s="38" t="inlineStr">
@@ -7464,7 +7504,11 @@
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-salesforce-2026-04-30.pdf</t>
         </is>
       </c>
-      <c r="M109" s="36" t="inlineStr"/>
+      <c r="M109" s="36" t="inlineStr">
+        <is>
+          <t>Status set via Telegram command</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="36" t="inlineStr">
@@ -7507,9 +7551,9 @@
           <t>2026-04-28 00:00 UTC</t>
         </is>
       </c>
-      <c r="I110" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
+      <c r="I110" s="35" t="inlineStr">
+        <is>
+          <t>Applied</t>
         </is>
       </c>
       <c r="J110" s="38" t="inlineStr">
@@ -7527,7 +7571,11 @@
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-billiontoone-2026-04-30.pdf</t>
         </is>
       </c>
-      <c r="M110" s="36" t="inlineStr"/>
+      <c r="M110" s="36" t="inlineStr">
+        <is>
+          <t>Status set via Telegram command  [Status set via Telegram command]</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="36" t="inlineStr">

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -6893,9 +6893,9 @@
           <t>2026-04-29 02:48 UTC</t>
         </is>
       </c>
-      <c r="I100" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
+      <c r="I100" s="35" t="inlineStr">
+        <is>
+          <t>Applied</t>
         </is>
       </c>
       <c r="J100" s="38" t="inlineStr">
@@ -6913,7 +6913,11 @@
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-perspectum-2026-04-30.pdf</t>
         </is>
       </c>
-      <c r="M100" s="36" t="inlineStr"/>
+      <c r="M100" s="36" t="inlineStr">
+        <is>
+          <t>Status set via Telegram command</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="36" t="inlineStr">
@@ -7023,9 +7027,9 @@
           <t>2026-04-29 14:12 UTC</t>
         </is>
       </c>
-      <c r="I102" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
+      <c r="I102" s="35" t="inlineStr">
+        <is>
+          <t>Applied</t>
         </is>
       </c>
       <c r="J102" s="38" t="inlineStr">
@@ -7043,7 +7047,11 @@
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-redtech-recruitment-2026-04-30.pdf</t>
         </is>
       </c>
-      <c r="M102" s="36" t="inlineStr"/>
+      <c r="M102" s="36" t="inlineStr">
+        <is>
+          <t>Status set via Telegram command</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="36" t="inlineStr">
@@ -7618,9 +7626,9 @@
           <t>2026-04-28 10:25 UTC</t>
         </is>
       </c>
-      <c r="I111" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
+      <c r="I111" s="35" t="inlineStr">
+        <is>
+          <t>Applied</t>
         </is>
       </c>
       <c r="J111" s="38" t="inlineStr">
@@ -7638,7 +7646,11 @@
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-rooflineai-gmbh-2026-04-30.pdf</t>
         </is>
       </c>
-      <c r="M111" s="36" t="inlineStr"/>
+      <c r="M111" s="36" t="inlineStr">
+        <is>
+          <t>Status set via Telegram command</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Internship Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,6 +193,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -569,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M111"/>
+  <dimension ref="A1:M121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7362,9 +7371,9 @@
           <t>2026-04-28 00:00 UTC</t>
         </is>
       </c>
-      <c r="I107" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
+      <c r="I107" s="35" t="inlineStr">
+        <is>
+          <t>Applied</t>
         </is>
       </c>
       <c r="J107" s="38" t="inlineStr">
@@ -7382,7 +7391,11 @@
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-gravis-robotics-2026-04-30.pdf</t>
         </is>
       </c>
-      <c r="M107" s="36" t="inlineStr"/>
+      <c r="M107" s="36" t="inlineStr">
+        <is>
+          <t>Gmail auto: 'Thank you for your application to Gravis Robotics'</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="36" t="inlineStr">
@@ -7651,6 +7664,636 @@
           <t>Status set via Telegram command</t>
         </is>
       </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="39" t="inlineStr">
+        <is>
+          <t>indeed_b46127f3094baf9c</t>
+        </is>
+      </c>
+      <c r="B112" s="39" t="inlineStr">
+        <is>
+          <t>2026-04-30 19:44</t>
+        </is>
+      </c>
+      <c r="C112" s="39" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="D112" s="39" t="inlineStr">
+        <is>
+          <t>Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="E112" s="39" t="inlineStr">
+        <is>
+          <t>AI Research Intern - Knowledge Graphs</t>
+        </is>
+      </c>
+      <c r="F112" s="39" t="inlineStr">
+        <is>
+          <t>Staines-upon-Thames, ENG, GB</t>
+        </is>
+      </c>
+      <c r="G112" s="39" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H112" s="39" t="inlineStr">
+        <is>
+          <t>2026-04-30 00:00 UTC</t>
+        </is>
+      </c>
+      <c r="I112" s="40" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J112" s="41" t="inlineStr">
+        <is>
+          <t>https://uk.indeed.com/viewjob?jk=b05d9dc856a34ddc</t>
+        </is>
+      </c>
+      <c r="K112" s="39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-samsung-electronics-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L112" s="39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-samsung-electronics-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M112" s="39" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="39" t="inlineStr">
+        <is>
+          <t>indeed_58cc8f372fab2f7f</t>
+        </is>
+      </c>
+      <c r="B113" s="39" t="inlineStr">
+        <is>
+          <t>2026-04-30 19:44</t>
+        </is>
+      </c>
+      <c r="C113" s="39" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="D113" s="39" t="inlineStr">
+        <is>
+          <t>Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="E113" s="39" t="inlineStr">
+        <is>
+          <t>AI Research Intern - Agentic AI</t>
+        </is>
+      </c>
+      <c r="F113" s="39" t="inlineStr">
+        <is>
+          <t>Staines-upon-Thames, ENG, GB</t>
+        </is>
+      </c>
+      <c r="G113" s="39" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H113" s="39" t="inlineStr">
+        <is>
+          <t>2026-04-30 00:00 UTC</t>
+        </is>
+      </c>
+      <c r="I113" s="40" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J113" s="41" t="inlineStr">
+        <is>
+          <t>https://uk.indeed.com/viewjob?jk=b1c2cc7eed940506</t>
+        </is>
+      </c>
+      <c r="K113" s="39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-samsung-electronics-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L113" s="39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-samsung-electronics-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M113" s="39" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="39" t="inlineStr">
+        <is>
+          <t>indeed_85947217d57dfa14</t>
+        </is>
+      </c>
+      <c r="B114" s="39" t="inlineStr">
+        <is>
+          <t>2026-04-30 19:44</t>
+        </is>
+      </c>
+      <c r="C114" s="39" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="D114" s="39" t="inlineStr">
+        <is>
+          <t>Damen</t>
+        </is>
+      </c>
+      <c r="E114" s="39" t="inlineStr">
+        <is>
+          <t>Internship: Speeding up Simulations</t>
+        </is>
+      </c>
+      <c r="F114" s="39" t="inlineStr">
+        <is>
+          <t>Gorinchem, ZH, NL</t>
+        </is>
+      </c>
+      <c r="G114" s="39" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H114" s="39" t="inlineStr">
+        <is>
+          <t>2026-04-30 00:00 UTC</t>
+        </is>
+      </c>
+      <c r="I114" s="40" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J114" s="41" t="inlineStr">
+        <is>
+          <t>https://nl.indeed.com/viewjob?jk=814c007e610dd4da</t>
+        </is>
+      </c>
+      <c r="K114" s="39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-damen-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L114" s="39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-damen-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M114" s="39" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="39" t="inlineStr">
+        <is>
+          <t>indeed_13bc97be8fcd9fbb</t>
+        </is>
+      </c>
+      <c r="B115" s="39" t="inlineStr">
+        <is>
+          <t>2026-04-30 19:44</t>
+        </is>
+      </c>
+      <c r="C115" s="39" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="D115" s="39" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="E115" s="39" t="inlineStr">
+        <is>
+          <t>PhD Student Intern - AI Research</t>
+        </is>
+      </c>
+      <c r="F115" s="39" t="inlineStr">
+        <is>
+          <t>Queenstown, S00, SG</t>
+        </is>
+      </c>
+      <c r="G115" s="39" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H115" s="39" t="inlineStr">
+        <is>
+          <t>2026-04-30 00:00 UTC</t>
+        </is>
+      </c>
+      <c r="I115" s="40" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J115" s="41" t="inlineStr">
+        <is>
+          <t>https://sg.indeed.com/viewjob?jk=d74d82461fdd7733</t>
+        </is>
+      </c>
+      <c r="K115" s="39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-sap-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L115" s="39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-sap-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M115" s="39" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="39" t="inlineStr">
+        <is>
+          <t>adzuna_5714457524</t>
+        </is>
+      </c>
+      <c r="B116" s="39" t="inlineStr">
+        <is>
+          <t>2026-04-30 19:44</t>
+        </is>
+      </c>
+      <c r="C116" s="39" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="D116" s="39" t="inlineStr">
+        <is>
+          <t>Intel Corporation</t>
+        </is>
+      </c>
+      <c r="E116" s="39" t="inlineStr">
+        <is>
+          <t>AI Systems and Solutions Engineering Intern</t>
+        </is>
+      </c>
+      <c r="F116" s="39" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="G116" s="39" t="inlineStr">
+        <is>
+          <t>South_America</t>
+        </is>
+      </c>
+      <c r="H116" s="39" t="inlineStr">
+        <is>
+          <t>2026-04-30 04:02 UTC</t>
+        </is>
+      </c>
+      <c r="I116" s="40" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J116" s="41" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.com.mx/land/ad/5714457524?se=BMQFXMtE8RGgCKExt3-rCA&amp;utm_medium=api&amp;utm_source=9f5acb07&amp;v=50AE411945085D5A15A51A553C3AE2B6C53F9F29</t>
+        </is>
+      </c>
+      <c r="K116" s="39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-intel-corporation-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L116" s="39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-intel-corporation-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M116" s="39" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="39" t="inlineStr">
+        <is>
+          <t>adzuna_5713877019</t>
+        </is>
+      </c>
+      <c r="B117" s="39" t="inlineStr">
+        <is>
+          <t>2026-04-30 19:44</t>
+        </is>
+      </c>
+      <c r="C117" s="39" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="D117" s="39" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E117" s="39" t="inlineStr">
+        <is>
+          <t>AI Systems and Solutions Engineering Intern</t>
+        </is>
+      </c>
+      <c r="F117" s="39" t="inlineStr">
+        <is>
+          <t>Guadalajara, Jalisco</t>
+        </is>
+      </c>
+      <c r="G117" s="39" t="inlineStr">
+        <is>
+          <t>South_America</t>
+        </is>
+      </c>
+      <c r="H117" s="39" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:36 UTC</t>
+        </is>
+      </c>
+      <c r="I117" s="40" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J117" s="41" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.com.mx/details/5713877019?utm_medium=api&amp;utm_source=9f5acb07</t>
+        </is>
+      </c>
+      <c r="K117" s="39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-intel-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L117" s="39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-intel-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M117" s="39" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="39" t="inlineStr">
+        <is>
+          <t>adzuna_5712639986</t>
+        </is>
+      </c>
+      <c r="B118" s="39" t="inlineStr">
+        <is>
+          <t>2026-04-30 19:44</t>
+        </is>
+      </c>
+      <c r="C118" s="39" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="D118" s="39" t="inlineStr">
+        <is>
+          <t>Intel Corporation</t>
+        </is>
+      </c>
+      <c r="E118" s="39" t="inlineStr">
+        <is>
+          <t>AI-Driven Software Dev Intern (Hybrid, Mexico)</t>
+        </is>
+      </c>
+      <c r="F118" s="39" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="G118" s="39" t="inlineStr">
+        <is>
+          <t>South_America</t>
+        </is>
+      </c>
+      <c r="H118" s="39" t="inlineStr">
+        <is>
+          <t>2026-04-28 04:10 UTC</t>
+        </is>
+      </c>
+      <c r="I118" s="40" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J118" s="41" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.com.mx/land/ad/5712639986?se=BMQFXMtE8RGgCKExt3-rCA&amp;utm_medium=api&amp;utm_source=9f5acb07&amp;v=18879AC0EA0B3DABD6F8C280C87738D644CC4FC7</t>
+        </is>
+      </c>
+      <c r="K118" s="39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-intel-corporation-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L118" s="39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-intel-corporation-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M118" s="39" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="39" t="inlineStr">
+        <is>
+          <t>indeed_5e64904124a76761</t>
+        </is>
+      </c>
+      <c r="B119" s="39" t="inlineStr">
+        <is>
+          <t>2026-04-30 19:44</t>
+        </is>
+      </c>
+      <c r="C119" s="39" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="D119" s="39" t="inlineStr">
+        <is>
+          <t>QUADRIC PTY LTD</t>
+        </is>
+      </c>
+      <c r="E119" s="39" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern - Kernels</t>
+        </is>
+      </c>
+      <c r="F119" s="39" t="inlineStr">
+        <is>
+          <t>Burlingame, CA, US</t>
+        </is>
+      </c>
+      <c r="G119" s="39" t="inlineStr">
+        <is>
+          <t>USA_Canada</t>
+        </is>
+      </c>
+      <c r="H119" s="39" t="inlineStr">
+        <is>
+          <t>2026-04-28 00:00 UTC</t>
+        </is>
+      </c>
+      <c r="I119" s="40" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J119" s="41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d831d774e018ad88</t>
+        </is>
+      </c>
+      <c r="K119" s="39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-quadric-pty-ltd-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L119" s="39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-quadric-pty-ltd-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M119" s="39" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="39" t="inlineStr">
+        <is>
+          <t>adzuna_5713795151</t>
+        </is>
+      </c>
+      <c r="B120" s="39" t="inlineStr">
+        <is>
+          <t>2026-04-30 19:44</t>
+        </is>
+      </c>
+      <c r="C120" s="39" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="D120" s="39" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E120" s="39" t="inlineStr">
+        <is>
+          <t>Software Development Intern</t>
+        </is>
+      </c>
+      <c r="F120" s="39" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="G120" s="39" t="inlineStr">
+        <is>
+          <t>South_America</t>
+        </is>
+      </c>
+      <c r="H120" s="39" t="inlineStr">
+        <is>
+          <t>2026-04-29 12:21 UTC</t>
+        </is>
+      </c>
+      <c r="I120" s="40" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J120" s="41" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.com.mx/land/ad/5713795151?se=BMQFXMtE8RGgCKExt3-rCA&amp;utm_medium=api&amp;utm_source=9f5acb07&amp;v=96A8ADD6530F798E08F8BCC393F5A709C105EDD4</t>
+        </is>
+      </c>
+      <c r="K120" s="39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-intel-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L120" s="39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-intel-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M120" s="39" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="39" t="inlineStr">
+        <is>
+          <t>adzuna_5712598305</t>
+        </is>
+      </c>
+      <c r="B121" s="39" t="inlineStr">
+        <is>
+          <t>2026-04-30 19:44</t>
+        </is>
+      </c>
+      <c r="C121" s="39" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="D121" s="39" t="inlineStr">
+        <is>
+          <t>Activate Interactive Pte Ltd</t>
+        </is>
+      </c>
+      <c r="E121" s="39" t="inlineStr">
+        <is>
+          <t>Intern - Data Science Intern</t>
+        </is>
+      </c>
+      <c r="F121" s="39" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G121" s="39" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="H121" s="39" t="inlineStr">
+        <is>
+          <t>2026-04-28 17:12 UTC</t>
+        </is>
+      </c>
+      <c r="I121" s="40" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J121" s="41" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.sg/details/5712598305?utm_medium=api&amp;utm_source=9f5acb07</t>
+        </is>
+      </c>
+      <c r="K121" s="39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-activate-interactive-pte-ltd-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="L121" s="39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-activate-interactive-pte-ltd-2026-04-30.pdf</t>
+        </is>
+      </c>
+      <c r="M121" s="39" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -7764,6 +8407,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J109" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J110" r:id="rId109"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J121" r:id="rId120"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,6 +193,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -578,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M121"/>
+  <dimension ref="A1:M125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -664,861 +673,861 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="36" t="inlineStr">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>linkedin_4401809501</t>
         </is>
       </c>
-      <c r="B2" s="36" t="inlineStr">
+      <c r="B2" s="39" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C2" s="36" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D2" s="36" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D2" s="39" t="inlineStr">
         <is>
           <t>Skycliff IT</t>
         </is>
       </c>
-      <c r="E2" s="36" t="inlineStr">
+      <c r="E2" s="39" t="inlineStr">
         <is>
           <t>Research Intern</t>
         </is>
       </c>
-      <c r="F2" s="36" t="inlineStr">
+      <c r="F2" s="39" t="inlineStr">
         <is>
           <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
-      <c r="G2" s="36" t="inlineStr">
+      <c r="G2" s="39" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H2" s="36" t="inlineStr">
+      <c r="H2" s="39" t="inlineStr">
         <is>
           <t>2026-04-15 22:19 UTC</t>
         </is>
       </c>
-      <c r="I2" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J2" s="38" t="inlineStr">
+      <c r="I2" s="40" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J2" s="41" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/research-intern-at-skycliff-it-4401809501?refId=HHi6SaK1fggu3E9dI3MtVg%3D%3D&amp;trackingId=r33pSo29lHStfk9FH82pyw%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K2" s="36" t="inlineStr">
+      <c r="K2" s="39" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L2" s="36" t="inlineStr">
+      <c r="L2" s="39" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-skycliff-it-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M2" s="36" t="inlineStr"/>
+      <c r="M2" s="39" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>linkedin_4402568578</t>
         </is>
       </c>
-      <c r="B3" s="36" t="inlineStr">
+      <c r="B3" s="39" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C3" s="36" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D3" s="36" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D3" s="39" t="inlineStr">
         <is>
           <t>Webs X UM</t>
         </is>
       </c>
-      <c r="E3" s="36" t="inlineStr">
+      <c r="E3" s="39" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F3" s="36" t="inlineStr">
+      <c r="F3" s="39" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="G3" s="36" t="inlineStr">
+      <c r="G3" s="39" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H3" s="36" t="inlineStr">
+      <c r="H3" s="39" t="inlineStr">
         <is>
           <t>2026-04-15 19:20 UTC</t>
         </is>
       </c>
-      <c r="I3" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J3" s="38" t="inlineStr">
+      <c r="I3" s="40" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J3" s="41" t="inlineStr">
         <is>
           <t>https://in.linkedin.com/jobs/view/data-analyst-intern-at-webs-x-um-4402568578?refId=g89JM6cY8EFeoLk6JL5tVg%3D%3D&amp;trackingId=uFZVJJX7SSI0XCPFIrLqmA%3D%3D&amp;position=19&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K3" s="36" t="inlineStr">
+      <c r="K3" s="39" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-webs-x-um-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L3" s="36" t="inlineStr">
+      <c r="L3" s="39" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-webs-x-um-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M3" s="36" t="inlineStr"/>
+      <c r="M3" s="39" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>linkedin_4399996740</t>
         </is>
       </c>
-      <c r="B4" s="36" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C4" s="36" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D4" s="36" t="inlineStr">
+      <c r="C4" s="39" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D4" s="39" t="inlineStr">
         <is>
           <t>SUN PHARMA</t>
         </is>
       </c>
-      <c r="E4" s="36" t="inlineStr">
+      <c r="E4" s="39" t="inlineStr">
         <is>
           <t>Becario</t>
         </is>
       </c>
-      <c r="F4" s="36" t="inlineStr">
+      <c r="F4" s="39" t="inlineStr">
         <is>
           <t>Mexico City, Mexico</t>
         </is>
       </c>
-      <c r="G4" s="36" t="inlineStr">
+      <c r="G4" s="39" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H4" s="36" t="inlineStr">
+      <c r="H4" s="39" t="inlineStr">
         <is>
           <t>2026-04-15 17:59 UTC</t>
         </is>
       </c>
-      <c r="I4" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J4" s="38" t="inlineStr">
+      <c r="I4" s="40" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J4" s="41" t="inlineStr">
         <is>
           <t>https://mx.linkedin.com/jobs/view/becario-at-sun-pharma-4399996740?refId=g89JM6cY8EFeoLk6JL5tVg%3D%3D&amp;trackingId=sZ0Fkcf4RHuIpzXu4mJRNg%3D%3D&amp;position=22&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K4" s="36" t="inlineStr">
+      <c r="K4" s="39" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-sun-pharma-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L4" s="36" t="inlineStr">
+      <c r="L4" s="39" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-sun-pharma-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M4" s="36" t="inlineStr"/>
+      <c r="M4" s="39" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>linkedin_4399975959</t>
         </is>
       </c>
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C5" s="36" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="C5" s="39" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D5" s="39" t="inlineStr">
         <is>
           <t>LS Direct</t>
         </is>
       </c>
-      <c r="E5" s="36" t="inlineStr">
+      <c r="E5" s="39" t="inlineStr">
         <is>
           <t>Data Analytics Intern</t>
         </is>
       </c>
-      <c r="F5" s="36" t="inlineStr">
+      <c r="F5" s="39" t="inlineStr">
         <is>
           <t>Suffern, NY</t>
         </is>
       </c>
-      <c r="G5" s="36" t="inlineStr">
+      <c r="G5" s="39" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="H5" s="36" t="inlineStr">
+      <c r="H5" s="39" t="inlineStr">
         <is>
           <t>2026-04-15 14:26 UTC</t>
         </is>
       </c>
-      <c r="I5" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J5" s="38" t="inlineStr">
+      <c r="I5" s="40" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J5" s="41" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/data-analytics-intern-at-ls-direct-4399975959?refId=pg0ll3e89fatVyUznLcdpw%3D%3D&amp;trackingId=5b41IoyQfIfx3Tu42domiQ%3D%3D&amp;position=23&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K5" s="36" t="inlineStr">
+      <c r="K5" s="39" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-ls-direct-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L5" s="36" t="inlineStr">
+      <c r="L5" s="39" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-ls-direct-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M5" s="36" t="inlineStr"/>
+      <c r="M5" s="39" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>linkedin_4370546718</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="39" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D6" s="36" t="inlineStr">
+      <c r="C6" s="39" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D6" s="39" t="inlineStr">
         <is>
           <t>Clarivate</t>
         </is>
       </c>
-      <c r="E6" s="36" t="inlineStr">
+      <c r="E6" s="39" t="inlineStr">
         <is>
           <t>Lead Data Scientist</t>
         </is>
       </c>
-      <c r="F6" s="36" t="inlineStr">
+      <c r="F6" s="39" t="inlineStr">
         <is>
           <t>Barcelona, Catalonia, Spain</t>
         </is>
       </c>
-      <c r="G6" s="36" t="inlineStr">
+      <c r="G6" s="39" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H6" s="36" t="inlineStr">
+      <c r="H6" s="39" t="inlineStr">
         <is>
           <t>2026-04-15 12:16 UTC</t>
         </is>
       </c>
-      <c r="I6" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J6" s="38" t="inlineStr">
+      <c r="I6" s="40" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J6" s="41" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/lead-data-scientist-at-clarivate-4370546718?refId=FyyqQfduMQ8KZ7B5LeF0UQ%3D%3D&amp;trackingId=1i1kXdbV7SMunyFTiSJHJg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K6" s="36" t="inlineStr">
+      <c r="K6" s="39" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-clarivate-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L6" s="36" t="inlineStr">
+      <c r="L6" s="39" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-clarivate-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M6" s="36" t="inlineStr"/>
+      <c r="M6" s="39" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>linkedin_4389810164</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C7" s="36" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D7" s="36" t="inlineStr">
+      <c r="C7" s="39" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D7" s="39" t="inlineStr">
         <is>
           <t>Vitality</t>
         </is>
       </c>
-      <c r="E7" s="36" t="inlineStr">
+      <c r="E7" s="39" t="inlineStr">
         <is>
           <t>Senior Data Scientist - 12 Month FTC</t>
         </is>
       </c>
-      <c r="F7" s="36" t="inlineStr">
+      <c r="F7" s="39" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G7" s="36" t="inlineStr">
+      <c r="G7" s="39" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H7" s="36" t="inlineStr">
+      <c r="H7" s="39" t="inlineStr">
         <is>
           <t>2026-04-15 09:39 UTC</t>
         </is>
       </c>
-      <c r="I7" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J7" s="38" t="inlineStr">
+      <c r="I7" s="40" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J7" s="41" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/senior-data-scientist-12-month-ftc-at-vitality-4389810164?refId=FPz%2BrPoaQeqgXBm%2FfOzGGA%3D%3D&amp;trackingId=yVNh55t2X2xocDT4i6HDqQ%3D%3D&amp;position=3&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K7" s="36" t="inlineStr">
+      <c r="K7" s="39" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-vitality-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L7" s="36" t="inlineStr">
+      <c r="L7" s="39" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-vitality-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M7" s="36" t="inlineStr"/>
+      <c r="M7" s="39" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>linkedin_4399952059</t>
         </is>
       </c>
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C8" s="36" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D8" s="36" t="inlineStr">
+      <c r="C8" s="39" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D8" s="39" t="inlineStr">
         <is>
           <t>traide AI</t>
         </is>
       </c>
-      <c r="E8" s="36" t="inlineStr">
+      <c r="E8" s="39" t="inlineStr">
         <is>
           <t>AI Associate (f/m/x) (B2B SaaS Startup) - Intern/Working Student</t>
         </is>
       </c>
-      <c r="F8" s="36" t="inlineStr">
+      <c r="F8" s="39" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G8" s="36" t="inlineStr">
+      <c r="G8" s="39" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H8" s="36" t="inlineStr">
+      <c r="H8" s="39" t="inlineStr">
         <is>
           <t>2026-04-15 07:04 UTC</t>
         </is>
       </c>
-      <c r="I8" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J8" s="38" t="inlineStr">
+      <c r="I8" s="40" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J8" s="41" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/ai-associate-f-m-x-b2b-saas-startup-intern-working-student-at-traide-ai-4399952059?refId=x0uIkl175n0hipT17L%2FGRw%3D%3D&amp;trackingId=8kdzUQgW%2B7rCk2pO2oIErg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K8" s="36" t="inlineStr">
+      <c r="K8" s="39" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-traide-ai-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L8" s="36" t="inlineStr">
+      <c r="L8" s="39" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-traide-ai-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M8" s="36" t="inlineStr"/>
+      <c r="M8" s="39" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="39" t="inlineStr">
         <is>
           <t>linkedin_4399933254</t>
         </is>
       </c>
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="39" t="inlineStr">
         <is>
           <t>2026-04-16 02:47</t>
         </is>
       </c>
-      <c r="C9" s="36" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D9" s="36" t="inlineStr">
+      <c r="C9" s="39" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D9" s="39" t="inlineStr">
         <is>
           <t>Briink</t>
         </is>
       </c>
-      <c r="E9" s="36" t="inlineStr">
+      <c r="E9" s="39" t="inlineStr">
         <is>
           <t>Growth Intern (Merantix AI Campus)</t>
         </is>
       </c>
-      <c r="F9" s="36" t="inlineStr">
+      <c r="F9" s="39" t="inlineStr">
         <is>
           <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
-      <c r="G9" s="36" t="inlineStr">
+      <c r="G9" s="39" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H9" s="36" t="inlineStr">
+      <c r="H9" s="39" t="inlineStr">
         <is>
           <t>2026-04-15 05:03 UTC</t>
         </is>
       </c>
-      <c r="I9" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J9" s="38" t="inlineStr">
+      <c r="I9" s="40" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J9" s="41" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/jobs/view/growth-intern-merantix-ai-campus-at-briink-4399933254?refId=x0uIkl175n0hipT17L%2FGRw%3D%3D&amp;trackingId=qEKtyJNA03Kbr6AYDlhsBw%3D%3D&amp;position=2&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K9" s="36" t="inlineStr">
+      <c r="K9" s="39" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/resumes/cv-aymane-ait-dads-briink-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L9" s="36" t="inlineStr">
+      <c r="L9" s="39" t="inlineStr">
         <is>
           <t>/Users/aaitdads/Desktop/career-ops/cover_letters/cover-aymane-ait-dads-briink-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M9" s="36" t="inlineStr"/>
+      <c r="M9" s="39" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>linkedin_4400429367</t>
         </is>
       </c>
-      <c r="B10" s="36" t="inlineStr">
+      <c r="B10" s="39" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C10" s="36" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D10" s="36" t="inlineStr">
+      <c r="C10" s="39" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D10" s="39" t="inlineStr">
         <is>
           <t>Tata Consultancy Services</t>
         </is>
       </c>
-      <c r="E10" s="36" t="inlineStr">
+      <c r="E10" s="39" t="inlineStr">
         <is>
           <t>HR -Data Scientist</t>
         </is>
       </c>
-      <c r="F10" s="36" t="inlineStr">
+      <c r="F10" s="39" t="inlineStr">
         <is>
           <t>Renton, WA</t>
         </is>
       </c>
-      <c r="G10" s="36" t="inlineStr">
+      <c r="G10" s="39" t="inlineStr">
         <is>
           <t>USA_Canada</t>
         </is>
       </c>
-      <c r="H10" s="36" t="inlineStr">
+      <c r="H10" s="39" t="inlineStr">
         <is>
           <t>2026-04-16 16:56 UTC</t>
         </is>
       </c>
-      <c r="I10" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J10" s="38" t="inlineStr">
+      <c r="I10" s="40" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J10" s="41" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/hr-data-scientist-at-tata-consultancy-services-4400429367?refId=vJILgNySaXYUQknbyaKZZQ%3D%3D&amp;trackingId=7cZ0KYh8Sv5%2Fh6%2FG86%2BLug%3D%3D&amp;position=5&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K10" s="36" t="inlineStr">
+      <c r="K10" s="39" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-tata-consultancy-services-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L10" s="36" t="inlineStr">
+      <c r="L10" s="39" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-tata-consultancy-services-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M10" s="36" t="inlineStr"/>
+      <c r="M10" s="39" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="39" t="inlineStr">
         <is>
           <t>linkedin_4390814627</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
+      <c r="B11" s="39" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C11" s="36" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="C11" s="39" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D11" s="39" t="inlineStr">
         <is>
           <t>Criteo</t>
         </is>
       </c>
-      <c r="E11" s="36" t="inlineStr">
+      <c r="E11" s="39" t="inlineStr">
         <is>
           <t>Data Analyst Intern</t>
         </is>
       </c>
-      <c r="F11" s="36" t="inlineStr">
+      <c r="F11" s="39" t="inlineStr">
         <is>
           <t>Barcelona, Catalonia, Spain</t>
         </is>
       </c>
-      <c r="G11" s="36" t="inlineStr">
+      <c r="G11" s="39" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H11" s="36" t="inlineStr">
+      <c r="H11" s="39" t="inlineStr">
         <is>
           <t>2026-04-16 12:19 UTC</t>
         </is>
       </c>
-      <c r="I11" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J11" s="38" t="inlineStr">
+      <c r="I11" s="40" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J11" s="41" t="inlineStr">
         <is>
           <t>https://es.linkedin.com/jobs/view/data-analyst-intern-at-criteo-4390814627?refId=PCZWvfzZIzNkx6giU9jTsA%3D%3D&amp;trackingId=T%2FMog6vtgG8P3ihAU9b1uQ%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K11" s="36" t="inlineStr">
+      <c r="K11" s="39" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-criteo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L11" s="36" t="inlineStr">
+      <c r="L11" s="39" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-criteo-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M11" s="36" t="inlineStr"/>
+      <c r="M11" s="39" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="39" t="inlineStr">
         <is>
           <t>linkedin_4402983364</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C12" s="36" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D12" s="36" t="inlineStr">
+      <c r="C12" s="39" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D12" s="39" t="inlineStr">
         <is>
           <t>ENGIE Belgium</t>
         </is>
       </c>
-      <c r="E12" s="36" t="inlineStr">
+      <c r="E12" s="39" t="inlineStr">
         <is>
           <t>Internship: Algorithmic trading strategies (hydropower)</t>
         </is>
       </c>
-      <c r="F12" s="36" t="inlineStr">
+      <c r="F12" s="39" t="inlineStr">
         <is>
           <t>Brussels, Brussels Region, Belgium</t>
         </is>
       </c>
-      <c r="G12" s="36" t="inlineStr">
+      <c r="G12" s="39" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H12" s="36" t="inlineStr">
+      <c r="H12" s="39" t="inlineStr">
         <is>
           <t>2026-04-16 16:09 UTC</t>
         </is>
       </c>
-      <c r="I12" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J12" s="38" t="inlineStr">
+      <c r="I12" s="40" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J12" s="41" t="inlineStr">
         <is>
           <t>https://be.linkedin.com/jobs/view/internship-algorithmic-trading-strategies-hydropower-at-engie-belgium-4402983364?refId=FFebzR6jiv0%2BWWMeb5n7oQ%3D%3D&amp;trackingId=zV4sJQyNyQg%2FS%2BYm6Ba9Eg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K12" s="36" t="inlineStr">
+      <c r="K12" s="39" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L12" s="36" t="inlineStr">
+      <c r="L12" s="39" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-engie-belgium-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M12" s="36" t="inlineStr"/>
+      <c r="M12" s="39" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="A13" s="39" t="inlineStr">
         <is>
           <t>linkedin_4390725142</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="39" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C13" s="36" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D13" s="36" t="inlineStr">
+      <c r="C13" s="39" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D13" s="39" t="inlineStr">
         <is>
           <t>Boston Consulting Group (BCG)</t>
         </is>
       </c>
-      <c r="E13" s="36" t="inlineStr">
+      <c r="E13" s="39" t="inlineStr">
         <is>
           <t>Forward Deployed AI Engineer, Internship, United Kingdom - BCG X</t>
         </is>
       </c>
-      <c r="F13" s="36" t="inlineStr">
+      <c r="F13" s="39" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G13" s="36" t="inlineStr">
+      <c r="G13" s="39" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H13" s="36" t="inlineStr">
+      <c r="H13" s="39" t="inlineStr">
         <is>
           <t>2026-04-16 16:24 UTC</t>
         </is>
       </c>
-      <c r="I13" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J13" s="38" t="inlineStr">
+      <c r="I13" s="40" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J13" s="41" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/forward-deployed-ai-engineer-internship-united-kingdom-bcg-x-at-boston-consulting-group-bcg-4390725142?refId=YHAZO5vAx9Qtg1RXMma%2F%2BA%3D%3D&amp;trackingId=E8kiSHzcdYe%2FH6s%2FCkGtMw%3D%3D&amp;position=7&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K13" s="36" t="inlineStr">
+      <c r="K13" s="39" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L13" s="36" t="inlineStr">
+      <c r="L13" s="39" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-boston-consulting-group-bcg-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M13" s="36" t="inlineStr"/>
+      <c r="M13" s="39" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="inlineStr">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>linkedin_4400428064</t>
         </is>
       </c>
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C14" s="36" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D14" s="36" t="inlineStr">
+      <c r="C14" s="39" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D14" s="39" t="inlineStr">
         <is>
           <t>Fanatics</t>
         </is>
       </c>
-      <c r="E14" s="36" t="inlineStr">
+      <c r="E14" s="39" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="F14" s="36" t="inlineStr">
+      <c r="F14" s="39" t="inlineStr">
         <is>
           <t>London, England, United Kingdom</t>
         </is>
       </c>
-      <c r="G14" s="36" t="inlineStr">
+      <c r="G14" s="39" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H14" s="36" t="inlineStr">
+      <c r="H14" s="39" t="inlineStr">
         <is>
           <t>2026-04-16 16:16 UTC</t>
         </is>
       </c>
-      <c r="I14" s="37" t="inlineStr">
-        <is>
-          <t>Waiting to apply</t>
-        </is>
-      </c>
-      <c r="J14" s="38" t="inlineStr">
+      <c r="I14" s="40" t="inlineStr">
+        <is>
+          <t>Waiting to apply</t>
+        </is>
+      </c>
+      <c r="J14" s="41" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/jobs/view/data-scientist-at-fanatics-4400428064?refId=SNMwEp9%2FBozAkX4FBnhJwQ%3D%3D&amp;trackingId=cAX0aKWV%2FBX1fvQzm%2FkEMg%3D%3D&amp;position=1&amp;pageNum=0</t>
         </is>
       </c>
-      <c r="K14" s="36" t="inlineStr">
+      <c r="K14" s="39" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/resumes/cv-aymane-ait-dads-fanatics-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="L14" s="36" t="inlineStr">
+      <c r="L14" s="39" t="inlineStr">
         <is>
           <t>/home/runner/work/career-ops/career-ops/cover_letters/cover-aymane-ait-dads-fanatics-2026-04-16.pdf</t>
         </is>
       </c>
-      <c r="M14" s="36" t="inlineStr"/>
+      <c r="M14" s="39" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="A15" s="39" t="inlineStr">
         <is>
           <t>linkedin_4390730090</t>
         </is>
       </c>
-      <c r="B15" s="36" t="inlineStr">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t>2026-04-16 20:37</t>
         </is>
       </c>
-      <c r="C15" s="36" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D15" s="36" t="inlineStr">
+      <c r="C15" s="39" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D15" s="39" t="inlineStr">
         <is>
           <t>Boston Consulting Group 